--- a/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
@@ -502,14 +502,14 @@
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Реестр взаиморасчётов</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Одна строка — одна операция. Начисления вводите положительными суммами, оплаты и зачёты — тоже положительными: знак ставит тип операции. Каждая операция, влияющая на долг, относится к конкретному акту: идентификатор акта в колонке F должен совпадать со строкой листа «Долг по актам». Система не распределяет платежи между актами сама — очередность зачёта определяется назначением платежа и договором, и правовой вывод за вас никто не делает. Строк 500; записи ниже таблицы блокируют итог, а не отбрасываются.</t>
@@ -13664,8 +13664,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="L15:M20"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C5:C504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
@@ -13691,7 +13693,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -13703,14 +13705,14 @@
     <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Долг по актам: что переносить в расчёт процентов</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="33" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Одна строка — один акт (или часть долга) со своим сроком оплаты. Начисления, оплаты и зачёты берутся из листа «Взаиморасчёты» по идентификатору акта. Колонка H — долг на первый день просрочки: он нужен файлу 08, лист «Акты». Колонка J — текущий остаток: он нужен там же для сверки, но не как сумма долга. Оплаты, поступившие в первый день просрочки и позже, переносятся в файл 08, лист «Оплаты», с тем же идентификатором акта.</t>
@@ -15025,6 +15027,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -15052,14 +15058,14 @@
     <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Реестр передачи документов и доказательств передачи</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="33" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Одна строка — одно ваше отправление: уведомление, претензия, копия иска. Без доказательства направления документ для спора считается ненаправленным. Порядок — файл 07. Входящие документы заказчика (гарантийное письмо, ответ, возражения, акт сверки) сюда не вносятся: их отметка — в файле 02, «Контроль ответа», и строкой в «Реестре приложений».</t>
@@ -20535,6 +20541,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>"Нарочно с отметкой о получении,Почта: ценное письмо с описью и уведомлением,ЭДО,Электронная почта по договору,Курьерская служба с описью"</formula1>
@@ -20565,14 +20575,14 @@
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Реестр приложений к претензии и иску</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Что прикладывается, в каком виде и где лежит. Из этого реестра собирается список приложений претензии (файл 09) и иска (файл 10). Входящие документы заказчика — гарантийное письмо, протокол или соглашение, подписанный им акт сверки, возражения — вносятся сюда же: отдельного реестра входящих нет.</t>
@@ -21360,6 +21370,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="E5:E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
       <formula1>"Копия,Оригинал,Электронный образ"</formula1>

--- a/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="J5" s="5">
-        <f>G5</f>
+        <f>IF(AND(B5="",C5="",E5=""),"",SUM($G$5:G5))</f>
         <v/>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="J6" s="5">
-        <f>J5+G6</f>
+        <f>IF(AND(B6="",C6="",E6=""),"",SUM($G$5:G6))</f>
         <v/>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="J7" s="5">
-        <f>J6+G7</f>
+        <f>IF(AND(B7="",C7="",E7=""),"",SUM($G$5:G7))</f>
         <v/>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="J8" s="5">
-        <f>J7+G8</f>
+        <f>IF(AND(B8="",C8="",E8=""),"",SUM($G$5:G8))</f>
         <v/>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -739,7 +739,7 @@
         <v/>
       </c>
       <c r="J9" s="5">
-        <f>J8+G9</f>
+        <f>IF(AND(B9="",C9="",E9=""),"",SUM($G$5:G9))</f>
         <v/>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
         <v/>
       </c>
       <c r="J10" s="5">
-        <f>J9+G10</f>
+        <f>IF(AND(B10="",C10="",E10=""),"",SUM($G$5:G10))</f>
         <v/>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -809,7 +809,7 @@
         <v/>
       </c>
       <c r="J11" s="5">
-        <f>J10+G11</f>
+        <f>IF(AND(B11="",C11="",E11=""),"",SUM($G$5:G11))</f>
         <v/>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -844,7 +844,7 @@
         <v/>
       </c>
       <c r="J12" s="5">
-        <f>J11+G12</f>
+        <f>IF(AND(B12="",C12="",E12=""),"",SUM($G$5:G12))</f>
         <v/>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -879,7 +879,7 @@
         <v/>
       </c>
       <c r="J13" s="5">
-        <f>J12+G13</f>
+        <f>IF(AND(B13="",C13="",E13=""),"",SUM($G$5:G13))</f>
         <v/>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
         <v/>
       </c>
       <c r="J14" s="5">
-        <f>J13+G14</f>
+        <f>IF(AND(B14="",C14="",E14=""),"",SUM($G$5:G14))</f>
         <v/>
       </c>
     </row>
@@ -940,7 +940,7 @@
         <v/>
       </c>
       <c r="J15" s="5">
-        <f>J14+G15</f>
+        <f>IF(AND(B15="",C15="",E15=""),"",SUM($G$5:G15))</f>
         <v/>
       </c>
       <c r="L15" s="10" t="inlineStr">
@@ -971,7 +971,7 @@
         <v/>
       </c>
       <c r="J16" s="5">
-        <f>J15+G16</f>
+        <f>IF(AND(B16="",C16="",E16=""),"",SUM($G$5:G16))</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
         <v/>
       </c>
       <c r="J17" s="5">
-        <f>J16+G17</f>
+        <f>IF(AND(B17="",C17="",E17=""),"",SUM($G$5:G17))</f>
         <v/>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         <v/>
       </c>
       <c r="J18" s="5">
-        <f>J17+G18</f>
+        <f>IF(AND(B18="",C18="",E18=""),"",SUM($G$5:G18))</f>
         <v/>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="J19" s="5">
-        <f>J18+G19</f>
+        <f>IF(AND(B19="",C19="",E19=""),"",SUM($G$5:G19))</f>
         <v/>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="J20" s="5">
-        <f>J19+G20</f>
+        <f>IF(AND(B20="",C20="",E20=""),"",SUM($G$5:G20))</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
         <v/>
       </c>
       <c r="J21" s="5">
-        <f>J20+G21</f>
+        <f>IF(AND(B21="",C21="",E21=""),"",SUM($G$5:G21))</f>
         <v/>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="J22" s="5">
-        <f>J21+G22</f>
+        <f>IF(AND(B22="",C22="",E22=""),"",SUM($G$5:G22))</f>
         <v/>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         <v/>
       </c>
       <c r="J23" s="5">
-        <f>J22+G23</f>
+        <f>IF(AND(B23="",C23="",E23=""),"",SUM($G$5:G23))</f>
         <v/>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="J24" s="5">
-        <f>J23+G24</f>
+        <f>IF(AND(B24="",C24="",E24=""),"",SUM($G$5:G24))</f>
         <v/>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
         <v/>
       </c>
       <c r="J25" s="5">
-        <f>J24+G25</f>
+        <f>IF(AND(B25="",C25="",E25=""),"",SUM($G$5:G25))</f>
         <v/>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v/>
       </c>
       <c r="J26" s="5">
-        <f>J25+G26</f>
+        <f>IF(AND(B26="",C26="",E26=""),"",SUM($G$5:G26))</f>
         <v/>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="J27" s="5">
-        <f>J26+G27</f>
+        <f>IF(AND(B27="",C27="",E27=""),"",SUM($G$5:G27))</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
         <v/>
       </c>
       <c r="J28" s="5">
-        <f>J27+G28</f>
+        <f>IF(AND(B28="",C28="",E28=""),"",SUM($G$5:G28))</f>
         <v/>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
         <v/>
       </c>
       <c r="J29" s="5">
-        <f>J28+G29</f>
+        <f>IF(AND(B29="",C29="",E29=""),"",SUM($G$5:G29))</f>
         <v/>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
         <v/>
       </c>
       <c r="J30" s="5">
-        <f>J29+G30</f>
+        <f>IF(AND(B30="",C30="",E30=""),"",SUM($G$5:G30))</f>
         <v/>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
         <v/>
       </c>
       <c r="J31" s="5">
-        <f>J30+G31</f>
+        <f>IF(AND(B31="",C31="",E31=""),"",SUM($G$5:G31))</f>
         <v/>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
       <c r="J32" s="5">
-        <f>J31+G32</f>
+        <f>IF(AND(B32="",C32="",E32=""),"",SUM($G$5:G32))</f>
         <v/>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v/>
       </c>
       <c r="J33" s="5">
-        <f>J32+G33</f>
+        <f>IF(AND(B33="",C33="",E33=""),"",SUM($G$5:G33))</f>
         <v/>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="J34" s="5">
-        <f>J33+G34</f>
+        <f>IF(AND(B34="",C34="",E34=""),"",SUM($G$5:G34))</f>
         <v/>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         <v/>
       </c>
       <c r="J35" s="5">
-        <f>J34+G35</f>
+        <f>IF(AND(B35="",C35="",E35=""),"",SUM($G$5:G35))</f>
         <v/>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         <v/>
       </c>
       <c r="J36" s="5">
-        <f>J35+G36</f>
+        <f>IF(AND(B36="",C36="",E36=""),"",SUM($G$5:G36))</f>
         <v/>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="J37" s="5">
-        <f>J36+G37</f>
+        <f>IF(AND(B37="",C37="",E37=""),"",SUM($G$5:G37))</f>
         <v/>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="J38" s="5">
-        <f>J37+G38</f>
+        <f>IF(AND(B38="",C38="",E38=""),"",SUM($G$5:G38))</f>
         <v/>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="J39" s="5">
-        <f>J38+G39</f>
+        <f>IF(AND(B39="",C39="",E39=""),"",SUM($G$5:G39))</f>
         <v/>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
         <v/>
       </c>
       <c r="J40" s="5">
-        <f>J39+G40</f>
+        <f>IF(AND(B40="",C40="",E40=""),"",SUM($G$5:G40))</f>
         <v/>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         <v/>
       </c>
       <c r="J41" s="5">
-        <f>J40+G41</f>
+        <f>IF(AND(B41="",C41="",E41=""),"",SUM($G$5:G41))</f>
         <v/>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
       <c r="J42" s="5">
-        <f>J41+G42</f>
+        <f>IF(AND(B42="",C42="",E42=""),"",SUM($G$5:G42))</f>
         <v/>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="J43" s="5">
-        <f>J42+G43</f>
+        <f>IF(AND(B43="",C43="",E43=""),"",SUM($G$5:G43))</f>
         <v/>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v/>
       </c>
       <c r="J44" s="5">
-        <f>J43+G44</f>
+        <f>IF(AND(B44="",C44="",E44=""),"",SUM($G$5:G44))</f>
         <v/>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
         <v/>
       </c>
       <c r="J45" s="5">
-        <f>J44+G45</f>
+        <f>IF(AND(B45="",C45="",E45=""),"",SUM($G$5:G45))</f>
         <v/>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v/>
       </c>
       <c r="J46" s="5">
-        <f>J45+G46</f>
+        <f>IF(AND(B46="",C46="",E46=""),"",SUM($G$5:G46))</f>
         <v/>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         <v/>
       </c>
       <c r="J47" s="5">
-        <f>J46+G47</f>
+        <f>IF(AND(B47="",C47="",E47=""),"",SUM($G$5:G47))</f>
         <v/>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         <v/>
       </c>
       <c r="J48" s="5">
-        <f>J47+G48</f>
+        <f>IF(AND(B48="",C48="",E48=""),"",SUM($G$5:G48))</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
         <v/>
       </c>
       <c r="J49" s="5">
-        <f>J48+G49</f>
+        <f>IF(AND(B49="",C49="",E49=""),"",SUM($G$5:G49))</f>
         <v/>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J50" s="5">
-        <f>J49+G50</f>
+        <f>IF(AND(B50="",C50="",E50=""),"",SUM($G$5:G50))</f>
         <v/>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="J51" s="5">
-        <f>J50+G51</f>
+        <f>IF(AND(B51="",C51="",E51=""),"",SUM($G$5:G51))</f>
         <v/>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
         <v/>
       </c>
       <c r="J52" s="5">
-        <f>J51+G52</f>
+        <f>IF(AND(B52="",C52="",E52=""),"",SUM($G$5:G52))</f>
         <v/>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="J53" s="5">
-        <f>J52+G53</f>
+        <f>IF(AND(B53="",C53="",E53=""),"",SUM($G$5:G53))</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v/>
       </c>
       <c r="J54" s="5">
-        <f>J53+G54</f>
+        <f>IF(AND(B54="",C54="",E54=""),"",SUM($G$5:G54))</f>
         <v/>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
         <v/>
       </c>
       <c r="J55" s="5">
-        <f>J54+G55</f>
+        <f>IF(AND(B55="",C55="",E55=""),"",SUM($G$5:G55))</f>
         <v/>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="J56" s="5">
-        <f>J55+G56</f>
+        <f>IF(AND(B56="",C56="",E56=""),"",SUM($G$5:G56))</f>
         <v/>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         <v/>
       </c>
       <c r="J57" s="5">
-        <f>J56+G57</f>
+        <f>IF(AND(B57="",C57="",E57=""),"",SUM($G$5:G57))</f>
         <v/>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         <v/>
       </c>
       <c r="J58" s="5">
-        <f>J57+G58</f>
+        <f>IF(AND(B58="",C58="",E58=""),"",SUM($G$5:G58))</f>
         <v/>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="J59" s="5">
-        <f>J58+G59</f>
+        <f>IF(AND(B59="",C59="",E59=""),"",SUM($G$5:G59))</f>
         <v/>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         <v/>
       </c>
       <c r="J60" s="5">
-        <f>J59+G60</f>
+        <f>IF(AND(B60="",C60="",E60=""),"",SUM($G$5:G60))</f>
         <v/>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
         <v/>
       </c>
       <c r="J61" s="5">
-        <f>J60+G61</f>
+        <f>IF(AND(B61="",C61="",E61=""),"",SUM($G$5:G61))</f>
         <v/>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="J62" s="5">
-        <f>J61+G62</f>
+        <f>IF(AND(B62="",C62="",E62=""),"",SUM($G$5:G62))</f>
         <v/>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
         <v/>
       </c>
       <c r="J63" s="5">
-        <f>J62+G63</f>
+        <f>IF(AND(B63="",C63="",E63=""),"",SUM($G$5:G63))</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v/>
       </c>
       <c r="J64" s="5">
-        <f>J63+G64</f>
+        <f>IF(AND(B64="",C64="",E64=""),"",SUM($G$5:G64))</f>
         <v/>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
         <v/>
       </c>
       <c r="J65" s="5">
-        <f>J64+G65</f>
+        <f>IF(AND(B65="",C65="",E65=""),"",SUM($G$5:G65))</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v/>
       </c>
       <c r="J66" s="5">
-        <f>J65+G66</f>
+        <f>IF(AND(B66="",C66="",E66=""),"",SUM($G$5:G66))</f>
         <v/>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
         <v/>
       </c>
       <c r="J67" s="5">
-        <f>J66+G67</f>
+        <f>IF(AND(B67="",C67="",E67=""),"",SUM($G$5:G67))</f>
         <v/>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
         <v/>
       </c>
       <c r="J68" s="5">
-        <f>J67+G68</f>
+        <f>IF(AND(B68="",C68="",E68=""),"",SUM($G$5:G68))</f>
         <v/>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="J69" s="5">
-        <f>J68+G69</f>
+        <f>IF(AND(B69="",C69="",E69=""),"",SUM($G$5:G69))</f>
         <v/>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v/>
       </c>
       <c r="J70" s="5">
-        <f>J69+G70</f>
+        <f>IF(AND(B70="",C70="",E70=""),"",SUM($G$5:G70))</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v/>
       </c>
       <c r="J71" s="5">
-        <f>J70+G71</f>
+        <f>IF(AND(B71="",C71="",E71=""),"",SUM($G$5:G71))</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="J72" s="5">
-        <f>J71+G72</f>
+        <f>IF(AND(B72="",C72="",E72=""),"",SUM($G$5:G72))</f>
         <v/>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="J73" s="5">
-        <f>J72+G73</f>
+        <f>IF(AND(B73="",C73="",E73=""),"",SUM($G$5:G73))</f>
         <v/>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
         <v/>
       </c>
       <c r="J74" s="5">
-        <f>J73+G74</f>
+        <f>IF(AND(B74="",C74="",E74=""),"",SUM($G$5:G74))</f>
         <v/>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
         <v/>
       </c>
       <c r="J75" s="5">
-        <f>J74+G75</f>
+        <f>IF(AND(B75="",C75="",E75=""),"",SUM($G$5:G75))</f>
         <v/>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
         <v/>
       </c>
       <c r="J76" s="5">
-        <f>J75+G76</f>
+        <f>IF(AND(B76="",C76="",E76=""),"",SUM($G$5:G76))</f>
         <v/>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
         <v/>
       </c>
       <c r="J77" s="5">
-        <f>J76+G77</f>
+        <f>IF(AND(B77="",C77="",E77=""),"",SUM($G$5:G77))</f>
         <v/>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
         <v/>
       </c>
       <c r="J78" s="5">
-        <f>J77+G78</f>
+        <f>IF(AND(B78="",C78="",E78=""),"",SUM($G$5:G78))</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v/>
       </c>
       <c r="J79" s="5">
-        <f>J78+G79</f>
+        <f>IF(AND(B79="",C79="",E79=""),"",SUM($G$5:G79))</f>
         <v/>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         <v/>
       </c>
       <c r="J80" s="5">
-        <f>J79+G80</f>
+        <f>IF(AND(B80="",C80="",E80=""),"",SUM($G$5:G80))</f>
         <v/>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="J81" s="5">
-        <f>J80+G81</f>
+        <f>IF(AND(B81="",C81="",E81=""),"",SUM($G$5:G81))</f>
         <v/>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
         <v/>
       </c>
       <c r="J82" s="5">
-        <f>J81+G82</f>
+        <f>IF(AND(B82="",C82="",E82=""),"",SUM($G$5:G82))</f>
         <v/>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
         <v/>
       </c>
       <c r="J83" s="5">
-        <f>J82+G83</f>
+        <f>IF(AND(B83="",C83="",E83=""),"",SUM($G$5:G83))</f>
         <v/>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v/>
       </c>
       <c r="J84" s="5">
-        <f>J83+G84</f>
+        <f>IF(AND(B84="",C84="",E84=""),"",SUM($G$5:G84))</f>
         <v/>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         <v/>
       </c>
       <c r="J85" s="5">
-        <f>J84+G85</f>
+        <f>IF(AND(B85="",C85="",E85=""),"",SUM($G$5:G85))</f>
         <v/>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
         <v/>
       </c>
       <c r="J86" s="5">
-        <f>J85+G86</f>
+        <f>IF(AND(B86="",C86="",E86=""),"",SUM($G$5:G86))</f>
         <v/>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="J87" s="5">
-        <f>J86+G87</f>
+        <f>IF(AND(B87="",C87="",E87=""),"",SUM($G$5:G87))</f>
         <v/>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
         <v/>
       </c>
       <c r="J88" s="5">
-        <f>J87+G88</f>
+        <f>IF(AND(B88="",C88="",E88=""),"",SUM($G$5:G88))</f>
         <v/>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
         <v/>
       </c>
       <c r="J89" s="5">
-        <f>J88+G89</f>
+        <f>IF(AND(B89="",C89="",E89=""),"",SUM($G$5:G89))</f>
         <v/>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="J90" s="5">
-        <f>J89+G90</f>
+        <f>IF(AND(B90="",C90="",E90=""),"",SUM($G$5:G90))</f>
         <v/>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="J91" s="5">
-        <f>J90+G91</f>
+        <f>IF(AND(B91="",C91="",E91=""),"",SUM($G$5:G91))</f>
         <v/>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
         <v/>
       </c>
       <c r="J92" s="5">
-        <f>J91+G92</f>
+        <f>IF(AND(B92="",C92="",E92=""),"",SUM($G$5:G92))</f>
         <v/>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
         <v/>
       </c>
       <c r="J93" s="5">
-        <f>J92+G93</f>
+        <f>IF(AND(B93="",C93="",E93=""),"",SUM($G$5:G93))</f>
         <v/>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
         <v/>
       </c>
       <c r="J94" s="5">
-        <f>J93+G94</f>
+        <f>IF(AND(B94="",C94="",E94=""),"",SUM($G$5:G94))</f>
         <v/>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v/>
       </c>
       <c r="J95" s="5">
-        <f>J94+G95</f>
+        <f>IF(AND(B95="",C95="",E95=""),"",SUM($G$5:G95))</f>
         <v/>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
         <v/>
       </c>
       <c r="J96" s="5">
-        <f>J95+G96</f>
+        <f>IF(AND(B96="",C96="",E96=""),"",SUM($G$5:G96))</f>
         <v/>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="J97" s="5">
-        <f>J96+G97</f>
+        <f>IF(AND(B97="",C97="",E97=""),"",SUM($G$5:G97))</f>
         <v/>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v/>
       </c>
       <c r="J98" s="5">
-        <f>J97+G98</f>
+        <f>IF(AND(B98="",C98="",E98=""),"",SUM($G$5:G98))</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J99" s="5">
-        <f>J98+G99</f>
+        <f>IF(AND(B99="",C99="",E99=""),"",SUM($G$5:G99))</f>
         <v/>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="J100" s="5">
-        <f>J99+G100</f>
+        <f>IF(AND(B100="",C100="",E100=""),"",SUM($G$5:G100))</f>
         <v/>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
         <v/>
       </c>
       <c r="J101" s="5">
-        <f>J100+G101</f>
+        <f>IF(AND(B101="",C101="",E101=""),"",SUM($G$5:G101))</f>
         <v/>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
         <v/>
       </c>
       <c r="J102" s="5">
-        <f>J101+G102</f>
+        <f>IF(AND(B102="",C102="",E102=""),"",SUM($G$5:G102))</f>
         <v/>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
         <v/>
       </c>
       <c r="J103" s="5">
-        <f>J102+G103</f>
+        <f>IF(AND(B103="",C103="",E103=""),"",SUM($G$5:G103))</f>
         <v/>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
         <v/>
       </c>
       <c r="J104" s="5">
-        <f>J103+G104</f>
+        <f>IF(AND(B104="",C104="",E104=""),"",SUM($G$5:G104))</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v/>
       </c>
       <c r="J105" s="5">
-        <f>J104+G105</f>
+        <f>IF(AND(B105="",C105="",E105=""),"",SUM($G$5:G105))</f>
         <v/>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
         <v/>
       </c>
       <c r="J106" s="5">
-        <f>J105+G106</f>
+        <f>IF(AND(B106="",C106="",E106=""),"",SUM($G$5:G106))</f>
         <v/>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="J107" s="5">
-        <f>J106+G107</f>
+        <f>IF(AND(B107="",C107="",E107=""),"",SUM($G$5:G107))</f>
         <v/>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         <v/>
       </c>
       <c r="J108" s="5">
-        <f>J107+G108</f>
+        <f>IF(AND(B108="",C108="",E108=""),"",SUM($G$5:G108))</f>
         <v/>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
         <v/>
       </c>
       <c r="J109" s="5">
-        <f>J108+G109</f>
+        <f>IF(AND(B109="",C109="",E109=""),"",SUM($G$5:G109))</f>
         <v/>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="J110" s="5">
-        <f>J109+G110</f>
+        <f>IF(AND(B110="",C110="",E110=""),"",SUM($G$5:G110))</f>
         <v/>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
         <v/>
       </c>
       <c r="J111" s="5">
-        <f>J110+G111</f>
+        <f>IF(AND(B111="",C111="",E111=""),"",SUM($G$5:G111))</f>
         <v/>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
         <v/>
       </c>
       <c r="J112" s="5">
-        <f>J111+G112</f>
+        <f>IF(AND(B112="",C112="",E112=""),"",SUM($G$5:G112))</f>
         <v/>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
         <v/>
       </c>
       <c r="J113" s="5">
-        <f>J112+G113</f>
+        <f>IF(AND(B113="",C113="",E113=""),"",SUM($G$5:G113))</f>
         <v/>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
         <v/>
       </c>
       <c r="J114" s="5">
-        <f>J113+G114</f>
+        <f>IF(AND(B114="",C114="",E114=""),"",SUM($G$5:G114))</f>
         <v/>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
         <v/>
       </c>
       <c r="J115" s="5">
-        <f>J114+G115</f>
+        <f>IF(AND(B115="",C115="",E115=""),"",SUM($G$5:G115))</f>
         <v/>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
         <v/>
       </c>
       <c r="J116" s="5">
-        <f>J115+G116</f>
+        <f>IF(AND(B116="",C116="",E116=""),"",SUM($G$5:G116))</f>
         <v/>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
         <v/>
       </c>
       <c r="J117" s="5">
-        <f>J116+G117</f>
+        <f>IF(AND(B117="",C117="",E117=""),"",SUM($G$5:G117))</f>
         <v/>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
         <v/>
       </c>
       <c r="J118" s="5">
-        <f>J117+G118</f>
+        <f>IF(AND(B118="",C118="",E118=""),"",SUM($G$5:G118))</f>
         <v/>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="J119" s="5">
-        <f>J118+G119</f>
+        <f>IF(AND(B119="",C119="",E119=""),"",SUM($G$5:G119))</f>
         <v/>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v/>
       </c>
       <c r="J120" s="5">
-        <f>J119+G120</f>
+        <f>IF(AND(B120="",C120="",E120=""),"",SUM($G$5:G120))</f>
         <v/>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
         <v/>
       </c>
       <c r="J121" s="5">
-        <f>J120+G121</f>
+        <f>IF(AND(B121="",C121="",E121=""),"",SUM($G$5:G121))</f>
         <v/>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         <v/>
       </c>
       <c r="J122" s="5">
-        <f>J121+G122</f>
+        <f>IF(AND(B122="",C122="",E122=""),"",SUM($G$5:G122))</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
         <v/>
       </c>
       <c r="J123" s="5">
-        <f>J122+G123</f>
+        <f>IF(AND(B123="",C123="",E123=""),"",SUM($G$5:G123))</f>
         <v/>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="J124" s="5">
-        <f>J123+G124</f>
+        <f>IF(AND(B124="",C124="",E124=""),"",SUM($G$5:G124))</f>
         <v/>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
         <v/>
       </c>
       <c r="J125" s="5">
-        <f>J124+G125</f>
+        <f>IF(AND(B125="",C125="",E125=""),"",SUM($G$5:G125))</f>
         <v/>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
         <v/>
       </c>
       <c r="J126" s="5">
-        <f>J125+G126</f>
+        <f>IF(AND(B126="",C126="",E126=""),"",SUM($G$5:G126))</f>
         <v/>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
         <v/>
       </c>
       <c r="J127" s="5">
-        <f>J126+G127</f>
+        <f>IF(AND(B127="",C127="",E127=""),"",SUM($G$5:G127))</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v/>
       </c>
       <c r="J128" s="5">
-        <f>J127+G128</f>
+        <f>IF(AND(B128="",C128="",E128=""),"",SUM($G$5:G128))</f>
         <v/>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="J129" s="5">
-        <f>J128+G129</f>
+        <f>IF(AND(B129="",C129="",E129=""),"",SUM($G$5:G129))</f>
         <v/>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v/>
       </c>
       <c r="J130" s="5">
-        <f>J129+G130</f>
+        <f>IF(AND(B130="",C130="",E130=""),"",SUM($G$5:G130))</f>
         <v/>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
         <v/>
       </c>
       <c r="J131" s="5">
-        <f>J130+G131</f>
+        <f>IF(AND(B131="",C131="",E131=""),"",SUM($G$5:G131))</f>
         <v/>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
         <v/>
       </c>
       <c r="J132" s="5">
-        <f>J131+G132</f>
+        <f>IF(AND(B132="",C132="",E132=""),"",SUM($G$5:G132))</f>
         <v/>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
         <v/>
       </c>
       <c r="J133" s="5">
-        <f>J132+G133</f>
+        <f>IF(AND(B133="",C133="",E133=""),"",SUM($G$5:G133))</f>
         <v/>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
         <v/>
       </c>
       <c r="J134" s="5">
-        <f>J133+G134</f>
+        <f>IF(AND(B134="",C134="",E134=""),"",SUM($G$5:G134))</f>
         <v/>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
         <v/>
       </c>
       <c r="J135" s="5">
-        <f>J134+G135</f>
+        <f>IF(AND(B135="",C135="",E135=""),"",SUM($G$5:G135))</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v/>
       </c>
       <c r="J136" s="5">
-        <f>J135+G136</f>
+        <f>IF(AND(B136="",C136="",E136=""),"",SUM($G$5:G136))</f>
         <v/>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
         <v/>
       </c>
       <c r="J137" s="5">
-        <f>J136+G137</f>
+        <f>IF(AND(B137="",C137="",E137=""),"",SUM($G$5:G137))</f>
         <v/>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="J138" s="5">
-        <f>J137+G138</f>
+        <f>IF(AND(B138="",C138="",E138=""),"",SUM($G$5:G138))</f>
         <v/>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
         <v/>
       </c>
       <c r="J139" s="5">
-        <f>J138+G139</f>
+        <f>IF(AND(B139="",C139="",E139=""),"",SUM($G$5:G139))</f>
         <v/>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="J140" s="5">
-        <f>J139+G140</f>
+        <f>IF(AND(B140="",C140="",E140=""),"",SUM($G$5:G140))</f>
         <v/>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="J141" s="5">
-        <f>J140+G141</f>
+        <f>IF(AND(B141="",C141="",E141=""),"",SUM($G$5:G141))</f>
         <v/>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
         <v/>
       </c>
       <c r="J142" s="5">
-        <f>J141+G142</f>
+        <f>IF(AND(B142="",C142="",E142=""),"",SUM($G$5:G142))</f>
         <v/>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v/>
       </c>
       <c r="J143" s="5">
-        <f>J142+G143</f>
+        <f>IF(AND(B143="",C143="",E143=""),"",SUM($G$5:G143))</f>
         <v/>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
         <v/>
       </c>
       <c r="J144" s="5">
-        <f>J143+G144</f>
+        <f>IF(AND(B144="",C144="",E144=""),"",SUM($G$5:G144))</f>
         <v/>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
         <v/>
       </c>
       <c r="J145" s="5">
-        <f>J144+G145</f>
+        <f>IF(AND(B145="",C145="",E145=""),"",SUM($G$5:G145))</f>
         <v/>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
         <v/>
       </c>
       <c r="J146" s="5">
-        <f>J145+G146</f>
+        <f>IF(AND(B146="",C146="",E146=""),"",SUM($G$5:G146))</f>
         <v/>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
         <v/>
       </c>
       <c r="J147" s="5">
-        <f>J146+G147</f>
+        <f>IF(AND(B147="",C147="",E147=""),"",SUM($G$5:G147))</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J148" s="5">
-        <f>J147+G148</f>
+        <f>IF(AND(B148="",C148="",E148=""),"",SUM($G$5:G148))</f>
         <v/>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
         <v/>
       </c>
       <c r="J149" s="5">
-        <f>J148+G149</f>
+        <f>IF(AND(B149="",C149="",E149=""),"",SUM($G$5:G149))</f>
         <v/>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v/>
       </c>
       <c r="J150" s="5">
-        <f>J149+G150</f>
+        <f>IF(AND(B150="",C150="",E150=""),"",SUM($G$5:G150))</f>
         <v/>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
         <v/>
       </c>
       <c r="J151" s="5">
-        <f>J150+G151</f>
+        <f>IF(AND(B151="",C151="",E151=""),"",SUM($G$5:G151))</f>
         <v/>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
         <v/>
       </c>
       <c r="J152" s="5">
-        <f>J151+G152</f>
+        <f>IF(AND(B152="",C152="",E152=""),"",SUM($G$5:G152))</f>
         <v/>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         <v/>
       </c>
       <c r="J153" s="5">
-        <f>J152+G153</f>
+        <f>IF(AND(B153="",C153="",E153=""),"",SUM($G$5:G153))</f>
         <v/>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
         <v/>
       </c>
       <c r="J154" s="5">
-        <f>J153+G154</f>
+        <f>IF(AND(B154="",C154="",E154=""),"",SUM($G$5:G154))</f>
         <v/>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
         <v/>
       </c>
       <c r="J155" s="5">
-        <f>J154+G155</f>
+        <f>IF(AND(B155="",C155="",E155=""),"",SUM($G$5:G155))</f>
         <v/>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="J156" s="5">
-        <f>J155+G156</f>
+        <f>IF(AND(B156="",C156="",E156=""),"",SUM($G$5:G156))</f>
         <v/>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         <v/>
       </c>
       <c r="J157" s="5">
-        <f>J156+G157</f>
+        <f>IF(AND(B157="",C157="",E157=""),"",SUM($G$5:G157))</f>
         <v/>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
         <v/>
       </c>
       <c r="J158" s="5">
-        <f>J157+G158</f>
+        <f>IF(AND(B158="",C158="",E158=""),"",SUM($G$5:G158))</f>
         <v/>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
         <v/>
       </c>
       <c r="J159" s="5">
-        <f>J158+G159</f>
+        <f>IF(AND(B159="",C159="",E159=""),"",SUM($G$5:G159))</f>
         <v/>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
         <v/>
       </c>
       <c r="J160" s="5">
-        <f>J159+G160</f>
+        <f>IF(AND(B160="",C160="",E160=""),"",SUM($G$5:G160))</f>
         <v/>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
         <v/>
       </c>
       <c r="J161" s="5">
-        <f>J160+G161</f>
+        <f>IF(AND(B161="",C161="",E161=""),"",SUM($G$5:G161))</f>
         <v/>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
         <v/>
       </c>
       <c r="J162" s="5">
-        <f>J161+G162</f>
+        <f>IF(AND(B162="",C162="",E162=""),"",SUM($G$5:G162))</f>
         <v/>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
         <v/>
       </c>
       <c r="J163" s="5">
-        <f>J162+G163</f>
+        <f>IF(AND(B163="",C163="",E163=""),"",SUM($G$5:G163))</f>
         <v/>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
         <v/>
       </c>
       <c r="J164" s="5">
-        <f>J163+G164</f>
+        <f>IF(AND(B164="",C164="",E164=""),"",SUM($G$5:G164))</f>
         <v/>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
         <v/>
       </c>
       <c r="J165" s="5">
-        <f>J164+G165</f>
+        <f>IF(AND(B165="",C165="",E165=""),"",SUM($G$5:G165))</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
         <v/>
       </c>
       <c r="J166" s="5">
-        <f>J165+G166</f>
+        <f>IF(AND(B166="",C166="",E166=""),"",SUM($G$5:G166))</f>
         <v/>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
         <v/>
       </c>
       <c r="J167" s="5">
-        <f>J166+G167</f>
+        <f>IF(AND(B167="",C167="",E167=""),"",SUM($G$5:G167))</f>
         <v/>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
         <v/>
       </c>
       <c r="J168" s="5">
-        <f>J167+G168</f>
+        <f>IF(AND(B168="",C168="",E168=""),"",SUM($G$5:G168))</f>
         <v/>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
         <v/>
       </c>
       <c r="J169" s="5">
-        <f>J168+G169</f>
+        <f>IF(AND(B169="",C169="",E169=""),"",SUM($G$5:G169))</f>
         <v/>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
         <v/>
       </c>
       <c r="J170" s="5">
-        <f>J169+G170</f>
+        <f>IF(AND(B170="",C170="",E170=""),"",SUM($G$5:G170))</f>
         <v/>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         <v/>
       </c>
       <c r="J171" s="5">
-        <f>J170+G171</f>
+        <f>IF(AND(B171="",C171="",E171=""),"",SUM($G$5:G171))</f>
         <v/>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
         <v/>
       </c>
       <c r="J172" s="5">
-        <f>J171+G172</f>
+        <f>IF(AND(B172="",C172="",E172=""),"",SUM($G$5:G172))</f>
         <v/>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
         <v/>
       </c>
       <c r="J173" s="5">
-        <f>J172+G173</f>
+        <f>IF(AND(B173="",C173="",E173=""),"",SUM($G$5:G173))</f>
         <v/>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
         <v/>
       </c>
       <c r="J174" s="5">
-        <f>J173+G174</f>
+        <f>IF(AND(B174="",C174="",E174=""),"",SUM($G$5:G174))</f>
         <v/>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="J175" s="5">
-        <f>J174+G175</f>
+        <f>IF(AND(B175="",C175="",E175=""),"",SUM($G$5:G175))</f>
         <v/>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         <v/>
       </c>
       <c r="J176" s="5">
-        <f>J175+G176</f>
+        <f>IF(AND(B176="",C176="",E176=""),"",SUM($G$5:G176))</f>
         <v/>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
         <v/>
       </c>
       <c r="J177" s="5">
-        <f>J176+G177</f>
+        <f>IF(AND(B177="",C177="",E177=""),"",SUM($G$5:G177))</f>
         <v/>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
         <v/>
       </c>
       <c r="J178" s="5">
-        <f>J177+G178</f>
+        <f>IF(AND(B178="",C178="",E178=""),"",SUM($G$5:G178))</f>
         <v/>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
         <v/>
       </c>
       <c r="J179" s="5">
-        <f>J178+G179</f>
+        <f>IF(AND(B179="",C179="",E179=""),"",SUM($G$5:G179))</f>
         <v/>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
         <v/>
       </c>
       <c r="J180" s="5">
-        <f>J179+G180</f>
+        <f>IF(AND(B180="",C180="",E180=""),"",SUM($G$5:G180))</f>
         <v/>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
         <v/>
       </c>
       <c r="J181" s="5">
-        <f>J180+G181</f>
+        <f>IF(AND(B181="",C181="",E181=""),"",SUM($G$5:G181))</f>
         <v/>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
         <v/>
       </c>
       <c r="J182" s="5">
-        <f>J181+G182</f>
+        <f>IF(AND(B182="",C182="",E182=""),"",SUM($G$5:G182))</f>
         <v/>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
         <v/>
       </c>
       <c r="J183" s="5">
-        <f>J182+G183</f>
+        <f>IF(AND(B183="",C183="",E183=""),"",SUM($G$5:G183))</f>
         <v/>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
         <v/>
       </c>
       <c r="J184" s="5">
-        <f>J183+G184</f>
+        <f>IF(AND(B184="",C184="",E184=""),"",SUM($G$5:G184))</f>
         <v/>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
         <v/>
       </c>
       <c r="J185" s="5">
-        <f>J184+G185</f>
+        <f>IF(AND(B185="",C185="",E185=""),"",SUM($G$5:G185))</f>
         <v/>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
         <v/>
       </c>
       <c r="J186" s="5">
-        <f>J185+G186</f>
+        <f>IF(AND(B186="",C186="",E186=""),"",SUM($G$5:G186))</f>
         <v/>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
         <v/>
       </c>
       <c r="J187" s="5">
-        <f>J186+G187</f>
+        <f>IF(AND(B187="",C187="",E187=""),"",SUM($G$5:G187))</f>
         <v/>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v/>
       </c>
       <c r="J188" s="5">
-        <f>J187+G188</f>
+        <f>IF(AND(B188="",C188="",E188=""),"",SUM($G$5:G188))</f>
         <v/>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
         <v/>
       </c>
       <c r="J189" s="5">
-        <f>J188+G189</f>
+        <f>IF(AND(B189="",C189="",E189=""),"",SUM($G$5:G189))</f>
         <v/>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
         <v/>
       </c>
       <c r="J190" s="5">
-        <f>J189+G190</f>
+        <f>IF(AND(B190="",C190="",E190=""),"",SUM($G$5:G190))</f>
         <v/>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
         <v/>
       </c>
       <c r="J191" s="5">
-        <f>J190+G191</f>
+        <f>IF(AND(B191="",C191="",E191=""),"",SUM($G$5:G191))</f>
         <v/>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
         <v/>
       </c>
       <c r="J192" s="5">
-        <f>J191+G192</f>
+        <f>IF(AND(B192="",C192="",E192=""),"",SUM($G$5:G192))</f>
         <v/>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="J193" s="5">
-        <f>J192+G193</f>
+        <f>IF(AND(B193="",C193="",E193=""),"",SUM($G$5:G193))</f>
         <v/>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
         <v/>
       </c>
       <c r="J194" s="5">
-        <f>J193+G194</f>
+        <f>IF(AND(B194="",C194="",E194=""),"",SUM($G$5:G194))</f>
         <v/>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v/>
       </c>
       <c r="J195" s="5">
-        <f>J194+G195</f>
+        <f>IF(AND(B195="",C195="",E195=""),"",SUM($G$5:G195))</f>
         <v/>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
         <v/>
       </c>
       <c r="J196" s="5">
-        <f>J195+G196</f>
+        <f>IF(AND(B196="",C196="",E196=""),"",SUM($G$5:G196))</f>
         <v/>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J197" s="5">
-        <f>J196+G197</f>
+        <f>IF(AND(B197="",C197="",E197=""),"",SUM($G$5:G197))</f>
         <v/>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
         <v/>
       </c>
       <c r="J198" s="5">
-        <f>J197+G198</f>
+        <f>IF(AND(B198="",C198="",E198=""),"",SUM($G$5:G198))</f>
         <v/>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
         <v/>
       </c>
       <c r="J199" s="5">
-        <f>J198+G199</f>
+        <f>IF(AND(B199="",C199="",E199=""),"",SUM($G$5:G199))</f>
         <v/>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         <v/>
       </c>
       <c r="J200" s="5">
-        <f>J199+G200</f>
+        <f>IF(AND(B200="",C200="",E200=""),"",SUM($G$5:G200))</f>
         <v/>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
         <v/>
       </c>
       <c r="J201" s="5">
-        <f>J200+G201</f>
+        <f>IF(AND(B201="",C201="",E201=""),"",SUM($G$5:G201))</f>
         <v/>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v/>
       </c>
       <c r="J202" s="5">
-        <f>J201+G202</f>
+        <f>IF(AND(B202="",C202="",E202=""),"",SUM($G$5:G202))</f>
         <v/>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
         <v/>
       </c>
       <c r="J203" s="5">
-        <f>J202+G203</f>
+        <f>IF(AND(B203="",C203="",E203=""),"",SUM($G$5:G203))</f>
         <v/>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
         <v/>
       </c>
       <c r="J204" s="5">
-        <f>J203+G204</f>
+        <f>IF(AND(B204="",C204="",E204=""),"",SUM($G$5:G204))</f>
         <v/>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
         <v/>
       </c>
       <c r="J205" s="5">
-        <f>J204+G205</f>
+        <f>IF(AND(B205="",C205="",E205=""),"",SUM($G$5:G205))</f>
         <v/>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
         <v/>
       </c>
       <c r="J206" s="5">
-        <f>J205+G206</f>
+        <f>IF(AND(B206="",C206="",E206=""),"",SUM($G$5:G206))</f>
         <v/>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         <v/>
       </c>
       <c r="J207" s="5">
-        <f>J206+G207</f>
+        <f>IF(AND(B207="",C207="",E207=""),"",SUM($G$5:G207))</f>
         <v/>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
         <v/>
       </c>
       <c r="J208" s="5">
-        <f>J207+G208</f>
+        <f>IF(AND(B208="",C208="",E208=""),"",SUM($G$5:G208))</f>
         <v/>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
         <v/>
       </c>
       <c r="J209" s="5">
-        <f>J208+G209</f>
+        <f>IF(AND(B209="",C209="",E209=""),"",SUM($G$5:G209))</f>
         <v/>
       </c>
     </row>
@@ -6015,7 +6015,7 @@
         <v/>
       </c>
       <c r="J210" s="5">
-        <f>J209+G210</f>
+        <f>IF(AND(B210="",C210="",E210=""),"",SUM($G$5:G210))</f>
         <v/>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
         <v/>
       </c>
       <c r="J211" s="5">
-        <f>J210+G211</f>
+        <f>IF(AND(B211="",C211="",E211=""),"",SUM($G$5:G211))</f>
         <v/>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
         <v/>
       </c>
       <c r="J212" s="5">
-        <f>J211+G212</f>
+        <f>IF(AND(B212="",C212="",E212=""),"",SUM($G$5:G212))</f>
         <v/>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
         <v/>
       </c>
       <c r="J213" s="5">
-        <f>J212+G213</f>
+        <f>IF(AND(B213="",C213="",E213=""),"",SUM($G$5:G213))</f>
         <v/>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
         <v/>
       </c>
       <c r="J214" s="5">
-        <f>J213+G214</f>
+        <f>IF(AND(B214="",C214="",E214=""),"",SUM($G$5:G214))</f>
         <v/>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="J215" s="5">
-        <f>J214+G215</f>
+        <f>IF(AND(B215="",C215="",E215=""),"",SUM($G$5:G215))</f>
         <v/>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
         <v/>
       </c>
       <c r="J216" s="5">
-        <f>J215+G216</f>
+        <f>IF(AND(B216="",C216="",E216=""),"",SUM($G$5:G216))</f>
         <v/>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v/>
       </c>
       <c r="J217" s="5">
-        <f>J216+G217</f>
+        <f>IF(AND(B217="",C217="",E217=""),"",SUM($G$5:G217))</f>
         <v/>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
         <v/>
       </c>
       <c r="J218" s="5">
-        <f>J217+G218</f>
+        <f>IF(AND(B218="",C218="",E218=""),"",SUM($G$5:G218))</f>
         <v/>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
         <v/>
       </c>
       <c r="J219" s="5">
-        <f>J218+G219</f>
+        <f>IF(AND(B219="",C219="",E219=""),"",SUM($G$5:G219))</f>
         <v/>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
         <v/>
       </c>
       <c r="J220" s="5">
-        <f>J219+G220</f>
+        <f>IF(AND(B220="",C220="",E220=""),"",SUM($G$5:G220))</f>
         <v/>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
         <v/>
       </c>
       <c r="J221" s="5">
-        <f>J220+G221</f>
+        <f>IF(AND(B221="",C221="",E221=""),"",SUM($G$5:G221))</f>
         <v/>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
         <v/>
       </c>
       <c r="J222" s="5">
-        <f>J221+G222</f>
+        <f>IF(AND(B222="",C222="",E222=""),"",SUM($G$5:G222))</f>
         <v/>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
         <v/>
       </c>
       <c r="J223" s="5">
-        <f>J222+G223</f>
+        <f>IF(AND(B223="",C223="",E223=""),"",SUM($G$5:G223))</f>
         <v/>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
         <v/>
       </c>
       <c r="J224" s="5">
-        <f>J223+G224</f>
+        <f>IF(AND(B224="",C224="",E224=""),"",SUM($G$5:G224))</f>
         <v/>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
         <v/>
       </c>
       <c r="J225" s="5">
-        <f>J224+G225</f>
+        <f>IF(AND(B225="",C225="",E225=""),"",SUM($G$5:G225))</f>
         <v/>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
         <v/>
       </c>
       <c r="J226" s="5">
-        <f>J225+G226</f>
+        <f>IF(AND(B226="",C226="",E226=""),"",SUM($G$5:G226))</f>
         <v/>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v/>
       </c>
       <c r="J227" s="5">
-        <f>J226+G227</f>
+        <f>IF(AND(B227="",C227="",E227=""),"",SUM($G$5:G227))</f>
         <v/>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
         <v/>
       </c>
       <c r="J228" s="5">
-        <f>J227+G228</f>
+        <f>IF(AND(B228="",C228="",E228=""),"",SUM($G$5:G228))</f>
         <v/>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
         <v/>
       </c>
       <c r="J229" s="5">
-        <f>J228+G229</f>
+        <f>IF(AND(B229="",C229="",E229=""),"",SUM($G$5:G229))</f>
         <v/>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
         <v/>
       </c>
       <c r="J230" s="5">
-        <f>J229+G230</f>
+        <f>IF(AND(B230="",C230="",E230=""),"",SUM($G$5:G230))</f>
         <v/>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
         <v/>
       </c>
       <c r="J231" s="5">
-        <f>J230+G231</f>
+        <f>IF(AND(B231="",C231="",E231=""),"",SUM($G$5:G231))</f>
         <v/>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
         <v/>
       </c>
       <c r="J232" s="5">
-        <f>J231+G232</f>
+        <f>IF(AND(B232="",C232="",E232=""),"",SUM($G$5:G232))</f>
         <v/>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
         <v/>
       </c>
       <c r="J233" s="5">
-        <f>J232+G233</f>
+        <f>IF(AND(B233="",C233="",E233=""),"",SUM($G$5:G233))</f>
         <v/>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
         <v/>
       </c>
       <c r="J234" s="5">
-        <f>J233+G234</f>
+        <f>IF(AND(B234="",C234="",E234=""),"",SUM($G$5:G234))</f>
         <v/>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
         <v/>
       </c>
       <c r="J235" s="5">
-        <f>J234+G235</f>
+        <f>IF(AND(B235="",C235="",E235=""),"",SUM($G$5:G235))</f>
         <v/>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
         <v/>
       </c>
       <c r="J236" s="5">
-        <f>J235+G236</f>
+        <f>IF(AND(B236="",C236="",E236=""),"",SUM($G$5:G236))</f>
         <v/>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v/>
       </c>
       <c r="J237" s="5">
-        <f>J236+G237</f>
+        <f>IF(AND(B237="",C237="",E237=""),"",SUM($G$5:G237))</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
         <v/>
       </c>
       <c r="J238" s="5">
-        <f>J237+G238</f>
+        <f>IF(AND(B238="",C238="",E238=""),"",SUM($G$5:G238))</f>
         <v/>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
         <v/>
       </c>
       <c r="J239" s="5">
-        <f>J238+G239</f>
+        <f>IF(AND(B239="",C239="",E239=""),"",SUM($G$5:G239))</f>
         <v/>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
         <v/>
       </c>
       <c r="J240" s="5">
-        <f>J239+G240</f>
+        <f>IF(AND(B240="",C240="",E240=""),"",SUM($G$5:G240))</f>
         <v/>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
         <v/>
       </c>
       <c r="J241" s="5">
-        <f>J240+G241</f>
+        <f>IF(AND(B241="",C241="",E241=""),"",SUM($G$5:G241))</f>
         <v/>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
         <v/>
       </c>
       <c r="J242" s="5">
-        <f>J241+G242</f>
+        <f>IF(AND(B242="",C242="",E242=""),"",SUM($G$5:G242))</f>
         <v/>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
         <v/>
       </c>
       <c r="J243" s="5">
-        <f>J242+G243</f>
+        <f>IF(AND(B243="",C243="",E243=""),"",SUM($G$5:G243))</f>
         <v/>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
         <v/>
       </c>
       <c r="J244" s="5">
-        <f>J243+G244</f>
+        <f>IF(AND(B244="",C244="",E244=""),"",SUM($G$5:G244))</f>
         <v/>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
         <v/>
       </c>
       <c r="J245" s="5">
-        <f>J244+G245</f>
+        <f>IF(AND(B245="",C245="",E245=""),"",SUM($G$5:G245))</f>
         <v/>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="J246" s="5">
-        <f>J245+G246</f>
+        <f>IF(AND(B246="",C246="",E246=""),"",SUM($G$5:G246))</f>
         <v/>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v/>
       </c>
       <c r="J247" s="5">
-        <f>J246+G247</f>
+        <f>IF(AND(B247="",C247="",E247=""),"",SUM($G$5:G247))</f>
         <v/>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
         <v/>
       </c>
       <c r="J248" s="5">
-        <f>J247+G248</f>
+        <f>IF(AND(B248="",C248="",E248=""),"",SUM($G$5:G248))</f>
         <v/>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
         <v/>
       </c>
       <c r="J249" s="5">
-        <f>J248+G249</f>
+        <f>IF(AND(B249="",C249="",E249=""),"",SUM($G$5:G249))</f>
         <v/>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
         <v/>
       </c>
       <c r="J250" s="5">
-        <f>J249+G250</f>
+        <f>IF(AND(B250="",C250="",E250=""),"",SUM($G$5:G250))</f>
         <v/>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
         <v/>
       </c>
       <c r="J251" s="5">
-        <f>J250+G251</f>
+        <f>IF(AND(B251="",C251="",E251=""),"",SUM($G$5:G251))</f>
         <v/>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
         <v/>
       </c>
       <c r="J252" s="5">
-        <f>J251+G252</f>
+        <f>IF(AND(B252="",C252="",E252=""),"",SUM($G$5:G252))</f>
         <v/>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
         <v/>
       </c>
       <c r="J253" s="5">
-        <f>J252+G253</f>
+        <f>IF(AND(B253="",C253="",E253=""),"",SUM($G$5:G253))</f>
         <v/>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         <v/>
       </c>
       <c r="J254" s="5">
-        <f>J253+G254</f>
+        <f>IF(AND(B254="",C254="",E254=""),"",SUM($G$5:G254))</f>
         <v/>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
         <v/>
       </c>
       <c r="J255" s="5">
-        <f>J254+G255</f>
+        <f>IF(AND(B255="",C255="",E255=""),"",SUM($G$5:G255))</f>
         <v/>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
         <v/>
       </c>
       <c r="J256" s="5">
-        <f>J255+G256</f>
+        <f>IF(AND(B256="",C256="",E256=""),"",SUM($G$5:G256))</f>
         <v/>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
         <v/>
       </c>
       <c r="J257" s="5">
-        <f>J256+G257</f>
+        <f>IF(AND(B257="",C257="",E257=""),"",SUM($G$5:G257))</f>
         <v/>
       </c>
     </row>
@@ -7263,7 +7263,7 @@
         <v/>
       </c>
       <c r="J258" s="5">
-        <f>J257+G258</f>
+        <f>IF(AND(B258="",C258="",E258=""),"",SUM($G$5:G258))</f>
         <v/>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
         <v/>
       </c>
       <c r="J259" s="5">
-        <f>J258+G259</f>
+        <f>IF(AND(B259="",C259="",E259=""),"",SUM($G$5:G259))</f>
         <v/>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
         <v/>
       </c>
       <c r="J260" s="5">
-        <f>J259+G260</f>
+        <f>IF(AND(B260="",C260="",E260=""),"",SUM($G$5:G260))</f>
         <v/>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
         <v/>
       </c>
       <c r="J261" s="5">
-        <f>J260+G261</f>
+        <f>IF(AND(B261="",C261="",E261=""),"",SUM($G$5:G261))</f>
         <v/>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
         <v/>
       </c>
       <c r="J262" s="5">
-        <f>J261+G262</f>
+        <f>IF(AND(B262="",C262="",E262=""),"",SUM($G$5:G262))</f>
         <v/>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
         <v/>
       </c>
       <c r="J263" s="5">
-        <f>J262+G263</f>
+        <f>IF(AND(B263="",C263="",E263=""),"",SUM($G$5:G263))</f>
         <v/>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
         <v/>
       </c>
       <c r="J264" s="5">
-        <f>J263+G264</f>
+        <f>IF(AND(B264="",C264="",E264=""),"",SUM($G$5:G264))</f>
         <v/>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
         <v/>
       </c>
       <c r="J265" s="5">
-        <f>J264+G265</f>
+        <f>IF(AND(B265="",C265="",E265=""),"",SUM($G$5:G265))</f>
         <v/>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
         <v/>
       </c>
       <c r="J266" s="5">
-        <f>J265+G266</f>
+        <f>IF(AND(B266="",C266="",E266=""),"",SUM($G$5:G266))</f>
         <v/>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v/>
       </c>
       <c r="J267" s="5">
-        <f>J266+G267</f>
+        <f>IF(AND(B267="",C267="",E267=""),"",SUM($G$5:G267))</f>
         <v/>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
         <v/>
       </c>
       <c r="J268" s="5">
-        <f>J267+G268</f>
+        <f>IF(AND(B268="",C268="",E268=""),"",SUM($G$5:G268))</f>
         <v/>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
         <v/>
       </c>
       <c r="J269" s="5">
-        <f>J268+G269</f>
+        <f>IF(AND(B269="",C269="",E269=""),"",SUM($G$5:G269))</f>
         <v/>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
         <v/>
       </c>
       <c r="J270" s="5">
-        <f>J269+G270</f>
+        <f>IF(AND(B270="",C270="",E270=""),"",SUM($G$5:G270))</f>
         <v/>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
         <v/>
       </c>
       <c r="J271" s="5">
-        <f>J270+G271</f>
+        <f>IF(AND(B271="",C271="",E271=""),"",SUM($G$5:G271))</f>
         <v/>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="J272" s="5">
-        <f>J271+G272</f>
+        <f>IF(AND(B272="",C272="",E272=""),"",SUM($G$5:G272))</f>
         <v/>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
         <v/>
       </c>
       <c r="J273" s="5">
-        <f>J272+G273</f>
+        <f>IF(AND(B273="",C273="",E273=""),"",SUM($G$5:G273))</f>
         <v/>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="J274" s="5">
-        <f>J273+G274</f>
+        <f>IF(AND(B274="",C274="",E274=""),"",SUM($G$5:G274))</f>
         <v/>
       </c>
     </row>
@@ -7705,7 +7705,7 @@
         <v/>
       </c>
       <c r="J275" s="5">
-        <f>J274+G275</f>
+        <f>IF(AND(B275="",C275="",E275=""),"",SUM($G$5:G275))</f>
         <v/>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
         <v/>
       </c>
       <c r="J276" s="5">
-        <f>J275+G276</f>
+        <f>IF(AND(B276="",C276="",E276=""),"",SUM($G$5:G276))</f>
         <v/>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
         <v/>
       </c>
       <c r="J277" s="5">
-        <f>J276+G277</f>
+        <f>IF(AND(B277="",C277="",E277=""),"",SUM($G$5:G277))</f>
         <v/>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         <v/>
       </c>
       <c r="J278" s="5">
-        <f>J277+G278</f>
+        <f>IF(AND(B278="",C278="",E278=""),"",SUM($G$5:G278))</f>
         <v/>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
         <v/>
       </c>
       <c r="J279" s="5">
-        <f>J278+G279</f>
+        <f>IF(AND(B279="",C279="",E279=""),"",SUM($G$5:G279))</f>
         <v/>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
         <v/>
       </c>
       <c r="J280" s="5">
-        <f>J279+G280</f>
+        <f>IF(AND(B280="",C280="",E280=""),"",SUM($G$5:G280))</f>
         <v/>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
         <v/>
       </c>
       <c r="J281" s="5">
-        <f>J280+G281</f>
+        <f>IF(AND(B281="",C281="",E281=""),"",SUM($G$5:G281))</f>
         <v/>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
         <v/>
       </c>
       <c r="J282" s="5">
-        <f>J281+G282</f>
+        <f>IF(AND(B282="",C282="",E282=""),"",SUM($G$5:G282))</f>
         <v/>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
         <v/>
       </c>
       <c r="J283" s="5">
-        <f>J282+G283</f>
+        <f>IF(AND(B283="",C283="",E283=""),"",SUM($G$5:G283))</f>
         <v/>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
         <v/>
       </c>
       <c r="J284" s="5">
-        <f>J283+G284</f>
+        <f>IF(AND(B284="",C284="",E284=""),"",SUM($G$5:G284))</f>
         <v/>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
         <v/>
       </c>
       <c r="J285" s="5">
-        <f>J284+G285</f>
+        <f>IF(AND(B285="",C285="",E285=""),"",SUM($G$5:G285))</f>
         <v/>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
         <v/>
       </c>
       <c r="J286" s="5">
-        <f>J285+G286</f>
+        <f>IF(AND(B286="",C286="",E286=""),"",SUM($G$5:G286))</f>
         <v/>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
         <v/>
       </c>
       <c r="J287" s="5">
-        <f>J286+G287</f>
+        <f>IF(AND(B287="",C287="",E287=""),"",SUM($G$5:G287))</f>
         <v/>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
         <v/>
       </c>
       <c r="J288" s="5">
-        <f>J287+G288</f>
+        <f>IF(AND(B288="",C288="",E288=""),"",SUM($G$5:G288))</f>
         <v/>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
         <v/>
       </c>
       <c r="J289" s="5">
-        <f>J288+G289</f>
+        <f>IF(AND(B289="",C289="",E289=""),"",SUM($G$5:G289))</f>
         <v/>
       </c>
     </row>
@@ -8095,7 +8095,7 @@
         <v/>
       </c>
       <c r="J290" s="5">
-        <f>J289+G290</f>
+        <f>IF(AND(B290="",C290="",E290=""),"",SUM($G$5:G290))</f>
         <v/>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
         <v/>
       </c>
       <c r="J291" s="5">
-        <f>J290+G291</f>
+        <f>IF(AND(B291="",C291="",E291=""),"",SUM($G$5:G291))</f>
         <v/>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v/>
       </c>
       <c r="J292" s="5">
-        <f>J291+G292</f>
+        <f>IF(AND(B292="",C292="",E292=""),"",SUM($G$5:G292))</f>
         <v/>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
         <v/>
       </c>
       <c r="J293" s="5">
-        <f>J292+G293</f>
+        <f>IF(AND(B293="",C293="",E293=""),"",SUM($G$5:G293))</f>
         <v/>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
         <v/>
       </c>
       <c r="J294" s="5">
-        <f>J293+G294</f>
+        <f>IF(AND(B294="",C294="",E294=""),"",SUM($G$5:G294))</f>
         <v/>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
         <v/>
       </c>
       <c r="J295" s="5">
-        <f>J294+G295</f>
+        <f>IF(AND(B295="",C295="",E295=""),"",SUM($G$5:G295))</f>
         <v/>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
         <v/>
       </c>
       <c r="J296" s="5">
-        <f>J295+G296</f>
+        <f>IF(AND(B296="",C296="",E296=""),"",SUM($G$5:G296))</f>
         <v/>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
         <v/>
       </c>
       <c r="J297" s="5">
-        <f>J296+G297</f>
+        <f>IF(AND(B297="",C297="",E297=""),"",SUM($G$5:G297))</f>
         <v/>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
         <v/>
       </c>
       <c r="J298" s="5">
-        <f>J297+G298</f>
+        <f>IF(AND(B298="",C298="",E298=""),"",SUM($G$5:G298))</f>
         <v/>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="J299" s="5">
-        <f>J298+G299</f>
+        <f>IF(AND(B299="",C299="",E299=""),"",SUM($G$5:G299))</f>
         <v/>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
         <v/>
       </c>
       <c r="J300" s="5">
-        <f>J299+G300</f>
+        <f>IF(AND(B300="",C300="",E300=""),"",SUM($G$5:G300))</f>
         <v/>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
         <v/>
       </c>
       <c r="J301" s="5">
-        <f>J300+G301</f>
+        <f>IF(AND(B301="",C301="",E301=""),"",SUM($G$5:G301))</f>
         <v/>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
         <v/>
       </c>
       <c r="J302" s="5">
-        <f>J301+G302</f>
+        <f>IF(AND(B302="",C302="",E302=""),"",SUM($G$5:G302))</f>
         <v/>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
         <v/>
       </c>
       <c r="J303" s="5">
-        <f>J302+G303</f>
+        <f>IF(AND(B303="",C303="",E303=""),"",SUM($G$5:G303))</f>
         <v/>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
         <v/>
       </c>
       <c r="J304" s="5">
-        <f>J303+G304</f>
+        <f>IF(AND(B304="",C304="",E304=""),"",SUM($G$5:G304))</f>
         <v/>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
         <v/>
       </c>
       <c r="J305" s="5">
-        <f>J304+G305</f>
+        <f>IF(AND(B305="",C305="",E305=""),"",SUM($G$5:G305))</f>
         <v/>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
         <v/>
       </c>
       <c r="J306" s="5">
-        <f>J305+G306</f>
+        <f>IF(AND(B306="",C306="",E306=""),"",SUM($G$5:G306))</f>
         <v/>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
         <v/>
       </c>
       <c r="J307" s="5">
-        <f>J306+G307</f>
+        <f>IF(AND(B307="",C307="",E307=""),"",SUM($G$5:G307))</f>
         <v/>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
         <v/>
       </c>
       <c r="J308" s="5">
-        <f>J307+G308</f>
+        <f>IF(AND(B308="",C308="",E308=""),"",SUM($G$5:G308))</f>
         <v/>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
         <v/>
       </c>
       <c r="J309" s="5">
-        <f>J308+G309</f>
+        <f>IF(AND(B309="",C309="",E309=""),"",SUM($G$5:G309))</f>
         <v/>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
         <v/>
       </c>
       <c r="J310" s="5">
-        <f>J309+G310</f>
+        <f>IF(AND(B310="",C310="",E310=""),"",SUM($G$5:G310))</f>
         <v/>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
         <v/>
       </c>
       <c r="J311" s="5">
-        <f>J310+G311</f>
+        <f>IF(AND(B311="",C311="",E311=""),"",SUM($G$5:G311))</f>
         <v/>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
         <v/>
       </c>
       <c r="J312" s="5">
-        <f>J311+G312</f>
+        <f>IF(AND(B312="",C312="",E312=""),"",SUM($G$5:G312))</f>
         <v/>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
         <v/>
       </c>
       <c r="J313" s="5">
-        <f>J312+G313</f>
+        <f>IF(AND(B313="",C313="",E313=""),"",SUM($G$5:G313))</f>
         <v/>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
         <v/>
       </c>
       <c r="J314" s="5">
-        <f>J313+G314</f>
+        <f>IF(AND(B314="",C314="",E314=""),"",SUM($G$5:G314))</f>
         <v/>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
         <v/>
       </c>
       <c r="J315" s="5">
-        <f>J314+G315</f>
+        <f>IF(AND(B315="",C315="",E315=""),"",SUM($G$5:G315))</f>
         <v/>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
         <v/>
       </c>
       <c r="J316" s="5">
-        <f>J315+G316</f>
+        <f>IF(AND(B316="",C316="",E316=""),"",SUM($G$5:G316))</f>
         <v/>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
         <v/>
       </c>
       <c r="J317" s="5">
-        <f>J316+G317</f>
+        <f>IF(AND(B317="",C317="",E317=""),"",SUM($G$5:G317))</f>
         <v/>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
         <v/>
       </c>
       <c r="J318" s="5">
-        <f>J317+G318</f>
+        <f>IF(AND(B318="",C318="",E318=""),"",SUM($G$5:G318))</f>
         <v/>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
         <v/>
       </c>
       <c r="J319" s="5">
-        <f>J318+G319</f>
+        <f>IF(AND(B319="",C319="",E319=""),"",SUM($G$5:G319))</f>
         <v/>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
         <v/>
       </c>
       <c r="J320" s="5">
-        <f>J319+G320</f>
+        <f>IF(AND(B320="",C320="",E320=""),"",SUM($G$5:G320))</f>
         <v/>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
         <v/>
       </c>
       <c r="J321" s="5">
-        <f>J320+G321</f>
+        <f>IF(AND(B321="",C321="",E321=""),"",SUM($G$5:G321))</f>
         <v/>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
         <v/>
       </c>
       <c r="J322" s="5">
-        <f>J321+G322</f>
+        <f>IF(AND(B322="",C322="",E322=""),"",SUM($G$5:G322))</f>
         <v/>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
         <v/>
       </c>
       <c r="J323" s="5">
-        <f>J322+G323</f>
+        <f>IF(AND(B323="",C323="",E323=""),"",SUM($G$5:G323))</f>
         <v/>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
         <v/>
       </c>
       <c r="J324" s="5">
-        <f>J323+G324</f>
+        <f>IF(AND(B324="",C324="",E324=""),"",SUM($G$5:G324))</f>
         <v/>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
         <v/>
       </c>
       <c r="J325" s="5">
-        <f>J324+G325</f>
+        <f>IF(AND(B325="",C325="",E325=""),"",SUM($G$5:G325))</f>
         <v/>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
         <v/>
       </c>
       <c r="J326" s="5">
-        <f>J325+G326</f>
+        <f>IF(AND(B326="",C326="",E326=""),"",SUM($G$5:G326))</f>
         <v/>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
         <v/>
       </c>
       <c r="J327" s="5">
-        <f>J326+G327</f>
+        <f>IF(AND(B327="",C327="",E327=""),"",SUM($G$5:G327))</f>
         <v/>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
         <v/>
       </c>
       <c r="J328" s="5">
-        <f>J327+G328</f>
+        <f>IF(AND(B328="",C328="",E328=""),"",SUM($G$5:G328))</f>
         <v/>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
         <v/>
       </c>
       <c r="J329" s="5">
-        <f>J328+G329</f>
+        <f>IF(AND(B329="",C329="",E329=""),"",SUM($G$5:G329))</f>
         <v/>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
         <v/>
       </c>
       <c r="J330" s="5">
-        <f>J329+G330</f>
+        <f>IF(AND(B330="",C330="",E330=""),"",SUM($G$5:G330))</f>
         <v/>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
         <v/>
       </c>
       <c r="J331" s="5">
-        <f>J330+G331</f>
+        <f>IF(AND(B331="",C331="",E331=""),"",SUM($G$5:G331))</f>
         <v/>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
         <v/>
       </c>
       <c r="J332" s="5">
-        <f>J331+G332</f>
+        <f>IF(AND(B332="",C332="",E332=""),"",SUM($G$5:G332))</f>
         <v/>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
         <v/>
       </c>
       <c r="J333" s="5">
-        <f>J332+G333</f>
+        <f>IF(AND(B333="",C333="",E333=""),"",SUM($G$5:G333))</f>
         <v/>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         <v/>
       </c>
       <c r="J334" s="5">
-        <f>J333+G334</f>
+        <f>IF(AND(B334="",C334="",E334=""),"",SUM($G$5:G334))</f>
         <v/>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
         <v/>
       </c>
       <c r="J335" s="5">
-        <f>J334+G335</f>
+        <f>IF(AND(B335="",C335="",E335=""),"",SUM($G$5:G335))</f>
         <v/>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
         <v/>
       </c>
       <c r="J336" s="5">
-        <f>J335+G336</f>
+        <f>IF(AND(B336="",C336="",E336=""),"",SUM($G$5:G336))</f>
         <v/>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v/>
       </c>
       <c r="J337" s="5">
-        <f>J336+G337</f>
+        <f>IF(AND(B337="",C337="",E337=""),"",SUM($G$5:G337))</f>
         <v/>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
         <v/>
       </c>
       <c r="J338" s="5">
-        <f>J337+G338</f>
+        <f>IF(AND(B338="",C338="",E338=""),"",SUM($G$5:G338))</f>
         <v/>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
         <v/>
       </c>
       <c r="J339" s="5">
-        <f>J338+G339</f>
+        <f>IF(AND(B339="",C339="",E339=""),"",SUM($G$5:G339))</f>
         <v/>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
         <v/>
       </c>
       <c r="J340" s="5">
-        <f>J339+G340</f>
+        <f>IF(AND(B340="",C340="",E340=""),"",SUM($G$5:G340))</f>
         <v/>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
         <v/>
       </c>
       <c r="J341" s="5">
-        <f>J340+G341</f>
+        <f>IF(AND(B341="",C341="",E341=""),"",SUM($G$5:G341))</f>
         <v/>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         <v/>
       </c>
       <c r="J342" s="5">
-        <f>J341+G342</f>
+        <f>IF(AND(B342="",C342="",E342=""),"",SUM($G$5:G342))</f>
         <v/>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
         <v/>
       </c>
       <c r="J343" s="5">
-        <f>J342+G343</f>
+        <f>IF(AND(B343="",C343="",E343=""),"",SUM($G$5:G343))</f>
         <v/>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v/>
       </c>
       <c r="J344" s="5">
-        <f>J343+G344</f>
+        <f>IF(AND(B344="",C344="",E344=""),"",SUM($G$5:G344))</f>
         <v/>
       </c>
     </row>
@@ -9525,7 +9525,7 @@
         <v/>
       </c>
       <c r="J345" s="5">
-        <f>J344+G345</f>
+        <f>IF(AND(B345="",C345="",E345=""),"",SUM($G$5:G345))</f>
         <v/>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
         <v/>
       </c>
       <c r="J346" s="5">
-        <f>J345+G346</f>
+        <f>IF(AND(B346="",C346="",E346=""),"",SUM($G$5:G346))</f>
         <v/>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="J347" s="5">
-        <f>J346+G347</f>
+        <f>IF(AND(B347="",C347="",E347=""),"",SUM($G$5:G347))</f>
         <v/>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
         <v/>
       </c>
       <c r="J348" s="5">
-        <f>J347+G348</f>
+        <f>IF(AND(B348="",C348="",E348=""),"",SUM($G$5:G348))</f>
         <v/>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
         <v/>
       </c>
       <c r="J349" s="5">
-        <f>J348+G349</f>
+        <f>IF(AND(B349="",C349="",E349=""),"",SUM($G$5:G349))</f>
         <v/>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
         <v/>
       </c>
       <c r="J350" s="5">
-        <f>J349+G350</f>
+        <f>IF(AND(B350="",C350="",E350=""),"",SUM($G$5:G350))</f>
         <v/>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         <v/>
       </c>
       <c r="J351" s="5">
-        <f>J350+G351</f>
+        <f>IF(AND(B351="",C351="",E351=""),"",SUM($G$5:G351))</f>
         <v/>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="J352" s="5">
-        <f>J351+G352</f>
+        <f>IF(AND(B352="",C352="",E352=""),"",SUM($G$5:G352))</f>
         <v/>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
         <v/>
       </c>
       <c r="J353" s="5">
-        <f>J352+G353</f>
+        <f>IF(AND(B353="",C353="",E353=""),"",SUM($G$5:G353))</f>
         <v/>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
         <v/>
       </c>
       <c r="J354" s="5">
-        <f>J353+G354</f>
+        <f>IF(AND(B354="",C354="",E354=""),"",SUM($G$5:G354))</f>
         <v/>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
         <v/>
       </c>
       <c r="J355" s="5">
-        <f>J354+G355</f>
+        <f>IF(AND(B355="",C355="",E355=""),"",SUM($G$5:G355))</f>
         <v/>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
         <v/>
       </c>
       <c r="J356" s="5">
-        <f>J355+G356</f>
+        <f>IF(AND(B356="",C356="",E356=""),"",SUM($G$5:G356))</f>
         <v/>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
         <v/>
       </c>
       <c r="J357" s="5">
-        <f>J356+G357</f>
+        <f>IF(AND(B357="",C357="",E357=""),"",SUM($G$5:G357))</f>
         <v/>
       </c>
     </row>
@@ -9863,7 +9863,7 @@
         <v/>
       </c>
       <c r="J358" s="5">
-        <f>J357+G358</f>
+        <f>IF(AND(B358="",C358="",E358=""),"",SUM($G$5:G358))</f>
         <v/>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
         <v/>
       </c>
       <c r="J359" s="5">
-        <f>J358+G359</f>
+        <f>IF(AND(B359="",C359="",E359=""),"",SUM($G$5:G359))</f>
         <v/>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
         <v/>
       </c>
       <c r="J360" s="5">
-        <f>J359+G360</f>
+        <f>IF(AND(B360="",C360="",E360=""),"",SUM($G$5:G360))</f>
         <v/>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
         <v/>
       </c>
       <c r="J361" s="5">
-        <f>J360+G361</f>
+        <f>IF(AND(B361="",C361="",E361=""),"",SUM($G$5:G361))</f>
         <v/>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
         <v/>
       </c>
       <c r="J362" s="5">
-        <f>J361+G362</f>
+        <f>IF(AND(B362="",C362="",E362=""),"",SUM($G$5:G362))</f>
         <v/>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
         <v/>
       </c>
       <c r="J363" s="5">
-        <f>J362+G363</f>
+        <f>IF(AND(B363="",C363="",E363=""),"",SUM($G$5:G363))</f>
         <v/>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v/>
       </c>
       <c r="J364" s="5">
-        <f>J363+G364</f>
+        <f>IF(AND(B364="",C364="",E364=""),"",SUM($G$5:G364))</f>
         <v/>
       </c>
     </row>
@@ -10045,7 +10045,7 @@
         <v/>
       </c>
       <c r="J365" s="5">
-        <f>J364+G365</f>
+        <f>IF(AND(B365="",C365="",E365=""),"",SUM($G$5:G365))</f>
         <v/>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
         <v/>
       </c>
       <c r="J366" s="5">
-        <f>J365+G366</f>
+        <f>IF(AND(B366="",C366="",E366=""),"",SUM($G$5:G366))</f>
         <v/>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
         <v/>
       </c>
       <c r="J367" s="5">
-        <f>J366+G367</f>
+        <f>IF(AND(B367="",C367="",E367=""),"",SUM($G$5:G367))</f>
         <v/>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
         <v/>
       </c>
       <c r="J368" s="5">
-        <f>J367+G368</f>
+        <f>IF(AND(B368="",C368="",E368=""),"",SUM($G$5:G368))</f>
         <v/>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
         <v/>
       </c>
       <c r="J369" s="5">
-        <f>J368+G369</f>
+        <f>IF(AND(B369="",C369="",E369=""),"",SUM($G$5:G369))</f>
         <v/>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
         <v/>
       </c>
       <c r="J370" s="5">
-        <f>J369+G370</f>
+        <f>IF(AND(B370="",C370="",E370=""),"",SUM($G$5:G370))</f>
         <v/>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
         <v/>
       </c>
       <c r="J371" s="5">
-        <f>J370+G371</f>
+        <f>IF(AND(B371="",C371="",E371=""),"",SUM($G$5:G371))</f>
         <v/>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
         <v/>
       </c>
       <c r="J372" s="5">
-        <f>J371+G372</f>
+        <f>IF(AND(B372="",C372="",E372=""),"",SUM($G$5:G372))</f>
         <v/>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
         <v/>
       </c>
       <c r="J373" s="5">
-        <f>J372+G373</f>
+        <f>IF(AND(B373="",C373="",E373=""),"",SUM($G$5:G373))</f>
         <v/>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
         <v/>
       </c>
       <c r="J374" s="5">
-        <f>J373+G374</f>
+        <f>IF(AND(B374="",C374="",E374=""),"",SUM($G$5:G374))</f>
         <v/>
       </c>
     </row>
@@ -10305,7 +10305,7 @@
         <v/>
       </c>
       <c r="J375" s="5">
-        <f>J374+G375</f>
+        <f>IF(AND(B375="",C375="",E375=""),"",SUM($G$5:G375))</f>
         <v/>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
         <v/>
       </c>
       <c r="J376" s="5">
-        <f>J375+G376</f>
+        <f>IF(AND(B376="",C376="",E376=""),"",SUM($G$5:G376))</f>
         <v/>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
         <v/>
       </c>
       <c r="J377" s="5">
-        <f>J376+G377</f>
+        <f>IF(AND(B377="",C377="",E377=""),"",SUM($G$5:G377))</f>
         <v/>
       </c>
     </row>
@@ -10383,7 +10383,7 @@
         <v/>
       </c>
       <c r="J378" s="5">
-        <f>J377+G378</f>
+        <f>IF(AND(B378="",C378="",E378=""),"",SUM($G$5:G378))</f>
         <v/>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
         <v/>
       </c>
       <c r="J379" s="5">
-        <f>J378+G379</f>
+        <f>IF(AND(B379="",C379="",E379=""),"",SUM($G$5:G379))</f>
         <v/>
       </c>
     </row>
@@ -10435,7 +10435,7 @@
         <v/>
       </c>
       <c r="J380" s="5">
-        <f>J379+G380</f>
+        <f>IF(AND(B380="",C380="",E380=""),"",SUM($G$5:G380))</f>
         <v/>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
         <v/>
       </c>
       <c r="J381" s="5">
-        <f>J380+G381</f>
+        <f>IF(AND(B381="",C381="",E381=""),"",SUM($G$5:G381))</f>
         <v/>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
         <v/>
       </c>
       <c r="J382" s="5">
-        <f>J381+G382</f>
+        <f>IF(AND(B382="",C382="",E382=""),"",SUM($G$5:G382))</f>
         <v/>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
         <v/>
       </c>
       <c r="J383" s="5">
-        <f>J382+G383</f>
+        <f>IF(AND(B383="",C383="",E383=""),"",SUM($G$5:G383))</f>
         <v/>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
         <v/>
       </c>
       <c r="J384" s="5">
-        <f>J383+G384</f>
+        <f>IF(AND(B384="",C384="",E384=""),"",SUM($G$5:G384))</f>
         <v/>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
         <v/>
       </c>
       <c r="J385" s="5">
-        <f>J384+G385</f>
+        <f>IF(AND(B385="",C385="",E385=""),"",SUM($G$5:G385))</f>
         <v/>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
         <v/>
       </c>
       <c r="J386" s="5">
-        <f>J385+G386</f>
+        <f>IF(AND(B386="",C386="",E386=""),"",SUM($G$5:G386))</f>
         <v/>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
         <v/>
       </c>
       <c r="J387" s="5">
-        <f>J386+G387</f>
+        <f>IF(AND(B387="",C387="",E387=""),"",SUM($G$5:G387))</f>
         <v/>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
         <v/>
       </c>
       <c r="J388" s="5">
-        <f>J387+G388</f>
+        <f>IF(AND(B388="",C388="",E388=""),"",SUM($G$5:G388))</f>
         <v/>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
         <v/>
       </c>
       <c r="J389" s="5">
-        <f>J388+G389</f>
+        <f>IF(AND(B389="",C389="",E389=""),"",SUM($G$5:G389))</f>
         <v/>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
         <v/>
       </c>
       <c r="J390" s="5">
-        <f>J389+G390</f>
+        <f>IF(AND(B390="",C390="",E390=""),"",SUM($G$5:G390))</f>
         <v/>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
         <v/>
       </c>
       <c r="J391" s="5">
-        <f>J390+G391</f>
+        <f>IF(AND(B391="",C391="",E391=""),"",SUM($G$5:G391))</f>
         <v/>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="J392" s="5">
-        <f>J391+G392</f>
+        <f>IF(AND(B392="",C392="",E392=""),"",SUM($G$5:G392))</f>
         <v/>
       </c>
     </row>
@@ -10773,7 +10773,7 @@
         <v/>
       </c>
       <c r="J393" s="5">
-        <f>J392+G393</f>
+        <f>IF(AND(B393="",C393="",E393=""),"",SUM($G$5:G393))</f>
         <v/>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
         <v/>
       </c>
       <c r="J394" s="5">
-        <f>J393+G394</f>
+        <f>IF(AND(B394="",C394="",E394=""),"",SUM($G$5:G394))</f>
         <v/>
       </c>
     </row>
@@ -10825,7 +10825,7 @@
         <v/>
       </c>
       <c r="J395" s="5">
-        <f>J394+G395</f>
+        <f>IF(AND(B395="",C395="",E395=""),"",SUM($G$5:G395))</f>
         <v/>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
         <v/>
       </c>
       <c r="J396" s="5">
-        <f>J395+G396</f>
+        <f>IF(AND(B396="",C396="",E396=""),"",SUM($G$5:G396))</f>
         <v/>
       </c>
     </row>
@@ -10877,7 +10877,7 @@
         <v/>
       </c>
       <c r="J397" s="5">
-        <f>J396+G397</f>
+        <f>IF(AND(B397="",C397="",E397=""),"",SUM($G$5:G397))</f>
         <v/>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
         <v/>
       </c>
       <c r="J398" s="5">
-        <f>J397+G398</f>
+        <f>IF(AND(B398="",C398="",E398=""),"",SUM($G$5:G398))</f>
         <v/>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
         <v/>
       </c>
       <c r="J399" s="5">
-        <f>J398+G399</f>
+        <f>IF(AND(B399="",C399="",E399=""),"",SUM($G$5:G399))</f>
         <v/>
       </c>
     </row>
@@ -10955,7 +10955,7 @@
         <v/>
       </c>
       <c r="J400" s="5">
-        <f>J399+G400</f>
+        <f>IF(AND(B400="",C400="",E400=""),"",SUM($G$5:G400))</f>
         <v/>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
         <v/>
       </c>
       <c r="J401" s="5">
-        <f>J400+G401</f>
+        <f>IF(AND(B401="",C401="",E401=""),"",SUM($G$5:G401))</f>
         <v/>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
         <v/>
       </c>
       <c r="J402" s="5">
-        <f>J401+G402</f>
+        <f>IF(AND(B402="",C402="",E402=""),"",SUM($G$5:G402))</f>
         <v/>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
         <v/>
       </c>
       <c r="J403" s="5">
-        <f>J402+G403</f>
+        <f>IF(AND(B403="",C403="",E403=""),"",SUM($G$5:G403))</f>
         <v/>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
         <v/>
       </c>
       <c r="J404" s="5">
-        <f>J403+G404</f>
+        <f>IF(AND(B404="",C404="",E404=""),"",SUM($G$5:G404))</f>
         <v/>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="J405" s="5">
-        <f>J404+G405</f>
+        <f>IF(AND(B405="",C405="",E405=""),"",SUM($G$5:G405))</f>
         <v/>
       </c>
     </row>
@@ -11111,7 +11111,7 @@
         <v/>
       </c>
       <c r="J406" s="5">
-        <f>J405+G406</f>
+        <f>IF(AND(B406="",C406="",E406=""),"",SUM($G$5:G406))</f>
         <v/>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
         <v/>
       </c>
       <c r="J407" s="5">
-        <f>J406+G407</f>
+        <f>IF(AND(B407="",C407="",E407=""),"",SUM($G$5:G407))</f>
         <v/>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
         <v/>
       </c>
       <c r="J408" s="5">
-        <f>J407+G408</f>
+        <f>IF(AND(B408="",C408="",E408=""),"",SUM($G$5:G408))</f>
         <v/>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
         <v/>
       </c>
       <c r="J409" s="5">
-        <f>J408+G409</f>
+        <f>IF(AND(B409="",C409="",E409=""),"",SUM($G$5:G409))</f>
         <v/>
       </c>
     </row>
@@ -11215,7 +11215,7 @@
         <v/>
       </c>
       <c r="J410" s="5">
-        <f>J409+G410</f>
+        <f>IF(AND(B410="",C410="",E410=""),"",SUM($G$5:G410))</f>
         <v/>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
         <v/>
       </c>
       <c r="J411" s="5">
-        <f>J410+G411</f>
+        <f>IF(AND(B411="",C411="",E411=""),"",SUM($G$5:G411))</f>
         <v/>
       </c>
     </row>
@@ -11267,7 +11267,7 @@
         <v/>
       </c>
       <c r="J412" s="5">
-        <f>J411+G412</f>
+        <f>IF(AND(B412="",C412="",E412=""),"",SUM($G$5:G412))</f>
         <v/>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
         <v/>
       </c>
       <c r="J413" s="5">
-        <f>J412+G413</f>
+        <f>IF(AND(B413="",C413="",E413=""),"",SUM($G$5:G413))</f>
         <v/>
       </c>
     </row>
@@ -11319,7 +11319,7 @@
         <v/>
       </c>
       <c r="J414" s="5">
-        <f>J413+G414</f>
+        <f>IF(AND(B414="",C414="",E414=""),"",SUM($G$5:G414))</f>
         <v/>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
         <v/>
       </c>
       <c r="J415" s="5">
-        <f>J414+G415</f>
+        <f>IF(AND(B415="",C415="",E415=""),"",SUM($G$5:G415))</f>
         <v/>
       </c>
     </row>
@@ -11371,7 +11371,7 @@
         <v/>
       </c>
       <c r="J416" s="5">
-        <f>J415+G416</f>
+        <f>IF(AND(B416="",C416="",E416=""),"",SUM($G$5:G416))</f>
         <v/>
       </c>
     </row>
@@ -11397,7 +11397,7 @@
         <v/>
       </c>
       <c r="J417" s="5">
-        <f>J416+G417</f>
+        <f>IF(AND(B417="",C417="",E417=""),"",SUM($G$5:G417))</f>
         <v/>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
         <v/>
       </c>
       <c r="J418" s="5">
-        <f>J417+G418</f>
+        <f>IF(AND(B418="",C418="",E418=""),"",SUM($G$5:G418))</f>
         <v/>
       </c>
     </row>
@@ -11449,7 +11449,7 @@
         <v/>
       </c>
       <c r="J419" s="5">
-        <f>J418+G419</f>
+        <f>IF(AND(B419="",C419="",E419=""),"",SUM($G$5:G419))</f>
         <v/>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         <v/>
       </c>
       <c r="J420" s="5">
-        <f>J419+G420</f>
+        <f>IF(AND(B420="",C420="",E420=""),"",SUM($G$5:G420))</f>
         <v/>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
         <v/>
       </c>
       <c r="J421" s="5">
-        <f>J420+G421</f>
+        <f>IF(AND(B421="",C421="",E421=""),"",SUM($G$5:G421))</f>
         <v/>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
         <v/>
       </c>
       <c r="J422" s="5">
-        <f>J421+G422</f>
+        <f>IF(AND(B422="",C422="",E422=""),"",SUM($G$5:G422))</f>
         <v/>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
         <v/>
       </c>
       <c r="J423" s="5">
-        <f>J422+G423</f>
+        <f>IF(AND(B423="",C423="",E423=""),"",SUM($G$5:G423))</f>
         <v/>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
         <v/>
       </c>
       <c r="J424" s="5">
-        <f>J423+G424</f>
+        <f>IF(AND(B424="",C424="",E424=""),"",SUM($G$5:G424))</f>
         <v/>
       </c>
     </row>
@@ -11605,7 +11605,7 @@
         <v/>
       </c>
       <c r="J425" s="5">
-        <f>J424+G425</f>
+        <f>IF(AND(B425="",C425="",E425=""),"",SUM($G$5:G425))</f>
         <v/>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
         <v/>
       </c>
       <c r="J426" s="5">
-        <f>J425+G426</f>
+        <f>IF(AND(B426="",C426="",E426=""),"",SUM($G$5:G426))</f>
         <v/>
       </c>
     </row>
@@ -11657,7 +11657,7 @@
         <v/>
       </c>
       <c r="J427" s="5">
-        <f>J426+G427</f>
+        <f>IF(AND(B427="",C427="",E427=""),"",SUM($G$5:G427))</f>
         <v/>
       </c>
     </row>
@@ -11683,7 +11683,7 @@
         <v/>
       </c>
       <c r="J428" s="5">
-        <f>J427+G428</f>
+        <f>IF(AND(B428="",C428="",E428=""),"",SUM($G$5:G428))</f>
         <v/>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
         <v/>
       </c>
       <c r="J429" s="5">
-        <f>J428+G429</f>
+        <f>IF(AND(B429="",C429="",E429=""),"",SUM($G$5:G429))</f>
         <v/>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
         <v/>
       </c>
       <c r="J430" s="5">
-        <f>J429+G430</f>
+        <f>IF(AND(B430="",C430="",E430=""),"",SUM($G$5:G430))</f>
         <v/>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
         <v/>
       </c>
       <c r="J431" s="5">
-        <f>J430+G431</f>
+        <f>IF(AND(B431="",C431="",E431=""),"",SUM($G$5:G431))</f>
         <v/>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
         <v/>
       </c>
       <c r="J432" s="5">
-        <f>J431+G432</f>
+        <f>IF(AND(B432="",C432="",E432=""),"",SUM($G$5:G432))</f>
         <v/>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
         <v/>
       </c>
       <c r="J433" s="5">
-        <f>J432+G433</f>
+        <f>IF(AND(B433="",C433="",E433=""),"",SUM($G$5:G433))</f>
         <v/>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
         <v/>
       </c>
       <c r="J434" s="5">
-        <f>J433+G434</f>
+        <f>IF(AND(B434="",C434="",E434=""),"",SUM($G$5:G434))</f>
         <v/>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
         <v/>
       </c>
       <c r="J435" s="5">
-        <f>J434+G435</f>
+        <f>IF(AND(B435="",C435="",E435=""),"",SUM($G$5:G435))</f>
         <v/>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
         <v/>
       </c>
       <c r="J436" s="5">
-        <f>J435+G436</f>
+        <f>IF(AND(B436="",C436="",E436=""),"",SUM($G$5:G436))</f>
         <v/>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
         <v/>
       </c>
       <c r="J437" s="5">
-        <f>J436+G437</f>
+        <f>IF(AND(B437="",C437="",E437=""),"",SUM($G$5:G437))</f>
         <v/>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
         <v/>
       </c>
       <c r="J438" s="5">
-        <f>J437+G438</f>
+        <f>IF(AND(B438="",C438="",E438=""),"",SUM($G$5:G438))</f>
         <v/>
       </c>
     </row>
@@ -11969,7 +11969,7 @@
         <v/>
       </c>
       <c r="J439" s="5">
-        <f>J438+G439</f>
+        <f>IF(AND(B439="",C439="",E439=""),"",SUM($G$5:G439))</f>
         <v/>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
         <v/>
       </c>
       <c r="J440" s="5">
-        <f>J439+G440</f>
+        <f>IF(AND(B440="",C440="",E440=""),"",SUM($G$5:G440))</f>
         <v/>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
         <v/>
       </c>
       <c r="J441" s="5">
-        <f>J440+G441</f>
+        <f>IF(AND(B441="",C441="",E441=""),"",SUM($G$5:G441))</f>
         <v/>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
         <v/>
       </c>
       <c r="J442" s="5">
-        <f>J441+G442</f>
+        <f>IF(AND(B442="",C442="",E442=""),"",SUM($G$5:G442))</f>
         <v/>
       </c>
     </row>
@@ -12073,7 +12073,7 @@
         <v/>
       </c>
       <c r="J443" s="5">
-        <f>J442+G443</f>
+        <f>IF(AND(B443="",C443="",E443=""),"",SUM($G$5:G443))</f>
         <v/>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
         <v/>
       </c>
       <c r="J444" s="5">
-        <f>J443+G444</f>
+        <f>IF(AND(B444="",C444="",E444=""),"",SUM($G$5:G444))</f>
         <v/>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
         <v/>
       </c>
       <c r="J445" s="5">
-        <f>J444+G445</f>
+        <f>IF(AND(B445="",C445="",E445=""),"",SUM($G$5:G445))</f>
         <v/>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
         <v/>
       </c>
       <c r="J446" s="5">
-        <f>J445+G446</f>
+        <f>IF(AND(B446="",C446="",E446=""),"",SUM($G$5:G446))</f>
         <v/>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
         <v/>
       </c>
       <c r="J447" s="5">
-        <f>J446+G447</f>
+        <f>IF(AND(B447="",C447="",E447=""),"",SUM($G$5:G447))</f>
         <v/>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
         <v/>
       </c>
       <c r="J448" s="5">
-        <f>J447+G448</f>
+        <f>IF(AND(B448="",C448="",E448=""),"",SUM($G$5:G448))</f>
         <v/>
       </c>
     </row>
@@ -12229,7 +12229,7 @@
         <v/>
       </c>
       <c r="J449" s="5">
-        <f>J448+G449</f>
+        <f>IF(AND(B449="",C449="",E449=""),"",SUM($G$5:G449))</f>
         <v/>
       </c>
     </row>
@@ -12255,7 +12255,7 @@
         <v/>
       </c>
       <c r="J450" s="5">
-        <f>J449+G450</f>
+        <f>IF(AND(B450="",C450="",E450=""),"",SUM($G$5:G450))</f>
         <v/>
       </c>
     </row>
@@ -12281,7 +12281,7 @@
         <v/>
       </c>
       <c r="J451" s="5">
-        <f>J450+G451</f>
+        <f>IF(AND(B451="",C451="",E451=""),"",SUM($G$5:G451))</f>
         <v/>
       </c>
     </row>
@@ -12307,7 +12307,7 @@
         <v/>
       </c>
       <c r="J452" s="5">
-        <f>J451+G452</f>
+        <f>IF(AND(B452="",C452="",E452=""),"",SUM($G$5:G452))</f>
         <v/>
       </c>
     </row>
@@ -12333,7 +12333,7 @@
         <v/>
       </c>
       <c r="J453" s="5">
-        <f>J452+G453</f>
+        <f>IF(AND(B453="",C453="",E453=""),"",SUM($G$5:G453))</f>
         <v/>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
         <v/>
       </c>
       <c r="J454" s="5">
-        <f>J453+G454</f>
+        <f>IF(AND(B454="",C454="",E454=""),"",SUM($G$5:G454))</f>
         <v/>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
         <v/>
       </c>
       <c r="J455" s="5">
-        <f>J454+G455</f>
+        <f>IF(AND(B455="",C455="",E455=""),"",SUM($G$5:G455))</f>
         <v/>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
         <v/>
       </c>
       <c r="J456" s="5">
-        <f>J455+G456</f>
+        <f>IF(AND(B456="",C456="",E456=""),"",SUM($G$5:G456))</f>
         <v/>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
         <v/>
       </c>
       <c r="J457" s="5">
-        <f>J456+G457</f>
+        <f>IF(AND(B457="",C457="",E457=""),"",SUM($G$5:G457))</f>
         <v/>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
         <v/>
       </c>
       <c r="J458" s="5">
-        <f>J457+G458</f>
+        <f>IF(AND(B458="",C458="",E458=""),"",SUM($G$5:G458))</f>
         <v/>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
         <v/>
       </c>
       <c r="J459" s="5">
-        <f>J458+G459</f>
+        <f>IF(AND(B459="",C459="",E459=""),"",SUM($G$5:G459))</f>
         <v/>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
         <v/>
       </c>
       <c r="J460" s="5">
-        <f>J459+G460</f>
+        <f>IF(AND(B460="",C460="",E460=""),"",SUM($G$5:G460))</f>
         <v/>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         <v/>
       </c>
       <c r="J461" s="5">
-        <f>J460+G461</f>
+        <f>IF(AND(B461="",C461="",E461=""),"",SUM($G$5:G461))</f>
         <v/>
       </c>
     </row>
@@ -12567,7 +12567,7 @@
         <v/>
       </c>
       <c r="J462" s="5">
-        <f>J461+G462</f>
+        <f>IF(AND(B462="",C462="",E462=""),"",SUM($G$5:G462))</f>
         <v/>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
         <v/>
       </c>
       <c r="J463" s="5">
-        <f>J462+G463</f>
+        <f>IF(AND(B463="",C463="",E463=""),"",SUM($G$5:G463))</f>
         <v/>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
         <v/>
       </c>
       <c r="J464" s="5">
-        <f>J463+G464</f>
+        <f>IF(AND(B464="",C464="",E464=""),"",SUM($G$5:G464))</f>
         <v/>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
         <v/>
       </c>
       <c r="J465" s="5">
-        <f>J464+G465</f>
+        <f>IF(AND(B465="",C465="",E465=""),"",SUM($G$5:G465))</f>
         <v/>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
         <v/>
       </c>
       <c r="J466" s="5">
-        <f>J465+G466</f>
+        <f>IF(AND(B466="",C466="",E466=""),"",SUM($G$5:G466))</f>
         <v/>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
         <v/>
       </c>
       <c r="J467" s="5">
-        <f>J466+G467</f>
+        <f>IF(AND(B467="",C467="",E467=""),"",SUM($G$5:G467))</f>
         <v/>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
         <v/>
       </c>
       <c r="J468" s="5">
-        <f>J467+G468</f>
+        <f>IF(AND(B468="",C468="",E468=""),"",SUM($G$5:G468))</f>
         <v/>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
         <v/>
       </c>
       <c r="J469" s="5">
-        <f>J468+G469</f>
+        <f>IF(AND(B469="",C469="",E469=""),"",SUM($G$5:G469))</f>
         <v/>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
         <v/>
       </c>
       <c r="J470" s="5">
-        <f>J469+G470</f>
+        <f>IF(AND(B470="",C470="",E470=""),"",SUM($G$5:G470))</f>
         <v/>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
         <v/>
       </c>
       <c r="J471" s="5">
-        <f>J470+G471</f>
+        <f>IF(AND(B471="",C471="",E471=""),"",SUM($G$5:G471))</f>
         <v/>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
         <v/>
       </c>
       <c r="J472" s="5">
-        <f>J471+G472</f>
+        <f>IF(AND(B472="",C472="",E472=""),"",SUM($G$5:G472))</f>
         <v/>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
         <v/>
       </c>
       <c r="J473" s="5">
-        <f>J472+G473</f>
+        <f>IF(AND(B473="",C473="",E473=""),"",SUM($G$5:G473))</f>
         <v/>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
         <v/>
       </c>
       <c r="J474" s="5">
-        <f>J473+G474</f>
+        <f>IF(AND(B474="",C474="",E474=""),"",SUM($G$5:G474))</f>
         <v/>
       </c>
     </row>
@@ -12905,7 +12905,7 @@
         <v/>
       </c>
       <c r="J475" s="5">
-        <f>J474+G475</f>
+        <f>IF(AND(B475="",C475="",E475=""),"",SUM($G$5:G475))</f>
         <v/>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
         <v/>
       </c>
       <c r="J476" s="5">
-        <f>J475+G476</f>
+        <f>IF(AND(B476="",C476="",E476=""),"",SUM($G$5:G476))</f>
         <v/>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
         <v/>
       </c>
       <c r="J477" s="5">
-        <f>J476+G477</f>
+        <f>IF(AND(B477="",C477="",E477=""),"",SUM($G$5:G477))</f>
         <v/>
       </c>
     </row>
@@ -12983,7 +12983,7 @@
         <v/>
       </c>
       <c r="J478" s="5">
-        <f>J477+G478</f>
+        <f>IF(AND(B478="",C478="",E478=""),"",SUM($G$5:G478))</f>
         <v/>
       </c>
     </row>
@@ -13009,7 +13009,7 @@
         <v/>
       </c>
       <c r="J479" s="5">
-        <f>J478+G479</f>
+        <f>IF(AND(B479="",C479="",E479=""),"",SUM($G$5:G479))</f>
         <v/>
       </c>
     </row>
@@ -13035,7 +13035,7 @@
         <v/>
       </c>
       <c r="J480" s="5">
-        <f>J479+G480</f>
+        <f>IF(AND(B480="",C480="",E480=""),"",SUM($G$5:G480))</f>
         <v/>
       </c>
     </row>
@@ -13061,7 +13061,7 @@
         <v/>
       </c>
       <c r="J481" s="5">
-        <f>J480+G481</f>
+        <f>IF(AND(B481="",C481="",E481=""),"",SUM($G$5:G481))</f>
         <v/>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
         <v/>
       </c>
       <c r="J482" s="5">
-        <f>J481+G482</f>
+        <f>IF(AND(B482="",C482="",E482=""),"",SUM($G$5:G482))</f>
         <v/>
       </c>
     </row>
@@ -13113,7 +13113,7 @@
         <v/>
       </c>
       <c r="J483" s="5">
-        <f>J482+G483</f>
+        <f>IF(AND(B483="",C483="",E483=""),"",SUM($G$5:G483))</f>
         <v/>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         <v/>
       </c>
       <c r="J484" s="5">
-        <f>J483+G484</f>
+        <f>IF(AND(B484="",C484="",E484=""),"",SUM($G$5:G484))</f>
         <v/>
       </c>
     </row>
@@ -13165,7 +13165,7 @@
         <v/>
       </c>
       <c r="J485" s="5">
-        <f>J484+G485</f>
+        <f>IF(AND(B485="",C485="",E485=""),"",SUM($G$5:G485))</f>
         <v/>
       </c>
     </row>
@@ -13191,7 +13191,7 @@
         <v/>
       </c>
       <c r="J486" s="5">
-        <f>J485+G486</f>
+        <f>IF(AND(B486="",C486="",E486=""),"",SUM($G$5:G486))</f>
         <v/>
       </c>
     </row>
@@ -13217,7 +13217,7 @@
         <v/>
       </c>
       <c r="J487" s="5">
-        <f>J486+G487</f>
+        <f>IF(AND(B487="",C487="",E487=""),"",SUM($G$5:G487))</f>
         <v/>
       </c>
     </row>
@@ -13243,7 +13243,7 @@
         <v/>
       </c>
       <c r="J488" s="5">
-        <f>J487+G488</f>
+        <f>IF(AND(B488="",C488="",E488=""),"",SUM($G$5:G488))</f>
         <v/>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
         <v/>
       </c>
       <c r="J489" s="5">
-        <f>J488+G489</f>
+        <f>IF(AND(B489="",C489="",E489=""),"",SUM($G$5:G489))</f>
         <v/>
       </c>
     </row>
@@ -13295,7 +13295,7 @@
         <v/>
       </c>
       <c r="J490" s="5">
-        <f>J489+G490</f>
+        <f>IF(AND(B490="",C490="",E490=""),"",SUM($G$5:G490))</f>
         <v/>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
         <v/>
       </c>
       <c r="J491" s="5">
-        <f>J490+G491</f>
+        <f>IF(AND(B491="",C491="",E491=""),"",SUM($G$5:G491))</f>
         <v/>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
         <v/>
       </c>
       <c r="J492" s="5">
-        <f>J491+G492</f>
+        <f>IF(AND(B492="",C492="",E492=""),"",SUM($G$5:G492))</f>
         <v/>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
         <v/>
       </c>
       <c r="J493" s="5">
-        <f>J492+G493</f>
+        <f>IF(AND(B493="",C493="",E493=""),"",SUM($G$5:G493))</f>
         <v/>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
         <v/>
       </c>
       <c r="J494" s="5">
-        <f>J493+G494</f>
+        <f>IF(AND(B494="",C494="",E494=""),"",SUM($G$5:G494))</f>
         <v/>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
         <v/>
       </c>
       <c r="J495" s="5">
-        <f>J494+G495</f>
+        <f>IF(AND(B495="",C495="",E495=""),"",SUM($G$5:G495))</f>
         <v/>
       </c>
     </row>
@@ -13451,7 +13451,7 @@
         <v/>
       </c>
       <c r="J496" s="5">
-        <f>J495+G496</f>
+        <f>IF(AND(B496="",C496="",E496=""),"",SUM($G$5:G496))</f>
         <v/>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
         <v/>
       </c>
       <c r="J497" s="5">
-        <f>J496+G497</f>
+        <f>IF(AND(B497="",C497="",E497=""),"",SUM($G$5:G497))</f>
         <v/>
       </c>
     </row>
@@ -13503,7 +13503,7 @@
         <v/>
       </c>
       <c r="J498" s="5">
-        <f>J497+G498</f>
+        <f>IF(AND(B498="",C498="",E498=""),"",SUM($G$5:G498))</f>
         <v/>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
         <v/>
       </c>
       <c r="J499" s="5">
-        <f>J498+G499</f>
+        <f>IF(AND(B499="",C499="",E499=""),"",SUM($G$5:G499))</f>
         <v/>
       </c>
     </row>
@@ -13555,7 +13555,7 @@
         <v/>
       </c>
       <c r="J500" s="5">
-        <f>J499+G500</f>
+        <f>IF(AND(B500="",C500="",E500=""),"",SUM($G$5:G500))</f>
         <v/>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
         <v/>
       </c>
       <c r="J501" s="5">
-        <f>J500+G501</f>
+        <f>IF(AND(B501="",C501="",E501=""),"",SUM($G$5:G501))</f>
         <v/>
       </c>
     </row>
@@ -13607,7 +13607,7 @@
         <v/>
       </c>
       <c r="J502" s="5">
-        <f>J501+G502</f>
+        <f>IF(AND(B502="",C502="",E502=""),"",SUM($G$5:G502))</f>
         <v/>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
         <v/>
       </c>
       <c r="J503" s="5">
-        <f>J502+G503</f>
+        <f>IF(AND(B503="",C503="",E503=""),"",SUM($G$5:G503))</f>
         <v/>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
         <v/>
       </c>
       <c r="J504" s="5">
-        <f>J503+G504</f>
+        <f>IF(AND(B504="",C504="",E504=""),"",SUM($G$5:G504))</f>
         <v/>
       </c>
     </row>
@@ -20710,7 +20710,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Переписка о замечаниях и их устранении</t>
+          <t>Переписка с заказчиком об оплате</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>

--- a/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
@@ -9,10 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Взаиморасчёты" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Долг по актам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр передачи" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр приложений" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Акт сверки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр передачи" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр приложений" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Акт сверки'!$12:$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Акт сверки'!$A$1:$J$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -85,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -118,6 +122,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,10 +519,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="63" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Одна строка — одна операция. Начисления вводите положительными суммами, оплаты и зачёты — тоже положительными: знак ставит тип операции. Каждая операция, влияющая на долг, относится к конкретному акту: идентификатор акта в колонке F должен совпадать со строкой листа «Долг по актам». Система не распределяет платежи между актами сама — очередность зачёта определяется назначением платежа и договором, и правовой вывод за вас никто не делает. Строк 500; записи ниже таблицы блокируют итог, а не отбрасываются.</t>
+          <t>Одна строка — одна операция. Начисления вводите положительными суммами, оплаты и зачёты — тоже положительными: знак ставит тип операции. Каждая операция, влияющая на долг, относится к конкретному акту: идентификатор акта в колонке F должен совпадать со строкой листа «Долг по актам». Система не распределяет платежи между актами сама — очередность зачёта определяется назначением платежа и договором, и правовой вывод за вас никто не делает. Спорные операции — «Удержание», «Зачёт встречного требования», «Неустойка заявлена», «Допработы без соглашения (спорно)» — общий долг не уменьшают: их сумма показывается отдельно как спорная часть, у каждой обязателен акт. В расчёт процентов и претензию идёт только бесспорная часть. Строк 500; записи ниже таблицы блокируют итог, а не отбрасываются.</t>
         </is>
       </c>
     </row>
@@ -549,12 +559,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Влияние на бесспорный долг</t>
+          <t>Влияние на общий долг</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Спорная сумма (граница B2)</t>
+          <t>Спорная сумма (границы B2, B5)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -564,7 +574,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Бесспорный долг нарастающим итогом</t>
+          <t>Общий долг нарастающим итогом</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -591,11 +601,11 @@
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>IF(OR(C5="Удержание",C5="Зачёт встречного требования",C5="Неустойка заявлена"),N(E5),0)</f>
+        <f>IF(OR(C5="Удержание",C5="Зачёт встречного требования",C5="Неустойка заявлена",C5="Допработы без соглашения (спорно)"),N(E5),0)</f>
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>IF(AND(B5="",C5="",D5="",E5="",F5=""),"",IF(OR(B5="",C5="",E5=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E5)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G5&lt;&gt;0,F5=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F5&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F5)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C5)*($E$5:$E$504=E5)*(($D$5:$D$504=D5)*(D5&lt;&gt;"")+($B$5:$B$504=B5)*(B5&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B5="",C5="",D5="",E5="",F5=""),"",IF(OR(B5="",C5="",E5=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E5)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H5&lt;&gt;0,F5=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G5&lt;&gt;0,F5=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F5&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F5)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C5)*($E$5:$E$504=E5)*(($D$5:$D$504=D5)*(D5&lt;&gt;"")+($B$5:$B$504=B5)*(B5&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J5" s="5">
@@ -626,11 +636,11 @@
         <v/>
       </c>
       <c r="H6" s="5">
-        <f>IF(OR(C6="Удержание",C6="Зачёт встречного требования",C6="Неустойка заявлена"),N(E6),0)</f>
+        <f>IF(OR(C6="Удержание",C6="Зачёт встречного требования",C6="Неустойка заявлена",C6="Допработы без соглашения (спорно)"),N(E6),0)</f>
         <v/>
       </c>
       <c r="I6" s="6">
-        <f>IF(AND(B6="",C6="",D6="",E6="",F6=""),"",IF(OR(B6="",C6="",E6=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E6)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G6&lt;&gt;0,F6=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F6&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F6)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C6)*($E$5:$E$504=E6)*(($D$5:$D$504=D6)*(D6&lt;&gt;"")+($B$5:$B$504=B6)*(B6&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B6="",C6="",D6="",E6="",F6=""),"",IF(OR(B6="",C6="",E6=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E6)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H6&lt;&gt;0,F6=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G6&lt;&gt;0,F6=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F6&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F6)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C6)*($E$5:$E$504=E6)*(($D$5:$D$504=D6)*(D6&lt;&gt;"")+($B$5:$B$504=B6)*(B6&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J6" s="5">
@@ -661,11 +671,11 @@
         <v/>
       </c>
       <c r="H7" s="5">
-        <f>IF(OR(C7="Удержание",C7="Зачёт встречного требования",C7="Неустойка заявлена"),N(E7),0)</f>
+        <f>IF(OR(C7="Удержание",C7="Зачёт встречного требования",C7="Неустойка заявлена",C7="Допработы без соглашения (спорно)"),N(E7),0)</f>
         <v/>
       </c>
       <c r="I7" s="6">
-        <f>IF(AND(B7="",C7="",D7="",E7="",F7=""),"",IF(OR(B7="",C7="",E7=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E7)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G7&lt;&gt;0,F7=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F7&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F7)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C7)*($E$5:$E$504=E7)*(($D$5:$D$504=D7)*(D7&lt;&gt;"")+($B$5:$B$504=B7)*(B7&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B7="",C7="",D7="",E7="",F7=""),"",IF(OR(B7="",C7="",E7=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E7)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H7&lt;&gt;0,F7=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G7&lt;&gt;0,F7=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F7&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F7)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C7)*($E$5:$E$504=E7)*(($D$5:$D$504=D7)*(D7&lt;&gt;"")+($B$5:$B$504=B7)*(B7&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J7" s="5">
@@ -696,11 +706,11 @@
         <v/>
       </c>
       <c r="H8" s="5">
-        <f>IF(OR(C8="Удержание",C8="Зачёт встречного требования",C8="Неустойка заявлена"),N(E8),0)</f>
+        <f>IF(OR(C8="Удержание",C8="Зачёт встречного требования",C8="Неустойка заявлена",C8="Допработы без соглашения (спорно)"),N(E8),0)</f>
         <v/>
       </c>
       <c r="I8" s="6">
-        <f>IF(AND(B8="",C8="",D8="",E8="",F8=""),"",IF(OR(B8="",C8="",E8=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E8)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G8&lt;&gt;0,F8=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F8&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F8)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C8)*($E$5:$E$504=E8)*(($D$5:$D$504=D8)*(D8&lt;&gt;"")+($B$5:$B$504=B8)*(B8&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B8="",C8="",D8="",E8="",F8=""),"",IF(OR(B8="",C8="",E8=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E8)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H8&lt;&gt;0,F8=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G8&lt;&gt;0,F8=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F8&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F8)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C8)*($E$5:$E$504=E8)*(($D$5:$D$504=D8)*(D8&lt;&gt;"")+($B$5:$B$504=B8)*(B8&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J8" s="5">
@@ -709,7 +719,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Спорные операции (удержание, зачёт, неустойка)</t>
+          <t>Спорные операции (удержание, зачёт встречного требования, неустойка, допработы без соглашения)</t>
         </is>
       </c>
       <c r="M8" s="5">
@@ -731,11 +741,11 @@
         <v/>
       </c>
       <c r="H9" s="5">
-        <f>IF(OR(C9="Удержание",C9="Зачёт встречного требования",C9="Неустойка заявлена"),N(E9),0)</f>
+        <f>IF(OR(C9="Удержание",C9="Зачёт встречного требования",C9="Неустойка заявлена",C9="Допработы без соглашения (спорно)"),N(E9),0)</f>
         <v/>
       </c>
       <c r="I9" s="6">
-        <f>IF(AND(B9="",C9="",D9="",E9="",F9=""),"",IF(OR(B9="",C9="",E9=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E9)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G9&lt;&gt;0,F9=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F9&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F9)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C9)*($E$5:$E$504=E9)*(($D$5:$D$504=D9)*(D9&lt;&gt;"")+($B$5:$B$504=B9)*(B9&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B9="",C9="",D9="",E9="",F9=""),"",IF(OR(B9="",C9="",E9=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E9)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H9&lt;&gt;0,F9=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G9&lt;&gt;0,F9=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F9&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F9)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C9)*($E$5:$E$504=E9)*(($D$5:$D$504=D9)*(D9&lt;&gt;"")+($B$5:$B$504=B9)*(B9&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J9" s="5">
@@ -766,11 +776,11 @@
         <v/>
       </c>
       <c r="H10" s="5">
-        <f>IF(OR(C10="Удержание",C10="Зачёт встречного требования",C10="Неустойка заявлена"),N(E10),0)</f>
+        <f>IF(OR(C10="Удержание",C10="Зачёт встречного требования",C10="Неустойка заявлена",C10="Допработы без соглашения (спорно)"),N(E10),0)</f>
         <v/>
       </c>
       <c r="I10" s="6">
-        <f>IF(AND(B10="",C10="",D10="",E10="",F10=""),"",IF(OR(B10="",C10="",E10=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E10)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G10&lt;&gt;0,F10=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F10&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F10)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C10)*($E$5:$E$504=E10)*(($D$5:$D$504=D10)*(D10&lt;&gt;"")+($B$5:$B$504=B10)*(B10&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B10="",C10="",D10="",E10="",F10=""),"",IF(OR(B10="",C10="",E10=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E10)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H10&lt;&gt;0,F10=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G10&lt;&gt;0,F10=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F10&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F10)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C10)*($E$5:$E$504=E10)*(($D$5:$D$504=D10)*(D10&lt;&gt;"")+($B$5:$B$504=B10)*(B10&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J10" s="5">
@@ -779,11 +789,11 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ТЕКУЩИЙ БЕССПОРНЫЙ ДОЛГ, руб.</t>
+          <t>ОБЩИЙ ДОЛГ ПО ДАННЫМ СУБПОДРЯДЧИКА, руб.</t>
         </is>
       </c>
       <c r="M10" s="5">
-        <f>IF(OR(M9&gt;0,M12&gt;0,M13&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка строки» и строки свода",M4-M5-M6+M7)</f>
+        <f>IF(OR(M9&gt;0,M14&gt;0,M15&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка строки» и строки свода",M4-M5-M6+M7)</f>
         <v/>
       </c>
     </row>
@@ -801,11 +811,11 @@
         <v/>
       </c>
       <c r="H11" s="5">
-        <f>IF(OR(C11="Удержание",C11="Зачёт встречного требования",C11="Неустойка заявлена"),N(E11),0)</f>
+        <f>IF(OR(C11="Удержание",C11="Зачёт встречного требования",C11="Неустойка заявлена",C11="Допработы без соглашения (спорно)"),N(E11),0)</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>IF(AND(B11="",C11="",D11="",E11="",F11=""),"",IF(OR(B11="",C11="",E11=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E11)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G11&lt;&gt;0,F11=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F11&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F11)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C11)*($E$5:$E$504=E11)*(($D$5:$D$504=D11)*(D11&lt;&gt;"")+($B$5:$B$504=B11)*(B11&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B11="",C11="",D11="",E11="",F11=""),"",IF(OR(B11="",C11="",E11=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E11)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H11&lt;&gt;0,F11=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G11&lt;&gt;0,F11=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F11&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F11)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C11)*($E$5:$E$504=E11)*(($D$5:$D$504=D11)*(D11&lt;&gt;"")+($B$5:$B$504=B11)*(B11&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J11" s="5">
@@ -814,11 +824,11 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Граница</t>
+          <t>СПОРНАЯ ЧАСТЬ, руб. (в том числе оспаривается Заказчиком)</t>
         </is>
       </c>
       <c r="M11" s="5">
-        <f>IF(M8&gt;0,"ГРАНИЦА B2: спорные операции на сумму "&amp;FIXED(M8,2)&amp;" руб. — к специалисту","нет")</f>
+        <f>IF(NOT(ISNUMBER(M10)),"ИТОГ ЗАБЛОКИРОВАН: см. строку общего долга",M8)</f>
         <v/>
       </c>
     </row>
@@ -836,11 +846,11 @@
         <v/>
       </c>
       <c r="H12" s="5">
-        <f>IF(OR(C12="Удержание",C12="Зачёт встречного требования",C12="Неустойка заявлена"),N(E12),0)</f>
+        <f>IF(OR(C12="Удержание",C12="Зачёт встречного требования",C12="Неустойка заявлена",C12="Допработы без соглашения (спорно)"),N(E12),0)</f>
         <v/>
       </c>
       <c r="I12" s="6">
-        <f>IF(AND(B12="",C12="",D12="",E12="",F12=""),"",IF(OR(B12="",C12="",E12=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E12)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G12&lt;&gt;0,F12=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F12&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F12)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C12)*($E$5:$E$504=E12)*(($D$5:$D$504=D12)*(D12&lt;&gt;"")+($B$5:$B$504=B12)*(B12&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B12="",C12="",D12="",E12="",F12=""),"",IF(OR(B12="",C12="",E12=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E12)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H12&lt;&gt;0,F12=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G12&lt;&gt;0,F12=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F12&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F12)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C12)*($E$5:$E$504=E12)*(($D$5:$D$504=D12)*(D12&lt;&gt;"")+($B$5:$B$504=B12)*(B12&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J12" s="5">
@@ -849,11 +859,11 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Операций без типа или суммы</t>
+          <t>БЕССПОРНАЯ ЧАСТЬ, руб. (общий долг − спорная часть; по актам — лист «Долг по актам»)</t>
         </is>
       </c>
       <c r="M12" s="5">
-        <f>SUMPRODUCT((B5:B504&lt;&gt;"")*(((C5:C504="")+(E5:E504=""))&gt;0))</f>
+        <f>IF(NOT(ISNUMBER(M10)),"ИТОГ ЗАБЛОКИРОВАН: см. строку общего долга",IF(OR(M11&gt;M10,COUNTIF('Долг по актам'!$N$5:$N$34,"БЛОК: спорная*")&gt;0),"БЛОК: спорная часть больше общего долга (в целом или по акту) — проверьте суммы спорных операций и акты, к которым они отнесены: бесспорная часть не может быть отрицательной",M10-M11))</f>
         <v/>
       </c>
     </row>
@@ -871,11 +881,11 @@
         <v/>
       </c>
       <c r="H13" s="5">
-        <f>IF(OR(C13="Удержание",C13="Зачёт встречного требования",C13="Неустойка заявлена"),N(E13),0)</f>
+        <f>IF(OR(C13="Удержание",C13="Зачёт встречного требования",C13="Неустойка заявлена",C13="Допработы без соглашения (спорно)"),N(E13),0)</f>
         <v/>
       </c>
       <c r="I13" s="6">
-        <f>IF(AND(B13="",C13="",D13="",E13="",F13=""),"",IF(OR(B13="",C13="",E13=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E13)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G13&lt;&gt;0,F13=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F13&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F13)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C13)*($E$5:$E$504=E13)*(($D$5:$D$504=D13)*(D13&lt;&gt;"")+($B$5:$B$504=B13)*(B13&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B13="",C13="",D13="",E13="",F13=""),"",IF(OR(B13="",C13="",E13=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E13)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H13&lt;&gt;0,F13=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G13&lt;&gt;0,F13=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F13&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F13)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C13)*($E$5:$E$504=E13)*(($D$5:$D$504=D13)*(D13&lt;&gt;"")+($B$5:$B$504=B13)*(B13&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J13" s="5">
@@ -884,11 +894,11 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Строк с ошибкой в колонке «Проверка строки»</t>
+          <t>Граница</t>
         </is>
       </c>
       <c r="M13" s="5">
-        <f>COUNTIF(I5:I504,"БЛОК*")</f>
+        <f>IF(M8&gt;0,TRIM(IF(M8-SUMIF(C5:C504,"Допработы без соглашения (спорно)",E5:E504)&gt;0,"ГРАНИЦА B2: удержание, зачёт встречного требования, неустойка на сумму "&amp;FIXED(M8-SUMIF(C5:C504,"Допработы без соглашения (спорно)",E5:E504),2)&amp;" руб. — к специалисту. ","")&amp;IF(SUMIF(C5:C504,"Допработы без соглашения (спорно)",E5:E504)&gt;0,"ГРАНИЦА B5: допработы без соглашения на сумму "&amp;FIXED(SUMIF(C5:C504,"Допработы без соглашения (спорно)",E5:E504),2)&amp;" руб. — к специалисту.","")),"нет")</f>
         <v/>
       </c>
     </row>
@@ -906,15 +916,24 @@
         <v/>
       </c>
       <c r="H14" s="5">
-        <f>IF(OR(C14="Удержание",C14="Зачёт встречного требования",C14="Неустойка заявлена"),N(E14),0)</f>
+        <f>IF(OR(C14="Удержание",C14="Зачёт встречного требования",C14="Неустойка заявлена",C14="Допработы без соглашения (спорно)"),N(E14),0)</f>
         <v/>
       </c>
       <c r="I14" s="6">
-        <f>IF(AND(B14="",C14="",D14="",E14="",F14=""),"",IF(OR(B14="",C14="",E14=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E14)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G14&lt;&gt;0,F14=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F14&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F14)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C14)*($E$5:$E$504=E14)*(($D$5:$D$504=D14)*(D14&lt;&gt;"")+($B$5:$B$504=B14)*(B14&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B14="",C14="",D14="",E14="",F14=""),"",IF(OR(B14="",C14="",E14=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E14)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H14&lt;&gt;0,F14=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G14&lt;&gt;0,F14=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F14&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F14)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C14)*($E$5:$E$504=E14)*(($D$5:$D$504=D14)*(D14&lt;&gt;"")+($B$5:$B$504=B14)*(B14&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J14" s="5">
         <f>IF(AND(B14="",C14="",E14=""),"",SUM($G$5:G14))</f>
+        <v/>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Операций без типа или суммы</t>
+        </is>
+      </c>
+      <c r="M14" s="5">
+        <f>SUMPRODUCT((B5:B504&lt;&gt;"")*(((C5:C504="")+(E5:E504=""))&gt;0))</f>
         <v/>
       </c>
     </row>
@@ -932,21 +951,25 @@
         <v/>
       </c>
       <c r="H15" s="5">
-        <f>IF(OR(C15="Удержание",C15="Зачёт встречного требования",C15="Неустойка заявлена"),N(E15),0)</f>
+        <f>IF(OR(C15="Удержание",C15="Зачёт встречного требования",C15="Неустойка заявлена",C15="Допработы без соглашения (спорно)"),N(E15),0)</f>
         <v/>
       </c>
       <c r="I15" s="6">
-        <f>IF(AND(B15="",C15="",D15="",E15="",F15=""),"",IF(OR(B15="",C15="",E15=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E15)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G15&lt;&gt;0,F15=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F15&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F15)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C15)*($E$5:$E$504=E15)*(($D$5:$D$504=D15)*(D15&lt;&gt;"")+($B$5:$B$504=B15)*(B15&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B15="",C15="",D15="",E15="",F15=""),"",IF(OR(B15="",C15="",E15=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E15)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H15&lt;&gt;0,F15=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G15&lt;&gt;0,F15=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F15&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F15)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C15)*($E$5:$E$504=E15)*(($D$5:$D$504=D15)*(D15&lt;&gt;"")+($B$5:$B$504=B15)*(B15&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J15" s="5">
         <f>IF(AND(B15="",C15="",E15=""),"",SUM($G$5:G15))</f>
         <v/>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Это ТЕКУЩИЙ остаток: из него уже вычтены все оплаты, в том числе поступившие после начала просрочки. В расчёт процентов (файл 08) его переносить нельзя — там нужен долг на первый день просрочки по каждому акту. Оба числа берите на листе «Долг по актам».</t>
+          <t>Строк с ошибкой в колонке «Проверка строки»</t>
         </is>
+      </c>
+      <c r="M15" s="5">
+        <f>COUNTIF(I5:I504,"БЛОК*")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -963,11 +986,11 @@
         <v/>
       </c>
       <c r="H16" s="5">
-        <f>IF(OR(C16="Удержание",C16="Зачёт встречного требования",C16="Неустойка заявлена"),N(E16),0)</f>
+        <f>IF(OR(C16="Удержание",C16="Зачёт встречного требования",C16="Неустойка заявлена",C16="Допработы без соглашения (спорно)"),N(E16),0)</f>
         <v/>
       </c>
       <c r="I16" s="6">
-        <f>IF(AND(B16="",C16="",D16="",E16="",F16=""),"",IF(OR(B16="",C16="",E16=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E16)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G16&lt;&gt;0,F16=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F16&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F16)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C16)*($E$5:$E$504=E16)*(($D$5:$D$504=D16)*(D16&lt;&gt;"")+($B$5:$B$504=B16)*(B16&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B16="",C16="",D16="",E16="",F16=""),"",IF(OR(B16="",C16="",E16=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E16)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H16&lt;&gt;0,F16=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G16&lt;&gt;0,F16=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F16&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F16)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C16)*($E$5:$E$504=E16)*(($D$5:$D$504=D16)*(D16&lt;&gt;"")+($B$5:$B$504=B16)*(B16&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J16" s="5">
@@ -989,11 +1012,11 @@
         <v/>
       </c>
       <c r="H17" s="5">
-        <f>IF(OR(C17="Удержание",C17="Зачёт встречного требования",C17="Неустойка заявлена"),N(E17),0)</f>
+        <f>IF(OR(C17="Удержание",C17="Зачёт встречного требования",C17="Неустойка заявлена",C17="Допработы без соглашения (спорно)"),N(E17),0)</f>
         <v/>
       </c>
       <c r="I17" s="6">
-        <f>IF(AND(B17="",C17="",D17="",E17="",F17=""),"",IF(OR(B17="",C17="",E17=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E17)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G17&lt;&gt;0,F17=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F17&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F17)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C17)*($E$5:$E$504=E17)*(($D$5:$D$504=D17)*(D17&lt;&gt;"")+($B$5:$B$504=B17)*(B17&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B17="",C17="",D17="",E17="",F17=""),"",IF(OR(B17="",C17="",E17=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E17)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H17&lt;&gt;0,F17=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G17&lt;&gt;0,F17=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F17&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F17)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C17)*($E$5:$E$504=E17)*(($D$5:$D$504=D17)*(D17&lt;&gt;"")+($B$5:$B$504=B17)*(B17&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J17" s="5">
@@ -1015,16 +1038,21 @@
         <v/>
       </c>
       <c r="H18" s="5">
-        <f>IF(OR(C18="Удержание",C18="Зачёт встречного требования",C18="Неустойка заявлена"),N(E18),0)</f>
+        <f>IF(OR(C18="Удержание",C18="Зачёт встречного требования",C18="Неустойка заявлена",C18="Допработы без соглашения (спорно)"),N(E18),0)</f>
         <v/>
       </c>
       <c r="I18" s="6">
-        <f>IF(AND(B18="",C18="",D18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E18)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G18&lt;&gt;0,F18=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F18&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F18)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C18)*($E$5:$E$504=E18)*(($D$5:$D$504=D18)*(D18&lt;&gt;"")+($B$5:$B$504=B18)*(B18&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B18="",C18="",D18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E18)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H18&lt;&gt;0,F18=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G18&lt;&gt;0,F18=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F18&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F18)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C18)*($E$5:$E$504=E18)*(($D$5:$D$504=D18)*(D18&lt;&gt;"")+($B$5:$B$504=B18)*(B18&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J18" s="5">
         <f>IF(AND(B18="",C18="",E18=""),"",SUM($G$5:G18))</f>
         <v/>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>Общий долг — ТЕКУЩИЙ остаток: из него уже вычтены все оплаты, в том числе поступившие после начала просрочки. В расчёт процентов (файл 08) его переносить нельзя — там нужен бесспорный долг на первый день просрочки по каждому акту. Спорная часть в расчёт процентов и претензию не идёт: её оценка — у специалиста. Числа по актам берите на листе «Долг по актам», для заказчика — лист «Акт сверки».</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1041,11 +1069,11 @@
         <v/>
       </c>
       <c r="H19" s="5">
-        <f>IF(OR(C19="Удержание",C19="Зачёт встречного требования",C19="Неустойка заявлена"),N(E19),0)</f>
+        <f>IF(OR(C19="Удержание",C19="Зачёт встречного требования",C19="Неустойка заявлена",C19="Допработы без соглашения (спорно)"),N(E19),0)</f>
         <v/>
       </c>
       <c r="I19" s="6">
-        <f>IF(AND(B19="",C19="",D19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E19)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G19&lt;&gt;0,F19=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F19&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F19)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C19)*($E$5:$E$504=E19)*(($D$5:$D$504=D19)*(D19&lt;&gt;"")+($B$5:$B$504=B19)*(B19&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B19="",C19="",D19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E19)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H19&lt;&gt;0,F19=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G19&lt;&gt;0,F19=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F19&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F19)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C19)*($E$5:$E$504=E19)*(($D$5:$D$504=D19)*(D19&lt;&gt;"")+($B$5:$B$504=B19)*(B19&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J19" s="5">
@@ -1067,11 +1095,11 @@
         <v/>
       </c>
       <c r="H20" s="5">
-        <f>IF(OR(C20="Удержание",C20="Зачёт встречного требования",C20="Неустойка заявлена"),N(E20),0)</f>
+        <f>IF(OR(C20="Удержание",C20="Зачёт встречного требования",C20="Неустойка заявлена",C20="Допработы без соглашения (спорно)"),N(E20),0)</f>
         <v/>
       </c>
       <c r="I20" s="6">
-        <f>IF(AND(B20="",C20="",D20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E20)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G20&lt;&gt;0,F20=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F20&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F20)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C20)*($E$5:$E$504=E20)*(($D$5:$D$504=D20)*(D20&lt;&gt;"")+($B$5:$B$504=B20)*(B20&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B20="",C20="",D20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E20)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H20&lt;&gt;0,F20=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G20&lt;&gt;0,F20=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F20&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F20)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C20)*($E$5:$E$504=E20)*(($D$5:$D$504=D20)*(D20&lt;&gt;"")+($B$5:$B$504=B20)*(B20&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J20" s="5">
@@ -1093,11 +1121,11 @@
         <v/>
       </c>
       <c r="H21" s="5">
-        <f>IF(OR(C21="Удержание",C21="Зачёт встречного требования",C21="Неустойка заявлена"),N(E21),0)</f>
+        <f>IF(OR(C21="Удержание",C21="Зачёт встречного требования",C21="Неустойка заявлена",C21="Допработы без соглашения (спорно)"),N(E21),0)</f>
         <v/>
       </c>
       <c r="I21" s="6">
-        <f>IF(AND(B21="",C21="",D21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E21)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G21&lt;&gt;0,F21=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F21&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F21)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C21)*($E$5:$E$504=E21)*(($D$5:$D$504=D21)*(D21&lt;&gt;"")+($B$5:$B$504=B21)*(B21&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B21="",C21="",D21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E21)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H21&lt;&gt;0,F21=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G21&lt;&gt;0,F21=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F21&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F21)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C21)*($E$5:$E$504=E21)*(($D$5:$D$504=D21)*(D21&lt;&gt;"")+($B$5:$B$504=B21)*(B21&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J21" s="5">
@@ -1119,11 +1147,11 @@
         <v/>
       </c>
       <c r="H22" s="5">
-        <f>IF(OR(C22="Удержание",C22="Зачёт встречного требования",C22="Неустойка заявлена"),N(E22),0)</f>
+        <f>IF(OR(C22="Удержание",C22="Зачёт встречного требования",C22="Неустойка заявлена",C22="Допработы без соглашения (спорно)"),N(E22),0)</f>
         <v/>
       </c>
       <c r="I22" s="6">
-        <f>IF(AND(B22="",C22="",D22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E22)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G22&lt;&gt;0,F22=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F22&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F22)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C22)*($E$5:$E$504=E22)*(($D$5:$D$504=D22)*(D22&lt;&gt;"")+($B$5:$B$504=B22)*(B22&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B22="",C22="",D22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E22)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H22&lt;&gt;0,F22=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G22&lt;&gt;0,F22=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F22&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F22)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C22)*($E$5:$E$504=E22)*(($D$5:$D$504=D22)*(D22&lt;&gt;"")+($B$5:$B$504=B22)*(B22&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J22" s="5">
@@ -1145,11 +1173,11 @@
         <v/>
       </c>
       <c r="H23" s="5">
-        <f>IF(OR(C23="Удержание",C23="Зачёт встречного требования",C23="Неустойка заявлена"),N(E23),0)</f>
+        <f>IF(OR(C23="Удержание",C23="Зачёт встречного требования",C23="Неустойка заявлена",C23="Допработы без соглашения (спорно)"),N(E23),0)</f>
         <v/>
       </c>
       <c r="I23" s="6">
-        <f>IF(AND(B23="",C23="",D23="",E23="",F23=""),"",IF(OR(B23="",C23="",E23=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E23)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G23&lt;&gt;0,F23=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F23&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F23)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C23)*($E$5:$E$504=E23)*(($D$5:$D$504=D23)*(D23&lt;&gt;"")+($B$5:$B$504=B23)*(B23&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B23="",C23="",D23="",E23="",F23=""),"",IF(OR(B23="",C23="",E23=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E23)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H23&lt;&gt;0,F23=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G23&lt;&gt;0,F23=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F23&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F23)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C23)*($E$5:$E$504=E23)*(($D$5:$D$504=D23)*(D23&lt;&gt;"")+($B$5:$B$504=B23)*(B23&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J23" s="5">
@@ -1171,11 +1199,11 @@
         <v/>
       </c>
       <c r="H24" s="5">
-        <f>IF(OR(C24="Удержание",C24="Зачёт встречного требования",C24="Неустойка заявлена"),N(E24),0)</f>
+        <f>IF(OR(C24="Удержание",C24="Зачёт встречного требования",C24="Неустойка заявлена",C24="Допработы без соглашения (спорно)"),N(E24),0)</f>
         <v/>
       </c>
       <c r="I24" s="6">
-        <f>IF(AND(B24="",C24="",D24="",E24="",F24=""),"",IF(OR(B24="",C24="",E24=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E24)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G24&lt;&gt;0,F24=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F24&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F24)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C24)*($E$5:$E$504=E24)*(($D$5:$D$504=D24)*(D24&lt;&gt;"")+($B$5:$B$504=B24)*(B24&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B24="",C24="",D24="",E24="",F24=""),"",IF(OR(B24="",C24="",E24=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E24)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H24&lt;&gt;0,F24=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G24&lt;&gt;0,F24=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F24&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F24)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C24)*($E$5:$E$504=E24)*(($D$5:$D$504=D24)*(D24&lt;&gt;"")+($B$5:$B$504=B24)*(B24&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J24" s="5">
@@ -1197,11 +1225,11 @@
         <v/>
       </c>
       <c r="H25" s="5">
-        <f>IF(OR(C25="Удержание",C25="Зачёт встречного требования",C25="Неустойка заявлена"),N(E25),0)</f>
+        <f>IF(OR(C25="Удержание",C25="Зачёт встречного требования",C25="Неустойка заявлена",C25="Допработы без соглашения (спорно)"),N(E25),0)</f>
         <v/>
       </c>
       <c r="I25" s="6">
-        <f>IF(AND(B25="",C25="",D25="",E25="",F25=""),"",IF(OR(B25="",C25="",E25=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E25)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G25&lt;&gt;0,F25=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F25&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F25)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C25)*($E$5:$E$504=E25)*(($D$5:$D$504=D25)*(D25&lt;&gt;"")+($B$5:$B$504=B25)*(B25&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B25="",C25="",D25="",E25="",F25=""),"",IF(OR(B25="",C25="",E25=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E25)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H25&lt;&gt;0,F25=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G25&lt;&gt;0,F25=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F25&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F25)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C25)*($E$5:$E$504=E25)*(($D$5:$D$504=D25)*(D25&lt;&gt;"")+($B$5:$B$504=B25)*(B25&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J25" s="5">
@@ -1223,11 +1251,11 @@
         <v/>
       </c>
       <c r="H26" s="5">
-        <f>IF(OR(C26="Удержание",C26="Зачёт встречного требования",C26="Неустойка заявлена"),N(E26),0)</f>
+        <f>IF(OR(C26="Удержание",C26="Зачёт встречного требования",C26="Неустойка заявлена",C26="Допработы без соглашения (спорно)"),N(E26),0)</f>
         <v/>
       </c>
       <c r="I26" s="6">
-        <f>IF(AND(B26="",C26="",D26="",E26="",F26=""),"",IF(OR(B26="",C26="",E26=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E26)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G26&lt;&gt;0,F26=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F26&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F26)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C26)*($E$5:$E$504=E26)*(($D$5:$D$504=D26)*(D26&lt;&gt;"")+($B$5:$B$504=B26)*(B26&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B26="",C26="",D26="",E26="",F26=""),"",IF(OR(B26="",C26="",E26=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E26)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H26&lt;&gt;0,F26=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G26&lt;&gt;0,F26=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F26&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F26)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C26)*($E$5:$E$504=E26)*(($D$5:$D$504=D26)*(D26&lt;&gt;"")+($B$5:$B$504=B26)*(B26&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J26" s="5">
@@ -1249,11 +1277,11 @@
         <v/>
       </c>
       <c r="H27" s="5">
-        <f>IF(OR(C27="Удержание",C27="Зачёт встречного требования",C27="Неустойка заявлена"),N(E27),0)</f>
+        <f>IF(OR(C27="Удержание",C27="Зачёт встречного требования",C27="Неустойка заявлена",C27="Допработы без соглашения (спорно)"),N(E27),0)</f>
         <v/>
       </c>
       <c r="I27" s="6">
-        <f>IF(AND(B27="",C27="",D27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E27)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G27&lt;&gt;0,F27=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F27&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F27)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C27)*($E$5:$E$504=E27)*(($D$5:$D$504=D27)*(D27&lt;&gt;"")+($B$5:$B$504=B27)*(B27&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B27="",C27="",D27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E27)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H27&lt;&gt;0,F27=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G27&lt;&gt;0,F27=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F27&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F27)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C27)*($E$5:$E$504=E27)*(($D$5:$D$504=D27)*(D27&lt;&gt;"")+($B$5:$B$504=B27)*(B27&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J27" s="5">
@@ -1275,11 +1303,11 @@
         <v/>
       </c>
       <c r="H28" s="5">
-        <f>IF(OR(C28="Удержание",C28="Зачёт встречного требования",C28="Неустойка заявлена"),N(E28),0)</f>
+        <f>IF(OR(C28="Удержание",C28="Зачёт встречного требования",C28="Неустойка заявлена",C28="Допработы без соглашения (спорно)"),N(E28),0)</f>
         <v/>
       </c>
       <c r="I28" s="6">
-        <f>IF(AND(B28="",C28="",D28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E28)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G28&lt;&gt;0,F28=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F28&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F28)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C28)*($E$5:$E$504=E28)*(($D$5:$D$504=D28)*(D28&lt;&gt;"")+($B$5:$B$504=B28)*(B28&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B28="",C28="",D28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E28)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H28&lt;&gt;0,F28=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G28&lt;&gt;0,F28=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F28&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F28)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C28)*($E$5:$E$504=E28)*(($D$5:$D$504=D28)*(D28&lt;&gt;"")+($B$5:$B$504=B28)*(B28&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J28" s="5">
@@ -1301,11 +1329,11 @@
         <v/>
       </c>
       <c r="H29" s="5">
-        <f>IF(OR(C29="Удержание",C29="Зачёт встречного требования",C29="Неустойка заявлена"),N(E29),0)</f>
+        <f>IF(OR(C29="Удержание",C29="Зачёт встречного требования",C29="Неустойка заявлена",C29="Допработы без соглашения (спорно)"),N(E29),0)</f>
         <v/>
       </c>
       <c r="I29" s="6">
-        <f>IF(AND(B29="",C29="",D29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E29)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G29&lt;&gt;0,F29=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F29&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F29)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C29)*($E$5:$E$504=E29)*(($D$5:$D$504=D29)*(D29&lt;&gt;"")+($B$5:$B$504=B29)*(B29&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B29="",C29="",D29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E29)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H29&lt;&gt;0,F29=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G29&lt;&gt;0,F29=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F29&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F29)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C29)*($E$5:$E$504=E29)*(($D$5:$D$504=D29)*(D29&lt;&gt;"")+($B$5:$B$504=B29)*(B29&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J29" s="5">
@@ -1327,11 +1355,11 @@
         <v/>
       </c>
       <c r="H30" s="5">
-        <f>IF(OR(C30="Удержание",C30="Зачёт встречного требования",C30="Неустойка заявлена"),N(E30),0)</f>
+        <f>IF(OR(C30="Удержание",C30="Зачёт встречного требования",C30="Неустойка заявлена",C30="Допработы без соглашения (спорно)"),N(E30),0)</f>
         <v/>
       </c>
       <c r="I30" s="6">
-        <f>IF(AND(B30="",C30="",D30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E30)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G30&lt;&gt;0,F30=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F30&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F30)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C30)*($E$5:$E$504=E30)*(($D$5:$D$504=D30)*(D30&lt;&gt;"")+($B$5:$B$504=B30)*(B30&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B30="",C30="",D30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E30)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H30&lt;&gt;0,F30=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G30&lt;&gt;0,F30=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F30&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F30)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C30)*($E$5:$E$504=E30)*(($D$5:$D$504=D30)*(D30&lt;&gt;"")+($B$5:$B$504=B30)*(B30&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J30" s="5">
@@ -1353,11 +1381,11 @@
         <v/>
       </c>
       <c r="H31" s="5">
-        <f>IF(OR(C31="Удержание",C31="Зачёт встречного требования",C31="Неустойка заявлена"),N(E31),0)</f>
+        <f>IF(OR(C31="Удержание",C31="Зачёт встречного требования",C31="Неустойка заявлена",C31="Допработы без соглашения (спорно)"),N(E31),0)</f>
         <v/>
       </c>
       <c r="I31" s="6">
-        <f>IF(AND(B31="",C31="",D31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E31)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G31&lt;&gt;0,F31=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F31&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F31)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C31)*($E$5:$E$504=E31)*(($D$5:$D$504=D31)*(D31&lt;&gt;"")+($B$5:$B$504=B31)*(B31&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B31="",C31="",D31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E31)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H31&lt;&gt;0,F31=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G31&lt;&gt;0,F31=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F31&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F31)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C31)*($E$5:$E$504=E31)*(($D$5:$D$504=D31)*(D31&lt;&gt;"")+($B$5:$B$504=B31)*(B31&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J31" s="5">
@@ -1379,11 +1407,11 @@
         <v/>
       </c>
       <c r="H32" s="5">
-        <f>IF(OR(C32="Удержание",C32="Зачёт встречного требования",C32="Неустойка заявлена"),N(E32),0)</f>
+        <f>IF(OR(C32="Удержание",C32="Зачёт встречного требования",C32="Неустойка заявлена",C32="Допработы без соглашения (спорно)"),N(E32),0)</f>
         <v/>
       </c>
       <c r="I32" s="6">
-        <f>IF(AND(B32="",C32="",D32="",E32="",F32=""),"",IF(OR(B32="",C32="",E32=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E32)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G32&lt;&gt;0,F32=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F32&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F32)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C32)*($E$5:$E$504=E32)*(($D$5:$D$504=D32)*(D32&lt;&gt;"")+($B$5:$B$504=B32)*(B32&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B32="",C32="",D32="",E32="",F32=""),"",IF(OR(B32="",C32="",E32=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E32)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H32&lt;&gt;0,F32=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G32&lt;&gt;0,F32=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F32&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F32)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C32)*($E$5:$E$504=E32)*(($D$5:$D$504=D32)*(D32&lt;&gt;"")+($B$5:$B$504=B32)*(B32&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J32" s="5">
@@ -1405,11 +1433,11 @@
         <v/>
       </c>
       <c r="H33" s="5">
-        <f>IF(OR(C33="Удержание",C33="Зачёт встречного требования",C33="Неустойка заявлена"),N(E33),0)</f>
+        <f>IF(OR(C33="Удержание",C33="Зачёт встречного требования",C33="Неустойка заявлена",C33="Допработы без соглашения (спорно)"),N(E33),0)</f>
         <v/>
       </c>
       <c r="I33" s="6">
-        <f>IF(AND(B33="",C33="",D33="",E33="",F33=""),"",IF(OR(B33="",C33="",E33=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E33)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G33&lt;&gt;0,F33=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F33&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F33)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C33)*($E$5:$E$504=E33)*(($D$5:$D$504=D33)*(D33&lt;&gt;"")+($B$5:$B$504=B33)*(B33&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B33="",C33="",D33="",E33="",F33=""),"",IF(OR(B33="",C33="",E33=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E33)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H33&lt;&gt;0,F33=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G33&lt;&gt;0,F33=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F33&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F33)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C33)*($E$5:$E$504=E33)*(($D$5:$D$504=D33)*(D33&lt;&gt;"")+($B$5:$B$504=B33)*(B33&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J33" s="5">
@@ -1431,11 +1459,11 @@
         <v/>
       </c>
       <c r="H34" s="5">
-        <f>IF(OR(C34="Удержание",C34="Зачёт встречного требования",C34="Неустойка заявлена"),N(E34),0)</f>
+        <f>IF(OR(C34="Удержание",C34="Зачёт встречного требования",C34="Неустойка заявлена",C34="Допработы без соглашения (спорно)"),N(E34),0)</f>
         <v/>
       </c>
       <c r="I34" s="6">
-        <f>IF(AND(B34="",C34="",D34="",E34="",F34=""),"",IF(OR(B34="",C34="",E34=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E34)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G34&lt;&gt;0,F34=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F34&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F34)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C34)*($E$5:$E$504=E34)*(($D$5:$D$504=D34)*(D34&lt;&gt;"")+($B$5:$B$504=B34)*(B34&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B34="",C34="",D34="",E34="",F34=""),"",IF(OR(B34="",C34="",E34=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E34)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H34&lt;&gt;0,F34=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G34&lt;&gt;0,F34=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F34&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F34)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C34)*($E$5:$E$504=E34)*(($D$5:$D$504=D34)*(D34&lt;&gt;"")+($B$5:$B$504=B34)*(B34&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J34" s="5">
@@ -1457,11 +1485,11 @@
         <v/>
       </c>
       <c r="H35" s="5">
-        <f>IF(OR(C35="Удержание",C35="Зачёт встречного требования",C35="Неустойка заявлена"),N(E35),0)</f>
+        <f>IF(OR(C35="Удержание",C35="Зачёт встречного требования",C35="Неустойка заявлена",C35="Допработы без соглашения (спорно)"),N(E35),0)</f>
         <v/>
       </c>
       <c r="I35" s="6">
-        <f>IF(AND(B35="",C35="",D35="",E35="",F35=""),"",IF(OR(B35="",C35="",E35=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E35)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G35&lt;&gt;0,F35=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F35&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F35)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C35)*($E$5:$E$504=E35)*(($D$5:$D$504=D35)*(D35&lt;&gt;"")+($B$5:$B$504=B35)*(B35&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B35="",C35="",D35="",E35="",F35=""),"",IF(OR(B35="",C35="",E35=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E35)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H35&lt;&gt;0,F35=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G35&lt;&gt;0,F35=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F35&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F35)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C35)*($E$5:$E$504=E35)*(($D$5:$D$504=D35)*(D35&lt;&gt;"")+($B$5:$B$504=B35)*(B35&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J35" s="5">
@@ -1483,11 +1511,11 @@
         <v/>
       </c>
       <c r="H36" s="5">
-        <f>IF(OR(C36="Удержание",C36="Зачёт встречного требования",C36="Неустойка заявлена"),N(E36),0)</f>
+        <f>IF(OR(C36="Удержание",C36="Зачёт встречного требования",C36="Неустойка заявлена",C36="Допработы без соглашения (спорно)"),N(E36),0)</f>
         <v/>
       </c>
       <c r="I36" s="6">
-        <f>IF(AND(B36="",C36="",D36="",E36="",F36=""),"",IF(OR(B36="",C36="",E36=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E36)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G36&lt;&gt;0,F36=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F36&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F36)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C36)*($E$5:$E$504=E36)*(($D$5:$D$504=D36)*(D36&lt;&gt;"")+($B$5:$B$504=B36)*(B36&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B36="",C36="",D36="",E36="",F36=""),"",IF(OR(B36="",C36="",E36=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E36)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H36&lt;&gt;0,F36=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G36&lt;&gt;0,F36=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F36&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F36)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C36)*($E$5:$E$504=E36)*(($D$5:$D$504=D36)*(D36&lt;&gt;"")+($B$5:$B$504=B36)*(B36&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J36" s="5">
@@ -1509,11 +1537,11 @@
         <v/>
       </c>
       <c r="H37" s="5">
-        <f>IF(OR(C37="Удержание",C37="Зачёт встречного требования",C37="Неустойка заявлена"),N(E37),0)</f>
+        <f>IF(OR(C37="Удержание",C37="Зачёт встречного требования",C37="Неустойка заявлена",C37="Допработы без соглашения (спорно)"),N(E37),0)</f>
         <v/>
       </c>
       <c r="I37" s="6">
-        <f>IF(AND(B37="",C37="",D37="",E37="",F37=""),"",IF(OR(B37="",C37="",E37=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E37)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G37&lt;&gt;0,F37=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F37&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F37)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C37)*($E$5:$E$504=E37)*(($D$5:$D$504=D37)*(D37&lt;&gt;"")+($B$5:$B$504=B37)*(B37&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B37="",C37="",D37="",E37="",F37=""),"",IF(OR(B37="",C37="",E37=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E37)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H37&lt;&gt;0,F37=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G37&lt;&gt;0,F37=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F37&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F37)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C37)*($E$5:$E$504=E37)*(($D$5:$D$504=D37)*(D37&lt;&gt;"")+($B$5:$B$504=B37)*(B37&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J37" s="5">
@@ -1535,11 +1563,11 @@
         <v/>
       </c>
       <c r="H38" s="5">
-        <f>IF(OR(C38="Удержание",C38="Зачёт встречного требования",C38="Неустойка заявлена"),N(E38),0)</f>
+        <f>IF(OR(C38="Удержание",C38="Зачёт встречного требования",C38="Неустойка заявлена",C38="Допработы без соглашения (спорно)"),N(E38),0)</f>
         <v/>
       </c>
       <c r="I38" s="6">
-        <f>IF(AND(B38="",C38="",D38="",E38="",F38=""),"",IF(OR(B38="",C38="",E38=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E38)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G38&lt;&gt;0,F38=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F38&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F38)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C38)*($E$5:$E$504=E38)*(($D$5:$D$504=D38)*(D38&lt;&gt;"")+($B$5:$B$504=B38)*(B38&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B38="",C38="",D38="",E38="",F38=""),"",IF(OR(B38="",C38="",E38=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E38)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H38&lt;&gt;0,F38=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G38&lt;&gt;0,F38=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F38&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F38)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C38)*($E$5:$E$504=E38)*(($D$5:$D$504=D38)*(D38&lt;&gt;"")+($B$5:$B$504=B38)*(B38&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J38" s="5">
@@ -1561,11 +1589,11 @@
         <v/>
       </c>
       <c r="H39" s="5">
-        <f>IF(OR(C39="Удержание",C39="Зачёт встречного требования",C39="Неустойка заявлена"),N(E39),0)</f>
+        <f>IF(OR(C39="Удержание",C39="Зачёт встречного требования",C39="Неустойка заявлена",C39="Допработы без соглашения (спорно)"),N(E39),0)</f>
         <v/>
       </c>
       <c r="I39" s="6">
-        <f>IF(AND(B39="",C39="",D39="",E39="",F39=""),"",IF(OR(B39="",C39="",E39=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E39)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G39&lt;&gt;0,F39=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F39&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F39)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C39)*($E$5:$E$504=E39)*(($D$5:$D$504=D39)*(D39&lt;&gt;"")+($B$5:$B$504=B39)*(B39&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B39="",C39="",D39="",E39="",F39=""),"",IF(OR(B39="",C39="",E39=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E39)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H39&lt;&gt;0,F39=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G39&lt;&gt;0,F39=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F39&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F39)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C39)*($E$5:$E$504=E39)*(($D$5:$D$504=D39)*(D39&lt;&gt;"")+($B$5:$B$504=B39)*(B39&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J39" s="5">
@@ -1587,11 +1615,11 @@
         <v/>
       </c>
       <c r="H40" s="5">
-        <f>IF(OR(C40="Удержание",C40="Зачёт встречного требования",C40="Неустойка заявлена"),N(E40),0)</f>
+        <f>IF(OR(C40="Удержание",C40="Зачёт встречного требования",C40="Неустойка заявлена",C40="Допработы без соглашения (спорно)"),N(E40),0)</f>
         <v/>
       </c>
       <c r="I40" s="6">
-        <f>IF(AND(B40="",C40="",D40="",E40="",F40=""),"",IF(OR(B40="",C40="",E40=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E40)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G40&lt;&gt;0,F40=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F40&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F40)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C40)*($E$5:$E$504=E40)*(($D$5:$D$504=D40)*(D40&lt;&gt;"")+($B$5:$B$504=B40)*(B40&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B40="",C40="",D40="",E40="",F40=""),"",IF(OR(B40="",C40="",E40=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E40)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H40&lt;&gt;0,F40=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G40&lt;&gt;0,F40=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F40&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F40)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C40)*($E$5:$E$504=E40)*(($D$5:$D$504=D40)*(D40&lt;&gt;"")+($B$5:$B$504=B40)*(B40&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J40" s="5">
@@ -1613,11 +1641,11 @@
         <v/>
       </c>
       <c r="H41" s="5">
-        <f>IF(OR(C41="Удержание",C41="Зачёт встречного требования",C41="Неустойка заявлена"),N(E41),0)</f>
+        <f>IF(OR(C41="Удержание",C41="Зачёт встречного требования",C41="Неустойка заявлена",C41="Допработы без соглашения (спорно)"),N(E41),0)</f>
         <v/>
       </c>
       <c r="I41" s="6">
-        <f>IF(AND(B41="",C41="",D41="",E41="",F41=""),"",IF(OR(B41="",C41="",E41=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E41)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G41&lt;&gt;0,F41=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F41&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F41)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C41)*($E$5:$E$504=E41)*(($D$5:$D$504=D41)*(D41&lt;&gt;"")+($B$5:$B$504=B41)*(B41&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B41="",C41="",D41="",E41="",F41=""),"",IF(OR(B41="",C41="",E41=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E41)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H41&lt;&gt;0,F41=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G41&lt;&gt;0,F41=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F41&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F41)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C41)*($E$5:$E$504=E41)*(($D$5:$D$504=D41)*(D41&lt;&gt;"")+($B$5:$B$504=B41)*(B41&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J41" s="5">
@@ -1639,11 +1667,11 @@
         <v/>
       </c>
       <c r="H42" s="5">
-        <f>IF(OR(C42="Удержание",C42="Зачёт встречного требования",C42="Неустойка заявлена"),N(E42),0)</f>
+        <f>IF(OR(C42="Удержание",C42="Зачёт встречного требования",C42="Неустойка заявлена",C42="Допработы без соглашения (спорно)"),N(E42),0)</f>
         <v/>
       </c>
       <c r="I42" s="6">
-        <f>IF(AND(B42="",C42="",D42="",E42="",F42=""),"",IF(OR(B42="",C42="",E42=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E42)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G42&lt;&gt;0,F42=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F42&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F42)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C42)*($E$5:$E$504=E42)*(($D$5:$D$504=D42)*(D42&lt;&gt;"")+($B$5:$B$504=B42)*(B42&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B42="",C42="",D42="",E42="",F42=""),"",IF(OR(B42="",C42="",E42=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E42)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H42&lt;&gt;0,F42=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G42&lt;&gt;0,F42=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F42&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F42)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C42)*($E$5:$E$504=E42)*(($D$5:$D$504=D42)*(D42&lt;&gt;"")+($B$5:$B$504=B42)*(B42&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J42" s="5">
@@ -1665,11 +1693,11 @@
         <v/>
       </c>
       <c r="H43" s="5">
-        <f>IF(OR(C43="Удержание",C43="Зачёт встречного требования",C43="Неустойка заявлена"),N(E43),0)</f>
+        <f>IF(OR(C43="Удержание",C43="Зачёт встречного требования",C43="Неустойка заявлена",C43="Допработы без соглашения (спорно)"),N(E43),0)</f>
         <v/>
       </c>
       <c r="I43" s="6">
-        <f>IF(AND(B43="",C43="",D43="",E43="",F43=""),"",IF(OR(B43="",C43="",E43=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E43)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G43&lt;&gt;0,F43=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F43&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F43)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C43)*($E$5:$E$504=E43)*(($D$5:$D$504=D43)*(D43&lt;&gt;"")+($B$5:$B$504=B43)*(B43&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B43="",C43="",D43="",E43="",F43=""),"",IF(OR(B43="",C43="",E43=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E43)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H43&lt;&gt;0,F43=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G43&lt;&gt;0,F43=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F43&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F43)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C43)*($E$5:$E$504=E43)*(($D$5:$D$504=D43)*(D43&lt;&gt;"")+($B$5:$B$504=B43)*(B43&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J43" s="5">
@@ -1691,11 +1719,11 @@
         <v/>
       </c>
       <c r="H44" s="5">
-        <f>IF(OR(C44="Удержание",C44="Зачёт встречного требования",C44="Неустойка заявлена"),N(E44),0)</f>
+        <f>IF(OR(C44="Удержание",C44="Зачёт встречного требования",C44="Неустойка заявлена",C44="Допработы без соглашения (спорно)"),N(E44),0)</f>
         <v/>
       </c>
       <c r="I44" s="6">
-        <f>IF(AND(B44="",C44="",D44="",E44="",F44=""),"",IF(OR(B44="",C44="",E44=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E44)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G44&lt;&gt;0,F44=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F44&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F44)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C44)*($E$5:$E$504=E44)*(($D$5:$D$504=D44)*(D44&lt;&gt;"")+($B$5:$B$504=B44)*(B44&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B44="",C44="",D44="",E44="",F44=""),"",IF(OR(B44="",C44="",E44=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E44)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H44&lt;&gt;0,F44=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G44&lt;&gt;0,F44=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F44&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F44)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C44)*($E$5:$E$504=E44)*(($D$5:$D$504=D44)*(D44&lt;&gt;"")+($B$5:$B$504=B44)*(B44&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J44" s="5">
@@ -1717,11 +1745,11 @@
         <v/>
       </c>
       <c r="H45" s="5">
-        <f>IF(OR(C45="Удержание",C45="Зачёт встречного требования",C45="Неустойка заявлена"),N(E45),0)</f>
+        <f>IF(OR(C45="Удержание",C45="Зачёт встречного требования",C45="Неустойка заявлена",C45="Допработы без соглашения (спорно)"),N(E45),0)</f>
         <v/>
       </c>
       <c r="I45" s="6">
-        <f>IF(AND(B45="",C45="",D45="",E45="",F45=""),"",IF(OR(B45="",C45="",E45=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E45)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G45&lt;&gt;0,F45=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F45&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F45)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C45)*($E$5:$E$504=E45)*(($D$5:$D$504=D45)*(D45&lt;&gt;"")+($B$5:$B$504=B45)*(B45&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B45="",C45="",D45="",E45="",F45=""),"",IF(OR(B45="",C45="",E45=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E45)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H45&lt;&gt;0,F45=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G45&lt;&gt;0,F45=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F45&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F45)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C45)*($E$5:$E$504=E45)*(($D$5:$D$504=D45)*(D45&lt;&gt;"")+($B$5:$B$504=B45)*(B45&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J45" s="5">
@@ -1743,11 +1771,11 @@
         <v/>
       </c>
       <c r="H46" s="5">
-        <f>IF(OR(C46="Удержание",C46="Зачёт встречного требования",C46="Неустойка заявлена"),N(E46),0)</f>
+        <f>IF(OR(C46="Удержание",C46="Зачёт встречного требования",C46="Неустойка заявлена",C46="Допработы без соглашения (спорно)"),N(E46),0)</f>
         <v/>
       </c>
       <c r="I46" s="6">
-        <f>IF(AND(B46="",C46="",D46="",E46="",F46=""),"",IF(OR(B46="",C46="",E46=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E46)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G46&lt;&gt;0,F46=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F46&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F46)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C46)*($E$5:$E$504=E46)*(($D$5:$D$504=D46)*(D46&lt;&gt;"")+($B$5:$B$504=B46)*(B46&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B46="",C46="",D46="",E46="",F46=""),"",IF(OR(B46="",C46="",E46=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E46)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H46&lt;&gt;0,F46=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G46&lt;&gt;0,F46=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F46&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F46)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C46)*($E$5:$E$504=E46)*(($D$5:$D$504=D46)*(D46&lt;&gt;"")+($B$5:$B$504=B46)*(B46&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J46" s="5">
@@ -1769,11 +1797,11 @@
         <v/>
       </c>
       <c r="H47" s="5">
-        <f>IF(OR(C47="Удержание",C47="Зачёт встречного требования",C47="Неустойка заявлена"),N(E47),0)</f>
+        <f>IF(OR(C47="Удержание",C47="Зачёт встречного требования",C47="Неустойка заявлена",C47="Допработы без соглашения (спорно)"),N(E47),0)</f>
         <v/>
       </c>
       <c r="I47" s="6">
-        <f>IF(AND(B47="",C47="",D47="",E47="",F47=""),"",IF(OR(B47="",C47="",E47=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E47)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G47&lt;&gt;0,F47=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F47&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F47)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C47)*($E$5:$E$504=E47)*(($D$5:$D$504=D47)*(D47&lt;&gt;"")+($B$5:$B$504=B47)*(B47&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B47="",C47="",D47="",E47="",F47=""),"",IF(OR(B47="",C47="",E47=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E47)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H47&lt;&gt;0,F47=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G47&lt;&gt;0,F47=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F47&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F47)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C47)*($E$5:$E$504=E47)*(($D$5:$D$504=D47)*(D47&lt;&gt;"")+($B$5:$B$504=B47)*(B47&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J47" s="5">
@@ -1795,11 +1823,11 @@
         <v/>
       </c>
       <c r="H48" s="5">
-        <f>IF(OR(C48="Удержание",C48="Зачёт встречного требования",C48="Неустойка заявлена"),N(E48),0)</f>
+        <f>IF(OR(C48="Удержание",C48="Зачёт встречного требования",C48="Неустойка заявлена",C48="Допработы без соглашения (спорно)"),N(E48),0)</f>
         <v/>
       </c>
       <c r="I48" s="6">
-        <f>IF(AND(B48="",C48="",D48="",E48="",F48=""),"",IF(OR(B48="",C48="",E48=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E48)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G48&lt;&gt;0,F48=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F48&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F48)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C48)*($E$5:$E$504=E48)*(($D$5:$D$504=D48)*(D48&lt;&gt;"")+($B$5:$B$504=B48)*(B48&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B48="",C48="",D48="",E48="",F48=""),"",IF(OR(B48="",C48="",E48=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E48)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H48&lt;&gt;0,F48=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G48&lt;&gt;0,F48=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F48&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F48)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C48)*($E$5:$E$504=E48)*(($D$5:$D$504=D48)*(D48&lt;&gt;"")+($B$5:$B$504=B48)*(B48&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J48" s="5">
@@ -1821,11 +1849,11 @@
         <v/>
       </c>
       <c r="H49" s="5">
-        <f>IF(OR(C49="Удержание",C49="Зачёт встречного требования",C49="Неустойка заявлена"),N(E49),0)</f>
+        <f>IF(OR(C49="Удержание",C49="Зачёт встречного требования",C49="Неустойка заявлена",C49="Допработы без соглашения (спорно)"),N(E49),0)</f>
         <v/>
       </c>
       <c r="I49" s="6">
-        <f>IF(AND(B49="",C49="",D49="",E49="",F49=""),"",IF(OR(B49="",C49="",E49=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E49)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G49&lt;&gt;0,F49=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F49&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F49)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C49)*($E$5:$E$504=E49)*(($D$5:$D$504=D49)*(D49&lt;&gt;"")+($B$5:$B$504=B49)*(B49&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B49="",C49="",D49="",E49="",F49=""),"",IF(OR(B49="",C49="",E49=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E49)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H49&lt;&gt;0,F49=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G49&lt;&gt;0,F49=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F49&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F49)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C49)*($E$5:$E$504=E49)*(($D$5:$D$504=D49)*(D49&lt;&gt;"")+($B$5:$B$504=B49)*(B49&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J49" s="5">
@@ -1847,11 +1875,11 @@
         <v/>
       </c>
       <c r="H50" s="5">
-        <f>IF(OR(C50="Удержание",C50="Зачёт встречного требования",C50="Неустойка заявлена"),N(E50),0)</f>
+        <f>IF(OR(C50="Удержание",C50="Зачёт встречного требования",C50="Неустойка заявлена",C50="Допработы без соглашения (спорно)"),N(E50),0)</f>
         <v/>
       </c>
       <c r="I50" s="6">
-        <f>IF(AND(B50="",C50="",D50="",E50="",F50=""),"",IF(OR(B50="",C50="",E50=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E50)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G50&lt;&gt;0,F50=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F50&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F50)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C50)*($E$5:$E$504=E50)*(($D$5:$D$504=D50)*(D50&lt;&gt;"")+($B$5:$B$504=B50)*(B50&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B50="",C50="",D50="",E50="",F50=""),"",IF(OR(B50="",C50="",E50=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E50)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H50&lt;&gt;0,F50=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G50&lt;&gt;0,F50=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F50&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F50)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C50)*($E$5:$E$504=E50)*(($D$5:$D$504=D50)*(D50&lt;&gt;"")+($B$5:$B$504=B50)*(B50&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J50" s="5">
@@ -1873,11 +1901,11 @@
         <v/>
       </c>
       <c r="H51" s="5">
-        <f>IF(OR(C51="Удержание",C51="Зачёт встречного требования",C51="Неустойка заявлена"),N(E51),0)</f>
+        <f>IF(OR(C51="Удержание",C51="Зачёт встречного требования",C51="Неустойка заявлена",C51="Допработы без соглашения (спорно)"),N(E51),0)</f>
         <v/>
       </c>
       <c r="I51" s="6">
-        <f>IF(AND(B51="",C51="",D51="",E51="",F51=""),"",IF(OR(B51="",C51="",E51=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E51)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G51&lt;&gt;0,F51=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F51&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F51)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C51)*($E$5:$E$504=E51)*(($D$5:$D$504=D51)*(D51&lt;&gt;"")+($B$5:$B$504=B51)*(B51&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B51="",C51="",D51="",E51="",F51=""),"",IF(OR(B51="",C51="",E51=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E51)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H51&lt;&gt;0,F51=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G51&lt;&gt;0,F51=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F51&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F51)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C51)*($E$5:$E$504=E51)*(($D$5:$D$504=D51)*(D51&lt;&gt;"")+($B$5:$B$504=B51)*(B51&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J51" s="5">
@@ -1899,11 +1927,11 @@
         <v/>
       </c>
       <c r="H52" s="5">
-        <f>IF(OR(C52="Удержание",C52="Зачёт встречного требования",C52="Неустойка заявлена"),N(E52),0)</f>
+        <f>IF(OR(C52="Удержание",C52="Зачёт встречного требования",C52="Неустойка заявлена",C52="Допработы без соглашения (спорно)"),N(E52),0)</f>
         <v/>
       </c>
       <c r="I52" s="6">
-        <f>IF(AND(B52="",C52="",D52="",E52="",F52=""),"",IF(OR(B52="",C52="",E52=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E52)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G52&lt;&gt;0,F52=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F52&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F52)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C52)*($E$5:$E$504=E52)*(($D$5:$D$504=D52)*(D52&lt;&gt;"")+($B$5:$B$504=B52)*(B52&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B52="",C52="",D52="",E52="",F52=""),"",IF(OR(B52="",C52="",E52=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E52)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H52&lt;&gt;0,F52=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G52&lt;&gt;0,F52=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F52&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F52)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C52)*($E$5:$E$504=E52)*(($D$5:$D$504=D52)*(D52&lt;&gt;"")+($B$5:$B$504=B52)*(B52&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J52" s="5">
@@ -1925,11 +1953,11 @@
         <v/>
       </c>
       <c r="H53" s="5">
-        <f>IF(OR(C53="Удержание",C53="Зачёт встречного требования",C53="Неустойка заявлена"),N(E53),0)</f>
+        <f>IF(OR(C53="Удержание",C53="Зачёт встречного требования",C53="Неустойка заявлена",C53="Допработы без соглашения (спорно)"),N(E53),0)</f>
         <v/>
       </c>
       <c r="I53" s="6">
-        <f>IF(AND(B53="",C53="",D53="",E53="",F53=""),"",IF(OR(B53="",C53="",E53=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E53)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G53&lt;&gt;0,F53=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F53&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F53)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C53)*($E$5:$E$504=E53)*(($D$5:$D$504=D53)*(D53&lt;&gt;"")+($B$5:$B$504=B53)*(B53&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B53="",C53="",D53="",E53="",F53=""),"",IF(OR(B53="",C53="",E53=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E53)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H53&lt;&gt;0,F53=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G53&lt;&gt;0,F53=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F53&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F53)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C53)*($E$5:$E$504=E53)*(($D$5:$D$504=D53)*(D53&lt;&gt;"")+($B$5:$B$504=B53)*(B53&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J53" s="5">
@@ -1951,11 +1979,11 @@
         <v/>
       </c>
       <c r="H54" s="5">
-        <f>IF(OR(C54="Удержание",C54="Зачёт встречного требования",C54="Неустойка заявлена"),N(E54),0)</f>
+        <f>IF(OR(C54="Удержание",C54="Зачёт встречного требования",C54="Неустойка заявлена",C54="Допработы без соглашения (спорно)"),N(E54),0)</f>
         <v/>
       </c>
       <c r="I54" s="6">
-        <f>IF(AND(B54="",C54="",D54="",E54="",F54=""),"",IF(OR(B54="",C54="",E54=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E54)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G54&lt;&gt;0,F54=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F54&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F54)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C54)*($E$5:$E$504=E54)*(($D$5:$D$504=D54)*(D54&lt;&gt;"")+($B$5:$B$504=B54)*(B54&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B54="",C54="",D54="",E54="",F54=""),"",IF(OR(B54="",C54="",E54=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E54)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H54&lt;&gt;0,F54=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G54&lt;&gt;0,F54=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F54&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F54)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C54)*($E$5:$E$504=E54)*(($D$5:$D$504=D54)*(D54&lt;&gt;"")+($B$5:$B$504=B54)*(B54&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J54" s="5">
@@ -1977,11 +2005,11 @@
         <v/>
       </c>
       <c r="H55" s="5">
-        <f>IF(OR(C55="Удержание",C55="Зачёт встречного требования",C55="Неустойка заявлена"),N(E55),0)</f>
+        <f>IF(OR(C55="Удержание",C55="Зачёт встречного требования",C55="Неустойка заявлена",C55="Допработы без соглашения (спорно)"),N(E55),0)</f>
         <v/>
       </c>
       <c r="I55" s="6">
-        <f>IF(AND(B55="",C55="",D55="",E55="",F55=""),"",IF(OR(B55="",C55="",E55=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E55)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G55&lt;&gt;0,F55=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F55&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F55)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C55)*($E$5:$E$504=E55)*(($D$5:$D$504=D55)*(D55&lt;&gt;"")+($B$5:$B$504=B55)*(B55&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B55="",C55="",D55="",E55="",F55=""),"",IF(OR(B55="",C55="",E55=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E55)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H55&lt;&gt;0,F55=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G55&lt;&gt;0,F55=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F55&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F55)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C55)*($E$5:$E$504=E55)*(($D$5:$D$504=D55)*(D55&lt;&gt;"")+($B$5:$B$504=B55)*(B55&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J55" s="5">
@@ -2003,11 +2031,11 @@
         <v/>
       </c>
       <c r="H56" s="5">
-        <f>IF(OR(C56="Удержание",C56="Зачёт встречного требования",C56="Неустойка заявлена"),N(E56),0)</f>
+        <f>IF(OR(C56="Удержание",C56="Зачёт встречного требования",C56="Неустойка заявлена",C56="Допработы без соглашения (спорно)"),N(E56),0)</f>
         <v/>
       </c>
       <c r="I56" s="6">
-        <f>IF(AND(B56="",C56="",D56="",E56="",F56=""),"",IF(OR(B56="",C56="",E56=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E56)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G56&lt;&gt;0,F56=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F56&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F56)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C56)*($E$5:$E$504=E56)*(($D$5:$D$504=D56)*(D56&lt;&gt;"")+($B$5:$B$504=B56)*(B56&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B56="",C56="",D56="",E56="",F56=""),"",IF(OR(B56="",C56="",E56=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E56)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H56&lt;&gt;0,F56=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G56&lt;&gt;0,F56=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F56&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F56)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C56)*($E$5:$E$504=E56)*(($D$5:$D$504=D56)*(D56&lt;&gt;"")+($B$5:$B$504=B56)*(B56&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J56" s="5">
@@ -2029,11 +2057,11 @@
         <v/>
       </c>
       <c r="H57" s="5">
-        <f>IF(OR(C57="Удержание",C57="Зачёт встречного требования",C57="Неустойка заявлена"),N(E57),0)</f>
+        <f>IF(OR(C57="Удержание",C57="Зачёт встречного требования",C57="Неустойка заявлена",C57="Допработы без соглашения (спорно)"),N(E57),0)</f>
         <v/>
       </c>
       <c r="I57" s="6">
-        <f>IF(AND(B57="",C57="",D57="",E57="",F57=""),"",IF(OR(B57="",C57="",E57=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E57)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G57&lt;&gt;0,F57=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F57&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F57)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C57)*($E$5:$E$504=E57)*(($D$5:$D$504=D57)*(D57&lt;&gt;"")+($B$5:$B$504=B57)*(B57&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B57="",C57="",D57="",E57="",F57=""),"",IF(OR(B57="",C57="",E57=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E57)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H57&lt;&gt;0,F57=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G57&lt;&gt;0,F57=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F57&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F57)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C57)*($E$5:$E$504=E57)*(($D$5:$D$504=D57)*(D57&lt;&gt;"")+($B$5:$B$504=B57)*(B57&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J57" s="5">
@@ -2055,11 +2083,11 @@
         <v/>
       </c>
       <c r="H58" s="5">
-        <f>IF(OR(C58="Удержание",C58="Зачёт встречного требования",C58="Неустойка заявлена"),N(E58),0)</f>
+        <f>IF(OR(C58="Удержание",C58="Зачёт встречного требования",C58="Неустойка заявлена",C58="Допработы без соглашения (спорно)"),N(E58),0)</f>
         <v/>
       </c>
       <c r="I58" s="6">
-        <f>IF(AND(B58="",C58="",D58="",E58="",F58=""),"",IF(OR(B58="",C58="",E58=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E58)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G58&lt;&gt;0,F58=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F58&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F58)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C58)*($E$5:$E$504=E58)*(($D$5:$D$504=D58)*(D58&lt;&gt;"")+($B$5:$B$504=B58)*(B58&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B58="",C58="",D58="",E58="",F58=""),"",IF(OR(B58="",C58="",E58=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E58)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H58&lt;&gt;0,F58=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G58&lt;&gt;0,F58=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F58&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F58)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C58)*($E$5:$E$504=E58)*(($D$5:$D$504=D58)*(D58&lt;&gt;"")+($B$5:$B$504=B58)*(B58&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J58" s="5">
@@ -2081,11 +2109,11 @@
         <v/>
       </c>
       <c r="H59" s="5">
-        <f>IF(OR(C59="Удержание",C59="Зачёт встречного требования",C59="Неустойка заявлена"),N(E59),0)</f>
+        <f>IF(OR(C59="Удержание",C59="Зачёт встречного требования",C59="Неустойка заявлена",C59="Допработы без соглашения (спорно)"),N(E59),0)</f>
         <v/>
       </c>
       <c r="I59" s="6">
-        <f>IF(AND(B59="",C59="",D59="",E59="",F59=""),"",IF(OR(B59="",C59="",E59=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E59)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G59&lt;&gt;0,F59=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F59&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F59)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C59)*($E$5:$E$504=E59)*(($D$5:$D$504=D59)*(D59&lt;&gt;"")+($B$5:$B$504=B59)*(B59&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B59="",C59="",D59="",E59="",F59=""),"",IF(OR(B59="",C59="",E59=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E59)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H59&lt;&gt;0,F59=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G59&lt;&gt;0,F59=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F59&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F59)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C59)*($E$5:$E$504=E59)*(($D$5:$D$504=D59)*(D59&lt;&gt;"")+($B$5:$B$504=B59)*(B59&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J59" s="5">
@@ -2107,11 +2135,11 @@
         <v/>
       </c>
       <c r="H60" s="5">
-        <f>IF(OR(C60="Удержание",C60="Зачёт встречного требования",C60="Неустойка заявлена"),N(E60),0)</f>
+        <f>IF(OR(C60="Удержание",C60="Зачёт встречного требования",C60="Неустойка заявлена",C60="Допработы без соглашения (спорно)"),N(E60),0)</f>
         <v/>
       </c>
       <c r="I60" s="6">
-        <f>IF(AND(B60="",C60="",D60="",E60="",F60=""),"",IF(OR(B60="",C60="",E60=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E60)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G60&lt;&gt;0,F60=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F60&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F60)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C60)*($E$5:$E$504=E60)*(($D$5:$D$504=D60)*(D60&lt;&gt;"")+($B$5:$B$504=B60)*(B60&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B60="",C60="",D60="",E60="",F60=""),"",IF(OR(B60="",C60="",E60=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E60)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H60&lt;&gt;0,F60=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G60&lt;&gt;0,F60=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F60&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F60)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C60)*($E$5:$E$504=E60)*(($D$5:$D$504=D60)*(D60&lt;&gt;"")+($B$5:$B$504=B60)*(B60&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J60" s="5">
@@ -2133,11 +2161,11 @@
         <v/>
       </c>
       <c r="H61" s="5">
-        <f>IF(OR(C61="Удержание",C61="Зачёт встречного требования",C61="Неустойка заявлена"),N(E61),0)</f>
+        <f>IF(OR(C61="Удержание",C61="Зачёт встречного требования",C61="Неустойка заявлена",C61="Допработы без соглашения (спорно)"),N(E61),0)</f>
         <v/>
       </c>
       <c r="I61" s="6">
-        <f>IF(AND(B61="",C61="",D61="",E61="",F61=""),"",IF(OR(B61="",C61="",E61=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E61)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G61&lt;&gt;0,F61=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F61&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F61)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C61)*($E$5:$E$504=E61)*(($D$5:$D$504=D61)*(D61&lt;&gt;"")+($B$5:$B$504=B61)*(B61&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B61="",C61="",D61="",E61="",F61=""),"",IF(OR(B61="",C61="",E61=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E61)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H61&lt;&gt;0,F61=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G61&lt;&gt;0,F61=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F61&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F61)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C61)*($E$5:$E$504=E61)*(($D$5:$D$504=D61)*(D61&lt;&gt;"")+($B$5:$B$504=B61)*(B61&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J61" s="5">
@@ -2159,11 +2187,11 @@
         <v/>
       </c>
       <c r="H62" s="5">
-        <f>IF(OR(C62="Удержание",C62="Зачёт встречного требования",C62="Неустойка заявлена"),N(E62),0)</f>
+        <f>IF(OR(C62="Удержание",C62="Зачёт встречного требования",C62="Неустойка заявлена",C62="Допработы без соглашения (спорно)"),N(E62),0)</f>
         <v/>
       </c>
       <c r="I62" s="6">
-        <f>IF(AND(B62="",C62="",D62="",E62="",F62=""),"",IF(OR(B62="",C62="",E62=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E62)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G62&lt;&gt;0,F62=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F62&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F62)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C62)*($E$5:$E$504=E62)*(($D$5:$D$504=D62)*(D62&lt;&gt;"")+($B$5:$B$504=B62)*(B62&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B62="",C62="",D62="",E62="",F62=""),"",IF(OR(B62="",C62="",E62=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E62)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H62&lt;&gt;0,F62=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G62&lt;&gt;0,F62=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F62&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F62)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C62)*($E$5:$E$504=E62)*(($D$5:$D$504=D62)*(D62&lt;&gt;"")+($B$5:$B$504=B62)*(B62&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J62" s="5">
@@ -2185,11 +2213,11 @@
         <v/>
       </c>
       <c r="H63" s="5">
-        <f>IF(OR(C63="Удержание",C63="Зачёт встречного требования",C63="Неустойка заявлена"),N(E63),0)</f>
+        <f>IF(OR(C63="Удержание",C63="Зачёт встречного требования",C63="Неустойка заявлена",C63="Допработы без соглашения (спорно)"),N(E63),0)</f>
         <v/>
       </c>
       <c r="I63" s="6">
-        <f>IF(AND(B63="",C63="",D63="",E63="",F63=""),"",IF(OR(B63="",C63="",E63=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E63)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G63&lt;&gt;0,F63=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F63&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F63)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C63)*($E$5:$E$504=E63)*(($D$5:$D$504=D63)*(D63&lt;&gt;"")+($B$5:$B$504=B63)*(B63&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B63="",C63="",D63="",E63="",F63=""),"",IF(OR(B63="",C63="",E63=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E63)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H63&lt;&gt;0,F63=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G63&lt;&gt;0,F63=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F63&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F63)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C63)*($E$5:$E$504=E63)*(($D$5:$D$504=D63)*(D63&lt;&gt;"")+($B$5:$B$504=B63)*(B63&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J63" s="5">
@@ -2211,11 +2239,11 @@
         <v/>
       </c>
       <c r="H64" s="5">
-        <f>IF(OR(C64="Удержание",C64="Зачёт встречного требования",C64="Неустойка заявлена"),N(E64),0)</f>
+        <f>IF(OR(C64="Удержание",C64="Зачёт встречного требования",C64="Неустойка заявлена",C64="Допработы без соглашения (спорно)"),N(E64),0)</f>
         <v/>
       </c>
       <c r="I64" s="6">
-        <f>IF(AND(B64="",C64="",D64="",E64="",F64=""),"",IF(OR(B64="",C64="",E64=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E64)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G64&lt;&gt;0,F64=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F64&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F64)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C64)*($E$5:$E$504=E64)*(($D$5:$D$504=D64)*(D64&lt;&gt;"")+($B$5:$B$504=B64)*(B64&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B64="",C64="",D64="",E64="",F64=""),"",IF(OR(B64="",C64="",E64=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E64)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H64&lt;&gt;0,F64=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G64&lt;&gt;0,F64=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F64&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F64)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C64)*($E$5:$E$504=E64)*(($D$5:$D$504=D64)*(D64&lt;&gt;"")+($B$5:$B$504=B64)*(B64&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J64" s="5">
@@ -2237,11 +2265,11 @@
         <v/>
       </c>
       <c r="H65" s="5">
-        <f>IF(OR(C65="Удержание",C65="Зачёт встречного требования",C65="Неустойка заявлена"),N(E65),0)</f>
+        <f>IF(OR(C65="Удержание",C65="Зачёт встречного требования",C65="Неустойка заявлена",C65="Допработы без соглашения (спорно)"),N(E65),0)</f>
         <v/>
       </c>
       <c r="I65" s="6">
-        <f>IF(AND(B65="",C65="",D65="",E65="",F65=""),"",IF(OR(B65="",C65="",E65=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E65)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G65&lt;&gt;0,F65=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F65&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F65)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C65)*($E$5:$E$504=E65)*(($D$5:$D$504=D65)*(D65&lt;&gt;"")+($B$5:$B$504=B65)*(B65&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B65="",C65="",D65="",E65="",F65=""),"",IF(OR(B65="",C65="",E65=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E65)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H65&lt;&gt;0,F65=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G65&lt;&gt;0,F65=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F65&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F65)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C65)*($E$5:$E$504=E65)*(($D$5:$D$504=D65)*(D65&lt;&gt;"")+($B$5:$B$504=B65)*(B65&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J65" s="5">
@@ -2263,11 +2291,11 @@
         <v/>
       </c>
       <c r="H66" s="5">
-        <f>IF(OR(C66="Удержание",C66="Зачёт встречного требования",C66="Неустойка заявлена"),N(E66),0)</f>
+        <f>IF(OR(C66="Удержание",C66="Зачёт встречного требования",C66="Неустойка заявлена",C66="Допработы без соглашения (спорно)"),N(E66),0)</f>
         <v/>
       </c>
       <c r="I66" s="6">
-        <f>IF(AND(B66="",C66="",D66="",E66="",F66=""),"",IF(OR(B66="",C66="",E66=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E66)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G66&lt;&gt;0,F66=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F66&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F66)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C66)*($E$5:$E$504=E66)*(($D$5:$D$504=D66)*(D66&lt;&gt;"")+($B$5:$B$504=B66)*(B66&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B66="",C66="",D66="",E66="",F66=""),"",IF(OR(B66="",C66="",E66=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E66)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H66&lt;&gt;0,F66=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G66&lt;&gt;0,F66=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F66&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F66)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C66)*($E$5:$E$504=E66)*(($D$5:$D$504=D66)*(D66&lt;&gt;"")+($B$5:$B$504=B66)*(B66&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J66" s="5">
@@ -2289,11 +2317,11 @@
         <v/>
       </c>
       <c r="H67" s="5">
-        <f>IF(OR(C67="Удержание",C67="Зачёт встречного требования",C67="Неустойка заявлена"),N(E67),0)</f>
+        <f>IF(OR(C67="Удержание",C67="Зачёт встречного требования",C67="Неустойка заявлена",C67="Допработы без соглашения (спорно)"),N(E67),0)</f>
         <v/>
       </c>
       <c r="I67" s="6">
-        <f>IF(AND(B67="",C67="",D67="",E67="",F67=""),"",IF(OR(B67="",C67="",E67=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E67)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G67&lt;&gt;0,F67=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F67&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F67)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C67)*($E$5:$E$504=E67)*(($D$5:$D$504=D67)*(D67&lt;&gt;"")+($B$5:$B$504=B67)*(B67&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B67="",C67="",D67="",E67="",F67=""),"",IF(OR(B67="",C67="",E67=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E67)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H67&lt;&gt;0,F67=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G67&lt;&gt;0,F67=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F67&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F67)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C67)*($E$5:$E$504=E67)*(($D$5:$D$504=D67)*(D67&lt;&gt;"")+($B$5:$B$504=B67)*(B67&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J67" s="5">
@@ -2315,11 +2343,11 @@
         <v/>
       </c>
       <c r="H68" s="5">
-        <f>IF(OR(C68="Удержание",C68="Зачёт встречного требования",C68="Неустойка заявлена"),N(E68),0)</f>
+        <f>IF(OR(C68="Удержание",C68="Зачёт встречного требования",C68="Неустойка заявлена",C68="Допработы без соглашения (спорно)"),N(E68),0)</f>
         <v/>
       </c>
       <c r="I68" s="6">
-        <f>IF(AND(B68="",C68="",D68="",E68="",F68=""),"",IF(OR(B68="",C68="",E68=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E68)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G68&lt;&gt;0,F68=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F68&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F68)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C68)*($E$5:$E$504=E68)*(($D$5:$D$504=D68)*(D68&lt;&gt;"")+($B$5:$B$504=B68)*(B68&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B68="",C68="",D68="",E68="",F68=""),"",IF(OR(B68="",C68="",E68=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E68)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H68&lt;&gt;0,F68=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G68&lt;&gt;0,F68=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F68&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F68)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C68)*($E$5:$E$504=E68)*(($D$5:$D$504=D68)*(D68&lt;&gt;"")+($B$5:$B$504=B68)*(B68&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J68" s="5">
@@ -2341,11 +2369,11 @@
         <v/>
       </c>
       <c r="H69" s="5">
-        <f>IF(OR(C69="Удержание",C69="Зачёт встречного требования",C69="Неустойка заявлена"),N(E69),0)</f>
+        <f>IF(OR(C69="Удержание",C69="Зачёт встречного требования",C69="Неустойка заявлена",C69="Допработы без соглашения (спорно)"),N(E69),0)</f>
         <v/>
       </c>
       <c r="I69" s="6">
-        <f>IF(AND(B69="",C69="",D69="",E69="",F69=""),"",IF(OR(B69="",C69="",E69=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E69)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G69&lt;&gt;0,F69=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F69&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F69)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C69)*($E$5:$E$504=E69)*(($D$5:$D$504=D69)*(D69&lt;&gt;"")+($B$5:$B$504=B69)*(B69&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B69="",C69="",D69="",E69="",F69=""),"",IF(OR(B69="",C69="",E69=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E69)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H69&lt;&gt;0,F69=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G69&lt;&gt;0,F69=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F69&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F69)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C69)*($E$5:$E$504=E69)*(($D$5:$D$504=D69)*(D69&lt;&gt;"")+($B$5:$B$504=B69)*(B69&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J69" s="5">
@@ -2367,11 +2395,11 @@
         <v/>
       </c>
       <c r="H70" s="5">
-        <f>IF(OR(C70="Удержание",C70="Зачёт встречного требования",C70="Неустойка заявлена"),N(E70),0)</f>
+        <f>IF(OR(C70="Удержание",C70="Зачёт встречного требования",C70="Неустойка заявлена",C70="Допработы без соглашения (спорно)"),N(E70),0)</f>
         <v/>
       </c>
       <c r="I70" s="6">
-        <f>IF(AND(B70="",C70="",D70="",E70="",F70=""),"",IF(OR(B70="",C70="",E70=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E70)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G70&lt;&gt;0,F70=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F70&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F70)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C70)*($E$5:$E$504=E70)*(($D$5:$D$504=D70)*(D70&lt;&gt;"")+($B$5:$B$504=B70)*(B70&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B70="",C70="",D70="",E70="",F70=""),"",IF(OR(B70="",C70="",E70=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E70)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H70&lt;&gt;0,F70=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G70&lt;&gt;0,F70=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F70&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F70)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C70)*($E$5:$E$504=E70)*(($D$5:$D$504=D70)*(D70&lt;&gt;"")+($B$5:$B$504=B70)*(B70&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J70" s="5">
@@ -2393,11 +2421,11 @@
         <v/>
       </c>
       <c r="H71" s="5">
-        <f>IF(OR(C71="Удержание",C71="Зачёт встречного требования",C71="Неустойка заявлена"),N(E71),0)</f>
+        <f>IF(OR(C71="Удержание",C71="Зачёт встречного требования",C71="Неустойка заявлена",C71="Допработы без соглашения (спорно)"),N(E71),0)</f>
         <v/>
       </c>
       <c r="I71" s="6">
-        <f>IF(AND(B71="",C71="",D71="",E71="",F71=""),"",IF(OR(B71="",C71="",E71=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E71)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G71&lt;&gt;0,F71=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F71&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F71)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C71)*($E$5:$E$504=E71)*(($D$5:$D$504=D71)*(D71&lt;&gt;"")+($B$5:$B$504=B71)*(B71&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B71="",C71="",D71="",E71="",F71=""),"",IF(OR(B71="",C71="",E71=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E71)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H71&lt;&gt;0,F71=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G71&lt;&gt;0,F71=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F71&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F71)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C71)*($E$5:$E$504=E71)*(($D$5:$D$504=D71)*(D71&lt;&gt;"")+($B$5:$B$504=B71)*(B71&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J71" s="5">
@@ -2419,11 +2447,11 @@
         <v/>
       </c>
       <c r="H72" s="5">
-        <f>IF(OR(C72="Удержание",C72="Зачёт встречного требования",C72="Неустойка заявлена"),N(E72),0)</f>
+        <f>IF(OR(C72="Удержание",C72="Зачёт встречного требования",C72="Неустойка заявлена",C72="Допработы без соглашения (спорно)"),N(E72),0)</f>
         <v/>
       </c>
       <c r="I72" s="6">
-        <f>IF(AND(B72="",C72="",D72="",E72="",F72=""),"",IF(OR(B72="",C72="",E72=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E72)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G72&lt;&gt;0,F72=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F72&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F72)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C72)*($E$5:$E$504=E72)*(($D$5:$D$504=D72)*(D72&lt;&gt;"")+($B$5:$B$504=B72)*(B72&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B72="",C72="",D72="",E72="",F72=""),"",IF(OR(B72="",C72="",E72=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E72)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H72&lt;&gt;0,F72=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G72&lt;&gt;0,F72=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F72&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F72)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C72)*($E$5:$E$504=E72)*(($D$5:$D$504=D72)*(D72&lt;&gt;"")+($B$5:$B$504=B72)*(B72&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J72" s="5">
@@ -2445,11 +2473,11 @@
         <v/>
       </c>
       <c r="H73" s="5">
-        <f>IF(OR(C73="Удержание",C73="Зачёт встречного требования",C73="Неустойка заявлена"),N(E73),0)</f>
+        <f>IF(OR(C73="Удержание",C73="Зачёт встречного требования",C73="Неустойка заявлена",C73="Допработы без соглашения (спорно)"),N(E73),0)</f>
         <v/>
       </c>
       <c r="I73" s="6">
-        <f>IF(AND(B73="",C73="",D73="",E73="",F73=""),"",IF(OR(B73="",C73="",E73=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E73)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G73&lt;&gt;0,F73=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F73&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F73)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C73)*($E$5:$E$504=E73)*(($D$5:$D$504=D73)*(D73&lt;&gt;"")+($B$5:$B$504=B73)*(B73&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B73="",C73="",D73="",E73="",F73=""),"",IF(OR(B73="",C73="",E73=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E73)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H73&lt;&gt;0,F73=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G73&lt;&gt;0,F73=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F73&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F73)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C73)*($E$5:$E$504=E73)*(($D$5:$D$504=D73)*(D73&lt;&gt;"")+($B$5:$B$504=B73)*(B73&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J73" s="5">
@@ -2471,11 +2499,11 @@
         <v/>
       </c>
       <c r="H74" s="5">
-        <f>IF(OR(C74="Удержание",C74="Зачёт встречного требования",C74="Неустойка заявлена"),N(E74),0)</f>
+        <f>IF(OR(C74="Удержание",C74="Зачёт встречного требования",C74="Неустойка заявлена",C74="Допработы без соглашения (спорно)"),N(E74),0)</f>
         <v/>
       </c>
       <c r="I74" s="6">
-        <f>IF(AND(B74="",C74="",D74="",E74="",F74=""),"",IF(OR(B74="",C74="",E74=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E74)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G74&lt;&gt;0,F74=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F74&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F74)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C74)*($E$5:$E$504=E74)*(($D$5:$D$504=D74)*(D74&lt;&gt;"")+($B$5:$B$504=B74)*(B74&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B74="",C74="",D74="",E74="",F74=""),"",IF(OR(B74="",C74="",E74=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E74)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H74&lt;&gt;0,F74=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G74&lt;&gt;0,F74=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F74&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F74)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C74)*($E$5:$E$504=E74)*(($D$5:$D$504=D74)*(D74&lt;&gt;"")+($B$5:$B$504=B74)*(B74&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J74" s="5">
@@ -2497,11 +2525,11 @@
         <v/>
       </c>
       <c r="H75" s="5">
-        <f>IF(OR(C75="Удержание",C75="Зачёт встречного требования",C75="Неустойка заявлена"),N(E75),0)</f>
+        <f>IF(OR(C75="Удержание",C75="Зачёт встречного требования",C75="Неустойка заявлена",C75="Допработы без соглашения (спорно)"),N(E75),0)</f>
         <v/>
       </c>
       <c r="I75" s="6">
-        <f>IF(AND(B75="",C75="",D75="",E75="",F75=""),"",IF(OR(B75="",C75="",E75=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E75)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G75&lt;&gt;0,F75=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F75&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F75)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C75)*($E$5:$E$504=E75)*(($D$5:$D$504=D75)*(D75&lt;&gt;"")+($B$5:$B$504=B75)*(B75&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B75="",C75="",D75="",E75="",F75=""),"",IF(OR(B75="",C75="",E75=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E75)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H75&lt;&gt;0,F75=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G75&lt;&gt;0,F75=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F75&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F75)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C75)*($E$5:$E$504=E75)*(($D$5:$D$504=D75)*(D75&lt;&gt;"")+($B$5:$B$504=B75)*(B75&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J75" s="5">
@@ -2523,11 +2551,11 @@
         <v/>
       </c>
       <c r="H76" s="5">
-        <f>IF(OR(C76="Удержание",C76="Зачёт встречного требования",C76="Неустойка заявлена"),N(E76),0)</f>
+        <f>IF(OR(C76="Удержание",C76="Зачёт встречного требования",C76="Неустойка заявлена",C76="Допработы без соглашения (спорно)"),N(E76),0)</f>
         <v/>
       </c>
       <c r="I76" s="6">
-        <f>IF(AND(B76="",C76="",D76="",E76="",F76=""),"",IF(OR(B76="",C76="",E76=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E76)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G76&lt;&gt;0,F76=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F76&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F76)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C76)*($E$5:$E$504=E76)*(($D$5:$D$504=D76)*(D76&lt;&gt;"")+($B$5:$B$504=B76)*(B76&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B76="",C76="",D76="",E76="",F76=""),"",IF(OR(B76="",C76="",E76=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E76)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H76&lt;&gt;0,F76=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G76&lt;&gt;0,F76=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F76&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F76)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C76)*($E$5:$E$504=E76)*(($D$5:$D$504=D76)*(D76&lt;&gt;"")+($B$5:$B$504=B76)*(B76&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J76" s="5">
@@ -2549,11 +2577,11 @@
         <v/>
       </c>
       <c r="H77" s="5">
-        <f>IF(OR(C77="Удержание",C77="Зачёт встречного требования",C77="Неустойка заявлена"),N(E77),0)</f>
+        <f>IF(OR(C77="Удержание",C77="Зачёт встречного требования",C77="Неустойка заявлена",C77="Допработы без соглашения (спорно)"),N(E77),0)</f>
         <v/>
       </c>
       <c r="I77" s="6">
-        <f>IF(AND(B77="",C77="",D77="",E77="",F77=""),"",IF(OR(B77="",C77="",E77=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E77)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G77&lt;&gt;0,F77=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F77&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F77)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C77)*($E$5:$E$504=E77)*(($D$5:$D$504=D77)*(D77&lt;&gt;"")+($B$5:$B$504=B77)*(B77&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B77="",C77="",D77="",E77="",F77=""),"",IF(OR(B77="",C77="",E77=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E77)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H77&lt;&gt;0,F77=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G77&lt;&gt;0,F77=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F77&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F77)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C77)*($E$5:$E$504=E77)*(($D$5:$D$504=D77)*(D77&lt;&gt;"")+($B$5:$B$504=B77)*(B77&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J77" s="5">
@@ -2575,11 +2603,11 @@
         <v/>
       </c>
       <c r="H78" s="5">
-        <f>IF(OR(C78="Удержание",C78="Зачёт встречного требования",C78="Неустойка заявлена"),N(E78),0)</f>
+        <f>IF(OR(C78="Удержание",C78="Зачёт встречного требования",C78="Неустойка заявлена",C78="Допработы без соглашения (спорно)"),N(E78),0)</f>
         <v/>
       </c>
       <c r="I78" s="6">
-        <f>IF(AND(B78="",C78="",D78="",E78="",F78=""),"",IF(OR(B78="",C78="",E78=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E78)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G78&lt;&gt;0,F78=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F78&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F78)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C78)*($E$5:$E$504=E78)*(($D$5:$D$504=D78)*(D78&lt;&gt;"")+($B$5:$B$504=B78)*(B78&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B78="",C78="",D78="",E78="",F78=""),"",IF(OR(B78="",C78="",E78=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E78)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H78&lt;&gt;0,F78=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G78&lt;&gt;0,F78=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F78&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F78)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C78)*($E$5:$E$504=E78)*(($D$5:$D$504=D78)*(D78&lt;&gt;"")+($B$5:$B$504=B78)*(B78&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J78" s="5">
@@ -2601,11 +2629,11 @@
         <v/>
       </c>
       <c r="H79" s="5">
-        <f>IF(OR(C79="Удержание",C79="Зачёт встречного требования",C79="Неустойка заявлена"),N(E79),0)</f>
+        <f>IF(OR(C79="Удержание",C79="Зачёт встречного требования",C79="Неустойка заявлена",C79="Допработы без соглашения (спорно)"),N(E79),0)</f>
         <v/>
       </c>
       <c r="I79" s="6">
-        <f>IF(AND(B79="",C79="",D79="",E79="",F79=""),"",IF(OR(B79="",C79="",E79=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E79)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G79&lt;&gt;0,F79=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F79&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F79)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C79)*($E$5:$E$504=E79)*(($D$5:$D$504=D79)*(D79&lt;&gt;"")+($B$5:$B$504=B79)*(B79&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B79="",C79="",D79="",E79="",F79=""),"",IF(OR(B79="",C79="",E79=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E79)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H79&lt;&gt;0,F79=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G79&lt;&gt;0,F79=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F79&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F79)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C79)*($E$5:$E$504=E79)*(($D$5:$D$504=D79)*(D79&lt;&gt;"")+($B$5:$B$504=B79)*(B79&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J79" s="5">
@@ -2627,11 +2655,11 @@
         <v/>
       </c>
       <c r="H80" s="5">
-        <f>IF(OR(C80="Удержание",C80="Зачёт встречного требования",C80="Неустойка заявлена"),N(E80),0)</f>
+        <f>IF(OR(C80="Удержание",C80="Зачёт встречного требования",C80="Неустойка заявлена",C80="Допработы без соглашения (спорно)"),N(E80),0)</f>
         <v/>
       </c>
       <c r="I80" s="6">
-        <f>IF(AND(B80="",C80="",D80="",E80="",F80=""),"",IF(OR(B80="",C80="",E80=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E80)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G80&lt;&gt;0,F80=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F80&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F80)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C80)*($E$5:$E$504=E80)*(($D$5:$D$504=D80)*(D80&lt;&gt;"")+($B$5:$B$504=B80)*(B80&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B80="",C80="",D80="",E80="",F80=""),"",IF(OR(B80="",C80="",E80=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E80)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H80&lt;&gt;0,F80=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G80&lt;&gt;0,F80=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F80&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F80)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C80)*($E$5:$E$504=E80)*(($D$5:$D$504=D80)*(D80&lt;&gt;"")+($B$5:$B$504=B80)*(B80&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J80" s="5">
@@ -2653,11 +2681,11 @@
         <v/>
       </c>
       <c r="H81" s="5">
-        <f>IF(OR(C81="Удержание",C81="Зачёт встречного требования",C81="Неустойка заявлена"),N(E81),0)</f>
+        <f>IF(OR(C81="Удержание",C81="Зачёт встречного требования",C81="Неустойка заявлена",C81="Допработы без соглашения (спорно)"),N(E81),0)</f>
         <v/>
       </c>
       <c r="I81" s="6">
-        <f>IF(AND(B81="",C81="",D81="",E81="",F81=""),"",IF(OR(B81="",C81="",E81=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E81)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G81&lt;&gt;0,F81=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F81&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F81)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C81)*($E$5:$E$504=E81)*(($D$5:$D$504=D81)*(D81&lt;&gt;"")+($B$5:$B$504=B81)*(B81&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B81="",C81="",D81="",E81="",F81=""),"",IF(OR(B81="",C81="",E81=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E81)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H81&lt;&gt;0,F81=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G81&lt;&gt;0,F81=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F81&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F81)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C81)*($E$5:$E$504=E81)*(($D$5:$D$504=D81)*(D81&lt;&gt;"")+($B$5:$B$504=B81)*(B81&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J81" s="5">
@@ -2679,11 +2707,11 @@
         <v/>
       </c>
       <c r="H82" s="5">
-        <f>IF(OR(C82="Удержание",C82="Зачёт встречного требования",C82="Неустойка заявлена"),N(E82),0)</f>
+        <f>IF(OR(C82="Удержание",C82="Зачёт встречного требования",C82="Неустойка заявлена",C82="Допработы без соглашения (спорно)"),N(E82),0)</f>
         <v/>
       </c>
       <c r="I82" s="6">
-        <f>IF(AND(B82="",C82="",D82="",E82="",F82=""),"",IF(OR(B82="",C82="",E82=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E82)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G82&lt;&gt;0,F82=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F82&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F82)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C82)*($E$5:$E$504=E82)*(($D$5:$D$504=D82)*(D82&lt;&gt;"")+($B$5:$B$504=B82)*(B82&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B82="",C82="",D82="",E82="",F82=""),"",IF(OR(B82="",C82="",E82=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E82)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H82&lt;&gt;0,F82=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G82&lt;&gt;0,F82=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F82&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F82)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C82)*($E$5:$E$504=E82)*(($D$5:$D$504=D82)*(D82&lt;&gt;"")+($B$5:$B$504=B82)*(B82&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J82" s="5">
@@ -2705,11 +2733,11 @@
         <v/>
       </c>
       <c r="H83" s="5">
-        <f>IF(OR(C83="Удержание",C83="Зачёт встречного требования",C83="Неустойка заявлена"),N(E83),0)</f>
+        <f>IF(OR(C83="Удержание",C83="Зачёт встречного требования",C83="Неустойка заявлена",C83="Допработы без соглашения (спорно)"),N(E83),0)</f>
         <v/>
       </c>
       <c r="I83" s="6">
-        <f>IF(AND(B83="",C83="",D83="",E83="",F83=""),"",IF(OR(B83="",C83="",E83=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E83)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G83&lt;&gt;0,F83=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F83&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F83)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C83)*($E$5:$E$504=E83)*(($D$5:$D$504=D83)*(D83&lt;&gt;"")+($B$5:$B$504=B83)*(B83&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B83="",C83="",D83="",E83="",F83=""),"",IF(OR(B83="",C83="",E83=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E83)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H83&lt;&gt;0,F83=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G83&lt;&gt;0,F83=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F83&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F83)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C83)*($E$5:$E$504=E83)*(($D$5:$D$504=D83)*(D83&lt;&gt;"")+($B$5:$B$504=B83)*(B83&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J83" s="5">
@@ -2731,11 +2759,11 @@
         <v/>
       </c>
       <c r="H84" s="5">
-        <f>IF(OR(C84="Удержание",C84="Зачёт встречного требования",C84="Неустойка заявлена"),N(E84),0)</f>
+        <f>IF(OR(C84="Удержание",C84="Зачёт встречного требования",C84="Неустойка заявлена",C84="Допработы без соглашения (спорно)"),N(E84),0)</f>
         <v/>
       </c>
       <c r="I84" s="6">
-        <f>IF(AND(B84="",C84="",D84="",E84="",F84=""),"",IF(OR(B84="",C84="",E84=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E84)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G84&lt;&gt;0,F84=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F84&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F84)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C84)*($E$5:$E$504=E84)*(($D$5:$D$504=D84)*(D84&lt;&gt;"")+($B$5:$B$504=B84)*(B84&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B84="",C84="",D84="",E84="",F84=""),"",IF(OR(B84="",C84="",E84=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E84)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H84&lt;&gt;0,F84=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G84&lt;&gt;0,F84=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F84&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F84)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C84)*($E$5:$E$504=E84)*(($D$5:$D$504=D84)*(D84&lt;&gt;"")+($B$5:$B$504=B84)*(B84&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J84" s="5">
@@ -2757,11 +2785,11 @@
         <v/>
       </c>
       <c r="H85" s="5">
-        <f>IF(OR(C85="Удержание",C85="Зачёт встречного требования",C85="Неустойка заявлена"),N(E85),0)</f>
+        <f>IF(OR(C85="Удержание",C85="Зачёт встречного требования",C85="Неустойка заявлена",C85="Допработы без соглашения (спорно)"),N(E85),0)</f>
         <v/>
       </c>
       <c r="I85" s="6">
-        <f>IF(AND(B85="",C85="",D85="",E85="",F85=""),"",IF(OR(B85="",C85="",E85=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E85)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G85&lt;&gt;0,F85=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F85&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F85)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C85)*($E$5:$E$504=E85)*(($D$5:$D$504=D85)*(D85&lt;&gt;"")+($B$5:$B$504=B85)*(B85&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B85="",C85="",D85="",E85="",F85=""),"",IF(OR(B85="",C85="",E85=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E85)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H85&lt;&gt;0,F85=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G85&lt;&gt;0,F85=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F85&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F85)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C85)*($E$5:$E$504=E85)*(($D$5:$D$504=D85)*(D85&lt;&gt;"")+($B$5:$B$504=B85)*(B85&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J85" s="5">
@@ -2783,11 +2811,11 @@
         <v/>
       </c>
       <c r="H86" s="5">
-        <f>IF(OR(C86="Удержание",C86="Зачёт встречного требования",C86="Неустойка заявлена"),N(E86),0)</f>
+        <f>IF(OR(C86="Удержание",C86="Зачёт встречного требования",C86="Неустойка заявлена",C86="Допработы без соглашения (спорно)"),N(E86),0)</f>
         <v/>
       </c>
       <c r="I86" s="6">
-        <f>IF(AND(B86="",C86="",D86="",E86="",F86=""),"",IF(OR(B86="",C86="",E86=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E86)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G86&lt;&gt;0,F86=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F86&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F86)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C86)*($E$5:$E$504=E86)*(($D$5:$D$504=D86)*(D86&lt;&gt;"")+($B$5:$B$504=B86)*(B86&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B86="",C86="",D86="",E86="",F86=""),"",IF(OR(B86="",C86="",E86=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E86)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H86&lt;&gt;0,F86=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G86&lt;&gt;0,F86=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F86&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F86)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C86)*($E$5:$E$504=E86)*(($D$5:$D$504=D86)*(D86&lt;&gt;"")+($B$5:$B$504=B86)*(B86&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J86" s="5">
@@ -2809,11 +2837,11 @@
         <v/>
       </c>
       <c r="H87" s="5">
-        <f>IF(OR(C87="Удержание",C87="Зачёт встречного требования",C87="Неустойка заявлена"),N(E87),0)</f>
+        <f>IF(OR(C87="Удержание",C87="Зачёт встречного требования",C87="Неустойка заявлена",C87="Допработы без соглашения (спорно)"),N(E87),0)</f>
         <v/>
       </c>
       <c r="I87" s="6">
-        <f>IF(AND(B87="",C87="",D87="",E87="",F87=""),"",IF(OR(B87="",C87="",E87=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E87)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G87&lt;&gt;0,F87=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F87&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F87)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C87)*($E$5:$E$504=E87)*(($D$5:$D$504=D87)*(D87&lt;&gt;"")+($B$5:$B$504=B87)*(B87&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B87="",C87="",D87="",E87="",F87=""),"",IF(OR(B87="",C87="",E87=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E87)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H87&lt;&gt;0,F87=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G87&lt;&gt;0,F87=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F87&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F87)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C87)*($E$5:$E$504=E87)*(($D$5:$D$504=D87)*(D87&lt;&gt;"")+($B$5:$B$504=B87)*(B87&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J87" s="5">
@@ -2835,11 +2863,11 @@
         <v/>
       </c>
       <c r="H88" s="5">
-        <f>IF(OR(C88="Удержание",C88="Зачёт встречного требования",C88="Неустойка заявлена"),N(E88),0)</f>
+        <f>IF(OR(C88="Удержание",C88="Зачёт встречного требования",C88="Неустойка заявлена",C88="Допработы без соглашения (спорно)"),N(E88),0)</f>
         <v/>
       </c>
       <c r="I88" s="6">
-        <f>IF(AND(B88="",C88="",D88="",E88="",F88=""),"",IF(OR(B88="",C88="",E88=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E88)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G88&lt;&gt;0,F88=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F88&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F88)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C88)*($E$5:$E$504=E88)*(($D$5:$D$504=D88)*(D88&lt;&gt;"")+($B$5:$B$504=B88)*(B88&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B88="",C88="",D88="",E88="",F88=""),"",IF(OR(B88="",C88="",E88=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E88)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H88&lt;&gt;0,F88=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G88&lt;&gt;0,F88=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F88&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F88)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C88)*($E$5:$E$504=E88)*(($D$5:$D$504=D88)*(D88&lt;&gt;"")+($B$5:$B$504=B88)*(B88&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J88" s="5">
@@ -2861,11 +2889,11 @@
         <v/>
       </c>
       <c r="H89" s="5">
-        <f>IF(OR(C89="Удержание",C89="Зачёт встречного требования",C89="Неустойка заявлена"),N(E89),0)</f>
+        <f>IF(OR(C89="Удержание",C89="Зачёт встречного требования",C89="Неустойка заявлена",C89="Допработы без соглашения (спорно)"),N(E89),0)</f>
         <v/>
       </c>
       <c r="I89" s="6">
-        <f>IF(AND(B89="",C89="",D89="",E89="",F89=""),"",IF(OR(B89="",C89="",E89=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E89)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G89&lt;&gt;0,F89=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F89&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F89)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C89)*($E$5:$E$504=E89)*(($D$5:$D$504=D89)*(D89&lt;&gt;"")+($B$5:$B$504=B89)*(B89&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B89="",C89="",D89="",E89="",F89=""),"",IF(OR(B89="",C89="",E89=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E89)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H89&lt;&gt;0,F89=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G89&lt;&gt;0,F89=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F89&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F89)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C89)*($E$5:$E$504=E89)*(($D$5:$D$504=D89)*(D89&lt;&gt;"")+($B$5:$B$504=B89)*(B89&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J89" s="5">
@@ -2887,11 +2915,11 @@
         <v/>
       </c>
       <c r="H90" s="5">
-        <f>IF(OR(C90="Удержание",C90="Зачёт встречного требования",C90="Неустойка заявлена"),N(E90),0)</f>
+        <f>IF(OR(C90="Удержание",C90="Зачёт встречного требования",C90="Неустойка заявлена",C90="Допработы без соглашения (спорно)"),N(E90),0)</f>
         <v/>
       </c>
       <c r="I90" s="6">
-        <f>IF(AND(B90="",C90="",D90="",E90="",F90=""),"",IF(OR(B90="",C90="",E90=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E90)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G90&lt;&gt;0,F90=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F90&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F90)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C90)*($E$5:$E$504=E90)*(($D$5:$D$504=D90)*(D90&lt;&gt;"")+($B$5:$B$504=B90)*(B90&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B90="",C90="",D90="",E90="",F90=""),"",IF(OR(B90="",C90="",E90=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E90)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H90&lt;&gt;0,F90=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G90&lt;&gt;0,F90=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F90&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F90)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C90)*($E$5:$E$504=E90)*(($D$5:$D$504=D90)*(D90&lt;&gt;"")+($B$5:$B$504=B90)*(B90&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J90" s="5">
@@ -2913,11 +2941,11 @@
         <v/>
       </c>
       <c r="H91" s="5">
-        <f>IF(OR(C91="Удержание",C91="Зачёт встречного требования",C91="Неустойка заявлена"),N(E91),0)</f>
+        <f>IF(OR(C91="Удержание",C91="Зачёт встречного требования",C91="Неустойка заявлена",C91="Допработы без соглашения (спорно)"),N(E91),0)</f>
         <v/>
       </c>
       <c r="I91" s="6">
-        <f>IF(AND(B91="",C91="",D91="",E91="",F91=""),"",IF(OR(B91="",C91="",E91=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E91)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G91&lt;&gt;0,F91=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F91&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F91)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C91)*($E$5:$E$504=E91)*(($D$5:$D$504=D91)*(D91&lt;&gt;"")+($B$5:$B$504=B91)*(B91&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B91="",C91="",D91="",E91="",F91=""),"",IF(OR(B91="",C91="",E91=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E91)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H91&lt;&gt;0,F91=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G91&lt;&gt;0,F91=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F91&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F91)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C91)*($E$5:$E$504=E91)*(($D$5:$D$504=D91)*(D91&lt;&gt;"")+($B$5:$B$504=B91)*(B91&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J91" s="5">
@@ -2939,11 +2967,11 @@
         <v/>
       </c>
       <c r="H92" s="5">
-        <f>IF(OR(C92="Удержание",C92="Зачёт встречного требования",C92="Неустойка заявлена"),N(E92),0)</f>
+        <f>IF(OR(C92="Удержание",C92="Зачёт встречного требования",C92="Неустойка заявлена",C92="Допработы без соглашения (спорно)"),N(E92),0)</f>
         <v/>
       </c>
       <c r="I92" s="6">
-        <f>IF(AND(B92="",C92="",D92="",E92="",F92=""),"",IF(OR(B92="",C92="",E92=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E92)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G92&lt;&gt;0,F92=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F92&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F92)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C92)*($E$5:$E$504=E92)*(($D$5:$D$504=D92)*(D92&lt;&gt;"")+($B$5:$B$504=B92)*(B92&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B92="",C92="",D92="",E92="",F92=""),"",IF(OR(B92="",C92="",E92=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E92)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H92&lt;&gt;0,F92=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G92&lt;&gt;0,F92=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F92&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F92)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C92)*($E$5:$E$504=E92)*(($D$5:$D$504=D92)*(D92&lt;&gt;"")+($B$5:$B$504=B92)*(B92&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J92" s="5">
@@ -2965,11 +2993,11 @@
         <v/>
       </c>
       <c r="H93" s="5">
-        <f>IF(OR(C93="Удержание",C93="Зачёт встречного требования",C93="Неустойка заявлена"),N(E93),0)</f>
+        <f>IF(OR(C93="Удержание",C93="Зачёт встречного требования",C93="Неустойка заявлена",C93="Допработы без соглашения (спорно)"),N(E93),0)</f>
         <v/>
       </c>
       <c r="I93" s="6">
-        <f>IF(AND(B93="",C93="",D93="",E93="",F93=""),"",IF(OR(B93="",C93="",E93=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E93)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G93&lt;&gt;0,F93=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F93&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F93)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C93)*($E$5:$E$504=E93)*(($D$5:$D$504=D93)*(D93&lt;&gt;"")+($B$5:$B$504=B93)*(B93&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B93="",C93="",D93="",E93="",F93=""),"",IF(OR(B93="",C93="",E93=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E93)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H93&lt;&gt;0,F93=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G93&lt;&gt;0,F93=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F93&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F93)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C93)*($E$5:$E$504=E93)*(($D$5:$D$504=D93)*(D93&lt;&gt;"")+($B$5:$B$504=B93)*(B93&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J93" s="5">
@@ -2991,11 +3019,11 @@
         <v/>
       </c>
       <c r="H94" s="5">
-        <f>IF(OR(C94="Удержание",C94="Зачёт встречного требования",C94="Неустойка заявлена"),N(E94),0)</f>
+        <f>IF(OR(C94="Удержание",C94="Зачёт встречного требования",C94="Неустойка заявлена",C94="Допработы без соглашения (спорно)"),N(E94),0)</f>
         <v/>
       </c>
       <c r="I94" s="6">
-        <f>IF(AND(B94="",C94="",D94="",E94="",F94=""),"",IF(OR(B94="",C94="",E94=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E94)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G94&lt;&gt;0,F94=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F94&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F94)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C94)*($E$5:$E$504=E94)*(($D$5:$D$504=D94)*(D94&lt;&gt;"")+($B$5:$B$504=B94)*(B94&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B94="",C94="",D94="",E94="",F94=""),"",IF(OR(B94="",C94="",E94=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E94)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H94&lt;&gt;0,F94=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G94&lt;&gt;0,F94=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F94&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F94)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C94)*($E$5:$E$504=E94)*(($D$5:$D$504=D94)*(D94&lt;&gt;"")+($B$5:$B$504=B94)*(B94&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J94" s="5">
@@ -3017,11 +3045,11 @@
         <v/>
       </c>
       <c r="H95" s="5">
-        <f>IF(OR(C95="Удержание",C95="Зачёт встречного требования",C95="Неустойка заявлена"),N(E95),0)</f>
+        <f>IF(OR(C95="Удержание",C95="Зачёт встречного требования",C95="Неустойка заявлена",C95="Допработы без соглашения (спорно)"),N(E95),0)</f>
         <v/>
       </c>
       <c r="I95" s="6">
-        <f>IF(AND(B95="",C95="",D95="",E95="",F95=""),"",IF(OR(B95="",C95="",E95=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E95)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G95&lt;&gt;0,F95=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F95&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F95)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C95)*($E$5:$E$504=E95)*(($D$5:$D$504=D95)*(D95&lt;&gt;"")+($B$5:$B$504=B95)*(B95&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B95="",C95="",D95="",E95="",F95=""),"",IF(OR(B95="",C95="",E95=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E95)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H95&lt;&gt;0,F95=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G95&lt;&gt;0,F95=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F95&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F95)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C95)*($E$5:$E$504=E95)*(($D$5:$D$504=D95)*(D95&lt;&gt;"")+($B$5:$B$504=B95)*(B95&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J95" s="5">
@@ -3043,11 +3071,11 @@
         <v/>
       </c>
       <c r="H96" s="5">
-        <f>IF(OR(C96="Удержание",C96="Зачёт встречного требования",C96="Неустойка заявлена"),N(E96),0)</f>
+        <f>IF(OR(C96="Удержание",C96="Зачёт встречного требования",C96="Неустойка заявлена",C96="Допработы без соглашения (спорно)"),N(E96),0)</f>
         <v/>
       </c>
       <c r="I96" s="6">
-        <f>IF(AND(B96="",C96="",D96="",E96="",F96=""),"",IF(OR(B96="",C96="",E96=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E96)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G96&lt;&gt;0,F96=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F96&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F96)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C96)*($E$5:$E$504=E96)*(($D$5:$D$504=D96)*(D96&lt;&gt;"")+($B$5:$B$504=B96)*(B96&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B96="",C96="",D96="",E96="",F96=""),"",IF(OR(B96="",C96="",E96=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E96)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H96&lt;&gt;0,F96=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G96&lt;&gt;0,F96=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F96&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F96)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C96)*($E$5:$E$504=E96)*(($D$5:$D$504=D96)*(D96&lt;&gt;"")+($B$5:$B$504=B96)*(B96&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J96" s="5">
@@ -3069,11 +3097,11 @@
         <v/>
       </c>
       <c r="H97" s="5">
-        <f>IF(OR(C97="Удержание",C97="Зачёт встречного требования",C97="Неустойка заявлена"),N(E97),0)</f>
+        <f>IF(OR(C97="Удержание",C97="Зачёт встречного требования",C97="Неустойка заявлена",C97="Допработы без соглашения (спорно)"),N(E97),0)</f>
         <v/>
       </c>
       <c r="I97" s="6">
-        <f>IF(AND(B97="",C97="",D97="",E97="",F97=""),"",IF(OR(B97="",C97="",E97=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E97)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G97&lt;&gt;0,F97=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F97&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F97)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C97)*($E$5:$E$504=E97)*(($D$5:$D$504=D97)*(D97&lt;&gt;"")+($B$5:$B$504=B97)*(B97&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B97="",C97="",D97="",E97="",F97=""),"",IF(OR(B97="",C97="",E97=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E97)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H97&lt;&gt;0,F97=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G97&lt;&gt;0,F97=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F97&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F97)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C97)*($E$5:$E$504=E97)*(($D$5:$D$504=D97)*(D97&lt;&gt;"")+($B$5:$B$504=B97)*(B97&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J97" s="5">
@@ -3095,11 +3123,11 @@
         <v/>
       </c>
       <c r="H98" s="5">
-        <f>IF(OR(C98="Удержание",C98="Зачёт встречного требования",C98="Неустойка заявлена"),N(E98),0)</f>
+        <f>IF(OR(C98="Удержание",C98="Зачёт встречного требования",C98="Неустойка заявлена",C98="Допработы без соглашения (спорно)"),N(E98),0)</f>
         <v/>
       </c>
       <c r="I98" s="6">
-        <f>IF(AND(B98="",C98="",D98="",E98="",F98=""),"",IF(OR(B98="",C98="",E98=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E98)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G98&lt;&gt;0,F98=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F98&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F98)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C98)*($E$5:$E$504=E98)*(($D$5:$D$504=D98)*(D98&lt;&gt;"")+($B$5:$B$504=B98)*(B98&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B98="",C98="",D98="",E98="",F98=""),"",IF(OR(B98="",C98="",E98=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E98)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H98&lt;&gt;0,F98=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G98&lt;&gt;0,F98=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F98&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F98)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C98)*($E$5:$E$504=E98)*(($D$5:$D$504=D98)*(D98&lt;&gt;"")+($B$5:$B$504=B98)*(B98&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J98" s="5">
@@ -3121,11 +3149,11 @@
         <v/>
       </c>
       <c r="H99" s="5">
-        <f>IF(OR(C99="Удержание",C99="Зачёт встречного требования",C99="Неустойка заявлена"),N(E99),0)</f>
+        <f>IF(OR(C99="Удержание",C99="Зачёт встречного требования",C99="Неустойка заявлена",C99="Допработы без соглашения (спорно)"),N(E99),0)</f>
         <v/>
       </c>
       <c r="I99" s="6">
-        <f>IF(AND(B99="",C99="",D99="",E99="",F99=""),"",IF(OR(B99="",C99="",E99=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E99)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G99&lt;&gt;0,F99=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F99&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F99)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C99)*($E$5:$E$504=E99)*(($D$5:$D$504=D99)*(D99&lt;&gt;"")+($B$5:$B$504=B99)*(B99&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B99="",C99="",D99="",E99="",F99=""),"",IF(OR(B99="",C99="",E99=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E99)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H99&lt;&gt;0,F99=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G99&lt;&gt;0,F99=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F99&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F99)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C99)*($E$5:$E$504=E99)*(($D$5:$D$504=D99)*(D99&lt;&gt;"")+($B$5:$B$504=B99)*(B99&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J99" s="5">
@@ -3147,11 +3175,11 @@
         <v/>
       </c>
       <c r="H100" s="5">
-        <f>IF(OR(C100="Удержание",C100="Зачёт встречного требования",C100="Неустойка заявлена"),N(E100),0)</f>
+        <f>IF(OR(C100="Удержание",C100="Зачёт встречного требования",C100="Неустойка заявлена",C100="Допработы без соглашения (спорно)"),N(E100),0)</f>
         <v/>
       </c>
       <c r="I100" s="6">
-        <f>IF(AND(B100="",C100="",D100="",E100="",F100=""),"",IF(OR(B100="",C100="",E100=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E100)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G100&lt;&gt;0,F100=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F100&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F100)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C100)*($E$5:$E$504=E100)*(($D$5:$D$504=D100)*(D100&lt;&gt;"")+($B$5:$B$504=B100)*(B100&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B100="",C100="",D100="",E100="",F100=""),"",IF(OR(B100="",C100="",E100=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E100)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H100&lt;&gt;0,F100=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G100&lt;&gt;0,F100=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F100&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F100)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C100)*($E$5:$E$504=E100)*(($D$5:$D$504=D100)*(D100&lt;&gt;"")+($B$5:$B$504=B100)*(B100&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J100" s="5">
@@ -3173,11 +3201,11 @@
         <v/>
       </c>
       <c r="H101" s="5">
-        <f>IF(OR(C101="Удержание",C101="Зачёт встречного требования",C101="Неустойка заявлена"),N(E101),0)</f>
+        <f>IF(OR(C101="Удержание",C101="Зачёт встречного требования",C101="Неустойка заявлена",C101="Допработы без соглашения (спорно)"),N(E101),0)</f>
         <v/>
       </c>
       <c r="I101" s="6">
-        <f>IF(AND(B101="",C101="",D101="",E101="",F101=""),"",IF(OR(B101="",C101="",E101=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E101)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G101&lt;&gt;0,F101=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F101&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F101)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C101)*($E$5:$E$504=E101)*(($D$5:$D$504=D101)*(D101&lt;&gt;"")+($B$5:$B$504=B101)*(B101&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B101="",C101="",D101="",E101="",F101=""),"",IF(OR(B101="",C101="",E101=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E101)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H101&lt;&gt;0,F101=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G101&lt;&gt;0,F101=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F101&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F101)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C101)*($E$5:$E$504=E101)*(($D$5:$D$504=D101)*(D101&lt;&gt;"")+($B$5:$B$504=B101)*(B101&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J101" s="5">
@@ -3199,11 +3227,11 @@
         <v/>
       </c>
       <c r="H102" s="5">
-        <f>IF(OR(C102="Удержание",C102="Зачёт встречного требования",C102="Неустойка заявлена"),N(E102),0)</f>
+        <f>IF(OR(C102="Удержание",C102="Зачёт встречного требования",C102="Неустойка заявлена",C102="Допработы без соглашения (спорно)"),N(E102),0)</f>
         <v/>
       </c>
       <c r="I102" s="6">
-        <f>IF(AND(B102="",C102="",D102="",E102="",F102=""),"",IF(OR(B102="",C102="",E102=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E102)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G102&lt;&gt;0,F102=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F102&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F102)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C102)*($E$5:$E$504=E102)*(($D$5:$D$504=D102)*(D102&lt;&gt;"")+($B$5:$B$504=B102)*(B102&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B102="",C102="",D102="",E102="",F102=""),"",IF(OR(B102="",C102="",E102=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E102)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H102&lt;&gt;0,F102=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G102&lt;&gt;0,F102=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F102&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F102)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C102)*($E$5:$E$504=E102)*(($D$5:$D$504=D102)*(D102&lt;&gt;"")+($B$5:$B$504=B102)*(B102&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J102" s="5">
@@ -3225,11 +3253,11 @@
         <v/>
       </c>
       <c r="H103" s="5">
-        <f>IF(OR(C103="Удержание",C103="Зачёт встречного требования",C103="Неустойка заявлена"),N(E103),0)</f>
+        <f>IF(OR(C103="Удержание",C103="Зачёт встречного требования",C103="Неустойка заявлена",C103="Допработы без соглашения (спорно)"),N(E103),0)</f>
         <v/>
       </c>
       <c r="I103" s="6">
-        <f>IF(AND(B103="",C103="",D103="",E103="",F103=""),"",IF(OR(B103="",C103="",E103=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E103)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G103&lt;&gt;0,F103=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F103&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F103)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C103)*($E$5:$E$504=E103)*(($D$5:$D$504=D103)*(D103&lt;&gt;"")+($B$5:$B$504=B103)*(B103&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B103="",C103="",D103="",E103="",F103=""),"",IF(OR(B103="",C103="",E103=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E103)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H103&lt;&gt;0,F103=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G103&lt;&gt;0,F103=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F103&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F103)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C103)*($E$5:$E$504=E103)*(($D$5:$D$504=D103)*(D103&lt;&gt;"")+($B$5:$B$504=B103)*(B103&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J103" s="5">
@@ -3251,11 +3279,11 @@
         <v/>
       </c>
       <c r="H104" s="5">
-        <f>IF(OR(C104="Удержание",C104="Зачёт встречного требования",C104="Неустойка заявлена"),N(E104),0)</f>
+        <f>IF(OR(C104="Удержание",C104="Зачёт встречного требования",C104="Неустойка заявлена",C104="Допработы без соглашения (спорно)"),N(E104),0)</f>
         <v/>
       </c>
       <c r="I104" s="6">
-        <f>IF(AND(B104="",C104="",D104="",E104="",F104=""),"",IF(OR(B104="",C104="",E104=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E104)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G104&lt;&gt;0,F104=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F104&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F104)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C104)*($E$5:$E$504=E104)*(($D$5:$D$504=D104)*(D104&lt;&gt;"")+($B$5:$B$504=B104)*(B104&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B104="",C104="",D104="",E104="",F104=""),"",IF(OR(B104="",C104="",E104=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E104)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H104&lt;&gt;0,F104=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G104&lt;&gt;0,F104=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F104&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F104)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C104)*($E$5:$E$504=E104)*(($D$5:$D$504=D104)*(D104&lt;&gt;"")+($B$5:$B$504=B104)*(B104&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J104" s="5">
@@ -3277,11 +3305,11 @@
         <v/>
       </c>
       <c r="H105" s="5">
-        <f>IF(OR(C105="Удержание",C105="Зачёт встречного требования",C105="Неустойка заявлена"),N(E105),0)</f>
+        <f>IF(OR(C105="Удержание",C105="Зачёт встречного требования",C105="Неустойка заявлена",C105="Допработы без соглашения (спорно)"),N(E105),0)</f>
         <v/>
       </c>
       <c r="I105" s="6">
-        <f>IF(AND(B105="",C105="",D105="",E105="",F105=""),"",IF(OR(B105="",C105="",E105=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E105)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G105&lt;&gt;0,F105=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F105&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F105)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C105)*($E$5:$E$504=E105)*(($D$5:$D$504=D105)*(D105&lt;&gt;"")+($B$5:$B$504=B105)*(B105&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B105="",C105="",D105="",E105="",F105=""),"",IF(OR(B105="",C105="",E105=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E105)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H105&lt;&gt;0,F105=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G105&lt;&gt;0,F105=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F105&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F105)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C105)*($E$5:$E$504=E105)*(($D$5:$D$504=D105)*(D105&lt;&gt;"")+($B$5:$B$504=B105)*(B105&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J105" s="5">
@@ -3303,11 +3331,11 @@
         <v/>
       </c>
       <c r="H106" s="5">
-        <f>IF(OR(C106="Удержание",C106="Зачёт встречного требования",C106="Неустойка заявлена"),N(E106),0)</f>
+        <f>IF(OR(C106="Удержание",C106="Зачёт встречного требования",C106="Неустойка заявлена",C106="Допработы без соглашения (спорно)"),N(E106),0)</f>
         <v/>
       </c>
       <c r="I106" s="6">
-        <f>IF(AND(B106="",C106="",D106="",E106="",F106=""),"",IF(OR(B106="",C106="",E106=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E106)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G106&lt;&gt;0,F106=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F106&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F106)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C106)*($E$5:$E$504=E106)*(($D$5:$D$504=D106)*(D106&lt;&gt;"")+($B$5:$B$504=B106)*(B106&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B106="",C106="",D106="",E106="",F106=""),"",IF(OR(B106="",C106="",E106=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E106)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H106&lt;&gt;0,F106=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G106&lt;&gt;0,F106=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F106&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F106)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C106)*($E$5:$E$504=E106)*(($D$5:$D$504=D106)*(D106&lt;&gt;"")+($B$5:$B$504=B106)*(B106&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J106" s="5">
@@ -3329,11 +3357,11 @@
         <v/>
       </c>
       <c r="H107" s="5">
-        <f>IF(OR(C107="Удержание",C107="Зачёт встречного требования",C107="Неустойка заявлена"),N(E107),0)</f>
+        <f>IF(OR(C107="Удержание",C107="Зачёт встречного требования",C107="Неустойка заявлена",C107="Допработы без соглашения (спорно)"),N(E107),0)</f>
         <v/>
       </c>
       <c r="I107" s="6">
-        <f>IF(AND(B107="",C107="",D107="",E107="",F107=""),"",IF(OR(B107="",C107="",E107=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E107)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G107&lt;&gt;0,F107=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F107&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F107)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C107)*($E$5:$E$504=E107)*(($D$5:$D$504=D107)*(D107&lt;&gt;"")+($B$5:$B$504=B107)*(B107&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B107="",C107="",D107="",E107="",F107=""),"",IF(OR(B107="",C107="",E107=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E107)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H107&lt;&gt;0,F107=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G107&lt;&gt;0,F107=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F107&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F107)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C107)*($E$5:$E$504=E107)*(($D$5:$D$504=D107)*(D107&lt;&gt;"")+($B$5:$B$504=B107)*(B107&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J107" s="5">
@@ -3355,11 +3383,11 @@
         <v/>
       </c>
       <c r="H108" s="5">
-        <f>IF(OR(C108="Удержание",C108="Зачёт встречного требования",C108="Неустойка заявлена"),N(E108),0)</f>
+        <f>IF(OR(C108="Удержание",C108="Зачёт встречного требования",C108="Неустойка заявлена",C108="Допработы без соглашения (спорно)"),N(E108),0)</f>
         <v/>
       </c>
       <c r="I108" s="6">
-        <f>IF(AND(B108="",C108="",D108="",E108="",F108=""),"",IF(OR(B108="",C108="",E108=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E108)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G108&lt;&gt;0,F108=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F108&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F108)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C108)*($E$5:$E$504=E108)*(($D$5:$D$504=D108)*(D108&lt;&gt;"")+($B$5:$B$504=B108)*(B108&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B108="",C108="",D108="",E108="",F108=""),"",IF(OR(B108="",C108="",E108=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E108)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H108&lt;&gt;0,F108=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G108&lt;&gt;0,F108=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F108&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F108)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C108)*($E$5:$E$504=E108)*(($D$5:$D$504=D108)*(D108&lt;&gt;"")+($B$5:$B$504=B108)*(B108&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J108" s="5">
@@ -3381,11 +3409,11 @@
         <v/>
       </c>
       <c r="H109" s="5">
-        <f>IF(OR(C109="Удержание",C109="Зачёт встречного требования",C109="Неустойка заявлена"),N(E109),0)</f>
+        <f>IF(OR(C109="Удержание",C109="Зачёт встречного требования",C109="Неустойка заявлена",C109="Допработы без соглашения (спорно)"),N(E109),0)</f>
         <v/>
       </c>
       <c r="I109" s="6">
-        <f>IF(AND(B109="",C109="",D109="",E109="",F109=""),"",IF(OR(B109="",C109="",E109=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E109)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G109&lt;&gt;0,F109=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F109&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F109)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C109)*($E$5:$E$504=E109)*(($D$5:$D$504=D109)*(D109&lt;&gt;"")+($B$5:$B$504=B109)*(B109&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B109="",C109="",D109="",E109="",F109=""),"",IF(OR(B109="",C109="",E109=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E109)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H109&lt;&gt;0,F109=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G109&lt;&gt;0,F109=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F109&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F109)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C109)*($E$5:$E$504=E109)*(($D$5:$D$504=D109)*(D109&lt;&gt;"")+($B$5:$B$504=B109)*(B109&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J109" s="5">
@@ -3407,11 +3435,11 @@
         <v/>
       </c>
       <c r="H110" s="5">
-        <f>IF(OR(C110="Удержание",C110="Зачёт встречного требования",C110="Неустойка заявлена"),N(E110),0)</f>
+        <f>IF(OR(C110="Удержание",C110="Зачёт встречного требования",C110="Неустойка заявлена",C110="Допработы без соглашения (спорно)"),N(E110),0)</f>
         <v/>
       </c>
       <c r="I110" s="6">
-        <f>IF(AND(B110="",C110="",D110="",E110="",F110=""),"",IF(OR(B110="",C110="",E110=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E110)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G110&lt;&gt;0,F110=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F110&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F110)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C110)*($E$5:$E$504=E110)*(($D$5:$D$504=D110)*(D110&lt;&gt;"")+($B$5:$B$504=B110)*(B110&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B110="",C110="",D110="",E110="",F110=""),"",IF(OR(B110="",C110="",E110=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E110)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H110&lt;&gt;0,F110=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G110&lt;&gt;0,F110=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F110&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F110)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C110)*($E$5:$E$504=E110)*(($D$5:$D$504=D110)*(D110&lt;&gt;"")+($B$5:$B$504=B110)*(B110&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J110" s="5">
@@ -3433,11 +3461,11 @@
         <v/>
       </c>
       <c r="H111" s="5">
-        <f>IF(OR(C111="Удержание",C111="Зачёт встречного требования",C111="Неустойка заявлена"),N(E111),0)</f>
+        <f>IF(OR(C111="Удержание",C111="Зачёт встречного требования",C111="Неустойка заявлена",C111="Допработы без соглашения (спорно)"),N(E111),0)</f>
         <v/>
       </c>
       <c r="I111" s="6">
-        <f>IF(AND(B111="",C111="",D111="",E111="",F111=""),"",IF(OR(B111="",C111="",E111=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E111)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G111&lt;&gt;0,F111=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F111&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F111)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C111)*($E$5:$E$504=E111)*(($D$5:$D$504=D111)*(D111&lt;&gt;"")+($B$5:$B$504=B111)*(B111&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B111="",C111="",D111="",E111="",F111=""),"",IF(OR(B111="",C111="",E111=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E111)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H111&lt;&gt;0,F111=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G111&lt;&gt;0,F111=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F111&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F111)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C111)*($E$5:$E$504=E111)*(($D$5:$D$504=D111)*(D111&lt;&gt;"")+($B$5:$B$504=B111)*(B111&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J111" s="5">
@@ -3459,11 +3487,11 @@
         <v/>
       </c>
       <c r="H112" s="5">
-        <f>IF(OR(C112="Удержание",C112="Зачёт встречного требования",C112="Неустойка заявлена"),N(E112),0)</f>
+        <f>IF(OR(C112="Удержание",C112="Зачёт встречного требования",C112="Неустойка заявлена",C112="Допработы без соглашения (спорно)"),N(E112),0)</f>
         <v/>
       </c>
       <c r="I112" s="6">
-        <f>IF(AND(B112="",C112="",D112="",E112="",F112=""),"",IF(OR(B112="",C112="",E112=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E112)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G112&lt;&gt;0,F112=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F112&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F112)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C112)*($E$5:$E$504=E112)*(($D$5:$D$504=D112)*(D112&lt;&gt;"")+($B$5:$B$504=B112)*(B112&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B112="",C112="",D112="",E112="",F112=""),"",IF(OR(B112="",C112="",E112=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E112)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H112&lt;&gt;0,F112=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G112&lt;&gt;0,F112=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F112&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F112)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C112)*($E$5:$E$504=E112)*(($D$5:$D$504=D112)*(D112&lt;&gt;"")+($B$5:$B$504=B112)*(B112&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J112" s="5">
@@ -3485,11 +3513,11 @@
         <v/>
       </c>
       <c r="H113" s="5">
-        <f>IF(OR(C113="Удержание",C113="Зачёт встречного требования",C113="Неустойка заявлена"),N(E113),0)</f>
+        <f>IF(OR(C113="Удержание",C113="Зачёт встречного требования",C113="Неустойка заявлена",C113="Допработы без соглашения (спорно)"),N(E113),0)</f>
         <v/>
       </c>
       <c r="I113" s="6">
-        <f>IF(AND(B113="",C113="",D113="",E113="",F113=""),"",IF(OR(B113="",C113="",E113=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E113)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G113&lt;&gt;0,F113=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F113&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F113)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C113)*($E$5:$E$504=E113)*(($D$5:$D$504=D113)*(D113&lt;&gt;"")+($B$5:$B$504=B113)*(B113&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B113="",C113="",D113="",E113="",F113=""),"",IF(OR(B113="",C113="",E113=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E113)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H113&lt;&gt;0,F113=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G113&lt;&gt;0,F113=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F113&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F113)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C113)*($E$5:$E$504=E113)*(($D$5:$D$504=D113)*(D113&lt;&gt;"")+($B$5:$B$504=B113)*(B113&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J113" s="5">
@@ -3511,11 +3539,11 @@
         <v/>
       </c>
       <c r="H114" s="5">
-        <f>IF(OR(C114="Удержание",C114="Зачёт встречного требования",C114="Неустойка заявлена"),N(E114),0)</f>
+        <f>IF(OR(C114="Удержание",C114="Зачёт встречного требования",C114="Неустойка заявлена",C114="Допработы без соглашения (спорно)"),N(E114),0)</f>
         <v/>
       </c>
       <c r="I114" s="6">
-        <f>IF(AND(B114="",C114="",D114="",E114="",F114=""),"",IF(OR(B114="",C114="",E114=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E114)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G114&lt;&gt;0,F114=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F114&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F114)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C114)*($E$5:$E$504=E114)*(($D$5:$D$504=D114)*(D114&lt;&gt;"")+($B$5:$B$504=B114)*(B114&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B114="",C114="",D114="",E114="",F114=""),"",IF(OR(B114="",C114="",E114=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E114)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H114&lt;&gt;0,F114=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G114&lt;&gt;0,F114=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F114&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F114)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C114)*($E$5:$E$504=E114)*(($D$5:$D$504=D114)*(D114&lt;&gt;"")+($B$5:$B$504=B114)*(B114&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J114" s="5">
@@ -3537,11 +3565,11 @@
         <v/>
       </c>
       <c r="H115" s="5">
-        <f>IF(OR(C115="Удержание",C115="Зачёт встречного требования",C115="Неустойка заявлена"),N(E115),0)</f>
+        <f>IF(OR(C115="Удержание",C115="Зачёт встречного требования",C115="Неустойка заявлена",C115="Допработы без соглашения (спорно)"),N(E115),0)</f>
         <v/>
       </c>
       <c r="I115" s="6">
-        <f>IF(AND(B115="",C115="",D115="",E115="",F115=""),"",IF(OR(B115="",C115="",E115=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E115)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G115&lt;&gt;0,F115=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F115&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F115)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C115)*($E$5:$E$504=E115)*(($D$5:$D$504=D115)*(D115&lt;&gt;"")+($B$5:$B$504=B115)*(B115&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B115="",C115="",D115="",E115="",F115=""),"",IF(OR(B115="",C115="",E115=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E115)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H115&lt;&gt;0,F115=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G115&lt;&gt;0,F115=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F115&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F115)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C115)*($E$5:$E$504=E115)*(($D$5:$D$504=D115)*(D115&lt;&gt;"")+($B$5:$B$504=B115)*(B115&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J115" s="5">
@@ -3563,11 +3591,11 @@
         <v/>
       </c>
       <c r="H116" s="5">
-        <f>IF(OR(C116="Удержание",C116="Зачёт встречного требования",C116="Неустойка заявлена"),N(E116),0)</f>
+        <f>IF(OR(C116="Удержание",C116="Зачёт встречного требования",C116="Неустойка заявлена",C116="Допработы без соглашения (спорно)"),N(E116),0)</f>
         <v/>
       </c>
       <c r="I116" s="6">
-        <f>IF(AND(B116="",C116="",D116="",E116="",F116=""),"",IF(OR(B116="",C116="",E116=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E116)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G116&lt;&gt;0,F116=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F116&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F116)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C116)*($E$5:$E$504=E116)*(($D$5:$D$504=D116)*(D116&lt;&gt;"")+($B$5:$B$504=B116)*(B116&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B116="",C116="",D116="",E116="",F116=""),"",IF(OR(B116="",C116="",E116=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E116)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H116&lt;&gt;0,F116=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G116&lt;&gt;0,F116=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F116&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F116)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C116)*($E$5:$E$504=E116)*(($D$5:$D$504=D116)*(D116&lt;&gt;"")+($B$5:$B$504=B116)*(B116&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J116" s="5">
@@ -3589,11 +3617,11 @@
         <v/>
       </c>
       <c r="H117" s="5">
-        <f>IF(OR(C117="Удержание",C117="Зачёт встречного требования",C117="Неустойка заявлена"),N(E117),0)</f>
+        <f>IF(OR(C117="Удержание",C117="Зачёт встречного требования",C117="Неустойка заявлена",C117="Допработы без соглашения (спорно)"),N(E117),0)</f>
         <v/>
       </c>
       <c r="I117" s="6">
-        <f>IF(AND(B117="",C117="",D117="",E117="",F117=""),"",IF(OR(B117="",C117="",E117=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E117)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G117&lt;&gt;0,F117=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F117&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F117)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C117)*($E$5:$E$504=E117)*(($D$5:$D$504=D117)*(D117&lt;&gt;"")+($B$5:$B$504=B117)*(B117&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B117="",C117="",D117="",E117="",F117=""),"",IF(OR(B117="",C117="",E117=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E117)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H117&lt;&gt;0,F117=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G117&lt;&gt;0,F117=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F117&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F117)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C117)*($E$5:$E$504=E117)*(($D$5:$D$504=D117)*(D117&lt;&gt;"")+($B$5:$B$504=B117)*(B117&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J117" s="5">
@@ -3615,11 +3643,11 @@
         <v/>
       </c>
       <c r="H118" s="5">
-        <f>IF(OR(C118="Удержание",C118="Зачёт встречного требования",C118="Неустойка заявлена"),N(E118),0)</f>
+        <f>IF(OR(C118="Удержание",C118="Зачёт встречного требования",C118="Неустойка заявлена",C118="Допработы без соглашения (спорно)"),N(E118),0)</f>
         <v/>
       </c>
       <c r="I118" s="6">
-        <f>IF(AND(B118="",C118="",D118="",E118="",F118=""),"",IF(OR(B118="",C118="",E118=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E118)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G118&lt;&gt;0,F118=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F118&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F118)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C118)*($E$5:$E$504=E118)*(($D$5:$D$504=D118)*(D118&lt;&gt;"")+($B$5:$B$504=B118)*(B118&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B118="",C118="",D118="",E118="",F118=""),"",IF(OR(B118="",C118="",E118=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E118)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H118&lt;&gt;0,F118=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G118&lt;&gt;0,F118=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F118&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F118)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C118)*($E$5:$E$504=E118)*(($D$5:$D$504=D118)*(D118&lt;&gt;"")+($B$5:$B$504=B118)*(B118&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J118" s="5">
@@ -3641,11 +3669,11 @@
         <v/>
       </c>
       <c r="H119" s="5">
-        <f>IF(OR(C119="Удержание",C119="Зачёт встречного требования",C119="Неустойка заявлена"),N(E119),0)</f>
+        <f>IF(OR(C119="Удержание",C119="Зачёт встречного требования",C119="Неустойка заявлена",C119="Допработы без соглашения (спорно)"),N(E119),0)</f>
         <v/>
       </c>
       <c r="I119" s="6">
-        <f>IF(AND(B119="",C119="",D119="",E119="",F119=""),"",IF(OR(B119="",C119="",E119=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E119)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G119&lt;&gt;0,F119=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F119&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F119)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C119)*($E$5:$E$504=E119)*(($D$5:$D$504=D119)*(D119&lt;&gt;"")+($B$5:$B$504=B119)*(B119&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B119="",C119="",D119="",E119="",F119=""),"",IF(OR(B119="",C119="",E119=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E119)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H119&lt;&gt;0,F119=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G119&lt;&gt;0,F119=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F119&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F119)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C119)*($E$5:$E$504=E119)*(($D$5:$D$504=D119)*(D119&lt;&gt;"")+($B$5:$B$504=B119)*(B119&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J119" s="5">
@@ -3667,11 +3695,11 @@
         <v/>
       </c>
       <c r="H120" s="5">
-        <f>IF(OR(C120="Удержание",C120="Зачёт встречного требования",C120="Неустойка заявлена"),N(E120),0)</f>
+        <f>IF(OR(C120="Удержание",C120="Зачёт встречного требования",C120="Неустойка заявлена",C120="Допработы без соглашения (спорно)"),N(E120),0)</f>
         <v/>
       </c>
       <c r="I120" s="6">
-        <f>IF(AND(B120="",C120="",D120="",E120="",F120=""),"",IF(OR(B120="",C120="",E120=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E120)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G120&lt;&gt;0,F120=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F120&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F120)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C120)*($E$5:$E$504=E120)*(($D$5:$D$504=D120)*(D120&lt;&gt;"")+($B$5:$B$504=B120)*(B120&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B120="",C120="",D120="",E120="",F120=""),"",IF(OR(B120="",C120="",E120=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E120)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H120&lt;&gt;0,F120=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G120&lt;&gt;0,F120=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F120&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F120)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C120)*($E$5:$E$504=E120)*(($D$5:$D$504=D120)*(D120&lt;&gt;"")+($B$5:$B$504=B120)*(B120&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J120" s="5">
@@ -3693,11 +3721,11 @@
         <v/>
       </c>
       <c r="H121" s="5">
-        <f>IF(OR(C121="Удержание",C121="Зачёт встречного требования",C121="Неустойка заявлена"),N(E121),0)</f>
+        <f>IF(OR(C121="Удержание",C121="Зачёт встречного требования",C121="Неустойка заявлена",C121="Допработы без соглашения (спорно)"),N(E121),0)</f>
         <v/>
       </c>
       <c r="I121" s="6">
-        <f>IF(AND(B121="",C121="",D121="",E121="",F121=""),"",IF(OR(B121="",C121="",E121=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E121)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G121&lt;&gt;0,F121=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F121&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F121)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C121)*($E$5:$E$504=E121)*(($D$5:$D$504=D121)*(D121&lt;&gt;"")+($B$5:$B$504=B121)*(B121&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B121="",C121="",D121="",E121="",F121=""),"",IF(OR(B121="",C121="",E121=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E121)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H121&lt;&gt;0,F121=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G121&lt;&gt;0,F121=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F121&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F121)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C121)*($E$5:$E$504=E121)*(($D$5:$D$504=D121)*(D121&lt;&gt;"")+($B$5:$B$504=B121)*(B121&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J121" s="5">
@@ -3719,11 +3747,11 @@
         <v/>
       </c>
       <c r="H122" s="5">
-        <f>IF(OR(C122="Удержание",C122="Зачёт встречного требования",C122="Неустойка заявлена"),N(E122),0)</f>
+        <f>IF(OR(C122="Удержание",C122="Зачёт встречного требования",C122="Неустойка заявлена",C122="Допработы без соглашения (спорно)"),N(E122),0)</f>
         <v/>
       </c>
       <c r="I122" s="6">
-        <f>IF(AND(B122="",C122="",D122="",E122="",F122=""),"",IF(OR(B122="",C122="",E122=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E122)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G122&lt;&gt;0,F122=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F122&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F122)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C122)*($E$5:$E$504=E122)*(($D$5:$D$504=D122)*(D122&lt;&gt;"")+($B$5:$B$504=B122)*(B122&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B122="",C122="",D122="",E122="",F122=""),"",IF(OR(B122="",C122="",E122=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E122)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H122&lt;&gt;0,F122=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G122&lt;&gt;0,F122=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F122&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F122)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C122)*($E$5:$E$504=E122)*(($D$5:$D$504=D122)*(D122&lt;&gt;"")+($B$5:$B$504=B122)*(B122&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J122" s="5">
@@ -3745,11 +3773,11 @@
         <v/>
       </c>
       <c r="H123" s="5">
-        <f>IF(OR(C123="Удержание",C123="Зачёт встречного требования",C123="Неустойка заявлена"),N(E123),0)</f>
+        <f>IF(OR(C123="Удержание",C123="Зачёт встречного требования",C123="Неустойка заявлена",C123="Допработы без соглашения (спорно)"),N(E123),0)</f>
         <v/>
       </c>
       <c r="I123" s="6">
-        <f>IF(AND(B123="",C123="",D123="",E123="",F123=""),"",IF(OR(B123="",C123="",E123=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E123)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G123&lt;&gt;0,F123=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F123&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F123)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C123)*($E$5:$E$504=E123)*(($D$5:$D$504=D123)*(D123&lt;&gt;"")+($B$5:$B$504=B123)*(B123&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B123="",C123="",D123="",E123="",F123=""),"",IF(OR(B123="",C123="",E123=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E123)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H123&lt;&gt;0,F123=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G123&lt;&gt;0,F123=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F123&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F123)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C123)*($E$5:$E$504=E123)*(($D$5:$D$504=D123)*(D123&lt;&gt;"")+($B$5:$B$504=B123)*(B123&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J123" s="5">
@@ -3771,11 +3799,11 @@
         <v/>
       </c>
       <c r="H124" s="5">
-        <f>IF(OR(C124="Удержание",C124="Зачёт встречного требования",C124="Неустойка заявлена"),N(E124),0)</f>
+        <f>IF(OR(C124="Удержание",C124="Зачёт встречного требования",C124="Неустойка заявлена",C124="Допработы без соглашения (спорно)"),N(E124),0)</f>
         <v/>
       </c>
       <c r="I124" s="6">
-        <f>IF(AND(B124="",C124="",D124="",E124="",F124=""),"",IF(OR(B124="",C124="",E124=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E124)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G124&lt;&gt;0,F124=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F124&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F124)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C124)*($E$5:$E$504=E124)*(($D$5:$D$504=D124)*(D124&lt;&gt;"")+($B$5:$B$504=B124)*(B124&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B124="",C124="",D124="",E124="",F124=""),"",IF(OR(B124="",C124="",E124=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E124)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H124&lt;&gt;0,F124=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G124&lt;&gt;0,F124=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F124&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F124)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C124)*($E$5:$E$504=E124)*(($D$5:$D$504=D124)*(D124&lt;&gt;"")+($B$5:$B$504=B124)*(B124&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J124" s="5">
@@ -3797,11 +3825,11 @@
         <v/>
       </c>
       <c r="H125" s="5">
-        <f>IF(OR(C125="Удержание",C125="Зачёт встречного требования",C125="Неустойка заявлена"),N(E125),0)</f>
+        <f>IF(OR(C125="Удержание",C125="Зачёт встречного требования",C125="Неустойка заявлена",C125="Допработы без соглашения (спорно)"),N(E125),0)</f>
         <v/>
       </c>
       <c r="I125" s="6">
-        <f>IF(AND(B125="",C125="",D125="",E125="",F125=""),"",IF(OR(B125="",C125="",E125=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E125)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G125&lt;&gt;0,F125=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F125&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F125)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C125)*($E$5:$E$504=E125)*(($D$5:$D$504=D125)*(D125&lt;&gt;"")+($B$5:$B$504=B125)*(B125&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B125="",C125="",D125="",E125="",F125=""),"",IF(OR(B125="",C125="",E125=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E125)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H125&lt;&gt;0,F125=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G125&lt;&gt;0,F125=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F125&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F125)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C125)*($E$5:$E$504=E125)*(($D$5:$D$504=D125)*(D125&lt;&gt;"")+($B$5:$B$504=B125)*(B125&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J125" s="5">
@@ -3823,11 +3851,11 @@
         <v/>
       </c>
       <c r="H126" s="5">
-        <f>IF(OR(C126="Удержание",C126="Зачёт встречного требования",C126="Неустойка заявлена"),N(E126),0)</f>
+        <f>IF(OR(C126="Удержание",C126="Зачёт встречного требования",C126="Неустойка заявлена",C126="Допработы без соглашения (спорно)"),N(E126),0)</f>
         <v/>
       </c>
       <c r="I126" s="6">
-        <f>IF(AND(B126="",C126="",D126="",E126="",F126=""),"",IF(OR(B126="",C126="",E126=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E126)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G126&lt;&gt;0,F126=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F126&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F126)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C126)*($E$5:$E$504=E126)*(($D$5:$D$504=D126)*(D126&lt;&gt;"")+($B$5:$B$504=B126)*(B126&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B126="",C126="",D126="",E126="",F126=""),"",IF(OR(B126="",C126="",E126=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E126)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H126&lt;&gt;0,F126=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G126&lt;&gt;0,F126=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F126&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F126)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C126)*($E$5:$E$504=E126)*(($D$5:$D$504=D126)*(D126&lt;&gt;"")+($B$5:$B$504=B126)*(B126&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J126" s="5">
@@ -3849,11 +3877,11 @@
         <v/>
       </c>
       <c r="H127" s="5">
-        <f>IF(OR(C127="Удержание",C127="Зачёт встречного требования",C127="Неустойка заявлена"),N(E127),0)</f>
+        <f>IF(OR(C127="Удержание",C127="Зачёт встречного требования",C127="Неустойка заявлена",C127="Допработы без соглашения (спорно)"),N(E127),0)</f>
         <v/>
       </c>
       <c r="I127" s="6">
-        <f>IF(AND(B127="",C127="",D127="",E127="",F127=""),"",IF(OR(B127="",C127="",E127=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E127)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G127&lt;&gt;0,F127=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F127&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F127)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C127)*($E$5:$E$504=E127)*(($D$5:$D$504=D127)*(D127&lt;&gt;"")+($B$5:$B$504=B127)*(B127&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B127="",C127="",D127="",E127="",F127=""),"",IF(OR(B127="",C127="",E127=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E127)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H127&lt;&gt;0,F127=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G127&lt;&gt;0,F127=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F127&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F127)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C127)*($E$5:$E$504=E127)*(($D$5:$D$504=D127)*(D127&lt;&gt;"")+($B$5:$B$504=B127)*(B127&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J127" s="5">
@@ -3875,11 +3903,11 @@
         <v/>
       </c>
       <c r="H128" s="5">
-        <f>IF(OR(C128="Удержание",C128="Зачёт встречного требования",C128="Неустойка заявлена"),N(E128),0)</f>
+        <f>IF(OR(C128="Удержание",C128="Зачёт встречного требования",C128="Неустойка заявлена",C128="Допработы без соглашения (спорно)"),N(E128),0)</f>
         <v/>
       </c>
       <c r="I128" s="6">
-        <f>IF(AND(B128="",C128="",D128="",E128="",F128=""),"",IF(OR(B128="",C128="",E128=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E128)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G128&lt;&gt;0,F128=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F128&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F128)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C128)*($E$5:$E$504=E128)*(($D$5:$D$504=D128)*(D128&lt;&gt;"")+($B$5:$B$504=B128)*(B128&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B128="",C128="",D128="",E128="",F128=""),"",IF(OR(B128="",C128="",E128=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E128)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H128&lt;&gt;0,F128=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G128&lt;&gt;0,F128=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F128&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F128)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C128)*($E$5:$E$504=E128)*(($D$5:$D$504=D128)*(D128&lt;&gt;"")+($B$5:$B$504=B128)*(B128&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J128" s="5">
@@ -3901,11 +3929,11 @@
         <v/>
       </c>
       <c r="H129" s="5">
-        <f>IF(OR(C129="Удержание",C129="Зачёт встречного требования",C129="Неустойка заявлена"),N(E129),0)</f>
+        <f>IF(OR(C129="Удержание",C129="Зачёт встречного требования",C129="Неустойка заявлена",C129="Допработы без соглашения (спорно)"),N(E129),0)</f>
         <v/>
       </c>
       <c r="I129" s="6">
-        <f>IF(AND(B129="",C129="",D129="",E129="",F129=""),"",IF(OR(B129="",C129="",E129=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E129)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G129&lt;&gt;0,F129=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F129&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F129)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C129)*($E$5:$E$504=E129)*(($D$5:$D$504=D129)*(D129&lt;&gt;"")+($B$5:$B$504=B129)*(B129&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B129="",C129="",D129="",E129="",F129=""),"",IF(OR(B129="",C129="",E129=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E129)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H129&lt;&gt;0,F129=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G129&lt;&gt;0,F129=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F129&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F129)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C129)*($E$5:$E$504=E129)*(($D$5:$D$504=D129)*(D129&lt;&gt;"")+($B$5:$B$504=B129)*(B129&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J129" s="5">
@@ -3927,11 +3955,11 @@
         <v/>
       </c>
       <c r="H130" s="5">
-        <f>IF(OR(C130="Удержание",C130="Зачёт встречного требования",C130="Неустойка заявлена"),N(E130),0)</f>
+        <f>IF(OR(C130="Удержание",C130="Зачёт встречного требования",C130="Неустойка заявлена",C130="Допработы без соглашения (спорно)"),N(E130),0)</f>
         <v/>
       </c>
       <c r="I130" s="6">
-        <f>IF(AND(B130="",C130="",D130="",E130="",F130=""),"",IF(OR(B130="",C130="",E130=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E130)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G130&lt;&gt;0,F130=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F130&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F130)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C130)*($E$5:$E$504=E130)*(($D$5:$D$504=D130)*(D130&lt;&gt;"")+($B$5:$B$504=B130)*(B130&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B130="",C130="",D130="",E130="",F130=""),"",IF(OR(B130="",C130="",E130=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E130)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H130&lt;&gt;0,F130=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G130&lt;&gt;0,F130=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F130&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F130)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C130)*($E$5:$E$504=E130)*(($D$5:$D$504=D130)*(D130&lt;&gt;"")+($B$5:$B$504=B130)*(B130&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J130" s="5">
@@ -3953,11 +3981,11 @@
         <v/>
       </c>
       <c r="H131" s="5">
-        <f>IF(OR(C131="Удержание",C131="Зачёт встречного требования",C131="Неустойка заявлена"),N(E131),0)</f>
+        <f>IF(OR(C131="Удержание",C131="Зачёт встречного требования",C131="Неустойка заявлена",C131="Допработы без соглашения (спорно)"),N(E131),0)</f>
         <v/>
       </c>
       <c r="I131" s="6">
-        <f>IF(AND(B131="",C131="",D131="",E131="",F131=""),"",IF(OR(B131="",C131="",E131=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E131)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G131&lt;&gt;0,F131=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F131&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F131)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C131)*($E$5:$E$504=E131)*(($D$5:$D$504=D131)*(D131&lt;&gt;"")+($B$5:$B$504=B131)*(B131&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B131="",C131="",D131="",E131="",F131=""),"",IF(OR(B131="",C131="",E131=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E131)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H131&lt;&gt;0,F131=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G131&lt;&gt;0,F131=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F131&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F131)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C131)*($E$5:$E$504=E131)*(($D$5:$D$504=D131)*(D131&lt;&gt;"")+($B$5:$B$504=B131)*(B131&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J131" s="5">
@@ -3979,11 +4007,11 @@
         <v/>
       </c>
       <c r="H132" s="5">
-        <f>IF(OR(C132="Удержание",C132="Зачёт встречного требования",C132="Неустойка заявлена"),N(E132),0)</f>
+        <f>IF(OR(C132="Удержание",C132="Зачёт встречного требования",C132="Неустойка заявлена",C132="Допработы без соглашения (спорно)"),N(E132),0)</f>
         <v/>
       </c>
       <c r="I132" s="6">
-        <f>IF(AND(B132="",C132="",D132="",E132="",F132=""),"",IF(OR(B132="",C132="",E132=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E132)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G132&lt;&gt;0,F132=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F132&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F132)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C132)*($E$5:$E$504=E132)*(($D$5:$D$504=D132)*(D132&lt;&gt;"")+($B$5:$B$504=B132)*(B132&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B132="",C132="",D132="",E132="",F132=""),"",IF(OR(B132="",C132="",E132=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E132)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H132&lt;&gt;0,F132=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G132&lt;&gt;0,F132=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F132&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F132)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C132)*($E$5:$E$504=E132)*(($D$5:$D$504=D132)*(D132&lt;&gt;"")+($B$5:$B$504=B132)*(B132&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J132" s="5">
@@ -4005,11 +4033,11 @@
         <v/>
       </c>
       <c r="H133" s="5">
-        <f>IF(OR(C133="Удержание",C133="Зачёт встречного требования",C133="Неустойка заявлена"),N(E133),0)</f>
+        <f>IF(OR(C133="Удержание",C133="Зачёт встречного требования",C133="Неустойка заявлена",C133="Допработы без соглашения (спорно)"),N(E133),0)</f>
         <v/>
       </c>
       <c r="I133" s="6">
-        <f>IF(AND(B133="",C133="",D133="",E133="",F133=""),"",IF(OR(B133="",C133="",E133=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E133)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G133&lt;&gt;0,F133=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F133&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F133)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C133)*($E$5:$E$504=E133)*(($D$5:$D$504=D133)*(D133&lt;&gt;"")+($B$5:$B$504=B133)*(B133&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B133="",C133="",D133="",E133="",F133=""),"",IF(OR(B133="",C133="",E133=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E133)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H133&lt;&gt;0,F133=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G133&lt;&gt;0,F133=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F133&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F133)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C133)*($E$5:$E$504=E133)*(($D$5:$D$504=D133)*(D133&lt;&gt;"")+($B$5:$B$504=B133)*(B133&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J133" s="5">
@@ -4031,11 +4059,11 @@
         <v/>
       </c>
       <c r="H134" s="5">
-        <f>IF(OR(C134="Удержание",C134="Зачёт встречного требования",C134="Неустойка заявлена"),N(E134),0)</f>
+        <f>IF(OR(C134="Удержание",C134="Зачёт встречного требования",C134="Неустойка заявлена",C134="Допработы без соглашения (спорно)"),N(E134),0)</f>
         <v/>
       </c>
       <c r="I134" s="6">
-        <f>IF(AND(B134="",C134="",D134="",E134="",F134=""),"",IF(OR(B134="",C134="",E134=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E134)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G134&lt;&gt;0,F134=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F134&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F134)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C134)*($E$5:$E$504=E134)*(($D$5:$D$504=D134)*(D134&lt;&gt;"")+($B$5:$B$504=B134)*(B134&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B134="",C134="",D134="",E134="",F134=""),"",IF(OR(B134="",C134="",E134=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E134)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H134&lt;&gt;0,F134=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G134&lt;&gt;0,F134=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F134&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F134)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C134)*($E$5:$E$504=E134)*(($D$5:$D$504=D134)*(D134&lt;&gt;"")+($B$5:$B$504=B134)*(B134&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J134" s="5">
@@ -4057,11 +4085,11 @@
         <v/>
       </c>
       <c r="H135" s="5">
-        <f>IF(OR(C135="Удержание",C135="Зачёт встречного требования",C135="Неустойка заявлена"),N(E135),0)</f>
+        <f>IF(OR(C135="Удержание",C135="Зачёт встречного требования",C135="Неустойка заявлена",C135="Допработы без соглашения (спорно)"),N(E135),0)</f>
         <v/>
       </c>
       <c r="I135" s="6">
-        <f>IF(AND(B135="",C135="",D135="",E135="",F135=""),"",IF(OR(B135="",C135="",E135=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E135)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G135&lt;&gt;0,F135=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F135&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F135)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C135)*($E$5:$E$504=E135)*(($D$5:$D$504=D135)*(D135&lt;&gt;"")+($B$5:$B$504=B135)*(B135&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B135="",C135="",D135="",E135="",F135=""),"",IF(OR(B135="",C135="",E135=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E135)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H135&lt;&gt;0,F135=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G135&lt;&gt;0,F135=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F135&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F135)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C135)*($E$5:$E$504=E135)*(($D$5:$D$504=D135)*(D135&lt;&gt;"")+($B$5:$B$504=B135)*(B135&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J135" s="5">
@@ -4083,11 +4111,11 @@
         <v/>
       </c>
       <c r="H136" s="5">
-        <f>IF(OR(C136="Удержание",C136="Зачёт встречного требования",C136="Неустойка заявлена"),N(E136),0)</f>
+        <f>IF(OR(C136="Удержание",C136="Зачёт встречного требования",C136="Неустойка заявлена",C136="Допработы без соглашения (спорно)"),N(E136),0)</f>
         <v/>
       </c>
       <c r="I136" s="6">
-        <f>IF(AND(B136="",C136="",D136="",E136="",F136=""),"",IF(OR(B136="",C136="",E136=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E136)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G136&lt;&gt;0,F136=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F136&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F136)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C136)*($E$5:$E$504=E136)*(($D$5:$D$504=D136)*(D136&lt;&gt;"")+($B$5:$B$504=B136)*(B136&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B136="",C136="",D136="",E136="",F136=""),"",IF(OR(B136="",C136="",E136=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E136)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H136&lt;&gt;0,F136=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G136&lt;&gt;0,F136=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F136&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F136)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C136)*($E$5:$E$504=E136)*(($D$5:$D$504=D136)*(D136&lt;&gt;"")+($B$5:$B$504=B136)*(B136&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J136" s="5">
@@ -4109,11 +4137,11 @@
         <v/>
       </c>
       <c r="H137" s="5">
-        <f>IF(OR(C137="Удержание",C137="Зачёт встречного требования",C137="Неустойка заявлена"),N(E137),0)</f>
+        <f>IF(OR(C137="Удержание",C137="Зачёт встречного требования",C137="Неустойка заявлена",C137="Допработы без соглашения (спорно)"),N(E137),0)</f>
         <v/>
       </c>
       <c r="I137" s="6">
-        <f>IF(AND(B137="",C137="",D137="",E137="",F137=""),"",IF(OR(B137="",C137="",E137=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E137)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G137&lt;&gt;0,F137=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F137&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F137)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C137)*($E$5:$E$504=E137)*(($D$5:$D$504=D137)*(D137&lt;&gt;"")+($B$5:$B$504=B137)*(B137&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B137="",C137="",D137="",E137="",F137=""),"",IF(OR(B137="",C137="",E137=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E137)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H137&lt;&gt;0,F137=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G137&lt;&gt;0,F137=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F137&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F137)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C137)*($E$5:$E$504=E137)*(($D$5:$D$504=D137)*(D137&lt;&gt;"")+($B$5:$B$504=B137)*(B137&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J137" s="5">
@@ -4135,11 +4163,11 @@
         <v/>
       </c>
       <c r="H138" s="5">
-        <f>IF(OR(C138="Удержание",C138="Зачёт встречного требования",C138="Неустойка заявлена"),N(E138),0)</f>
+        <f>IF(OR(C138="Удержание",C138="Зачёт встречного требования",C138="Неустойка заявлена",C138="Допработы без соглашения (спорно)"),N(E138),0)</f>
         <v/>
       </c>
       <c r="I138" s="6">
-        <f>IF(AND(B138="",C138="",D138="",E138="",F138=""),"",IF(OR(B138="",C138="",E138=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E138)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G138&lt;&gt;0,F138=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F138&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F138)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C138)*($E$5:$E$504=E138)*(($D$5:$D$504=D138)*(D138&lt;&gt;"")+($B$5:$B$504=B138)*(B138&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B138="",C138="",D138="",E138="",F138=""),"",IF(OR(B138="",C138="",E138=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E138)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H138&lt;&gt;0,F138=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G138&lt;&gt;0,F138=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F138&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F138)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C138)*($E$5:$E$504=E138)*(($D$5:$D$504=D138)*(D138&lt;&gt;"")+($B$5:$B$504=B138)*(B138&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J138" s="5">
@@ -4161,11 +4189,11 @@
         <v/>
       </c>
       <c r="H139" s="5">
-        <f>IF(OR(C139="Удержание",C139="Зачёт встречного требования",C139="Неустойка заявлена"),N(E139),0)</f>
+        <f>IF(OR(C139="Удержание",C139="Зачёт встречного требования",C139="Неустойка заявлена",C139="Допработы без соглашения (спорно)"),N(E139),0)</f>
         <v/>
       </c>
       <c r="I139" s="6">
-        <f>IF(AND(B139="",C139="",D139="",E139="",F139=""),"",IF(OR(B139="",C139="",E139=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E139)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G139&lt;&gt;0,F139=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F139&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F139)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C139)*($E$5:$E$504=E139)*(($D$5:$D$504=D139)*(D139&lt;&gt;"")+($B$5:$B$504=B139)*(B139&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B139="",C139="",D139="",E139="",F139=""),"",IF(OR(B139="",C139="",E139=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E139)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H139&lt;&gt;0,F139=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G139&lt;&gt;0,F139=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F139&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F139)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C139)*($E$5:$E$504=E139)*(($D$5:$D$504=D139)*(D139&lt;&gt;"")+($B$5:$B$504=B139)*(B139&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J139" s="5">
@@ -4187,11 +4215,11 @@
         <v/>
       </c>
       <c r="H140" s="5">
-        <f>IF(OR(C140="Удержание",C140="Зачёт встречного требования",C140="Неустойка заявлена"),N(E140),0)</f>
+        <f>IF(OR(C140="Удержание",C140="Зачёт встречного требования",C140="Неустойка заявлена",C140="Допработы без соглашения (спорно)"),N(E140),0)</f>
         <v/>
       </c>
       <c r="I140" s="6">
-        <f>IF(AND(B140="",C140="",D140="",E140="",F140=""),"",IF(OR(B140="",C140="",E140=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E140)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G140&lt;&gt;0,F140=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F140&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F140)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C140)*($E$5:$E$504=E140)*(($D$5:$D$504=D140)*(D140&lt;&gt;"")+($B$5:$B$504=B140)*(B140&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B140="",C140="",D140="",E140="",F140=""),"",IF(OR(B140="",C140="",E140=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E140)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H140&lt;&gt;0,F140=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G140&lt;&gt;0,F140=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F140&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F140)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C140)*($E$5:$E$504=E140)*(($D$5:$D$504=D140)*(D140&lt;&gt;"")+($B$5:$B$504=B140)*(B140&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J140" s="5">
@@ -4213,11 +4241,11 @@
         <v/>
       </c>
       <c r="H141" s="5">
-        <f>IF(OR(C141="Удержание",C141="Зачёт встречного требования",C141="Неустойка заявлена"),N(E141),0)</f>
+        <f>IF(OR(C141="Удержание",C141="Зачёт встречного требования",C141="Неустойка заявлена",C141="Допработы без соглашения (спорно)"),N(E141),0)</f>
         <v/>
       </c>
       <c r="I141" s="6">
-        <f>IF(AND(B141="",C141="",D141="",E141="",F141=""),"",IF(OR(B141="",C141="",E141=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E141)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G141&lt;&gt;0,F141=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F141&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F141)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C141)*($E$5:$E$504=E141)*(($D$5:$D$504=D141)*(D141&lt;&gt;"")+($B$5:$B$504=B141)*(B141&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B141="",C141="",D141="",E141="",F141=""),"",IF(OR(B141="",C141="",E141=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E141)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H141&lt;&gt;0,F141=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G141&lt;&gt;0,F141=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F141&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F141)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C141)*($E$5:$E$504=E141)*(($D$5:$D$504=D141)*(D141&lt;&gt;"")+($B$5:$B$504=B141)*(B141&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J141" s="5">
@@ -4239,11 +4267,11 @@
         <v/>
       </c>
       <c r="H142" s="5">
-        <f>IF(OR(C142="Удержание",C142="Зачёт встречного требования",C142="Неустойка заявлена"),N(E142),0)</f>
+        <f>IF(OR(C142="Удержание",C142="Зачёт встречного требования",C142="Неустойка заявлена",C142="Допработы без соглашения (спорно)"),N(E142),0)</f>
         <v/>
       </c>
       <c r="I142" s="6">
-        <f>IF(AND(B142="",C142="",D142="",E142="",F142=""),"",IF(OR(B142="",C142="",E142=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E142)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G142&lt;&gt;0,F142=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F142&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F142)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C142)*($E$5:$E$504=E142)*(($D$5:$D$504=D142)*(D142&lt;&gt;"")+($B$5:$B$504=B142)*(B142&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B142="",C142="",D142="",E142="",F142=""),"",IF(OR(B142="",C142="",E142=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E142)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H142&lt;&gt;0,F142=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G142&lt;&gt;0,F142=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F142&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F142)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C142)*($E$5:$E$504=E142)*(($D$5:$D$504=D142)*(D142&lt;&gt;"")+($B$5:$B$504=B142)*(B142&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J142" s="5">
@@ -4265,11 +4293,11 @@
         <v/>
       </c>
       <c r="H143" s="5">
-        <f>IF(OR(C143="Удержание",C143="Зачёт встречного требования",C143="Неустойка заявлена"),N(E143),0)</f>
+        <f>IF(OR(C143="Удержание",C143="Зачёт встречного требования",C143="Неустойка заявлена",C143="Допработы без соглашения (спорно)"),N(E143),0)</f>
         <v/>
       </c>
       <c r="I143" s="6">
-        <f>IF(AND(B143="",C143="",D143="",E143="",F143=""),"",IF(OR(B143="",C143="",E143=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E143)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G143&lt;&gt;0,F143=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F143&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F143)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C143)*($E$5:$E$504=E143)*(($D$5:$D$504=D143)*(D143&lt;&gt;"")+($B$5:$B$504=B143)*(B143&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B143="",C143="",D143="",E143="",F143=""),"",IF(OR(B143="",C143="",E143=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E143)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H143&lt;&gt;0,F143=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G143&lt;&gt;0,F143=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F143&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F143)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C143)*($E$5:$E$504=E143)*(($D$5:$D$504=D143)*(D143&lt;&gt;"")+($B$5:$B$504=B143)*(B143&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J143" s="5">
@@ -4291,11 +4319,11 @@
         <v/>
       </c>
       <c r="H144" s="5">
-        <f>IF(OR(C144="Удержание",C144="Зачёт встречного требования",C144="Неустойка заявлена"),N(E144),0)</f>
+        <f>IF(OR(C144="Удержание",C144="Зачёт встречного требования",C144="Неустойка заявлена",C144="Допработы без соглашения (спорно)"),N(E144),0)</f>
         <v/>
       </c>
       <c r="I144" s="6">
-        <f>IF(AND(B144="",C144="",D144="",E144="",F144=""),"",IF(OR(B144="",C144="",E144=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E144)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G144&lt;&gt;0,F144=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F144&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F144)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C144)*($E$5:$E$504=E144)*(($D$5:$D$504=D144)*(D144&lt;&gt;"")+($B$5:$B$504=B144)*(B144&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B144="",C144="",D144="",E144="",F144=""),"",IF(OR(B144="",C144="",E144=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E144)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H144&lt;&gt;0,F144=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G144&lt;&gt;0,F144=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F144&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F144)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C144)*($E$5:$E$504=E144)*(($D$5:$D$504=D144)*(D144&lt;&gt;"")+($B$5:$B$504=B144)*(B144&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J144" s="5">
@@ -4317,11 +4345,11 @@
         <v/>
       </c>
       <c r="H145" s="5">
-        <f>IF(OR(C145="Удержание",C145="Зачёт встречного требования",C145="Неустойка заявлена"),N(E145),0)</f>
+        <f>IF(OR(C145="Удержание",C145="Зачёт встречного требования",C145="Неустойка заявлена",C145="Допработы без соглашения (спорно)"),N(E145),0)</f>
         <v/>
       </c>
       <c r="I145" s="6">
-        <f>IF(AND(B145="",C145="",D145="",E145="",F145=""),"",IF(OR(B145="",C145="",E145=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E145)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G145&lt;&gt;0,F145=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F145&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F145)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C145)*($E$5:$E$504=E145)*(($D$5:$D$504=D145)*(D145&lt;&gt;"")+($B$5:$B$504=B145)*(B145&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B145="",C145="",D145="",E145="",F145=""),"",IF(OR(B145="",C145="",E145=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E145)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H145&lt;&gt;0,F145=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G145&lt;&gt;0,F145=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F145&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F145)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C145)*($E$5:$E$504=E145)*(($D$5:$D$504=D145)*(D145&lt;&gt;"")+($B$5:$B$504=B145)*(B145&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J145" s="5">
@@ -4343,11 +4371,11 @@
         <v/>
       </c>
       <c r="H146" s="5">
-        <f>IF(OR(C146="Удержание",C146="Зачёт встречного требования",C146="Неустойка заявлена"),N(E146),0)</f>
+        <f>IF(OR(C146="Удержание",C146="Зачёт встречного требования",C146="Неустойка заявлена",C146="Допработы без соглашения (спорно)"),N(E146),0)</f>
         <v/>
       </c>
       <c r="I146" s="6">
-        <f>IF(AND(B146="",C146="",D146="",E146="",F146=""),"",IF(OR(B146="",C146="",E146=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E146)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G146&lt;&gt;0,F146=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F146&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F146)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C146)*($E$5:$E$504=E146)*(($D$5:$D$504=D146)*(D146&lt;&gt;"")+($B$5:$B$504=B146)*(B146&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B146="",C146="",D146="",E146="",F146=""),"",IF(OR(B146="",C146="",E146=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E146)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H146&lt;&gt;0,F146=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G146&lt;&gt;0,F146=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F146&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F146)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C146)*($E$5:$E$504=E146)*(($D$5:$D$504=D146)*(D146&lt;&gt;"")+($B$5:$B$504=B146)*(B146&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J146" s="5">
@@ -4369,11 +4397,11 @@
         <v/>
       </c>
       <c r="H147" s="5">
-        <f>IF(OR(C147="Удержание",C147="Зачёт встречного требования",C147="Неустойка заявлена"),N(E147),0)</f>
+        <f>IF(OR(C147="Удержание",C147="Зачёт встречного требования",C147="Неустойка заявлена",C147="Допработы без соглашения (спорно)"),N(E147),0)</f>
         <v/>
       </c>
       <c r="I147" s="6">
-        <f>IF(AND(B147="",C147="",D147="",E147="",F147=""),"",IF(OR(B147="",C147="",E147=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E147)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G147&lt;&gt;0,F147=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F147&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F147)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C147)*($E$5:$E$504=E147)*(($D$5:$D$504=D147)*(D147&lt;&gt;"")+($B$5:$B$504=B147)*(B147&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B147="",C147="",D147="",E147="",F147=""),"",IF(OR(B147="",C147="",E147=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E147)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H147&lt;&gt;0,F147=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G147&lt;&gt;0,F147=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F147&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F147)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C147)*($E$5:$E$504=E147)*(($D$5:$D$504=D147)*(D147&lt;&gt;"")+($B$5:$B$504=B147)*(B147&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J147" s="5">
@@ -4395,11 +4423,11 @@
         <v/>
       </c>
       <c r="H148" s="5">
-        <f>IF(OR(C148="Удержание",C148="Зачёт встречного требования",C148="Неустойка заявлена"),N(E148),0)</f>
+        <f>IF(OR(C148="Удержание",C148="Зачёт встречного требования",C148="Неустойка заявлена",C148="Допработы без соглашения (спорно)"),N(E148),0)</f>
         <v/>
       </c>
       <c r="I148" s="6">
-        <f>IF(AND(B148="",C148="",D148="",E148="",F148=""),"",IF(OR(B148="",C148="",E148=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E148)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G148&lt;&gt;0,F148=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F148&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F148)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C148)*($E$5:$E$504=E148)*(($D$5:$D$504=D148)*(D148&lt;&gt;"")+($B$5:$B$504=B148)*(B148&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B148="",C148="",D148="",E148="",F148=""),"",IF(OR(B148="",C148="",E148=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E148)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H148&lt;&gt;0,F148=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G148&lt;&gt;0,F148=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F148&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F148)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C148)*($E$5:$E$504=E148)*(($D$5:$D$504=D148)*(D148&lt;&gt;"")+($B$5:$B$504=B148)*(B148&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J148" s="5">
@@ -4421,11 +4449,11 @@
         <v/>
       </c>
       <c r="H149" s="5">
-        <f>IF(OR(C149="Удержание",C149="Зачёт встречного требования",C149="Неустойка заявлена"),N(E149),0)</f>
+        <f>IF(OR(C149="Удержание",C149="Зачёт встречного требования",C149="Неустойка заявлена",C149="Допработы без соглашения (спорно)"),N(E149),0)</f>
         <v/>
       </c>
       <c r="I149" s="6">
-        <f>IF(AND(B149="",C149="",D149="",E149="",F149=""),"",IF(OR(B149="",C149="",E149=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E149)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G149&lt;&gt;0,F149=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F149&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F149)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C149)*($E$5:$E$504=E149)*(($D$5:$D$504=D149)*(D149&lt;&gt;"")+($B$5:$B$504=B149)*(B149&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B149="",C149="",D149="",E149="",F149=""),"",IF(OR(B149="",C149="",E149=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E149)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H149&lt;&gt;0,F149=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G149&lt;&gt;0,F149=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F149&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F149)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C149)*($E$5:$E$504=E149)*(($D$5:$D$504=D149)*(D149&lt;&gt;"")+($B$5:$B$504=B149)*(B149&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J149" s="5">
@@ -4447,11 +4475,11 @@
         <v/>
       </c>
       <c r="H150" s="5">
-        <f>IF(OR(C150="Удержание",C150="Зачёт встречного требования",C150="Неустойка заявлена"),N(E150),0)</f>
+        <f>IF(OR(C150="Удержание",C150="Зачёт встречного требования",C150="Неустойка заявлена",C150="Допработы без соглашения (спорно)"),N(E150),0)</f>
         <v/>
       </c>
       <c r="I150" s="6">
-        <f>IF(AND(B150="",C150="",D150="",E150="",F150=""),"",IF(OR(B150="",C150="",E150=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E150)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G150&lt;&gt;0,F150=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F150&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F150)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C150)*($E$5:$E$504=E150)*(($D$5:$D$504=D150)*(D150&lt;&gt;"")+($B$5:$B$504=B150)*(B150&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B150="",C150="",D150="",E150="",F150=""),"",IF(OR(B150="",C150="",E150=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E150)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H150&lt;&gt;0,F150=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G150&lt;&gt;0,F150=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F150&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F150)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C150)*($E$5:$E$504=E150)*(($D$5:$D$504=D150)*(D150&lt;&gt;"")+($B$5:$B$504=B150)*(B150&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J150" s="5">
@@ -4473,11 +4501,11 @@
         <v/>
       </c>
       <c r="H151" s="5">
-        <f>IF(OR(C151="Удержание",C151="Зачёт встречного требования",C151="Неустойка заявлена"),N(E151),0)</f>
+        <f>IF(OR(C151="Удержание",C151="Зачёт встречного требования",C151="Неустойка заявлена",C151="Допработы без соглашения (спорно)"),N(E151),0)</f>
         <v/>
       </c>
       <c r="I151" s="6">
-        <f>IF(AND(B151="",C151="",D151="",E151="",F151=""),"",IF(OR(B151="",C151="",E151=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E151)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G151&lt;&gt;0,F151=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F151&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F151)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C151)*($E$5:$E$504=E151)*(($D$5:$D$504=D151)*(D151&lt;&gt;"")+($B$5:$B$504=B151)*(B151&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B151="",C151="",D151="",E151="",F151=""),"",IF(OR(B151="",C151="",E151=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E151)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H151&lt;&gt;0,F151=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G151&lt;&gt;0,F151=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F151&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F151)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C151)*($E$5:$E$504=E151)*(($D$5:$D$504=D151)*(D151&lt;&gt;"")+($B$5:$B$504=B151)*(B151&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J151" s="5">
@@ -4499,11 +4527,11 @@
         <v/>
       </c>
       <c r="H152" s="5">
-        <f>IF(OR(C152="Удержание",C152="Зачёт встречного требования",C152="Неустойка заявлена"),N(E152),0)</f>
+        <f>IF(OR(C152="Удержание",C152="Зачёт встречного требования",C152="Неустойка заявлена",C152="Допработы без соглашения (спорно)"),N(E152),0)</f>
         <v/>
       </c>
       <c r="I152" s="6">
-        <f>IF(AND(B152="",C152="",D152="",E152="",F152=""),"",IF(OR(B152="",C152="",E152=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E152)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G152&lt;&gt;0,F152=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F152&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F152)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C152)*($E$5:$E$504=E152)*(($D$5:$D$504=D152)*(D152&lt;&gt;"")+($B$5:$B$504=B152)*(B152&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B152="",C152="",D152="",E152="",F152=""),"",IF(OR(B152="",C152="",E152=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E152)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H152&lt;&gt;0,F152=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G152&lt;&gt;0,F152=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F152&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F152)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C152)*($E$5:$E$504=E152)*(($D$5:$D$504=D152)*(D152&lt;&gt;"")+($B$5:$B$504=B152)*(B152&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J152" s="5">
@@ -4525,11 +4553,11 @@
         <v/>
       </c>
       <c r="H153" s="5">
-        <f>IF(OR(C153="Удержание",C153="Зачёт встречного требования",C153="Неустойка заявлена"),N(E153),0)</f>
+        <f>IF(OR(C153="Удержание",C153="Зачёт встречного требования",C153="Неустойка заявлена",C153="Допработы без соглашения (спорно)"),N(E153),0)</f>
         <v/>
       </c>
       <c r="I153" s="6">
-        <f>IF(AND(B153="",C153="",D153="",E153="",F153=""),"",IF(OR(B153="",C153="",E153=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E153)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G153&lt;&gt;0,F153=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F153&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F153)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C153)*($E$5:$E$504=E153)*(($D$5:$D$504=D153)*(D153&lt;&gt;"")+($B$5:$B$504=B153)*(B153&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B153="",C153="",D153="",E153="",F153=""),"",IF(OR(B153="",C153="",E153=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E153)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H153&lt;&gt;0,F153=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G153&lt;&gt;0,F153=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F153&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F153)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C153)*($E$5:$E$504=E153)*(($D$5:$D$504=D153)*(D153&lt;&gt;"")+($B$5:$B$504=B153)*(B153&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J153" s="5">
@@ -4551,11 +4579,11 @@
         <v/>
       </c>
       <c r="H154" s="5">
-        <f>IF(OR(C154="Удержание",C154="Зачёт встречного требования",C154="Неустойка заявлена"),N(E154),0)</f>
+        <f>IF(OR(C154="Удержание",C154="Зачёт встречного требования",C154="Неустойка заявлена",C154="Допработы без соглашения (спорно)"),N(E154),0)</f>
         <v/>
       </c>
       <c r="I154" s="6">
-        <f>IF(AND(B154="",C154="",D154="",E154="",F154=""),"",IF(OR(B154="",C154="",E154=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E154)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G154&lt;&gt;0,F154=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F154&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F154)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C154)*($E$5:$E$504=E154)*(($D$5:$D$504=D154)*(D154&lt;&gt;"")+($B$5:$B$504=B154)*(B154&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B154="",C154="",D154="",E154="",F154=""),"",IF(OR(B154="",C154="",E154=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E154)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H154&lt;&gt;0,F154=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G154&lt;&gt;0,F154=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F154&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F154)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C154)*($E$5:$E$504=E154)*(($D$5:$D$504=D154)*(D154&lt;&gt;"")+($B$5:$B$504=B154)*(B154&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J154" s="5">
@@ -4577,11 +4605,11 @@
         <v/>
       </c>
       <c r="H155" s="5">
-        <f>IF(OR(C155="Удержание",C155="Зачёт встречного требования",C155="Неустойка заявлена"),N(E155),0)</f>
+        <f>IF(OR(C155="Удержание",C155="Зачёт встречного требования",C155="Неустойка заявлена",C155="Допработы без соглашения (спорно)"),N(E155),0)</f>
         <v/>
       </c>
       <c r="I155" s="6">
-        <f>IF(AND(B155="",C155="",D155="",E155="",F155=""),"",IF(OR(B155="",C155="",E155=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E155)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G155&lt;&gt;0,F155=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F155&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F155)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C155)*($E$5:$E$504=E155)*(($D$5:$D$504=D155)*(D155&lt;&gt;"")+($B$5:$B$504=B155)*(B155&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B155="",C155="",D155="",E155="",F155=""),"",IF(OR(B155="",C155="",E155=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E155)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H155&lt;&gt;0,F155=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G155&lt;&gt;0,F155=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F155&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F155)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C155)*($E$5:$E$504=E155)*(($D$5:$D$504=D155)*(D155&lt;&gt;"")+($B$5:$B$504=B155)*(B155&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J155" s="5">
@@ -4603,11 +4631,11 @@
         <v/>
       </c>
       <c r="H156" s="5">
-        <f>IF(OR(C156="Удержание",C156="Зачёт встречного требования",C156="Неустойка заявлена"),N(E156),0)</f>
+        <f>IF(OR(C156="Удержание",C156="Зачёт встречного требования",C156="Неустойка заявлена",C156="Допработы без соглашения (спорно)"),N(E156),0)</f>
         <v/>
       </c>
       <c r="I156" s="6">
-        <f>IF(AND(B156="",C156="",D156="",E156="",F156=""),"",IF(OR(B156="",C156="",E156=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E156)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G156&lt;&gt;0,F156=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F156&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F156)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C156)*($E$5:$E$504=E156)*(($D$5:$D$504=D156)*(D156&lt;&gt;"")+($B$5:$B$504=B156)*(B156&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B156="",C156="",D156="",E156="",F156=""),"",IF(OR(B156="",C156="",E156=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E156)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H156&lt;&gt;0,F156=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G156&lt;&gt;0,F156=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F156&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F156)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C156)*($E$5:$E$504=E156)*(($D$5:$D$504=D156)*(D156&lt;&gt;"")+($B$5:$B$504=B156)*(B156&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J156" s="5">
@@ -4629,11 +4657,11 @@
         <v/>
       </c>
       <c r="H157" s="5">
-        <f>IF(OR(C157="Удержание",C157="Зачёт встречного требования",C157="Неустойка заявлена"),N(E157),0)</f>
+        <f>IF(OR(C157="Удержание",C157="Зачёт встречного требования",C157="Неустойка заявлена",C157="Допработы без соглашения (спорно)"),N(E157),0)</f>
         <v/>
       </c>
       <c r="I157" s="6">
-        <f>IF(AND(B157="",C157="",D157="",E157="",F157=""),"",IF(OR(B157="",C157="",E157=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E157)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G157&lt;&gt;0,F157=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F157&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F157)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C157)*($E$5:$E$504=E157)*(($D$5:$D$504=D157)*(D157&lt;&gt;"")+($B$5:$B$504=B157)*(B157&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B157="",C157="",D157="",E157="",F157=""),"",IF(OR(B157="",C157="",E157=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E157)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H157&lt;&gt;0,F157=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G157&lt;&gt;0,F157=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F157&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F157)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C157)*($E$5:$E$504=E157)*(($D$5:$D$504=D157)*(D157&lt;&gt;"")+($B$5:$B$504=B157)*(B157&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J157" s="5">
@@ -4655,11 +4683,11 @@
         <v/>
       </c>
       <c r="H158" s="5">
-        <f>IF(OR(C158="Удержание",C158="Зачёт встречного требования",C158="Неустойка заявлена"),N(E158),0)</f>
+        <f>IF(OR(C158="Удержание",C158="Зачёт встречного требования",C158="Неустойка заявлена",C158="Допработы без соглашения (спорно)"),N(E158),0)</f>
         <v/>
       </c>
       <c r="I158" s="6">
-        <f>IF(AND(B158="",C158="",D158="",E158="",F158=""),"",IF(OR(B158="",C158="",E158=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E158)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G158&lt;&gt;0,F158=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F158&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F158)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C158)*($E$5:$E$504=E158)*(($D$5:$D$504=D158)*(D158&lt;&gt;"")+($B$5:$B$504=B158)*(B158&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B158="",C158="",D158="",E158="",F158=""),"",IF(OR(B158="",C158="",E158=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E158)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H158&lt;&gt;0,F158=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G158&lt;&gt;0,F158=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F158&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F158)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C158)*($E$5:$E$504=E158)*(($D$5:$D$504=D158)*(D158&lt;&gt;"")+($B$5:$B$504=B158)*(B158&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J158" s="5">
@@ -4681,11 +4709,11 @@
         <v/>
       </c>
       <c r="H159" s="5">
-        <f>IF(OR(C159="Удержание",C159="Зачёт встречного требования",C159="Неустойка заявлена"),N(E159),0)</f>
+        <f>IF(OR(C159="Удержание",C159="Зачёт встречного требования",C159="Неустойка заявлена",C159="Допработы без соглашения (спорно)"),N(E159),0)</f>
         <v/>
       </c>
       <c r="I159" s="6">
-        <f>IF(AND(B159="",C159="",D159="",E159="",F159=""),"",IF(OR(B159="",C159="",E159=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E159)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G159&lt;&gt;0,F159=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F159&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F159)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C159)*($E$5:$E$504=E159)*(($D$5:$D$504=D159)*(D159&lt;&gt;"")+($B$5:$B$504=B159)*(B159&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B159="",C159="",D159="",E159="",F159=""),"",IF(OR(B159="",C159="",E159=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E159)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H159&lt;&gt;0,F159=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G159&lt;&gt;0,F159=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F159&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F159)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C159)*($E$5:$E$504=E159)*(($D$5:$D$504=D159)*(D159&lt;&gt;"")+($B$5:$B$504=B159)*(B159&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J159" s="5">
@@ -4707,11 +4735,11 @@
         <v/>
       </c>
       <c r="H160" s="5">
-        <f>IF(OR(C160="Удержание",C160="Зачёт встречного требования",C160="Неустойка заявлена"),N(E160),0)</f>
+        <f>IF(OR(C160="Удержание",C160="Зачёт встречного требования",C160="Неустойка заявлена",C160="Допработы без соглашения (спорно)"),N(E160),0)</f>
         <v/>
       </c>
       <c r="I160" s="6">
-        <f>IF(AND(B160="",C160="",D160="",E160="",F160=""),"",IF(OR(B160="",C160="",E160=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E160)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G160&lt;&gt;0,F160=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F160&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F160)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C160)*($E$5:$E$504=E160)*(($D$5:$D$504=D160)*(D160&lt;&gt;"")+($B$5:$B$504=B160)*(B160&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B160="",C160="",D160="",E160="",F160=""),"",IF(OR(B160="",C160="",E160=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E160)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H160&lt;&gt;0,F160=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G160&lt;&gt;0,F160=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F160&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F160)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C160)*($E$5:$E$504=E160)*(($D$5:$D$504=D160)*(D160&lt;&gt;"")+($B$5:$B$504=B160)*(B160&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J160" s="5">
@@ -4733,11 +4761,11 @@
         <v/>
       </c>
       <c r="H161" s="5">
-        <f>IF(OR(C161="Удержание",C161="Зачёт встречного требования",C161="Неустойка заявлена"),N(E161),0)</f>
+        <f>IF(OR(C161="Удержание",C161="Зачёт встречного требования",C161="Неустойка заявлена",C161="Допработы без соглашения (спорно)"),N(E161),0)</f>
         <v/>
       </c>
       <c r="I161" s="6">
-        <f>IF(AND(B161="",C161="",D161="",E161="",F161=""),"",IF(OR(B161="",C161="",E161=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E161)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G161&lt;&gt;0,F161=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F161&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F161)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C161)*($E$5:$E$504=E161)*(($D$5:$D$504=D161)*(D161&lt;&gt;"")+($B$5:$B$504=B161)*(B161&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B161="",C161="",D161="",E161="",F161=""),"",IF(OR(B161="",C161="",E161=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E161)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H161&lt;&gt;0,F161=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G161&lt;&gt;0,F161=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F161&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F161)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C161)*($E$5:$E$504=E161)*(($D$5:$D$504=D161)*(D161&lt;&gt;"")+($B$5:$B$504=B161)*(B161&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J161" s="5">
@@ -4759,11 +4787,11 @@
         <v/>
       </c>
       <c r="H162" s="5">
-        <f>IF(OR(C162="Удержание",C162="Зачёт встречного требования",C162="Неустойка заявлена"),N(E162),0)</f>
+        <f>IF(OR(C162="Удержание",C162="Зачёт встречного требования",C162="Неустойка заявлена",C162="Допработы без соглашения (спорно)"),N(E162),0)</f>
         <v/>
       </c>
       <c r="I162" s="6">
-        <f>IF(AND(B162="",C162="",D162="",E162="",F162=""),"",IF(OR(B162="",C162="",E162=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E162)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G162&lt;&gt;0,F162=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F162&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F162)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C162)*($E$5:$E$504=E162)*(($D$5:$D$504=D162)*(D162&lt;&gt;"")+($B$5:$B$504=B162)*(B162&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B162="",C162="",D162="",E162="",F162=""),"",IF(OR(B162="",C162="",E162=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E162)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H162&lt;&gt;0,F162=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G162&lt;&gt;0,F162=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F162&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F162)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C162)*($E$5:$E$504=E162)*(($D$5:$D$504=D162)*(D162&lt;&gt;"")+($B$5:$B$504=B162)*(B162&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J162" s="5">
@@ -4785,11 +4813,11 @@
         <v/>
       </c>
       <c r="H163" s="5">
-        <f>IF(OR(C163="Удержание",C163="Зачёт встречного требования",C163="Неустойка заявлена"),N(E163),0)</f>
+        <f>IF(OR(C163="Удержание",C163="Зачёт встречного требования",C163="Неустойка заявлена",C163="Допработы без соглашения (спорно)"),N(E163),0)</f>
         <v/>
       </c>
       <c r="I163" s="6">
-        <f>IF(AND(B163="",C163="",D163="",E163="",F163=""),"",IF(OR(B163="",C163="",E163=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E163)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G163&lt;&gt;0,F163=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F163&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F163)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C163)*($E$5:$E$504=E163)*(($D$5:$D$504=D163)*(D163&lt;&gt;"")+($B$5:$B$504=B163)*(B163&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B163="",C163="",D163="",E163="",F163=""),"",IF(OR(B163="",C163="",E163=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E163)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H163&lt;&gt;0,F163=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G163&lt;&gt;0,F163=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F163&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F163)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C163)*($E$5:$E$504=E163)*(($D$5:$D$504=D163)*(D163&lt;&gt;"")+($B$5:$B$504=B163)*(B163&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J163" s="5">
@@ -4811,11 +4839,11 @@
         <v/>
       </c>
       <c r="H164" s="5">
-        <f>IF(OR(C164="Удержание",C164="Зачёт встречного требования",C164="Неустойка заявлена"),N(E164),0)</f>
+        <f>IF(OR(C164="Удержание",C164="Зачёт встречного требования",C164="Неустойка заявлена",C164="Допработы без соглашения (спорно)"),N(E164),0)</f>
         <v/>
       </c>
       <c r="I164" s="6">
-        <f>IF(AND(B164="",C164="",D164="",E164="",F164=""),"",IF(OR(B164="",C164="",E164=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E164)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G164&lt;&gt;0,F164=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F164&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F164)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C164)*($E$5:$E$504=E164)*(($D$5:$D$504=D164)*(D164&lt;&gt;"")+($B$5:$B$504=B164)*(B164&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B164="",C164="",D164="",E164="",F164=""),"",IF(OR(B164="",C164="",E164=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E164)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H164&lt;&gt;0,F164=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G164&lt;&gt;0,F164=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F164&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F164)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C164)*($E$5:$E$504=E164)*(($D$5:$D$504=D164)*(D164&lt;&gt;"")+($B$5:$B$504=B164)*(B164&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J164" s="5">
@@ -4837,11 +4865,11 @@
         <v/>
       </c>
       <c r="H165" s="5">
-        <f>IF(OR(C165="Удержание",C165="Зачёт встречного требования",C165="Неустойка заявлена"),N(E165),0)</f>
+        <f>IF(OR(C165="Удержание",C165="Зачёт встречного требования",C165="Неустойка заявлена",C165="Допработы без соглашения (спорно)"),N(E165),0)</f>
         <v/>
       </c>
       <c r="I165" s="6">
-        <f>IF(AND(B165="",C165="",D165="",E165="",F165=""),"",IF(OR(B165="",C165="",E165=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E165)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G165&lt;&gt;0,F165=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F165&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F165)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C165)*($E$5:$E$504=E165)*(($D$5:$D$504=D165)*(D165&lt;&gt;"")+($B$5:$B$504=B165)*(B165&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B165="",C165="",D165="",E165="",F165=""),"",IF(OR(B165="",C165="",E165=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E165)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H165&lt;&gt;0,F165=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G165&lt;&gt;0,F165=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F165&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F165)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C165)*($E$5:$E$504=E165)*(($D$5:$D$504=D165)*(D165&lt;&gt;"")+($B$5:$B$504=B165)*(B165&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J165" s="5">
@@ -4863,11 +4891,11 @@
         <v/>
       </c>
       <c r="H166" s="5">
-        <f>IF(OR(C166="Удержание",C166="Зачёт встречного требования",C166="Неустойка заявлена"),N(E166),0)</f>
+        <f>IF(OR(C166="Удержание",C166="Зачёт встречного требования",C166="Неустойка заявлена",C166="Допработы без соглашения (спорно)"),N(E166),0)</f>
         <v/>
       </c>
       <c r="I166" s="6">
-        <f>IF(AND(B166="",C166="",D166="",E166="",F166=""),"",IF(OR(B166="",C166="",E166=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E166)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G166&lt;&gt;0,F166=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F166&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F166)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C166)*($E$5:$E$504=E166)*(($D$5:$D$504=D166)*(D166&lt;&gt;"")+($B$5:$B$504=B166)*(B166&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B166="",C166="",D166="",E166="",F166=""),"",IF(OR(B166="",C166="",E166=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E166)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H166&lt;&gt;0,F166=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G166&lt;&gt;0,F166=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F166&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F166)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C166)*($E$5:$E$504=E166)*(($D$5:$D$504=D166)*(D166&lt;&gt;"")+($B$5:$B$504=B166)*(B166&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J166" s="5">
@@ -4889,11 +4917,11 @@
         <v/>
       </c>
       <c r="H167" s="5">
-        <f>IF(OR(C167="Удержание",C167="Зачёт встречного требования",C167="Неустойка заявлена"),N(E167),0)</f>
+        <f>IF(OR(C167="Удержание",C167="Зачёт встречного требования",C167="Неустойка заявлена",C167="Допработы без соглашения (спорно)"),N(E167),0)</f>
         <v/>
       </c>
       <c r="I167" s="6">
-        <f>IF(AND(B167="",C167="",D167="",E167="",F167=""),"",IF(OR(B167="",C167="",E167=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E167)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G167&lt;&gt;0,F167=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F167&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F167)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C167)*($E$5:$E$504=E167)*(($D$5:$D$504=D167)*(D167&lt;&gt;"")+($B$5:$B$504=B167)*(B167&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B167="",C167="",D167="",E167="",F167=""),"",IF(OR(B167="",C167="",E167=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E167)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H167&lt;&gt;0,F167=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G167&lt;&gt;0,F167=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F167&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F167)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C167)*($E$5:$E$504=E167)*(($D$5:$D$504=D167)*(D167&lt;&gt;"")+($B$5:$B$504=B167)*(B167&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J167" s="5">
@@ -4915,11 +4943,11 @@
         <v/>
       </c>
       <c r="H168" s="5">
-        <f>IF(OR(C168="Удержание",C168="Зачёт встречного требования",C168="Неустойка заявлена"),N(E168),0)</f>
+        <f>IF(OR(C168="Удержание",C168="Зачёт встречного требования",C168="Неустойка заявлена",C168="Допработы без соглашения (спорно)"),N(E168),0)</f>
         <v/>
       </c>
       <c r="I168" s="6">
-        <f>IF(AND(B168="",C168="",D168="",E168="",F168=""),"",IF(OR(B168="",C168="",E168=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E168)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G168&lt;&gt;0,F168=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F168&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F168)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C168)*($E$5:$E$504=E168)*(($D$5:$D$504=D168)*(D168&lt;&gt;"")+($B$5:$B$504=B168)*(B168&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B168="",C168="",D168="",E168="",F168=""),"",IF(OR(B168="",C168="",E168=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E168)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H168&lt;&gt;0,F168=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G168&lt;&gt;0,F168=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F168&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F168)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C168)*($E$5:$E$504=E168)*(($D$5:$D$504=D168)*(D168&lt;&gt;"")+($B$5:$B$504=B168)*(B168&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J168" s="5">
@@ -4941,11 +4969,11 @@
         <v/>
       </c>
       <c r="H169" s="5">
-        <f>IF(OR(C169="Удержание",C169="Зачёт встречного требования",C169="Неустойка заявлена"),N(E169),0)</f>
+        <f>IF(OR(C169="Удержание",C169="Зачёт встречного требования",C169="Неустойка заявлена",C169="Допработы без соглашения (спорно)"),N(E169),0)</f>
         <v/>
       </c>
       <c r="I169" s="6">
-        <f>IF(AND(B169="",C169="",D169="",E169="",F169=""),"",IF(OR(B169="",C169="",E169=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E169)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G169&lt;&gt;0,F169=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F169&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F169)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C169)*($E$5:$E$504=E169)*(($D$5:$D$504=D169)*(D169&lt;&gt;"")+($B$5:$B$504=B169)*(B169&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B169="",C169="",D169="",E169="",F169=""),"",IF(OR(B169="",C169="",E169=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E169)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H169&lt;&gt;0,F169=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G169&lt;&gt;0,F169=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F169&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F169)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C169)*($E$5:$E$504=E169)*(($D$5:$D$504=D169)*(D169&lt;&gt;"")+($B$5:$B$504=B169)*(B169&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J169" s="5">
@@ -4967,11 +4995,11 @@
         <v/>
       </c>
       <c r="H170" s="5">
-        <f>IF(OR(C170="Удержание",C170="Зачёт встречного требования",C170="Неустойка заявлена"),N(E170),0)</f>
+        <f>IF(OR(C170="Удержание",C170="Зачёт встречного требования",C170="Неустойка заявлена",C170="Допработы без соглашения (спорно)"),N(E170),0)</f>
         <v/>
       </c>
       <c r="I170" s="6">
-        <f>IF(AND(B170="",C170="",D170="",E170="",F170=""),"",IF(OR(B170="",C170="",E170=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E170)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G170&lt;&gt;0,F170=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F170&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F170)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C170)*($E$5:$E$504=E170)*(($D$5:$D$504=D170)*(D170&lt;&gt;"")+($B$5:$B$504=B170)*(B170&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B170="",C170="",D170="",E170="",F170=""),"",IF(OR(B170="",C170="",E170=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E170)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H170&lt;&gt;0,F170=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G170&lt;&gt;0,F170=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F170&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F170)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C170)*($E$5:$E$504=E170)*(($D$5:$D$504=D170)*(D170&lt;&gt;"")+($B$5:$B$504=B170)*(B170&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J170" s="5">
@@ -4993,11 +5021,11 @@
         <v/>
       </c>
       <c r="H171" s="5">
-        <f>IF(OR(C171="Удержание",C171="Зачёт встречного требования",C171="Неустойка заявлена"),N(E171),0)</f>
+        <f>IF(OR(C171="Удержание",C171="Зачёт встречного требования",C171="Неустойка заявлена",C171="Допработы без соглашения (спорно)"),N(E171),0)</f>
         <v/>
       </c>
       <c r="I171" s="6">
-        <f>IF(AND(B171="",C171="",D171="",E171="",F171=""),"",IF(OR(B171="",C171="",E171=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E171)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G171&lt;&gt;0,F171=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F171&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F171)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C171)*($E$5:$E$504=E171)*(($D$5:$D$504=D171)*(D171&lt;&gt;"")+($B$5:$B$504=B171)*(B171&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B171="",C171="",D171="",E171="",F171=""),"",IF(OR(B171="",C171="",E171=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E171)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H171&lt;&gt;0,F171=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G171&lt;&gt;0,F171=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F171&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F171)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C171)*($E$5:$E$504=E171)*(($D$5:$D$504=D171)*(D171&lt;&gt;"")+($B$5:$B$504=B171)*(B171&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J171" s="5">
@@ -5019,11 +5047,11 @@
         <v/>
       </c>
       <c r="H172" s="5">
-        <f>IF(OR(C172="Удержание",C172="Зачёт встречного требования",C172="Неустойка заявлена"),N(E172),0)</f>
+        <f>IF(OR(C172="Удержание",C172="Зачёт встречного требования",C172="Неустойка заявлена",C172="Допработы без соглашения (спорно)"),N(E172),0)</f>
         <v/>
       </c>
       <c r="I172" s="6">
-        <f>IF(AND(B172="",C172="",D172="",E172="",F172=""),"",IF(OR(B172="",C172="",E172=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E172)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G172&lt;&gt;0,F172=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F172&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F172)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C172)*($E$5:$E$504=E172)*(($D$5:$D$504=D172)*(D172&lt;&gt;"")+($B$5:$B$504=B172)*(B172&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B172="",C172="",D172="",E172="",F172=""),"",IF(OR(B172="",C172="",E172=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E172)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H172&lt;&gt;0,F172=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G172&lt;&gt;0,F172=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F172&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F172)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C172)*($E$5:$E$504=E172)*(($D$5:$D$504=D172)*(D172&lt;&gt;"")+($B$5:$B$504=B172)*(B172&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J172" s="5">
@@ -5045,11 +5073,11 @@
         <v/>
       </c>
       <c r="H173" s="5">
-        <f>IF(OR(C173="Удержание",C173="Зачёт встречного требования",C173="Неустойка заявлена"),N(E173),0)</f>
+        <f>IF(OR(C173="Удержание",C173="Зачёт встречного требования",C173="Неустойка заявлена",C173="Допработы без соглашения (спорно)"),N(E173),0)</f>
         <v/>
       </c>
       <c r="I173" s="6">
-        <f>IF(AND(B173="",C173="",D173="",E173="",F173=""),"",IF(OR(B173="",C173="",E173=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E173)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G173&lt;&gt;0,F173=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F173&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F173)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C173)*($E$5:$E$504=E173)*(($D$5:$D$504=D173)*(D173&lt;&gt;"")+($B$5:$B$504=B173)*(B173&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B173="",C173="",D173="",E173="",F173=""),"",IF(OR(B173="",C173="",E173=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E173)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H173&lt;&gt;0,F173=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G173&lt;&gt;0,F173=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F173&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F173)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C173)*($E$5:$E$504=E173)*(($D$5:$D$504=D173)*(D173&lt;&gt;"")+($B$5:$B$504=B173)*(B173&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J173" s="5">
@@ -5071,11 +5099,11 @@
         <v/>
       </c>
       <c r="H174" s="5">
-        <f>IF(OR(C174="Удержание",C174="Зачёт встречного требования",C174="Неустойка заявлена"),N(E174),0)</f>
+        <f>IF(OR(C174="Удержание",C174="Зачёт встречного требования",C174="Неустойка заявлена",C174="Допработы без соглашения (спорно)"),N(E174),0)</f>
         <v/>
       </c>
       <c r="I174" s="6">
-        <f>IF(AND(B174="",C174="",D174="",E174="",F174=""),"",IF(OR(B174="",C174="",E174=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E174)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G174&lt;&gt;0,F174=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F174&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F174)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C174)*($E$5:$E$504=E174)*(($D$5:$D$504=D174)*(D174&lt;&gt;"")+($B$5:$B$504=B174)*(B174&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B174="",C174="",D174="",E174="",F174=""),"",IF(OR(B174="",C174="",E174=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E174)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H174&lt;&gt;0,F174=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G174&lt;&gt;0,F174=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F174&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F174)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C174)*($E$5:$E$504=E174)*(($D$5:$D$504=D174)*(D174&lt;&gt;"")+($B$5:$B$504=B174)*(B174&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J174" s="5">
@@ -5097,11 +5125,11 @@
         <v/>
       </c>
       <c r="H175" s="5">
-        <f>IF(OR(C175="Удержание",C175="Зачёт встречного требования",C175="Неустойка заявлена"),N(E175),0)</f>
+        <f>IF(OR(C175="Удержание",C175="Зачёт встречного требования",C175="Неустойка заявлена",C175="Допработы без соглашения (спорно)"),N(E175),0)</f>
         <v/>
       </c>
       <c r="I175" s="6">
-        <f>IF(AND(B175="",C175="",D175="",E175="",F175=""),"",IF(OR(B175="",C175="",E175=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E175)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G175&lt;&gt;0,F175=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F175&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F175)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C175)*($E$5:$E$504=E175)*(($D$5:$D$504=D175)*(D175&lt;&gt;"")+($B$5:$B$504=B175)*(B175&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B175="",C175="",D175="",E175="",F175=""),"",IF(OR(B175="",C175="",E175=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E175)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H175&lt;&gt;0,F175=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G175&lt;&gt;0,F175=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F175&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F175)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C175)*($E$5:$E$504=E175)*(($D$5:$D$504=D175)*(D175&lt;&gt;"")+($B$5:$B$504=B175)*(B175&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J175" s="5">
@@ -5123,11 +5151,11 @@
         <v/>
       </c>
       <c r="H176" s="5">
-        <f>IF(OR(C176="Удержание",C176="Зачёт встречного требования",C176="Неустойка заявлена"),N(E176),0)</f>
+        <f>IF(OR(C176="Удержание",C176="Зачёт встречного требования",C176="Неустойка заявлена",C176="Допработы без соглашения (спорно)"),N(E176),0)</f>
         <v/>
       </c>
       <c r="I176" s="6">
-        <f>IF(AND(B176="",C176="",D176="",E176="",F176=""),"",IF(OR(B176="",C176="",E176=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E176)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G176&lt;&gt;0,F176=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F176&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F176)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C176)*($E$5:$E$504=E176)*(($D$5:$D$504=D176)*(D176&lt;&gt;"")+($B$5:$B$504=B176)*(B176&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B176="",C176="",D176="",E176="",F176=""),"",IF(OR(B176="",C176="",E176=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E176)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H176&lt;&gt;0,F176=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G176&lt;&gt;0,F176=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F176&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F176)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C176)*($E$5:$E$504=E176)*(($D$5:$D$504=D176)*(D176&lt;&gt;"")+($B$5:$B$504=B176)*(B176&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J176" s="5">
@@ -5149,11 +5177,11 @@
         <v/>
       </c>
       <c r="H177" s="5">
-        <f>IF(OR(C177="Удержание",C177="Зачёт встречного требования",C177="Неустойка заявлена"),N(E177),0)</f>
+        <f>IF(OR(C177="Удержание",C177="Зачёт встречного требования",C177="Неустойка заявлена",C177="Допработы без соглашения (спорно)"),N(E177),0)</f>
         <v/>
       </c>
       <c r="I177" s="6">
-        <f>IF(AND(B177="",C177="",D177="",E177="",F177=""),"",IF(OR(B177="",C177="",E177=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E177)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G177&lt;&gt;0,F177=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F177&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F177)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C177)*($E$5:$E$504=E177)*(($D$5:$D$504=D177)*(D177&lt;&gt;"")+($B$5:$B$504=B177)*(B177&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B177="",C177="",D177="",E177="",F177=""),"",IF(OR(B177="",C177="",E177=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E177)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H177&lt;&gt;0,F177=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G177&lt;&gt;0,F177=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F177&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F177)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C177)*($E$5:$E$504=E177)*(($D$5:$D$504=D177)*(D177&lt;&gt;"")+($B$5:$B$504=B177)*(B177&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J177" s="5">
@@ -5175,11 +5203,11 @@
         <v/>
       </c>
       <c r="H178" s="5">
-        <f>IF(OR(C178="Удержание",C178="Зачёт встречного требования",C178="Неустойка заявлена"),N(E178),0)</f>
+        <f>IF(OR(C178="Удержание",C178="Зачёт встречного требования",C178="Неустойка заявлена",C178="Допработы без соглашения (спорно)"),N(E178),0)</f>
         <v/>
       </c>
       <c r="I178" s="6">
-        <f>IF(AND(B178="",C178="",D178="",E178="",F178=""),"",IF(OR(B178="",C178="",E178=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E178)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G178&lt;&gt;0,F178=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F178&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F178)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C178)*($E$5:$E$504=E178)*(($D$5:$D$504=D178)*(D178&lt;&gt;"")+($B$5:$B$504=B178)*(B178&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B178="",C178="",D178="",E178="",F178=""),"",IF(OR(B178="",C178="",E178=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E178)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H178&lt;&gt;0,F178=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G178&lt;&gt;0,F178=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F178&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F178)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C178)*($E$5:$E$504=E178)*(($D$5:$D$504=D178)*(D178&lt;&gt;"")+($B$5:$B$504=B178)*(B178&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J178" s="5">
@@ -5201,11 +5229,11 @@
         <v/>
       </c>
       <c r="H179" s="5">
-        <f>IF(OR(C179="Удержание",C179="Зачёт встречного требования",C179="Неустойка заявлена"),N(E179),0)</f>
+        <f>IF(OR(C179="Удержание",C179="Зачёт встречного требования",C179="Неустойка заявлена",C179="Допработы без соглашения (спорно)"),N(E179),0)</f>
         <v/>
       </c>
       <c r="I179" s="6">
-        <f>IF(AND(B179="",C179="",D179="",E179="",F179=""),"",IF(OR(B179="",C179="",E179=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E179)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G179&lt;&gt;0,F179=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F179&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F179)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C179)*($E$5:$E$504=E179)*(($D$5:$D$504=D179)*(D179&lt;&gt;"")+($B$5:$B$504=B179)*(B179&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B179="",C179="",D179="",E179="",F179=""),"",IF(OR(B179="",C179="",E179=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E179)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H179&lt;&gt;0,F179=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G179&lt;&gt;0,F179=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F179&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F179)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C179)*($E$5:$E$504=E179)*(($D$5:$D$504=D179)*(D179&lt;&gt;"")+($B$5:$B$504=B179)*(B179&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J179" s="5">
@@ -5227,11 +5255,11 @@
         <v/>
       </c>
       <c r="H180" s="5">
-        <f>IF(OR(C180="Удержание",C180="Зачёт встречного требования",C180="Неустойка заявлена"),N(E180),0)</f>
+        <f>IF(OR(C180="Удержание",C180="Зачёт встречного требования",C180="Неустойка заявлена",C180="Допработы без соглашения (спорно)"),N(E180),0)</f>
         <v/>
       </c>
       <c r="I180" s="6">
-        <f>IF(AND(B180="",C180="",D180="",E180="",F180=""),"",IF(OR(B180="",C180="",E180=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E180)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G180&lt;&gt;0,F180=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F180&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F180)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C180)*($E$5:$E$504=E180)*(($D$5:$D$504=D180)*(D180&lt;&gt;"")+($B$5:$B$504=B180)*(B180&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B180="",C180="",D180="",E180="",F180=""),"",IF(OR(B180="",C180="",E180=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E180)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H180&lt;&gt;0,F180=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G180&lt;&gt;0,F180=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F180&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F180)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C180)*($E$5:$E$504=E180)*(($D$5:$D$504=D180)*(D180&lt;&gt;"")+($B$5:$B$504=B180)*(B180&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J180" s="5">
@@ -5253,11 +5281,11 @@
         <v/>
       </c>
       <c r="H181" s="5">
-        <f>IF(OR(C181="Удержание",C181="Зачёт встречного требования",C181="Неустойка заявлена"),N(E181),0)</f>
+        <f>IF(OR(C181="Удержание",C181="Зачёт встречного требования",C181="Неустойка заявлена",C181="Допработы без соглашения (спорно)"),N(E181),0)</f>
         <v/>
       </c>
       <c r="I181" s="6">
-        <f>IF(AND(B181="",C181="",D181="",E181="",F181=""),"",IF(OR(B181="",C181="",E181=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E181)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G181&lt;&gt;0,F181=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F181&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F181)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C181)*($E$5:$E$504=E181)*(($D$5:$D$504=D181)*(D181&lt;&gt;"")+($B$5:$B$504=B181)*(B181&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B181="",C181="",D181="",E181="",F181=""),"",IF(OR(B181="",C181="",E181=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E181)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H181&lt;&gt;0,F181=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G181&lt;&gt;0,F181=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F181&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F181)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C181)*($E$5:$E$504=E181)*(($D$5:$D$504=D181)*(D181&lt;&gt;"")+($B$5:$B$504=B181)*(B181&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J181" s="5">
@@ -5279,11 +5307,11 @@
         <v/>
       </c>
       <c r="H182" s="5">
-        <f>IF(OR(C182="Удержание",C182="Зачёт встречного требования",C182="Неустойка заявлена"),N(E182),0)</f>
+        <f>IF(OR(C182="Удержание",C182="Зачёт встречного требования",C182="Неустойка заявлена",C182="Допработы без соглашения (спорно)"),N(E182),0)</f>
         <v/>
       </c>
       <c r="I182" s="6">
-        <f>IF(AND(B182="",C182="",D182="",E182="",F182=""),"",IF(OR(B182="",C182="",E182=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E182)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G182&lt;&gt;0,F182=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F182&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F182)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C182)*($E$5:$E$504=E182)*(($D$5:$D$504=D182)*(D182&lt;&gt;"")+($B$5:$B$504=B182)*(B182&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B182="",C182="",D182="",E182="",F182=""),"",IF(OR(B182="",C182="",E182=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E182)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H182&lt;&gt;0,F182=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G182&lt;&gt;0,F182=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F182&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F182)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C182)*($E$5:$E$504=E182)*(($D$5:$D$504=D182)*(D182&lt;&gt;"")+($B$5:$B$504=B182)*(B182&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J182" s="5">
@@ -5305,11 +5333,11 @@
         <v/>
       </c>
       <c r="H183" s="5">
-        <f>IF(OR(C183="Удержание",C183="Зачёт встречного требования",C183="Неустойка заявлена"),N(E183),0)</f>
+        <f>IF(OR(C183="Удержание",C183="Зачёт встречного требования",C183="Неустойка заявлена",C183="Допработы без соглашения (спорно)"),N(E183),0)</f>
         <v/>
       </c>
       <c r="I183" s="6">
-        <f>IF(AND(B183="",C183="",D183="",E183="",F183=""),"",IF(OR(B183="",C183="",E183=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E183)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G183&lt;&gt;0,F183=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F183&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F183)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C183)*($E$5:$E$504=E183)*(($D$5:$D$504=D183)*(D183&lt;&gt;"")+($B$5:$B$504=B183)*(B183&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B183="",C183="",D183="",E183="",F183=""),"",IF(OR(B183="",C183="",E183=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E183)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H183&lt;&gt;0,F183=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G183&lt;&gt;0,F183=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F183&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F183)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C183)*($E$5:$E$504=E183)*(($D$5:$D$504=D183)*(D183&lt;&gt;"")+($B$5:$B$504=B183)*(B183&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J183" s="5">
@@ -5331,11 +5359,11 @@
         <v/>
       </c>
       <c r="H184" s="5">
-        <f>IF(OR(C184="Удержание",C184="Зачёт встречного требования",C184="Неустойка заявлена"),N(E184),0)</f>
+        <f>IF(OR(C184="Удержание",C184="Зачёт встречного требования",C184="Неустойка заявлена",C184="Допработы без соглашения (спорно)"),N(E184),0)</f>
         <v/>
       </c>
       <c r="I184" s="6">
-        <f>IF(AND(B184="",C184="",D184="",E184="",F184=""),"",IF(OR(B184="",C184="",E184=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E184)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G184&lt;&gt;0,F184=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F184&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F184)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C184)*($E$5:$E$504=E184)*(($D$5:$D$504=D184)*(D184&lt;&gt;"")+($B$5:$B$504=B184)*(B184&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B184="",C184="",D184="",E184="",F184=""),"",IF(OR(B184="",C184="",E184=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E184)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H184&lt;&gt;0,F184=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G184&lt;&gt;0,F184=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F184&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F184)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C184)*($E$5:$E$504=E184)*(($D$5:$D$504=D184)*(D184&lt;&gt;"")+($B$5:$B$504=B184)*(B184&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J184" s="5">
@@ -5357,11 +5385,11 @@
         <v/>
       </c>
       <c r="H185" s="5">
-        <f>IF(OR(C185="Удержание",C185="Зачёт встречного требования",C185="Неустойка заявлена"),N(E185),0)</f>
+        <f>IF(OR(C185="Удержание",C185="Зачёт встречного требования",C185="Неустойка заявлена",C185="Допработы без соглашения (спорно)"),N(E185),0)</f>
         <v/>
       </c>
       <c r="I185" s="6">
-        <f>IF(AND(B185="",C185="",D185="",E185="",F185=""),"",IF(OR(B185="",C185="",E185=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E185)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G185&lt;&gt;0,F185=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F185&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F185)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C185)*($E$5:$E$504=E185)*(($D$5:$D$504=D185)*(D185&lt;&gt;"")+($B$5:$B$504=B185)*(B185&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B185="",C185="",D185="",E185="",F185=""),"",IF(OR(B185="",C185="",E185=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E185)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H185&lt;&gt;0,F185=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G185&lt;&gt;0,F185=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F185&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F185)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C185)*($E$5:$E$504=E185)*(($D$5:$D$504=D185)*(D185&lt;&gt;"")+($B$5:$B$504=B185)*(B185&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J185" s="5">
@@ -5383,11 +5411,11 @@
         <v/>
       </c>
       <c r="H186" s="5">
-        <f>IF(OR(C186="Удержание",C186="Зачёт встречного требования",C186="Неустойка заявлена"),N(E186),0)</f>
+        <f>IF(OR(C186="Удержание",C186="Зачёт встречного требования",C186="Неустойка заявлена",C186="Допработы без соглашения (спорно)"),N(E186),0)</f>
         <v/>
       </c>
       <c r="I186" s="6">
-        <f>IF(AND(B186="",C186="",D186="",E186="",F186=""),"",IF(OR(B186="",C186="",E186=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E186)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G186&lt;&gt;0,F186=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F186&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F186)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C186)*($E$5:$E$504=E186)*(($D$5:$D$504=D186)*(D186&lt;&gt;"")+($B$5:$B$504=B186)*(B186&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B186="",C186="",D186="",E186="",F186=""),"",IF(OR(B186="",C186="",E186=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E186)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H186&lt;&gt;0,F186=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G186&lt;&gt;0,F186=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F186&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F186)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C186)*($E$5:$E$504=E186)*(($D$5:$D$504=D186)*(D186&lt;&gt;"")+($B$5:$B$504=B186)*(B186&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J186" s="5">
@@ -5409,11 +5437,11 @@
         <v/>
       </c>
       <c r="H187" s="5">
-        <f>IF(OR(C187="Удержание",C187="Зачёт встречного требования",C187="Неустойка заявлена"),N(E187),0)</f>
+        <f>IF(OR(C187="Удержание",C187="Зачёт встречного требования",C187="Неустойка заявлена",C187="Допработы без соглашения (спорно)"),N(E187),0)</f>
         <v/>
       </c>
       <c r="I187" s="6">
-        <f>IF(AND(B187="",C187="",D187="",E187="",F187=""),"",IF(OR(B187="",C187="",E187=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E187)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G187&lt;&gt;0,F187=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F187&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F187)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C187)*($E$5:$E$504=E187)*(($D$5:$D$504=D187)*(D187&lt;&gt;"")+($B$5:$B$504=B187)*(B187&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B187="",C187="",D187="",E187="",F187=""),"",IF(OR(B187="",C187="",E187=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E187)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H187&lt;&gt;0,F187=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G187&lt;&gt;0,F187=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F187&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F187)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C187)*($E$5:$E$504=E187)*(($D$5:$D$504=D187)*(D187&lt;&gt;"")+($B$5:$B$504=B187)*(B187&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J187" s="5">
@@ -5435,11 +5463,11 @@
         <v/>
       </c>
       <c r="H188" s="5">
-        <f>IF(OR(C188="Удержание",C188="Зачёт встречного требования",C188="Неустойка заявлена"),N(E188),0)</f>
+        <f>IF(OR(C188="Удержание",C188="Зачёт встречного требования",C188="Неустойка заявлена",C188="Допработы без соглашения (спорно)"),N(E188),0)</f>
         <v/>
       </c>
       <c r="I188" s="6">
-        <f>IF(AND(B188="",C188="",D188="",E188="",F188=""),"",IF(OR(B188="",C188="",E188=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E188)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G188&lt;&gt;0,F188=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F188&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F188)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C188)*($E$5:$E$504=E188)*(($D$5:$D$504=D188)*(D188&lt;&gt;"")+($B$5:$B$504=B188)*(B188&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B188="",C188="",D188="",E188="",F188=""),"",IF(OR(B188="",C188="",E188=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E188)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H188&lt;&gt;0,F188=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G188&lt;&gt;0,F188=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F188&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F188)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C188)*($E$5:$E$504=E188)*(($D$5:$D$504=D188)*(D188&lt;&gt;"")+($B$5:$B$504=B188)*(B188&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J188" s="5">
@@ -5461,11 +5489,11 @@
         <v/>
       </c>
       <c r="H189" s="5">
-        <f>IF(OR(C189="Удержание",C189="Зачёт встречного требования",C189="Неустойка заявлена"),N(E189),0)</f>
+        <f>IF(OR(C189="Удержание",C189="Зачёт встречного требования",C189="Неустойка заявлена",C189="Допработы без соглашения (спорно)"),N(E189),0)</f>
         <v/>
       </c>
       <c r="I189" s="6">
-        <f>IF(AND(B189="",C189="",D189="",E189="",F189=""),"",IF(OR(B189="",C189="",E189=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E189)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G189&lt;&gt;0,F189=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F189&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F189)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C189)*($E$5:$E$504=E189)*(($D$5:$D$504=D189)*(D189&lt;&gt;"")+($B$5:$B$504=B189)*(B189&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B189="",C189="",D189="",E189="",F189=""),"",IF(OR(B189="",C189="",E189=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E189)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H189&lt;&gt;0,F189=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G189&lt;&gt;0,F189=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F189&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F189)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C189)*($E$5:$E$504=E189)*(($D$5:$D$504=D189)*(D189&lt;&gt;"")+($B$5:$B$504=B189)*(B189&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J189" s="5">
@@ -5487,11 +5515,11 @@
         <v/>
       </c>
       <c r="H190" s="5">
-        <f>IF(OR(C190="Удержание",C190="Зачёт встречного требования",C190="Неустойка заявлена"),N(E190),0)</f>
+        <f>IF(OR(C190="Удержание",C190="Зачёт встречного требования",C190="Неустойка заявлена",C190="Допработы без соглашения (спорно)"),N(E190),0)</f>
         <v/>
       </c>
       <c r="I190" s="6">
-        <f>IF(AND(B190="",C190="",D190="",E190="",F190=""),"",IF(OR(B190="",C190="",E190=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E190)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G190&lt;&gt;0,F190=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F190&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F190)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C190)*($E$5:$E$504=E190)*(($D$5:$D$504=D190)*(D190&lt;&gt;"")+($B$5:$B$504=B190)*(B190&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B190="",C190="",D190="",E190="",F190=""),"",IF(OR(B190="",C190="",E190=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E190)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H190&lt;&gt;0,F190=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G190&lt;&gt;0,F190=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F190&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F190)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C190)*($E$5:$E$504=E190)*(($D$5:$D$504=D190)*(D190&lt;&gt;"")+($B$5:$B$504=B190)*(B190&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J190" s="5">
@@ -5513,11 +5541,11 @@
         <v/>
       </c>
       <c r="H191" s="5">
-        <f>IF(OR(C191="Удержание",C191="Зачёт встречного требования",C191="Неустойка заявлена"),N(E191),0)</f>
+        <f>IF(OR(C191="Удержание",C191="Зачёт встречного требования",C191="Неустойка заявлена",C191="Допработы без соглашения (спорно)"),N(E191),0)</f>
         <v/>
       </c>
       <c r="I191" s="6">
-        <f>IF(AND(B191="",C191="",D191="",E191="",F191=""),"",IF(OR(B191="",C191="",E191=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E191)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G191&lt;&gt;0,F191=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F191&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F191)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C191)*($E$5:$E$504=E191)*(($D$5:$D$504=D191)*(D191&lt;&gt;"")+($B$5:$B$504=B191)*(B191&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B191="",C191="",D191="",E191="",F191=""),"",IF(OR(B191="",C191="",E191=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E191)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H191&lt;&gt;0,F191=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G191&lt;&gt;0,F191=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F191&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F191)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C191)*($E$5:$E$504=E191)*(($D$5:$D$504=D191)*(D191&lt;&gt;"")+($B$5:$B$504=B191)*(B191&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J191" s="5">
@@ -5539,11 +5567,11 @@
         <v/>
       </c>
       <c r="H192" s="5">
-        <f>IF(OR(C192="Удержание",C192="Зачёт встречного требования",C192="Неустойка заявлена"),N(E192),0)</f>
+        <f>IF(OR(C192="Удержание",C192="Зачёт встречного требования",C192="Неустойка заявлена",C192="Допработы без соглашения (спорно)"),N(E192),0)</f>
         <v/>
       </c>
       <c r="I192" s="6">
-        <f>IF(AND(B192="",C192="",D192="",E192="",F192=""),"",IF(OR(B192="",C192="",E192=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E192)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G192&lt;&gt;0,F192=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F192&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F192)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C192)*($E$5:$E$504=E192)*(($D$5:$D$504=D192)*(D192&lt;&gt;"")+($B$5:$B$504=B192)*(B192&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B192="",C192="",D192="",E192="",F192=""),"",IF(OR(B192="",C192="",E192=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E192)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H192&lt;&gt;0,F192=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G192&lt;&gt;0,F192=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F192&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F192)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C192)*($E$5:$E$504=E192)*(($D$5:$D$504=D192)*(D192&lt;&gt;"")+($B$5:$B$504=B192)*(B192&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J192" s="5">
@@ -5565,11 +5593,11 @@
         <v/>
       </c>
       <c r="H193" s="5">
-        <f>IF(OR(C193="Удержание",C193="Зачёт встречного требования",C193="Неустойка заявлена"),N(E193),0)</f>
+        <f>IF(OR(C193="Удержание",C193="Зачёт встречного требования",C193="Неустойка заявлена",C193="Допработы без соглашения (спорно)"),N(E193),0)</f>
         <v/>
       </c>
       <c r="I193" s="6">
-        <f>IF(AND(B193="",C193="",D193="",E193="",F193=""),"",IF(OR(B193="",C193="",E193=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E193)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G193&lt;&gt;0,F193=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F193&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F193)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C193)*($E$5:$E$504=E193)*(($D$5:$D$504=D193)*(D193&lt;&gt;"")+($B$5:$B$504=B193)*(B193&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B193="",C193="",D193="",E193="",F193=""),"",IF(OR(B193="",C193="",E193=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E193)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H193&lt;&gt;0,F193=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G193&lt;&gt;0,F193=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F193&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F193)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C193)*($E$5:$E$504=E193)*(($D$5:$D$504=D193)*(D193&lt;&gt;"")+($B$5:$B$504=B193)*(B193&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J193" s="5">
@@ -5591,11 +5619,11 @@
         <v/>
       </c>
       <c r="H194" s="5">
-        <f>IF(OR(C194="Удержание",C194="Зачёт встречного требования",C194="Неустойка заявлена"),N(E194),0)</f>
+        <f>IF(OR(C194="Удержание",C194="Зачёт встречного требования",C194="Неустойка заявлена",C194="Допработы без соглашения (спорно)"),N(E194),0)</f>
         <v/>
       </c>
       <c r="I194" s="6">
-        <f>IF(AND(B194="",C194="",D194="",E194="",F194=""),"",IF(OR(B194="",C194="",E194=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E194)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G194&lt;&gt;0,F194=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F194&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F194)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C194)*($E$5:$E$504=E194)*(($D$5:$D$504=D194)*(D194&lt;&gt;"")+($B$5:$B$504=B194)*(B194&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B194="",C194="",D194="",E194="",F194=""),"",IF(OR(B194="",C194="",E194=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E194)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H194&lt;&gt;0,F194=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G194&lt;&gt;0,F194=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F194&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F194)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C194)*($E$5:$E$504=E194)*(($D$5:$D$504=D194)*(D194&lt;&gt;"")+($B$5:$B$504=B194)*(B194&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J194" s="5">
@@ -5617,11 +5645,11 @@
         <v/>
       </c>
       <c r="H195" s="5">
-        <f>IF(OR(C195="Удержание",C195="Зачёт встречного требования",C195="Неустойка заявлена"),N(E195),0)</f>
+        <f>IF(OR(C195="Удержание",C195="Зачёт встречного требования",C195="Неустойка заявлена",C195="Допработы без соглашения (спорно)"),N(E195),0)</f>
         <v/>
       </c>
       <c r="I195" s="6">
-        <f>IF(AND(B195="",C195="",D195="",E195="",F195=""),"",IF(OR(B195="",C195="",E195=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E195)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G195&lt;&gt;0,F195=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F195&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F195)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C195)*($E$5:$E$504=E195)*(($D$5:$D$504=D195)*(D195&lt;&gt;"")+($B$5:$B$504=B195)*(B195&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B195="",C195="",D195="",E195="",F195=""),"",IF(OR(B195="",C195="",E195=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E195)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H195&lt;&gt;0,F195=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G195&lt;&gt;0,F195=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F195&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F195)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C195)*($E$5:$E$504=E195)*(($D$5:$D$504=D195)*(D195&lt;&gt;"")+($B$5:$B$504=B195)*(B195&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J195" s="5">
@@ -5643,11 +5671,11 @@
         <v/>
       </c>
       <c r="H196" s="5">
-        <f>IF(OR(C196="Удержание",C196="Зачёт встречного требования",C196="Неустойка заявлена"),N(E196),0)</f>
+        <f>IF(OR(C196="Удержание",C196="Зачёт встречного требования",C196="Неустойка заявлена",C196="Допработы без соглашения (спорно)"),N(E196),0)</f>
         <v/>
       </c>
       <c r="I196" s="6">
-        <f>IF(AND(B196="",C196="",D196="",E196="",F196=""),"",IF(OR(B196="",C196="",E196=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E196)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G196&lt;&gt;0,F196=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F196&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F196)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C196)*($E$5:$E$504=E196)*(($D$5:$D$504=D196)*(D196&lt;&gt;"")+($B$5:$B$504=B196)*(B196&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B196="",C196="",D196="",E196="",F196=""),"",IF(OR(B196="",C196="",E196=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E196)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H196&lt;&gt;0,F196=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G196&lt;&gt;0,F196=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F196&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F196)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C196)*($E$5:$E$504=E196)*(($D$5:$D$504=D196)*(D196&lt;&gt;"")+($B$5:$B$504=B196)*(B196&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J196" s="5">
@@ -5669,11 +5697,11 @@
         <v/>
       </c>
       <c r="H197" s="5">
-        <f>IF(OR(C197="Удержание",C197="Зачёт встречного требования",C197="Неустойка заявлена"),N(E197),0)</f>
+        <f>IF(OR(C197="Удержание",C197="Зачёт встречного требования",C197="Неустойка заявлена",C197="Допработы без соглашения (спорно)"),N(E197),0)</f>
         <v/>
       </c>
       <c r="I197" s="6">
-        <f>IF(AND(B197="",C197="",D197="",E197="",F197=""),"",IF(OR(B197="",C197="",E197=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E197)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G197&lt;&gt;0,F197=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F197&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F197)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C197)*($E$5:$E$504=E197)*(($D$5:$D$504=D197)*(D197&lt;&gt;"")+($B$5:$B$504=B197)*(B197&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B197="",C197="",D197="",E197="",F197=""),"",IF(OR(B197="",C197="",E197=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E197)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H197&lt;&gt;0,F197=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G197&lt;&gt;0,F197=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F197&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F197)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C197)*($E$5:$E$504=E197)*(($D$5:$D$504=D197)*(D197&lt;&gt;"")+($B$5:$B$504=B197)*(B197&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J197" s="5">
@@ -5695,11 +5723,11 @@
         <v/>
       </c>
       <c r="H198" s="5">
-        <f>IF(OR(C198="Удержание",C198="Зачёт встречного требования",C198="Неустойка заявлена"),N(E198),0)</f>
+        <f>IF(OR(C198="Удержание",C198="Зачёт встречного требования",C198="Неустойка заявлена",C198="Допработы без соглашения (спорно)"),N(E198),0)</f>
         <v/>
       </c>
       <c r="I198" s="6">
-        <f>IF(AND(B198="",C198="",D198="",E198="",F198=""),"",IF(OR(B198="",C198="",E198=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E198)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G198&lt;&gt;0,F198=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F198&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F198)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C198)*($E$5:$E$504=E198)*(($D$5:$D$504=D198)*(D198&lt;&gt;"")+($B$5:$B$504=B198)*(B198&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B198="",C198="",D198="",E198="",F198=""),"",IF(OR(B198="",C198="",E198=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E198)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H198&lt;&gt;0,F198=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G198&lt;&gt;0,F198=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F198&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F198)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C198)*($E$5:$E$504=E198)*(($D$5:$D$504=D198)*(D198&lt;&gt;"")+($B$5:$B$504=B198)*(B198&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J198" s="5">
@@ -5721,11 +5749,11 @@
         <v/>
       </c>
       <c r="H199" s="5">
-        <f>IF(OR(C199="Удержание",C199="Зачёт встречного требования",C199="Неустойка заявлена"),N(E199),0)</f>
+        <f>IF(OR(C199="Удержание",C199="Зачёт встречного требования",C199="Неустойка заявлена",C199="Допработы без соглашения (спорно)"),N(E199),0)</f>
         <v/>
       </c>
       <c r="I199" s="6">
-        <f>IF(AND(B199="",C199="",D199="",E199="",F199=""),"",IF(OR(B199="",C199="",E199=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E199)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G199&lt;&gt;0,F199=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F199&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F199)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C199)*($E$5:$E$504=E199)*(($D$5:$D$504=D199)*(D199&lt;&gt;"")+($B$5:$B$504=B199)*(B199&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B199="",C199="",D199="",E199="",F199=""),"",IF(OR(B199="",C199="",E199=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E199)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H199&lt;&gt;0,F199=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G199&lt;&gt;0,F199=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F199&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F199)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C199)*($E$5:$E$504=E199)*(($D$5:$D$504=D199)*(D199&lt;&gt;"")+($B$5:$B$504=B199)*(B199&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J199" s="5">
@@ -5747,11 +5775,11 @@
         <v/>
       </c>
       <c r="H200" s="5">
-        <f>IF(OR(C200="Удержание",C200="Зачёт встречного требования",C200="Неустойка заявлена"),N(E200),0)</f>
+        <f>IF(OR(C200="Удержание",C200="Зачёт встречного требования",C200="Неустойка заявлена",C200="Допработы без соглашения (спорно)"),N(E200),0)</f>
         <v/>
       </c>
       <c r="I200" s="6">
-        <f>IF(AND(B200="",C200="",D200="",E200="",F200=""),"",IF(OR(B200="",C200="",E200=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E200)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G200&lt;&gt;0,F200=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F200&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F200)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C200)*($E$5:$E$504=E200)*(($D$5:$D$504=D200)*(D200&lt;&gt;"")+($B$5:$B$504=B200)*(B200&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B200="",C200="",D200="",E200="",F200=""),"",IF(OR(B200="",C200="",E200=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E200)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H200&lt;&gt;0,F200=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G200&lt;&gt;0,F200=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F200&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F200)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C200)*($E$5:$E$504=E200)*(($D$5:$D$504=D200)*(D200&lt;&gt;"")+($B$5:$B$504=B200)*(B200&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J200" s="5">
@@ -5773,11 +5801,11 @@
         <v/>
       </c>
       <c r="H201" s="5">
-        <f>IF(OR(C201="Удержание",C201="Зачёт встречного требования",C201="Неустойка заявлена"),N(E201),0)</f>
+        <f>IF(OR(C201="Удержание",C201="Зачёт встречного требования",C201="Неустойка заявлена",C201="Допработы без соглашения (спорно)"),N(E201),0)</f>
         <v/>
       </c>
       <c r="I201" s="6">
-        <f>IF(AND(B201="",C201="",D201="",E201="",F201=""),"",IF(OR(B201="",C201="",E201=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E201)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G201&lt;&gt;0,F201=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F201&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F201)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C201)*($E$5:$E$504=E201)*(($D$5:$D$504=D201)*(D201&lt;&gt;"")+($B$5:$B$504=B201)*(B201&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B201="",C201="",D201="",E201="",F201=""),"",IF(OR(B201="",C201="",E201=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E201)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H201&lt;&gt;0,F201=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G201&lt;&gt;0,F201=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F201&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F201)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C201)*($E$5:$E$504=E201)*(($D$5:$D$504=D201)*(D201&lt;&gt;"")+($B$5:$B$504=B201)*(B201&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J201" s="5">
@@ -5799,11 +5827,11 @@
         <v/>
       </c>
       <c r="H202" s="5">
-        <f>IF(OR(C202="Удержание",C202="Зачёт встречного требования",C202="Неустойка заявлена"),N(E202),0)</f>
+        <f>IF(OR(C202="Удержание",C202="Зачёт встречного требования",C202="Неустойка заявлена",C202="Допработы без соглашения (спорно)"),N(E202),0)</f>
         <v/>
       </c>
       <c r="I202" s="6">
-        <f>IF(AND(B202="",C202="",D202="",E202="",F202=""),"",IF(OR(B202="",C202="",E202=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E202)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G202&lt;&gt;0,F202=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F202&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F202)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C202)*($E$5:$E$504=E202)*(($D$5:$D$504=D202)*(D202&lt;&gt;"")+($B$5:$B$504=B202)*(B202&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B202="",C202="",D202="",E202="",F202=""),"",IF(OR(B202="",C202="",E202=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E202)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H202&lt;&gt;0,F202=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G202&lt;&gt;0,F202=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F202&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F202)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C202)*($E$5:$E$504=E202)*(($D$5:$D$504=D202)*(D202&lt;&gt;"")+($B$5:$B$504=B202)*(B202&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J202" s="5">
@@ -5825,11 +5853,11 @@
         <v/>
       </c>
       <c r="H203" s="5">
-        <f>IF(OR(C203="Удержание",C203="Зачёт встречного требования",C203="Неустойка заявлена"),N(E203),0)</f>
+        <f>IF(OR(C203="Удержание",C203="Зачёт встречного требования",C203="Неустойка заявлена",C203="Допработы без соглашения (спорно)"),N(E203),0)</f>
         <v/>
       </c>
       <c r="I203" s="6">
-        <f>IF(AND(B203="",C203="",D203="",E203="",F203=""),"",IF(OR(B203="",C203="",E203=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E203)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G203&lt;&gt;0,F203=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F203&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F203)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C203)*($E$5:$E$504=E203)*(($D$5:$D$504=D203)*(D203&lt;&gt;"")+($B$5:$B$504=B203)*(B203&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B203="",C203="",D203="",E203="",F203=""),"",IF(OR(B203="",C203="",E203=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E203)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H203&lt;&gt;0,F203=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G203&lt;&gt;0,F203=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F203&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F203)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C203)*($E$5:$E$504=E203)*(($D$5:$D$504=D203)*(D203&lt;&gt;"")+($B$5:$B$504=B203)*(B203&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J203" s="5">
@@ -5851,11 +5879,11 @@
         <v/>
       </c>
       <c r="H204" s="5">
-        <f>IF(OR(C204="Удержание",C204="Зачёт встречного требования",C204="Неустойка заявлена"),N(E204),0)</f>
+        <f>IF(OR(C204="Удержание",C204="Зачёт встречного требования",C204="Неустойка заявлена",C204="Допработы без соглашения (спорно)"),N(E204),0)</f>
         <v/>
       </c>
       <c r="I204" s="6">
-        <f>IF(AND(B204="",C204="",D204="",E204="",F204=""),"",IF(OR(B204="",C204="",E204=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E204)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G204&lt;&gt;0,F204=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F204&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F204)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C204)*($E$5:$E$504=E204)*(($D$5:$D$504=D204)*(D204&lt;&gt;"")+($B$5:$B$504=B204)*(B204&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B204="",C204="",D204="",E204="",F204=""),"",IF(OR(B204="",C204="",E204=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E204)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H204&lt;&gt;0,F204=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G204&lt;&gt;0,F204=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F204&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F204)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C204)*($E$5:$E$504=E204)*(($D$5:$D$504=D204)*(D204&lt;&gt;"")+($B$5:$B$504=B204)*(B204&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J204" s="5">
@@ -5877,11 +5905,11 @@
         <v/>
       </c>
       <c r="H205" s="5">
-        <f>IF(OR(C205="Удержание",C205="Зачёт встречного требования",C205="Неустойка заявлена"),N(E205),0)</f>
+        <f>IF(OR(C205="Удержание",C205="Зачёт встречного требования",C205="Неустойка заявлена",C205="Допработы без соглашения (спорно)"),N(E205),0)</f>
         <v/>
       </c>
       <c r="I205" s="6">
-        <f>IF(AND(B205="",C205="",D205="",E205="",F205=""),"",IF(OR(B205="",C205="",E205=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E205)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G205&lt;&gt;0,F205=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F205&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F205)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C205)*($E$5:$E$504=E205)*(($D$5:$D$504=D205)*(D205&lt;&gt;"")+($B$5:$B$504=B205)*(B205&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B205="",C205="",D205="",E205="",F205=""),"",IF(OR(B205="",C205="",E205=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E205)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H205&lt;&gt;0,F205=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G205&lt;&gt;0,F205=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F205&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F205)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C205)*($E$5:$E$504=E205)*(($D$5:$D$504=D205)*(D205&lt;&gt;"")+($B$5:$B$504=B205)*(B205&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J205" s="5">
@@ -5903,11 +5931,11 @@
         <v/>
       </c>
       <c r="H206" s="5">
-        <f>IF(OR(C206="Удержание",C206="Зачёт встречного требования",C206="Неустойка заявлена"),N(E206),0)</f>
+        <f>IF(OR(C206="Удержание",C206="Зачёт встречного требования",C206="Неустойка заявлена",C206="Допработы без соглашения (спорно)"),N(E206),0)</f>
         <v/>
       </c>
       <c r="I206" s="6">
-        <f>IF(AND(B206="",C206="",D206="",E206="",F206=""),"",IF(OR(B206="",C206="",E206=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E206)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G206&lt;&gt;0,F206=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F206&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F206)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C206)*($E$5:$E$504=E206)*(($D$5:$D$504=D206)*(D206&lt;&gt;"")+($B$5:$B$504=B206)*(B206&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B206="",C206="",D206="",E206="",F206=""),"",IF(OR(B206="",C206="",E206=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E206)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H206&lt;&gt;0,F206=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G206&lt;&gt;0,F206=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F206&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F206)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C206)*($E$5:$E$504=E206)*(($D$5:$D$504=D206)*(D206&lt;&gt;"")+($B$5:$B$504=B206)*(B206&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J206" s="5">
@@ -5929,11 +5957,11 @@
         <v/>
       </c>
       <c r="H207" s="5">
-        <f>IF(OR(C207="Удержание",C207="Зачёт встречного требования",C207="Неустойка заявлена"),N(E207),0)</f>
+        <f>IF(OR(C207="Удержание",C207="Зачёт встречного требования",C207="Неустойка заявлена",C207="Допработы без соглашения (спорно)"),N(E207),0)</f>
         <v/>
       </c>
       <c r="I207" s="6">
-        <f>IF(AND(B207="",C207="",D207="",E207="",F207=""),"",IF(OR(B207="",C207="",E207=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E207)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G207&lt;&gt;0,F207=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F207&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F207)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C207)*($E$5:$E$504=E207)*(($D$5:$D$504=D207)*(D207&lt;&gt;"")+($B$5:$B$504=B207)*(B207&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B207="",C207="",D207="",E207="",F207=""),"",IF(OR(B207="",C207="",E207=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E207)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H207&lt;&gt;0,F207=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G207&lt;&gt;0,F207=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F207&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F207)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C207)*($E$5:$E$504=E207)*(($D$5:$D$504=D207)*(D207&lt;&gt;"")+($B$5:$B$504=B207)*(B207&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J207" s="5">
@@ -5955,11 +5983,11 @@
         <v/>
       </c>
       <c r="H208" s="5">
-        <f>IF(OR(C208="Удержание",C208="Зачёт встречного требования",C208="Неустойка заявлена"),N(E208),0)</f>
+        <f>IF(OR(C208="Удержание",C208="Зачёт встречного требования",C208="Неустойка заявлена",C208="Допработы без соглашения (спорно)"),N(E208),0)</f>
         <v/>
       </c>
       <c r="I208" s="6">
-        <f>IF(AND(B208="",C208="",D208="",E208="",F208=""),"",IF(OR(B208="",C208="",E208=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E208)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G208&lt;&gt;0,F208=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F208&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F208)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C208)*($E$5:$E$504=E208)*(($D$5:$D$504=D208)*(D208&lt;&gt;"")+($B$5:$B$504=B208)*(B208&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B208="",C208="",D208="",E208="",F208=""),"",IF(OR(B208="",C208="",E208=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E208)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H208&lt;&gt;0,F208=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G208&lt;&gt;0,F208=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F208&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F208)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C208)*($E$5:$E$504=E208)*(($D$5:$D$504=D208)*(D208&lt;&gt;"")+($B$5:$B$504=B208)*(B208&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J208" s="5">
@@ -5981,11 +6009,11 @@
         <v/>
       </c>
       <c r="H209" s="5">
-        <f>IF(OR(C209="Удержание",C209="Зачёт встречного требования",C209="Неустойка заявлена"),N(E209),0)</f>
+        <f>IF(OR(C209="Удержание",C209="Зачёт встречного требования",C209="Неустойка заявлена",C209="Допработы без соглашения (спорно)"),N(E209),0)</f>
         <v/>
       </c>
       <c r="I209" s="6">
-        <f>IF(AND(B209="",C209="",D209="",E209="",F209=""),"",IF(OR(B209="",C209="",E209=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E209)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G209&lt;&gt;0,F209=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F209&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F209)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C209)*($E$5:$E$504=E209)*(($D$5:$D$504=D209)*(D209&lt;&gt;"")+($B$5:$B$504=B209)*(B209&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B209="",C209="",D209="",E209="",F209=""),"",IF(OR(B209="",C209="",E209=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E209)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H209&lt;&gt;0,F209=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G209&lt;&gt;0,F209=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F209&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F209)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C209)*($E$5:$E$504=E209)*(($D$5:$D$504=D209)*(D209&lt;&gt;"")+($B$5:$B$504=B209)*(B209&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J209" s="5">
@@ -6007,11 +6035,11 @@
         <v/>
       </c>
       <c r="H210" s="5">
-        <f>IF(OR(C210="Удержание",C210="Зачёт встречного требования",C210="Неустойка заявлена"),N(E210),0)</f>
+        <f>IF(OR(C210="Удержание",C210="Зачёт встречного требования",C210="Неустойка заявлена",C210="Допработы без соглашения (спорно)"),N(E210),0)</f>
         <v/>
       </c>
       <c r="I210" s="6">
-        <f>IF(AND(B210="",C210="",D210="",E210="",F210=""),"",IF(OR(B210="",C210="",E210=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E210)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G210&lt;&gt;0,F210=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F210&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F210)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C210)*($E$5:$E$504=E210)*(($D$5:$D$504=D210)*(D210&lt;&gt;"")+($B$5:$B$504=B210)*(B210&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B210="",C210="",D210="",E210="",F210=""),"",IF(OR(B210="",C210="",E210=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E210)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H210&lt;&gt;0,F210=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G210&lt;&gt;0,F210=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F210&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F210)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C210)*($E$5:$E$504=E210)*(($D$5:$D$504=D210)*(D210&lt;&gt;"")+($B$5:$B$504=B210)*(B210&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J210" s="5">
@@ -6033,11 +6061,11 @@
         <v/>
       </c>
       <c r="H211" s="5">
-        <f>IF(OR(C211="Удержание",C211="Зачёт встречного требования",C211="Неустойка заявлена"),N(E211),0)</f>
+        <f>IF(OR(C211="Удержание",C211="Зачёт встречного требования",C211="Неустойка заявлена",C211="Допработы без соглашения (спорно)"),N(E211),0)</f>
         <v/>
       </c>
       <c r="I211" s="6">
-        <f>IF(AND(B211="",C211="",D211="",E211="",F211=""),"",IF(OR(B211="",C211="",E211=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E211)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G211&lt;&gt;0,F211=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F211&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F211)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C211)*($E$5:$E$504=E211)*(($D$5:$D$504=D211)*(D211&lt;&gt;"")+($B$5:$B$504=B211)*(B211&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B211="",C211="",D211="",E211="",F211=""),"",IF(OR(B211="",C211="",E211=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E211)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H211&lt;&gt;0,F211=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G211&lt;&gt;0,F211=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F211&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F211)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C211)*($E$5:$E$504=E211)*(($D$5:$D$504=D211)*(D211&lt;&gt;"")+($B$5:$B$504=B211)*(B211&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J211" s="5">
@@ -6059,11 +6087,11 @@
         <v/>
       </c>
       <c r="H212" s="5">
-        <f>IF(OR(C212="Удержание",C212="Зачёт встречного требования",C212="Неустойка заявлена"),N(E212),0)</f>
+        <f>IF(OR(C212="Удержание",C212="Зачёт встречного требования",C212="Неустойка заявлена",C212="Допработы без соглашения (спорно)"),N(E212),0)</f>
         <v/>
       </c>
       <c r="I212" s="6">
-        <f>IF(AND(B212="",C212="",D212="",E212="",F212=""),"",IF(OR(B212="",C212="",E212=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E212)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G212&lt;&gt;0,F212=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F212&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F212)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C212)*($E$5:$E$504=E212)*(($D$5:$D$504=D212)*(D212&lt;&gt;"")+($B$5:$B$504=B212)*(B212&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B212="",C212="",D212="",E212="",F212=""),"",IF(OR(B212="",C212="",E212=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E212)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H212&lt;&gt;0,F212=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G212&lt;&gt;0,F212=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F212&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F212)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C212)*($E$5:$E$504=E212)*(($D$5:$D$504=D212)*(D212&lt;&gt;"")+($B$5:$B$504=B212)*(B212&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J212" s="5">
@@ -6085,11 +6113,11 @@
         <v/>
       </c>
       <c r="H213" s="5">
-        <f>IF(OR(C213="Удержание",C213="Зачёт встречного требования",C213="Неустойка заявлена"),N(E213),0)</f>
+        <f>IF(OR(C213="Удержание",C213="Зачёт встречного требования",C213="Неустойка заявлена",C213="Допработы без соглашения (спорно)"),N(E213),0)</f>
         <v/>
       </c>
       <c r="I213" s="6">
-        <f>IF(AND(B213="",C213="",D213="",E213="",F213=""),"",IF(OR(B213="",C213="",E213=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E213)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G213&lt;&gt;0,F213=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F213&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F213)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C213)*($E$5:$E$504=E213)*(($D$5:$D$504=D213)*(D213&lt;&gt;"")+($B$5:$B$504=B213)*(B213&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B213="",C213="",D213="",E213="",F213=""),"",IF(OR(B213="",C213="",E213=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E213)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H213&lt;&gt;0,F213=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G213&lt;&gt;0,F213=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F213&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F213)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C213)*($E$5:$E$504=E213)*(($D$5:$D$504=D213)*(D213&lt;&gt;"")+($B$5:$B$504=B213)*(B213&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J213" s="5">
@@ -6111,11 +6139,11 @@
         <v/>
       </c>
       <c r="H214" s="5">
-        <f>IF(OR(C214="Удержание",C214="Зачёт встречного требования",C214="Неустойка заявлена"),N(E214),0)</f>
+        <f>IF(OR(C214="Удержание",C214="Зачёт встречного требования",C214="Неустойка заявлена",C214="Допработы без соглашения (спорно)"),N(E214),0)</f>
         <v/>
       </c>
       <c r="I214" s="6">
-        <f>IF(AND(B214="",C214="",D214="",E214="",F214=""),"",IF(OR(B214="",C214="",E214=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E214)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G214&lt;&gt;0,F214=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F214&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F214)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C214)*($E$5:$E$504=E214)*(($D$5:$D$504=D214)*(D214&lt;&gt;"")+($B$5:$B$504=B214)*(B214&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B214="",C214="",D214="",E214="",F214=""),"",IF(OR(B214="",C214="",E214=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E214)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H214&lt;&gt;0,F214=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G214&lt;&gt;0,F214=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F214&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F214)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C214)*($E$5:$E$504=E214)*(($D$5:$D$504=D214)*(D214&lt;&gt;"")+($B$5:$B$504=B214)*(B214&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J214" s="5">
@@ -6137,11 +6165,11 @@
         <v/>
       </c>
       <c r="H215" s="5">
-        <f>IF(OR(C215="Удержание",C215="Зачёт встречного требования",C215="Неустойка заявлена"),N(E215),0)</f>
+        <f>IF(OR(C215="Удержание",C215="Зачёт встречного требования",C215="Неустойка заявлена",C215="Допработы без соглашения (спорно)"),N(E215),0)</f>
         <v/>
       </c>
       <c r="I215" s="6">
-        <f>IF(AND(B215="",C215="",D215="",E215="",F215=""),"",IF(OR(B215="",C215="",E215=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E215)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G215&lt;&gt;0,F215=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F215&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F215)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C215)*($E$5:$E$504=E215)*(($D$5:$D$504=D215)*(D215&lt;&gt;"")+($B$5:$B$504=B215)*(B215&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B215="",C215="",D215="",E215="",F215=""),"",IF(OR(B215="",C215="",E215=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E215)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H215&lt;&gt;0,F215=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G215&lt;&gt;0,F215=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F215&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F215)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C215)*($E$5:$E$504=E215)*(($D$5:$D$504=D215)*(D215&lt;&gt;"")+($B$5:$B$504=B215)*(B215&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J215" s="5">
@@ -6163,11 +6191,11 @@
         <v/>
       </c>
       <c r="H216" s="5">
-        <f>IF(OR(C216="Удержание",C216="Зачёт встречного требования",C216="Неустойка заявлена"),N(E216),0)</f>
+        <f>IF(OR(C216="Удержание",C216="Зачёт встречного требования",C216="Неустойка заявлена",C216="Допработы без соглашения (спорно)"),N(E216),0)</f>
         <v/>
       </c>
       <c r="I216" s="6">
-        <f>IF(AND(B216="",C216="",D216="",E216="",F216=""),"",IF(OR(B216="",C216="",E216=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E216)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G216&lt;&gt;0,F216=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F216&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F216)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C216)*($E$5:$E$504=E216)*(($D$5:$D$504=D216)*(D216&lt;&gt;"")+($B$5:$B$504=B216)*(B216&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B216="",C216="",D216="",E216="",F216=""),"",IF(OR(B216="",C216="",E216=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E216)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H216&lt;&gt;0,F216=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G216&lt;&gt;0,F216=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F216&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F216)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C216)*($E$5:$E$504=E216)*(($D$5:$D$504=D216)*(D216&lt;&gt;"")+($B$5:$B$504=B216)*(B216&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J216" s="5">
@@ -6189,11 +6217,11 @@
         <v/>
       </c>
       <c r="H217" s="5">
-        <f>IF(OR(C217="Удержание",C217="Зачёт встречного требования",C217="Неустойка заявлена"),N(E217),0)</f>
+        <f>IF(OR(C217="Удержание",C217="Зачёт встречного требования",C217="Неустойка заявлена",C217="Допработы без соглашения (спорно)"),N(E217),0)</f>
         <v/>
       </c>
       <c r="I217" s="6">
-        <f>IF(AND(B217="",C217="",D217="",E217="",F217=""),"",IF(OR(B217="",C217="",E217=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E217)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G217&lt;&gt;0,F217=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F217&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F217)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C217)*($E$5:$E$504=E217)*(($D$5:$D$504=D217)*(D217&lt;&gt;"")+($B$5:$B$504=B217)*(B217&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B217="",C217="",D217="",E217="",F217=""),"",IF(OR(B217="",C217="",E217=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E217)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H217&lt;&gt;0,F217=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G217&lt;&gt;0,F217=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F217&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F217)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C217)*($E$5:$E$504=E217)*(($D$5:$D$504=D217)*(D217&lt;&gt;"")+($B$5:$B$504=B217)*(B217&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J217" s="5">
@@ -6215,11 +6243,11 @@
         <v/>
       </c>
       <c r="H218" s="5">
-        <f>IF(OR(C218="Удержание",C218="Зачёт встречного требования",C218="Неустойка заявлена"),N(E218),0)</f>
+        <f>IF(OR(C218="Удержание",C218="Зачёт встречного требования",C218="Неустойка заявлена",C218="Допработы без соглашения (спорно)"),N(E218),0)</f>
         <v/>
       </c>
       <c r="I218" s="6">
-        <f>IF(AND(B218="",C218="",D218="",E218="",F218=""),"",IF(OR(B218="",C218="",E218=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E218)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G218&lt;&gt;0,F218=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F218&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F218)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C218)*($E$5:$E$504=E218)*(($D$5:$D$504=D218)*(D218&lt;&gt;"")+($B$5:$B$504=B218)*(B218&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B218="",C218="",D218="",E218="",F218=""),"",IF(OR(B218="",C218="",E218=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E218)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H218&lt;&gt;0,F218=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G218&lt;&gt;0,F218=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F218&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F218)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C218)*($E$5:$E$504=E218)*(($D$5:$D$504=D218)*(D218&lt;&gt;"")+($B$5:$B$504=B218)*(B218&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J218" s="5">
@@ -6241,11 +6269,11 @@
         <v/>
       </c>
       <c r="H219" s="5">
-        <f>IF(OR(C219="Удержание",C219="Зачёт встречного требования",C219="Неустойка заявлена"),N(E219),0)</f>
+        <f>IF(OR(C219="Удержание",C219="Зачёт встречного требования",C219="Неустойка заявлена",C219="Допработы без соглашения (спорно)"),N(E219),0)</f>
         <v/>
       </c>
       <c r="I219" s="6">
-        <f>IF(AND(B219="",C219="",D219="",E219="",F219=""),"",IF(OR(B219="",C219="",E219=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E219)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G219&lt;&gt;0,F219=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F219&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F219)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C219)*($E$5:$E$504=E219)*(($D$5:$D$504=D219)*(D219&lt;&gt;"")+($B$5:$B$504=B219)*(B219&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B219="",C219="",D219="",E219="",F219=""),"",IF(OR(B219="",C219="",E219=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E219)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H219&lt;&gt;0,F219=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G219&lt;&gt;0,F219=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F219&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F219)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C219)*($E$5:$E$504=E219)*(($D$5:$D$504=D219)*(D219&lt;&gt;"")+($B$5:$B$504=B219)*(B219&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J219" s="5">
@@ -6267,11 +6295,11 @@
         <v/>
       </c>
       <c r="H220" s="5">
-        <f>IF(OR(C220="Удержание",C220="Зачёт встречного требования",C220="Неустойка заявлена"),N(E220),0)</f>
+        <f>IF(OR(C220="Удержание",C220="Зачёт встречного требования",C220="Неустойка заявлена",C220="Допработы без соглашения (спорно)"),N(E220),0)</f>
         <v/>
       </c>
       <c r="I220" s="6">
-        <f>IF(AND(B220="",C220="",D220="",E220="",F220=""),"",IF(OR(B220="",C220="",E220=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E220)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G220&lt;&gt;0,F220=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F220&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F220)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C220)*($E$5:$E$504=E220)*(($D$5:$D$504=D220)*(D220&lt;&gt;"")+($B$5:$B$504=B220)*(B220&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B220="",C220="",D220="",E220="",F220=""),"",IF(OR(B220="",C220="",E220=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E220)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H220&lt;&gt;0,F220=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G220&lt;&gt;0,F220=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F220&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F220)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C220)*($E$5:$E$504=E220)*(($D$5:$D$504=D220)*(D220&lt;&gt;"")+($B$5:$B$504=B220)*(B220&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J220" s="5">
@@ -6293,11 +6321,11 @@
         <v/>
       </c>
       <c r="H221" s="5">
-        <f>IF(OR(C221="Удержание",C221="Зачёт встречного требования",C221="Неустойка заявлена"),N(E221),0)</f>
+        <f>IF(OR(C221="Удержание",C221="Зачёт встречного требования",C221="Неустойка заявлена",C221="Допработы без соглашения (спорно)"),N(E221),0)</f>
         <v/>
       </c>
       <c r="I221" s="6">
-        <f>IF(AND(B221="",C221="",D221="",E221="",F221=""),"",IF(OR(B221="",C221="",E221=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E221)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G221&lt;&gt;0,F221=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F221&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F221)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C221)*($E$5:$E$504=E221)*(($D$5:$D$504=D221)*(D221&lt;&gt;"")+($B$5:$B$504=B221)*(B221&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B221="",C221="",D221="",E221="",F221=""),"",IF(OR(B221="",C221="",E221=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E221)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H221&lt;&gt;0,F221=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G221&lt;&gt;0,F221=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F221&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F221)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C221)*($E$5:$E$504=E221)*(($D$5:$D$504=D221)*(D221&lt;&gt;"")+($B$5:$B$504=B221)*(B221&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J221" s="5">
@@ -6319,11 +6347,11 @@
         <v/>
       </c>
       <c r="H222" s="5">
-        <f>IF(OR(C222="Удержание",C222="Зачёт встречного требования",C222="Неустойка заявлена"),N(E222),0)</f>
+        <f>IF(OR(C222="Удержание",C222="Зачёт встречного требования",C222="Неустойка заявлена",C222="Допработы без соглашения (спорно)"),N(E222),0)</f>
         <v/>
       </c>
       <c r="I222" s="6">
-        <f>IF(AND(B222="",C222="",D222="",E222="",F222=""),"",IF(OR(B222="",C222="",E222=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E222)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G222&lt;&gt;0,F222=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F222&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F222)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C222)*($E$5:$E$504=E222)*(($D$5:$D$504=D222)*(D222&lt;&gt;"")+($B$5:$B$504=B222)*(B222&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B222="",C222="",D222="",E222="",F222=""),"",IF(OR(B222="",C222="",E222=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E222)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H222&lt;&gt;0,F222=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G222&lt;&gt;0,F222=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F222&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F222)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C222)*($E$5:$E$504=E222)*(($D$5:$D$504=D222)*(D222&lt;&gt;"")+($B$5:$B$504=B222)*(B222&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J222" s="5">
@@ -6345,11 +6373,11 @@
         <v/>
       </c>
       <c r="H223" s="5">
-        <f>IF(OR(C223="Удержание",C223="Зачёт встречного требования",C223="Неустойка заявлена"),N(E223),0)</f>
+        <f>IF(OR(C223="Удержание",C223="Зачёт встречного требования",C223="Неустойка заявлена",C223="Допработы без соглашения (спорно)"),N(E223),0)</f>
         <v/>
       </c>
       <c r="I223" s="6">
-        <f>IF(AND(B223="",C223="",D223="",E223="",F223=""),"",IF(OR(B223="",C223="",E223=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E223)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G223&lt;&gt;0,F223=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F223&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F223)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C223)*($E$5:$E$504=E223)*(($D$5:$D$504=D223)*(D223&lt;&gt;"")+($B$5:$B$504=B223)*(B223&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B223="",C223="",D223="",E223="",F223=""),"",IF(OR(B223="",C223="",E223=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E223)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H223&lt;&gt;0,F223=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G223&lt;&gt;0,F223=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F223&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F223)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C223)*($E$5:$E$504=E223)*(($D$5:$D$504=D223)*(D223&lt;&gt;"")+($B$5:$B$504=B223)*(B223&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J223" s="5">
@@ -6371,11 +6399,11 @@
         <v/>
       </c>
       <c r="H224" s="5">
-        <f>IF(OR(C224="Удержание",C224="Зачёт встречного требования",C224="Неустойка заявлена"),N(E224),0)</f>
+        <f>IF(OR(C224="Удержание",C224="Зачёт встречного требования",C224="Неустойка заявлена",C224="Допработы без соглашения (спорно)"),N(E224),0)</f>
         <v/>
       </c>
       <c r="I224" s="6">
-        <f>IF(AND(B224="",C224="",D224="",E224="",F224=""),"",IF(OR(B224="",C224="",E224=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E224)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G224&lt;&gt;0,F224=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F224&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F224)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C224)*($E$5:$E$504=E224)*(($D$5:$D$504=D224)*(D224&lt;&gt;"")+($B$5:$B$504=B224)*(B224&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B224="",C224="",D224="",E224="",F224=""),"",IF(OR(B224="",C224="",E224=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E224)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H224&lt;&gt;0,F224=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G224&lt;&gt;0,F224=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F224&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F224)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C224)*($E$5:$E$504=E224)*(($D$5:$D$504=D224)*(D224&lt;&gt;"")+($B$5:$B$504=B224)*(B224&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J224" s="5">
@@ -6397,11 +6425,11 @@
         <v/>
       </c>
       <c r="H225" s="5">
-        <f>IF(OR(C225="Удержание",C225="Зачёт встречного требования",C225="Неустойка заявлена"),N(E225),0)</f>
+        <f>IF(OR(C225="Удержание",C225="Зачёт встречного требования",C225="Неустойка заявлена",C225="Допработы без соглашения (спорно)"),N(E225),0)</f>
         <v/>
       </c>
       <c r="I225" s="6">
-        <f>IF(AND(B225="",C225="",D225="",E225="",F225=""),"",IF(OR(B225="",C225="",E225=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E225)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G225&lt;&gt;0,F225=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F225&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F225)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C225)*($E$5:$E$504=E225)*(($D$5:$D$504=D225)*(D225&lt;&gt;"")+($B$5:$B$504=B225)*(B225&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B225="",C225="",D225="",E225="",F225=""),"",IF(OR(B225="",C225="",E225=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E225)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H225&lt;&gt;0,F225=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G225&lt;&gt;0,F225=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F225&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F225)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C225)*($E$5:$E$504=E225)*(($D$5:$D$504=D225)*(D225&lt;&gt;"")+($B$5:$B$504=B225)*(B225&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J225" s="5">
@@ -6423,11 +6451,11 @@
         <v/>
       </c>
       <c r="H226" s="5">
-        <f>IF(OR(C226="Удержание",C226="Зачёт встречного требования",C226="Неустойка заявлена"),N(E226),0)</f>
+        <f>IF(OR(C226="Удержание",C226="Зачёт встречного требования",C226="Неустойка заявлена",C226="Допработы без соглашения (спорно)"),N(E226),0)</f>
         <v/>
       </c>
       <c r="I226" s="6">
-        <f>IF(AND(B226="",C226="",D226="",E226="",F226=""),"",IF(OR(B226="",C226="",E226=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E226)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G226&lt;&gt;0,F226=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F226&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F226)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C226)*($E$5:$E$504=E226)*(($D$5:$D$504=D226)*(D226&lt;&gt;"")+($B$5:$B$504=B226)*(B226&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B226="",C226="",D226="",E226="",F226=""),"",IF(OR(B226="",C226="",E226=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E226)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H226&lt;&gt;0,F226=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G226&lt;&gt;0,F226=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F226&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F226)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C226)*($E$5:$E$504=E226)*(($D$5:$D$504=D226)*(D226&lt;&gt;"")+($B$5:$B$504=B226)*(B226&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J226" s="5">
@@ -6449,11 +6477,11 @@
         <v/>
       </c>
       <c r="H227" s="5">
-        <f>IF(OR(C227="Удержание",C227="Зачёт встречного требования",C227="Неустойка заявлена"),N(E227),0)</f>
+        <f>IF(OR(C227="Удержание",C227="Зачёт встречного требования",C227="Неустойка заявлена",C227="Допработы без соглашения (спорно)"),N(E227),0)</f>
         <v/>
       </c>
       <c r="I227" s="6">
-        <f>IF(AND(B227="",C227="",D227="",E227="",F227=""),"",IF(OR(B227="",C227="",E227=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E227)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G227&lt;&gt;0,F227=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F227&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F227)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C227)*($E$5:$E$504=E227)*(($D$5:$D$504=D227)*(D227&lt;&gt;"")+($B$5:$B$504=B227)*(B227&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B227="",C227="",D227="",E227="",F227=""),"",IF(OR(B227="",C227="",E227=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E227)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H227&lt;&gt;0,F227=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G227&lt;&gt;0,F227=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F227&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F227)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C227)*($E$5:$E$504=E227)*(($D$5:$D$504=D227)*(D227&lt;&gt;"")+($B$5:$B$504=B227)*(B227&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J227" s="5">
@@ -6475,11 +6503,11 @@
         <v/>
       </c>
       <c r="H228" s="5">
-        <f>IF(OR(C228="Удержание",C228="Зачёт встречного требования",C228="Неустойка заявлена"),N(E228),0)</f>
+        <f>IF(OR(C228="Удержание",C228="Зачёт встречного требования",C228="Неустойка заявлена",C228="Допработы без соглашения (спорно)"),N(E228),0)</f>
         <v/>
       </c>
       <c r="I228" s="6">
-        <f>IF(AND(B228="",C228="",D228="",E228="",F228=""),"",IF(OR(B228="",C228="",E228=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E228)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G228&lt;&gt;0,F228=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F228&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F228)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C228)*($E$5:$E$504=E228)*(($D$5:$D$504=D228)*(D228&lt;&gt;"")+($B$5:$B$504=B228)*(B228&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B228="",C228="",D228="",E228="",F228=""),"",IF(OR(B228="",C228="",E228=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E228)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H228&lt;&gt;0,F228=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G228&lt;&gt;0,F228=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F228&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F228)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C228)*($E$5:$E$504=E228)*(($D$5:$D$504=D228)*(D228&lt;&gt;"")+($B$5:$B$504=B228)*(B228&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J228" s="5">
@@ -6501,11 +6529,11 @@
         <v/>
       </c>
       <c r="H229" s="5">
-        <f>IF(OR(C229="Удержание",C229="Зачёт встречного требования",C229="Неустойка заявлена"),N(E229),0)</f>
+        <f>IF(OR(C229="Удержание",C229="Зачёт встречного требования",C229="Неустойка заявлена",C229="Допработы без соглашения (спорно)"),N(E229),0)</f>
         <v/>
       </c>
       <c r="I229" s="6">
-        <f>IF(AND(B229="",C229="",D229="",E229="",F229=""),"",IF(OR(B229="",C229="",E229=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E229)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G229&lt;&gt;0,F229=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F229&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F229)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C229)*($E$5:$E$504=E229)*(($D$5:$D$504=D229)*(D229&lt;&gt;"")+($B$5:$B$504=B229)*(B229&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B229="",C229="",D229="",E229="",F229=""),"",IF(OR(B229="",C229="",E229=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E229)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H229&lt;&gt;0,F229=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G229&lt;&gt;0,F229=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F229&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F229)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C229)*($E$5:$E$504=E229)*(($D$5:$D$504=D229)*(D229&lt;&gt;"")+($B$5:$B$504=B229)*(B229&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J229" s="5">
@@ -6527,11 +6555,11 @@
         <v/>
       </c>
       <c r="H230" s="5">
-        <f>IF(OR(C230="Удержание",C230="Зачёт встречного требования",C230="Неустойка заявлена"),N(E230),0)</f>
+        <f>IF(OR(C230="Удержание",C230="Зачёт встречного требования",C230="Неустойка заявлена",C230="Допработы без соглашения (спорно)"),N(E230),0)</f>
         <v/>
       </c>
       <c r="I230" s="6">
-        <f>IF(AND(B230="",C230="",D230="",E230="",F230=""),"",IF(OR(B230="",C230="",E230=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E230)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G230&lt;&gt;0,F230=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F230&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F230)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C230)*($E$5:$E$504=E230)*(($D$5:$D$504=D230)*(D230&lt;&gt;"")+($B$5:$B$504=B230)*(B230&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B230="",C230="",D230="",E230="",F230=""),"",IF(OR(B230="",C230="",E230=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E230)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H230&lt;&gt;0,F230=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G230&lt;&gt;0,F230=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F230&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F230)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C230)*($E$5:$E$504=E230)*(($D$5:$D$504=D230)*(D230&lt;&gt;"")+($B$5:$B$504=B230)*(B230&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J230" s="5">
@@ -6553,11 +6581,11 @@
         <v/>
       </c>
       <c r="H231" s="5">
-        <f>IF(OR(C231="Удержание",C231="Зачёт встречного требования",C231="Неустойка заявлена"),N(E231),0)</f>
+        <f>IF(OR(C231="Удержание",C231="Зачёт встречного требования",C231="Неустойка заявлена",C231="Допработы без соглашения (спорно)"),N(E231),0)</f>
         <v/>
       </c>
       <c r="I231" s="6">
-        <f>IF(AND(B231="",C231="",D231="",E231="",F231=""),"",IF(OR(B231="",C231="",E231=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E231)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G231&lt;&gt;0,F231=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F231&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F231)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C231)*($E$5:$E$504=E231)*(($D$5:$D$504=D231)*(D231&lt;&gt;"")+($B$5:$B$504=B231)*(B231&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B231="",C231="",D231="",E231="",F231=""),"",IF(OR(B231="",C231="",E231=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E231)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H231&lt;&gt;0,F231=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G231&lt;&gt;0,F231=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F231&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F231)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C231)*($E$5:$E$504=E231)*(($D$5:$D$504=D231)*(D231&lt;&gt;"")+($B$5:$B$504=B231)*(B231&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J231" s="5">
@@ -6579,11 +6607,11 @@
         <v/>
       </c>
       <c r="H232" s="5">
-        <f>IF(OR(C232="Удержание",C232="Зачёт встречного требования",C232="Неустойка заявлена"),N(E232),0)</f>
+        <f>IF(OR(C232="Удержание",C232="Зачёт встречного требования",C232="Неустойка заявлена",C232="Допработы без соглашения (спорно)"),N(E232),0)</f>
         <v/>
       </c>
       <c r="I232" s="6">
-        <f>IF(AND(B232="",C232="",D232="",E232="",F232=""),"",IF(OR(B232="",C232="",E232=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E232)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G232&lt;&gt;0,F232=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F232&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F232)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C232)*($E$5:$E$504=E232)*(($D$5:$D$504=D232)*(D232&lt;&gt;"")+($B$5:$B$504=B232)*(B232&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B232="",C232="",D232="",E232="",F232=""),"",IF(OR(B232="",C232="",E232=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E232)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H232&lt;&gt;0,F232=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G232&lt;&gt;0,F232=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F232&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F232)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C232)*($E$5:$E$504=E232)*(($D$5:$D$504=D232)*(D232&lt;&gt;"")+($B$5:$B$504=B232)*(B232&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J232" s="5">
@@ -6605,11 +6633,11 @@
         <v/>
       </c>
       <c r="H233" s="5">
-        <f>IF(OR(C233="Удержание",C233="Зачёт встречного требования",C233="Неустойка заявлена"),N(E233),0)</f>
+        <f>IF(OR(C233="Удержание",C233="Зачёт встречного требования",C233="Неустойка заявлена",C233="Допработы без соглашения (спорно)"),N(E233),0)</f>
         <v/>
       </c>
       <c r="I233" s="6">
-        <f>IF(AND(B233="",C233="",D233="",E233="",F233=""),"",IF(OR(B233="",C233="",E233=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E233)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G233&lt;&gt;0,F233=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F233&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F233)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C233)*($E$5:$E$504=E233)*(($D$5:$D$504=D233)*(D233&lt;&gt;"")+($B$5:$B$504=B233)*(B233&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B233="",C233="",D233="",E233="",F233=""),"",IF(OR(B233="",C233="",E233=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E233)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H233&lt;&gt;0,F233=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G233&lt;&gt;0,F233=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F233&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F233)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C233)*($E$5:$E$504=E233)*(($D$5:$D$504=D233)*(D233&lt;&gt;"")+($B$5:$B$504=B233)*(B233&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J233" s="5">
@@ -6631,11 +6659,11 @@
         <v/>
       </c>
       <c r="H234" s="5">
-        <f>IF(OR(C234="Удержание",C234="Зачёт встречного требования",C234="Неустойка заявлена"),N(E234),0)</f>
+        <f>IF(OR(C234="Удержание",C234="Зачёт встречного требования",C234="Неустойка заявлена",C234="Допработы без соглашения (спорно)"),N(E234),0)</f>
         <v/>
       </c>
       <c r="I234" s="6">
-        <f>IF(AND(B234="",C234="",D234="",E234="",F234=""),"",IF(OR(B234="",C234="",E234=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E234)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G234&lt;&gt;0,F234=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F234&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F234)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C234)*($E$5:$E$504=E234)*(($D$5:$D$504=D234)*(D234&lt;&gt;"")+($B$5:$B$504=B234)*(B234&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B234="",C234="",D234="",E234="",F234=""),"",IF(OR(B234="",C234="",E234=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E234)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H234&lt;&gt;0,F234=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G234&lt;&gt;0,F234=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F234&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F234)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C234)*($E$5:$E$504=E234)*(($D$5:$D$504=D234)*(D234&lt;&gt;"")+($B$5:$B$504=B234)*(B234&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J234" s="5">
@@ -6657,11 +6685,11 @@
         <v/>
       </c>
       <c r="H235" s="5">
-        <f>IF(OR(C235="Удержание",C235="Зачёт встречного требования",C235="Неустойка заявлена"),N(E235),0)</f>
+        <f>IF(OR(C235="Удержание",C235="Зачёт встречного требования",C235="Неустойка заявлена",C235="Допработы без соглашения (спорно)"),N(E235),0)</f>
         <v/>
       </c>
       <c r="I235" s="6">
-        <f>IF(AND(B235="",C235="",D235="",E235="",F235=""),"",IF(OR(B235="",C235="",E235=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E235)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G235&lt;&gt;0,F235=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F235&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F235)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C235)*($E$5:$E$504=E235)*(($D$5:$D$504=D235)*(D235&lt;&gt;"")+($B$5:$B$504=B235)*(B235&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B235="",C235="",D235="",E235="",F235=""),"",IF(OR(B235="",C235="",E235=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E235)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H235&lt;&gt;0,F235=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G235&lt;&gt;0,F235=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F235&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F235)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C235)*($E$5:$E$504=E235)*(($D$5:$D$504=D235)*(D235&lt;&gt;"")+($B$5:$B$504=B235)*(B235&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J235" s="5">
@@ -6683,11 +6711,11 @@
         <v/>
       </c>
       <c r="H236" s="5">
-        <f>IF(OR(C236="Удержание",C236="Зачёт встречного требования",C236="Неустойка заявлена"),N(E236),0)</f>
+        <f>IF(OR(C236="Удержание",C236="Зачёт встречного требования",C236="Неустойка заявлена",C236="Допработы без соглашения (спорно)"),N(E236),0)</f>
         <v/>
       </c>
       <c r="I236" s="6">
-        <f>IF(AND(B236="",C236="",D236="",E236="",F236=""),"",IF(OR(B236="",C236="",E236=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E236)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G236&lt;&gt;0,F236=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F236&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F236)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C236)*($E$5:$E$504=E236)*(($D$5:$D$504=D236)*(D236&lt;&gt;"")+($B$5:$B$504=B236)*(B236&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B236="",C236="",D236="",E236="",F236=""),"",IF(OR(B236="",C236="",E236=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E236)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H236&lt;&gt;0,F236=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G236&lt;&gt;0,F236=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F236&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F236)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C236)*($E$5:$E$504=E236)*(($D$5:$D$504=D236)*(D236&lt;&gt;"")+($B$5:$B$504=B236)*(B236&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J236" s="5">
@@ -6709,11 +6737,11 @@
         <v/>
       </c>
       <c r="H237" s="5">
-        <f>IF(OR(C237="Удержание",C237="Зачёт встречного требования",C237="Неустойка заявлена"),N(E237),0)</f>
+        <f>IF(OR(C237="Удержание",C237="Зачёт встречного требования",C237="Неустойка заявлена",C237="Допработы без соглашения (спорно)"),N(E237),0)</f>
         <v/>
       </c>
       <c r="I237" s="6">
-        <f>IF(AND(B237="",C237="",D237="",E237="",F237=""),"",IF(OR(B237="",C237="",E237=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E237)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G237&lt;&gt;0,F237=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F237&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F237)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C237)*($E$5:$E$504=E237)*(($D$5:$D$504=D237)*(D237&lt;&gt;"")+($B$5:$B$504=B237)*(B237&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B237="",C237="",D237="",E237="",F237=""),"",IF(OR(B237="",C237="",E237=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E237)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H237&lt;&gt;0,F237=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G237&lt;&gt;0,F237=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F237&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F237)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C237)*($E$5:$E$504=E237)*(($D$5:$D$504=D237)*(D237&lt;&gt;"")+($B$5:$B$504=B237)*(B237&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J237" s="5">
@@ -6735,11 +6763,11 @@
         <v/>
       </c>
       <c r="H238" s="5">
-        <f>IF(OR(C238="Удержание",C238="Зачёт встречного требования",C238="Неустойка заявлена"),N(E238),0)</f>
+        <f>IF(OR(C238="Удержание",C238="Зачёт встречного требования",C238="Неустойка заявлена",C238="Допработы без соглашения (спорно)"),N(E238),0)</f>
         <v/>
       </c>
       <c r="I238" s="6">
-        <f>IF(AND(B238="",C238="",D238="",E238="",F238=""),"",IF(OR(B238="",C238="",E238=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E238)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G238&lt;&gt;0,F238=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F238&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F238)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C238)*($E$5:$E$504=E238)*(($D$5:$D$504=D238)*(D238&lt;&gt;"")+($B$5:$B$504=B238)*(B238&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B238="",C238="",D238="",E238="",F238=""),"",IF(OR(B238="",C238="",E238=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E238)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H238&lt;&gt;0,F238=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G238&lt;&gt;0,F238=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F238&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F238)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C238)*($E$5:$E$504=E238)*(($D$5:$D$504=D238)*(D238&lt;&gt;"")+($B$5:$B$504=B238)*(B238&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J238" s="5">
@@ -6761,11 +6789,11 @@
         <v/>
       </c>
       <c r="H239" s="5">
-        <f>IF(OR(C239="Удержание",C239="Зачёт встречного требования",C239="Неустойка заявлена"),N(E239),0)</f>
+        <f>IF(OR(C239="Удержание",C239="Зачёт встречного требования",C239="Неустойка заявлена",C239="Допработы без соглашения (спорно)"),N(E239),0)</f>
         <v/>
       </c>
       <c r="I239" s="6">
-        <f>IF(AND(B239="",C239="",D239="",E239="",F239=""),"",IF(OR(B239="",C239="",E239=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E239)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G239&lt;&gt;0,F239=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F239&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F239)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C239)*($E$5:$E$504=E239)*(($D$5:$D$504=D239)*(D239&lt;&gt;"")+($B$5:$B$504=B239)*(B239&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B239="",C239="",D239="",E239="",F239=""),"",IF(OR(B239="",C239="",E239=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E239)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H239&lt;&gt;0,F239=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G239&lt;&gt;0,F239=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F239&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F239)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C239)*($E$5:$E$504=E239)*(($D$5:$D$504=D239)*(D239&lt;&gt;"")+($B$5:$B$504=B239)*(B239&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J239" s="5">
@@ -6787,11 +6815,11 @@
         <v/>
       </c>
       <c r="H240" s="5">
-        <f>IF(OR(C240="Удержание",C240="Зачёт встречного требования",C240="Неустойка заявлена"),N(E240),0)</f>
+        <f>IF(OR(C240="Удержание",C240="Зачёт встречного требования",C240="Неустойка заявлена",C240="Допработы без соглашения (спорно)"),N(E240),0)</f>
         <v/>
       </c>
       <c r="I240" s="6">
-        <f>IF(AND(B240="",C240="",D240="",E240="",F240=""),"",IF(OR(B240="",C240="",E240=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E240)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G240&lt;&gt;0,F240=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F240&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F240)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C240)*($E$5:$E$504=E240)*(($D$5:$D$504=D240)*(D240&lt;&gt;"")+($B$5:$B$504=B240)*(B240&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B240="",C240="",D240="",E240="",F240=""),"",IF(OR(B240="",C240="",E240=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E240)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H240&lt;&gt;0,F240=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G240&lt;&gt;0,F240=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F240&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F240)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C240)*($E$5:$E$504=E240)*(($D$5:$D$504=D240)*(D240&lt;&gt;"")+($B$5:$B$504=B240)*(B240&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J240" s="5">
@@ -6813,11 +6841,11 @@
         <v/>
       </c>
       <c r="H241" s="5">
-        <f>IF(OR(C241="Удержание",C241="Зачёт встречного требования",C241="Неустойка заявлена"),N(E241),0)</f>
+        <f>IF(OR(C241="Удержание",C241="Зачёт встречного требования",C241="Неустойка заявлена",C241="Допработы без соглашения (спорно)"),N(E241),0)</f>
         <v/>
       </c>
       <c r="I241" s="6">
-        <f>IF(AND(B241="",C241="",D241="",E241="",F241=""),"",IF(OR(B241="",C241="",E241=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E241)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G241&lt;&gt;0,F241=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F241&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F241)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C241)*($E$5:$E$504=E241)*(($D$5:$D$504=D241)*(D241&lt;&gt;"")+($B$5:$B$504=B241)*(B241&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B241="",C241="",D241="",E241="",F241=""),"",IF(OR(B241="",C241="",E241=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E241)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H241&lt;&gt;0,F241=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G241&lt;&gt;0,F241=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F241&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F241)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C241)*($E$5:$E$504=E241)*(($D$5:$D$504=D241)*(D241&lt;&gt;"")+($B$5:$B$504=B241)*(B241&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J241" s="5">
@@ -6839,11 +6867,11 @@
         <v/>
       </c>
       <c r="H242" s="5">
-        <f>IF(OR(C242="Удержание",C242="Зачёт встречного требования",C242="Неустойка заявлена"),N(E242),0)</f>
+        <f>IF(OR(C242="Удержание",C242="Зачёт встречного требования",C242="Неустойка заявлена",C242="Допработы без соглашения (спорно)"),N(E242),0)</f>
         <v/>
       </c>
       <c r="I242" s="6">
-        <f>IF(AND(B242="",C242="",D242="",E242="",F242=""),"",IF(OR(B242="",C242="",E242=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E242)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G242&lt;&gt;0,F242=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F242&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F242)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C242)*($E$5:$E$504=E242)*(($D$5:$D$504=D242)*(D242&lt;&gt;"")+($B$5:$B$504=B242)*(B242&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B242="",C242="",D242="",E242="",F242=""),"",IF(OR(B242="",C242="",E242=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E242)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H242&lt;&gt;0,F242=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G242&lt;&gt;0,F242=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F242&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F242)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C242)*($E$5:$E$504=E242)*(($D$5:$D$504=D242)*(D242&lt;&gt;"")+($B$5:$B$504=B242)*(B242&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J242" s="5">
@@ -6865,11 +6893,11 @@
         <v/>
       </c>
       <c r="H243" s="5">
-        <f>IF(OR(C243="Удержание",C243="Зачёт встречного требования",C243="Неустойка заявлена"),N(E243),0)</f>
+        <f>IF(OR(C243="Удержание",C243="Зачёт встречного требования",C243="Неустойка заявлена",C243="Допработы без соглашения (спорно)"),N(E243),0)</f>
         <v/>
       </c>
       <c r="I243" s="6">
-        <f>IF(AND(B243="",C243="",D243="",E243="",F243=""),"",IF(OR(B243="",C243="",E243=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E243)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G243&lt;&gt;0,F243=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F243&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F243)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C243)*($E$5:$E$504=E243)*(($D$5:$D$504=D243)*(D243&lt;&gt;"")+($B$5:$B$504=B243)*(B243&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B243="",C243="",D243="",E243="",F243=""),"",IF(OR(B243="",C243="",E243=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E243)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H243&lt;&gt;0,F243=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G243&lt;&gt;0,F243=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F243&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F243)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C243)*($E$5:$E$504=E243)*(($D$5:$D$504=D243)*(D243&lt;&gt;"")+($B$5:$B$504=B243)*(B243&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J243" s="5">
@@ -6891,11 +6919,11 @@
         <v/>
       </c>
       <c r="H244" s="5">
-        <f>IF(OR(C244="Удержание",C244="Зачёт встречного требования",C244="Неустойка заявлена"),N(E244),0)</f>
+        <f>IF(OR(C244="Удержание",C244="Зачёт встречного требования",C244="Неустойка заявлена",C244="Допработы без соглашения (спорно)"),N(E244),0)</f>
         <v/>
       </c>
       <c r="I244" s="6">
-        <f>IF(AND(B244="",C244="",D244="",E244="",F244=""),"",IF(OR(B244="",C244="",E244=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E244)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G244&lt;&gt;0,F244=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F244&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F244)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C244)*($E$5:$E$504=E244)*(($D$5:$D$504=D244)*(D244&lt;&gt;"")+($B$5:$B$504=B244)*(B244&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B244="",C244="",D244="",E244="",F244=""),"",IF(OR(B244="",C244="",E244=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E244)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H244&lt;&gt;0,F244=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G244&lt;&gt;0,F244=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F244&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F244)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C244)*($E$5:$E$504=E244)*(($D$5:$D$504=D244)*(D244&lt;&gt;"")+($B$5:$B$504=B244)*(B244&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J244" s="5">
@@ -6917,11 +6945,11 @@
         <v/>
       </c>
       <c r="H245" s="5">
-        <f>IF(OR(C245="Удержание",C245="Зачёт встречного требования",C245="Неустойка заявлена"),N(E245),0)</f>
+        <f>IF(OR(C245="Удержание",C245="Зачёт встречного требования",C245="Неустойка заявлена",C245="Допработы без соглашения (спорно)"),N(E245),0)</f>
         <v/>
       </c>
       <c r="I245" s="6">
-        <f>IF(AND(B245="",C245="",D245="",E245="",F245=""),"",IF(OR(B245="",C245="",E245=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E245)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G245&lt;&gt;0,F245=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F245&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F245)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C245)*($E$5:$E$504=E245)*(($D$5:$D$504=D245)*(D245&lt;&gt;"")+($B$5:$B$504=B245)*(B245&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B245="",C245="",D245="",E245="",F245=""),"",IF(OR(B245="",C245="",E245=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E245)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H245&lt;&gt;0,F245=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G245&lt;&gt;0,F245=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F245&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F245)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C245)*($E$5:$E$504=E245)*(($D$5:$D$504=D245)*(D245&lt;&gt;"")+($B$5:$B$504=B245)*(B245&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J245" s="5">
@@ -6943,11 +6971,11 @@
         <v/>
       </c>
       <c r="H246" s="5">
-        <f>IF(OR(C246="Удержание",C246="Зачёт встречного требования",C246="Неустойка заявлена"),N(E246),0)</f>
+        <f>IF(OR(C246="Удержание",C246="Зачёт встречного требования",C246="Неустойка заявлена",C246="Допработы без соглашения (спорно)"),N(E246),0)</f>
         <v/>
       </c>
       <c r="I246" s="6">
-        <f>IF(AND(B246="",C246="",D246="",E246="",F246=""),"",IF(OR(B246="",C246="",E246=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E246)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G246&lt;&gt;0,F246=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F246&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F246)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C246)*($E$5:$E$504=E246)*(($D$5:$D$504=D246)*(D246&lt;&gt;"")+($B$5:$B$504=B246)*(B246&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B246="",C246="",D246="",E246="",F246=""),"",IF(OR(B246="",C246="",E246=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E246)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H246&lt;&gt;0,F246=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G246&lt;&gt;0,F246=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F246&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F246)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C246)*($E$5:$E$504=E246)*(($D$5:$D$504=D246)*(D246&lt;&gt;"")+($B$5:$B$504=B246)*(B246&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J246" s="5">
@@ -6969,11 +6997,11 @@
         <v/>
       </c>
       <c r="H247" s="5">
-        <f>IF(OR(C247="Удержание",C247="Зачёт встречного требования",C247="Неустойка заявлена"),N(E247),0)</f>
+        <f>IF(OR(C247="Удержание",C247="Зачёт встречного требования",C247="Неустойка заявлена",C247="Допработы без соглашения (спорно)"),N(E247),0)</f>
         <v/>
       </c>
       <c r="I247" s="6">
-        <f>IF(AND(B247="",C247="",D247="",E247="",F247=""),"",IF(OR(B247="",C247="",E247=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E247)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G247&lt;&gt;0,F247=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F247&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F247)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C247)*($E$5:$E$504=E247)*(($D$5:$D$504=D247)*(D247&lt;&gt;"")+($B$5:$B$504=B247)*(B247&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B247="",C247="",D247="",E247="",F247=""),"",IF(OR(B247="",C247="",E247=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E247)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H247&lt;&gt;0,F247=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G247&lt;&gt;0,F247=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F247&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F247)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C247)*($E$5:$E$504=E247)*(($D$5:$D$504=D247)*(D247&lt;&gt;"")+($B$5:$B$504=B247)*(B247&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J247" s="5">
@@ -6995,11 +7023,11 @@
         <v/>
       </c>
       <c r="H248" s="5">
-        <f>IF(OR(C248="Удержание",C248="Зачёт встречного требования",C248="Неустойка заявлена"),N(E248),0)</f>
+        <f>IF(OR(C248="Удержание",C248="Зачёт встречного требования",C248="Неустойка заявлена",C248="Допработы без соглашения (спорно)"),N(E248),0)</f>
         <v/>
       </c>
       <c r="I248" s="6">
-        <f>IF(AND(B248="",C248="",D248="",E248="",F248=""),"",IF(OR(B248="",C248="",E248=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E248)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G248&lt;&gt;0,F248=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F248&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F248)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C248)*($E$5:$E$504=E248)*(($D$5:$D$504=D248)*(D248&lt;&gt;"")+($B$5:$B$504=B248)*(B248&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B248="",C248="",D248="",E248="",F248=""),"",IF(OR(B248="",C248="",E248=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E248)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H248&lt;&gt;0,F248=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G248&lt;&gt;0,F248=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F248&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F248)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C248)*($E$5:$E$504=E248)*(($D$5:$D$504=D248)*(D248&lt;&gt;"")+($B$5:$B$504=B248)*(B248&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J248" s="5">
@@ -7021,11 +7049,11 @@
         <v/>
       </c>
       <c r="H249" s="5">
-        <f>IF(OR(C249="Удержание",C249="Зачёт встречного требования",C249="Неустойка заявлена"),N(E249),0)</f>
+        <f>IF(OR(C249="Удержание",C249="Зачёт встречного требования",C249="Неустойка заявлена",C249="Допработы без соглашения (спорно)"),N(E249),0)</f>
         <v/>
       </c>
       <c r="I249" s="6">
-        <f>IF(AND(B249="",C249="",D249="",E249="",F249=""),"",IF(OR(B249="",C249="",E249=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E249)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G249&lt;&gt;0,F249=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F249&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F249)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C249)*($E$5:$E$504=E249)*(($D$5:$D$504=D249)*(D249&lt;&gt;"")+($B$5:$B$504=B249)*(B249&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B249="",C249="",D249="",E249="",F249=""),"",IF(OR(B249="",C249="",E249=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E249)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H249&lt;&gt;0,F249=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G249&lt;&gt;0,F249=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F249&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F249)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C249)*($E$5:$E$504=E249)*(($D$5:$D$504=D249)*(D249&lt;&gt;"")+($B$5:$B$504=B249)*(B249&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J249" s="5">
@@ -7047,11 +7075,11 @@
         <v/>
       </c>
       <c r="H250" s="5">
-        <f>IF(OR(C250="Удержание",C250="Зачёт встречного требования",C250="Неустойка заявлена"),N(E250),0)</f>
+        <f>IF(OR(C250="Удержание",C250="Зачёт встречного требования",C250="Неустойка заявлена",C250="Допработы без соглашения (спорно)"),N(E250),0)</f>
         <v/>
       </c>
       <c r="I250" s="6">
-        <f>IF(AND(B250="",C250="",D250="",E250="",F250=""),"",IF(OR(B250="",C250="",E250=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E250)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G250&lt;&gt;0,F250=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F250&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F250)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C250)*($E$5:$E$504=E250)*(($D$5:$D$504=D250)*(D250&lt;&gt;"")+($B$5:$B$504=B250)*(B250&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B250="",C250="",D250="",E250="",F250=""),"",IF(OR(B250="",C250="",E250=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E250)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H250&lt;&gt;0,F250=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G250&lt;&gt;0,F250=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F250&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F250)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C250)*($E$5:$E$504=E250)*(($D$5:$D$504=D250)*(D250&lt;&gt;"")+($B$5:$B$504=B250)*(B250&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J250" s="5">
@@ -7073,11 +7101,11 @@
         <v/>
       </c>
       <c r="H251" s="5">
-        <f>IF(OR(C251="Удержание",C251="Зачёт встречного требования",C251="Неустойка заявлена"),N(E251),0)</f>
+        <f>IF(OR(C251="Удержание",C251="Зачёт встречного требования",C251="Неустойка заявлена",C251="Допработы без соглашения (спорно)"),N(E251),0)</f>
         <v/>
       </c>
       <c r="I251" s="6">
-        <f>IF(AND(B251="",C251="",D251="",E251="",F251=""),"",IF(OR(B251="",C251="",E251=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E251)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G251&lt;&gt;0,F251=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F251&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F251)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C251)*($E$5:$E$504=E251)*(($D$5:$D$504=D251)*(D251&lt;&gt;"")+($B$5:$B$504=B251)*(B251&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B251="",C251="",D251="",E251="",F251=""),"",IF(OR(B251="",C251="",E251=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E251)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H251&lt;&gt;0,F251=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G251&lt;&gt;0,F251=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F251&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F251)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C251)*($E$5:$E$504=E251)*(($D$5:$D$504=D251)*(D251&lt;&gt;"")+($B$5:$B$504=B251)*(B251&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J251" s="5">
@@ -7099,11 +7127,11 @@
         <v/>
       </c>
       <c r="H252" s="5">
-        <f>IF(OR(C252="Удержание",C252="Зачёт встречного требования",C252="Неустойка заявлена"),N(E252),0)</f>
+        <f>IF(OR(C252="Удержание",C252="Зачёт встречного требования",C252="Неустойка заявлена",C252="Допработы без соглашения (спорно)"),N(E252),0)</f>
         <v/>
       </c>
       <c r="I252" s="6">
-        <f>IF(AND(B252="",C252="",D252="",E252="",F252=""),"",IF(OR(B252="",C252="",E252=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E252)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G252&lt;&gt;0,F252=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F252&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F252)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C252)*($E$5:$E$504=E252)*(($D$5:$D$504=D252)*(D252&lt;&gt;"")+($B$5:$B$504=B252)*(B252&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B252="",C252="",D252="",E252="",F252=""),"",IF(OR(B252="",C252="",E252=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E252)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H252&lt;&gt;0,F252=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G252&lt;&gt;0,F252=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F252&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F252)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C252)*($E$5:$E$504=E252)*(($D$5:$D$504=D252)*(D252&lt;&gt;"")+($B$5:$B$504=B252)*(B252&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J252" s="5">
@@ -7125,11 +7153,11 @@
         <v/>
       </c>
       <c r="H253" s="5">
-        <f>IF(OR(C253="Удержание",C253="Зачёт встречного требования",C253="Неустойка заявлена"),N(E253),0)</f>
+        <f>IF(OR(C253="Удержание",C253="Зачёт встречного требования",C253="Неустойка заявлена",C253="Допработы без соглашения (спорно)"),N(E253),0)</f>
         <v/>
       </c>
       <c r="I253" s="6">
-        <f>IF(AND(B253="",C253="",D253="",E253="",F253=""),"",IF(OR(B253="",C253="",E253=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E253)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G253&lt;&gt;0,F253=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F253&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F253)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C253)*($E$5:$E$504=E253)*(($D$5:$D$504=D253)*(D253&lt;&gt;"")+($B$5:$B$504=B253)*(B253&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B253="",C253="",D253="",E253="",F253=""),"",IF(OR(B253="",C253="",E253=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E253)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H253&lt;&gt;0,F253=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G253&lt;&gt;0,F253=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F253&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F253)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C253)*($E$5:$E$504=E253)*(($D$5:$D$504=D253)*(D253&lt;&gt;"")+($B$5:$B$504=B253)*(B253&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J253" s="5">
@@ -7151,11 +7179,11 @@
         <v/>
       </c>
       <c r="H254" s="5">
-        <f>IF(OR(C254="Удержание",C254="Зачёт встречного требования",C254="Неустойка заявлена"),N(E254),0)</f>
+        <f>IF(OR(C254="Удержание",C254="Зачёт встречного требования",C254="Неустойка заявлена",C254="Допработы без соглашения (спорно)"),N(E254),0)</f>
         <v/>
       </c>
       <c r="I254" s="6">
-        <f>IF(AND(B254="",C254="",D254="",E254="",F254=""),"",IF(OR(B254="",C254="",E254=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E254)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G254&lt;&gt;0,F254=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F254&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F254)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C254)*($E$5:$E$504=E254)*(($D$5:$D$504=D254)*(D254&lt;&gt;"")+($B$5:$B$504=B254)*(B254&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B254="",C254="",D254="",E254="",F254=""),"",IF(OR(B254="",C254="",E254=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E254)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H254&lt;&gt;0,F254=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G254&lt;&gt;0,F254=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F254&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F254)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C254)*($E$5:$E$504=E254)*(($D$5:$D$504=D254)*(D254&lt;&gt;"")+($B$5:$B$504=B254)*(B254&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J254" s="5">
@@ -7177,11 +7205,11 @@
         <v/>
       </c>
       <c r="H255" s="5">
-        <f>IF(OR(C255="Удержание",C255="Зачёт встречного требования",C255="Неустойка заявлена"),N(E255),0)</f>
+        <f>IF(OR(C255="Удержание",C255="Зачёт встречного требования",C255="Неустойка заявлена",C255="Допработы без соглашения (спорно)"),N(E255),0)</f>
         <v/>
       </c>
       <c r="I255" s="6">
-        <f>IF(AND(B255="",C255="",D255="",E255="",F255=""),"",IF(OR(B255="",C255="",E255=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E255)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G255&lt;&gt;0,F255=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F255&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F255)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C255)*($E$5:$E$504=E255)*(($D$5:$D$504=D255)*(D255&lt;&gt;"")+($B$5:$B$504=B255)*(B255&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B255="",C255="",D255="",E255="",F255=""),"",IF(OR(B255="",C255="",E255=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E255)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H255&lt;&gt;0,F255=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G255&lt;&gt;0,F255=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F255&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F255)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C255)*($E$5:$E$504=E255)*(($D$5:$D$504=D255)*(D255&lt;&gt;"")+($B$5:$B$504=B255)*(B255&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J255" s="5">
@@ -7203,11 +7231,11 @@
         <v/>
       </c>
       <c r="H256" s="5">
-        <f>IF(OR(C256="Удержание",C256="Зачёт встречного требования",C256="Неустойка заявлена"),N(E256),0)</f>
+        <f>IF(OR(C256="Удержание",C256="Зачёт встречного требования",C256="Неустойка заявлена",C256="Допработы без соглашения (спорно)"),N(E256),0)</f>
         <v/>
       </c>
       <c r="I256" s="6">
-        <f>IF(AND(B256="",C256="",D256="",E256="",F256=""),"",IF(OR(B256="",C256="",E256=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E256)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G256&lt;&gt;0,F256=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F256&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F256)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C256)*($E$5:$E$504=E256)*(($D$5:$D$504=D256)*(D256&lt;&gt;"")+($B$5:$B$504=B256)*(B256&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B256="",C256="",D256="",E256="",F256=""),"",IF(OR(B256="",C256="",E256=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E256)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H256&lt;&gt;0,F256=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G256&lt;&gt;0,F256=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F256&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F256)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C256)*($E$5:$E$504=E256)*(($D$5:$D$504=D256)*(D256&lt;&gt;"")+($B$5:$B$504=B256)*(B256&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J256" s="5">
@@ -7229,11 +7257,11 @@
         <v/>
       </c>
       <c r="H257" s="5">
-        <f>IF(OR(C257="Удержание",C257="Зачёт встречного требования",C257="Неустойка заявлена"),N(E257),0)</f>
+        <f>IF(OR(C257="Удержание",C257="Зачёт встречного требования",C257="Неустойка заявлена",C257="Допработы без соглашения (спорно)"),N(E257),0)</f>
         <v/>
       </c>
       <c r="I257" s="6">
-        <f>IF(AND(B257="",C257="",D257="",E257="",F257=""),"",IF(OR(B257="",C257="",E257=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E257)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G257&lt;&gt;0,F257=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F257&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F257)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C257)*($E$5:$E$504=E257)*(($D$5:$D$504=D257)*(D257&lt;&gt;"")+($B$5:$B$504=B257)*(B257&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B257="",C257="",D257="",E257="",F257=""),"",IF(OR(B257="",C257="",E257=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E257)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H257&lt;&gt;0,F257=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G257&lt;&gt;0,F257=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F257&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F257)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C257)*($E$5:$E$504=E257)*(($D$5:$D$504=D257)*(D257&lt;&gt;"")+($B$5:$B$504=B257)*(B257&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J257" s="5">
@@ -7255,11 +7283,11 @@
         <v/>
       </c>
       <c r="H258" s="5">
-        <f>IF(OR(C258="Удержание",C258="Зачёт встречного требования",C258="Неустойка заявлена"),N(E258),0)</f>
+        <f>IF(OR(C258="Удержание",C258="Зачёт встречного требования",C258="Неустойка заявлена",C258="Допработы без соглашения (спорно)"),N(E258),0)</f>
         <v/>
       </c>
       <c r="I258" s="6">
-        <f>IF(AND(B258="",C258="",D258="",E258="",F258=""),"",IF(OR(B258="",C258="",E258=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E258)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G258&lt;&gt;0,F258=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F258&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F258)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C258)*($E$5:$E$504=E258)*(($D$5:$D$504=D258)*(D258&lt;&gt;"")+($B$5:$B$504=B258)*(B258&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B258="",C258="",D258="",E258="",F258=""),"",IF(OR(B258="",C258="",E258=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E258)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H258&lt;&gt;0,F258=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G258&lt;&gt;0,F258=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F258&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F258)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C258)*($E$5:$E$504=E258)*(($D$5:$D$504=D258)*(D258&lt;&gt;"")+($B$5:$B$504=B258)*(B258&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J258" s="5">
@@ -7281,11 +7309,11 @@
         <v/>
       </c>
       <c r="H259" s="5">
-        <f>IF(OR(C259="Удержание",C259="Зачёт встречного требования",C259="Неустойка заявлена"),N(E259),0)</f>
+        <f>IF(OR(C259="Удержание",C259="Зачёт встречного требования",C259="Неустойка заявлена",C259="Допработы без соглашения (спорно)"),N(E259),0)</f>
         <v/>
       </c>
       <c r="I259" s="6">
-        <f>IF(AND(B259="",C259="",D259="",E259="",F259=""),"",IF(OR(B259="",C259="",E259=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E259)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G259&lt;&gt;0,F259=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F259&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F259)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C259)*($E$5:$E$504=E259)*(($D$5:$D$504=D259)*(D259&lt;&gt;"")+($B$5:$B$504=B259)*(B259&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B259="",C259="",D259="",E259="",F259=""),"",IF(OR(B259="",C259="",E259=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E259)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H259&lt;&gt;0,F259=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G259&lt;&gt;0,F259=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F259&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F259)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C259)*($E$5:$E$504=E259)*(($D$5:$D$504=D259)*(D259&lt;&gt;"")+($B$5:$B$504=B259)*(B259&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J259" s="5">
@@ -7307,11 +7335,11 @@
         <v/>
       </c>
       <c r="H260" s="5">
-        <f>IF(OR(C260="Удержание",C260="Зачёт встречного требования",C260="Неустойка заявлена"),N(E260),0)</f>
+        <f>IF(OR(C260="Удержание",C260="Зачёт встречного требования",C260="Неустойка заявлена",C260="Допработы без соглашения (спорно)"),N(E260),0)</f>
         <v/>
       </c>
       <c r="I260" s="6">
-        <f>IF(AND(B260="",C260="",D260="",E260="",F260=""),"",IF(OR(B260="",C260="",E260=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E260)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G260&lt;&gt;0,F260=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F260&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F260)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C260)*($E$5:$E$504=E260)*(($D$5:$D$504=D260)*(D260&lt;&gt;"")+($B$5:$B$504=B260)*(B260&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B260="",C260="",D260="",E260="",F260=""),"",IF(OR(B260="",C260="",E260=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E260)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H260&lt;&gt;0,F260=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G260&lt;&gt;0,F260=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F260&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F260)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C260)*($E$5:$E$504=E260)*(($D$5:$D$504=D260)*(D260&lt;&gt;"")+($B$5:$B$504=B260)*(B260&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J260" s="5">
@@ -7333,11 +7361,11 @@
         <v/>
       </c>
       <c r="H261" s="5">
-        <f>IF(OR(C261="Удержание",C261="Зачёт встречного требования",C261="Неустойка заявлена"),N(E261),0)</f>
+        <f>IF(OR(C261="Удержание",C261="Зачёт встречного требования",C261="Неустойка заявлена",C261="Допработы без соглашения (спорно)"),N(E261),0)</f>
         <v/>
       </c>
       <c r="I261" s="6">
-        <f>IF(AND(B261="",C261="",D261="",E261="",F261=""),"",IF(OR(B261="",C261="",E261=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E261)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G261&lt;&gt;0,F261=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F261&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F261)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C261)*($E$5:$E$504=E261)*(($D$5:$D$504=D261)*(D261&lt;&gt;"")+($B$5:$B$504=B261)*(B261&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B261="",C261="",D261="",E261="",F261=""),"",IF(OR(B261="",C261="",E261=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E261)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H261&lt;&gt;0,F261=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G261&lt;&gt;0,F261=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F261&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F261)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C261)*($E$5:$E$504=E261)*(($D$5:$D$504=D261)*(D261&lt;&gt;"")+($B$5:$B$504=B261)*(B261&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J261" s="5">
@@ -7359,11 +7387,11 @@
         <v/>
       </c>
       <c r="H262" s="5">
-        <f>IF(OR(C262="Удержание",C262="Зачёт встречного требования",C262="Неустойка заявлена"),N(E262),0)</f>
+        <f>IF(OR(C262="Удержание",C262="Зачёт встречного требования",C262="Неустойка заявлена",C262="Допработы без соглашения (спорно)"),N(E262),0)</f>
         <v/>
       </c>
       <c r="I262" s="6">
-        <f>IF(AND(B262="",C262="",D262="",E262="",F262=""),"",IF(OR(B262="",C262="",E262=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E262)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G262&lt;&gt;0,F262=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F262&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F262)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C262)*($E$5:$E$504=E262)*(($D$5:$D$504=D262)*(D262&lt;&gt;"")+($B$5:$B$504=B262)*(B262&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B262="",C262="",D262="",E262="",F262=""),"",IF(OR(B262="",C262="",E262=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E262)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H262&lt;&gt;0,F262=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G262&lt;&gt;0,F262=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F262&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F262)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C262)*($E$5:$E$504=E262)*(($D$5:$D$504=D262)*(D262&lt;&gt;"")+($B$5:$B$504=B262)*(B262&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J262" s="5">
@@ -7385,11 +7413,11 @@
         <v/>
       </c>
       <c r="H263" s="5">
-        <f>IF(OR(C263="Удержание",C263="Зачёт встречного требования",C263="Неустойка заявлена"),N(E263),0)</f>
+        <f>IF(OR(C263="Удержание",C263="Зачёт встречного требования",C263="Неустойка заявлена",C263="Допработы без соглашения (спорно)"),N(E263),0)</f>
         <v/>
       </c>
       <c r="I263" s="6">
-        <f>IF(AND(B263="",C263="",D263="",E263="",F263=""),"",IF(OR(B263="",C263="",E263=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E263)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G263&lt;&gt;0,F263=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F263&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F263)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C263)*($E$5:$E$504=E263)*(($D$5:$D$504=D263)*(D263&lt;&gt;"")+($B$5:$B$504=B263)*(B263&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B263="",C263="",D263="",E263="",F263=""),"",IF(OR(B263="",C263="",E263=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E263)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H263&lt;&gt;0,F263=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G263&lt;&gt;0,F263=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F263&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F263)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C263)*($E$5:$E$504=E263)*(($D$5:$D$504=D263)*(D263&lt;&gt;"")+($B$5:$B$504=B263)*(B263&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J263" s="5">
@@ -7411,11 +7439,11 @@
         <v/>
       </c>
       <c r="H264" s="5">
-        <f>IF(OR(C264="Удержание",C264="Зачёт встречного требования",C264="Неустойка заявлена"),N(E264),0)</f>
+        <f>IF(OR(C264="Удержание",C264="Зачёт встречного требования",C264="Неустойка заявлена",C264="Допработы без соглашения (спорно)"),N(E264),0)</f>
         <v/>
       </c>
       <c r="I264" s="6">
-        <f>IF(AND(B264="",C264="",D264="",E264="",F264=""),"",IF(OR(B264="",C264="",E264=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E264)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G264&lt;&gt;0,F264=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F264&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F264)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C264)*($E$5:$E$504=E264)*(($D$5:$D$504=D264)*(D264&lt;&gt;"")+($B$5:$B$504=B264)*(B264&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B264="",C264="",D264="",E264="",F264=""),"",IF(OR(B264="",C264="",E264=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E264)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H264&lt;&gt;0,F264=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G264&lt;&gt;0,F264=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F264&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F264)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C264)*($E$5:$E$504=E264)*(($D$5:$D$504=D264)*(D264&lt;&gt;"")+($B$5:$B$504=B264)*(B264&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J264" s="5">
@@ -7437,11 +7465,11 @@
         <v/>
       </c>
       <c r="H265" s="5">
-        <f>IF(OR(C265="Удержание",C265="Зачёт встречного требования",C265="Неустойка заявлена"),N(E265),0)</f>
+        <f>IF(OR(C265="Удержание",C265="Зачёт встречного требования",C265="Неустойка заявлена",C265="Допработы без соглашения (спорно)"),N(E265),0)</f>
         <v/>
       </c>
       <c r="I265" s="6">
-        <f>IF(AND(B265="",C265="",D265="",E265="",F265=""),"",IF(OR(B265="",C265="",E265=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E265)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G265&lt;&gt;0,F265=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F265&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F265)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C265)*($E$5:$E$504=E265)*(($D$5:$D$504=D265)*(D265&lt;&gt;"")+($B$5:$B$504=B265)*(B265&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B265="",C265="",D265="",E265="",F265=""),"",IF(OR(B265="",C265="",E265=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E265)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H265&lt;&gt;0,F265=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G265&lt;&gt;0,F265=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F265&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F265)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C265)*($E$5:$E$504=E265)*(($D$5:$D$504=D265)*(D265&lt;&gt;"")+($B$5:$B$504=B265)*(B265&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J265" s="5">
@@ -7463,11 +7491,11 @@
         <v/>
       </c>
       <c r="H266" s="5">
-        <f>IF(OR(C266="Удержание",C266="Зачёт встречного требования",C266="Неустойка заявлена"),N(E266),0)</f>
+        <f>IF(OR(C266="Удержание",C266="Зачёт встречного требования",C266="Неустойка заявлена",C266="Допработы без соглашения (спорно)"),N(E266),0)</f>
         <v/>
       </c>
       <c r="I266" s="6">
-        <f>IF(AND(B266="",C266="",D266="",E266="",F266=""),"",IF(OR(B266="",C266="",E266=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E266)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G266&lt;&gt;0,F266=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F266&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F266)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C266)*($E$5:$E$504=E266)*(($D$5:$D$504=D266)*(D266&lt;&gt;"")+($B$5:$B$504=B266)*(B266&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B266="",C266="",D266="",E266="",F266=""),"",IF(OR(B266="",C266="",E266=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E266)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H266&lt;&gt;0,F266=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G266&lt;&gt;0,F266=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F266&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F266)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C266)*($E$5:$E$504=E266)*(($D$5:$D$504=D266)*(D266&lt;&gt;"")+($B$5:$B$504=B266)*(B266&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J266" s="5">
@@ -7489,11 +7517,11 @@
         <v/>
       </c>
       <c r="H267" s="5">
-        <f>IF(OR(C267="Удержание",C267="Зачёт встречного требования",C267="Неустойка заявлена"),N(E267),0)</f>
+        <f>IF(OR(C267="Удержание",C267="Зачёт встречного требования",C267="Неустойка заявлена",C267="Допработы без соглашения (спорно)"),N(E267),0)</f>
         <v/>
       </c>
       <c r="I267" s="6">
-        <f>IF(AND(B267="",C267="",D267="",E267="",F267=""),"",IF(OR(B267="",C267="",E267=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E267)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G267&lt;&gt;0,F267=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F267&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F267)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C267)*($E$5:$E$504=E267)*(($D$5:$D$504=D267)*(D267&lt;&gt;"")+($B$5:$B$504=B267)*(B267&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B267="",C267="",D267="",E267="",F267=""),"",IF(OR(B267="",C267="",E267=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E267)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H267&lt;&gt;0,F267=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G267&lt;&gt;0,F267=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F267&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F267)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C267)*($E$5:$E$504=E267)*(($D$5:$D$504=D267)*(D267&lt;&gt;"")+($B$5:$B$504=B267)*(B267&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J267" s="5">
@@ -7515,11 +7543,11 @@
         <v/>
       </c>
       <c r="H268" s="5">
-        <f>IF(OR(C268="Удержание",C268="Зачёт встречного требования",C268="Неустойка заявлена"),N(E268),0)</f>
+        <f>IF(OR(C268="Удержание",C268="Зачёт встречного требования",C268="Неустойка заявлена",C268="Допработы без соглашения (спорно)"),N(E268),0)</f>
         <v/>
       </c>
       <c r="I268" s="6">
-        <f>IF(AND(B268="",C268="",D268="",E268="",F268=""),"",IF(OR(B268="",C268="",E268=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E268)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G268&lt;&gt;0,F268=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F268&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F268)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C268)*($E$5:$E$504=E268)*(($D$5:$D$504=D268)*(D268&lt;&gt;"")+($B$5:$B$504=B268)*(B268&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B268="",C268="",D268="",E268="",F268=""),"",IF(OR(B268="",C268="",E268=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E268)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H268&lt;&gt;0,F268=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G268&lt;&gt;0,F268=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F268&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F268)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C268)*($E$5:$E$504=E268)*(($D$5:$D$504=D268)*(D268&lt;&gt;"")+($B$5:$B$504=B268)*(B268&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J268" s="5">
@@ -7541,11 +7569,11 @@
         <v/>
       </c>
       <c r="H269" s="5">
-        <f>IF(OR(C269="Удержание",C269="Зачёт встречного требования",C269="Неустойка заявлена"),N(E269),0)</f>
+        <f>IF(OR(C269="Удержание",C269="Зачёт встречного требования",C269="Неустойка заявлена",C269="Допработы без соглашения (спорно)"),N(E269),0)</f>
         <v/>
       </c>
       <c r="I269" s="6">
-        <f>IF(AND(B269="",C269="",D269="",E269="",F269=""),"",IF(OR(B269="",C269="",E269=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E269)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G269&lt;&gt;0,F269=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F269&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F269)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C269)*($E$5:$E$504=E269)*(($D$5:$D$504=D269)*(D269&lt;&gt;"")+($B$5:$B$504=B269)*(B269&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B269="",C269="",D269="",E269="",F269=""),"",IF(OR(B269="",C269="",E269=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E269)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H269&lt;&gt;0,F269=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G269&lt;&gt;0,F269=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F269&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F269)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C269)*($E$5:$E$504=E269)*(($D$5:$D$504=D269)*(D269&lt;&gt;"")+($B$5:$B$504=B269)*(B269&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J269" s="5">
@@ -7567,11 +7595,11 @@
         <v/>
       </c>
       <c r="H270" s="5">
-        <f>IF(OR(C270="Удержание",C270="Зачёт встречного требования",C270="Неустойка заявлена"),N(E270),0)</f>
+        <f>IF(OR(C270="Удержание",C270="Зачёт встречного требования",C270="Неустойка заявлена",C270="Допработы без соглашения (спорно)"),N(E270),0)</f>
         <v/>
       </c>
       <c r="I270" s="6">
-        <f>IF(AND(B270="",C270="",D270="",E270="",F270=""),"",IF(OR(B270="",C270="",E270=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E270)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G270&lt;&gt;0,F270=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F270&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F270)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C270)*($E$5:$E$504=E270)*(($D$5:$D$504=D270)*(D270&lt;&gt;"")+($B$5:$B$504=B270)*(B270&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B270="",C270="",D270="",E270="",F270=""),"",IF(OR(B270="",C270="",E270=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E270)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H270&lt;&gt;0,F270=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G270&lt;&gt;0,F270=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F270&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F270)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C270)*($E$5:$E$504=E270)*(($D$5:$D$504=D270)*(D270&lt;&gt;"")+($B$5:$B$504=B270)*(B270&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J270" s="5">
@@ -7593,11 +7621,11 @@
         <v/>
       </c>
       <c r="H271" s="5">
-        <f>IF(OR(C271="Удержание",C271="Зачёт встречного требования",C271="Неустойка заявлена"),N(E271),0)</f>
+        <f>IF(OR(C271="Удержание",C271="Зачёт встречного требования",C271="Неустойка заявлена",C271="Допработы без соглашения (спорно)"),N(E271),0)</f>
         <v/>
       </c>
       <c r="I271" s="6">
-        <f>IF(AND(B271="",C271="",D271="",E271="",F271=""),"",IF(OR(B271="",C271="",E271=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E271)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G271&lt;&gt;0,F271=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F271&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F271)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C271)*($E$5:$E$504=E271)*(($D$5:$D$504=D271)*(D271&lt;&gt;"")+($B$5:$B$504=B271)*(B271&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B271="",C271="",D271="",E271="",F271=""),"",IF(OR(B271="",C271="",E271=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E271)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H271&lt;&gt;0,F271=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G271&lt;&gt;0,F271=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F271&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F271)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C271)*($E$5:$E$504=E271)*(($D$5:$D$504=D271)*(D271&lt;&gt;"")+($B$5:$B$504=B271)*(B271&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J271" s="5">
@@ -7619,11 +7647,11 @@
         <v/>
       </c>
       <c r="H272" s="5">
-        <f>IF(OR(C272="Удержание",C272="Зачёт встречного требования",C272="Неустойка заявлена"),N(E272),0)</f>
+        <f>IF(OR(C272="Удержание",C272="Зачёт встречного требования",C272="Неустойка заявлена",C272="Допработы без соглашения (спорно)"),N(E272),0)</f>
         <v/>
       </c>
       <c r="I272" s="6">
-        <f>IF(AND(B272="",C272="",D272="",E272="",F272=""),"",IF(OR(B272="",C272="",E272=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E272)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G272&lt;&gt;0,F272=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F272&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F272)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C272)*($E$5:$E$504=E272)*(($D$5:$D$504=D272)*(D272&lt;&gt;"")+($B$5:$B$504=B272)*(B272&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B272="",C272="",D272="",E272="",F272=""),"",IF(OR(B272="",C272="",E272=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E272)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H272&lt;&gt;0,F272=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G272&lt;&gt;0,F272=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F272&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F272)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C272)*($E$5:$E$504=E272)*(($D$5:$D$504=D272)*(D272&lt;&gt;"")+($B$5:$B$504=B272)*(B272&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J272" s="5">
@@ -7645,11 +7673,11 @@
         <v/>
       </c>
       <c r="H273" s="5">
-        <f>IF(OR(C273="Удержание",C273="Зачёт встречного требования",C273="Неустойка заявлена"),N(E273),0)</f>
+        <f>IF(OR(C273="Удержание",C273="Зачёт встречного требования",C273="Неустойка заявлена",C273="Допработы без соглашения (спорно)"),N(E273),0)</f>
         <v/>
       </c>
       <c r="I273" s="6">
-        <f>IF(AND(B273="",C273="",D273="",E273="",F273=""),"",IF(OR(B273="",C273="",E273=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E273)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G273&lt;&gt;0,F273=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F273&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F273)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C273)*($E$5:$E$504=E273)*(($D$5:$D$504=D273)*(D273&lt;&gt;"")+($B$5:$B$504=B273)*(B273&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B273="",C273="",D273="",E273="",F273=""),"",IF(OR(B273="",C273="",E273=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E273)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H273&lt;&gt;0,F273=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G273&lt;&gt;0,F273=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F273&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F273)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C273)*($E$5:$E$504=E273)*(($D$5:$D$504=D273)*(D273&lt;&gt;"")+($B$5:$B$504=B273)*(B273&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J273" s="5">
@@ -7671,11 +7699,11 @@
         <v/>
       </c>
       <c r="H274" s="5">
-        <f>IF(OR(C274="Удержание",C274="Зачёт встречного требования",C274="Неустойка заявлена"),N(E274),0)</f>
+        <f>IF(OR(C274="Удержание",C274="Зачёт встречного требования",C274="Неустойка заявлена",C274="Допработы без соглашения (спорно)"),N(E274),0)</f>
         <v/>
       </c>
       <c r="I274" s="6">
-        <f>IF(AND(B274="",C274="",D274="",E274="",F274=""),"",IF(OR(B274="",C274="",E274=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E274)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G274&lt;&gt;0,F274=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F274&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F274)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C274)*($E$5:$E$504=E274)*(($D$5:$D$504=D274)*(D274&lt;&gt;"")+($B$5:$B$504=B274)*(B274&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B274="",C274="",D274="",E274="",F274=""),"",IF(OR(B274="",C274="",E274=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E274)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H274&lt;&gt;0,F274=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G274&lt;&gt;0,F274=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F274&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F274)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C274)*($E$5:$E$504=E274)*(($D$5:$D$504=D274)*(D274&lt;&gt;"")+($B$5:$B$504=B274)*(B274&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J274" s="5">
@@ -7697,11 +7725,11 @@
         <v/>
       </c>
       <c r="H275" s="5">
-        <f>IF(OR(C275="Удержание",C275="Зачёт встречного требования",C275="Неустойка заявлена"),N(E275),0)</f>
+        <f>IF(OR(C275="Удержание",C275="Зачёт встречного требования",C275="Неустойка заявлена",C275="Допработы без соглашения (спорно)"),N(E275),0)</f>
         <v/>
       </c>
       <c r="I275" s="6">
-        <f>IF(AND(B275="",C275="",D275="",E275="",F275=""),"",IF(OR(B275="",C275="",E275=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E275)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G275&lt;&gt;0,F275=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F275&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F275)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C275)*($E$5:$E$504=E275)*(($D$5:$D$504=D275)*(D275&lt;&gt;"")+($B$5:$B$504=B275)*(B275&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B275="",C275="",D275="",E275="",F275=""),"",IF(OR(B275="",C275="",E275=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E275)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H275&lt;&gt;0,F275=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G275&lt;&gt;0,F275=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F275&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F275)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C275)*($E$5:$E$504=E275)*(($D$5:$D$504=D275)*(D275&lt;&gt;"")+($B$5:$B$504=B275)*(B275&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J275" s="5">
@@ -7723,11 +7751,11 @@
         <v/>
       </c>
       <c r="H276" s="5">
-        <f>IF(OR(C276="Удержание",C276="Зачёт встречного требования",C276="Неустойка заявлена"),N(E276),0)</f>
+        <f>IF(OR(C276="Удержание",C276="Зачёт встречного требования",C276="Неустойка заявлена",C276="Допработы без соглашения (спорно)"),N(E276),0)</f>
         <v/>
       </c>
       <c r="I276" s="6">
-        <f>IF(AND(B276="",C276="",D276="",E276="",F276=""),"",IF(OR(B276="",C276="",E276=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E276)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G276&lt;&gt;0,F276=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F276&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F276)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C276)*($E$5:$E$504=E276)*(($D$5:$D$504=D276)*(D276&lt;&gt;"")+($B$5:$B$504=B276)*(B276&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B276="",C276="",D276="",E276="",F276=""),"",IF(OR(B276="",C276="",E276=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E276)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H276&lt;&gt;0,F276=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G276&lt;&gt;0,F276=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F276&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F276)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C276)*($E$5:$E$504=E276)*(($D$5:$D$504=D276)*(D276&lt;&gt;"")+($B$5:$B$504=B276)*(B276&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J276" s="5">
@@ -7749,11 +7777,11 @@
         <v/>
       </c>
       <c r="H277" s="5">
-        <f>IF(OR(C277="Удержание",C277="Зачёт встречного требования",C277="Неустойка заявлена"),N(E277),0)</f>
+        <f>IF(OR(C277="Удержание",C277="Зачёт встречного требования",C277="Неустойка заявлена",C277="Допработы без соглашения (спорно)"),N(E277),0)</f>
         <v/>
       </c>
       <c r="I277" s="6">
-        <f>IF(AND(B277="",C277="",D277="",E277="",F277=""),"",IF(OR(B277="",C277="",E277=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E277)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G277&lt;&gt;0,F277=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F277&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F277)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C277)*($E$5:$E$504=E277)*(($D$5:$D$504=D277)*(D277&lt;&gt;"")+($B$5:$B$504=B277)*(B277&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B277="",C277="",D277="",E277="",F277=""),"",IF(OR(B277="",C277="",E277=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E277)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H277&lt;&gt;0,F277=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G277&lt;&gt;0,F277=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F277&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F277)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C277)*($E$5:$E$504=E277)*(($D$5:$D$504=D277)*(D277&lt;&gt;"")+($B$5:$B$504=B277)*(B277&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J277" s="5">
@@ -7775,11 +7803,11 @@
         <v/>
       </c>
       <c r="H278" s="5">
-        <f>IF(OR(C278="Удержание",C278="Зачёт встречного требования",C278="Неустойка заявлена"),N(E278),0)</f>
+        <f>IF(OR(C278="Удержание",C278="Зачёт встречного требования",C278="Неустойка заявлена",C278="Допработы без соглашения (спорно)"),N(E278),0)</f>
         <v/>
       </c>
       <c r="I278" s="6">
-        <f>IF(AND(B278="",C278="",D278="",E278="",F278=""),"",IF(OR(B278="",C278="",E278=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E278)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G278&lt;&gt;0,F278=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F278&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F278)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C278)*($E$5:$E$504=E278)*(($D$5:$D$504=D278)*(D278&lt;&gt;"")+($B$5:$B$504=B278)*(B278&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B278="",C278="",D278="",E278="",F278=""),"",IF(OR(B278="",C278="",E278=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E278)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H278&lt;&gt;0,F278=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G278&lt;&gt;0,F278=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F278&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F278)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C278)*($E$5:$E$504=E278)*(($D$5:$D$504=D278)*(D278&lt;&gt;"")+($B$5:$B$504=B278)*(B278&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J278" s="5">
@@ -7801,11 +7829,11 @@
         <v/>
       </c>
       <c r="H279" s="5">
-        <f>IF(OR(C279="Удержание",C279="Зачёт встречного требования",C279="Неустойка заявлена"),N(E279),0)</f>
+        <f>IF(OR(C279="Удержание",C279="Зачёт встречного требования",C279="Неустойка заявлена",C279="Допработы без соглашения (спорно)"),N(E279),0)</f>
         <v/>
       </c>
       <c r="I279" s="6">
-        <f>IF(AND(B279="",C279="",D279="",E279="",F279=""),"",IF(OR(B279="",C279="",E279=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E279)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G279&lt;&gt;0,F279=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F279&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F279)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C279)*($E$5:$E$504=E279)*(($D$5:$D$504=D279)*(D279&lt;&gt;"")+($B$5:$B$504=B279)*(B279&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B279="",C279="",D279="",E279="",F279=""),"",IF(OR(B279="",C279="",E279=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E279)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H279&lt;&gt;0,F279=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G279&lt;&gt;0,F279=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F279&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F279)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C279)*($E$5:$E$504=E279)*(($D$5:$D$504=D279)*(D279&lt;&gt;"")+($B$5:$B$504=B279)*(B279&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J279" s="5">
@@ -7827,11 +7855,11 @@
         <v/>
       </c>
       <c r="H280" s="5">
-        <f>IF(OR(C280="Удержание",C280="Зачёт встречного требования",C280="Неустойка заявлена"),N(E280),0)</f>
+        <f>IF(OR(C280="Удержание",C280="Зачёт встречного требования",C280="Неустойка заявлена",C280="Допработы без соглашения (спорно)"),N(E280),0)</f>
         <v/>
       </c>
       <c r="I280" s="6">
-        <f>IF(AND(B280="",C280="",D280="",E280="",F280=""),"",IF(OR(B280="",C280="",E280=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E280)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G280&lt;&gt;0,F280=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F280&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F280)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C280)*($E$5:$E$504=E280)*(($D$5:$D$504=D280)*(D280&lt;&gt;"")+($B$5:$B$504=B280)*(B280&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B280="",C280="",D280="",E280="",F280=""),"",IF(OR(B280="",C280="",E280=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E280)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H280&lt;&gt;0,F280=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G280&lt;&gt;0,F280=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F280&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F280)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C280)*($E$5:$E$504=E280)*(($D$5:$D$504=D280)*(D280&lt;&gt;"")+($B$5:$B$504=B280)*(B280&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J280" s="5">
@@ -7853,11 +7881,11 @@
         <v/>
       </c>
       <c r="H281" s="5">
-        <f>IF(OR(C281="Удержание",C281="Зачёт встречного требования",C281="Неустойка заявлена"),N(E281),0)</f>
+        <f>IF(OR(C281="Удержание",C281="Зачёт встречного требования",C281="Неустойка заявлена",C281="Допработы без соглашения (спорно)"),N(E281),0)</f>
         <v/>
       </c>
       <c r="I281" s="6">
-        <f>IF(AND(B281="",C281="",D281="",E281="",F281=""),"",IF(OR(B281="",C281="",E281=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E281)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G281&lt;&gt;0,F281=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F281&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F281)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C281)*($E$5:$E$504=E281)*(($D$5:$D$504=D281)*(D281&lt;&gt;"")+($B$5:$B$504=B281)*(B281&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B281="",C281="",D281="",E281="",F281=""),"",IF(OR(B281="",C281="",E281=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E281)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H281&lt;&gt;0,F281=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G281&lt;&gt;0,F281=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F281&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F281)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C281)*($E$5:$E$504=E281)*(($D$5:$D$504=D281)*(D281&lt;&gt;"")+($B$5:$B$504=B281)*(B281&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J281" s="5">
@@ -7879,11 +7907,11 @@
         <v/>
       </c>
       <c r="H282" s="5">
-        <f>IF(OR(C282="Удержание",C282="Зачёт встречного требования",C282="Неустойка заявлена"),N(E282),0)</f>
+        <f>IF(OR(C282="Удержание",C282="Зачёт встречного требования",C282="Неустойка заявлена",C282="Допработы без соглашения (спорно)"),N(E282),0)</f>
         <v/>
       </c>
       <c r="I282" s="6">
-        <f>IF(AND(B282="",C282="",D282="",E282="",F282=""),"",IF(OR(B282="",C282="",E282=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E282)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G282&lt;&gt;0,F282=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F282&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F282)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C282)*($E$5:$E$504=E282)*(($D$5:$D$504=D282)*(D282&lt;&gt;"")+($B$5:$B$504=B282)*(B282&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B282="",C282="",D282="",E282="",F282=""),"",IF(OR(B282="",C282="",E282=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E282)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H282&lt;&gt;0,F282=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G282&lt;&gt;0,F282=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F282&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F282)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C282)*($E$5:$E$504=E282)*(($D$5:$D$504=D282)*(D282&lt;&gt;"")+($B$5:$B$504=B282)*(B282&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J282" s="5">
@@ -7905,11 +7933,11 @@
         <v/>
       </c>
       <c r="H283" s="5">
-        <f>IF(OR(C283="Удержание",C283="Зачёт встречного требования",C283="Неустойка заявлена"),N(E283),0)</f>
+        <f>IF(OR(C283="Удержание",C283="Зачёт встречного требования",C283="Неустойка заявлена",C283="Допработы без соглашения (спорно)"),N(E283),0)</f>
         <v/>
       </c>
       <c r="I283" s="6">
-        <f>IF(AND(B283="",C283="",D283="",E283="",F283=""),"",IF(OR(B283="",C283="",E283=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E283)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G283&lt;&gt;0,F283=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F283&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F283)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C283)*($E$5:$E$504=E283)*(($D$5:$D$504=D283)*(D283&lt;&gt;"")+($B$5:$B$504=B283)*(B283&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B283="",C283="",D283="",E283="",F283=""),"",IF(OR(B283="",C283="",E283=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E283)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H283&lt;&gt;0,F283=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G283&lt;&gt;0,F283=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F283&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F283)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C283)*($E$5:$E$504=E283)*(($D$5:$D$504=D283)*(D283&lt;&gt;"")+($B$5:$B$504=B283)*(B283&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J283" s="5">
@@ -7931,11 +7959,11 @@
         <v/>
       </c>
       <c r="H284" s="5">
-        <f>IF(OR(C284="Удержание",C284="Зачёт встречного требования",C284="Неустойка заявлена"),N(E284),0)</f>
+        <f>IF(OR(C284="Удержание",C284="Зачёт встречного требования",C284="Неустойка заявлена",C284="Допработы без соглашения (спорно)"),N(E284),0)</f>
         <v/>
       </c>
       <c r="I284" s="6">
-        <f>IF(AND(B284="",C284="",D284="",E284="",F284=""),"",IF(OR(B284="",C284="",E284=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E284)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G284&lt;&gt;0,F284=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F284&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F284)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C284)*($E$5:$E$504=E284)*(($D$5:$D$504=D284)*(D284&lt;&gt;"")+($B$5:$B$504=B284)*(B284&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B284="",C284="",D284="",E284="",F284=""),"",IF(OR(B284="",C284="",E284=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E284)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H284&lt;&gt;0,F284=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G284&lt;&gt;0,F284=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F284&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F284)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C284)*($E$5:$E$504=E284)*(($D$5:$D$504=D284)*(D284&lt;&gt;"")+($B$5:$B$504=B284)*(B284&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J284" s="5">
@@ -7957,11 +7985,11 @@
         <v/>
       </c>
       <c r="H285" s="5">
-        <f>IF(OR(C285="Удержание",C285="Зачёт встречного требования",C285="Неустойка заявлена"),N(E285),0)</f>
+        <f>IF(OR(C285="Удержание",C285="Зачёт встречного требования",C285="Неустойка заявлена",C285="Допработы без соглашения (спорно)"),N(E285),0)</f>
         <v/>
       </c>
       <c r="I285" s="6">
-        <f>IF(AND(B285="",C285="",D285="",E285="",F285=""),"",IF(OR(B285="",C285="",E285=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E285)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G285&lt;&gt;0,F285=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F285&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F285)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C285)*($E$5:$E$504=E285)*(($D$5:$D$504=D285)*(D285&lt;&gt;"")+($B$5:$B$504=B285)*(B285&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B285="",C285="",D285="",E285="",F285=""),"",IF(OR(B285="",C285="",E285=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E285)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H285&lt;&gt;0,F285=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G285&lt;&gt;0,F285=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F285&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F285)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C285)*($E$5:$E$504=E285)*(($D$5:$D$504=D285)*(D285&lt;&gt;"")+($B$5:$B$504=B285)*(B285&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J285" s="5">
@@ -7983,11 +8011,11 @@
         <v/>
       </c>
       <c r="H286" s="5">
-        <f>IF(OR(C286="Удержание",C286="Зачёт встречного требования",C286="Неустойка заявлена"),N(E286),0)</f>
+        <f>IF(OR(C286="Удержание",C286="Зачёт встречного требования",C286="Неустойка заявлена",C286="Допработы без соглашения (спорно)"),N(E286),0)</f>
         <v/>
       </c>
       <c r="I286" s="6">
-        <f>IF(AND(B286="",C286="",D286="",E286="",F286=""),"",IF(OR(B286="",C286="",E286=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E286)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G286&lt;&gt;0,F286=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F286&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F286)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C286)*($E$5:$E$504=E286)*(($D$5:$D$504=D286)*(D286&lt;&gt;"")+($B$5:$B$504=B286)*(B286&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B286="",C286="",D286="",E286="",F286=""),"",IF(OR(B286="",C286="",E286=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E286)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H286&lt;&gt;0,F286=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G286&lt;&gt;0,F286=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F286&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F286)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C286)*($E$5:$E$504=E286)*(($D$5:$D$504=D286)*(D286&lt;&gt;"")+($B$5:$B$504=B286)*(B286&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J286" s="5">
@@ -8009,11 +8037,11 @@
         <v/>
       </c>
       <c r="H287" s="5">
-        <f>IF(OR(C287="Удержание",C287="Зачёт встречного требования",C287="Неустойка заявлена"),N(E287),0)</f>
+        <f>IF(OR(C287="Удержание",C287="Зачёт встречного требования",C287="Неустойка заявлена",C287="Допработы без соглашения (спорно)"),N(E287),0)</f>
         <v/>
       </c>
       <c r="I287" s="6">
-        <f>IF(AND(B287="",C287="",D287="",E287="",F287=""),"",IF(OR(B287="",C287="",E287=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E287)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G287&lt;&gt;0,F287=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F287&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F287)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C287)*($E$5:$E$504=E287)*(($D$5:$D$504=D287)*(D287&lt;&gt;"")+($B$5:$B$504=B287)*(B287&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B287="",C287="",D287="",E287="",F287=""),"",IF(OR(B287="",C287="",E287=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E287)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H287&lt;&gt;0,F287=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G287&lt;&gt;0,F287=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F287&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F287)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C287)*($E$5:$E$504=E287)*(($D$5:$D$504=D287)*(D287&lt;&gt;"")+($B$5:$B$504=B287)*(B287&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J287" s="5">
@@ -8035,11 +8063,11 @@
         <v/>
       </c>
       <c r="H288" s="5">
-        <f>IF(OR(C288="Удержание",C288="Зачёт встречного требования",C288="Неустойка заявлена"),N(E288),0)</f>
+        <f>IF(OR(C288="Удержание",C288="Зачёт встречного требования",C288="Неустойка заявлена",C288="Допработы без соглашения (спорно)"),N(E288),0)</f>
         <v/>
       </c>
       <c r="I288" s="6">
-        <f>IF(AND(B288="",C288="",D288="",E288="",F288=""),"",IF(OR(B288="",C288="",E288=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E288)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G288&lt;&gt;0,F288=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F288&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F288)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C288)*($E$5:$E$504=E288)*(($D$5:$D$504=D288)*(D288&lt;&gt;"")+($B$5:$B$504=B288)*(B288&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B288="",C288="",D288="",E288="",F288=""),"",IF(OR(B288="",C288="",E288=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E288)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H288&lt;&gt;0,F288=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G288&lt;&gt;0,F288=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F288&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F288)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C288)*($E$5:$E$504=E288)*(($D$5:$D$504=D288)*(D288&lt;&gt;"")+($B$5:$B$504=B288)*(B288&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J288" s="5">
@@ -8061,11 +8089,11 @@
         <v/>
       </c>
       <c r="H289" s="5">
-        <f>IF(OR(C289="Удержание",C289="Зачёт встречного требования",C289="Неустойка заявлена"),N(E289),0)</f>
+        <f>IF(OR(C289="Удержание",C289="Зачёт встречного требования",C289="Неустойка заявлена",C289="Допработы без соглашения (спорно)"),N(E289),0)</f>
         <v/>
       </c>
       <c r="I289" s="6">
-        <f>IF(AND(B289="",C289="",D289="",E289="",F289=""),"",IF(OR(B289="",C289="",E289=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E289)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G289&lt;&gt;0,F289=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F289&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F289)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C289)*($E$5:$E$504=E289)*(($D$5:$D$504=D289)*(D289&lt;&gt;"")+($B$5:$B$504=B289)*(B289&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B289="",C289="",D289="",E289="",F289=""),"",IF(OR(B289="",C289="",E289=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E289)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H289&lt;&gt;0,F289=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G289&lt;&gt;0,F289=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F289&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F289)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C289)*($E$5:$E$504=E289)*(($D$5:$D$504=D289)*(D289&lt;&gt;"")+($B$5:$B$504=B289)*(B289&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J289" s="5">
@@ -8087,11 +8115,11 @@
         <v/>
       </c>
       <c r="H290" s="5">
-        <f>IF(OR(C290="Удержание",C290="Зачёт встречного требования",C290="Неустойка заявлена"),N(E290),0)</f>
+        <f>IF(OR(C290="Удержание",C290="Зачёт встречного требования",C290="Неустойка заявлена",C290="Допработы без соглашения (спорно)"),N(E290),0)</f>
         <v/>
       </c>
       <c r="I290" s="6">
-        <f>IF(AND(B290="",C290="",D290="",E290="",F290=""),"",IF(OR(B290="",C290="",E290=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E290)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G290&lt;&gt;0,F290=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F290&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F290)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C290)*($E$5:$E$504=E290)*(($D$5:$D$504=D290)*(D290&lt;&gt;"")+($B$5:$B$504=B290)*(B290&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B290="",C290="",D290="",E290="",F290=""),"",IF(OR(B290="",C290="",E290=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E290)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H290&lt;&gt;0,F290=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G290&lt;&gt;0,F290=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F290&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F290)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C290)*($E$5:$E$504=E290)*(($D$5:$D$504=D290)*(D290&lt;&gt;"")+($B$5:$B$504=B290)*(B290&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J290" s="5">
@@ -8113,11 +8141,11 @@
         <v/>
       </c>
       <c r="H291" s="5">
-        <f>IF(OR(C291="Удержание",C291="Зачёт встречного требования",C291="Неустойка заявлена"),N(E291),0)</f>
+        <f>IF(OR(C291="Удержание",C291="Зачёт встречного требования",C291="Неустойка заявлена",C291="Допработы без соглашения (спорно)"),N(E291),0)</f>
         <v/>
       </c>
       <c r="I291" s="6">
-        <f>IF(AND(B291="",C291="",D291="",E291="",F291=""),"",IF(OR(B291="",C291="",E291=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E291)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G291&lt;&gt;0,F291=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F291&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F291)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C291)*($E$5:$E$504=E291)*(($D$5:$D$504=D291)*(D291&lt;&gt;"")+($B$5:$B$504=B291)*(B291&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B291="",C291="",D291="",E291="",F291=""),"",IF(OR(B291="",C291="",E291=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E291)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H291&lt;&gt;0,F291=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G291&lt;&gt;0,F291=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F291&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F291)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C291)*($E$5:$E$504=E291)*(($D$5:$D$504=D291)*(D291&lt;&gt;"")+($B$5:$B$504=B291)*(B291&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J291" s="5">
@@ -8139,11 +8167,11 @@
         <v/>
       </c>
       <c r="H292" s="5">
-        <f>IF(OR(C292="Удержание",C292="Зачёт встречного требования",C292="Неустойка заявлена"),N(E292),0)</f>
+        <f>IF(OR(C292="Удержание",C292="Зачёт встречного требования",C292="Неустойка заявлена",C292="Допработы без соглашения (спорно)"),N(E292),0)</f>
         <v/>
       </c>
       <c r="I292" s="6">
-        <f>IF(AND(B292="",C292="",D292="",E292="",F292=""),"",IF(OR(B292="",C292="",E292=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E292)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G292&lt;&gt;0,F292=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F292&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F292)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C292)*($E$5:$E$504=E292)*(($D$5:$D$504=D292)*(D292&lt;&gt;"")+($B$5:$B$504=B292)*(B292&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B292="",C292="",D292="",E292="",F292=""),"",IF(OR(B292="",C292="",E292=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E292)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H292&lt;&gt;0,F292=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G292&lt;&gt;0,F292=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F292&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F292)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C292)*($E$5:$E$504=E292)*(($D$5:$D$504=D292)*(D292&lt;&gt;"")+($B$5:$B$504=B292)*(B292&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J292" s="5">
@@ -8165,11 +8193,11 @@
         <v/>
       </c>
       <c r="H293" s="5">
-        <f>IF(OR(C293="Удержание",C293="Зачёт встречного требования",C293="Неустойка заявлена"),N(E293),0)</f>
+        <f>IF(OR(C293="Удержание",C293="Зачёт встречного требования",C293="Неустойка заявлена",C293="Допработы без соглашения (спорно)"),N(E293),0)</f>
         <v/>
       </c>
       <c r="I293" s="6">
-        <f>IF(AND(B293="",C293="",D293="",E293="",F293=""),"",IF(OR(B293="",C293="",E293=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E293)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G293&lt;&gt;0,F293=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F293&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F293)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C293)*($E$5:$E$504=E293)*(($D$5:$D$504=D293)*(D293&lt;&gt;"")+($B$5:$B$504=B293)*(B293&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B293="",C293="",D293="",E293="",F293=""),"",IF(OR(B293="",C293="",E293=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E293)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H293&lt;&gt;0,F293=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G293&lt;&gt;0,F293=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F293&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F293)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C293)*($E$5:$E$504=E293)*(($D$5:$D$504=D293)*(D293&lt;&gt;"")+($B$5:$B$504=B293)*(B293&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J293" s="5">
@@ -8191,11 +8219,11 @@
         <v/>
       </c>
       <c r="H294" s="5">
-        <f>IF(OR(C294="Удержание",C294="Зачёт встречного требования",C294="Неустойка заявлена"),N(E294),0)</f>
+        <f>IF(OR(C294="Удержание",C294="Зачёт встречного требования",C294="Неустойка заявлена",C294="Допработы без соглашения (спорно)"),N(E294),0)</f>
         <v/>
       </c>
       <c r="I294" s="6">
-        <f>IF(AND(B294="",C294="",D294="",E294="",F294=""),"",IF(OR(B294="",C294="",E294=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E294)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G294&lt;&gt;0,F294=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F294&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F294)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C294)*($E$5:$E$504=E294)*(($D$5:$D$504=D294)*(D294&lt;&gt;"")+($B$5:$B$504=B294)*(B294&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B294="",C294="",D294="",E294="",F294=""),"",IF(OR(B294="",C294="",E294=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E294)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H294&lt;&gt;0,F294=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G294&lt;&gt;0,F294=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F294&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F294)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C294)*($E$5:$E$504=E294)*(($D$5:$D$504=D294)*(D294&lt;&gt;"")+($B$5:$B$504=B294)*(B294&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J294" s="5">
@@ -8217,11 +8245,11 @@
         <v/>
       </c>
       <c r="H295" s="5">
-        <f>IF(OR(C295="Удержание",C295="Зачёт встречного требования",C295="Неустойка заявлена"),N(E295),0)</f>
+        <f>IF(OR(C295="Удержание",C295="Зачёт встречного требования",C295="Неустойка заявлена",C295="Допработы без соглашения (спорно)"),N(E295),0)</f>
         <v/>
       </c>
       <c r="I295" s="6">
-        <f>IF(AND(B295="",C295="",D295="",E295="",F295=""),"",IF(OR(B295="",C295="",E295=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E295)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G295&lt;&gt;0,F295=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F295&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F295)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C295)*($E$5:$E$504=E295)*(($D$5:$D$504=D295)*(D295&lt;&gt;"")+($B$5:$B$504=B295)*(B295&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B295="",C295="",D295="",E295="",F295=""),"",IF(OR(B295="",C295="",E295=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E295)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H295&lt;&gt;0,F295=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G295&lt;&gt;0,F295=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F295&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F295)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C295)*($E$5:$E$504=E295)*(($D$5:$D$504=D295)*(D295&lt;&gt;"")+($B$5:$B$504=B295)*(B295&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J295" s="5">
@@ -8243,11 +8271,11 @@
         <v/>
       </c>
       <c r="H296" s="5">
-        <f>IF(OR(C296="Удержание",C296="Зачёт встречного требования",C296="Неустойка заявлена"),N(E296),0)</f>
+        <f>IF(OR(C296="Удержание",C296="Зачёт встречного требования",C296="Неустойка заявлена",C296="Допработы без соглашения (спорно)"),N(E296),0)</f>
         <v/>
       </c>
       <c r="I296" s="6">
-        <f>IF(AND(B296="",C296="",D296="",E296="",F296=""),"",IF(OR(B296="",C296="",E296=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E296)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G296&lt;&gt;0,F296=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F296&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F296)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C296)*($E$5:$E$504=E296)*(($D$5:$D$504=D296)*(D296&lt;&gt;"")+($B$5:$B$504=B296)*(B296&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B296="",C296="",D296="",E296="",F296=""),"",IF(OR(B296="",C296="",E296=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E296)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H296&lt;&gt;0,F296=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G296&lt;&gt;0,F296=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F296&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F296)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C296)*($E$5:$E$504=E296)*(($D$5:$D$504=D296)*(D296&lt;&gt;"")+($B$5:$B$504=B296)*(B296&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J296" s="5">
@@ -8269,11 +8297,11 @@
         <v/>
       </c>
       <c r="H297" s="5">
-        <f>IF(OR(C297="Удержание",C297="Зачёт встречного требования",C297="Неустойка заявлена"),N(E297),0)</f>
+        <f>IF(OR(C297="Удержание",C297="Зачёт встречного требования",C297="Неустойка заявлена",C297="Допработы без соглашения (спорно)"),N(E297),0)</f>
         <v/>
       </c>
       <c r="I297" s="6">
-        <f>IF(AND(B297="",C297="",D297="",E297="",F297=""),"",IF(OR(B297="",C297="",E297=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E297)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G297&lt;&gt;0,F297=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F297&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F297)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C297)*($E$5:$E$504=E297)*(($D$5:$D$504=D297)*(D297&lt;&gt;"")+($B$5:$B$504=B297)*(B297&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B297="",C297="",D297="",E297="",F297=""),"",IF(OR(B297="",C297="",E297=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E297)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H297&lt;&gt;0,F297=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G297&lt;&gt;0,F297=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F297&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F297)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C297)*($E$5:$E$504=E297)*(($D$5:$D$504=D297)*(D297&lt;&gt;"")+($B$5:$B$504=B297)*(B297&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J297" s="5">
@@ -8295,11 +8323,11 @@
         <v/>
       </c>
       <c r="H298" s="5">
-        <f>IF(OR(C298="Удержание",C298="Зачёт встречного требования",C298="Неустойка заявлена"),N(E298),0)</f>
+        <f>IF(OR(C298="Удержание",C298="Зачёт встречного требования",C298="Неустойка заявлена",C298="Допработы без соглашения (спорно)"),N(E298),0)</f>
         <v/>
       </c>
       <c r="I298" s="6">
-        <f>IF(AND(B298="",C298="",D298="",E298="",F298=""),"",IF(OR(B298="",C298="",E298=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E298)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G298&lt;&gt;0,F298=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F298&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F298)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C298)*($E$5:$E$504=E298)*(($D$5:$D$504=D298)*(D298&lt;&gt;"")+($B$5:$B$504=B298)*(B298&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B298="",C298="",D298="",E298="",F298=""),"",IF(OR(B298="",C298="",E298=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E298)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H298&lt;&gt;0,F298=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G298&lt;&gt;0,F298=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F298&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F298)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C298)*($E$5:$E$504=E298)*(($D$5:$D$504=D298)*(D298&lt;&gt;"")+($B$5:$B$504=B298)*(B298&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J298" s="5">
@@ -8321,11 +8349,11 @@
         <v/>
       </c>
       <c r="H299" s="5">
-        <f>IF(OR(C299="Удержание",C299="Зачёт встречного требования",C299="Неустойка заявлена"),N(E299),0)</f>
+        <f>IF(OR(C299="Удержание",C299="Зачёт встречного требования",C299="Неустойка заявлена",C299="Допработы без соглашения (спорно)"),N(E299),0)</f>
         <v/>
       </c>
       <c r="I299" s="6">
-        <f>IF(AND(B299="",C299="",D299="",E299="",F299=""),"",IF(OR(B299="",C299="",E299=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E299)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G299&lt;&gt;0,F299=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F299&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F299)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C299)*($E$5:$E$504=E299)*(($D$5:$D$504=D299)*(D299&lt;&gt;"")+($B$5:$B$504=B299)*(B299&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B299="",C299="",D299="",E299="",F299=""),"",IF(OR(B299="",C299="",E299=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E299)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H299&lt;&gt;0,F299=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G299&lt;&gt;0,F299=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F299&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F299)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C299)*($E$5:$E$504=E299)*(($D$5:$D$504=D299)*(D299&lt;&gt;"")+($B$5:$B$504=B299)*(B299&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J299" s="5">
@@ -8347,11 +8375,11 @@
         <v/>
       </c>
       <c r="H300" s="5">
-        <f>IF(OR(C300="Удержание",C300="Зачёт встречного требования",C300="Неустойка заявлена"),N(E300),0)</f>
+        <f>IF(OR(C300="Удержание",C300="Зачёт встречного требования",C300="Неустойка заявлена",C300="Допработы без соглашения (спорно)"),N(E300),0)</f>
         <v/>
       </c>
       <c r="I300" s="6">
-        <f>IF(AND(B300="",C300="",D300="",E300="",F300=""),"",IF(OR(B300="",C300="",E300=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E300)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G300&lt;&gt;0,F300=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F300&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F300)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C300)*($E$5:$E$504=E300)*(($D$5:$D$504=D300)*(D300&lt;&gt;"")+($B$5:$B$504=B300)*(B300&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B300="",C300="",D300="",E300="",F300=""),"",IF(OR(B300="",C300="",E300=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E300)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H300&lt;&gt;0,F300=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G300&lt;&gt;0,F300=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F300&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F300)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C300)*($E$5:$E$504=E300)*(($D$5:$D$504=D300)*(D300&lt;&gt;"")+($B$5:$B$504=B300)*(B300&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J300" s="5">
@@ -8373,11 +8401,11 @@
         <v/>
       </c>
       <c r="H301" s="5">
-        <f>IF(OR(C301="Удержание",C301="Зачёт встречного требования",C301="Неустойка заявлена"),N(E301),0)</f>
+        <f>IF(OR(C301="Удержание",C301="Зачёт встречного требования",C301="Неустойка заявлена",C301="Допработы без соглашения (спорно)"),N(E301),0)</f>
         <v/>
       </c>
       <c r="I301" s="6">
-        <f>IF(AND(B301="",C301="",D301="",E301="",F301=""),"",IF(OR(B301="",C301="",E301=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E301)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G301&lt;&gt;0,F301=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F301&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F301)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C301)*($E$5:$E$504=E301)*(($D$5:$D$504=D301)*(D301&lt;&gt;"")+($B$5:$B$504=B301)*(B301&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B301="",C301="",D301="",E301="",F301=""),"",IF(OR(B301="",C301="",E301=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E301)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H301&lt;&gt;0,F301=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G301&lt;&gt;0,F301=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F301&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F301)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C301)*($E$5:$E$504=E301)*(($D$5:$D$504=D301)*(D301&lt;&gt;"")+($B$5:$B$504=B301)*(B301&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J301" s="5">
@@ -8399,11 +8427,11 @@
         <v/>
       </c>
       <c r="H302" s="5">
-        <f>IF(OR(C302="Удержание",C302="Зачёт встречного требования",C302="Неустойка заявлена"),N(E302),0)</f>
+        <f>IF(OR(C302="Удержание",C302="Зачёт встречного требования",C302="Неустойка заявлена",C302="Допработы без соглашения (спорно)"),N(E302),0)</f>
         <v/>
       </c>
       <c r="I302" s="6">
-        <f>IF(AND(B302="",C302="",D302="",E302="",F302=""),"",IF(OR(B302="",C302="",E302=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E302)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G302&lt;&gt;0,F302=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F302&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F302)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C302)*($E$5:$E$504=E302)*(($D$5:$D$504=D302)*(D302&lt;&gt;"")+($B$5:$B$504=B302)*(B302&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B302="",C302="",D302="",E302="",F302=""),"",IF(OR(B302="",C302="",E302=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E302)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H302&lt;&gt;0,F302=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G302&lt;&gt;0,F302=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F302&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F302)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C302)*($E$5:$E$504=E302)*(($D$5:$D$504=D302)*(D302&lt;&gt;"")+($B$5:$B$504=B302)*(B302&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J302" s="5">
@@ -8425,11 +8453,11 @@
         <v/>
       </c>
       <c r="H303" s="5">
-        <f>IF(OR(C303="Удержание",C303="Зачёт встречного требования",C303="Неустойка заявлена"),N(E303),0)</f>
+        <f>IF(OR(C303="Удержание",C303="Зачёт встречного требования",C303="Неустойка заявлена",C303="Допработы без соглашения (спорно)"),N(E303),0)</f>
         <v/>
       </c>
       <c r="I303" s="6">
-        <f>IF(AND(B303="",C303="",D303="",E303="",F303=""),"",IF(OR(B303="",C303="",E303=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E303)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G303&lt;&gt;0,F303=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F303&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F303)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C303)*($E$5:$E$504=E303)*(($D$5:$D$504=D303)*(D303&lt;&gt;"")+($B$5:$B$504=B303)*(B303&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B303="",C303="",D303="",E303="",F303=""),"",IF(OR(B303="",C303="",E303=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E303)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H303&lt;&gt;0,F303=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G303&lt;&gt;0,F303=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F303&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F303)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C303)*($E$5:$E$504=E303)*(($D$5:$D$504=D303)*(D303&lt;&gt;"")+($B$5:$B$504=B303)*(B303&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J303" s="5">
@@ -8451,11 +8479,11 @@
         <v/>
       </c>
       <c r="H304" s="5">
-        <f>IF(OR(C304="Удержание",C304="Зачёт встречного требования",C304="Неустойка заявлена"),N(E304),0)</f>
+        <f>IF(OR(C304="Удержание",C304="Зачёт встречного требования",C304="Неустойка заявлена",C304="Допработы без соглашения (спорно)"),N(E304),0)</f>
         <v/>
       </c>
       <c r="I304" s="6">
-        <f>IF(AND(B304="",C304="",D304="",E304="",F304=""),"",IF(OR(B304="",C304="",E304=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E304)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G304&lt;&gt;0,F304=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F304&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F304)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C304)*($E$5:$E$504=E304)*(($D$5:$D$504=D304)*(D304&lt;&gt;"")+($B$5:$B$504=B304)*(B304&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B304="",C304="",D304="",E304="",F304=""),"",IF(OR(B304="",C304="",E304=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E304)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H304&lt;&gt;0,F304=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G304&lt;&gt;0,F304=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F304&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F304)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C304)*($E$5:$E$504=E304)*(($D$5:$D$504=D304)*(D304&lt;&gt;"")+($B$5:$B$504=B304)*(B304&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J304" s="5">
@@ -8477,11 +8505,11 @@
         <v/>
       </c>
       <c r="H305" s="5">
-        <f>IF(OR(C305="Удержание",C305="Зачёт встречного требования",C305="Неустойка заявлена"),N(E305),0)</f>
+        <f>IF(OR(C305="Удержание",C305="Зачёт встречного требования",C305="Неустойка заявлена",C305="Допработы без соглашения (спорно)"),N(E305),0)</f>
         <v/>
       </c>
       <c r="I305" s="6">
-        <f>IF(AND(B305="",C305="",D305="",E305="",F305=""),"",IF(OR(B305="",C305="",E305=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E305)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G305&lt;&gt;0,F305=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F305&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F305)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C305)*($E$5:$E$504=E305)*(($D$5:$D$504=D305)*(D305&lt;&gt;"")+($B$5:$B$504=B305)*(B305&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B305="",C305="",D305="",E305="",F305=""),"",IF(OR(B305="",C305="",E305=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E305)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H305&lt;&gt;0,F305=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G305&lt;&gt;0,F305=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F305&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F305)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C305)*($E$5:$E$504=E305)*(($D$5:$D$504=D305)*(D305&lt;&gt;"")+($B$5:$B$504=B305)*(B305&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J305" s="5">
@@ -8503,11 +8531,11 @@
         <v/>
       </c>
       <c r="H306" s="5">
-        <f>IF(OR(C306="Удержание",C306="Зачёт встречного требования",C306="Неустойка заявлена"),N(E306),0)</f>
+        <f>IF(OR(C306="Удержание",C306="Зачёт встречного требования",C306="Неустойка заявлена",C306="Допработы без соглашения (спорно)"),N(E306),0)</f>
         <v/>
       </c>
       <c r="I306" s="6">
-        <f>IF(AND(B306="",C306="",D306="",E306="",F306=""),"",IF(OR(B306="",C306="",E306=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E306)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G306&lt;&gt;0,F306=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F306&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F306)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C306)*($E$5:$E$504=E306)*(($D$5:$D$504=D306)*(D306&lt;&gt;"")+($B$5:$B$504=B306)*(B306&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B306="",C306="",D306="",E306="",F306=""),"",IF(OR(B306="",C306="",E306=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E306)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H306&lt;&gt;0,F306=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G306&lt;&gt;0,F306=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F306&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F306)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C306)*($E$5:$E$504=E306)*(($D$5:$D$504=D306)*(D306&lt;&gt;"")+($B$5:$B$504=B306)*(B306&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J306" s="5">
@@ -8529,11 +8557,11 @@
         <v/>
       </c>
       <c r="H307" s="5">
-        <f>IF(OR(C307="Удержание",C307="Зачёт встречного требования",C307="Неустойка заявлена"),N(E307),0)</f>
+        <f>IF(OR(C307="Удержание",C307="Зачёт встречного требования",C307="Неустойка заявлена",C307="Допработы без соглашения (спорно)"),N(E307),0)</f>
         <v/>
       </c>
       <c r="I307" s="6">
-        <f>IF(AND(B307="",C307="",D307="",E307="",F307=""),"",IF(OR(B307="",C307="",E307=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E307)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G307&lt;&gt;0,F307=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F307&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F307)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C307)*($E$5:$E$504=E307)*(($D$5:$D$504=D307)*(D307&lt;&gt;"")+($B$5:$B$504=B307)*(B307&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B307="",C307="",D307="",E307="",F307=""),"",IF(OR(B307="",C307="",E307=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E307)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H307&lt;&gt;0,F307=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G307&lt;&gt;0,F307=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F307&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F307)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C307)*($E$5:$E$504=E307)*(($D$5:$D$504=D307)*(D307&lt;&gt;"")+($B$5:$B$504=B307)*(B307&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J307" s="5">
@@ -8555,11 +8583,11 @@
         <v/>
       </c>
       <c r="H308" s="5">
-        <f>IF(OR(C308="Удержание",C308="Зачёт встречного требования",C308="Неустойка заявлена"),N(E308),0)</f>
+        <f>IF(OR(C308="Удержание",C308="Зачёт встречного требования",C308="Неустойка заявлена",C308="Допработы без соглашения (спорно)"),N(E308),0)</f>
         <v/>
       </c>
       <c r="I308" s="6">
-        <f>IF(AND(B308="",C308="",D308="",E308="",F308=""),"",IF(OR(B308="",C308="",E308=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E308)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G308&lt;&gt;0,F308=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F308&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F308)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C308)*($E$5:$E$504=E308)*(($D$5:$D$504=D308)*(D308&lt;&gt;"")+($B$5:$B$504=B308)*(B308&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B308="",C308="",D308="",E308="",F308=""),"",IF(OR(B308="",C308="",E308=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E308)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H308&lt;&gt;0,F308=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G308&lt;&gt;0,F308=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F308&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F308)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C308)*($E$5:$E$504=E308)*(($D$5:$D$504=D308)*(D308&lt;&gt;"")+($B$5:$B$504=B308)*(B308&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J308" s="5">
@@ -8581,11 +8609,11 @@
         <v/>
       </c>
       <c r="H309" s="5">
-        <f>IF(OR(C309="Удержание",C309="Зачёт встречного требования",C309="Неустойка заявлена"),N(E309),0)</f>
+        <f>IF(OR(C309="Удержание",C309="Зачёт встречного требования",C309="Неустойка заявлена",C309="Допработы без соглашения (спорно)"),N(E309),0)</f>
         <v/>
       </c>
       <c r="I309" s="6">
-        <f>IF(AND(B309="",C309="",D309="",E309="",F309=""),"",IF(OR(B309="",C309="",E309=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E309)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G309&lt;&gt;0,F309=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F309&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F309)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C309)*($E$5:$E$504=E309)*(($D$5:$D$504=D309)*(D309&lt;&gt;"")+($B$5:$B$504=B309)*(B309&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B309="",C309="",D309="",E309="",F309=""),"",IF(OR(B309="",C309="",E309=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E309)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H309&lt;&gt;0,F309=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G309&lt;&gt;0,F309=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F309&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F309)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C309)*($E$5:$E$504=E309)*(($D$5:$D$504=D309)*(D309&lt;&gt;"")+($B$5:$B$504=B309)*(B309&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J309" s="5">
@@ -8607,11 +8635,11 @@
         <v/>
       </c>
       <c r="H310" s="5">
-        <f>IF(OR(C310="Удержание",C310="Зачёт встречного требования",C310="Неустойка заявлена"),N(E310),0)</f>
+        <f>IF(OR(C310="Удержание",C310="Зачёт встречного требования",C310="Неустойка заявлена",C310="Допработы без соглашения (спорно)"),N(E310),0)</f>
         <v/>
       </c>
       <c r="I310" s="6">
-        <f>IF(AND(B310="",C310="",D310="",E310="",F310=""),"",IF(OR(B310="",C310="",E310=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E310)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G310&lt;&gt;0,F310=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F310&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F310)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C310)*($E$5:$E$504=E310)*(($D$5:$D$504=D310)*(D310&lt;&gt;"")+($B$5:$B$504=B310)*(B310&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B310="",C310="",D310="",E310="",F310=""),"",IF(OR(B310="",C310="",E310=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E310)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H310&lt;&gt;0,F310=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G310&lt;&gt;0,F310=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F310&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F310)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C310)*($E$5:$E$504=E310)*(($D$5:$D$504=D310)*(D310&lt;&gt;"")+($B$5:$B$504=B310)*(B310&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J310" s="5">
@@ -8633,11 +8661,11 @@
         <v/>
       </c>
       <c r="H311" s="5">
-        <f>IF(OR(C311="Удержание",C311="Зачёт встречного требования",C311="Неустойка заявлена"),N(E311),0)</f>
+        <f>IF(OR(C311="Удержание",C311="Зачёт встречного требования",C311="Неустойка заявлена",C311="Допработы без соглашения (спорно)"),N(E311),0)</f>
         <v/>
       </c>
       <c r="I311" s="6">
-        <f>IF(AND(B311="",C311="",D311="",E311="",F311=""),"",IF(OR(B311="",C311="",E311=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E311)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G311&lt;&gt;0,F311=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F311&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F311)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C311)*($E$5:$E$504=E311)*(($D$5:$D$504=D311)*(D311&lt;&gt;"")+($B$5:$B$504=B311)*(B311&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B311="",C311="",D311="",E311="",F311=""),"",IF(OR(B311="",C311="",E311=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E311)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H311&lt;&gt;0,F311=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G311&lt;&gt;0,F311=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F311&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F311)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C311)*($E$5:$E$504=E311)*(($D$5:$D$504=D311)*(D311&lt;&gt;"")+($B$5:$B$504=B311)*(B311&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J311" s="5">
@@ -8659,11 +8687,11 @@
         <v/>
       </c>
       <c r="H312" s="5">
-        <f>IF(OR(C312="Удержание",C312="Зачёт встречного требования",C312="Неустойка заявлена"),N(E312),0)</f>
+        <f>IF(OR(C312="Удержание",C312="Зачёт встречного требования",C312="Неустойка заявлена",C312="Допработы без соглашения (спорно)"),N(E312),0)</f>
         <v/>
       </c>
       <c r="I312" s="6">
-        <f>IF(AND(B312="",C312="",D312="",E312="",F312=""),"",IF(OR(B312="",C312="",E312=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E312)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G312&lt;&gt;0,F312=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F312&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F312)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C312)*($E$5:$E$504=E312)*(($D$5:$D$504=D312)*(D312&lt;&gt;"")+($B$5:$B$504=B312)*(B312&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B312="",C312="",D312="",E312="",F312=""),"",IF(OR(B312="",C312="",E312=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E312)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H312&lt;&gt;0,F312=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G312&lt;&gt;0,F312=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F312&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F312)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C312)*($E$5:$E$504=E312)*(($D$5:$D$504=D312)*(D312&lt;&gt;"")+($B$5:$B$504=B312)*(B312&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J312" s="5">
@@ -8685,11 +8713,11 @@
         <v/>
       </c>
       <c r="H313" s="5">
-        <f>IF(OR(C313="Удержание",C313="Зачёт встречного требования",C313="Неустойка заявлена"),N(E313),0)</f>
+        <f>IF(OR(C313="Удержание",C313="Зачёт встречного требования",C313="Неустойка заявлена",C313="Допработы без соглашения (спорно)"),N(E313),0)</f>
         <v/>
       </c>
       <c r="I313" s="6">
-        <f>IF(AND(B313="",C313="",D313="",E313="",F313=""),"",IF(OR(B313="",C313="",E313=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E313)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G313&lt;&gt;0,F313=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F313&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F313)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C313)*($E$5:$E$504=E313)*(($D$5:$D$504=D313)*(D313&lt;&gt;"")+($B$5:$B$504=B313)*(B313&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B313="",C313="",D313="",E313="",F313=""),"",IF(OR(B313="",C313="",E313=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E313)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H313&lt;&gt;0,F313=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G313&lt;&gt;0,F313=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F313&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F313)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C313)*($E$5:$E$504=E313)*(($D$5:$D$504=D313)*(D313&lt;&gt;"")+($B$5:$B$504=B313)*(B313&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J313" s="5">
@@ -8711,11 +8739,11 @@
         <v/>
       </c>
       <c r="H314" s="5">
-        <f>IF(OR(C314="Удержание",C314="Зачёт встречного требования",C314="Неустойка заявлена"),N(E314),0)</f>
+        <f>IF(OR(C314="Удержание",C314="Зачёт встречного требования",C314="Неустойка заявлена",C314="Допработы без соглашения (спорно)"),N(E314),0)</f>
         <v/>
       </c>
       <c r="I314" s="6">
-        <f>IF(AND(B314="",C314="",D314="",E314="",F314=""),"",IF(OR(B314="",C314="",E314=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E314)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G314&lt;&gt;0,F314=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F314&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F314)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C314)*($E$5:$E$504=E314)*(($D$5:$D$504=D314)*(D314&lt;&gt;"")+($B$5:$B$504=B314)*(B314&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B314="",C314="",D314="",E314="",F314=""),"",IF(OR(B314="",C314="",E314=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E314)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H314&lt;&gt;0,F314=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G314&lt;&gt;0,F314=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F314&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F314)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C314)*($E$5:$E$504=E314)*(($D$5:$D$504=D314)*(D314&lt;&gt;"")+($B$5:$B$504=B314)*(B314&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J314" s="5">
@@ -8737,11 +8765,11 @@
         <v/>
       </c>
       <c r="H315" s="5">
-        <f>IF(OR(C315="Удержание",C315="Зачёт встречного требования",C315="Неустойка заявлена"),N(E315),0)</f>
+        <f>IF(OR(C315="Удержание",C315="Зачёт встречного требования",C315="Неустойка заявлена",C315="Допработы без соглашения (спорно)"),N(E315),0)</f>
         <v/>
       </c>
       <c r="I315" s="6">
-        <f>IF(AND(B315="",C315="",D315="",E315="",F315=""),"",IF(OR(B315="",C315="",E315=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E315)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G315&lt;&gt;0,F315=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F315&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F315)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C315)*($E$5:$E$504=E315)*(($D$5:$D$504=D315)*(D315&lt;&gt;"")+($B$5:$B$504=B315)*(B315&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B315="",C315="",D315="",E315="",F315=""),"",IF(OR(B315="",C315="",E315=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E315)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H315&lt;&gt;0,F315=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G315&lt;&gt;0,F315=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F315&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F315)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C315)*($E$5:$E$504=E315)*(($D$5:$D$504=D315)*(D315&lt;&gt;"")+($B$5:$B$504=B315)*(B315&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J315" s="5">
@@ -8763,11 +8791,11 @@
         <v/>
       </c>
       <c r="H316" s="5">
-        <f>IF(OR(C316="Удержание",C316="Зачёт встречного требования",C316="Неустойка заявлена"),N(E316),0)</f>
+        <f>IF(OR(C316="Удержание",C316="Зачёт встречного требования",C316="Неустойка заявлена",C316="Допработы без соглашения (спорно)"),N(E316),0)</f>
         <v/>
       </c>
       <c r="I316" s="6">
-        <f>IF(AND(B316="",C316="",D316="",E316="",F316=""),"",IF(OR(B316="",C316="",E316=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E316)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G316&lt;&gt;0,F316=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F316&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F316)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C316)*($E$5:$E$504=E316)*(($D$5:$D$504=D316)*(D316&lt;&gt;"")+($B$5:$B$504=B316)*(B316&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B316="",C316="",D316="",E316="",F316=""),"",IF(OR(B316="",C316="",E316=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E316)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H316&lt;&gt;0,F316=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G316&lt;&gt;0,F316=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F316&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F316)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C316)*($E$5:$E$504=E316)*(($D$5:$D$504=D316)*(D316&lt;&gt;"")+($B$5:$B$504=B316)*(B316&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J316" s="5">
@@ -8789,11 +8817,11 @@
         <v/>
       </c>
       <c r="H317" s="5">
-        <f>IF(OR(C317="Удержание",C317="Зачёт встречного требования",C317="Неустойка заявлена"),N(E317),0)</f>
+        <f>IF(OR(C317="Удержание",C317="Зачёт встречного требования",C317="Неустойка заявлена",C317="Допработы без соглашения (спорно)"),N(E317),0)</f>
         <v/>
       </c>
       <c r="I317" s="6">
-        <f>IF(AND(B317="",C317="",D317="",E317="",F317=""),"",IF(OR(B317="",C317="",E317=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E317)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G317&lt;&gt;0,F317=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F317&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F317)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C317)*($E$5:$E$504=E317)*(($D$5:$D$504=D317)*(D317&lt;&gt;"")+($B$5:$B$504=B317)*(B317&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B317="",C317="",D317="",E317="",F317=""),"",IF(OR(B317="",C317="",E317=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E317)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H317&lt;&gt;0,F317=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G317&lt;&gt;0,F317=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F317&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F317)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C317)*($E$5:$E$504=E317)*(($D$5:$D$504=D317)*(D317&lt;&gt;"")+($B$5:$B$504=B317)*(B317&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J317" s="5">
@@ -8815,11 +8843,11 @@
         <v/>
       </c>
       <c r="H318" s="5">
-        <f>IF(OR(C318="Удержание",C318="Зачёт встречного требования",C318="Неустойка заявлена"),N(E318),0)</f>
+        <f>IF(OR(C318="Удержание",C318="Зачёт встречного требования",C318="Неустойка заявлена",C318="Допработы без соглашения (спорно)"),N(E318),0)</f>
         <v/>
       </c>
       <c r="I318" s="6">
-        <f>IF(AND(B318="",C318="",D318="",E318="",F318=""),"",IF(OR(B318="",C318="",E318=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E318)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G318&lt;&gt;0,F318=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F318&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F318)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C318)*($E$5:$E$504=E318)*(($D$5:$D$504=D318)*(D318&lt;&gt;"")+($B$5:$B$504=B318)*(B318&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B318="",C318="",D318="",E318="",F318=""),"",IF(OR(B318="",C318="",E318=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E318)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H318&lt;&gt;0,F318=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G318&lt;&gt;0,F318=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F318&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F318)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C318)*($E$5:$E$504=E318)*(($D$5:$D$504=D318)*(D318&lt;&gt;"")+($B$5:$B$504=B318)*(B318&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J318" s="5">
@@ -8841,11 +8869,11 @@
         <v/>
       </c>
       <c r="H319" s="5">
-        <f>IF(OR(C319="Удержание",C319="Зачёт встречного требования",C319="Неустойка заявлена"),N(E319),0)</f>
+        <f>IF(OR(C319="Удержание",C319="Зачёт встречного требования",C319="Неустойка заявлена",C319="Допработы без соглашения (спорно)"),N(E319),0)</f>
         <v/>
       </c>
       <c r="I319" s="6">
-        <f>IF(AND(B319="",C319="",D319="",E319="",F319=""),"",IF(OR(B319="",C319="",E319=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E319)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G319&lt;&gt;0,F319=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F319&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F319)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C319)*($E$5:$E$504=E319)*(($D$5:$D$504=D319)*(D319&lt;&gt;"")+($B$5:$B$504=B319)*(B319&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B319="",C319="",D319="",E319="",F319=""),"",IF(OR(B319="",C319="",E319=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E319)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H319&lt;&gt;0,F319=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G319&lt;&gt;0,F319=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F319&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F319)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C319)*($E$5:$E$504=E319)*(($D$5:$D$504=D319)*(D319&lt;&gt;"")+($B$5:$B$504=B319)*(B319&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J319" s="5">
@@ -8867,11 +8895,11 @@
         <v/>
       </c>
       <c r="H320" s="5">
-        <f>IF(OR(C320="Удержание",C320="Зачёт встречного требования",C320="Неустойка заявлена"),N(E320),0)</f>
+        <f>IF(OR(C320="Удержание",C320="Зачёт встречного требования",C320="Неустойка заявлена",C320="Допработы без соглашения (спорно)"),N(E320),0)</f>
         <v/>
       </c>
       <c r="I320" s="6">
-        <f>IF(AND(B320="",C320="",D320="",E320="",F320=""),"",IF(OR(B320="",C320="",E320=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E320)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G320&lt;&gt;0,F320=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F320&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F320)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C320)*($E$5:$E$504=E320)*(($D$5:$D$504=D320)*(D320&lt;&gt;"")+($B$5:$B$504=B320)*(B320&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B320="",C320="",D320="",E320="",F320=""),"",IF(OR(B320="",C320="",E320=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E320)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H320&lt;&gt;0,F320=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G320&lt;&gt;0,F320=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F320&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F320)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C320)*($E$5:$E$504=E320)*(($D$5:$D$504=D320)*(D320&lt;&gt;"")+($B$5:$B$504=B320)*(B320&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J320" s="5">
@@ -8893,11 +8921,11 @@
         <v/>
       </c>
       <c r="H321" s="5">
-        <f>IF(OR(C321="Удержание",C321="Зачёт встречного требования",C321="Неустойка заявлена"),N(E321),0)</f>
+        <f>IF(OR(C321="Удержание",C321="Зачёт встречного требования",C321="Неустойка заявлена",C321="Допработы без соглашения (спорно)"),N(E321),0)</f>
         <v/>
       </c>
       <c r="I321" s="6">
-        <f>IF(AND(B321="",C321="",D321="",E321="",F321=""),"",IF(OR(B321="",C321="",E321=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E321)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G321&lt;&gt;0,F321=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F321&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F321)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C321)*($E$5:$E$504=E321)*(($D$5:$D$504=D321)*(D321&lt;&gt;"")+($B$5:$B$504=B321)*(B321&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B321="",C321="",D321="",E321="",F321=""),"",IF(OR(B321="",C321="",E321=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E321)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H321&lt;&gt;0,F321=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G321&lt;&gt;0,F321=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F321&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F321)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C321)*($E$5:$E$504=E321)*(($D$5:$D$504=D321)*(D321&lt;&gt;"")+($B$5:$B$504=B321)*(B321&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J321" s="5">
@@ -8919,11 +8947,11 @@
         <v/>
       </c>
       <c r="H322" s="5">
-        <f>IF(OR(C322="Удержание",C322="Зачёт встречного требования",C322="Неустойка заявлена"),N(E322),0)</f>
+        <f>IF(OR(C322="Удержание",C322="Зачёт встречного требования",C322="Неустойка заявлена",C322="Допработы без соглашения (спорно)"),N(E322),0)</f>
         <v/>
       </c>
       <c r="I322" s="6">
-        <f>IF(AND(B322="",C322="",D322="",E322="",F322=""),"",IF(OR(B322="",C322="",E322=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E322)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G322&lt;&gt;0,F322=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F322&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F322)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C322)*($E$5:$E$504=E322)*(($D$5:$D$504=D322)*(D322&lt;&gt;"")+($B$5:$B$504=B322)*(B322&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B322="",C322="",D322="",E322="",F322=""),"",IF(OR(B322="",C322="",E322=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E322)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H322&lt;&gt;0,F322=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G322&lt;&gt;0,F322=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F322&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F322)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C322)*($E$5:$E$504=E322)*(($D$5:$D$504=D322)*(D322&lt;&gt;"")+($B$5:$B$504=B322)*(B322&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J322" s="5">
@@ -8945,11 +8973,11 @@
         <v/>
       </c>
       <c r="H323" s="5">
-        <f>IF(OR(C323="Удержание",C323="Зачёт встречного требования",C323="Неустойка заявлена"),N(E323),0)</f>
+        <f>IF(OR(C323="Удержание",C323="Зачёт встречного требования",C323="Неустойка заявлена",C323="Допработы без соглашения (спорно)"),N(E323),0)</f>
         <v/>
       </c>
       <c r="I323" s="6">
-        <f>IF(AND(B323="",C323="",D323="",E323="",F323=""),"",IF(OR(B323="",C323="",E323=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E323)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G323&lt;&gt;0,F323=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F323&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F323)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C323)*($E$5:$E$504=E323)*(($D$5:$D$504=D323)*(D323&lt;&gt;"")+($B$5:$B$504=B323)*(B323&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B323="",C323="",D323="",E323="",F323=""),"",IF(OR(B323="",C323="",E323=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E323)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H323&lt;&gt;0,F323=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G323&lt;&gt;0,F323=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F323&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F323)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C323)*($E$5:$E$504=E323)*(($D$5:$D$504=D323)*(D323&lt;&gt;"")+($B$5:$B$504=B323)*(B323&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J323" s="5">
@@ -8971,11 +8999,11 @@
         <v/>
       </c>
       <c r="H324" s="5">
-        <f>IF(OR(C324="Удержание",C324="Зачёт встречного требования",C324="Неустойка заявлена"),N(E324),0)</f>
+        <f>IF(OR(C324="Удержание",C324="Зачёт встречного требования",C324="Неустойка заявлена",C324="Допработы без соглашения (спорно)"),N(E324),0)</f>
         <v/>
       </c>
       <c r="I324" s="6">
-        <f>IF(AND(B324="",C324="",D324="",E324="",F324=""),"",IF(OR(B324="",C324="",E324=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E324)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G324&lt;&gt;0,F324=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F324&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F324)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C324)*($E$5:$E$504=E324)*(($D$5:$D$504=D324)*(D324&lt;&gt;"")+($B$5:$B$504=B324)*(B324&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B324="",C324="",D324="",E324="",F324=""),"",IF(OR(B324="",C324="",E324=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E324)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H324&lt;&gt;0,F324=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G324&lt;&gt;0,F324=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F324&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F324)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C324)*($E$5:$E$504=E324)*(($D$5:$D$504=D324)*(D324&lt;&gt;"")+($B$5:$B$504=B324)*(B324&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J324" s="5">
@@ -8997,11 +9025,11 @@
         <v/>
       </c>
       <c r="H325" s="5">
-        <f>IF(OR(C325="Удержание",C325="Зачёт встречного требования",C325="Неустойка заявлена"),N(E325),0)</f>
+        <f>IF(OR(C325="Удержание",C325="Зачёт встречного требования",C325="Неустойка заявлена",C325="Допработы без соглашения (спорно)"),N(E325),0)</f>
         <v/>
       </c>
       <c r="I325" s="6">
-        <f>IF(AND(B325="",C325="",D325="",E325="",F325=""),"",IF(OR(B325="",C325="",E325=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E325)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G325&lt;&gt;0,F325=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F325&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F325)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C325)*($E$5:$E$504=E325)*(($D$5:$D$504=D325)*(D325&lt;&gt;"")+($B$5:$B$504=B325)*(B325&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B325="",C325="",D325="",E325="",F325=""),"",IF(OR(B325="",C325="",E325=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E325)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H325&lt;&gt;0,F325=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G325&lt;&gt;0,F325=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F325&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F325)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C325)*($E$5:$E$504=E325)*(($D$5:$D$504=D325)*(D325&lt;&gt;"")+($B$5:$B$504=B325)*(B325&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J325" s="5">
@@ -9023,11 +9051,11 @@
         <v/>
       </c>
       <c r="H326" s="5">
-        <f>IF(OR(C326="Удержание",C326="Зачёт встречного требования",C326="Неустойка заявлена"),N(E326),0)</f>
+        <f>IF(OR(C326="Удержание",C326="Зачёт встречного требования",C326="Неустойка заявлена",C326="Допработы без соглашения (спорно)"),N(E326),0)</f>
         <v/>
       </c>
       <c r="I326" s="6">
-        <f>IF(AND(B326="",C326="",D326="",E326="",F326=""),"",IF(OR(B326="",C326="",E326=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E326)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G326&lt;&gt;0,F326=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F326&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F326)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C326)*($E$5:$E$504=E326)*(($D$5:$D$504=D326)*(D326&lt;&gt;"")+($B$5:$B$504=B326)*(B326&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B326="",C326="",D326="",E326="",F326=""),"",IF(OR(B326="",C326="",E326=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E326)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H326&lt;&gt;0,F326=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G326&lt;&gt;0,F326=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F326&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F326)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C326)*($E$5:$E$504=E326)*(($D$5:$D$504=D326)*(D326&lt;&gt;"")+($B$5:$B$504=B326)*(B326&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J326" s="5">
@@ -9049,11 +9077,11 @@
         <v/>
       </c>
       <c r="H327" s="5">
-        <f>IF(OR(C327="Удержание",C327="Зачёт встречного требования",C327="Неустойка заявлена"),N(E327),0)</f>
+        <f>IF(OR(C327="Удержание",C327="Зачёт встречного требования",C327="Неустойка заявлена",C327="Допработы без соглашения (спорно)"),N(E327),0)</f>
         <v/>
       </c>
       <c r="I327" s="6">
-        <f>IF(AND(B327="",C327="",D327="",E327="",F327=""),"",IF(OR(B327="",C327="",E327=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E327)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G327&lt;&gt;0,F327=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F327&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F327)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C327)*($E$5:$E$504=E327)*(($D$5:$D$504=D327)*(D327&lt;&gt;"")+($B$5:$B$504=B327)*(B327&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B327="",C327="",D327="",E327="",F327=""),"",IF(OR(B327="",C327="",E327=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E327)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H327&lt;&gt;0,F327=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G327&lt;&gt;0,F327=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F327&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F327)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C327)*($E$5:$E$504=E327)*(($D$5:$D$504=D327)*(D327&lt;&gt;"")+($B$5:$B$504=B327)*(B327&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J327" s="5">
@@ -9075,11 +9103,11 @@
         <v/>
       </c>
       <c r="H328" s="5">
-        <f>IF(OR(C328="Удержание",C328="Зачёт встречного требования",C328="Неустойка заявлена"),N(E328),0)</f>
+        <f>IF(OR(C328="Удержание",C328="Зачёт встречного требования",C328="Неустойка заявлена",C328="Допработы без соглашения (спорно)"),N(E328),0)</f>
         <v/>
       </c>
       <c r="I328" s="6">
-        <f>IF(AND(B328="",C328="",D328="",E328="",F328=""),"",IF(OR(B328="",C328="",E328=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E328)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G328&lt;&gt;0,F328=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F328&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F328)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C328)*($E$5:$E$504=E328)*(($D$5:$D$504=D328)*(D328&lt;&gt;"")+($B$5:$B$504=B328)*(B328&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B328="",C328="",D328="",E328="",F328=""),"",IF(OR(B328="",C328="",E328=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E328)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H328&lt;&gt;0,F328=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G328&lt;&gt;0,F328=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F328&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F328)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C328)*($E$5:$E$504=E328)*(($D$5:$D$504=D328)*(D328&lt;&gt;"")+($B$5:$B$504=B328)*(B328&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J328" s="5">
@@ -9101,11 +9129,11 @@
         <v/>
       </c>
       <c r="H329" s="5">
-        <f>IF(OR(C329="Удержание",C329="Зачёт встречного требования",C329="Неустойка заявлена"),N(E329),0)</f>
+        <f>IF(OR(C329="Удержание",C329="Зачёт встречного требования",C329="Неустойка заявлена",C329="Допработы без соглашения (спорно)"),N(E329),0)</f>
         <v/>
       </c>
       <c r="I329" s="6">
-        <f>IF(AND(B329="",C329="",D329="",E329="",F329=""),"",IF(OR(B329="",C329="",E329=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E329)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G329&lt;&gt;0,F329=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F329&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F329)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C329)*($E$5:$E$504=E329)*(($D$5:$D$504=D329)*(D329&lt;&gt;"")+($B$5:$B$504=B329)*(B329&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B329="",C329="",D329="",E329="",F329=""),"",IF(OR(B329="",C329="",E329=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E329)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H329&lt;&gt;0,F329=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G329&lt;&gt;0,F329=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F329&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F329)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C329)*($E$5:$E$504=E329)*(($D$5:$D$504=D329)*(D329&lt;&gt;"")+($B$5:$B$504=B329)*(B329&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J329" s="5">
@@ -9127,11 +9155,11 @@
         <v/>
       </c>
       <c r="H330" s="5">
-        <f>IF(OR(C330="Удержание",C330="Зачёт встречного требования",C330="Неустойка заявлена"),N(E330),0)</f>
+        <f>IF(OR(C330="Удержание",C330="Зачёт встречного требования",C330="Неустойка заявлена",C330="Допработы без соглашения (спорно)"),N(E330),0)</f>
         <v/>
       </c>
       <c r="I330" s="6">
-        <f>IF(AND(B330="",C330="",D330="",E330="",F330=""),"",IF(OR(B330="",C330="",E330=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E330)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G330&lt;&gt;0,F330=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F330&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F330)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C330)*($E$5:$E$504=E330)*(($D$5:$D$504=D330)*(D330&lt;&gt;"")+($B$5:$B$504=B330)*(B330&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B330="",C330="",D330="",E330="",F330=""),"",IF(OR(B330="",C330="",E330=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E330)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H330&lt;&gt;0,F330=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G330&lt;&gt;0,F330=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F330&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F330)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C330)*($E$5:$E$504=E330)*(($D$5:$D$504=D330)*(D330&lt;&gt;"")+($B$5:$B$504=B330)*(B330&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J330" s="5">
@@ -9153,11 +9181,11 @@
         <v/>
       </c>
       <c r="H331" s="5">
-        <f>IF(OR(C331="Удержание",C331="Зачёт встречного требования",C331="Неустойка заявлена"),N(E331),0)</f>
+        <f>IF(OR(C331="Удержание",C331="Зачёт встречного требования",C331="Неустойка заявлена",C331="Допработы без соглашения (спорно)"),N(E331),0)</f>
         <v/>
       </c>
       <c r="I331" s="6">
-        <f>IF(AND(B331="",C331="",D331="",E331="",F331=""),"",IF(OR(B331="",C331="",E331=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E331)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G331&lt;&gt;0,F331=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F331&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F331)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C331)*($E$5:$E$504=E331)*(($D$5:$D$504=D331)*(D331&lt;&gt;"")+($B$5:$B$504=B331)*(B331&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B331="",C331="",D331="",E331="",F331=""),"",IF(OR(B331="",C331="",E331=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E331)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H331&lt;&gt;0,F331=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G331&lt;&gt;0,F331=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F331&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F331)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C331)*($E$5:$E$504=E331)*(($D$5:$D$504=D331)*(D331&lt;&gt;"")+($B$5:$B$504=B331)*(B331&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J331" s="5">
@@ -9179,11 +9207,11 @@
         <v/>
       </c>
       <c r="H332" s="5">
-        <f>IF(OR(C332="Удержание",C332="Зачёт встречного требования",C332="Неустойка заявлена"),N(E332),0)</f>
+        <f>IF(OR(C332="Удержание",C332="Зачёт встречного требования",C332="Неустойка заявлена",C332="Допработы без соглашения (спорно)"),N(E332),0)</f>
         <v/>
       </c>
       <c r="I332" s="6">
-        <f>IF(AND(B332="",C332="",D332="",E332="",F332=""),"",IF(OR(B332="",C332="",E332=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E332)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G332&lt;&gt;0,F332=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F332&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F332)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C332)*($E$5:$E$504=E332)*(($D$5:$D$504=D332)*(D332&lt;&gt;"")+($B$5:$B$504=B332)*(B332&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B332="",C332="",D332="",E332="",F332=""),"",IF(OR(B332="",C332="",E332=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E332)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H332&lt;&gt;0,F332=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G332&lt;&gt;0,F332=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F332&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F332)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C332)*($E$5:$E$504=E332)*(($D$5:$D$504=D332)*(D332&lt;&gt;"")+($B$5:$B$504=B332)*(B332&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J332" s="5">
@@ -9205,11 +9233,11 @@
         <v/>
       </c>
       <c r="H333" s="5">
-        <f>IF(OR(C333="Удержание",C333="Зачёт встречного требования",C333="Неустойка заявлена"),N(E333),0)</f>
+        <f>IF(OR(C333="Удержание",C333="Зачёт встречного требования",C333="Неустойка заявлена",C333="Допработы без соглашения (спорно)"),N(E333),0)</f>
         <v/>
       </c>
       <c r="I333" s="6">
-        <f>IF(AND(B333="",C333="",D333="",E333="",F333=""),"",IF(OR(B333="",C333="",E333=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E333)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G333&lt;&gt;0,F333=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F333&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F333)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C333)*($E$5:$E$504=E333)*(($D$5:$D$504=D333)*(D333&lt;&gt;"")+($B$5:$B$504=B333)*(B333&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B333="",C333="",D333="",E333="",F333=""),"",IF(OR(B333="",C333="",E333=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E333)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H333&lt;&gt;0,F333=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G333&lt;&gt;0,F333=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F333&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F333)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C333)*($E$5:$E$504=E333)*(($D$5:$D$504=D333)*(D333&lt;&gt;"")+($B$5:$B$504=B333)*(B333&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J333" s="5">
@@ -9231,11 +9259,11 @@
         <v/>
       </c>
       <c r="H334" s="5">
-        <f>IF(OR(C334="Удержание",C334="Зачёт встречного требования",C334="Неустойка заявлена"),N(E334),0)</f>
+        <f>IF(OR(C334="Удержание",C334="Зачёт встречного требования",C334="Неустойка заявлена",C334="Допработы без соглашения (спорно)"),N(E334),0)</f>
         <v/>
       </c>
       <c r="I334" s="6">
-        <f>IF(AND(B334="",C334="",D334="",E334="",F334=""),"",IF(OR(B334="",C334="",E334=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E334)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G334&lt;&gt;0,F334=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F334&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F334)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C334)*($E$5:$E$504=E334)*(($D$5:$D$504=D334)*(D334&lt;&gt;"")+($B$5:$B$504=B334)*(B334&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B334="",C334="",D334="",E334="",F334=""),"",IF(OR(B334="",C334="",E334=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E334)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H334&lt;&gt;0,F334=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G334&lt;&gt;0,F334=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F334&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F334)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C334)*($E$5:$E$504=E334)*(($D$5:$D$504=D334)*(D334&lt;&gt;"")+($B$5:$B$504=B334)*(B334&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J334" s="5">
@@ -9257,11 +9285,11 @@
         <v/>
       </c>
       <c r="H335" s="5">
-        <f>IF(OR(C335="Удержание",C335="Зачёт встречного требования",C335="Неустойка заявлена"),N(E335),0)</f>
+        <f>IF(OR(C335="Удержание",C335="Зачёт встречного требования",C335="Неустойка заявлена",C335="Допработы без соглашения (спорно)"),N(E335),0)</f>
         <v/>
       </c>
       <c r="I335" s="6">
-        <f>IF(AND(B335="",C335="",D335="",E335="",F335=""),"",IF(OR(B335="",C335="",E335=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E335)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G335&lt;&gt;0,F335=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F335&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F335)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C335)*($E$5:$E$504=E335)*(($D$5:$D$504=D335)*(D335&lt;&gt;"")+($B$5:$B$504=B335)*(B335&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B335="",C335="",D335="",E335="",F335=""),"",IF(OR(B335="",C335="",E335=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E335)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H335&lt;&gt;0,F335=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G335&lt;&gt;0,F335=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F335&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F335)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C335)*($E$5:$E$504=E335)*(($D$5:$D$504=D335)*(D335&lt;&gt;"")+($B$5:$B$504=B335)*(B335&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J335" s="5">
@@ -9283,11 +9311,11 @@
         <v/>
       </c>
       <c r="H336" s="5">
-        <f>IF(OR(C336="Удержание",C336="Зачёт встречного требования",C336="Неустойка заявлена"),N(E336),0)</f>
+        <f>IF(OR(C336="Удержание",C336="Зачёт встречного требования",C336="Неустойка заявлена",C336="Допработы без соглашения (спорно)"),N(E336),0)</f>
         <v/>
       </c>
       <c r="I336" s="6">
-        <f>IF(AND(B336="",C336="",D336="",E336="",F336=""),"",IF(OR(B336="",C336="",E336=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E336)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G336&lt;&gt;0,F336=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F336&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F336)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C336)*($E$5:$E$504=E336)*(($D$5:$D$504=D336)*(D336&lt;&gt;"")+($B$5:$B$504=B336)*(B336&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B336="",C336="",D336="",E336="",F336=""),"",IF(OR(B336="",C336="",E336=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E336)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H336&lt;&gt;0,F336=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G336&lt;&gt;0,F336=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F336&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F336)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C336)*($E$5:$E$504=E336)*(($D$5:$D$504=D336)*(D336&lt;&gt;"")+($B$5:$B$504=B336)*(B336&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J336" s="5">
@@ -9309,11 +9337,11 @@
         <v/>
       </c>
       <c r="H337" s="5">
-        <f>IF(OR(C337="Удержание",C337="Зачёт встречного требования",C337="Неустойка заявлена"),N(E337),0)</f>
+        <f>IF(OR(C337="Удержание",C337="Зачёт встречного требования",C337="Неустойка заявлена",C337="Допработы без соглашения (спорно)"),N(E337),0)</f>
         <v/>
       </c>
       <c r="I337" s="6">
-        <f>IF(AND(B337="",C337="",D337="",E337="",F337=""),"",IF(OR(B337="",C337="",E337=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E337)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G337&lt;&gt;0,F337=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F337&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F337)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C337)*($E$5:$E$504=E337)*(($D$5:$D$504=D337)*(D337&lt;&gt;"")+($B$5:$B$504=B337)*(B337&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B337="",C337="",D337="",E337="",F337=""),"",IF(OR(B337="",C337="",E337=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E337)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H337&lt;&gt;0,F337=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G337&lt;&gt;0,F337=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F337&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F337)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C337)*($E$5:$E$504=E337)*(($D$5:$D$504=D337)*(D337&lt;&gt;"")+($B$5:$B$504=B337)*(B337&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J337" s="5">
@@ -9335,11 +9363,11 @@
         <v/>
       </c>
       <c r="H338" s="5">
-        <f>IF(OR(C338="Удержание",C338="Зачёт встречного требования",C338="Неустойка заявлена"),N(E338),0)</f>
+        <f>IF(OR(C338="Удержание",C338="Зачёт встречного требования",C338="Неустойка заявлена",C338="Допработы без соглашения (спорно)"),N(E338),0)</f>
         <v/>
       </c>
       <c r="I338" s="6">
-        <f>IF(AND(B338="",C338="",D338="",E338="",F338=""),"",IF(OR(B338="",C338="",E338=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E338)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G338&lt;&gt;0,F338=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F338&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F338)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C338)*($E$5:$E$504=E338)*(($D$5:$D$504=D338)*(D338&lt;&gt;"")+($B$5:$B$504=B338)*(B338&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B338="",C338="",D338="",E338="",F338=""),"",IF(OR(B338="",C338="",E338=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E338)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H338&lt;&gt;0,F338=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G338&lt;&gt;0,F338=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F338&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F338)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C338)*($E$5:$E$504=E338)*(($D$5:$D$504=D338)*(D338&lt;&gt;"")+($B$5:$B$504=B338)*(B338&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J338" s="5">
@@ -9361,11 +9389,11 @@
         <v/>
       </c>
       <c r="H339" s="5">
-        <f>IF(OR(C339="Удержание",C339="Зачёт встречного требования",C339="Неустойка заявлена"),N(E339),0)</f>
+        <f>IF(OR(C339="Удержание",C339="Зачёт встречного требования",C339="Неустойка заявлена",C339="Допработы без соглашения (спорно)"),N(E339),0)</f>
         <v/>
       </c>
       <c r="I339" s="6">
-        <f>IF(AND(B339="",C339="",D339="",E339="",F339=""),"",IF(OR(B339="",C339="",E339=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E339)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G339&lt;&gt;0,F339=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F339&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F339)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C339)*($E$5:$E$504=E339)*(($D$5:$D$504=D339)*(D339&lt;&gt;"")+($B$5:$B$504=B339)*(B339&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B339="",C339="",D339="",E339="",F339=""),"",IF(OR(B339="",C339="",E339=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E339)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H339&lt;&gt;0,F339=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G339&lt;&gt;0,F339=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F339&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F339)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C339)*($E$5:$E$504=E339)*(($D$5:$D$504=D339)*(D339&lt;&gt;"")+($B$5:$B$504=B339)*(B339&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J339" s="5">
@@ -9387,11 +9415,11 @@
         <v/>
       </c>
       <c r="H340" s="5">
-        <f>IF(OR(C340="Удержание",C340="Зачёт встречного требования",C340="Неустойка заявлена"),N(E340),0)</f>
+        <f>IF(OR(C340="Удержание",C340="Зачёт встречного требования",C340="Неустойка заявлена",C340="Допработы без соглашения (спорно)"),N(E340),0)</f>
         <v/>
       </c>
       <c r="I340" s="6">
-        <f>IF(AND(B340="",C340="",D340="",E340="",F340=""),"",IF(OR(B340="",C340="",E340=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E340)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G340&lt;&gt;0,F340=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F340&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F340)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C340)*($E$5:$E$504=E340)*(($D$5:$D$504=D340)*(D340&lt;&gt;"")+($B$5:$B$504=B340)*(B340&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B340="",C340="",D340="",E340="",F340=""),"",IF(OR(B340="",C340="",E340=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E340)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H340&lt;&gt;0,F340=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G340&lt;&gt;0,F340=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F340&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F340)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C340)*($E$5:$E$504=E340)*(($D$5:$D$504=D340)*(D340&lt;&gt;"")+($B$5:$B$504=B340)*(B340&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J340" s="5">
@@ -9413,11 +9441,11 @@
         <v/>
       </c>
       <c r="H341" s="5">
-        <f>IF(OR(C341="Удержание",C341="Зачёт встречного требования",C341="Неустойка заявлена"),N(E341),0)</f>
+        <f>IF(OR(C341="Удержание",C341="Зачёт встречного требования",C341="Неустойка заявлена",C341="Допработы без соглашения (спорно)"),N(E341),0)</f>
         <v/>
       </c>
       <c r="I341" s="6">
-        <f>IF(AND(B341="",C341="",D341="",E341="",F341=""),"",IF(OR(B341="",C341="",E341=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E341)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G341&lt;&gt;0,F341=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F341&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F341)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C341)*($E$5:$E$504=E341)*(($D$5:$D$504=D341)*(D341&lt;&gt;"")+($B$5:$B$504=B341)*(B341&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B341="",C341="",D341="",E341="",F341=""),"",IF(OR(B341="",C341="",E341=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E341)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H341&lt;&gt;0,F341=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G341&lt;&gt;0,F341=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F341&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F341)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C341)*($E$5:$E$504=E341)*(($D$5:$D$504=D341)*(D341&lt;&gt;"")+($B$5:$B$504=B341)*(B341&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J341" s="5">
@@ -9439,11 +9467,11 @@
         <v/>
       </c>
       <c r="H342" s="5">
-        <f>IF(OR(C342="Удержание",C342="Зачёт встречного требования",C342="Неустойка заявлена"),N(E342),0)</f>
+        <f>IF(OR(C342="Удержание",C342="Зачёт встречного требования",C342="Неустойка заявлена",C342="Допработы без соглашения (спорно)"),N(E342),0)</f>
         <v/>
       </c>
       <c r="I342" s="6">
-        <f>IF(AND(B342="",C342="",D342="",E342="",F342=""),"",IF(OR(B342="",C342="",E342=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E342)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G342&lt;&gt;0,F342=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F342&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F342)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C342)*($E$5:$E$504=E342)*(($D$5:$D$504=D342)*(D342&lt;&gt;"")+($B$5:$B$504=B342)*(B342&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B342="",C342="",D342="",E342="",F342=""),"",IF(OR(B342="",C342="",E342=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E342)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H342&lt;&gt;0,F342=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G342&lt;&gt;0,F342=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F342&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F342)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C342)*($E$5:$E$504=E342)*(($D$5:$D$504=D342)*(D342&lt;&gt;"")+($B$5:$B$504=B342)*(B342&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J342" s="5">
@@ -9465,11 +9493,11 @@
         <v/>
       </c>
       <c r="H343" s="5">
-        <f>IF(OR(C343="Удержание",C343="Зачёт встречного требования",C343="Неустойка заявлена"),N(E343),0)</f>
+        <f>IF(OR(C343="Удержание",C343="Зачёт встречного требования",C343="Неустойка заявлена",C343="Допработы без соглашения (спорно)"),N(E343),0)</f>
         <v/>
       </c>
       <c r="I343" s="6">
-        <f>IF(AND(B343="",C343="",D343="",E343="",F343=""),"",IF(OR(B343="",C343="",E343=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E343)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G343&lt;&gt;0,F343=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F343&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F343)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C343)*($E$5:$E$504=E343)*(($D$5:$D$504=D343)*(D343&lt;&gt;"")+($B$5:$B$504=B343)*(B343&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B343="",C343="",D343="",E343="",F343=""),"",IF(OR(B343="",C343="",E343=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E343)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H343&lt;&gt;0,F343=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G343&lt;&gt;0,F343=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F343&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F343)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C343)*($E$5:$E$504=E343)*(($D$5:$D$504=D343)*(D343&lt;&gt;"")+($B$5:$B$504=B343)*(B343&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J343" s="5">
@@ -9491,11 +9519,11 @@
         <v/>
       </c>
       <c r="H344" s="5">
-        <f>IF(OR(C344="Удержание",C344="Зачёт встречного требования",C344="Неустойка заявлена"),N(E344),0)</f>
+        <f>IF(OR(C344="Удержание",C344="Зачёт встречного требования",C344="Неустойка заявлена",C344="Допработы без соглашения (спорно)"),N(E344),0)</f>
         <v/>
       </c>
       <c r="I344" s="6">
-        <f>IF(AND(B344="",C344="",D344="",E344="",F344=""),"",IF(OR(B344="",C344="",E344=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E344)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G344&lt;&gt;0,F344=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F344&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F344)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C344)*($E$5:$E$504=E344)*(($D$5:$D$504=D344)*(D344&lt;&gt;"")+($B$5:$B$504=B344)*(B344&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B344="",C344="",D344="",E344="",F344=""),"",IF(OR(B344="",C344="",E344=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E344)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H344&lt;&gt;0,F344=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G344&lt;&gt;0,F344=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F344&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F344)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C344)*($E$5:$E$504=E344)*(($D$5:$D$504=D344)*(D344&lt;&gt;"")+($B$5:$B$504=B344)*(B344&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J344" s="5">
@@ -9517,11 +9545,11 @@
         <v/>
       </c>
       <c r="H345" s="5">
-        <f>IF(OR(C345="Удержание",C345="Зачёт встречного требования",C345="Неустойка заявлена"),N(E345),0)</f>
+        <f>IF(OR(C345="Удержание",C345="Зачёт встречного требования",C345="Неустойка заявлена",C345="Допработы без соглашения (спорно)"),N(E345),0)</f>
         <v/>
       </c>
       <c r="I345" s="6">
-        <f>IF(AND(B345="",C345="",D345="",E345="",F345=""),"",IF(OR(B345="",C345="",E345=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E345)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G345&lt;&gt;0,F345=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F345&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F345)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C345)*($E$5:$E$504=E345)*(($D$5:$D$504=D345)*(D345&lt;&gt;"")+($B$5:$B$504=B345)*(B345&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B345="",C345="",D345="",E345="",F345=""),"",IF(OR(B345="",C345="",E345=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E345)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H345&lt;&gt;0,F345=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G345&lt;&gt;0,F345=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F345&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F345)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C345)*($E$5:$E$504=E345)*(($D$5:$D$504=D345)*(D345&lt;&gt;"")+($B$5:$B$504=B345)*(B345&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J345" s="5">
@@ -9543,11 +9571,11 @@
         <v/>
       </c>
       <c r="H346" s="5">
-        <f>IF(OR(C346="Удержание",C346="Зачёт встречного требования",C346="Неустойка заявлена"),N(E346),0)</f>
+        <f>IF(OR(C346="Удержание",C346="Зачёт встречного требования",C346="Неустойка заявлена",C346="Допработы без соглашения (спорно)"),N(E346),0)</f>
         <v/>
       </c>
       <c r="I346" s="6">
-        <f>IF(AND(B346="",C346="",D346="",E346="",F346=""),"",IF(OR(B346="",C346="",E346=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E346)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G346&lt;&gt;0,F346=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F346&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F346)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C346)*($E$5:$E$504=E346)*(($D$5:$D$504=D346)*(D346&lt;&gt;"")+($B$5:$B$504=B346)*(B346&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B346="",C346="",D346="",E346="",F346=""),"",IF(OR(B346="",C346="",E346=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E346)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H346&lt;&gt;0,F346=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G346&lt;&gt;0,F346=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F346&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F346)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C346)*($E$5:$E$504=E346)*(($D$5:$D$504=D346)*(D346&lt;&gt;"")+($B$5:$B$504=B346)*(B346&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J346" s="5">
@@ -9569,11 +9597,11 @@
         <v/>
       </c>
       <c r="H347" s="5">
-        <f>IF(OR(C347="Удержание",C347="Зачёт встречного требования",C347="Неустойка заявлена"),N(E347),0)</f>
+        <f>IF(OR(C347="Удержание",C347="Зачёт встречного требования",C347="Неустойка заявлена",C347="Допработы без соглашения (спорно)"),N(E347),0)</f>
         <v/>
       </c>
       <c r="I347" s="6">
-        <f>IF(AND(B347="",C347="",D347="",E347="",F347=""),"",IF(OR(B347="",C347="",E347=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E347)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G347&lt;&gt;0,F347=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F347&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F347)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C347)*($E$5:$E$504=E347)*(($D$5:$D$504=D347)*(D347&lt;&gt;"")+($B$5:$B$504=B347)*(B347&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B347="",C347="",D347="",E347="",F347=""),"",IF(OR(B347="",C347="",E347=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E347)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H347&lt;&gt;0,F347=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G347&lt;&gt;0,F347=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F347&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F347)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C347)*($E$5:$E$504=E347)*(($D$5:$D$504=D347)*(D347&lt;&gt;"")+($B$5:$B$504=B347)*(B347&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J347" s="5">
@@ -9595,11 +9623,11 @@
         <v/>
       </c>
       <c r="H348" s="5">
-        <f>IF(OR(C348="Удержание",C348="Зачёт встречного требования",C348="Неустойка заявлена"),N(E348),0)</f>
+        <f>IF(OR(C348="Удержание",C348="Зачёт встречного требования",C348="Неустойка заявлена",C348="Допработы без соглашения (спорно)"),N(E348),0)</f>
         <v/>
       </c>
       <c r="I348" s="6">
-        <f>IF(AND(B348="",C348="",D348="",E348="",F348=""),"",IF(OR(B348="",C348="",E348=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E348)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G348&lt;&gt;0,F348=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F348&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F348)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C348)*($E$5:$E$504=E348)*(($D$5:$D$504=D348)*(D348&lt;&gt;"")+($B$5:$B$504=B348)*(B348&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B348="",C348="",D348="",E348="",F348=""),"",IF(OR(B348="",C348="",E348=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E348)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H348&lt;&gt;0,F348=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G348&lt;&gt;0,F348=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F348&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F348)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C348)*($E$5:$E$504=E348)*(($D$5:$D$504=D348)*(D348&lt;&gt;"")+($B$5:$B$504=B348)*(B348&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J348" s="5">
@@ -9621,11 +9649,11 @@
         <v/>
       </c>
       <c r="H349" s="5">
-        <f>IF(OR(C349="Удержание",C349="Зачёт встречного требования",C349="Неустойка заявлена"),N(E349),0)</f>
+        <f>IF(OR(C349="Удержание",C349="Зачёт встречного требования",C349="Неустойка заявлена",C349="Допработы без соглашения (спорно)"),N(E349),0)</f>
         <v/>
       </c>
       <c r="I349" s="6">
-        <f>IF(AND(B349="",C349="",D349="",E349="",F349=""),"",IF(OR(B349="",C349="",E349=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E349)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G349&lt;&gt;0,F349=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F349&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F349)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C349)*($E$5:$E$504=E349)*(($D$5:$D$504=D349)*(D349&lt;&gt;"")+($B$5:$B$504=B349)*(B349&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B349="",C349="",D349="",E349="",F349=""),"",IF(OR(B349="",C349="",E349=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E349)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H349&lt;&gt;0,F349=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G349&lt;&gt;0,F349=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F349&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F349)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C349)*($E$5:$E$504=E349)*(($D$5:$D$504=D349)*(D349&lt;&gt;"")+($B$5:$B$504=B349)*(B349&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J349" s="5">
@@ -9647,11 +9675,11 @@
         <v/>
       </c>
       <c r="H350" s="5">
-        <f>IF(OR(C350="Удержание",C350="Зачёт встречного требования",C350="Неустойка заявлена"),N(E350),0)</f>
+        <f>IF(OR(C350="Удержание",C350="Зачёт встречного требования",C350="Неустойка заявлена",C350="Допработы без соглашения (спорно)"),N(E350),0)</f>
         <v/>
       </c>
       <c r="I350" s="6">
-        <f>IF(AND(B350="",C350="",D350="",E350="",F350=""),"",IF(OR(B350="",C350="",E350=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E350)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G350&lt;&gt;0,F350=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F350&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F350)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C350)*($E$5:$E$504=E350)*(($D$5:$D$504=D350)*(D350&lt;&gt;"")+($B$5:$B$504=B350)*(B350&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B350="",C350="",D350="",E350="",F350=""),"",IF(OR(B350="",C350="",E350=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E350)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H350&lt;&gt;0,F350=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G350&lt;&gt;0,F350=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F350&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F350)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C350)*($E$5:$E$504=E350)*(($D$5:$D$504=D350)*(D350&lt;&gt;"")+($B$5:$B$504=B350)*(B350&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J350" s="5">
@@ -9673,11 +9701,11 @@
         <v/>
       </c>
       <c r="H351" s="5">
-        <f>IF(OR(C351="Удержание",C351="Зачёт встречного требования",C351="Неустойка заявлена"),N(E351),0)</f>
+        <f>IF(OR(C351="Удержание",C351="Зачёт встречного требования",C351="Неустойка заявлена",C351="Допработы без соглашения (спорно)"),N(E351),0)</f>
         <v/>
       </c>
       <c r="I351" s="6">
-        <f>IF(AND(B351="",C351="",D351="",E351="",F351=""),"",IF(OR(B351="",C351="",E351=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E351)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G351&lt;&gt;0,F351=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F351&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F351)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C351)*($E$5:$E$504=E351)*(($D$5:$D$504=D351)*(D351&lt;&gt;"")+($B$5:$B$504=B351)*(B351&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B351="",C351="",D351="",E351="",F351=""),"",IF(OR(B351="",C351="",E351=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E351)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H351&lt;&gt;0,F351=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G351&lt;&gt;0,F351=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F351&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F351)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C351)*($E$5:$E$504=E351)*(($D$5:$D$504=D351)*(D351&lt;&gt;"")+($B$5:$B$504=B351)*(B351&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J351" s="5">
@@ -9699,11 +9727,11 @@
         <v/>
       </c>
       <c r="H352" s="5">
-        <f>IF(OR(C352="Удержание",C352="Зачёт встречного требования",C352="Неустойка заявлена"),N(E352),0)</f>
+        <f>IF(OR(C352="Удержание",C352="Зачёт встречного требования",C352="Неустойка заявлена",C352="Допработы без соглашения (спорно)"),N(E352),0)</f>
         <v/>
       </c>
       <c r="I352" s="6">
-        <f>IF(AND(B352="",C352="",D352="",E352="",F352=""),"",IF(OR(B352="",C352="",E352=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E352)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G352&lt;&gt;0,F352=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F352&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F352)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C352)*($E$5:$E$504=E352)*(($D$5:$D$504=D352)*(D352&lt;&gt;"")+($B$5:$B$504=B352)*(B352&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B352="",C352="",D352="",E352="",F352=""),"",IF(OR(B352="",C352="",E352=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E352)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H352&lt;&gt;0,F352=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G352&lt;&gt;0,F352=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F352&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F352)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C352)*($E$5:$E$504=E352)*(($D$5:$D$504=D352)*(D352&lt;&gt;"")+($B$5:$B$504=B352)*(B352&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J352" s="5">
@@ -9725,11 +9753,11 @@
         <v/>
       </c>
       <c r="H353" s="5">
-        <f>IF(OR(C353="Удержание",C353="Зачёт встречного требования",C353="Неустойка заявлена"),N(E353),0)</f>
+        <f>IF(OR(C353="Удержание",C353="Зачёт встречного требования",C353="Неустойка заявлена",C353="Допработы без соглашения (спорно)"),N(E353),0)</f>
         <v/>
       </c>
       <c r="I353" s="6">
-        <f>IF(AND(B353="",C353="",D353="",E353="",F353=""),"",IF(OR(B353="",C353="",E353=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E353)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G353&lt;&gt;0,F353=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F353&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F353)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C353)*($E$5:$E$504=E353)*(($D$5:$D$504=D353)*(D353&lt;&gt;"")+($B$5:$B$504=B353)*(B353&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B353="",C353="",D353="",E353="",F353=""),"",IF(OR(B353="",C353="",E353=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E353)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H353&lt;&gt;0,F353=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G353&lt;&gt;0,F353=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F353&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F353)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C353)*($E$5:$E$504=E353)*(($D$5:$D$504=D353)*(D353&lt;&gt;"")+($B$5:$B$504=B353)*(B353&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J353" s="5">
@@ -9751,11 +9779,11 @@
         <v/>
       </c>
       <c r="H354" s="5">
-        <f>IF(OR(C354="Удержание",C354="Зачёт встречного требования",C354="Неустойка заявлена"),N(E354),0)</f>
+        <f>IF(OR(C354="Удержание",C354="Зачёт встречного требования",C354="Неустойка заявлена",C354="Допработы без соглашения (спорно)"),N(E354),0)</f>
         <v/>
       </c>
       <c r="I354" s="6">
-        <f>IF(AND(B354="",C354="",D354="",E354="",F354=""),"",IF(OR(B354="",C354="",E354=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E354)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G354&lt;&gt;0,F354=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F354&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F354)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C354)*($E$5:$E$504=E354)*(($D$5:$D$504=D354)*(D354&lt;&gt;"")+($B$5:$B$504=B354)*(B354&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B354="",C354="",D354="",E354="",F354=""),"",IF(OR(B354="",C354="",E354=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E354)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H354&lt;&gt;0,F354=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G354&lt;&gt;0,F354=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F354&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F354)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C354)*($E$5:$E$504=E354)*(($D$5:$D$504=D354)*(D354&lt;&gt;"")+($B$5:$B$504=B354)*(B354&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J354" s="5">
@@ -9777,11 +9805,11 @@
         <v/>
       </c>
       <c r="H355" s="5">
-        <f>IF(OR(C355="Удержание",C355="Зачёт встречного требования",C355="Неустойка заявлена"),N(E355),0)</f>
+        <f>IF(OR(C355="Удержание",C355="Зачёт встречного требования",C355="Неустойка заявлена",C355="Допработы без соглашения (спорно)"),N(E355),0)</f>
         <v/>
       </c>
       <c r="I355" s="6">
-        <f>IF(AND(B355="",C355="",D355="",E355="",F355=""),"",IF(OR(B355="",C355="",E355=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E355)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G355&lt;&gt;0,F355=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F355&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F355)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C355)*($E$5:$E$504=E355)*(($D$5:$D$504=D355)*(D355&lt;&gt;"")+($B$5:$B$504=B355)*(B355&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B355="",C355="",D355="",E355="",F355=""),"",IF(OR(B355="",C355="",E355=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E355)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H355&lt;&gt;0,F355=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G355&lt;&gt;0,F355=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F355&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F355)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C355)*($E$5:$E$504=E355)*(($D$5:$D$504=D355)*(D355&lt;&gt;"")+($B$5:$B$504=B355)*(B355&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J355" s="5">
@@ -9803,11 +9831,11 @@
         <v/>
       </c>
       <c r="H356" s="5">
-        <f>IF(OR(C356="Удержание",C356="Зачёт встречного требования",C356="Неустойка заявлена"),N(E356),0)</f>
+        <f>IF(OR(C356="Удержание",C356="Зачёт встречного требования",C356="Неустойка заявлена",C356="Допработы без соглашения (спорно)"),N(E356),0)</f>
         <v/>
       </c>
       <c r="I356" s="6">
-        <f>IF(AND(B356="",C356="",D356="",E356="",F356=""),"",IF(OR(B356="",C356="",E356=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E356)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G356&lt;&gt;0,F356=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F356&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F356)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C356)*($E$5:$E$504=E356)*(($D$5:$D$504=D356)*(D356&lt;&gt;"")+($B$5:$B$504=B356)*(B356&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B356="",C356="",D356="",E356="",F356=""),"",IF(OR(B356="",C356="",E356=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E356)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H356&lt;&gt;0,F356=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G356&lt;&gt;0,F356=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F356&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F356)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C356)*($E$5:$E$504=E356)*(($D$5:$D$504=D356)*(D356&lt;&gt;"")+($B$5:$B$504=B356)*(B356&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J356" s="5">
@@ -9829,11 +9857,11 @@
         <v/>
       </c>
       <c r="H357" s="5">
-        <f>IF(OR(C357="Удержание",C357="Зачёт встречного требования",C357="Неустойка заявлена"),N(E357),0)</f>
+        <f>IF(OR(C357="Удержание",C357="Зачёт встречного требования",C357="Неустойка заявлена",C357="Допработы без соглашения (спорно)"),N(E357),0)</f>
         <v/>
       </c>
       <c r="I357" s="6">
-        <f>IF(AND(B357="",C357="",D357="",E357="",F357=""),"",IF(OR(B357="",C357="",E357=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E357)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G357&lt;&gt;0,F357=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F357&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F357)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C357)*($E$5:$E$504=E357)*(($D$5:$D$504=D357)*(D357&lt;&gt;"")+($B$5:$B$504=B357)*(B357&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B357="",C357="",D357="",E357="",F357=""),"",IF(OR(B357="",C357="",E357=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E357)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H357&lt;&gt;0,F357=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G357&lt;&gt;0,F357=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F357&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F357)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C357)*($E$5:$E$504=E357)*(($D$5:$D$504=D357)*(D357&lt;&gt;"")+($B$5:$B$504=B357)*(B357&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J357" s="5">
@@ -9855,11 +9883,11 @@
         <v/>
       </c>
       <c r="H358" s="5">
-        <f>IF(OR(C358="Удержание",C358="Зачёт встречного требования",C358="Неустойка заявлена"),N(E358),0)</f>
+        <f>IF(OR(C358="Удержание",C358="Зачёт встречного требования",C358="Неустойка заявлена",C358="Допработы без соглашения (спорно)"),N(E358),0)</f>
         <v/>
       </c>
       <c r="I358" s="6">
-        <f>IF(AND(B358="",C358="",D358="",E358="",F358=""),"",IF(OR(B358="",C358="",E358=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E358)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G358&lt;&gt;0,F358=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F358&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F358)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C358)*($E$5:$E$504=E358)*(($D$5:$D$504=D358)*(D358&lt;&gt;"")+($B$5:$B$504=B358)*(B358&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B358="",C358="",D358="",E358="",F358=""),"",IF(OR(B358="",C358="",E358=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E358)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H358&lt;&gt;0,F358=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G358&lt;&gt;0,F358=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F358&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F358)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C358)*($E$5:$E$504=E358)*(($D$5:$D$504=D358)*(D358&lt;&gt;"")+($B$5:$B$504=B358)*(B358&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J358" s="5">
@@ -9881,11 +9909,11 @@
         <v/>
       </c>
       <c r="H359" s="5">
-        <f>IF(OR(C359="Удержание",C359="Зачёт встречного требования",C359="Неустойка заявлена"),N(E359),0)</f>
+        <f>IF(OR(C359="Удержание",C359="Зачёт встречного требования",C359="Неустойка заявлена",C359="Допработы без соглашения (спорно)"),N(E359),0)</f>
         <v/>
       </c>
       <c r="I359" s="6">
-        <f>IF(AND(B359="",C359="",D359="",E359="",F359=""),"",IF(OR(B359="",C359="",E359=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E359)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G359&lt;&gt;0,F359=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F359&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F359)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C359)*($E$5:$E$504=E359)*(($D$5:$D$504=D359)*(D359&lt;&gt;"")+($B$5:$B$504=B359)*(B359&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B359="",C359="",D359="",E359="",F359=""),"",IF(OR(B359="",C359="",E359=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E359)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H359&lt;&gt;0,F359=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G359&lt;&gt;0,F359=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F359&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F359)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C359)*($E$5:$E$504=E359)*(($D$5:$D$504=D359)*(D359&lt;&gt;"")+($B$5:$B$504=B359)*(B359&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J359" s="5">
@@ -9907,11 +9935,11 @@
         <v/>
       </c>
       <c r="H360" s="5">
-        <f>IF(OR(C360="Удержание",C360="Зачёт встречного требования",C360="Неустойка заявлена"),N(E360),0)</f>
+        <f>IF(OR(C360="Удержание",C360="Зачёт встречного требования",C360="Неустойка заявлена",C360="Допработы без соглашения (спорно)"),N(E360),0)</f>
         <v/>
       </c>
       <c r="I360" s="6">
-        <f>IF(AND(B360="",C360="",D360="",E360="",F360=""),"",IF(OR(B360="",C360="",E360=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E360)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G360&lt;&gt;0,F360=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F360&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F360)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C360)*($E$5:$E$504=E360)*(($D$5:$D$504=D360)*(D360&lt;&gt;"")+($B$5:$B$504=B360)*(B360&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B360="",C360="",D360="",E360="",F360=""),"",IF(OR(B360="",C360="",E360=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E360)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H360&lt;&gt;0,F360=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G360&lt;&gt;0,F360=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F360&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F360)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C360)*($E$5:$E$504=E360)*(($D$5:$D$504=D360)*(D360&lt;&gt;"")+($B$5:$B$504=B360)*(B360&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J360" s="5">
@@ -9933,11 +9961,11 @@
         <v/>
       </c>
       <c r="H361" s="5">
-        <f>IF(OR(C361="Удержание",C361="Зачёт встречного требования",C361="Неустойка заявлена"),N(E361),0)</f>
+        <f>IF(OR(C361="Удержание",C361="Зачёт встречного требования",C361="Неустойка заявлена",C361="Допработы без соглашения (спорно)"),N(E361),0)</f>
         <v/>
       </c>
       <c r="I361" s="6">
-        <f>IF(AND(B361="",C361="",D361="",E361="",F361=""),"",IF(OR(B361="",C361="",E361=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E361)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G361&lt;&gt;0,F361=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F361&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F361)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C361)*($E$5:$E$504=E361)*(($D$5:$D$504=D361)*(D361&lt;&gt;"")+($B$5:$B$504=B361)*(B361&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B361="",C361="",D361="",E361="",F361=""),"",IF(OR(B361="",C361="",E361=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E361)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H361&lt;&gt;0,F361=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G361&lt;&gt;0,F361=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F361&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F361)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C361)*($E$5:$E$504=E361)*(($D$5:$D$504=D361)*(D361&lt;&gt;"")+($B$5:$B$504=B361)*(B361&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J361" s="5">
@@ -9959,11 +9987,11 @@
         <v/>
       </c>
       <c r="H362" s="5">
-        <f>IF(OR(C362="Удержание",C362="Зачёт встречного требования",C362="Неустойка заявлена"),N(E362),0)</f>
+        <f>IF(OR(C362="Удержание",C362="Зачёт встречного требования",C362="Неустойка заявлена",C362="Допработы без соглашения (спорно)"),N(E362),0)</f>
         <v/>
       </c>
       <c r="I362" s="6">
-        <f>IF(AND(B362="",C362="",D362="",E362="",F362=""),"",IF(OR(B362="",C362="",E362=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E362)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G362&lt;&gt;0,F362=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F362&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F362)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C362)*($E$5:$E$504=E362)*(($D$5:$D$504=D362)*(D362&lt;&gt;"")+($B$5:$B$504=B362)*(B362&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B362="",C362="",D362="",E362="",F362=""),"",IF(OR(B362="",C362="",E362=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E362)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H362&lt;&gt;0,F362=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G362&lt;&gt;0,F362=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F362&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F362)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C362)*($E$5:$E$504=E362)*(($D$5:$D$504=D362)*(D362&lt;&gt;"")+($B$5:$B$504=B362)*(B362&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J362" s="5">
@@ -9985,11 +10013,11 @@
         <v/>
       </c>
       <c r="H363" s="5">
-        <f>IF(OR(C363="Удержание",C363="Зачёт встречного требования",C363="Неустойка заявлена"),N(E363),0)</f>
+        <f>IF(OR(C363="Удержание",C363="Зачёт встречного требования",C363="Неустойка заявлена",C363="Допработы без соглашения (спорно)"),N(E363),0)</f>
         <v/>
       </c>
       <c r="I363" s="6">
-        <f>IF(AND(B363="",C363="",D363="",E363="",F363=""),"",IF(OR(B363="",C363="",E363=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E363)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G363&lt;&gt;0,F363=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F363&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F363)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C363)*($E$5:$E$504=E363)*(($D$5:$D$504=D363)*(D363&lt;&gt;"")+($B$5:$B$504=B363)*(B363&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B363="",C363="",D363="",E363="",F363=""),"",IF(OR(B363="",C363="",E363=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E363)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H363&lt;&gt;0,F363=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G363&lt;&gt;0,F363=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F363&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F363)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C363)*($E$5:$E$504=E363)*(($D$5:$D$504=D363)*(D363&lt;&gt;"")+($B$5:$B$504=B363)*(B363&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J363" s="5">
@@ -10011,11 +10039,11 @@
         <v/>
       </c>
       <c r="H364" s="5">
-        <f>IF(OR(C364="Удержание",C364="Зачёт встречного требования",C364="Неустойка заявлена"),N(E364),0)</f>
+        <f>IF(OR(C364="Удержание",C364="Зачёт встречного требования",C364="Неустойка заявлена",C364="Допработы без соглашения (спорно)"),N(E364),0)</f>
         <v/>
       </c>
       <c r="I364" s="6">
-        <f>IF(AND(B364="",C364="",D364="",E364="",F364=""),"",IF(OR(B364="",C364="",E364=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E364)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G364&lt;&gt;0,F364=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F364&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F364)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C364)*($E$5:$E$504=E364)*(($D$5:$D$504=D364)*(D364&lt;&gt;"")+($B$5:$B$504=B364)*(B364&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B364="",C364="",D364="",E364="",F364=""),"",IF(OR(B364="",C364="",E364=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E364)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H364&lt;&gt;0,F364=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G364&lt;&gt;0,F364=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F364&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F364)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C364)*($E$5:$E$504=E364)*(($D$5:$D$504=D364)*(D364&lt;&gt;"")+($B$5:$B$504=B364)*(B364&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J364" s="5">
@@ -10037,11 +10065,11 @@
         <v/>
       </c>
       <c r="H365" s="5">
-        <f>IF(OR(C365="Удержание",C365="Зачёт встречного требования",C365="Неустойка заявлена"),N(E365),0)</f>
+        <f>IF(OR(C365="Удержание",C365="Зачёт встречного требования",C365="Неустойка заявлена",C365="Допработы без соглашения (спорно)"),N(E365),0)</f>
         <v/>
       </c>
       <c r="I365" s="6">
-        <f>IF(AND(B365="",C365="",D365="",E365="",F365=""),"",IF(OR(B365="",C365="",E365=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E365)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G365&lt;&gt;0,F365=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F365&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F365)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C365)*($E$5:$E$504=E365)*(($D$5:$D$504=D365)*(D365&lt;&gt;"")+($B$5:$B$504=B365)*(B365&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B365="",C365="",D365="",E365="",F365=""),"",IF(OR(B365="",C365="",E365=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E365)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H365&lt;&gt;0,F365=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G365&lt;&gt;0,F365=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F365&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F365)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C365)*($E$5:$E$504=E365)*(($D$5:$D$504=D365)*(D365&lt;&gt;"")+($B$5:$B$504=B365)*(B365&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J365" s="5">
@@ -10063,11 +10091,11 @@
         <v/>
       </c>
       <c r="H366" s="5">
-        <f>IF(OR(C366="Удержание",C366="Зачёт встречного требования",C366="Неустойка заявлена"),N(E366),0)</f>
+        <f>IF(OR(C366="Удержание",C366="Зачёт встречного требования",C366="Неустойка заявлена",C366="Допработы без соглашения (спорно)"),N(E366),0)</f>
         <v/>
       </c>
       <c r="I366" s="6">
-        <f>IF(AND(B366="",C366="",D366="",E366="",F366=""),"",IF(OR(B366="",C366="",E366=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E366)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G366&lt;&gt;0,F366=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F366&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F366)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C366)*($E$5:$E$504=E366)*(($D$5:$D$504=D366)*(D366&lt;&gt;"")+($B$5:$B$504=B366)*(B366&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B366="",C366="",D366="",E366="",F366=""),"",IF(OR(B366="",C366="",E366=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E366)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H366&lt;&gt;0,F366=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G366&lt;&gt;0,F366=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F366&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F366)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C366)*($E$5:$E$504=E366)*(($D$5:$D$504=D366)*(D366&lt;&gt;"")+($B$5:$B$504=B366)*(B366&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J366" s="5">
@@ -10089,11 +10117,11 @@
         <v/>
       </c>
       <c r="H367" s="5">
-        <f>IF(OR(C367="Удержание",C367="Зачёт встречного требования",C367="Неустойка заявлена"),N(E367),0)</f>
+        <f>IF(OR(C367="Удержание",C367="Зачёт встречного требования",C367="Неустойка заявлена",C367="Допработы без соглашения (спорно)"),N(E367),0)</f>
         <v/>
       </c>
       <c r="I367" s="6">
-        <f>IF(AND(B367="",C367="",D367="",E367="",F367=""),"",IF(OR(B367="",C367="",E367=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E367)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G367&lt;&gt;0,F367=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F367&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F367)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C367)*($E$5:$E$504=E367)*(($D$5:$D$504=D367)*(D367&lt;&gt;"")+($B$5:$B$504=B367)*(B367&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B367="",C367="",D367="",E367="",F367=""),"",IF(OR(B367="",C367="",E367=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E367)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H367&lt;&gt;0,F367=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G367&lt;&gt;0,F367=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F367&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F367)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C367)*($E$5:$E$504=E367)*(($D$5:$D$504=D367)*(D367&lt;&gt;"")+($B$5:$B$504=B367)*(B367&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J367" s="5">
@@ -10115,11 +10143,11 @@
         <v/>
       </c>
       <c r="H368" s="5">
-        <f>IF(OR(C368="Удержание",C368="Зачёт встречного требования",C368="Неустойка заявлена"),N(E368),0)</f>
+        <f>IF(OR(C368="Удержание",C368="Зачёт встречного требования",C368="Неустойка заявлена",C368="Допработы без соглашения (спорно)"),N(E368),0)</f>
         <v/>
       </c>
       <c r="I368" s="6">
-        <f>IF(AND(B368="",C368="",D368="",E368="",F368=""),"",IF(OR(B368="",C368="",E368=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E368)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G368&lt;&gt;0,F368=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F368&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F368)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C368)*($E$5:$E$504=E368)*(($D$5:$D$504=D368)*(D368&lt;&gt;"")+($B$5:$B$504=B368)*(B368&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B368="",C368="",D368="",E368="",F368=""),"",IF(OR(B368="",C368="",E368=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E368)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H368&lt;&gt;0,F368=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G368&lt;&gt;0,F368=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F368&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F368)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C368)*($E$5:$E$504=E368)*(($D$5:$D$504=D368)*(D368&lt;&gt;"")+($B$5:$B$504=B368)*(B368&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J368" s="5">
@@ -10141,11 +10169,11 @@
         <v/>
       </c>
       <c r="H369" s="5">
-        <f>IF(OR(C369="Удержание",C369="Зачёт встречного требования",C369="Неустойка заявлена"),N(E369),0)</f>
+        <f>IF(OR(C369="Удержание",C369="Зачёт встречного требования",C369="Неустойка заявлена",C369="Допработы без соглашения (спорно)"),N(E369),0)</f>
         <v/>
       </c>
       <c r="I369" s="6">
-        <f>IF(AND(B369="",C369="",D369="",E369="",F369=""),"",IF(OR(B369="",C369="",E369=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E369)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G369&lt;&gt;0,F369=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F369&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F369)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C369)*($E$5:$E$504=E369)*(($D$5:$D$504=D369)*(D369&lt;&gt;"")+($B$5:$B$504=B369)*(B369&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B369="",C369="",D369="",E369="",F369=""),"",IF(OR(B369="",C369="",E369=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E369)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H369&lt;&gt;0,F369=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G369&lt;&gt;0,F369=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F369&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F369)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C369)*($E$5:$E$504=E369)*(($D$5:$D$504=D369)*(D369&lt;&gt;"")+($B$5:$B$504=B369)*(B369&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J369" s="5">
@@ -10167,11 +10195,11 @@
         <v/>
       </c>
       <c r="H370" s="5">
-        <f>IF(OR(C370="Удержание",C370="Зачёт встречного требования",C370="Неустойка заявлена"),N(E370),0)</f>
+        <f>IF(OR(C370="Удержание",C370="Зачёт встречного требования",C370="Неустойка заявлена",C370="Допработы без соглашения (спорно)"),N(E370),0)</f>
         <v/>
       </c>
       <c r="I370" s="6">
-        <f>IF(AND(B370="",C370="",D370="",E370="",F370=""),"",IF(OR(B370="",C370="",E370=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E370)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G370&lt;&gt;0,F370=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F370&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F370)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C370)*($E$5:$E$504=E370)*(($D$5:$D$504=D370)*(D370&lt;&gt;"")+($B$5:$B$504=B370)*(B370&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B370="",C370="",D370="",E370="",F370=""),"",IF(OR(B370="",C370="",E370=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E370)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H370&lt;&gt;0,F370=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G370&lt;&gt;0,F370=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F370&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F370)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C370)*($E$5:$E$504=E370)*(($D$5:$D$504=D370)*(D370&lt;&gt;"")+($B$5:$B$504=B370)*(B370&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J370" s="5">
@@ -10193,11 +10221,11 @@
         <v/>
       </c>
       <c r="H371" s="5">
-        <f>IF(OR(C371="Удержание",C371="Зачёт встречного требования",C371="Неустойка заявлена"),N(E371),0)</f>
+        <f>IF(OR(C371="Удержание",C371="Зачёт встречного требования",C371="Неустойка заявлена",C371="Допработы без соглашения (спорно)"),N(E371),0)</f>
         <v/>
       </c>
       <c r="I371" s="6">
-        <f>IF(AND(B371="",C371="",D371="",E371="",F371=""),"",IF(OR(B371="",C371="",E371=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E371)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G371&lt;&gt;0,F371=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F371&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F371)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C371)*($E$5:$E$504=E371)*(($D$5:$D$504=D371)*(D371&lt;&gt;"")+($B$5:$B$504=B371)*(B371&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B371="",C371="",D371="",E371="",F371=""),"",IF(OR(B371="",C371="",E371=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E371)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H371&lt;&gt;0,F371=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G371&lt;&gt;0,F371=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F371&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F371)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C371)*($E$5:$E$504=E371)*(($D$5:$D$504=D371)*(D371&lt;&gt;"")+($B$5:$B$504=B371)*(B371&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J371" s="5">
@@ -10219,11 +10247,11 @@
         <v/>
       </c>
       <c r="H372" s="5">
-        <f>IF(OR(C372="Удержание",C372="Зачёт встречного требования",C372="Неустойка заявлена"),N(E372),0)</f>
+        <f>IF(OR(C372="Удержание",C372="Зачёт встречного требования",C372="Неустойка заявлена",C372="Допработы без соглашения (спорно)"),N(E372),0)</f>
         <v/>
       </c>
       <c r="I372" s="6">
-        <f>IF(AND(B372="",C372="",D372="",E372="",F372=""),"",IF(OR(B372="",C372="",E372=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E372)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G372&lt;&gt;0,F372=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F372&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F372)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C372)*($E$5:$E$504=E372)*(($D$5:$D$504=D372)*(D372&lt;&gt;"")+($B$5:$B$504=B372)*(B372&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B372="",C372="",D372="",E372="",F372=""),"",IF(OR(B372="",C372="",E372=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E372)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H372&lt;&gt;0,F372=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G372&lt;&gt;0,F372=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F372&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F372)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C372)*($E$5:$E$504=E372)*(($D$5:$D$504=D372)*(D372&lt;&gt;"")+($B$5:$B$504=B372)*(B372&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J372" s="5">
@@ -10245,11 +10273,11 @@
         <v/>
       </c>
       <c r="H373" s="5">
-        <f>IF(OR(C373="Удержание",C373="Зачёт встречного требования",C373="Неустойка заявлена"),N(E373),0)</f>
+        <f>IF(OR(C373="Удержание",C373="Зачёт встречного требования",C373="Неустойка заявлена",C373="Допработы без соглашения (спорно)"),N(E373),0)</f>
         <v/>
       </c>
       <c r="I373" s="6">
-        <f>IF(AND(B373="",C373="",D373="",E373="",F373=""),"",IF(OR(B373="",C373="",E373=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E373)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G373&lt;&gt;0,F373=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F373&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F373)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C373)*($E$5:$E$504=E373)*(($D$5:$D$504=D373)*(D373&lt;&gt;"")+($B$5:$B$504=B373)*(B373&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B373="",C373="",D373="",E373="",F373=""),"",IF(OR(B373="",C373="",E373=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E373)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H373&lt;&gt;0,F373=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G373&lt;&gt;0,F373=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F373&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F373)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C373)*($E$5:$E$504=E373)*(($D$5:$D$504=D373)*(D373&lt;&gt;"")+($B$5:$B$504=B373)*(B373&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J373" s="5">
@@ -10271,11 +10299,11 @@
         <v/>
       </c>
       <c r="H374" s="5">
-        <f>IF(OR(C374="Удержание",C374="Зачёт встречного требования",C374="Неустойка заявлена"),N(E374),0)</f>
+        <f>IF(OR(C374="Удержание",C374="Зачёт встречного требования",C374="Неустойка заявлена",C374="Допработы без соглашения (спорно)"),N(E374),0)</f>
         <v/>
       </c>
       <c r="I374" s="6">
-        <f>IF(AND(B374="",C374="",D374="",E374="",F374=""),"",IF(OR(B374="",C374="",E374=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E374)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G374&lt;&gt;0,F374=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F374&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F374)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C374)*($E$5:$E$504=E374)*(($D$5:$D$504=D374)*(D374&lt;&gt;"")+($B$5:$B$504=B374)*(B374&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B374="",C374="",D374="",E374="",F374=""),"",IF(OR(B374="",C374="",E374=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E374)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H374&lt;&gt;0,F374=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G374&lt;&gt;0,F374=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F374&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F374)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C374)*($E$5:$E$504=E374)*(($D$5:$D$504=D374)*(D374&lt;&gt;"")+($B$5:$B$504=B374)*(B374&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J374" s="5">
@@ -10297,11 +10325,11 @@
         <v/>
       </c>
       <c r="H375" s="5">
-        <f>IF(OR(C375="Удержание",C375="Зачёт встречного требования",C375="Неустойка заявлена"),N(E375),0)</f>
+        <f>IF(OR(C375="Удержание",C375="Зачёт встречного требования",C375="Неустойка заявлена",C375="Допработы без соглашения (спорно)"),N(E375),0)</f>
         <v/>
       </c>
       <c r="I375" s="6">
-        <f>IF(AND(B375="",C375="",D375="",E375="",F375=""),"",IF(OR(B375="",C375="",E375=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E375)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G375&lt;&gt;0,F375=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F375&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F375)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C375)*($E$5:$E$504=E375)*(($D$5:$D$504=D375)*(D375&lt;&gt;"")+($B$5:$B$504=B375)*(B375&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B375="",C375="",D375="",E375="",F375=""),"",IF(OR(B375="",C375="",E375=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E375)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H375&lt;&gt;0,F375=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G375&lt;&gt;0,F375=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F375&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F375)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C375)*($E$5:$E$504=E375)*(($D$5:$D$504=D375)*(D375&lt;&gt;"")+($B$5:$B$504=B375)*(B375&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J375" s="5">
@@ -10323,11 +10351,11 @@
         <v/>
       </c>
       <c r="H376" s="5">
-        <f>IF(OR(C376="Удержание",C376="Зачёт встречного требования",C376="Неустойка заявлена"),N(E376),0)</f>
+        <f>IF(OR(C376="Удержание",C376="Зачёт встречного требования",C376="Неустойка заявлена",C376="Допработы без соглашения (спорно)"),N(E376),0)</f>
         <v/>
       </c>
       <c r="I376" s="6">
-        <f>IF(AND(B376="",C376="",D376="",E376="",F376=""),"",IF(OR(B376="",C376="",E376=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E376)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G376&lt;&gt;0,F376=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F376&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F376)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C376)*($E$5:$E$504=E376)*(($D$5:$D$504=D376)*(D376&lt;&gt;"")+($B$5:$B$504=B376)*(B376&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B376="",C376="",D376="",E376="",F376=""),"",IF(OR(B376="",C376="",E376=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E376)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H376&lt;&gt;0,F376=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G376&lt;&gt;0,F376=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F376&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F376)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C376)*($E$5:$E$504=E376)*(($D$5:$D$504=D376)*(D376&lt;&gt;"")+($B$5:$B$504=B376)*(B376&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J376" s="5">
@@ -10349,11 +10377,11 @@
         <v/>
       </c>
       <c r="H377" s="5">
-        <f>IF(OR(C377="Удержание",C377="Зачёт встречного требования",C377="Неустойка заявлена"),N(E377),0)</f>
+        <f>IF(OR(C377="Удержание",C377="Зачёт встречного требования",C377="Неустойка заявлена",C377="Допработы без соглашения (спорно)"),N(E377),0)</f>
         <v/>
       </c>
       <c r="I377" s="6">
-        <f>IF(AND(B377="",C377="",D377="",E377="",F377=""),"",IF(OR(B377="",C377="",E377=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E377)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G377&lt;&gt;0,F377=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F377&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F377)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C377)*($E$5:$E$504=E377)*(($D$5:$D$504=D377)*(D377&lt;&gt;"")+($B$5:$B$504=B377)*(B377&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B377="",C377="",D377="",E377="",F377=""),"",IF(OR(B377="",C377="",E377=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E377)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H377&lt;&gt;0,F377=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G377&lt;&gt;0,F377=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F377&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F377)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C377)*($E$5:$E$504=E377)*(($D$5:$D$504=D377)*(D377&lt;&gt;"")+($B$5:$B$504=B377)*(B377&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J377" s="5">
@@ -10375,11 +10403,11 @@
         <v/>
       </c>
       <c r="H378" s="5">
-        <f>IF(OR(C378="Удержание",C378="Зачёт встречного требования",C378="Неустойка заявлена"),N(E378),0)</f>
+        <f>IF(OR(C378="Удержание",C378="Зачёт встречного требования",C378="Неустойка заявлена",C378="Допработы без соглашения (спорно)"),N(E378),0)</f>
         <v/>
       </c>
       <c r="I378" s="6">
-        <f>IF(AND(B378="",C378="",D378="",E378="",F378=""),"",IF(OR(B378="",C378="",E378=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E378)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G378&lt;&gt;0,F378=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F378&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F378)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C378)*($E$5:$E$504=E378)*(($D$5:$D$504=D378)*(D378&lt;&gt;"")+($B$5:$B$504=B378)*(B378&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B378="",C378="",D378="",E378="",F378=""),"",IF(OR(B378="",C378="",E378=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E378)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H378&lt;&gt;0,F378=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G378&lt;&gt;0,F378=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F378&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F378)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C378)*($E$5:$E$504=E378)*(($D$5:$D$504=D378)*(D378&lt;&gt;"")+($B$5:$B$504=B378)*(B378&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J378" s="5">
@@ -10401,11 +10429,11 @@
         <v/>
       </c>
       <c r="H379" s="5">
-        <f>IF(OR(C379="Удержание",C379="Зачёт встречного требования",C379="Неустойка заявлена"),N(E379),0)</f>
+        <f>IF(OR(C379="Удержание",C379="Зачёт встречного требования",C379="Неустойка заявлена",C379="Допработы без соглашения (спорно)"),N(E379),0)</f>
         <v/>
       </c>
       <c r="I379" s="6">
-        <f>IF(AND(B379="",C379="",D379="",E379="",F379=""),"",IF(OR(B379="",C379="",E379=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E379)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G379&lt;&gt;0,F379=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F379&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F379)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C379)*($E$5:$E$504=E379)*(($D$5:$D$504=D379)*(D379&lt;&gt;"")+($B$5:$B$504=B379)*(B379&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B379="",C379="",D379="",E379="",F379=""),"",IF(OR(B379="",C379="",E379=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E379)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H379&lt;&gt;0,F379=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G379&lt;&gt;0,F379=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F379&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F379)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C379)*($E$5:$E$504=E379)*(($D$5:$D$504=D379)*(D379&lt;&gt;"")+($B$5:$B$504=B379)*(B379&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J379" s="5">
@@ -10427,11 +10455,11 @@
         <v/>
       </c>
       <c r="H380" s="5">
-        <f>IF(OR(C380="Удержание",C380="Зачёт встречного требования",C380="Неустойка заявлена"),N(E380),0)</f>
+        <f>IF(OR(C380="Удержание",C380="Зачёт встречного требования",C380="Неустойка заявлена",C380="Допработы без соглашения (спорно)"),N(E380),0)</f>
         <v/>
       </c>
       <c r="I380" s="6">
-        <f>IF(AND(B380="",C380="",D380="",E380="",F380=""),"",IF(OR(B380="",C380="",E380=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E380)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G380&lt;&gt;0,F380=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F380&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F380)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C380)*($E$5:$E$504=E380)*(($D$5:$D$504=D380)*(D380&lt;&gt;"")+($B$5:$B$504=B380)*(B380&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B380="",C380="",D380="",E380="",F380=""),"",IF(OR(B380="",C380="",E380=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E380)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H380&lt;&gt;0,F380=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G380&lt;&gt;0,F380=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F380&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F380)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C380)*($E$5:$E$504=E380)*(($D$5:$D$504=D380)*(D380&lt;&gt;"")+($B$5:$B$504=B380)*(B380&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J380" s="5">
@@ -10453,11 +10481,11 @@
         <v/>
       </c>
       <c r="H381" s="5">
-        <f>IF(OR(C381="Удержание",C381="Зачёт встречного требования",C381="Неустойка заявлена"),N(E381),0)</f>
+        <f>IF(OR(C381="Удержание",C381="Зачёт встречного требования",C381="Неустойка заявлена",C381="Допработы без соглашения (спорно)"),N(E381),0)</f>
         <v/>
       </c>
       <c r="I381" s="6">
-        <f>IF(AND(B381="",C381="",D381="",E381="",F381=""),"",IF(OR(B381="",C381="",E381=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E381)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G381&lt;&gt;0,F381=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F381&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F381)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C381)*($E$5:$E$504=E381)*(($D$5:$D$504=D381)*(D381&lt;&gt;"")+($B$5:$B$504=B381)*(B381&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B381="",C381="",D381="",E381="",F381=""),"",IF(OR(B381="",C381="",E381=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E381)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H381&lt;&gt;0,F381=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G381&lt;&gt;0,F381=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F381&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F381)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C381)*($E$5:$E$504=E381)*(($D$5:$D$504=D381)*(D381&lt;&gt;"")+($B$5:$B$504=B381)*(B381&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J381" s="5">
@@ -10479,11 +10507,11 @@
         <v/>
       </c>
       <c r="H382" s="5">
-        <f>IF(OR(C382="Удержание",C382="Зачёт встречного требования",C382="Неустойка заявлена"),N(E382),0)</f>
+        <f>IF(OR(C382="Удержание",C382="Зачёт встречного требования",C382="Неустойка заявлена",C382="Допработы без соглашения (спорно)"),N(E382),0)</f>
         <v/>
       </c>
       <c r="I382" s="6">
-        <f>IF(AND(B382="",C382="",D382="",E382="",F382=""),"",IF(OR(B382="",C382="",E382=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E382)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G382&lt;&gt;0,F382=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F382&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F382)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C382)*($E$5:$E$504=E382)*(($D$5:$D$504=D382)*(D382&lt;&gt;"")+($B$5:$B$504=B382)*(B382&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B382="",C382="",D382="",E382="",F382=""),"",IF(OR(B382="",C382="",E382=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E382)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H382&lt;&gt;0,F382=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G382&lt;&gt;0,F382=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F382&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F382)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C382)*($E$5:$E$504=E382)*(($D$5:$D$504=D382)*(D382&lt;&gt;"")+($B$5:$B$504=B382)*(B382&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J382" s="5">
@@ -10505,11 +10533,11 @@
         <v/>
       </c>
       <c r="H383" s="5">
-        <f>IF(OR(C383="Удержание",C383="Зачёт встречного требования",C383="Неустойка заявлена"),N(E383),0)</f>
+        <f>IF(OR(C383="Удержание",C383="Зачёт встречного требования",C383="Неустойка заявлена",C383="Допработы без соглашения (спорно)"),N(E383),0)</f>
         <v/>
       </c>
       <c r="I383" s="6">
-        <f>IF(AND(B383="",C383="",D383="",E383="",F383=""),"",IF(OR(B383="",C383="",E383=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E383)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G383&lt;&gt;0,F383=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F383&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F383)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C383)*($E$5:$E$504=E383)*(($D$5:$D$504=D383)*(D383&lt;&gt;"")+($B$5:$B$504=B383)*(B383&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B383="",C383="",D383="",E383="",F383=""),"",IF(OR(B383="",C383="",E383=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E383)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H383&lt;&gt;0,F383=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G383&lt;&gt;0,F383=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F383&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F383)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C383)*($E$5:$E$504=E383)*(($D$5:$D$504=D383)*(D383&lt;&gt;"")+($B$5:$B$504=B383)*(B383&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J383" s="5">
@@ -10531,11 +10559,11 @@
         <v/>
       </c>
       <c r="H384" s="5">
-        <f>IF(OR(C384="Удержание",C384="Зачёт встречного требования",C384="Неустойка заявлена"),N(E384),0)</f>
+        <f>IF(OR(C384="Удержание",C384="Зачёт встречного требования",C384="Неустойка заявлена",C384="Допработы без соглашения (спорно)"),N(E384),0)</f>
         <v/>
       </c>
       <c r="I384" s="6">
-        <f>IF(AND(B384="",C384="",D384="",E384="",F384=""),"",IF(OR(B384="",C384="",E384=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E384)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G384&lt;&gt;0,F384=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F384&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F384)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C384)*($E$5:$E$504=E384)*(($D$5:$D$504=D384)*(D384&lt;&gt;"")+($B$5:$B$504=B384)*(B384&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B384="",C384="",D384="",E384="",F384=""),"",IF(OR(B384="",C384="",E384=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E384)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H384&lt;&gt;0,F384=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G384&lt;&gt;0,F384=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F384&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F384)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C384)*($E$5:$E$504=E384)*(($D$5:$D$504=D384)*(D384&lt;&gt;"")+($B$5:$B$504=B384)*(B384&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J384" s="5">
@@ -10557,11 +10585,11 @@
         <v/>
       </c>
       <c r="H385" s="5">
-        <f>IF(OR(C385="Удержание",C385="Зачёт встречного требования",C385="Неустойка заявлена"),N(E385),0)</f>
+        <f>IF(OR(C385="Удержание",C385="Зачёт встречного требования",C385="Неустойка заявлена",C385="Допработы без соглашения (спорно)"),N(E385),0)</f>
         <v/>
       </c>
       <c r="I385" s="6">
-        <f>IF(AND(B385="",C385="",D385="",E385="",F385=""),"",IF(OR(B385="",C385="",E385=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E385)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G385&lt;&gt;0,F385=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F385&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F385)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C385)*($E$5:$E$504=E385)*(($D$5:$D$504=D385)*(D385&lt;&gt;"")+($B$5:$B$504=B385)*(B385&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B385="",C385="",D385="",E385="",F385=""),"",IF(OR(B385="",C385="",E385=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E385)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H385&lt;&gt;0,F385=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G385&lt;&gt;0,F385=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F385&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F385)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C385)*($E$5:$E$504=E385)*(($D$5:$D$504=D385)*(D385&lt;&gt;"")+($B$5:$B$504=B385)*(B385&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J385" s="5">
@@ -10583,11 +10611,11 @@
         <v/>
       </c>
       <c r="H386" s="5">
-        <f>IF(OR(C386="Удержание",C386="Зачёт встречного требования",C386="Неустойка заявлена"),N(E386),0)</f>
+        <f>IF(OR(C386="Удержание",C386="Зачёт встречного требования",C386="Неустойка заявлена",C386="Допработы без соглашения (спорно)"),N(E386),0)</f>
         <v/>
       </c>
       <c r="I386" s="6">
-        <f>IF(AND(B386="",C386="",D386="",E386="",F386=""),"",IF(OR(B386="",C386="",E386=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E386)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G386&lt;&gt;0,F386=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F386&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F386)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C386)*($E$5:$E$504=E386)*(($D$5:$D$504=D386)*(D386&lt;&gt;"")+($B$5:$B$504=B386)*(B386&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B386="",C386="",D386="",E386="",F386=""),"",IF(OR(B386="",C386="",E386=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E386)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H386&lt;&gt;0,F386=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G386&lt;&gt;0,F386=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F386&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F386)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C386)*($E$5:$E$504=E386)*(($D$5:$D$504=D386)*(D386&lt;&gt;"")+($B$5:$B$504=B386)*(B386&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J386" s="5">
@@ -10609,11 +10637,11 @@
         <v/>
       </c>
       <c r="H387" s="5">
-        <f>IF(OR(C387="Удержание",C387="Зачёт встречного требования",C387="Неустойка заявлена"),N(E387),0)</f>
+        <f>IF(OR(C387="Удержание",C387="Зачёт встречного требования",C387="Неустойка заявлена",C387="Допработы без соглашения (спорно)"),N(E387),0)</f>
         <v/>
       </c>
       <c r="I387" s="6">
-        <f>IF(AND(B387="",C387="",D387="",E387="",F387=""),"",IF(OR(B387="",C387="",E387=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E387)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G387&lt;&gt;0,F387=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F387&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F387)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C387)*($E$5:$E$504=E387)*(($D$5:$D$504=D387)*(D387&lt;&gt;"")+($B$5:$B$504=B387)*(B387&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B387="",C387="",D387="",E387="",F387=""),"",IF(OR(B387="",C387="",E387=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E387)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H387&lt;&gt;0,F387=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G387&lt;&gt;0,F387=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F387&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F387)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C387)*($E$5:$E$504=E387)*(($D$5:$D$504=D387)*(D387&lt;&gt;"")+($B$5:$B$504=B387)*(B387&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J387" s="5">
@@ -10635,11 +10663,11 @@
         <v/>
       </c>
       <c r="H388" s="5">
-        <f>IF(OR(C388="Удержание",C388="Зачёт встречного требования",C388="Неустойка заявлена"),N(E388),0)</f>
+        <f>IF(OR(C388="Удержание",C388="Зачёт встречного требования",C388="Неустойка заявлена",C388="Допработы без соглашения (спорно)"),N(E388),0)</f>
         <v/>
       </c>
       <c r="I388" s="6">
-        <f>IF(AND(B388="",C388="",D388="",E388="",F388=""),"",IF(OR(B388="",C388="",E388=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E388)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G388&lt;&gt;0,F388=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F388&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F388)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C388)*($E$5:$E$504=E388)*(($D$5:$D$504=D388)*(D388&lt;&gt;"")+($B$5:$B$504=B388)*(B388&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B388="",C388="",D388="",E388="",F388=""),"",IF(OR(B388="",C388="",E388=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E388)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H388&lt;&gt;0,F388=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G388&lt;&gt;0,F388=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F388&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F388)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C388)*($E$5:$E$504=E388)*(($D$5:$D$504=D388)*(D388&lt;&gt;"")+($B$5:$B$504=B388)*(B388&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J388" s="5">
@@ -10661,11 +10689,11 @@
         <v/>
       </c>
       <c r="H389" s="5">
-        <f>IF(OR(C389="Удержание",C389="Зачёт встречного требования",C389="Неустойка заявлена"),N(E389),0)</f>
+        <f>IF(OR(C389="Удержание",C389="Зачёт встречного требования",C389="Неустойка заявлена",C389="Допработы без соглашения (спорно)"),N(E389),0)</f>
         <v/>
       </c>
       <c r="I389" s="6">
-        <f>IF(AND(B389="",C389="",D389="",E389="",F389=""),"",IF(OR(B389="",C389="",E389=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E389)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G389&lt;&gt;0,F389=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F389&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F389)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C389)*($E$5:$E$504=E389)*(($D$5:$D$504=D389)*(D389&lt;&gt;"")+($B$5:$B$504=B389)*(B389&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B389="",C389="",D389="",E389="",F389=""),"",IF(OR(B389="",C389="",E389=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E389)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H389&lt;&gt;0,F389=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G389&lt;&gt;0,F389=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F389&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F389)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C389)*($E$5:$E$504=E389)*(($D$5:$D$504=D389)*(D389&lt;&gt;"")+($B$5:$B$504=B389)*(B389&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J389" s="5">
@@ -10687,11 +10715,11 @@
         <v/>
       </c>
       <c r="H390" s="5">
-        <f>IF(OR(C390="Удержание",C390="Зачёт встречного требования",C390="Неустойка заявлена"),N(E390),0)</f>
+        <f>IF(OR(C390="Удержание",C390="Зачёт встречного требования",C390="Неустойка заявлена",C390="Допработы без соглашения (спорно)"),N(E390),0)</f>
         <v/>
       </c>
       <c r="I390" s="6">
-        <f>IF(AND(B390="",C390="",D390="",E390="",F390=""),"",IF(OR(B390="",C390="",E390=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E390)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G390&lt;&gt;0,F390=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F390&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F390)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C390)*($E$5:$E$504=E390)*(($D$5:$D$504=D390)*(D390&lt;&gt;"")+($B$5:$B$504=B390)*(B390&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B390="",C390="",D390="",E390="",F390=""),"",IF(OR(B390="",C390="",E390=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E390)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H390&lt;&gt;0,F390=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G390&lt;&gt;0,F390=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F390&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F390)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C390)*($E$5:$E$504=E390)*(($D$5:$D$504=D390)*(D390&lt;&gt;"")+($B$5:$B$504=B390)*(B390&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J390" s="5">
@@ -10713,11 +10741,11 @@
         <v/>
       </c>
       <c r="H391" s="5">
-        <f>IF(OR(C391="Удержание",C391="Зачёт встречного требования",C391="Неустойка заявлена"),N(E391),0)</f>
+        <f>IF(OR(C391="Удержание",C391="Зачёт встречного требования",C391="Неустойка заявлена",C391="Допработы без соглашения (спорно)"),N(E391),0)</f>
         <v/>
       </c>
       <c r="I391" s="6">
-        <f>IF(AND(B391="",C391="",D391="",E391="",F391=""),"",IF(OR(B391="",C391="",E391=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E391)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G391&lt;&gt;0,F391=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F391&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F391)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C391)*($E$5:$E$504=E391)*(($D$5:$D$504=D391)*(D391&lt;&gt;"")+($B$5:$B$504=B391)*(B391&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B391="",C391="",D391="",E391="",F391=""),"",IF(OR(B391="",C391="",E391=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E391)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H391&lt;&gt;0,F391=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G391&lt;&gt;0,F391=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F391&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F391)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C391)*($E$5:$E$504=E391)*(($D$5:$D$504=D391)*(D391&lt;&gt;"")+($B$5:$B$504=B391)*(B391&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J391" s="5">
@@ -10739,11 +10767,11 @@
         <v/>
       </c>
       <c r="H392" s="5">
-        <f>IF(OR(C392="Удержание",C392="Зачёт встречного требования",C392="Неустойка заявлена"),N(E392),0)</f>
+        <f>IF(OR(C392="Удержание",C392="Зачёт встречного требования",C392="Неустойка заявлена",C392="Допработы без соглашения (спорно)"),N(E392),0)</f>
         <v/>
       </c>
       <c r="I392" s="6">
-        <f>IF(AND(B392="",C392="",D392="",E392="",F392=""),"",IF(OR(B392="",C392="",E392=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E392)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G392&lt;&gt;0,F392=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F392&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F392)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C392)*($E$5:$E$504=E392)*(($D$5:$D$504=D392)*(D392&lt;&gt;"")+($B$5:$B$504=B392)*(B392&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B392="",C392="",D392="",E392="",F392=""),"",IF(OR(B392="",C392="",E392=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E392)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H392&lt;&gt;0,F392=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G392&lt;&gt;0,F392=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F392&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F392)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C392)*($E$5:$E$504=E392)*(($D$5:$D$504=D392)*(D392&lt;&gt;"")+($B$5:$B$504=B392)*(B392&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J392" s="5">
@@ -10765,11 +10793,11 @@
         <v/>
       </c>
       <c r="H393" s="5">
-        <f>IF(OR(C393="Удержание",C393="Зачёт встречного требования",C393="Неустойка заявлена"),N(E393),0)</f>
+        <f>IF(OR(C393="Удержание",C393="Зачёт встречного требования",C393="Неустойка заявлена",C393="Допработы без соглашения (спорно)"),N(E393),0)</f>
         <v/>
       </c>
       <c r="I393" s="6">
-        <f>IF(AND(B393="",C393="",D393="",E393="",F393=""),"",IF(OR(B393="",C393="",E393=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E393)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G393&lt;&gt;0,F393=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F393&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F393)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C393)*($E$5:$E$504=E393)*(($D$5:$D$504=D393)*(D393&lt;&gt;"")+($B$5:$B$504=B393)*(B393&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B393="",C393="",D393="",E393="",F393=""),"",IF(OR(B393="",C393="",E393=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E393)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H393&lt;&gt;0,F393=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G393&lt;&gt;0,F393=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F393&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F393)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C393)*($E$5:$E$504=E393)*(($D$5:$D$504=D393)*(D393&lt;&gt;"")+($B$5:$B$504=B393)*(B393&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J393" s="5">
@@ -10791,11 +10819,11 @@
         <v/>
       </c>
       <c r="H394" s="5">
-        <f>IF(OR(C394="Удержание",C394="Зачёт встречного требования",C394="Неустойка заявлена"),N(E394),0)</f>
+        <f>IF(OR(C394="Удержание",C394="Зачёт встречного требования",C394="Неустойка заявлена",C394="Допработы без соглашения (спорно)"),N(E394),0)</f>
         <v/>
       </c>
       <c r="I394" s="6">
-        <f>IF(AND(B394="",C394="",D394="",E394="",F394=""),"",IF(OR(B394="",C394="",E394=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E394)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G394&lt;&gt;0,F394=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F394&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F394)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C394)*($E$5:$E$504=E394)*(($D$5:$D$504=D394)*(D394&lt;&gt;"")+($B$5:$B$504=B394)*(B394&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B394="",C394="",D394="",E394="",F394=""),"",IF(OR(B394="",C394="",E394=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E394)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H394&lt;&gt;0,F394=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G394&lt;&gt;0,F394=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F394&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F394)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C394)*($E$5:$E$504=E394)*(($D$5:$D$504=D394)*(D394&lt;&gt;"")+($B$5:$B$504=B394)*(B394&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J394" s="5">
@@ -10817,11 +10845,11 @@
         <v/>
       </c>
       <c r="H395" s="5">
-        <f>IF(OR(C395="Удержание",C395="Зачёт встречного требования",C395="Неустойка заявлена"),N(E395),0)</f>
+        <f>IF(OR(C395="Удержание",C395="Зачёт встречного требования",C395="Неустойка заявлена",C395="Допработы без соглашения (спорно)"),N(E395),0)</f>
         <v/>
       </c>
       <c r="I395" s="6">
-        <f>IF(AND(B395="",C395="",D395="",E395="",F395=""),"",IF(OR(B395="",C395="",E395=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E395)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G395&lt;&gt;0,F395=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F395&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F395)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C395)*($E$5:$E$504=E395)*(($D$5:$D$504=D395)*(D395&lt;&gt;"")+($B$5:$B$504=B395)*(B395&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B395="",C395="",D395="",E395="",F395=""),"",IF(OR(B395="",C395="",E395=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E395)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H395&lt;&gt;0,F395=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G395&lt;&gt;0,F395=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F395&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F395)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C395)*($E$5:$E$504=E395)*(($D$5:$D$504=D395)*(D395&lt;&gt;"")+($B$5:$B$504=B395)*(B395&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J395" s="5">
@@ -10843,11 +10871,11 @@
         <v/>
       </c>
       <c r="H396" s="5">
-        <f>IF(OR(C396="Удержание",C396="Зачёт встречного требования",C396="Неустойка заявлена"),N(E396),0)</f>
+        <f>IF(OR(C396="Удержание",C396="Зачёт встречного требования",C396="Неустойка заявлена",C396="Допработы без соглашения (спорно)"),N(E396),0)</f>
         <v/>
       </c>
       <c r="I396" s="6">
-        <f>IF(AND(B396="",C396="",D396="",E396="",F396=""),"",IF(OR(B396="",C396="",E396=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E396)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G396&lt;&gt;0,F396=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F396&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F396)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C396)*($E$5:$E$504=E396)*(($D$5:$D$504=D396)*(D396&lt;&gt;"")+($B$5:$B$504=B396)*(B396&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B396="",C396="",D396="",E396="",F396=""),"",IF(OR(B396="",C396="",E396=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E396)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H396&lt;&gt;0,F396=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G396&lt;&gt;0,F396=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F396&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F396)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C396)*($E$5:$E$504=E396)*(($D$5:$D$504=D396)*(D396&lt;&gt;"")+($B$5:$B$504=B396)*(B396&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J396" s="5">
@@ -10869,11 +10897,11 @@
         <v/>
       </c>
       <c r="H397" s="5">
-        <f>IF(OR(C397="Удержание",C397="Зачёт встречного требования",C397="Неустойка заявлена"),N(E397),0)</f>
+        <f>IF(OR(C397="Удержание",C397="Зачёт встречного требования",C397="Неустойка заявлена",C397="Допработы без соглашения (спорно)"),N(E397),0)</f>
         <v/>
       </c>
       <c r="I397" s="6">
-        <f>IF(AND(B397="",C397="",D397="",E397="",F397=""),"",IF(OR(B397="",C397="",E397=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E397)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G397&lt;&gt;0,F397=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F397&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F397)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C397)*($E$5:$E$504=E397)*(($D$5:$D$504=D397)*(D397&lt;&gt;"")+($B$5:$B$504=B397)*(B397&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B397="",C397="",D397="",E397="",F397=""),"",IF(OR(B397="",C397="",E397=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E397)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H397&lt;&gt;0,F397=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G397&lt;&gt;0,F397=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F397&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F397)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C397)*($E$5:$E$504=E397)*(($D$5:$D$504=D397)*(D397&lt;&gt;"")+($B$5:$B$504=B397)*(B397&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J397" s="5">
@@ -10895,11 +10923,11 @@
         <v/>
       </c>
       <c r="H398" s="5">
-        <f>IF(OR(C398="Удержание",C398="Зачёт встречного требования",C398="Неустойка заявлена"),N(E398),0)</f>
+        <f>IF(OR(C398="Удержание",C398="Зачёт встречного требования",C398="Неустойка заявлена",C398="Допработы без соглашения (спорно)"),N(E398),0)</f>
         <v/>
       </c>
       <c r="I398" s="6">
-        <f>IF(AND(B398="",C398="",D398="",E398="",F398=""),"",IF(OR(B398="",C398="",E398=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E398)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G398&lt;&gt;0,F398=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F398&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F398)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C398)*($E$5:$E$504=E398)*(($D$5:$D$504=D398)*(D398&lt;&gt;"")+($B$5:$B$504=B398)*(B398&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B398="",C398="",D398="",E398="",F398=""),"",IF(OR(B398="",C398="",E398=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E398)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H398&lt;&gt;0,F398=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G398&lt;&gt;0,F398=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F398&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F398)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C398)*($E$5:$E$504=E398)*(($D$5:$D$504=D398)*(D398&lt;&gt;"")+($B$5:$B$504=B398)*(B398&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J398" s="5">
@@ -10921,11 +10949,11 @@
         <v/>
       </c>
       <c r="H399" s="5">
-        <f>IF(OR(C399="Удержание",C399="Зачёт встречного требования",C399="Неустойка заявлена"),N(E399),0)</f>
+        <f>IF(OR(C399="Удержание",C399="Зачёт встречного требования",C399="Неустойка заявлена",C399="Допработы без соглашения (спорно)"),N(E399),0)</f>
         <v/>
       </c>
       <c r="I399" s="6">
-        <f>IF(AND(B399="",C399="",D399="",E399="",F399=""),"",IF(OR(B399="",C399="",E399=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E399)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G399&lt;&gt;0,F399=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F399&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F399)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C399)*($E$5:$E$504=E399)*(($D$5:$D$504=D399)*(D399&lt;&gt;"")+($B$5:$B$504=B399)*(B399&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B399="",C399="",D399="",E399="",F399=""),"",IF(OR(B399="",C399="",E399=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E399)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H399&lt;&gt;0,F399=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G399&lt;&gt;0,F399=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F399&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F399)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C399)*($E$5:$E$504=E399)*(($D$5:$D$504=D399)*(D399&lt;&gt;"")+($B$5:$B$504=B399)*(B399&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J399" s="5">
@@ -10947,11 +10975,11 @@
         <v/>
       </c>
       <c r="H400" s="5">
-        <f>IF(OR(C400="Удержание",C400="Зачёт встречного требования",C400="Неустойка заявлена"),N(E400),0)</f>
+        <f>IF(OR(C400="Удержание",C400="Зачёт встречного требования",C400="Неустойка заявлена",C400="Допработы без соглашения (спорно)"),N(E400),0)</f>
         <v/>
       </c>
       <c r="I400" s="6">
-        <f>IF(AND(B400="",C400="",D400="",E400="",F400=""),"",IF(OR(B400="",C400="",E400=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E400)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G400&lt;&gt;0,F400=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F400&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F400)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C400)*($E$5:$E$504=E400)*(($D$5:$D$504=D400)*(D400&lt;&gt;"")+($B$5:$B$504=B400)*(B400&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B400="",C400="",D400="",E400="",F400=""),"",IF(OR(B400="",C400="",E400=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E400)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H400&lt;&gt;0,F400=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G400&lt;&gt;0,F400=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F400&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F400)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C400)*($E$5:$E$504=E400)*(($D$5:$D$504=D400)*(D400&lt;&gt;"")+($B$5:$B$504=B400)*(B400&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J400" s="5">
@@ -10973,11 +11001,11 @@
         <v/>
       </c>
       <c r="H401" s="5">
-        <f>IF(OR(C401="Удержание",C401="Зачёт встречного требования",C401="Неустойка заявлена"),N(E401),0)</f>
+        <f>IF(OR(C401="Удержание",C401="Зачёт встречного требования",C401="Неустойка заявлена",C401="Допработы без соглашения (спорно)"),N(E401),0)</f>
         <v/>
       </c>
       <c r="I401" s="6">
-        <f>IF(AND(B401="",C401="",D401="",E401="",F401=""),"",IF(OR(B401="",C401="",E401=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E401)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G401&lt;&gt;0,F401=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F401&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F401)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C401)*($E$5:$E$504=E401)*(($D$5:$D$504=D401)*(D401&lt;&gt;"")+($B$5:$B$504=B401)*(B401&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B401="",C401="",D401="",E401="",F401=""),"",IF(OR(B401="",C401="",E401=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E401)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H401&lt;&gt;0,F401=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G401&lt;&gt;0,F401=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F401&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F401)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C401)*($E$5:$E$504=E401)*(($D$5:$D$504=D401)*(D401&lt;&gt;"")+($B$5:$B$504=B401)*(B401&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J401" s="5">
@@ -10999,11 +11027,11 @@
         <v/>
       </c>
       <c r="H402" s="5">
-        <f>IF(OR(C402="Удержание",C402="Зачёт встречного требования",C402="Неустойка заявлена"),N(E402),0)</f>
+        <f>IF(OR(C402="Удержание",C402="Зачёт встречного требования",C402="Неустойка заявлена",C402="Допработы без соглашения (спорно)"),N(E402),0)</f>
         <v/>
       </c>
       <c r="I402" s="6">
-        <f>IF(AND(B402="",C402="",D402="",E402="",F402=""),"",IF(OR(B402="",C402="",E402=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E402)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G402&lt;&gt;0,F402=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F402&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F402)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C402)*($E$5:$E$504=E402)*(($D$5:$D$504=D402)*(D402&lt;&gt;"")+($B$5:$B$504=B402)*(B402&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B402="",C402="",D402="",E402="",F402=""),"",IF(OR(B402="",C402="",E402=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E402)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H402&lt;&gt;0,F402=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G402&lt;&gt;0,F402=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F402&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F402)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C402)*($E$5:$E$504=E402)*(($D$5:$D$504=D402)*(D402&lt;&gt;"")+($B$5:$B$504=B402)*(B402&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J402" s="5">
@@ -11025,11 +11053,11 @@
         <v/>
       </c>
       <c r="H403" s="5">
-        <f>IF(OR(C403="Удержание",C403="Зачёт встречного требования",C403="Неустойка заявлена"),N(E403),0)</f>
+        <f>IF(OR(C403="Удержание",C403="Зачёт встречного требования",C403="Неустойка заявлена",C403="Допработы без соглашения (спорно)"),N(E403),0)</f>
         <v/>
       </c>
       <c r="I403" s="6">
-        <f>IF(AND(B403="",C403="",D403="",E403="",F403=""),"",IF(OR(B403="",C403="",E403=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E403)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G403&lt;&gt;0,F403=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F403&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F403)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C403)*($E$5:$E$504=E403)*(($D$5:$D$504=D403)*(D403&lt;&gt;"")+($B$5:$B$504=B403)*(B403&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B403="",C403="",D403="",E403="",F403=""),"",IF(OR(B403="",C403="",E403=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E403)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H403&lt;&gt;0,F403=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G403&lt;&gt;0,F403=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F403&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F403)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C403)*($E$5:$E$504=E403)*(($D$5:$D$504=D403)*(D403&lt;&gt;"")+($B$5:$B$504=B403)*(B403&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J403" s="5">
@@ -11051,11 +11079,11 @@
         <v/>
       </c>
       <c r="H404" s="5">
-        <f>IF(OR(C404="Удержание",C404="Зачёт встречного требования",C404="Неустойка заявлена"),N(E404),0)</f>
+        <f>IF(OR(C404="Удержание",C404="Зачёт встречного требования",C404="Неустойка заявлена",C404="Допработы без соглашения (спорно)"),N(E404),0)</f>
         <v/>
       </c>
       <c r="I404" s="6">
-        <f>IF(AND(B404="",C404="",D404="",E404="",F404=""),"",IF(OR(B404="",C404="",E404=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E404)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G404&lt;&gt;0,F404=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F404&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F404)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C404)*($E$5:$E$504=E404)*(($D$5:$D$504=D404)*(D404&lt;&gt;"")+($B$5:$B$504=B404)*(B404&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B404="",C404="",D404="",E404="",F404=""),"",IF(OR(B404="",C404="",E404=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E404)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H404&lt;&gt;0,F404=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G404&lt;&gt;0,F404=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F404&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F404)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C404)*($E$5:$E$504=E404)*(($D$5:$D$504=D404)*(D404&lt;&gt;"")+($B$5:$B$504=B404)*(B404&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J404" s="5">
@@ -11077,11 +11105,11 @@
         <v/>
       </c>
       <c r="H405" s="5">
-        <f>IF(OR(C405="Удержание",C405="Зачёт встречного требования",C405="Неустойка заявлена"),N(E405),0)</f>
+        <f>IF(OR(C405="Удержание",C405="Зачёт встречного требования",C405="Неустойка заявлена",C405="Допработы без соглашения (спорно)"),N(E405),0)</f>
         <v/>
       </c>
       <c r="I405" s="6">
-        <f>IF(AND(B405="",C405="",D405="",E405="",F405=""),"",IF(OR(B405="",C405="",E405=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E405)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G405&lt;&gt;0,F405=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F405&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F405)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C405)*($E$5:$E$504=E405)*(($D$5:$D$504=D405)*(D405&lt;&gt;"")+($B$5:$B$504=B405)*(B405&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B405="",C405="",D405="",E405="",F405=""),"",IF(OR(B405="",C405="",E405=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E405)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H405&lt;&gt;0,F405=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G405&lt;&gt;0,F405=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F405&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F405)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C405)*($E$5:$E$504=E405)*(($D$5:$D$504=D405)*(D405&lt;&gt;"")+($B$5:$B$504=B405)*(B405&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J405" s="5">
@@ -11103,11 +11131,11 @@
         <v/>
       </c>
       <c r="H406" s="5">
-        <f>IF(OR(C406="Удержание",C406="Зачёт встречного требования",C406="Неустойка заявлена"),N(E406),0)</f>
+        <f>IF(OR(C406="Удержание",C406="Зачёт встречного требования",C406="Неустойка заявлена",C406="Допработы без соглашения (спорно)"),N(E406),0)</f>
         <v/>
       </c>
       <c r="I406" s="6">
-        <f>IF(AND(B406="",C406="",D406="",E406="",F406=""),"",IF(OR(B406="",C406="",E406=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E406)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G406&lt;&gt;0,F406=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F406&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F406)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C406)*($E$5:$E$504=E406)*(($D$5:$D$504=D406)*(D406&lt;&gt;"")+($B$5:$B$504=B406)*(B406&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B406="",C406="",D406="",E406="",F406=""),"",IF(OR(B406="",C406="",E406=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E406)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H406&lt;&gt;0,F406=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G406&lt;&gt;0,F406=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F406&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F406)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C406)*($E$5:$E$504=E406)*(($D$5:$D$504=D406)*(D406&lt;&gt;"")+($B$5:$B$504=B406)*(B406&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J406" s="5">
@@ -11129,11 +11157,11 @@
         <v/>
       </c>
       <c r="H407" s="5">
-        <f>IF(OR(C407="Удержание",C407="Зачёт встречного требования",C407="Неустойка заявлена"),N(E407),0)</f>
+        <f>IF(OR(C407="Удержание",C407="Зачёт встречного требования",C407="Неустойка заявлена",C407="Допработы без соглашения (спорно)"),N(E407),0)</f>
         <v/>
       </c>
       <c r="I407" s="6">
-        <f>IF(AND(B407="",C407="",D407="",E407="",F407=""),"",IF(OR(B407="",C407="",E407=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E407)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G407&lt;&gt;0,F407=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F407&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F407)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C407)*($E$5:$E$504=E407)*(($D$5:$D$504=D407)*(D407&lt;&gt;"")+($B$5:$B$504=B407)*(B407&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B407="",C407="",D407="",E407="",F407=""),"",IF(OR(B407="",C407="",E407=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E407)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H407&lt;&gt;0,F407=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G407&lt;&gt;0,F407=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F407&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F407)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C407)*($E$5:$E$504=E407)*(($D$5:$D$504=D407)*(D407&lt;&gt;"")+($B$5:$B$504=B407)*(B407&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J407" s="5">
@@ -11155,11 +11183,11 @@
         <v/>
       </c>
       <c r="H408" s="5">
-        <f>IF(OR(C408="Удержание",C408="Зачёт встречного требования",C408="Неустойка заявлена"),N(E408),0)</f>
+        <f>IF(OR(C408="Удержание",C408="Зачёт встречного требования",C408="Неустойка заявлена",C408="Допработы без соглашения (спорно)"),N(E408),0)</f>
         <v/>
       </c>
       <c r="I408" s="6">
-        <f>IF(AND(B408="",C408="",D408="",E408="",F408=""),"",IF(OR(B408="",C408="",E408=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E408)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G408&lt;&gt;0,F408=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F408&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F408)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C408)*($E$5:$E$504=E408)*(($D$5:$D$504=D408)*(D408&lt;&gt;"")+($B$5:$B$504=B408)*(B408&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B408="",C408="",D408="",E408="",F408=""),"",IF(OR(B408="",C408="",E408=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E408)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H408&lt;&gt;0,F408=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G408&lt;&gt;0,F408=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F408&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F408)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C408)*($E$5:$E$504=E408)*(($D$5:$D$504=D408)*(D408&lt;&gt;"")+($B$5:$B$504=B408)*(B408&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J408" s="5">
@@ -11181,11 +11209,11 @@
         <v/>
       </c>
       <c r="H409" s="5">
-        <f>IF(OR(C409="Удержание",C409="Зачёт встречного требования",C409="Неустойка заявлена"),N(E409),0)</f>
+        <f>IF(OR(C409="Удержание",C409="Зачёт встречного требования",C409="Неустойка заявлена",C409="Допработы без соглашения (спорно)"),N(E409),0)</f>
         <v/>
       </c>
       <c r="I409" s="6">
-        <f>IF(AND(B409="",C409="",D409="",E409="",F409=""),"",IF(OR(B409="",C409="",E409=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E409)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G409&lt;&gt;0,F409=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F409&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F409)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C409)*($E$5:$E$504=E409)*(($D$5:$D$504=D409)*(D409&lt;&gt;"")+($B$5:$B$504=B409)*(B409&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B409="",C409="",D409="",E409="",F409=""),"",IF(OR(B409="",C409="",E409=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E409)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H409&lt;&gt;0,F409=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G409&lt;&gt;0,F409=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F409&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F409)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C409)*($E$5:$E$504=E409)*(($D$5:$D$504=D409)*(D409&lt;&gt;"")+($B$5:$B$504=B409)*(B409&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J409" s="5">
@@ -11207,11 +11235,11 @@
         <v/>
       </c>
       <c r="H410" s="5">
-        <f>IF(OR(C410="Удержание",C410="Зачёт встречного требования",C410="Неустойка заявлена"),N(E410),0)</f>
+        <f>IF(OR(C410="Удержание",C410="Зачёт встречного требования",C410="Неустойка заявлена",C410="Допработы без соглашения (спорно)"),N(E410),0)</f>
         <v/>
       </c>
       <c r="I410" s="6">
-        <f>IF(AND(B410="",C410="",D410="",E410="",F410=""),"",IF(OR(B410="",C410="",E410=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E410)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G410&lt;&gt;0,F410=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F410&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F410)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C410)*($E$5:$E$504=E410)*(($D$5:$D$504=D410)*(D410&lt;&gt;"")+($B$5:$B$504=B410)*(B410&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B410="",C410="",D410="",E410="",F410=""),"",IF(OR(B410="",C410="",E410=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E410)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H410&lt;&gt;0,F410=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G410&lt;&gt;0,F410=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F410&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F410)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C410)*($E$5:$E$504=E410)*(($D$5:$D$504=D410)*(D410&lt;&gt;"")+($B$5:$B$504=B410)*(B410&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J410" s="5">
@@ -11233,11 +11261,11 @@
         <v/>
       </c>
       <c r="H411" s="5">
-        <f>IF(OR(C411="Удержание",C411="Зачёт встречного требования",C411="Неустойка заявлена"),N(E411),0)</f>
+        <f>IF(OR(C411="Удержание",C411="Зачёт встречного требования",C411="Неустойка заявлена",C411="Допработы без соглашения (спорно)"),N(E411),0)</f>
         <v/>
       </c>
       <c r="I411" s="6">
-        <f>IF(AND(B411="",C411="",D411="",E411="",F411=""),"",IF(OR(B411="",C411="",E411=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E411)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G411&lt;&gt;0,F411=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F411&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F411)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C411)*($E$5:$E$504=E411)*(($D$5:$D$504=D411)*(D411&lt;&gt;"")+($B$5:$B$504=B411)*(B411&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B411="",C411="",D411="",E411="",F411=""),"",IF(OR(B411="",C411="",E411=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E411)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H411&lt;&gt;0,F411=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G411&lt;&gt;0,F411=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F411&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F411)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C411)*($E$5:$E$504=E411)*(($D$5:$D$504=D411)*(D411&lt;&gt;"")+($B$5:$B$504=B411)*(B411&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J411" s="5">
@@ -11259,11 +11287,11 @@
         <v/>
       </c>
       <c r="H412" s="5">
-        <f>IF(OR(C412="Удержание",C412="Зачёт встречного требования",C412="Неустойка заявлена"),N(E412),0)</f>
+        <f>IF(OR(C412="Удержание",C412="Зачёт встречного требования",C412="Неустойка заявлена",C412="Допработы без соглашения (спорно)"),N(E412),0)</f>
         <v/>
       </c>
       <c r="I412" s="6">
-        <f>IF(AND(B412="",C412="",D412="",E412="",F412=""),"",IF(OR(B412="",C412="",E412=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E412)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G412&lt;&gt;0,F412=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F412&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F412)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C412)*($E$5:$E$504=E412)*(($D$5:$D$504=D412)*(D412&lt;&gt;"")+($B$5:$B$504=B412)*(B412&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B412="",C412="",D412="",E412="",F412=""),"",IF(OR(B412="",C412="",E412=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E412)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H412&lt;&gt;0,F412=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G412&lt;&gt;0,F412=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F412&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F412)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C412)*($E$5:$E$504=E412)*(($D$5:$D$504=D412)*(D412&lt;&gt;"")+($B$5:$B$504=B412)*(B412&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J412" s="5">
@@ -11285,11 +11313,11 @@
         <v/>
       </c>
       <c r="H413" s="5">
-        <f>IF(OR(C413="Удержание",C413="Зачёт встречного требования",C413="Неустойка заявлена"),N(E413),0)</f>
+        <f>IF(OR(C413="Удержание",C413="Зачёт встречного требования",C413="Неустойка заявлена",C413="Допработы без соглашения (спорно)"),N(E413),0)</f>
         <v/>
       </c>
       <c r="I413" s="6">
-        <f>IF(AND(B413="",C413="",D413="",E413="",F413=""),"",IF(OR(B413="",C413="",E413=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E413)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G413&lt;&gt;0,F413=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F413&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F413)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C413)*($E$5:$E$504=E413)*(($D$5:$D$504=D413)*(D413&lt;&gt;"")+($B$5:$B$504=B413)*(B413&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B413="",C413="",D413="",E413="",F413=""),"",IF(OR(B413="",C413="",E413=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E413)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H413&lt;&gt;0,F413=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G413&lt;&gt;0,F413=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F413&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F413)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C413)*($E$5:$E$504=E413)*(($D$5:$D$504=D413)*(D413&lt;&gt;"")+($B$5:$B$504=B413)*(B413&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J413" s="5">
@@ -11311,11 +11339,11 @@
         <v/>
       </c>
       <c r="H414" s="5">
-        <f>IF(OR(C414="Удержание",C414="Зачёт встречного требования",C414="Неустойка заявлена"),N(E414),0)</f>
+        <f>IF(OR(C414="Удержание",C414="Зачёт встречного требования",C414="Неустойка заявлена",C414="Допработы без соглашения (спорно)"),N(E414),0)</f>
         <v/>
       </c>
       <c r="I414" s="6">
-        <f>IF(AND(B414="",C414="",D414="",E414="",F414=""),"",IF(OR(B414="",C414="",E414=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E414)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G414&lt;&gt;0,F414=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F414&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F414)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C414)*($E$5:$E$504=E414)*(($D$5:$D$504=D414)*(D414&lt;&gt;"")+($B$5:$B$504=B414)*(B414&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B414="",C414="",D414="",E414="",F414=""),"",IF(OR(B414="",C414="",E414=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E414)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H414&lt;&gt;0,F414=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G414&lt;&gt;0,F414=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F414&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F414)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C414)*($E$5:$E$504=E414)*(($D$5:$D$504=D414)*(D414&lt;&gt;"")+($B$5:$B$504=B414)*(B414&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J414" s="5">
@@ -11337,11 +11365,11 @@
         <v/>
       </c>
       <c r="H415" s="5">
-        <f>IF(OR(C415="Удержание",C415="Зачёт встречного требования",C415="Неустойка заявлена"),N(E415),0)</f>
+        <f>IF(OR(C415="Удержание",C415="Зачёт встречного требования",C415="Неустойка заявлена",C415="Допработы без соглашения (спорно)"),N(E415),0)</f>
         <v/>
       </c>
       <c r="I415" s="6">
-        <f>IF(AND(B415="",C415="",D415="",E415="",F415=""),"",IF(OR(B415="",C415="",E415=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E415)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G415&lt;&gt;0,F415=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F415&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F415)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C415)*($E$5:$E$504=E415)*(($D$5:$D$504=D415)*(D415&lt;&gt;"")+($B$5:$B$504=B415)*(B415&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B415="",C415="",D415="",E415="",F415=""),"",IF(OR(B415="",C415="",E415=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E415)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H415&lt;&gt;0,F415=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G415&lt;&gt;0,F415=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F415&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F415)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C415)*($E$5:$E$504=E415)*(($D$5:$D$504=D415)*(D415&lt;&gt;"")+($B$5:$B$504=B415)*(B415&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J415" s="5">
@@ -11363,11 +11391,11 @@
         <v/>
       </c>
       <c r="H416" s="5">
-        <f>IF(OR(C416="Удержание",C416="Зачёт встречного требования",C416="Неустойка заявлена"),N(E416),0)</f>
+        <f>IF(OR(C416="Удержание",C416="Зачёт встречного требования",C416="Неустойка заявлена",C416="Допработы без соглашения (спорно)"),N(E416),0)</f>
         <v/>
       </c>
       <c r="I416" s="6">
-        <f>IF(AND(B416="",C416="",D416="",E416="",F416=""),"",IF(OR(B416="",C416="",E416=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E416)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G416&lt;&gt;0,F416=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F416&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F416)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C416)*($E$5:$E$504=E416)*(($D$5:$D$504=D416)*(D416&lt;&gt;"")+($B$5:$B$504=B416)*(B416&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B416="",C416="",D416="",E416="",F416=""),"",IF(OR(B416="",C416="",E416=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E416)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H416&lt;&gt;0,F416=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G416&lt;&gt;0,F416=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F416&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F416)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C416)*($E$5:$E$504=E416)*(($D$5:$D$504=D416)*(D416&lt;&gt;"")+($B$5:$B$504=B416)*(B416&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J416" s="5">
@@ -11389,11 +11417,11 @@
         <v/>
       </c>
       <c r="H417" s="5">
-        <f>IF(OR(C417="Удержание",C417="Зачёт встречного требования",C417="Неустойка заявлена"),N(E417),0)</f>
+        <f>IF(OR(C417="Удержание",C417="Зачёт встречного требования",C417="Неустойка заявлена",C417="Допработы без соглашения (спорно)"),N(E417),0)</f>
         <v/>
       </c>
       <c r="I417" s="6">
-        <f>IF(AND(B417="",C417="",D417="",E417="",F417=""),"",IF(OR(B417="",C417="",E417=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E417)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G417&lt;&gt;0,F417=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F417&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F417)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C417)*($E$5:$E$504=E417)*(($D$5:$D$504=D417)*(D417&lt;&gt;"")+($B$5:$B$504=B417)*(B417&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B417="",C417="",D417="",E417="",F417=""),"",IF(OR(B417="",C417="",E417=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E417)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H417&lt;&gt;0,F417=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G417&lt;&gt;0,F417=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F417&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F417)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C417)*($E$5:$E$504=E417)*(($D$5:$D$504=D417)*(D417&lt;&gt;"")+($B$5:$B$504=B417)*(B417&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J417" s="5">
@@ -11415,11 +11443,11 @@
         <v/>
       </c>
       <c r="H418" s="5">
-        <f>IF(OR(C418="Удержание",C418="Зачёт встречного требования",C418="Неустойка заявлена"),N(E418),0)</f>
+        <f>IF(OR(C418="Удержание",C418="Зачёт встречного требования",C418="Неустойка заявлена",C418="Допработы без соглашения (спорно)"),N(E418),0)</f>
         <v/>
       </c>
       <c r="I418" s="6">
-        <f>IF(AND(B418="",C418="",D418="",E418="",F418=""),"",IF(OR(B418="",C418="",E418=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E418)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G418&lt;&gt;0,F418=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F418&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F418)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C418)*($E$5:$E$504=E418)*(($D$5:$D$504=D418)*(D418&lt;&gt;"")+($B$5:$B$504=B418)*(B418&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B418="",C418="",D418="",E418="",F418=""),"",IF(OR(B418="",C418="",E418=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E418)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H418&lt;&gt;0,F418=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G418&lt;&gt;0,F418=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F418&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F418)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C418)*($E$5:$E$504=E418)*(($D$5:$D$504=D418)*(D418&lt;&gt;"")+($B$5:$B$504=B418)*(B418&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J418" s="5">
@@ -11441,11 +11469,11 @@
         <v/>
       </c>
       <c r="H419" s="5">
-        <f>IF(OR(C419="Удержание",C419="Зачёт встречного требования",C419="Неустойка заявлена"),N(E419),0)</f>
+        <f>IF(OR(C419="Удержание",C419="Зачёт встречного требования",C419="Неустойка заявлена",C419="Допработы без соглашения (спорно)"),N(E419),0)</f>
         <v/>
       </c>
       <c r="I419" s="6">
-        <f>IF(AND(B419="",C419="",D419="",E419="",F419=""),"",IF(OR(B419="",C419="",E419=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E419)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G419&lt;&gt;0,F419=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F419&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F419)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C419)*($E$5:$E$504=E419)*(($D$5:$D$504=D419)*(D419&lt;&gt;"")+($B$5:$B$504=B419)*(B419&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B419="",C419="",D419="",E419="",F419=""),"",IF(OR(B419="",C419="",E419=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E419)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H419&lt;&gt;0,F419=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G419&lt;&gt;0,F419=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F419&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F419)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C419)*($E$5:$E$504=E419)*(($D$5:$D$504=D419)*(D419&lt;&gt;"")+($B$5:$B$504=B419)*(B419&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J419" s="5">
@@ -11467,11 +11495,11 @@
         <v/>
       </c>
       <c r="H420" s="5">
-        <f>IF(OR(C420="Удержание",C420="Зачёт встречного требования",C420="Неустойка заявлена"),N(E420),0)</f>
+        <f>IF(OR(C420="Удержание",C420="Зачёт встречного требования",C420="Неустойка заявлена",C420="Допработы без соглашения (спорно)"),N(E420),0)</f>
         <v/>
       </c>
       <c r="I420" s="6">
-        <f>IF(AND(B420="",C420="",D420="",E420="",F420=""),"",IF(OR(B420="",C420="",E420=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E420)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G420&lt;&gt;0,F420=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F420&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F420)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C420)*($E$5:$E$504=E420)*(($D$5:$D$504=D420)*(D420&lt;&gt;"")+($B$5:$B$504=B420)*(B420&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B420="",C420="",D420="",E420="",F420=""),"",IF(OR(B420="",C420="",E420=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E420)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H420&lt;&gt;0,F420=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G420&lt;&gt;0,F420=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F420&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F420)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C420)*($E$5:$E$504=E420)*(($D$5:$D$504=D420)*(D420&lt;&gt;"")+($B$5:$B$504=B420)*(B420&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J420" s="5">
@@ -11493,11 +11521,11 @@
         <v/>
       </c>
       <c r="H421" s="5">
-        <f>IF(OR(C421="Удержание",C421="Зачёт встречного требования",C421="Неустойка заявлена"),N(E421),0)</f>
+        <f>IF(OR(C421="Удержание",C421="Зачёт встречного требования",C421="Неустойка заявлена",C421="Допработы без соглашения (спорно)"),N(E421),0)</f>
         <v/>
       </c>
       <c r="I421" s="6">
-        <f>IF(AND(B421="",C421="",D421="",E421="",F421=""),"",IF(OR(B421="",C421="",E421=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E421)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G421&lt;&gt;0,F421=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F421&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F421)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C421)*($E$5:$E$504=E421)*(($D$5:$D$504=D421)*(D421&lt;&gt;"")+($B$5:$B$504=B421)*(B421&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B421="",C421="",D421="",E421="",F421=""),"",IF(OR(B421="",C421="",E421=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E421)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H421&lt;&gt;0,F421=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G421&lt;&gt;0,F421=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F421&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F421)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C421)*($E$5:$E$504=E421)*(($D$5:$D$504=D421)*(D421&lt;&gt;"")+($B$5:$B$504=B421)*(B421&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J421" s="5">
@@ -11519,11 +11547,11 @@
         <v/>
       </c>
       <c r="H422" s="5">
-        <f>IF(OR(C422="Удержание",C422="Зачёт встречного требования",C422="Неустойка заявлена"),N(E422),0)</f>
+        <f>IF(OR(C422="Удержание",C422="Зачёт встречного требования",C422="Неустойка заявлена",C422="Допработы без соглашения (спорно)"),N(E422),0)</f>
         <v/>
       </c>
       <c r="I422" s="6">
-        <f>IF(AND(B422="",C422="",D422="",E422="",F422=""),"",IF(OR(B422="",C422="",E422=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E422)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G422&lt;&gt;0,F422=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F422&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F422)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C422)*($E$5:$E$504=E422)*(($D$5:$D$504=D422)*(D422&lt;&gt;"")+($B$5:$B$504=B422)*(B422&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B422="",C422="",D422="",E422="",F422=""),"",IF(OR(B422="",C422="",E422=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E422)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H422&lt;&gt;0,F422=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G422&lt;&gt;0,F422=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F422&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F422)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C422)*($E$5:$E$504=E422)*(($D$5:$D$504=D422)*(D422&lt;&gt;"")+($B$5:$B$504=B422)*(B422&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J422" s="5">
@@ -11545,11 +11573,11 @@
         <v/>
       </c>
       <c r="H423" s="5">
-        <f>IF(OR(C423="Удержание",C423="Зачёт встречного требования",C423="Неустойка заявлена"),N(E423),0)</f>
+        <f>IF(OR(C423="Удержание",C423="Зачёт встречного требования",C423="Неустойка заявлена",C423="Допработы без соглашения (спорно)"),N(E423),0)</f>
         <v/>
       </c>
       <c r="I423" s="6">
-        <f>IF(AND(B423="",C423="",D423="",E423="",F423=""),"",IF(OR(B423="",C423="",E423=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E423)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G423&lt;&gt;0,F423=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F423&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F423)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C423)*($E$5:$E$504=E423)*(($D$5:$D$504=D423)*(D423&lt;&gt;"")+($B$5:$B$504=B423)*(B423&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B423="",C423="",D423="",E423="",F423=""),"",IF(OR(B423="",C423="",E423=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E423)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H423&lt;&gt;0,F423=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G423&lt;&gt;0,F423=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F423&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F423)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C423)*($E$5:$E$504=E423)*(($D$5:$D$504=D423)*(D423&lt;&gt;"")+($B$5:$B$504=B423)*(B423&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J423" s="5">
@@ -11571,11 +11599,11 @@
         <v/>
       </c>
       <c r="H424" s="5">
-        <f>IF(OR(C424="Удержание",C424="Зачёт встречного требования",C424="Неустойка заявлена"),N(E424),0)</f>
+        <f>IF(OR(C424="Удержание",C424="Зачёт встречного требования",C424="Неустойка заявлена",C424="Допработы без соглашения (спорно)"),N(E424),0)</f>
         <v/>
       </c>
       <c r="I424" s="6">
-        <f>IF(AND(B424="",C424="",D424="",E424="",F424=""),"",IF(OR(B424="",C424="",E424=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E424)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G424&lt;&gt;0,F424=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F424&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F424)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C424)*($E$5:$E$504=E424)*(($D$5:$D$504=D424)*(D424&lt;&gt;"")+($B$5:$B$504=B424)*(B424&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B424="",C424="",D424="",E424="",F424=""),"",IF(OR(B424="",C424="",E424=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E424)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H424&lt;&gt;0,F424=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G424&lt;&gt;0,F424=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F424&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F424)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C424)*($E$5:$E$504=E424)*(($D$5:$D$504=D424)*(D424&lt;&gt;"")+($B$5:$B$504=B424)*(B424&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J424" s="5">
@@ -11597,11 +11625,11 @@
         <v/>
       </c>
       <c r="H425" s="5">
-        <f>IF(OR(C425="Удержание",C425="Зачёт встречного требования",C425="Неустойка заявлена"),N(E425),0)</f>
+        <f>IF(OR(C425="Удержание",C425="Зачёт встречного требования",C425="Неустойка заявлена",C425="Допработы без соглашения (спорно)"),N(E425),0)</f>
         <v/>
       </c>
       <c r="I425" s="6">
-        <f>IF(AND(B425="",C425="",D425="",E425="",F425=""),"",IF(OR(B425="",C425="",E425=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E425)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G425&lt;&gt;0,F425=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F425&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F425)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C425)*($E$5:$E$504=E425)*(($D$5:$D$504=D425)*(D425&lt;&gt;"")+($B$5:$B$504=B425)*(B425&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B425="",C425="",D425="",E425="",F425=""),"",IF(OR(B425="",C425="",E425=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E425)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H425&lt;&gt;0,F425=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G425&lt;&gt;0,F425=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F425&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F425)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C425)*($E$5:$E$504=E425)*(($D$5:$D$504=D425)*(D425&lt;&gt;"")+($B$5:$B$504=B425)*(B425&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J425" s="5">
@@ -11623,11 +11651,11 @@
         <v/>
       </c>
       <c r="H426" s="5">
-        <f>IF(OR(C426="Удержание",C426="Зачёт встречного требования",C426="Неустойка заявлена"),N(E426),0)</f>
+        <f>IF(OR(C426="Удержание",C426="Зачёт встречного требования",C426="Неустойка заявлена",C426="Допработы без соглашения (спорно)"),N(E426),0)</f>
         <v/>
       </c>
       <c r="I426" s="6">
-        <f>IF(AND(B426="",C426="",D426="",E426="",F426=""),"",IF(OR(B426="",C426="",E426=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E426)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G426&lt;&gt;0,F426=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F426&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F426)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C426)*($E$5:$E$504=E426)*(($D$5:$D$504=D426)*(D426&lt;&gt;"")+($B$5:$B$504=B426)*(B426&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B426="",C426="",D426="",E426="",F426=""),"",IF(OR(B426="",C426="",E426=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E426)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H426&lt;&gt;0,F426=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G426&lt;&gt;0,F426=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F426&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F426)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C426)*($E$5:$E$504=E426)*(($D$5:$D$504=D426)*(D426&lt;&gt;"")+($B$5:$B$504=B426)*(B426&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J426" s="5">
@@ -11649,11 +11677,11 @@
         <v/>
       </c>
       <c r="H427" s="5">
-        <f>IF(OR(C427="Удержание",C427="Зачёт встречного требования",C427="Неустойка заявлена"),N(E427),0)</f>
+        <f>IF(OR(C427="Удержание",C427="Зачёт встречного требования",C427="Неустойка заявлена",C427="Допработы без соглашения (спорно)"),N(E427),0)</f>
         <v/>
       </c>
       <c r="I427" s="6">
-        <f>IF(AND(B427="",C427="",D427="",E427="",F427=""),"",IF(OR(B427="",C427="",E427=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E427)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G427&lt;&gt;0,F427=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F427&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F427)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C427)*($E$5:$E$504=E427)*(($D$5:$D$504=D427)*(D427&lt;&gt;"")+($B$5:$B$504=B427)*(B427&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B427="",C427="",D427="",E427="",F427=""),"",IF(OR(B427="",C427="",E427=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E427)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H427&lt;&gt;0,F427=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G427&lt;&gt;0,F427=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F427&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F427)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C427)*($E$5:$E$504=E427)*(($D$5:$D$504=D427)*(D427&lt;&gt;"")+($B$5:$B$504=B427)*(B427&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J427" s="5">
@@ -11675,11 +11703,11 @@
         <v/>
       </c>
       <c r="H428" s="5">
-        <f>IF(OR(C428="Удержание",C428="Зачёт встречного требования",C428="Неустойка заявлена"),N(E428),0)</f>
+        <f>IF(OR(C428="Удержание",C428="Зачёт встречного требования",C428="Неустойка заявлена",C428="Допработы без соглашения (спорно)"),N(E428),0)</f>
         <v/>
       </c>
       <c r="I428" s="6">
-        <f>IF(AND(B428="",C428="",D428="",E428="",F428=""),"",IF(OR(B428="",C428="",E428=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E428)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G428&lt;&gt;0,F428=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F428&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F428)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C428)*($E$5:$E$504=E428)*(($D$5:$D$504=D428)*(D428&lt;&gt;"")+($B$5:$B$504=B428)*(B428&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B428="",C428="",D428="",E428="",F428=""),"",IF(OR(B428="",C428="",E428=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E428)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H428&lt;&gt;0,F428=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G428&lt;&gt;0,F428=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F428&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F428)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C428)*($E$5:$E$504=E428)*(($D$5:$D$504=D428)*(D428&lt;&gt;"")+($B$5:$B$504=B428)*(B428&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J428" s="5">
@@ -11701,11 +11729,11 @@
         <v/>
       </c>
       <c r="H429" s="5">
-        <f>IF(OR(C429="Удержание",C429="Зачёт встречного требования",C429="Неустойка заявлена"),N(E429),0)</f>
+        <f>IF(OR(C429="Удержание",C429="Зачёт встречного требования",C429="Неустойка заявлена",C429="Допработы без соглашения (спорно)"),N(E429),0)</f>
         <v/>
       </c>
       <c r="I429" s="6">
-        <f>IF(AND(B429="",C429="",D429="",E429="",F429=""),"",IF(OR(B429="",C429="",E429=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E429)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G429&lt;&gt;0,F429=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F429&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F429)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C429)*($E$5:$E$504=E429)*(($D$5:$D$504=D429)*(D429&lt;&gt;"")+($B$5:$B$504=B429)*(B429&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B429="",C429="",D429="",E429="",F429=""),"",IF(OR(B429="",C429="",E429=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E429)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H429&lt;&gt;0,F429=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G429&lt;&gt;0,F429=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F429&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F429)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C429)*($E$5:$E$504=E429)*(($D$5:$D$504=D429)*(D429&lt;&gt;"")+($B$5:$B$504=B429)*(B429&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J429" s="5">
@@ -11727,11 +11755,11 @@
         <v/>
       </c>
       <c r="H430" s="5">
-        <f>IF(OR(C430="Удержание",C430="Зачёт встречного требования",C430="Неустойка заявлена"),N(E430),0)</f>
+        <f>IF(OR(C430="Удержание",C430="Зачёт встречного требования",C430="Неустойка заявлена",C430="Допработы без соглашения (спорно)"),N(E430),0)</f>
         <v/>
       </c>
       <c r="I430" s="6">
-        <f>IF(AND(B430="",C430="",D430="",E430="",F430=""),"",IF(OR(B430="",C430="",E430=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E430)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G430&lt;&gt;0,F430=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F430&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F430)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C430)*($E$5:$E$504=E430)*(($D$5:$D$504=D430)*(D430&lt;&gt;"")+($B$5:$B$504=B430)*(B430&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B430="",C430="",D430="",E430="",F430=""),"",IF(OR(B430="",C430="",E430=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E430)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H430&lt;&gt;0,F430=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G430&lt;&gt;0,F430=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F430&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F430)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C430)*($E$5:$E$504=E430)*(($D$5:$D$504=D430)*(D430&lt;&gt;"")+($B$5:$B$504=B430)*(B430&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J430" s="5">
@@ -11753,11 +11781,11 @@
         <v/>
       </c>
       <c r="H431" s="5">
-        <f>IF(OR(C431="Удержание",C431="Зачёт встречного требования",C431="Неустойка заявлена"),N(E431),0)</f>
+        <f>IF(OR(C431="Удержание",C431="Зачёт встречного требования",C431="Неустойка заявлена",C431="Допработы без соглашения (спорно)"),N(E431),0)</f>
         <v/>
       </c>
       <c r="I431" s="6">
-        <f>IF(AND(B431="",C431="",D431="",E431="",F431=""),"",IF(OR(B431="",C431="",E431=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E431)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G431&lt;&gt;0,F431=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F431&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F431)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C431)*($E$5:$E$504=E431)*(($D$5:$D$504=D431)*(D431&lt;&gt;"")+($B$5:$B$504=B431)*(B431&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B431="",C431="",D431="",E431="",F431=""),"",IF(OR(B431="",C431="",E431=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E431)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H431&lt;&gt;0,F431=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G431&lt;&gt;0,F431=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F431&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F431)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C431)*($E$5:$E$504=E431)*(($D$5:$D$504=D431)*(D431&lt;&gt;"")+($B$5:$B$504=B431)*(B431&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J431" s="5">
@@ -11779,11 +11807,11 @@
         <v/>
       </c>
       <c r="H432" s="5">
-        <f>IF(OR(C432="Удержание",C432="Зачёт встречного требования",C432="Неустойка заявлена"),N(E432),0)</f>
+        <f>IF(OR(C432="Удержание",C432="Зачёт встречного требования",C432="Неустойка заявлена",C432="Допработы без соглашения (спорно)"),N(E432),0)</f>
         <v/>
       </c>
       <c r="I432" s="6">
-        <f>IF(AND(B432="",C432="",D432="",E432="",F432=""),"",IF(OR(B432="",C432="",E432=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E432)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G432&lt;&gt;0,F432=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F432&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F432)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C432)*($E$5:$E$504=E432)*(($D$5:$D$504=D432)*(D432&lt;&gt;"")+($B$5:$B$504=B432)*(B432&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B432="",C432="",D432="",E432="",F432=""),"",IF(OR(B432="",C432="",E432=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E432)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H432&lt;&gt;0,F432=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G432&lt;&gt;0,F432=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F432&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F432)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C432)*($E$5:$E$504=E432)*(($D$5:$D$504=D432)*(D432&lt;&gt;"")+($B$5:$B$504=B432)*(B432&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J432" s="5">
@@ -11805,11 +11833,11 @@
         <v/>
       </c>
       <c r="H433" s="5">
-        <f>IF(OR(C433="Удержание",C433="Зачёт встречного требования",C433="Неустойка заявлена"),N(E433),0)</f>
+        <f>IF(OR(C433="Удержание",C433="Зачёт встречного требования",C433="Неустойка заявлена",C433="Допработы без соглашения (спорно)"),N(E433),0)</f>
         <v/>
       </c>
       <c r="I433" s="6">
-        <f>IF(AND(B433="",C433="",D433="",E433="",F433=""),"",IF(OR(B433="",C433="",E433=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E433)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G433&lt;&gt;0,F433=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F433&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F433)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C433)*($E$5:$E$504=E433)*(($D$5:$D$504=D433)*(D433&lt;&gt;"")+($B$5:$B$504=B433)*(B433&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B433="",C433="",D433="",E433="",F433=""),"",IF(OR(B433="",C433="",E433=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E433)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H433&lt;&gt;0,F433=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G433&lt;&gt;0,F433=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F433&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F433)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C433)*($E$5:$E$504=E433)*(($D$5:$D$504=D433)*(D433&lt;&gt;"")+($B$5:$B$504=B433)*(B433&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J433" s="5">
@@ -11831,11 +11859,11 @@
         <v/>
       </c>
       <c r="H434" s="5">
-        <f>IF(OR(C434="Удержание",C434="Зачёт встречного требования",C434="Неустойка заявлена"),N(E434),0)</f>
+        <f>IF(OR(C434="Удержание",C434="Зачёт встречного требования",C434="Неустойка заявлена",C434="Допработы без соглашения (спорно)"),N(E434),0)</f>
         <v/>
       </c>
       <c r="I434" s="6">
-        <f>IF(AND(B434="",C434="",D434="",E434="",F434=""),"",IF(OR(B434="",C434="",E434=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E434)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G434&lt;&gt;0,F434=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F434&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F434)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C434)*($E$5:$E$504=E434)*(($D$5:$D$504=D434)*(D434&lt;&gt;"")+($B$5:$B$504=B434)*(B434&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B434="",C434="",D434="",E434="",F434=""),"",IF(OR(B434="",C434="",E434=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E434)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H434&lt;&gt;0,F434=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G434&lt;&gt;0,F434=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F434&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F434)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C434)*($E$5:$E$504=E434)*(($D$5:$D$504=D434)*(D434&lt;&gt;"")+($B$5:$B$504=B434)*(B434&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J434" s="5">
@@ -11857,11 +11885,11 @@
         <v/>
       </c>
       <c r="H435" s="5">
-        <f>IF(OR(C435="Удержание",C435="Зачёт встречного требования",C435="Неустойка заявлена"),N(E435),0)</f>
+        <f>IF(OR(C435="Удержание",C435="Зачёт встречного требования",C435="Неустойка заявлена",C435="Допработы без соглашения (спорно)"),N(E435),0)</f>
         <v/>
       </c>
       <c r="I435" s="6">
-        <f>IF(AND(B435="",C435="",D435="",E435="",F435=""),"",IF(OR(B435="",C435="",E435=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E435)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G435&lt;&gt;0,F435=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F435&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F435)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C435)*($E$5:$E$504=E435)*(($D$5:$D$504=D435)*(D435&lt;&gt;"")+($B$5:$B$504=B435)*(B435&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B435="",C435="",D435="",E435="",F435=""),"",IF(OR(B435="",C435="",E435=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E435)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H435&lt;&gt;0,F435=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G435&lt;&gt;0,F435=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F435&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F435)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C435)*($E$5:$E$504=E435)*(($D$5:$D$504=D435)*(D435&lt;&gt;"")+($B$5:$B$504=B435)*(B435&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J435" s="5">
@@ -11883,11 +11911,11 @@
         <v/>
       </c>
       <c r="H436" s="5">
-        <f>IF(OR(C436="Удержание",C436="Зачёт встречного требования",C436="Неустойка заявлена"),N(E436),0)</f>
+        <f>IF(OR(C436="Удержание",C436="Зачёт встречного требования",C436="Неустойка заявлена",C436="Допработы без соглашения (спорно)"),N(E436),0)</f>
         <v/>
       </c>
       <c r="I436" s="6">
-        <f>IF(AND(B436="",C436="",D436="",E436="",F436=""),"",IF(OR(B436="",C436="",E436=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E436)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G436&lt;&gt;0,F436=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F436&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F436)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C436)*($E$5:$E$504=E436)*(($D$5:$D$504=D436)*(D436&lt;&gt;"")+($B$5:$B$504=B436)*(B436&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B436="",C436="",D436="",E436="",F436=""),"",IF(OR(B436="",C436="",E436=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E436)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H436&lt;&gt;0,F436=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G436&lt;&gt;0,F436=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F436&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F436)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C436)*($E$5:$E$504=E436)*(($D$5:$D$504=D436)*(D436&lt;&gt;"")+($B$5:$B$504=B436)*(B436&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J436" s="5">
@@ -11909,11 +11937,11 @@
         <v/>
       </c>
       <c r="H437" s="5">
-        <f>IF(OR(C437="Удержание",C437="Зачёт встречного требования",C437="Неустойка заявлена"),N(E437),0)</f>
+        <f>IF(OR(C437="Удержание",C437="Зачёт встречного требования",C437="Неустойка заявлена",C437="Допработы без соглашения (спорно)"),N(E437),0)</f>
         <v/>
       </c>
       <c r="I437" s="6">
-        <f>IF(AND(B437="",C437="",D437="",E437="",F437=""),"",IF(OR(B437="",C437="",E437=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E437)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G437&lt;&gt;0,F437=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F437&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F437)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C437)*($E$5:$E$504=E437)*(($D$5:$D$504=D437)*(D437&lt;&gt;"")+($B$5:$B$504=B437)*(B437&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B437="",C437="",D437="",E437="",F437=""),"",IF(OR(B437="",C437="",E437=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E437)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H437&lt;&gt;0,F437=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G437&lt;&gt;0,F437=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F437&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F437)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C437)*($E$5:$E$504=E437)*(($D$5:$D$504=D437)*(D437&lt;&gt;"")+($B$5:$B$504=B437)*(B437&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J437" s="5">
@@ -11935,11 +11963,11 @@
         <v/>
       </c>
       <c r="H438" s="5">
-        <f>IF(OR(C438="Удержание",C438="Зачёт встречного требования",C438="Неустойка заявлена"),N(E438),0)</f>
+        <f>IF(OR(C438="Удержание",C438="Зачёт встречного требования",C438="Неустойка заявлена",C438="Допработы без соглашения (спорно)"),N(E438),0)</f>
         <v/>
       </c>
       <c r="I438" s="6">
-        <f>IF(AND(B438="",C438="",D438="",E438="",F438=""),"",IF(OR(B438="",C438="",E438=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E438)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G438&lt;&gt;0,F438=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F438&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F438)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C438)*($E$5:$E$504=E438)*(($D$5:$D$504=D438)*(D438&lt;&gt;"")+($B$5:$B$504=B438)*(B438&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B438="",C438="",D438="",E438="",F438=""),"",IF(OR(B438="",C438="",E438=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E438)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H438&lt;&gt;0,F438=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G438&lt;&gt;0,F438=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F438&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F438)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C438)*($E$5:$E$504=E438)*(($D$5:$D$504=D438)*(D438&lt;&gt;"")+($B$5:$B$504=B438)*(B438&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J438" s="5">
@@ -11961,11 +11989,11 @@
         <v/>
       </c>
       <c r="H439" s="5">
-        <f>IF(OR(C439="Удержание",C439="Зачёт встречного требования",C439="Неустойка заявлена"),N(E439),0)</f>
+        <f>IF(OR(C439="Удержание",C439="Зачёт встречного требования",C439="Неустойка заявлена",C439="Допработы без соглашения (спорно)"),N(E439),0)</f>
         <v/>
       </c>
       <c r="I439" s="6">
-        <f>IF(AND(B439="",C439="",D439="",E439="",F439=""),"",IF(OR(B439="",C439="",E439=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E439)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G439&lt;&gt;0,F439=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F439&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F439)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C439)*($E$5:$E$504=E439)*(($D$5:$D$504=D439)*(D439&lt;&gt;"")+($B$5:$B$504=B439)*(B439&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B439="",C439="",D439="",E439="",F439=""),"",IF(OR(B439="",C439="",E439=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E439)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H439&lt;&gt;0,F439=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G439&lt;&gt;0,F439=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F439&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F439)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C439)*($E$5:$E$504=E439)*(($D$5:$D$504=D439)*(D439&lt;&gt;"")+($B$5:$B$504=B439)*(B439&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J439" s="5">
@@ -11987,11 +12015,11 @@
         <v/>
       </c>
       <c r="H440" s="5">
-        <f>IF(OR(C440="Удержание",C440="Зачёт встречного требования",C440="Неустойка заявлена"),N(E440),0)</f>
+        <f>IF(OR(C440="Удержание",C440="Зачёт встречного требования",C440="Неустойка заявлена",C440="Допработы без соглашения (спорно)"),N(E440),0)</f>
         <v/>
       </c>
       <c r="I440" s="6">
-        <f>IF(AND(B440="",C440="",D440="",E440="",F440=""),"",IF(OR(B440="",C440="",E440=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E440)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G440&lt;&gt;0,F440=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F440&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F440)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C440)*($E$5:$E$504=E440)*(($D$5:$D$504=D440)*(D440&lt;&gt;"")+($B$5:$B$504=B440)*(B440&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B440="",C440="",D440="",E440="",F440=""),"",IF(OR(B440="",C440="",E440=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E440)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H440&lt;&gt;0,F440=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G440&lt;&gt;0,F440=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F440&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F440)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C440)*($E$5:$E$504=E440)*(($D$5:$D$504=D440)*(D440&lt;&gt;"")+($B$5:$B$504=B440)*(B440&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J440" s="5">
@@ -12013,11 +12041,11 @@
         <v/>
       </c>
       <c r="H441" s="5">
-        <f>IF(OR(C441="Удержание",C441="Зачёт встречного требования",C441="Неустойка заявлена"),N(E441),0)</f>
+        <f>IF(OR(C441="Удержание",C441="Зачёт встречного требования",C441="Неустойка заявлена",C441="Допработы без соглашения (спорно)"),N(E441),0)</f>
         <v/>
       </c>
       <c r="I441" s="6">
-        <f>IF(AND(B441="",C441="",D441="",E441="",F441=""),"",IF(OR(B441="",C441="",E441=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E441)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G441&lt;&gt;0,F441=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F441&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F441)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C441)*($E$5:$E$504=E441)*(($D$5:$D$504=D441)*(D441&lt;&gt;"")+($B$5:$B$504=B441)*(B441&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B441="",C441="",D441="",E441="",F441=""),"",IF(OR(B441="",C441="",E441=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E441)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H441&lt;&gt;0,F441=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G441&lt;&gt;0,F441=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F441&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F441)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C441)*($E$5:$E$504=E441)*(($D$5:$D$504=D441)*(D441&lt;&gt;"")+($B$5:$B$504=B441)*(B441&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J441" s="5">
@@ -12039,11 +12067,11 @@
         <v/>
       </c>
       <c r="H442" s="5">
-        <f>IF(OR(C442="Удержание",C442="Зачёт встречного требования",C442="Неустойка заявлена"),N(E442),0)</f>
+        <f>IF(OR(C442="Удержание",C442="Зачёт встречного требования",C442="Неустойка заявлена",C442="Допработы без соглашения (спорно)"),N(E442),0)</f>
         <v/>
       </c>
       <c r="I442" s="6">
-        <f>IF(AND(B442="",C442="",D442="",E442="",F442=""),"",IF(OR(B442="",C442="",E442=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E442)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G442&lt;&gt;0,F442=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F442&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F442)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C442)*($E$5:$E$504=E442)*(($D$5:$D$504=D442)*(D442&lt;&gt;"")+($B$5:$B$504=B442)*(B442&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B442="",C442="",D442="",E442="",F442=""),"",IF(OR(B442="",C442="",E442=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E442)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H442&lt;&gt;0,F442=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G442&lt;&gt;0,F442=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F442&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F442)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C442)*($E$5:$E$504=E442)*(($D$5:$D$504=D442)*(D442&lt;&gt;"")+($B$5:$B$504=B442)*(B442&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J442" s="5">
@@ -12065,11 +12093,11 @@
         <v/>
       </c>
       <c r="H443" s="5">
-        <f>IF(OR(C443="Удержание",C443="Зачёт встречного требования",C443="Неустойка заявлена"),N(E443),0)</f>
+        <f>IF(OR(C443="Удержание",C443="Зачёт встречного требования",C443="Неустойка заявлена",C443="Допработы без соглашения (спорно)"),N(E443),0)</f>
         <v/>
       </c>
       <c r="I443" s="6">
-        <f>IF(AND(B443="",C443="",D443="",E443="",F443=""),"",IF(OR(B443="",C443="",E443=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E443)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G443&lt;&gt;0,F443=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F443&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F443)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C443)*($E$5:$E$504=E443)*(($D$5:$D$504=D443)*(D443&lt;&gt;"")+($B$5:$B$504=B443)*(B443&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B443="",C443="",D443="",E443="",F443=""),"",IF(OR(B443="",C443="",E443=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E443)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H443&lt;&gt;0,F443=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G443&lt;&gt;0,F443=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F443&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F443)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C443)*($E$5:$E$504=E443)*(($D$5:$D$504=D443)*(D443&lt;&gt;"")+($B$5:$B$504=B443)*(B443&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J443" s="5">
@@ -12091,11 +12119,11 @@
         <v/>
       </c>
       <c r="H444" s="5">
-        <f>IF(OR(C444="Удержание",C444="Зачёт встречного требования",C444="Неустойка заявлена"),N(E444),0)</f>
+        <f>IF(OR(C444="Удержание",C444="Зачёт встречного требования",C444="Неустойка заявлена",C444="Допработы без соглашения (спорно)"),N(E444),0)</f>
         <v/>
       </c>
       <c r="I444" s="6">
-        <f>IF(AND(B444="",C444="",D444="",E444="",F444=""),"",IF(OR(B444="",C444="",E444=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E444)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G444&lt;&gt;0,F444=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F444&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F444)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C444)*($E$5:$E$504=E444)*(($D$5:$D$504=D444)*(D444&lt;&gt;"")+($B$5:$B$504=B444)*(B444&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B444="",C444="",D444="",E444="",F444=""),"",IF(OR(B444="",C444="",E444=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E444)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H444&lt;&gt;0,F444=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G444&lt;&gt;0,F444=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F444&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F444)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C444)*($E$5:$E$504=E444)*(($D$5:$D$504=D444)*(D444&lt;&gt;"")+($B$5:$B$504=B444)*(B444&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J444" s="5">
@@ -12117,11 +12145,11 @@
         <v/>
       </c>
       <c r="H445" s="5">
-        <f>IF(OR(C445="Удержание",C445="Зачёт встречного требования",C445="Неустойка заявлена"),N(E445),0)</f>
+        <f>IF(OR(C445="Удержание",C445="Зачёт встречного требования",C445="Неустойка заявлена",C445="Допработы без соглашения (спорно)"),N(E445),0)</f>
         <v/>
       </c>
       <c r="I445" s="6">
-        <f>IF(AND(B445="",C445="",D445="",E445="",F445=""),"",IF(OR(B445="",C445="",E445=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E445)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G445&lt;&gt;0,F445=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F445&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F445)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C445)*($E$5:$E$504=E445)*(($D$5:$D$504=D445)*(D445&lt;&gt;"")+($B$5:$B$504=B445)*(B445&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B445="",C445="",D445="",E445="",F445=""),"",IF(OR(B445="",C445="",E445=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E445)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H445&lt;&gt;0,F445=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G445&lt;&gt;0,F445=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F445&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F445)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C445)*($E$5:$E$504=E445)*(($D$5:$D$504=D445)*(D445&lt;&gt;"")+($B$5:$B$504=B445)*(B445&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J445" s="5">
@@ -12143,11 +12171,11 @@
         <v/>
       </c>
       <c r="H446" s="5">
-        <f>IF(OR(C446="Удержание",C446="Зачёт встречного требования",C446="Неустойка заявлена"),N(E446),0)</f>
+        <f>IF(OR(C446="Удержание",C446="Зачёт встречного требования",C446="Неустойка заявлена",C446="Допработы без соглашения (спорно)"),N(E446),0)</f>
         <v/>
       </c>
       <c r="I446" s="6">
-        <f>IF(AND(B446="",C446="",D446="",E446="",F446=""),"",IF(OR(B446="",C446="",E446=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E446)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G446&lt;&gt;0,F446=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F446&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F446)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C446)*($E$5:$E$504=E446)*(($D$5:$D$504=D446)*(D446&lt;&gt;"")+($B$5:$B$504=B446)*(B446&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B446="",C446="",D446="",E446="",F446=""),"",IF(OR(B446="",C446="",E446=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E446)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H446&lt;&gt;0,F446=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G446&lt;&gt;0,F446=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F446&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F446)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C446)*($E$5:$E$504=E446)*(($D$5:$D$504=D446)*(D446&lt;&gt;"")+($B$5:$B$504=B446)*(B446&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J446" s="5">
@@ -12169,11 +12197,11 @@
         <v/>
       </c>
       <c r="H447" s="5">
-        <f>IF(OR(C447="Удержание",C447="Зачёт встречного требования",C447="Неустойка заявлена"),N(E447),0)</f>
+        <f>IF(OR(C447="Удержание",C447="Зачёт встречного требования",C447="Неустойка заявлена",C447="Допработы без соглашения (спорно)"),N(E447),0)</f>
         <v/>
       </c>
       <c r="I447" s="6">
-        <f>IF(AND(B447="",C447="",D447="",E447="",F447=""),"",IF(OR(B447="",C447="",E447=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E447)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G447&lt;&gt;0,F447=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F447&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F447)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C447)*($E$5:$E$504=E447)*(($D$5:$D$504=D447)*(D447&lt;&gt;"")+($B$5:$B$504=B447)*(B447&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B447="",C447="",D447="",E447="",F447=""),"",IF(OR(B447="",C447="",E447=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E447)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H447&lt;&gt;0,F447=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G447&lt;&gt;0,F447=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F447&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F447)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C447)*($E$5:$E$504=E447)*(($D$5:$D$504=D447)*(D447&lt;&gt;"")+($B$5:$B$504=B447)*(B447&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J447" s="5">
@@ -12195,11 +12223,11 @@
         <v/>
       </c>
       <c r="H448" s="5">
-        <f>IF(OR(C448="Удержание",C448="Зачёт встречного требования",C448="Неустойка заявлена"),N(E448),0)</f>
+        <f>IF(OR(C448="Удержание",C448="Зачёт встречного требования",C448="Неустойка заявлена",C448="Допработы без соглашения (спорно)"),N(E448),0)</f>
         <v/>
       </c>
       <c r="I448" s="6">
-        <f>IF(AND(B448="",C448="",D448="",E448="",F448=""),"",IF(OR(B448="",C448="",E448=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E448)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G448&lt;&gt;0,F448=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F448&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F448)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C448)*($E$5:$E$504=E448)*(($D$5:$D$504=D448)*(D448&lt;&gt;"")+($B$5:$B$504=B448)*(B448&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B448="",C448="",D448="",E448="",F448=""),"",IF(OR(B448="",C448="",E448=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E448)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H448&lt;&gt;0,F448=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G448&lt;&gt;0,F448=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F448&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F448)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C448)*($E$5:$E$504=E448)*(($D$5:$D$504=D448)*(D448&lt;&gt;"")+($B$5:$B$504=B448)*(B448&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J448" s="5">
@@ -12221,11 +12249,11 @@
         <v/>
       </c>
       <c r="H449" s="5">
-        <f>IF(OR(C449="Удержание",C449="Зачёт встречного требования",C449="Неустойка заявлена"),N(E449),0)</f>
+        <f>IF(OR(C449="Удержание",C449="Зачёт встречного требования",C449="Неустойка заявлена",C449="Допработы без соглашения (спорно)"),N(E449),0)</f>
         <v/>
       </c>
       <c r="I449" s="6">
-        <f>IF(AND(B449="",C449="",D449="",E449="",F449=""),"",IF(OR(B449="",C449="",E449=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E449)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G449&lt;&gt;0,F449=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F449&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F449)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C449)*($E$5:$E$504=E449)*(($D$5:$D$504=D449)*(D449&lt;&gt;"")+($B$5:$B$504=B449)*(B449&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B449="",C449="",D449="",E449="",F449=""),"",IF(OR(B449="",C449="",E449=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E449)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H449&lt;&gt;0,F449=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G449&lt;&gt;0,F449=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F449&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F449)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C449)*($E$5:$E$504=E449)*(($D$5:$D$504=D449)*(D449&lt;&gt;"")+($B$5:$B$504=B449)*(B449&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J449" s="5">
@@ -12247,11 +12275,11 @@
         <v/>
       </c>
       <c r="H450" s="5">
-        <f>IF(OR(C450="Удержание",C450="Зачёт встречного требования",C450="Неустойка заявлена"),N(E450),0)</f>
+        <f>IF(OR(C450="Удержание",C450="Зачёт встречного требования",C450="Неустойка заявлена",C450="Допработы без соглашения (спорно)"),N(E450),0)</f>
         <v/>
       </c>
       <c r="I450" s="6">
-        <f>IF(AND(B450="",C450="",D450="",E450="",F450=""),"",IF(OR(B450="",C450="",E450=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E450)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G450&lt;&gt;0,F450=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F450&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F450)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C450)*($E$5:$E$504=E450)*(($D$5:$D$504=D450)*(D450&lt;&gt;"")+($B$5:$B$504=B450)*(B450&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B450="",C450="",D450="",E450="",F450=""),"",IF(OR(B450="",C450="",E450=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E450)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H450&lt;&gt;0,F450=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G450&lt;&gt;0,F450=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F450&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F450)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C450)*($E$5:$E$504=E450)*(($D$5:$D$504=D450)*(D450&lt;&gt;"")+($B$5:$B$504=B450)*(B450&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J450" s="5">
@@ -12273,11 +12301,11 @@
         <v/>
       </c>
       <c r="H451" s="5">
-        <f>IF(OR(C451="Удержание",C451="Зачёт встречного требования",C451="Неустойка заявлена"),N(E451),0)</f>
+        <f>IF(OR(C451="Удержание",C451="Зачёт встречного требования",C451="Неустойка заявлена",C451="Допработы без соглашения (спорно)"),N(E451),0)</f>
         <v/>
       </c>
       <c r="I451" s="6">
-        <f>IF(AND(B451="",C451="",D451="",E451="",F451=""),"",IF(OR(B451="",C451="",E451=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E451)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G451&lt;&gt;0,F451=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F451&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F451)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C451)*($E$5:$E$504=E451)*(($D$5:$D$504=D451)*(D451&lt;&gt;"")+($B$5:$B$504=B451)*(B451&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B451="",C451="",D451="",E451="",F451=""),"",IF(OR(B451="",C451="",E451=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E451)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H451&lt;&gt;0,F451=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G451&lt;&gt;0,F451=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F451&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F451)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C451)*($E$5:$E$504=E451)*(($D$5:$D$504=D451)*(D451&lt;&gt;"")+($B$5:$B$504=B451)*(B451&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J451" s="5">
@@ -12299,11 +12327,11 @@
         <v/>
       </c>
       <c r="H452" s="5">
-        <f>IF(OR(C452="Удержание",C452="Зачёт встречного требования",C452="Неустойка заявлена"),N(E452),0)</f>
+        <f>IF(OR(C452="Удержание",C452="Зачёт встречного требования",C452="Неустойка заявлена",C452="Допработы без соглашения (спорно)"),N(E452),0)</f>
         <v/>
       </c>
       <c r="I452" s="6">
-        <f>IF(AND(B452="",C452="",D452="",E452="",F452=""),"",IF(OR(B452="",C452="",E452=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E452)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G452&lt;&gt;0,F452=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F452&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F452)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C452)*($E$5:$E$504=E452)*(($D$5:$D$504=D452)*(D452&lt;&gt;"")+($B$5:$B$504=B452)*(B452&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B452="",C452="",D452="",E452="",F452=""),"",IF(OR(B452="",C452="",E452=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E452)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H452&lt;&gt;0,F452=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G452&lt;&gt;0,F452=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F452&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F452)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C452)*($E$5:$E$504=E452)*(($D$5:$D$504=D452)*(D452&lt;&gt;"")+($B$5:$B$504=B452)*(B452&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J452" s="5">
@@ -12325,11 +12353,11 @@
         <v/>
       </c>
       <c r="H453" s="5">
-        <f>IF(OR(C453="Удержание",C453="Зачёт встречного требования",C453="Неустойка заявлена"),N(E453),0)</f>
+        <f>IF(OR(C453="Удержание",C453="Зачёт встречного требования",C453="Неустойка заявлена",C453="Допработы без соглашения (спорно)"),N(E453),0)</f>
         <v/>
       </c>
       <c r="I453" s="6">
-        <f>IF(AND(B453="",C453="",D453="",E453="",F453=""),"",IF(OR(B453="",C453="",E453=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E453)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G453&lt;&gt;0,F453=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F453&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F453)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C453)*($E$5:$E$504=E453)*(($D$5:$D$504=D453)*(D453&lt;&gt;"")+($B$5:$B$504=B453)*(B453&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B453="",C453="",D453="",E453="",F453=""),"",IF(OR(B453="",C453="",E453=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E453)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H453&lt;&gt;0,F453=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G453&lt;&gt;0,F453=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F453&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F453)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C453)*($E$5:$E$504=E453)*(($D$5:$D$504=D453)*(D453&lt;&gt;"")+($B$5:$B$504=B453)*(B453&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J453" s="5">
@@ -12351,11 +12379,11 @@
         <v/>
       </c>
       <c r="H454" s="5">
-        <f>IF(OR(C454="Удержание",C454="Зачёт встречного требования",C454="Неустойка заявлена"),N(E454),0)</f>
+        <f>IF(OR(C454="Удержание",C454="Зачёт встречного требования",C454="Неустойка заявлена",C454="Допработы без соглашения (спорно)"),N(E454),0)</f>
         <v/>
       </c>
       <c r="I454" s="6">
-        <f>IF(AND(B454="",C454="",D454="",E454="",F454=""),"",IF(OR(B454="",C454="",E454=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E454)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G454&lt;&gt;0,F454=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F454&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F454)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C454)*($E$5:$E$504=E454)*(($D$5:$D$504=D454)*(D454&lt;&gt;"")+($B$5:$B$504=B454)*(B454&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B454="",C454="",D454="",E454="",F454=""),"",IF(OR(B454="",C454="",E454=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E454)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H454&lt;&gt;0,F454=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G454&lt;&gt;0,F454=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F454&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F454)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C454)*($E$5:$E$504=E454)*(($D$5:$D$504=D454)*(D454&lt;&gt;"")+($B$5:$B$504=B454)*(B454&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J454" s="5">
@@ -12377,11 +12405,11 @@
         <v/>
       </c>
       <c r="H455" s="5">
-        <f>IF(OR(C455="Удержание",C455="Зачёт встречного требования",C455="Неустойка заявлена"),N(E455),0)</f>
+        <f>IF(OR(C455="Удержание",C455="Зачёт встречного требования",C455="Неустойка заявлена",C455="Допработы без соглашения (спорно)"),N(E455),0)</f>
         <v/>
       </c>
       <c r="I455" s="6">
-        <f>IF(AND(B455="",C455="",D455="",E455="",F455=""),"",IF(OR(B455="",C455="",E455=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E455)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G455&lt;&gt;0,F455=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F455&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F455)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C455)*($E$5:$E$504=E455)*(($D$5:$D$504=D455)*(D455&lt;&gt;"")+($B$5:$B$504=B455)*(B455&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B455="",C455="",D455="",E455="",F455=""),"",IF(OR(B455="",C455="",E455=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E455)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H455&lt;&gt;0,F455=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G455&lt;&gt;0,F455=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F455&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F455)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C455)*($E$5:$E$504=E455)*(($D$5:$D$504=D455)*(D455&lt;&gt;"")+($B$5:$B$504=B455)*(B455&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J455" s="5">
@@ -12403,11 +12431,11 @@
         <v/>
       </c>
       <c r="H456" s="5">
-        <f>IF(OR(C456="Удержание",C456="Зачёт встречного требования",C456="Неустойка заявлена"),N(E456),0)</f>
+        <f>IF(OR(C456="Удержание",C456="Зачёт встречного требования",C456="Неустойка заявлена",C456="Допработы без соглашения (спорно)"),N(E456),0)</f>
         <v/>
       </c>
       <c r="I456" s="6">
-        <f>IF(AND(B456="",C456="",D456="",E456="",F456=""),"",IF(OR(B456="",C456="",E456=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E456)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G456&lt;&gt;0,F456=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F456&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F456)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C456)*($E$5:$E$504=E456)*(($D$5:$D$504=D456)*(D456&lt;&gt;"")+($B$5:$B$504=B456)*(B456&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B456="",C456="",D456="",E456="",F456=""),"",IF(OR(B456="",C456="",E456=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E456)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H456&lt;&gt;0,F456=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G456&lt;&gt;0,F456=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F456&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F456)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C456)*($E$5:$E$504=E456)*(($D$5:$D$504=D456)*(D456&lt;&gt;"")+($B$5:$B$504=B456)*(B456&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J456" s="5">
@@ -12429,11 +12457,11 @@
         <v/>
       </c>
       <c r="H457" s="5">
-        <f>IF(OR(C457="Удержание",C457="Зачёт встречного требования",C457="Неустойка заявлена"),N(E457),0)</f>
+        <f>IF(OR(C457="Удержание",C457="Зачёт встречного требования",C457="Неустойка заявлена",C457="Допработы без соглашения (спорно)"),N(E457),0)</f>
         <v/>
       </c>
       <c r="I457" s="6">
-        <f>IF(AND(B457="",C457="",D457="",E457="",F457=""),"",IF(OR(B457="",C457="",E457=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E457)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G457&lt;&gt;0,F457=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F457&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F457)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C457)*($E$5:$E$504=E457)*(($D$5:$D$504=D457)*(D457&lt;&gt;"")+($B$5:$B$504=B457)*(B457&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B457="",C457="",D457="",E457="",F457=""),"",IF(OR(B457="",C457="",E457=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E457)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H457&lt;&gt;0,F457=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G457&lt;&gt;0,F457=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F457&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F457)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C457)*($E$5:$E$504=E457)*(($D$5:$D$504=D457)*(D457&lt;&gt;"")+($B$5:$B$504=B457)*(B457&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J457" s="5">
@@ -12455,11 +12483,11 @@
         <v/>
       </c>
       <c r="H458" s="5">
-        <f>IF(OR(C458="Удержание",C458="Зачёт встречного требования",C458="Неустойка заявлена"),N(E458),0)</f>
+        <f>IF(OR(C458="Удержание",C458="Зачёт встречного требования",C458="Неустойка заявлена",C458="Допработы без соглашения (спорно)"),N(E458),0)</f>
         <v/>
       </c>
       <c r="I458" s="6">
-        <f>IF(AND(B458="",C458="",D458="",E458="",F458=""),"",IF(OR(B458="",C458="",E458=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E458)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G458&lt;&gt;0,F458=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F458&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F458)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C458)*($E$5:$E$504=E458)*(($D$5:$D$504=D458)*(D458&lt;&gt;"")+($B$5:$B$504=B458)*(B458&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B458="",C458="",D458="",E458="",F458=""),"",IF(OR(B458="",C458="",E458=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E458)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H458&lt;&gt;0,F458=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G458&lt;&gt;0,F458=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F458&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F458)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C458)*($E$5:$E$504=E458)*(($D$5:$D$504=D458)*(D458&lt;&gt;"")+($B$5:$B$504=B458)*(B458&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J458" s="5">
@@ -12481,11 +12509,11 @@
         <v/>
       </c>
       <c r="H459" s="5">
-        <f>IF(OR(C459="Удержание",C459="Зачёт встречного требования",C459="Неустойка заявлена"),N(E459),0)</f>
+        <f>IF(OR(C459="Удержание",C459="Зачёт встречного требования",C459="Неустойка заявлена",C459="Допработы без соглашения (спорно)"),N(E459),0)</f>
         <v/>
       </c>
       <c r="I459" s="6">
-        <f>IF(AND(B459="",C459="",D459="",E459="",F459=""),"",IF(OR(B459="",C459="",E459=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E459)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G459&lt;&gt;0,F459=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F459&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F459)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C459)*($E$5:$E$504=E459)*(($D$5:$D$504=D459)*(D459&lt;&gt;"")+($B$5:$B$504=B459)*(B459&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B459="",C459="",D459="",E459="",F459=""),"",IF(OR(B459="",C459="",E459=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E459)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H459&lt;&gt;0,F459=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G459&lt;&gt;0,F459=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F459&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F459)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C459)*($E$5:$E$504=E459)*(($D$5:$D$504=D459)*(D459&lt;&gt;"")+($B$5:$B$504=B459)*(B459&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J459" s="5">
@@ -12507,11 +12535,11 @@
         <v/>
       </c>
       <c r="H460" s="5">
-        <f>IF(OR(C460="Удержание",C460="Зачёт встречного требования",C460="Неустойка заявлена"),N(E460),0)</f>
+        <f>IF(OR(C460="Удержание",C460="Зачёт встречного требования",C460="Неустойка заявлена",C460="Допработы без соглашения (спорно)"),N(E460),0)</f>
         <v/>
       </c>
       <c r="I460" s="6">
-        <f>IF(AND(B460="",C460="",D460="",E460="",F460=""),"",IF(OR(B460="",C460="",E460=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E460)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G460&lt;&gt;0,F460=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F460&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F460)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C460)*($E$5:$E$504=E460)*(($D$5:$D$504=D460)*(D460&lt;&gt;"")+($B$5:$B$504=B460)*(B460&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B460="",C460="",D460="",E460="",F460=""),"",IF(OR(B460="",C460="",E460=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E460)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H460&lt;&gt;0,F460=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G460&lt;&gt;0,F460=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F460&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F460)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C460)*($E$5:$E$504=E460)*(($D$5:$D$504=D460)*(D460&lt;&gt;"")+($B$5:$B$504=B460)*(B460&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J460" s="5">
@@ -12533,11 +12561,11 @@
         <v/>
       </c>
       <c r="H461" s="5">
-        <f>IF(OR(C461="Удержание",C461="Зачёт встречного требования",C461="Неустойка заявлена"),N(E461),0)</f>
+        <f>IF(OR(C461="Удержание",C461="Зачёт встречного требования",C461="Неустойка заявлена",C461="Допработы без соглашения (спорно)"),N(E461),0)</f>
         <v/>
       </c>
       <c r="I461" s="6">
-        <f>IF(AND(B461="",C461="",D461="",E461="",F461=""),"",IF(OR(B461="",C461="",E461=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E461)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G461&lt;&gt;0,F461=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F461&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F461)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C461)*($E$5:$E$504=E461)*(($D$5:$D$504=D461)*(D461&lt;&gt;"")+($B$5:$B$504=B461)*(B461&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B461="",C461="",D461="",E461="",F461=""),"",IF(OR(B461="",C461="",E461=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E461)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H461&lt;&gt;0,F461=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G461&lt;&gt;0,F461=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F461&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F461)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C461)*($E$5:$E$504=E461)*(($D$5:$D$504=D461)*(D461&lt;&gt;"")+($B$5:$B$504=B461)*(B461&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J461" s="5">
@@ -12559,11 +12587,11 @@
         <v/>
       </c>
       <c r="H462" s="5">
-        <f>IF(OR(C462="Удержание",C462="Зачёт встречного требования",C462="Неустойка заявлена"),N(E462),0)</f>
+        <f>IF(OR(C462="Удержание",C462="Зачёт встречного требования",C462="Неустойка заявлена",C462="Допработы без соглашения (спорно)"),N(E462),0)</f>
         <v/>
       </c>
       <c r="I462" s="6">
-        <f>IF(AND(B462="",C462="",D462="",E462="",F462=""),"",IF(OR(B462="",C462="",E462=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E462)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G462&lt;&gt;0,F462=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F462&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F462)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C462)*($E$5:$E$504=E462)*(($D$5:$D$504=D462)*(D462&lt;&gt;"")+($B$5:$B$504=B462)*(B462&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B462="",C462="",D462="",E462="",F462=""),"",IF(OR(B462="",C462="",E462=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E462)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H462&lt;&gt;0,F462=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G462&lt;&gt;0,F462=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F462&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F462)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C462)*($E$5:$E$504=E462)*(($D$5:$D$504=D462)*(D462&lt;&gt;"")+($B$5:$B$504=B462)*(B462&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J462" s="5">
@@ -12585,11 +12613,11 @@
         <v/>
       </c>
       <c r="H463" s="5">
-        <f>IF(OR(C463="Удержание",C463="Зачёт встречного требования",C463="Неустойка заявлена"),N(E463),0)</f>
+        <f>IF(OR(C463="Удержание",C463="Зачёт встречного требования",C463="Неустойка заявлена",C463="Допработы без соглашения (спорно)"),N(E463),0)</f>
         <v/>
       </c>
       <c r="I463" s="6">
-        <f>IF(AND(B463="",C463="",D463="",E463="",F463=""),"",IF(OR(B463="",C463="",E463=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E463)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G463&lt;&gt;0,F463=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F463&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F463)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C463)*($E$5:$E$504=E463)*(($D$5:$D$504=D463)*(D463&lt;&gt;"")+($B$5:$B$504=B463)*(B463&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B463="",C463="",D463="",E463="",F463=""),"",IF(OR(B463="",C463="",E463=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E463)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H463&lt;&gt;0,F463=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G463&lt;&gt;0,F463=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F463&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F463)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C463)*($E$5:$E$504=E463)*(($D$5:$D$504=D463)*(D463&lt;&gt;"")+($B$5:$B$504=B463)*(B463&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J463" s="5">
@@ -12611,11 +12639,11 @@
         <v/>
       </c>
       <c r="H464" s="5">
-        <f>IF(OR(C464="Удержание",C464="Зачёт встречного требования",C464="Неустойка заявлена"),N(E464),0)</f>
+        <f>IF(OR(C464="Удержание",C464="Зачёт встречного требования",C464="Неустойка заявлена",C464="Допработы без соглашения (спорно)"),N(E464),0)</f>
         <v/>
       </c>
       <c r="I464" s="6">
-        <f>IF(AND(B464="",C464="",D464="",E464="",F464=""),"",IF(OR(B464="",C464="",E464=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E464)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G464&lt;&gt;0,F464=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F464&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F464)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C464)*($E$5:$E$504=E464)*(($D$5:$D$504=D464)*(D464&lt;&gt;"")+($B$5:$B$504=B464)*(B464&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B464="",C464="",D464="",E464="",F464=""),"",IF(OR(B464="",C464="",E464=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E464)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H464&lt;&gt;0,F464=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G464&lt;&gt;0,F464=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F464&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F464)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C464)*($E$5:$E$504=E464)*(($D$5:$D$504=D464)*(D464&lt;&gt;"")+($B$5:$B$504=B464)*(B464&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J464" s="5">
@@ -12637,11 +12665,11 @@
         <v/>
       </c>
       <c r="H465" s="5">
-        <f>IF(OR(C465="Удержание",C465="Зачёт встречного требования",C465="Неустойка заявлена"),N(E465),0)</f>
+        <f>IF(OR(C465="Удержание",C465="Зачёт встречного требования",C465="Неустойка заявлена",C465="Допработы без соглашения (спорно)"),N(E465),0)</f>
         <v/>
       </c>
       <c r="I465" s="6">
-        <f>IF(AND(B465="",C465="",D465="",E465="",F465=""),"",IF(OR(B465="",C465="",E465=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E465)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G465&lt;&gt;0,F465=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F465&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F465)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C465)*($E$5:$E$504=E465)*(($D$5:$D$504=D465)*(D465&lt;&gt;"")+($B$5:$B$504=B465)*(B465&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B465="",C465="",D465="",E465="",F465=""),"",IF(OR(B465="",C465="",E465=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E465)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H465&lt;&gt;0,F465=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G465&lt;&gt;0,F465=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F465&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F465)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C465)*($E$5:$E$504=E465)*(($D$5:$D$504=D465)*(D465&lt;&gt;"")+($B$5:$B$504=B465)*(B465&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J465" s="5">
@@ -12663,11 +12691,11 @@
         <v/>
       </c>
       <c r="H466" s="5">
-        <f>IF(OR(C466="Удержание",C466="Зачёт встречного требования",C466="Неустойка заявлена"),N(E466),0)</f>
+        <f>IF(OR(C466="Удержание",C466="Зачёт встречного требования",C466="Неустойка заявлена",C466="Допработы без соглашения (спорно)"),N(E466),0)</f>
         <v/>
       </c>
       <c r="I466" s="6">
-        <f>IF(AND(B466="",C466="",D466="",E466="",F466=""),"",IF(OR(B466="",C466="",E466=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E466)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G466&lt;&gt;0,F466=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F466&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F466)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C466)*($E$5:$E$504=E466)*(($D$5:$D$504=D466)*(D466&lt;&gt;"")+($B$5:$B$504=B466)*(B466&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B466="",C466="",D466="",E466="",F466=""),"",IF(OR(B466="",C466="",E466=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E466)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H466&lt;&gt;0,F466=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G466&lt;&gt;0,F466=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F466&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F466)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C466)*($E$5:$E$504=E466)*(($D$5:$D$504=D466)*(D466&lt;&gt;"")+($B$5:$B$504=B466)*(B466&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J466" s="5">
@@ -12689,11 +12717,11 @@
         <v/>
       </c>
       <c r="H467" s="5">
-        <f>IF(OR(C467="Удержание",C467="Зачёт встречного требования",C467="Неустойка заявлена"),N(E467),0)</f>
+        <f>IF(OR(C467="Удержание",C467="Зачёт встречного требования",C467="Неустойка заявлена",C467="Допработы без соглашения (спорно)"),N(E467),0)</f>
         <v/>
       </c>
       <c r="I467" s="6">
-        <f>IF(AND(B467="",C467="",D467="",E467="",F467=""),"",IF(OR(B467="",C467="",E467=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E467)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G467&lt;&gt;0,F467=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F467&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F467)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C467)*($E$5:$E$504=E467)*(($D$5:$D$504=D467)*(D467&lt;&gt;"")+($B$5:$B$504=B467)*(B467&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B467="",C467="",D467="",E467="",F467=""),"",IF(OR(B467="",C467="",E467=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E467)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H467&lt;&gt;0,F467=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G467&lt;&gt;0,F467=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F467&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F467)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C467)*($E$5:$E$504=E467)*(($D$5:$D$504=D467)*(D467&lt;&gt;"")+($B$5:$B$504=B467)*(B467&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J467" s="5">
@@ -12715,11 +12743,11 @@
         <v/>
       </c>
       <c r="H468" s="5">
-        <f>IF(OR(C468="Удержание",C468="Зачёт встречного требования",C468="Неустойка заявлена"),N(E468),0)</f>
+        <f>IF(OR(C468="Удержание",C468="Зачёт встречного требования",C468="Неустойка заявлена",C468="Допработы без соглашения (спорно)"),N(E468),0)</f>
         <v/>
       </c>
       <c r="I468" s="6">
-        <f>IF(AND(B468="",C468="",D468="",E468="",F468=""),"",IF(OR(B468="",C468="",E468=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E468)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G468&lt;&gt;0,F468=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F468&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F468)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C468)*($E$5:$E$504=E468)*(($D$5:$D$504=D468)*(D468&lt;&gt;"")+($B$5:$B$504=B468)*(B468&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B468="",C468="",D468="",E468="",F468=""),"",IF(OR(B468="",C468="",E468=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E468)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H468&lt;&gt;0,F468=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G468&lt;&gt;0,F468=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F468&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F468)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C468)*($E$5:$E$504=E468)*(($D$5:$D$504=D468)*(D468&lt;&gt;"")+($B$5:$B$504=B468)*(B468&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J468" s="5">
@@ -12741,11 +12769,11 @@
         <v/>
       </c>
       <c r="H469" s="5">
-        <f>IF(OR(C469="Удержание",C469="Зачёт встречного требования",C469="Неустойка заявлена"),N(E469),0)</f>
+        <f>IF(OR(C469="Удержание",C469="Зачёт встречного требования",C469="Неустойка заявлена",C469="Допработы без соглашения (спорно)"),N(E469),0)</f>
         <v/>
       </c>
       <c r="I469" s="6">
-        <f>IF(AND(B469="",C469="",D469="",E469="",F469=""),"",IF(OR(B469="",C469="",E469=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E469)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G469&lt;&gt;0,F469=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F469&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F469)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C469)*($E$5:$E$504=E469)*(($D$5:$D$504=D469)*(D469&lt;&gt;"")+($B$5:$B$504=B469)*(B469&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B469="",C469="",D469="",E469="",F469=""),"",IF(OR(B469="",C469="",E469=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E469)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H469&lt;&gt;0,F469=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G469&lt;&gt;0,F469=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F469&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F469)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C469)*($E$5:$E$504=E469)*(($D$5:$D$504=D469)*(D469&lt;&gt;"")+($B$5:$B$504=B469)*(B469&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J469" s="5">
@@ -12767,11 +12795,11 @@
         <v/>
       </c>
       <c r="H470" s="5">
-        <f>IF(OR(C470="Удержание",C470="Зачёт встречного требования",C470="Неустойка заявлена"),N(E470),0)</f>
+        <f>IF(OR(C470="Удержание",C470="Зачёт встречного требования",C470="Неустойка заявлена",C470="Допработы без соглашения (спорно)"),N(E470),0)</f>
         <v/>
       </c>
       <c r="I470" s="6">
-        <f>IF(AND(B470="",C470="",D470="",E470="",F470=""),"",IF(OR(B470="",C470="",E470=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E470)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G470&lt;&gt;0,F470=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F470&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F470)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C470)*($E$5:$E$504=E470)*(($D$5:$D$504=D470)*(D470&lt;&gt;"")+($B$5:$B$504=B470)*(B470&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B470="",C470="",D470="",E470="",F470=""),"",IF(OR(B470="",C470="",E470=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E470)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H470&lt;&gt;0,F470=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G470&lt;&gt;0,F470=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F470&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F470)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C470)*($E$5:$E$504=E470)*(($D$5:$D$504=D470)*(D470&lt;&gt;"")+($B$5:$B$504=B470)*(B470&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J470" s="5">
@@ -12793,11 +12821,11 @@
         <v/>
       </c>
       <c r="H471" s="5">
-        <f>IF(OR(C471="Удержание",C471="Зачёт встречного требования",C471="Неустойка заявлена"),N(E471),0)</f>
+        <f>IF(OR(C471="Удержание",C471="Зачёт встречного требования",C471="Неустойка заявлена",C471="Допработы без соглашения (спорно)"),N(E471),0)</f>
         <v/>
       </c>
       <c r="I471" s="6">
-        <f>IF(AND(B471="",C471="",D471="",E471="",F471=""),"",IF(OR(B471="",C471="",E471=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E471)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G471&lt;&gt;0,F471=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F471&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F471)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C471)*($E$5:$E$504=E471)*(($D$5:$D$504=D471)*(D471&lt;&gt;"")+($B$5:$B$504=B471)*(B471&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B471="",C471="",D471="",E471="",F471=""),"",IF(OR(B471="",C471="",E471=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E471)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H471&lt;&gt;0,F471=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G471&lt;&gt;0,F471=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F471&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F471)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C471)*($E$5:$E$504=E471)*(($D$5:$D$504=D471)*(D471&lt;&gt;"")+($B$5:$B$504=B471)*(B471&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J471" s="5">
@@ -12819,11 +12847,11 @@
         <v/>
       </c>
       <c r="H472" s="5">
-        <f>IF(OR(C472="Удержание",C472="Зачёт встречного требования",C472="Неустойка заявлена"),N(E472),0)</f>
+        <f>IF(OR(C472="Удержание",C472="Зачёт встречного требования",C472="Неустойка заявлена",C472="Допработы без соглашения (спорно)"),N(E472),0)</f>
         <v/>
       </c>
       <c r="I472" s="6">
-        <f>IF(AND(B472="",C472="",D472="",E472="",F472=""),"",IF(OR(B472="",C472="",E472=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E472)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G472&lt;&gt;0,F472=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F472&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F472)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C472)*($E$5:$E$504=E472)*(($D$5:$D$504=D472)*(D472&lt;&gt;"")+($B$5:$B$504=B472)*(B472&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B472="",C472="",D472="",E472="",F472=""),"",IF(OR(B472="",C472="",E472=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E472)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H472&lt;&gt;0,F472=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G472&lt;&gt;0,F472=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F472&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F472)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C472)*($E$5:$E$504=E472)*(($D$5:$D$504=D472)*(D472&lt;&gt;"")+($B$5:$B$504=B472)*(B472&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J472" s="5">
@@ -12845,11 +12873,11 @@
         <v/>
       </c>
       <c r="H473" s="5">
-        <f>IF(OR(C473="Удержание",C473="Зачёт встречного требования",C473="Неустойка заявлена"),N(E473),0)</f>
+        <f>IF(OR(C473="Удержание",C473="Зачёт встречного требования",C473="Неустойка заявлена",C473="Допработы без соглашения (спорно)"),N(E473),0)</f>
         <v/>
       </c>
       <c r="I473" s="6">
-        <f>IF(AND(B473="",C473="",D473="",E473="",F473=""),"",IF(OR(B473="",C473="",E473=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E473)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G473&lt;&gt;0,F473=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F473&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F473)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C473)*($E$5:$E$504=E473)*(($D$5:$D$504=D473)*(D473&lt;&gt;"")+($B$5:$B$504=B473)*(B473&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B473="",C473="",D473="",E473="",F473=""),"",IF(OR(B473="",C473="",E473=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E473)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H473&lt;&gt;0,F473=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G473&lt;&gt;0,F473=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F473&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F473)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C473)*($E$5:$E$504=E473)*(($D$5:$D$504=D473)*(D473&lt;&gt;"")+($B$5:$B$504=B473)*(B473&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J473" s="5">
@@ -12871,11 +12899,11 @@
         <v/>
       </c>
       <c r="H474" s="5">
-        <f>IF(OR(C474="Удержание",C474="Зачёт встречного требования",C474="Неустойка заявлена"),N(E474),0)</f>
+        <f>IF(OR(C474="Удержание",C474="Зачёт встречного требования",C474="Неустойка заявлена",C474="Допработы без соглашения (спорно)"),N(E474),0)</f>
         <v/>
       </c>
       <c r="I474" s="6">
-        <f>IF(AND(B474="",C474="",D474="",E474="",F474=""),"",IF(OR(B474="",C474="",E474=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E474)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G474&lt;&gt;0,F474=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F474&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F474)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C474)*($E$5:$E$504=E474)*(($D$5:$D$504=D474)*(D474&lt;&gt;"")+($B$5:$B$504=B474)*(B474&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B474="",C474="",D474="",E474="",F474=""),"",IF(OR(B474="",C474="",E474=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E474)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H474&lt;&gt;0,F474=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G474&lt;&gt;0,F474=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F474&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F474)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C474)*($E$5:$E$504=E474)*(($D$5:$D$504=D474)*(D474&lt;&gt;"")+($B$5:$B$504=B474)*(B474&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J474" s="5">
@@ -12897,11 +12925,11 @@
         <v/>
       </c>
       <c r="H475" s="5">
-        <f>IF(OR(C475="Удержание",C475="Зачёт встречного требования",C475="Неустойка заявлена"),N(E475),0)</f>
+        <f>IF(OR(C475="Удержание",C475="Зачёт встречного требования",C475="Неустойка заявлена",C475="Допработы без соглашения (спорно)"),N(E475),0)</f>
         <v/>
       </c>
       <c r="I475" s="6">
-        <f>IF(AND(B475="",C475="",D475="",E475="",F475=""),"",IF(OR(B475="",C475="",E475=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E475)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G475&lt;&gt;0,F475=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F475&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F475)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C475)*($E$5:$E$504=E475)*(($D$5:$D$504=D475)*(D475&lt;&gt;"")+($B$5:$B$504=B475)*(B475&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B475="",C475="",D475="",E475="",F475=""),"",IF(OR(B475="",C475="",E475=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E475)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H475&lt;&gt;0,F475=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G475&lt;&gt;0,F475=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F475&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F475)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C475)*($E$5:$E$504=E475)*(($D$5:$D$504=D475)*(D475&lt;&gt;"")+($B$5:$B$504=B475)*(B475&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J475" s="5">
@@ -12923,11 +12951,11 @@
         <v/>
       </c>
       <c r="H476" s="5">
-        <f>IF(OR(C476="Удержание",C476="Зачёт встречного требования",C476="Неустойка заявлена"),N(E476),0)</f>
+        <f>IF(OR(C476="Удержание",C476="Зачёт встречного требования",C476="Неустойка заявлена",C476="Допработы без соглашения (спорно)"),N(E476),0)</f>
         <v/>
       </c>
       <c r="I476" s="6">
-        <f>IF(AND(B476="",C476="",D476="",E476="",F476=""),"",IF(OR(B476="",C476="",E476=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E476)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G476&lt;&gt;0,F476=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F476&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F476)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C476)*($E$5:$E$504=E476)*(($D$5:$D$504=D476)*(D476&lt;&gt;"")+($B$5:$B$504=B476)*(B476&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B476="",C476="",D476="",E476="",F476=""),"",IF(OR(B476="",C476="",E476=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E476)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H476&lt;&gt;0,F476=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G476&lt;&gt;0,F476=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F476&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F476)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C476)*($E$5:$E$504=E476)*(($D$5:$D$504=D476)*(D476&lt;&gt;"")+($B$5:$B$504=B476)*(B476&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J476" s="5">
@@ -12949,11 +12977,11 @@
         <v/>
       </c>
       <c r="H477" s="5">
-        <f>IF(OR(C477="Удержание",C477="Зачёт встречного требования",C477="Неустойка заявлена"),N(E477),0)</f>
+        <f>IF(OR(C477="Удержание",C477="Зачёт встречного требования",C477="Неустойка заявлена",C477="Допработы без соглашения (спорно)"),N(E477),0)</f>
         <v/>
       </c>
       <c r="I477" s="6">
-        <f>IF(AND(B477="",C477="",D477="",E477="",F477=""),"",IF(OR(B477="",C477="",E477=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E477)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G477&lt;&gt;0,F477=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F477&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F477)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C477)*($E$5:$E$504=E477)*(($D$5:$D$504=D477)*(D477&lt;&gt;"")+($B$5:$B$504=B477)*(B477&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B477="",C477="",D477="",E477="",F477=""),"",IF(OR(B477="",C477="",E477=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E477)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H477&lt;&gt;0,F477=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G477&lt;&gt;0,F477=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F477&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F477)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C477)*($E$5:$E$504=E477)*(($D$5:$D$504=D477)*(D477&lt;&gt;"")+($B$5:$B$504=B477)*(B477&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J477" s="5">
@@ -12975,11 +13003,11 @@
         <v/>
       </c>
       <c r="H478" s="5">
-        <f>IF(OR(C478="Удержание",C478="Зачёт встречного требования",C478="Неустойка заявлена"),N(E478),0)</f>
+        <f>IF(OR(C478="Удержание",C478="Зачёт встречного требования",C478="Неустойка заявлена",C478="Допработы без соглашения (спорно)"),N(E478),0)</f>
         <v/>
       </c>
       <c r="I478" s="6">
-        <f>IF(AND(B478="",C478="",D478="",E478="",F478=""),"",IF(OR(B478="",C478="",E478=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E478)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G478&lt;&gt;0,F478=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F478&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F478)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C478)*($E$5:$E$504=E478)*(($D$5:$D$504=D478)*(D478&lt;&gt;"")+($B$5:$B$504=B478)*(B478&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B478="",C478="",D478="",E478="",F478=""),"",IF(OR(B478="",C478="",E478=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E478)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H478&lt;&gt;0,F478=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G478&lt;&gt;0,F478=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F478&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F478)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C478)*($E$5:$E$504=E478)*(($D$5:$D$504=D478)*(D478&lt;&gt;"")+($B$5:$B$504=B478)*(B478&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J478" s="5">
@@ -13001,11 +13029,11 @@
         <v/>
       </c>
       <c r="H479" s="5">
-        <f>IF(OR(C479="Удержание",C479="Зачёт встречного требования",C479="Неустойка заявлена"),N(E479),0)</f>
+        <f>IF(OR(C479="Удержание",C479="Зачёт встречного требования",C479="Неустойка заявлена",C479="Допработы без соглашения (спорно)"),N(E479),0)</f>
         <v/>
       </c>
       <c r="I479" s="6">
-        <f>IF(AND(B479="",C479="",D479="",E479="",F479=""),"",IF(OR(B479="",C479="",E479=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E479)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G479&lt;&gt;0,F479=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F479&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F479)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C479)*($E$5:$E$504=E479)*(($D$5:$D$504=D479)*(D479&lt;&gt;"")+($B$5:$B$504=B479)*(B479&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B479="",C479="",D479="",E479="",F479=""),"",IF(OR(B479="",C479="",E479=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E479)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H479&lt;&gt;0,F479=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G479&lt;&gt;0,F479=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F479&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F479)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C479)*($E$5:$E$504=E479)*(($D$5:$D$504=D479)*(D479&lt;&gt;"")+($B$5:$B$504=B479)*(B479&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J479" s="5">
@@ -13027,11 +13055,11 @@
         <v/>
       </c>
       <c r="H480" s="5">
-        <f>IF(OR(C480="Удержание",C480="Зачёт встречного требования",C480="Неустойка заявлена"),N(E480),0)</f>
+        <f>IF(OR(C480="Удержание",C480="Зачёт встречного требования",C480="Неустойка заявлена",C480="Допработы без соглашения (спорно)"),N(E480),0)</f>
         <v/>
       </c>
       <c r="I480" s="6">
-        <f>IF(AND(B480="",C480="",D480="",E480="",F480=""),"",IF(OR(B480="",C480="",E480=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E480)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G480&lt;&gt;0,F480=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F480&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F480)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C480)*($E$5:$E$504=E480)*(($D$5:$D$504=D480)*(D480&lt;&gt;"")+($B$5:$B$504=B480)*(B480&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B480="",C480="",D480="",E480="",F480=""),"",IF(OR(B480="",C480="",E480=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E480)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H480&lt;&gt;0,F480=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G480&lt;&gt;0,F480=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F480&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F480)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C480)*($E$5:$E$504=E480)*(($D$5:$D$504=D480)*(D480&lt;&gt;"")+($B$5:$B$504=B480)*(B480&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J480" s="5">
@@ -13053,11 +13081,11 @@
         <v/>
       </c>
       <c r="H481" s="5">
-        <f>IF(OR(C481="Удержание",C481="Зачёт встречного требования",C481="Неустойка заявлена"),N(E481),0)</f>
+        <f>IF(OR(C481="Удержание",C481="Зачёт встречного требования",C481="Неустойка заявлена",C481="Допработы без соглашения (спорно)"),N(E481),0)</f>
         <v/>
       </c>
       <c r="I481" s="6">
-        <f>IF(AND(B481="",C481="",D481="",E481="",F481=""),"",IF(OR(B481="",C481="",E481=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E481)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G481&lt;&gt;0,F481=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F481&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F481)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C481)*($E$5:$E$504=E481)*(($D$5:$D$504=D481)*(D481&lt;&gt;"")+($B$5:$B$504=B481)*(B481&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B481="",C481="",D481="",E481="",F481=""),"",IF(OR(B481="",C481="",E481=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E481)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H481&lt;&gt;0,F481=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G481&lt;&gt;0,F481=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F481&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F481)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C481)*($E$5:$E$504=E481)*(($D$5:$D$504=D481)*(D481&lt;&gt;"")+($B$5:$B$504=B481)*(B481&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J481" s="5">
@@ -13079,11 +13107,11 @@
         <v/>
       </c>
       <c r="H482" s="5">
-        <f>IF(OR(C482="Удержание",C482="Зачёт встречного требования",C482="Неустойка заявлена"),N(E482),0)</f>
+        <f>IF(OR(C482="Удержание",C482="Зачёт встречного требования",C482="Неустойка заявлена",C482="Допработы без соглашения (спорно)"),N(E482),0)</f>
         <v/>
       </c>
       <c r="I482" s="6">
-        <f>IF(AND(B482="",C482="",D482="",E482="",F482=""),"",IF(OR(B482="",C482="",E482=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E482)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G482&lt;&gt;0,F482=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F482&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F482)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C482)*($E$5:$E$504=E482)*(($D$5:$D$504=D482)*(D482&lt;&gt;"")+($B$5:$B$504=B482)*(B482&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B482="",C482="",D482="",E482="",F482=""),"",IF(OR(B482="",C482="",E482=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E482)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H482&lt;&gt;0,F482=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G482&lt;&gt;0,F482=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F482&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F482)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C482)*($E$5:$E$504=E482)*(($D$5:$D$504=D482)*(D482&lt;&gt;"")+($B$5:$B$504=B482)*(B482&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J482" s="5">
@@ -13105,11 +13133,11 @@
         <v/>
       </c>
       <c r="H483" s="5">
-        <f>IF(OR(C483="Удержание",C483="Зачёт встречного требования",C483="Неустойка заявлена"),N(E483),0)</f>
+        <f>IF(OR(C483="Удержание",C483="Зачёт встречного требования",C483="Неустойка заявлена",C483="Допработы без соглашения (спорно)"),N(E483),0)</f>
         <v/>
       </c>
       <c r="I483" s="6">
-        <f>IF(AND(B483="",C483="",D483="",E483="",F483=""),"",IF(OR(B483="",C483="",E483=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E483)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G483&lt;&gt;0,F483=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F483&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F483)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C483)*($E$5:$E$504=E483)*(($D$5:$D$504=D483)*(D483&lt;&gt;"")+($B$5:$B$504=B483)*(B483&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B483="",C483="",D483="",E483="",F483=""),"",IF(OR(B483="",C483="",E483=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E483)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H483&lt;&gt;0,F483=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G483&lt;&gt;0,F483=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F483&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F483)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C483)*($E$5:$E$504=E483)*(($D$5:$D$504=D483)*(D483&lt;&gt;"")+($B$5:$B$504=B483)*(B483&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J483" s="5">
@@ -13131,11 +13159,11 @@
         <v/>
       </c>
       <c r="H484" s="5">
-        <f>IF(OR(C484="Удержание",C484="Зачёт встречного требования",C484="Неустойка заявлена"),N(E484),0)</f>
+        <f>IF(OR(C484="Удержание",C484="Зачёт встречного требования",C484="Неустойка заявлена",C484="Допработы без соглашения (спорно)"),N(E484),0)</f>
         <v/>
       </c>
       <c r="I484" s="6">
-        <f>IF(AND(B484="",C484="",D484="",E484="",F484=""),"",IF(OR(B484="",C484="",E484=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E484)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G484&lt;&gt;0,F484=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F484&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F484)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C484)*($E$5:$E$504=E484)*(($D$5:$D$504=D484)*(D484&lt;&gt;"")+($B$5:$B$504=B484)*(B484&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B484="",C484="",D484="",E484="",F484=""),"",IF(OR(B484="",C484="",E484=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E484)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H484&lt;&gt;0,F484=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G484&lt;&gt;0,F484=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F484&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F484)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C484)*($E$5:$E$504=E484)*(($D$5:$D$504=D484)*(D484&lt;&gt;"")+($B$5:$B$504=B484)*(B484&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J484" s="5">
@@ -13157,11 +13185,11 @@
         <v/>
       </c>
       <c r="H485" s="5">
-        <f>IF(OR(C485="Удержание",C485="Зачёт встречного требования",C485="Неустойка заявлена"),N(E485),0)</f>
+        <f>IF(OR(C485="Удержание",C485="Зачёт встречного требования",C485="Неустойка заявлена",C485="Допработы без соглашения (спорно)"),N(E485),0)</f>
         <v/>
       </c>
       <c r="I485" s="6">
-        <f>IF(AND(B485="",C485="",D485="",E485="",F485=""),"",IF(OR(B485="",C485="",E485=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E485)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G485&lt;&gt;0,F485=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F485&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F485)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C485)*($E$5:$E$504=E485)*(($D$5:$D$504=D485)*(D485&lt;&gt;"")+($B$5:$B$504=B485)*(B485&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B485="",C485="",D485="",E485="",F485=""),"",IF(OR(B485="",C485="",E485=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E485)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H485&lt;&gt;0,F485=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G485&lt;&gt;0,F485=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F485&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F485)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C485)*($E$5:$E$504=E485)*(($D$5:$D$504=D485)*(D485&lt;&gt;"")+($B$5:$B$504=B485)*(B485&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J485" s="5">
@@ -13183,11 +13211,11 @@
         <v/>
       </c>
       <c r="H486" s="5">
-        <f>IF(OR(C486="Удержание",C486="Зачёт встречного требования",C486="Неустойка заявлена"),N(E486),0)</f>
+        <f>IF(OR(C486="Удержание",C486="Зачёт встречного требования",C486="Неустойка заявлена",C486="Допработы без соглашения (спорно)"),N(E486),0)</f>
         <v/>
       </c>
       <c r="I486" s="6">
-        <f>IF(AND(B486="",C486="",D486="",E486="",F486=""),"",IF(OR(B486="",C486="",E486=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E486)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G486&lt;&gt;0,F486=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F486&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F486)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C486)*($E$5:$E$504=E486)*(($D$5:$D$504=D486)*(D486&lt;&gt;"")+($B$5:$B$504=B486)*(B486&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B486="",C486="",D486="",E486="",F486=""),"",IF(OR(B486="",C486="",E486=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E486)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H486&lt;&gt;0,F486=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G486&lt;&gt;0,F486=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F486&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F486)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C486)*($E$5:$E$504=E486)*(($D$5:$D$504=D486)*(D486&lt;&gt;"")+($B$5:$B$504=B486)*(B486&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J486" s="5">
@@ -13209,11 +13237,11 @@
         <v/>
       </c>
       <c r="H487" s="5">
-        <f>IF(OR(C487="Удержание",C487="Зачёт встречного требования",C487="Неустойка заявлена"),N(E487),0)</f>
+        <f>IF(OR(C487="Удержание",C487="Зачёт встречного требования",C487="Неустойка заявлена",C487="Допработы без соглашения (спорно)"),N(E487),0)</f>
         <v/>
       </c>
       <c r="I487" s="6">
-        <f>IF(AND(B487="",C487="",D487="",E487="",F487=""),"",IF(OR(B487="",C487="",E487=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E487)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G487&lt;&gt;0,F487=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F487&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F487)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C487)*($E$5:$E$504=E487)*(($D$5:$D$504=D487)*(D487&lt;&gt;"")+($B$5:$B$504=B487)*(B487&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B487="",C487="",D487="",E487="",F487=""),"",IF(OR(B487="",C487="",E487=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E487)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H487&lt;&gt;0,F487=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G487&lt;&gt;0,F487=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F487&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F487)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C487)*($E$5:$E$504=E487)*(($D$5:$D$504=D487)*(D487&lt;&gt;"")+($B$5:$B$504=B487)*(B487&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J487" s="5">
@@ -13235,11 +13263,11 @@
         <v/>
       </c>
       <c r="H488" s="5">
-        <f>IF(OR(C488="Удержание",C488="Зачёт встречного требования",C488="Неустойка заявлена"),N(E488),0)</f>
+        <f>IF(OR(C488="Удержание",C488="Зачёт встречного требования",C488="Неустойка заявлена",C488="Допработы без соглашения (спорно)"),N(E488),0)</f>
         <v/>
       </c>
       <c r="I488" s="6">
-        <f>IF(AND(B488="",C488="",D488="",E488="",F488=""),"",IF(OR(B488="",C488="",E488=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E488)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G488&lt;&gt;0,F488=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F488&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F488)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C488)*($E$5:$E$504=E488)*(($D$5:$D$504=D488)*(D488&lt;&gt;"")+($B$5:$B$504=B488)*(B488&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B488="",C488="",D488="",E488="",F488=""),"",IF(OR(B488="",C488="",E488=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E488)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H488&lt;&gt;0,F488=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G488&lt;&gt;0,F488=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F488&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F488)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C488)*($E$5:$E$504=E488)*(($D$5:$D$504=D488)*(D488&lt;&gt;"")+($B$5:$B$504=B488)*(B488&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J488" s="5">
@@ -13261,11 +13289,11 @@
         <v/>
       </c>
       <c r="H489" s="5">
-        <f>IF(OR(C489="Удержание",C489="Зачёт встречного требования",C489="Неустойка заявлена"),N(E489),0)</f>
+        <f>IF(OR(C489="Удержание",C489="Зачёт встречного требования",C489="Неустойка заявлена",C489="Допработы без соглашения (спорно)"),N(E489),0)</f>
         <v/>
       </c>
       <c r="I489" s="6">
-        <f>IF(AND(B489="",C489="",D489="",E489="",F489=""),"",IF(OR(B489="",C489="",E489=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E489)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G489&lt;&gt;0,F489=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F489&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F489)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C489)*($E$5:$E$504=E489)*(($D$5:$D$504=D489)*(D489&lt;&gt;"")+($B$5:$B$504=B489)*(B489&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B489="",C489="",D489="",E489="",F489=""),"",IF(OR(B489="",C489="",E489=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E489)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H489&lt;&gt;0,F489=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G489&lt;&gt;0,F489=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F489&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F489)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C489)*($E$5:$E$504=E489)*(($D$5:$D$504=D489)*(D489&lt;&gt;"")+($B$5:$B$504=B489)*(B489&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J489" s="5">
@@ -13287,11 +13315,11 @@
         <v/>
       </c>
       <c r="H490" s="5">
-        <f>IF(OR(C490="Удержание",C490="Зачёт встречного требования",C490="Неустойка заявлена"),N(E490),0)</f>
+        <f>IF(OR(C490="Удержание",C490="Зачёт встречного требования",C490="Неустойка заявлена",C490="Допработы без соглашения (спорно)"),N(E490),0)</f>
         <v/>
       </c>
       <c r="I490" s="6">
-        <f>IF(AND(B490="",C490="",D490="",E490="",F490=""),"",IF(OR(B490="",C490="",E490=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E490)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G490&lt;&gt;0,F490=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F490&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F490)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C490)*($E$5:$E$504=E490)*(($D$5:$D$504=D490)*(D490&lt;&gt;"")+($B$5:$B$504=B490)*(B490&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B490="",C490="",D490="",E490="",F490=""),"",IF(OR(B490="",C490="",E490=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E490)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H490&lt;&gt;0,F490=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G490&lt;&gt;0,F490=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F490&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F490)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C490)*($E$5:$E$504=E490)*(($D$5:$D$504=D490)*(D490&lt;&gt;"")+($B$5:$B$504=B490)*(B490&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J490" s="5">
@@ -13313,11 +13341,11 @@
         <v/>
       </c>
       <c r="H491" s="5">
-        <f>IF(OR(C491="Удержание",C491="Зачёт встречного требования",C491="Неустойка заявлена"),N(E491),0)</f>
+        <f>IF(OR(C491="Удержание",C491="Зачёт встречного требования",C491="Неустойка заявлена",C491="Допработы без соглашения (спорно)"),N(E491),0)</f>
         <v/>
       </c>
       <c r="I491" s="6">
-        <f>IF(AND(B491="",C491="",D491="",E491="",F491=""),"",IF(OR(B491="",C491="",E491=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E491)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G491&lt;&gt;0,F491=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F491&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F491)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C491)*($E$5:$E$504=E491)*(($D$5:$D$504=D491)*(D491&lt;&gt;"")+($B$5:$B$504=B491)*(B491&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B491="",C491="",D491="",E491="",F491=""),"",IF(OR(B491="",C491="",E491=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E491)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H491&lt;&gt;0,F491=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G491&lt;&gt;0,F491=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F491&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F491)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C491)*($E$5:$E$504=E491)*(($D$5:$D$504=D491)*(D491&lt;&gt;"")+($B$5:$B$504=B491)*(B491&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J491" s="5">
@@ -13339,11 +13367,11 @@
         <v/>
       </c>
       <c r="H492" s="5">
-        <f>IF(OR(C492="Удержание",C492="Зачёт встречного требования",C492="Неустойка заявлена"),N(E492),0)</f>
+        <f>IF(OR(C492="Удержание",C492="Зачёт встречного требования",C492="Неустойка заявлена",C492="Допработы без соглашения (спорно)"),N(E492),0)</f>
         <v/>
       </c>
       <c r="I492" s="6">
-        <f>IF(AND(B492="",C492="",D492="",E492="",F492=""),"",IF(OR(B492="",C492="",E492=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E492)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G492&lt;&gt;0,F492=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F492&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F492)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C492)*($E$5:$E$504=E492)*(($D$5:$D$504=D492)*(D492&lt;&gt;"")+($B$5:$B$504=B492)*(B492&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B492="",C492="",D492="",E492="",F492=""),"",IF(OR(B492="",C492="",E492=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E492)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H492&lt;&gt;0,F492=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G492&lt;&gt;0,F492=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F492&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F492)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C492)*($E$5:$E$504=E492)*(($D$5:$D$504=D492)*(D492&lt;&gt;"")+($B$5:$B$504=B492)*(B492&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J492" s="5">
@@ -13365,11 +13393,11 @@
         <v/>
       </c>
       <c r="H493" s="5">
-        <f>IF(OR(C493="Удержание",C493="Зачёт встречного требования",C493="Неустойка заявлена"),N(E493),0)</f>
+        <f>IF(OR(C493="Удержание",C493="Зачёт встречного требования",C493="Неустойка заявлена",C493="Допработы без соглашения (спорно)"),N(E493),0)</f>
         <v/>
       </c>
       <c r="I493" s="6">
-        <f>IF(AND(B493="",C493="",D493="",E493="",F493=""),"",IF(OR(B493="",C493="",E493=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E493)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G493&lt;&gt;0,F493=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F493&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F493)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C493)*($E$5:$E$504=E493)*(($D$5:$D$504=D493)*(D493&lt;&gt;"")+($B$5:$B$504=B493)*(B493&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B493="",C493="",D493="",E493="",F493=""),"",IF(OR(B493="",C493="",E493=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E493)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H493&lt;&gt;0,F493=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G493&lt;&gt;0,F493=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F493&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F493)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C493)*($E$5:$E$504=E493)*(($D$5:$D$504=D493)*(D493&lt;&gt;"")+($B$5:$B$504=B493)*(B493&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J493" s="5">
@@ -13391,11 +13419,11 @@
         <v/>
       </c>
       <c r="H494" s="5">
-        <f>IF(OR(C494="Удержание",C494="Зачёт встречного требования",C494="Неустойка заявлена"),N(E494),0)</f>
+        <f>IF(OR(C494="Удержание",C494="Зачёт встречного требования",C494="Неустойка заявлена",C494="Допработы без соглашения (спорно)"),N(E494),0)</f>
         <v/>
       </c>
       <c r="I494" s="6">
-        <f>IF(AND(B494="",C494="",D494="",E494="",F494=""),"",IF(OR(B494="",C494="",E494=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E494)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G494&lt;&gt;0,F494=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F494&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F494)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C494)*($E$5:$E$504=E494)*(($D$5:$D$504=D494)*(D494&lt;&gt;"")+($B$5:$B$504=B494)*(B494&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B494="",C494="",D494="",E494="",F494=""),"",IF(OR(B494="",C494="",E494=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E494)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H494&lt;&gt;0,F494=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G494&lt;&gt;0,F494=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F494&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F494)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C494)*($E$5:$E$504=E494)*(($D$5:$D$504=D494)*(D494&lt;&gt;"")+($B$5:$B$504=B494)*(B494&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J494" s="5">
@@ -13417,11 +13445,11 @@
         <v/>
       </c>
       <c r="H495" s="5">
-        <f>IF(OR(C495="Удержание",C495="Зачёт встречного требования",C495="Неустойка заявлена"),N(E495),0)</f>
+        <f>IF(OR(C495="Удержание",C495="Зачёт встречного требования",C495="Неустойка заявлена",C495="Допработы без соглашения (спорно)"),N(E495),0)</f>
         <v/>
       </c>
       <c r="I495" s="6">
-        <f>IF(AND(B495="",C495="",D495="",E495="",F495=""),"",IF(OR(B495="",C495="",E495=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E495)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G495&lt;&gt;0,F495=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F495&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F495)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C495)*($E$5:$E$504=E495)*(($D$5:$D$504=D495)*(D495&lt;&gt;"")+($B$5:$B$504=B495)*(B495&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B495="",C495="",D495="",E495="",F495=""),"",IF(OR(B495="",C495="",E495=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E495)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H495&lt;&gt;0,F495=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G495&lt;&gt;0,F495=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F495&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F495)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C495)*($E$5:$E$504=E495)*(($D$5:$D$504=D495)*(D495&lt;&gt;"")+($B$5:$B$504=B495)*(B495&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J495" s="5">
@@ -13443,11 +13471,11 @@
         <v/>
       </c>
       <c r="H496" s="5">
-        <f>IF(OR(C496="Удержание",C496="Зачёт встречного требования",C496="Неустойка заявлена"),N(E496),0)</f>
+        <f>IF(OR(C496="Удержание",C496="Зачёт встречного требования",C496="Неустойка заявлена",C496="Допработы без соглашения (спорно)"),N(E496),0)</f>
         <v/>
       </c>
       <c r="I496" s="6">
-        <f>IF(AND(B496="",C496="",D496="",E496="",F496=""),"",IF(OR(B496="",C496="",E496=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E496)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G496&lt;&gt;0,F496=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F496&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F496)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C496)*($E$5:$E$504=E496)*(($D$5:$D$504=D496)*(D496&lt;&gt;"")+($B$5:$B$504=B496)*(B496&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B496="",C496="",D496="",E496="",F496=""),"",IF(OR(B496="",C496="",E496=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E496)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H496&lt;&gt;0,F496=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G496&lt;&gt;0,F496=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F496&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F496)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C496)*($E$5:$E$504=E496)*(($D$5:$D$504=D496)*(D496&lt;&gt;"")+($B$5:$B$504=B496)*(B496&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J496" s="5">
@@ -13469,11 +13497,11 @@
         <v/>
       </c>
       <c r="H497" s="5">
-        <f>IF(OR(C497="Удержание",C497="Зачёт встречного требования",C497="Неустойка заявлена"),N(E497),0)</f>
+        <f>IF(OR(C497="Удержание",C497="Зачёт встречного требования",C497="Неустойка заявлена",C497="Допработы без соглашения (спорно)"),N(E497),0)</f>
         <v/>
       </c>
       <c r="I497" s="6">
-        <f>IF(AND(B497="",C497="",D497="",E497="",F497=""),"",IF(OR(B497="",C497="",E497=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E497)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G497&lt;&gt;0,F497=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F497&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F497)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C497)*($E$5:$E$504=E497)*(($D$5:$D$504=D497)*(D497&lt;&gt;"")+($B$5:$B$504=B497)*(B497&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B497="",C497="",D497="",E497="",F497=""),"",IF(OR(B497="",C497="",E497=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E497)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H497&lt;&gt;0,F497=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G497&lt;&gt;0,F497=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F497&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F497)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C497)*($E$5:$E$504=E497)*(($D$5:$D$504=D497)*(D497&lt;&gt;"")+($B$5:$B$504=B497)*(B497&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J497" s="5">
@@ -13495,11 +13523,11 @@
         <v/>
       </c>
       <c r="H498" s="5">
-        <f>IF(OR(C498="Удержание",C498="Зачёт встречного требования",C498="Неустойка заявлена"),N(E498),0)</f>
+        <f>IF(OR(C498="Удержание",C498="Зачёт встречного требования",C498="Неустойка заявлена",C498="Допработы без соглашения (спорно)"),N(E498),0)</f>
         <v/>
       </c>
       <c r="I498" s="6">
-        <f>IF(AND(B498="",C498="",D498="",E498="",F498=""),"",IF(OR(B498="",C498="",E498=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E498)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G498&lt;&gt;0,F498=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F498&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F498)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C498)*($E$5:$E$504=E498)*(($D$5:$D$504=D498)*(D498&lt;&gt;"")+($B$5:$B$504=B498)*(B498&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B498="",C498="",D498="",E498="",F498=""),"",IF(OR(B498="",C498="",E498=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E498)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H498&lt;&gt;0,F498=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G498&lt;&gt;0,F498=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F498&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F498)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C498)*($E$5:$E$504=E498)*(($D$5:$D$504=D498)*(D498&lt;&gt;"")+($B$5:$B$504=B498)*(B498&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J498" s="5">
@@ -13521,11 +13549,11 @@
         <v/>
       </c>
       <c r="H499" s="5">
-        <f>IF(OR(C499="Удержание",C499="Зачёт встречного требования",C499="Неустойка заявлена"),N(E499),0)</f>
+        <f>IF(OR(C499="Удержание",C499="Зачёт встречного требования",C499="Неустойка заявлена",C499="Допработы без соглашения (спорно)"),N(E499),0)</f>
         <v/>
       </c>
       <c r="I499" s="6">
-        <f>IF(AND(B499="",C499="",D499="",E499="",F499=""),"",IF(OR(B499="",C499="",E499=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E499)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G499&lt;&gt;0,F499=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F499&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F499)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C499)*($E$5:$E$504=E499)*(($D$5:$D$504=D499)*(D499&lt;&gt;"")+($B$5:$B$504=B499)*(B499&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B499="",C499="",D499="",E499="",F499=""),"",IF(OR(B499="",C499="",E499=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E499)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H499&lt;&gt;0,F499=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G499&lt;&gt;0,F499=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F499&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F499)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C499)*($E$5:$E$504=E499)*(($D$5:$D$504=D499)*(D499&lt;&gt;"")+($B$5:$B$504=B499)*(B499&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J499" s="5">
@@ -13547,11 +13575,11 @@
         <v/>
       </c>
       <c r="H500" s="5">
-        <f>IF(OR(C500="Удержание",C500="Зачёт встречного требования",C500="Неустойка заявлена"),N(E500),0)</f>
+        <f>IF(OR(C500="Удержание",C500="Зачёт встречного требования",C500="Неустойка заявлена",C500="Допработы без соглашения (спорно)"),N(E500),0)</f>
         <v/>
       </c>
       <c r="I500" s="6">
-        <f>IF(AND(B500="",C500="",D500="",E500="",F500=""),"",IF(OR(B500="",C500="",E500=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E500)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G500&lt;&gt;0,F500=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F500&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F500)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C500)*($E$5:$E$504=E500)*(($D$5:$D$504=D500)*(D500&lt;&gt;"")+($B$5:$B$504=B500)*(B500&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B500="",C500="",D500="",E500="",F500=""),"",IF(OR(B500="",C500="",E500=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E500)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H500&lt;&gt;0,F500=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G500&lt;&gt;0,F500=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F500&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F500)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C500)*($E$5:$E$504=E500)*(($D$5:$D$504=D500)*(D500&lt;&gt;"")+($B$5:$B$504=B500)*(B500&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J500" s="5">
@@ -13573,11 +13601,11 @@
         <v/>
       </c>
       <c r="H501" s="5">
-        <f>IF(OR(C501="Удержание",C501="Зачёт встречного требования",C501="Неустойка заявлена"),N(E501),0)</f>
+        <f>IF(OR(C501="Удержание",C501="Зачёт встречного требования",C501="Неустойка заявлена",C501="Допработы без соглашения (спорно)"),N(E501),0)</f>
         <v/>
       </c>
       <c r="I501" s="6">
-        <f>IF(AND(B501="",C501="",D501="",E501="",F501=""),"",IF(OR(B501="",C501="",E501=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E501)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G501&lt;&gt;0,F501=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F501&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F501)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C501)*($E$5:$E$504=E501)*(($D$5:$D$504=D501)*(D501&lt;&gt;"")+($B$5:$B$504=B501)*(B501&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B501="",C501="",D501="",E501="",F501=""),"",IF(OR(B501="",C501="",E501=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E501)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H501&lt;&gt;0,F501=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G501&lt;&gt;0,F501=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F501&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F501)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C501)*($E$5:$E$504=E501)*(($D$5:$D$504=D501)*(D501&lt;&gt;"")+($B$5:$B$504=B501)*(B501&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J501" s="5">
@@ -13599,11 +13627,11 @@
         <v/>
       </c>
       <c r="H502" s="5">
-        <f>IF(OR(C502="Удержание",C502="Зачёт встречного требования",C502="Неустойка заявлена"),N(E502),0)</f>
+        <f>IF(OR(C502="Удержание",C502="Зачёт встречного требования",C502="Неустойка заявлена",C502="Допработы без соглашения (спорно)"),N(E502),0)</f>
         <v/>
       </c>
       <c r="I502" s="6">
-        <f>IF(AND(B502="",C502="",D502="",E502="",F502=""),"",IF(OR(B502="",C502="",E502=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E502)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G502&lt;&gt;0,F502=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F502&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F502)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C502)*($E$5:$E$504=E502)*(($D$5:$D$504=D502)*(D502&lt;&gt;"")+($B$5:$B$504=B502)*(B502&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B502="",C502="",D502="",E502="",F502=""),"",IF(OR(B502="",C502="",E502=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E502)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H502&lt;&gt;0,F502=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G502&lt;&gt;0,F502=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F502&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F502)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C502)*($E$5:$E$504=E502)*(($D$5:$D$504=D502)*(D502&lt;&gt;"")+($B$5:$B$504=B502)*(B502&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J502" s="5">
@@ -13625,11 +13653,11 @@
         <v/>
       </c>
       <c r="H503" s="5">
-        <f>IF(OR(C503="Удержание",C503="Зачёт встречного требования",C503="Неустойка заявлена"),N(E503),0)</f>
+        <f>IF(OR(C503="Удержание",C503="Зачёт встречного требования",C503="Неустойка заявлена",C503="Допработы без соглашения (спорно)"),N(E503),0)</f>
         <v/>
       </c>
       <c r="I503" s="6">
-        <f>IF(AND(B503="",C503="",D503="",E503="",F503=""),"",IF(OR(B503="",C503="",E503=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E503)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G503&lt;&gt;0,F503=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F503&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F503)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C503)*($E$5:$E$504=E503)*(($D$5:$D$504=D503)*(D503&lt;&gt;"")+($B$5:$B$504=B503)*(B503&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B503="",C503="",D503="",E503="",F503=""),"",IF(OR(B503="",C503="",E503=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E503)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H503&lt;&gt;0,F503=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G503&lt;&gt;0,F503=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F503&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F503)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C503)*($E$5:$E$504=E503)*(($D$5:$D$504=D503)*(D503&lt;&gt;"")+($B$5:$B$504=B503)*(B503&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J503" s="5">
@@ -13651,11 +13679,11 @@
         <v/>
       </c>
       <c r="H504" s="5">
-        <f>IF(OR(C504="Удержание",C504="Зачёт встречного требования",C504="Неустойка заявлена"),N(E504),0)</f>
+        <f>IF(OR(C504="Удержание",C504="Зачёт встречного требования",C504="Неустойка заявлена",C504="Допработы без соглашения (спорно)"),N(E504),0)</f>
         <v/>
       </c>
       <c r="I504" s="6">
-        <f>IF(AND(B504="",C504="",D504="",E504="",F504=""),"",IF(OR(B504="",C504="",E504=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E504)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(G504&lt;&gt;0,F504=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F504&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F504)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C504)*($E$5:$E$504=E504)*(($D$5:$D$504=D504)*(D504&lt;&gt;"")+($B$5:$B$504=B504)*(B504&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок"))))))</f>
+        <f>IF(AND(B504="",C504="",D504="",E504="",F504=""),"",IF(OR(B504="",C504="",E504=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E504)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H504&lt;&gt;0,F504=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G504&lt;&gt;0,F504=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F504&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F504)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C504)*($E$5:$E$504=E504)*(($D$5:$D$504=D504)*(D504&lt;&gt;"")+($B$5:$B$504=B504)*(B504&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
         <v/>
       </c>
       <c r="J504" s="5">
@@ -13665,13 +13693,13 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="L15:M20"/>
+    <mergeCell ref="L18:M24"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C5:C504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Недопустимое значение" error="Выберите значение из списка" type="list">
-      <formula1>"Начисление по акту,Оплата,Зачёт аванса по договору,Корректировка (подписана обеими сторонами),Удержание,Зачёт встречного требования,Неустойка заявлена"</formula1>
+      <formula1>"Начисление по акту,Оплата,Зачёт аванса по договору,Корректировка (подписана обеими сторонами),Удержание,Зачёт встречного требования,Неустойка заявлена,Допработы без соглашения (спорно)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13685,7 +13713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13695,14 +13723,17 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -13712,10 +13743,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Одна строка — один акт (или часть долга) со своим сроком оплаты. Начисления, оплаты и зачёты берутся из листа «Взаиморасчёты» по идентификатору акта. Колонка H — долг на первый день просрочки: он нужен файлу 08, лист «Акты». Колонка J — текущий остаток: он нужен там же для сверки, но не как сумма долга. Оплаты, поступившие в первый день просрочки и позже, переносятся в файл 08, лист «Оплаты», с тем же идентификатором акта.</t>
+          <t>Одна строка — один акт (или часть долга) со своим сроком оплаты. Начисления, оплаты, зачёты и спорные операции берутся из листа «Взаиморасчёты» по идентификатору акта. Колонка H — общий долг на первый день просрочки, колонка I — спорная часть по акту (удержание, зачёт встречного требования, неустойка, допработы без соглашения). В файл 08, лист «Акты», переносится только бесспорная часть: колонка J — бесспорный долг на первый день просрочки (в колонку D файла 08), колонка M — текущий бесспорный остаток (в колонку F файла 08, для сверки). Проценты на спорную часть книга не считает ни за какой период. Оплаты, поступившие в первый день просрочки и позже, переносятся в файл 08, лист «Оплаты», с тем же идентификатором акта.</t>
         </is>
       </c>
     </row>
@@ -13757,36 +13788,51 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>ДОЛГ НА ПЕРВЫЙ ДЕНЬ ПРОСРОЧКИ, руб. → файл 08, «Акты»</t>
+          <t>Общий на первый день просрочки, руб.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Спорно по акту, руб. (в расчёт и претензию не идёт)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Бесспорный на первый день просрочки, руб. → файл 08, «Акты», колонка D</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Оплачено с первого дня просрочки, руб. → файл 08, «Оплаты»</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Текущий остаток по акту, руб. → файл 08, «Акты», сверка</t>
+          <t>Текущий общий остаток по акту, руб. → акт сверки</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Текущий бесспорный остаток, руб. → файл 08, «Акты», колонка F (сверка); акт сверки</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Проверка</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Переносить в файл 08</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Актов к переносу в файл 08</t>
         </is>
       </c>
-      <c r="O4" s="5">
-        <f>COUNTIF(L5:L34,"да")</f>
+      <c r="R4" s="5">
+        <f>COUNTIF(O5:O34,"да")</f>
         <v/>
       </c>
     </row>
@@ -13814,28 +13860,40 @@
         <v/>
       </c>
       <c r="I5" s="5">
+        <f>IF(B5="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B5))</f>
+        <v/>
+      </c>
+      <c r="J5" s="5">
+        <f>IF(OR(B5="",E5=""),"",IF(OR(NOT(ISNUMBER(L5)),N(I5)&gt;N(L5)),"ЗАБЛОКИРОВАН",H5-I5))</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
         <f>IF(OR(B5="",E5=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B5,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E5)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B5,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E5))</f>
         <v/>
       </c>
-      <c r="J5" s="5">
-        <f>IF(OR(B5="",E5=""),"",IF(NOT(ISNUMBER(H5)),"ЗАБЛОКИРОВАН",H5-I5))</f>
-        <v/>
-      </c>
-      <c r="K5" s="6">
-        <f>IF(AND(B5="",C5="",D5=""),"",IF(B5="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B5)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D5)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B5)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H5)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J5)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L5" s="6">
-        <f>IF(OR(B5="",K5&lt;&gt;"ок"),"",IF(N(H5)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
-        <v/>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="L5" s="5">
+        <f>IF(OR(B5="",E5=""),"",IF(NOT(ISNUMBER(H5)),"ЗАБЛОКИРОВАН",H5-K5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="5">
+        <f>IF(OR(B5="",E5=""),"",IF(OR(NOT(ISNUMBER(L5)),N(I5)&gt;N(L5)),"ЗАБЛОКИРОВАН",L5-I5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="6">
+        <f>IF(AND(B5="",C5="",D5=""),"",IF(B5="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B5)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D5)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B5)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H5)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L5)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I5)&gt;N(L5),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="6">
+        <f>IF(OR(B5="",N5&lt;&gt;"ок"),"",IF(N(J5)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Строк с ошибкой в колонке «Проверка»</t>
         </is>
       </c>
-      <c r="O5" s="5">
-        <f>COUNTIF(K5:K34,"БЛОК*")</f>
+      <c r="R5" s="5">
+        <f>COUNTIF(N5:N34,"БЛОК*")</f>
         <v/>
       </c>
     </row>
@@ -13863,28 +13921,40 @@
         <v/>
       </c>
       <c r="I6" s="5">
+        <f>IF(B6="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="5">
+        <f>IF(OR(B6="",E6=""),"",IF(OR(NOT(ISNUMBER(L6)),N(I6)&gt;N(L6)),"ЗАБЛОКИРОВАН",H6-I6))</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
         <f>IF(OR(B6="",E6=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B6,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E6)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B6,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E6))</f>
         <v/>
       </c>
-      <c r="J6" s="5">
-        <f>IF(OR(B6="",E6=""),"",IF(NOT(ISNUMBER(H6)),"ЗАБЛОКИРОВАН",H6-I6))</f>
-        <v/>
-      </c>
-      <c r="K6" s="6">
-        <f>IF(AND(B6="",C6="",D6=""),"",IF(B6="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B6)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D6)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B6)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H6)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J6)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L6" s="6">
-        <f>IF(OR(B6="",K6&lt;&gt;"ок"),"",IF(N(H6)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
-        <v/>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="L6" s="5">
+        <f>IF(OR(B6="",E6=""),"",IF(NOT(ISNUMBER(H6)),"ЗАБЛОКИРОВАН",H6-K6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="5">
+        <f>IF(OR(B6="",E6=""),"",IF(OR(NOT(ISNUMBER(L6)),N(I6)&gt;N(L6)),"ЗАБЛОКИРОВАН",L6-I6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="6">
+        <f>IF(AND(B6="",C6="",D6=""),"",IF(B6="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B6)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D6)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B6)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H6)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L6)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I6)&gt;N(L6),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="6">
+        <f>IF(OR(B6="",N6&lt;&gt;"ок"),"",IF(N(J6)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Записей ниже таблицы (не учтены)</t>
         </is>
       </c>
-      <c r="O6" s="5">
-        <f>COUNTA(A35:L1000)</f>
+      <c r="R6" s="5">
+        <f>COUNTA(A35:O1000)</f>
         <v/>
       </c>
     </row>
@@ -13912,28 +13982,40 @@
         <v/>
       </c>
       <c r="I7" s="5">
+        <f>IF(B7="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(OR(B7="",E7=""),"",IF(OR(NOT(ISNUMBER(L7)),N(I7)&gt;N(L7)),"ЗАБЛОКИРОВАН",H7-I7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
         <f>IF(OR(B7="",E7=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B7,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E7)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B7,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E7))</f>
         <v/>
       </c>
-      <c r="J7" s="5">
-        <f>IF(OR(B7="",E7=""),"",IF(NOT(ISNUMBER(H7)),"ЗАБЛОКИРОВАН",H7-I7))</f>
-        <v/>
-      </c>
-      <c r="K7" s="6">
-        <f>IF(AND(B7="",C7="",D7=""),"",IF(B7="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B7)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D7)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B7)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H7)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J7)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L7" s="6">
-        <f>IF(OR(B7="",K7&lt;&gt;"ок"),"",IF(N(H7)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
-        <v/>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="L7" s="5">
+        <f>IF(OR(B7="",E7=""),"",IF(NOT(ISNUMBER(H7)),"ЗАБЛОКИРОВАН",H7-K7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
+        <f>IF(OR(B7="",E7=""),"",IF(OR(NOT(ISNUMBER(L7)),N(I7)&gt;N(L7)),"ЗАБЛОКИРОВАН",L7-I7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="6">
+        <f>IF(AND(B7="",C7="",D7=""),"",IF(B7="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B7)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D7)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B7)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H7)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L7)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I7)&gt;N(L7),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="6">
+        <f>IF(OR(B7="",N7&lt;&gt;"ок"),"",IF(N(J7)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Долг на первый день просрочки, всего по переносимым актам, руб.</t>
+          <t>Общий долг на первый день просрочки, всего по переносимым актам, руб.</t>
         </is>
       </c>
-      <c r="O7" s="5">
-        <f>IF(OR(O5&gt;0,O6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(L5:L34,"да",H5:H34))</f>
+      <c r="R7" s="5">
+        <f>IF(OR(R5&gt;0,R6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(O5:O34,"да",H5:H34))</f>
         <v/>
       </c>
     </row>
@@ -13961,28 +14043,40 @@
         <v/>
       </c>
       <c r="I8" s="5">
+        <f>IF(B8="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="5">
+        <f>IF(OR(B8="",E8=""),"",IF(OR(NOT(ISNUMBER(L8)),N(I8)&gt;N(L8)),"ЗАБЛОКИРОВАН",H8-I8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="5">
         <f>IF(OR(B8="",E8=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B8,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E8)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B8,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E8))</f>
         <v/>
       </c>
-      <c r="J8" s="5">
-        <f>IF(OR(B8="",E8=""),"",IF(NOT(ISNUMBER(H8)),"ЗАБЛОКИРОВАН",H8-I8))</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>IF(AND(B8="",C8="",D8=""),"",IF(B8="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B8)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D8)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B8)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H8)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J8)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L8" s="6">
-        <f>IF(OR(B8="",K8&lt;&gt;"ок"),"",IF(N(H8)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
-        <v/>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="L8" s="5">
+        <f>IF(OR(B8="",E8=""),"",IF(NOT(ISNUMBER(H8)),"ЗАБЛОКИРОВАН",H8-K8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="5">
+        <f>IF(OR(B8="",E8=""),"",IF(OR(NOT(ISNUMBER(L8)),N(I8)&gt;N(L8)),"ЗАБЛОКИРОВАН",L8-I8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="6">
+        <f>IF(AND(B8="",C8="",D8=""),"",IF(B8="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B8)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D8)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B8)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H8)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L8)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I8)&gt;N(L8),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="6">
+        <f>IF(OR(B8="",N8&lt;&gt;"ок"),"",IF(N(J8)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Текущий остаток, всего по переносимым актам, руб.</t>
+          <t>Спорно, всего по переносимым актам, руб.</t>
         </is>
       </c>
-      <c r="O8" s="5">
-        <f>IF(OR(O5&gt;0,O6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(L5:L34,"да",J5:J34))</f>
+      <c r="R8" s="5">
+        <f>IF(OR(R5&gt;0,R6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(O5:O34,"да",I5:I34))</f>
         <v/>
       </c>
     </row>
@@ -14010,19 +14104,40 @@
         <v/>
       </c>
       <c r="I9" s="5">
+        <f>IF(B9="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>IF(OR(B9="",E9=""),"",IF(OR(NOT(ISNUMBER(L9)),N(I9)&gt;N(L9)),"ЗАБЛОКИРОВАН",H9-I9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="5">
         <f>IF(OR(B9="",E9=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B9,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E9)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B9,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E9))</f>
         <v/>
       </c>
-      <c r="J9" s="5">
-        <f>IF(OR(B9="",E9=""),"",IF(NOT(ISNUMBER(H9)),"ЗАБЛОКИРОВАН",H9-I9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="6">
-        <f>IF(AND(B9="",C9="",D9=""),"",IF(B9="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B9)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D9)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B9)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H9)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J9)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L9" s="6">
-        <f>IF(OR(B9="",K9&lt;&gt;"ок"),"",IF(N(H9)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L9" s="5">
+        <f>IF(OR(B9="",E9=""),"",IF(NOT(ISNUMBER(H9)),"ЗАБЛОКИРОВАН",H9-K9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="5">
+        <f>IF(OR(B9="",E9=""),"",IF(OR(NOT(ISNUMBER(L9)),N(I9)&gt;N(L9)),"ЗАБЛОКИРОВАН",L9-I9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6">
+        <f>IF(AND(B9="",C9="",D9=""),"",IF(B9="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B9)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D9)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B9)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H9)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L9)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I9)&gt;N(L9),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="6">
+        <f>IF(OR(B9="",N9&lt;&gt;"ок"),"",IF(N(J9)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>БЕССПОРНЫЙ ДОЛГ НА ПЕРВЫЙ ДЕНЬ ПРОСРОЧКИ, всего по переносимым актам, руб.</t>
+        </is>
+      </c>
+      <c r="R9" s="5">
+        <f>IF(OR(R5&gt;0,R6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(O5:O34,"да",J5:J34))</f>
         <v/>
       </c>
     </row>
@@ -14050,19 +14165,40 @@
         <v/>
       </c>
       <c r="I10" s="5">
+        <f>IF(B10="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="5">
+        <f>IF(OR(B10="",E10=""),"",IF(OR(NOT(ISNUMBER(L10)),N(I10)&gt;N(L10)),"ЗАБЛОКИРОВАН",H10-I10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
         <f>IF(OR(B10="",E10=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B10,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E10)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B10,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E10))</f>
         <v/>
       </c>
-      <c r="J10" s="5">
-        <f>IF(OR(B10="",E10=""),"",IF(NOT(ISNUMBER(H10)),"ЗАБЛОКИРОВАН",H10-I10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>IF(AND(B10="",C10="",D10=""),"",IF(B10="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B10)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D10)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B10)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H10)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J10)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>IF(OR(B10="",K10&lt;&gt;"ок"),"",IF(N(H10)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L10" s="5">
+        <f>IF(OR(B10="",E10=""),"",IF(NOT(ISNUMBER(H10)),"ЗАБЛОКИРОВАН",H10-K10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="5">
+        <f>IF(OR(B10="",E10=""),"",IF(OR(NOT(ISNUMBER(L10)),N(I10)&gt;N(L10)),"ЗАБЛОКИРОВАН",L10-I10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6">
+        <f>IF(AND(B10="",C10="",D10=""),"",IF(B10="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B10)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D10)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B10)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H10)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L10)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I10)&gt;N(L10),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="6">
+        <f>IF(OR(B10="",N10&lt;&gt;"ок"),"",IF(N(J10)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Текущий бесспорный остаток, всего по переносимым актам, руб.</t>
+        </is>
+      </c>
+      <c r="R10" s="5">
+        <f>IF(OR(R5&gt;0,R6&gt;0),"ИТОГ ЗАБЛОКИРОВАН: см. колонку «Проверка»",SUMIF(O5:O34,"да",M5:M34))</f>
         <v/>
       </c>
     </row>
@@ -14090,19 +14226,31 @@
         <v/>
       </c>
       <c r="I11" s="5">
+        <f>IF(B11="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="5">
+        <f>IF(OR(B11="",E11=""),"",IF(OR(NOT(ISNUMBER(L11)),N(I11)&gt;N(L11)),"ЗАБЛОКИРОВАН",H11-I11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
         <f>IF(OR(B11="",E11=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B11,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E11)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B11,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E11))</f>
         <v/>
       </c>
-      <c r="J11" s="5">
-        <f>IF(OR(B11="",E11=""),"",IF(NOT(ISNUMBER(H11)),"ЗАБЛОКИРОВАН",H11-I11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>IF(AND(B11="",C11="",D11=""),"",IF(B11="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B11)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D11)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B11)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H11)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J11)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L11" s="6">
-        <f>IF(OR(B11="",K11&lt;&gt;"ок"),"",IF(N(H11)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L11" s="5">
+        <f>IF(OR(B11="",E11=""),"",IF(NOT(ISNUMBER(H11)),"ЗАБЛОКИРОВАН",H11-K11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="5">
+        <f>IF(OR(B11="",E11=""),"",IF(OR(NOT(ISNUMBER(L11)),N(I11)&gt;N(L11)),"ЗАБЛОКИРОВАН",L11-I11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>IF(AND(B11="",C11="",D11=""),"",IF(B11="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B11)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D11)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B11)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H11)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L11)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I11)&gt;N(L11),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="6">
+        <f>IF(OR(B11="",N11&lt;&gt;"ок"),"",IF(N(J11)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14130,19 +14278,31 @@
         <v/>
       </c>
       <c r="I12" s="5">
+        <f>IF(B12="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="5">
+        <f>IF(OR(B12="",E12=""),"",IF(OR(NOT(ISNUMBER(L12)),N(I12)&gt;N(L12)),"ЗАБЛОКИРОВАН",H12-I12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
         <f>IF(OR(B12="",E12=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B12,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E12)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B12,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E12))</f>
         <v/>
       </c>
-      <c r="J12" s="5">
-        <f>IF(OR(B12="",E12=""),"",IF(NOT(ISNUMBER(H12)),"ЗАБЛОКИРОВАН",H12-I12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="6">
-        <f>IF(AND(B12="",C12="",D12=""),"",IF(B12="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B12)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D12)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B12)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H12)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J12)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L12" s="6">
-        <f>IF(OR(B12="",K12&lt;&gt;"ок"),"",IF(N(H12)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L12" s="5">
+        <f>IF(OR(B12="",E12=""),"",IF(NOT(ISNUMBER(H12)),"ЗАБЛОКИРОВАН",H12-K12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="5">
+        <f>IF(OR(B12="",E12=""),"",IF(OR(NOT(ISNUMBER(L12)),N(I12)&gt;N(L12)),"ЗАБЛОКИРОВАН",L12-I12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>IF(AND(B12="",C12="",D12=""),"",IF(B12="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B12)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D12)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B12)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H12)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L12)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I12)&gt;N(L12),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="6">
+        <f>IF(OR(B12="",N12&lt;&gt;"ок"),"",IF(N(J12)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14170,19 +14330,31 @@
         <v/>
       </c>
       <c r="I13" s="5">
+        <f>IF(B13="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="5">
+        <f>IF(OR(B13="",E13=""),"",IF(OR(NOT(ISNUMBER(L13)),N(I13)&gt;N(L13)),"ЗАБЛОКИРОВАН",H13-I13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
         <f>IF(OR(B13="",E13=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B13,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E13)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B13,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E13))</f>
         <v/>
       </c>
-      <c r="J13" s="5">
-        <f>IF(OR(B13="",E13=""),"",IF(NOT(ISNUMBER(H13)),"ЗАБЛОКИРОВАН",H13-I13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="6">
-        <f>IF(AND(B13="",C13="",D13=""),"",IF(B13="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B13)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D13)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B13)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H13)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J13)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L13" s="6">
-        <f>IF(OR(B13="",K13&lt;&gt;"ок"),"",IF(N(H13)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L13" s="5">
+        <f>IF(OR(B13="",E13=""),"",IF(NOT(ISNUMBER(H13)),"ЗАБЛОКИРОВАН",H13-K13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="5">
+        <f>IF(OR(B13="",E13=""),"",IF(OR(NOT(ISNUMBER(L13)),N(I13)&gt;N(L13)),"ЗАБЛОКИРОВАН",L13-I13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="6">
+        <f>IF(AND(B13="",C13="",D13=""),"",IF(B13="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B13)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D13)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B13)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H13)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L13)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I13)&gt;N(L13),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="6">
+        <f>IF(OR(B13="",N13&lt;&gt;"ок"),"",IF(N(J13)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14210,19 +14382,31 @@
         <v/>
       </c>
       <c r="I14" s="5">
+        <f>IF(B14="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="5">
+        <f>IF(OR(B14="",E14=""),"",IF(OR(NOT(ISNUMBER(L14)),N(I14)&gt;N(L14)),"ЗАБЛОКИРОВАН",H14-I14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="5">
         <f>IF(OR(B14="",E14=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B14,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E14)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B14,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E14))</f>
         <v/>
       </c>
-      <c r="J14" s="5">
-        <f>IF(OR(B14="",E14=""),"",IF(NOT(ISNUMBER(H14)),"ЗАБЛОКИРОВАН",H14-I14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="6">
-        <f>IF(AND(B14="",C14="",D14=""),"",IF(B14="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B14)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D14)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B14)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H14)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J14)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="6">
-        <f>IF(OR(B14="",K14&lt;&gt;"ок"),"",IF(N(H14)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L14" s="5">
+        <f>IF(OR(B14="",E14=""),"",IF(NOT(ISNUMBER(H14)),"ЗАБЛОКИРОВАН",H14-K14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="5">
+        <f>IF(OR(B14="",E14=""),"",IF(OR(NOT(ISNUMBER(L14)),N(I14)&gt;N(L14)),"ЗАБЛОКИРОВАН",L14-I14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="6">
+        <f>IF(AND(B14="",C14="",D14=""),"",IF(B14="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B14)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D14)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B14)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H14)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L14)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I14)&gt;N(L14),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="6">
+        <f>IF(OR(B14="",N14&lt;&gt;"ок"),"",IF(N(J14)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14250,19 +14434,31 @@
         <v/>
       </c>
       <c r="I15" s="5">
+        <f>IF(B15="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="5">
+        <f>IF(OR(B15="",E15=""),"",IF(OR(NOT(ISNUMBER(L15)),N(I15)&gt;N(L15)),"ЗАБЛОКИРОВАН",H15-I15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
         <f>IF(OR(B15="",E15=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B15,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E15)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B15,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E15))</f>
         <v/>
       </c>
-      <c r="J15" s="5">
-        <f>IF(OR(B15="",E15=""),"",IF(NOT(ISNUMBER(H15)),"ЗАБЛОКИРОВАН",H15-I15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="6">
-        <f>IF(AND(B15="",C15="",D15=""),"",IF(B15="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B15)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D15)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B15)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H15)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J15)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L15" s="6">
-        <f>IF(OR(B15="",K15&lt;&gt;"ок"),"",IF(N(H15)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L15" s="5">
+        <f>IF(OR(B15="",E15=""),"",IF(NOT(ISNUMBER(H15)),"ЗАБЛОКИРОВАН",H15-K15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="5">
+        <f>IF(OR(B15="",E15=""),"",IF(OR(NOT(ISNUMBER(L15)),N(I15)&gt;N(L15)),"ЗАБЛОКИРОВАН",L15-I15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="6">
+        <f>IF(AND(B15="",C15="",D15=""),"",IF(B15="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B15)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D15)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B15)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H15)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L15)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I15)&gt;N(L15),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="6">
+        <f>IF(OR(B15="",N15&lt;&gt;"ок"),"",IF(N(J15)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14290,19 +14486,31 @@
         <v/>
       </c>
       <c r="I16" s="5">
+        <f>IF(B16="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="5">
+        <f>IF(OR(B16="",E16=""),"",IF(OR(NOT(ISNUMBER(L16)),N(I16)&gt;N(L16)),"ЗАБЛОКИРОВАН",H16-I16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="5">
         <f>IF(OR(B16="",E16=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B16,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E16)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B16,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E16))</f>
         <v/>
       </c>
-      <c r="J16" s="5">
-        <f>IF(OR(B16="",E16=""),"",IF(NOT(ISNUMBER(H16)),"ЗАБЛОКИРОВАН",H16-I16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="6">
-        <f>IF(AND(B16="",C16="",D16=""),"",IF(B16="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B16)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D16)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B16)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H16)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J16)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L16" s="6">
-        <f>IF(OR(B16="",K16&lt;&gt;"ок"),"",IF(N(H16)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L16" s="5">
+        <f>IF(OR(B16="",E16=""),"",IF(NOT(ISNUMBER(H16)),"ЗАБЛОКИРОВАН",H16-K16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="5">
+        <f>IF(OR(B16="",E16=""),"",IF(OR(NOT(ISNUMBER(L16)),N(I16)&gt;N(L16)),"ЗАБЛОКИРОВАН",L16-I16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="6">
+        <f>IF(AND(B16="",C16="",D16=""),"",IF(B16="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B16)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D16)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B16)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H16)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L16)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I16)&gt;N(L16),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O16" s="6">
+        <f>IF(OR(B16="",N16&lt;&gt;"ок"),"",IF(N(J16)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14330,19 +14538,31 @@
         <v/>
       </c>
       <c r="I17" s="5">
+        <f>IF(B17="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="5">
+        <f>IF(OR(B17="",E17=""),"",IF(OR(NOT(ISNUMBER(L17)),N(I17)&gt;N(L17)),"ЗАБЛОКИРОВАН",H17-I17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
         <f>IF(OR(B17="",E17=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B17,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E17)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B17,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E17))</f>
         <v/>
       </c>
-      <c r="J17" s="5">
-        <f>IF(OR(B17="",E17=""),"",IF(NOT(ISNUMBER(H17)),"ЗАБЛОКИРОВАН",H17-I17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="6">
-        <f>IF(AND(B17="",C17="",D17=""),"",IF(B17="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B17)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D17)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B17)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H17)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J17)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>IF(OR(B17="",K17&lt;&gt;"ок"),"",IF(N(H17)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L17" s="5">
+        <f>IF(OR(B17="",E17=""),"",IF(NOT(ISNUMBER(H17)),"ЗАБЛОКИРОВАН",H17-K17))</f>
+        <v/>
+      </c>
+      <c r="M17" s="5">
+        <f>IF(OR(B17="",E17=""),"",IF(OR(NOT(ISNUMBER(L17)),N(I17)&gt;N(L17)),"ЗАБЛОКИРОВАН",L17-I17))</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>IF(AND(B17="",C17="",D17=""),"",IF(B17="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B17)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D17)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B17)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H17)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L17)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I17)&gt;N(L17),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O17" s="6">
+        <f>IF(OR(B17="",N17&lt;&gt;"ок"),"",IF(N(J17)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14370,19 +14590,31 @@
         <v/>
       </c>
       <c r="I18" s="5">
+        <f>IF(B18="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="5">
+        <f>IF(OR(B18="",E18=""),"",IF(OR(NOT(ISNUMBER(L18)),N(I18)&gt;N(L18)),"ЗАБЛОКИРОВАН",H18-I18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="5">
         <f>IF(OR(B18="",E18=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B18,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E18)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B18,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E18))</f>
         <v/>
       </c>
-      <c r="J18" s="5">
-        <f>IF(OR(B18="",E18=""),"",IF(NOT(ISNUMBER(H18)),"ЗАБЛОКИРОВАН",H18-I18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="6">
-        <f>IF(AND(B18="",C18="",D18=""),"",IF(B18="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B18)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D18)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B18)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H18)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J18)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L18" s="6">
-        <f>IF(OR(B18="",K18&lt;&gt;"ок"),"",IF(N(H18)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L18" s="5">
+        <f>IF(OR(B18="",E18=""),"",IF(NOT(ISNUMBER(H18)),"ЗАБЛОКИРОВАН",H18-K18))</f>
+        <v/>
+      </c>
+      <c r="M18" s="5">
+        <f>IF(OR(B18="",E18=""),"",IF(OR(NOT(ISNUMBER(L18)),N(I18)&gt;N(L18)),"ЗАБЛОКИРОВАН",L18-I18))</f>
+        <v/>
+      </c>
+      <c r="N18" s="6">
+        <f>IF(AND(B18="",C18="",D18=""),"",IF(B18="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B18)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D18)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B18)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H18)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L18)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I18)&gt;N(L18),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="6">
+        <f>IF(OR(B18="",N18&lt;&gt;"ок"),"",IF(N(J18)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14410,19 +14642,31 @@
         <v/>
       </c>
       <c r="I19" s="5">
+        <f>IF(B19="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="5">
+        <f>IF(OR(B19="",E19=""),"",IF(OR(NOT(ISNUMBER(L19)),N(I19)&gt;N(L19)),"ЗАБЛОКИРОВАН",H19-I19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="5">
         <f>IF(OR(B19="",E19=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B19,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E19)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B19,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E19))</f>
         <v/>
       </c>
-      <c r="J19" s="5">
-        <f>IF(OR(B19="",E19=""),"",IF(NOT(ISNUMBER(H19)),"ЗАБЛОКИРОВАН",H19-I19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="6">
-        <f>IF(AND(B19="",C19="",D19=""),"",IF(B19="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B19)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D19)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B19)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H19)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J19)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L19" s="6">
-        <f>IF(OR(B19="",K19&lt;&gt;"ок"),"",IF(N(H19)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L19" s="5">
+        <f>IF(OR(B19="",E19=""),"",IF(NOT(ISNUMBER(H19)),"ЗАБЛОКИРОВАН",H19-K19))</f>
+        <v/>
+      </c>
+      <c r="M19" s="5">
+        <f>IF(OR(B19="",E19=""),"",IF(OR(NOT(ISNUMBER(L19)),N(I19)&gt;N(L19)),"ЗАБЛОКИРОВАН",L19-I19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="6">
+        <f>IF(AND(B19="",C19="",D19=""),"",IF(B19="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B19)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D19)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B19)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H19)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L19)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I19)&gt;N(L19),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O19" s="6">
+        <f>IF(OR(B19="",N19&lt;&gt;"ок"),"",IF(N(J19)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14450,19 +14694,31 @@
         <v/>
       </c>
       <c r="I20" s="5">
+        <f>IF(B20="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="5">
+        <f>IF(OR(B20="",E20=""),"",IF(OR(NOT(ISNUMBER(L20)),N(I20)&gt;N(L20)),"ЗАБЛОКИРОВАН",H20-I20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="5">
         <f>IF(OR(B20="",E20=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B20,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E20)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B20,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E20))</f>
         <v/>
       </c>
-      <c r="J20" s="5">
-        <f>IF(OR(B20="",E20=""),"",IF(NOT(ISNUMBER(H20)),"ЗАБЛОКИРОВАН",H20-I20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="6">
-        <f>IF(AND(B20="",C20="",D20=""),"",IF(B20="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B20)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D20)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B20)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H20)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J20)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L20" s="6">
-        <f>IF(OR(B20="",K20&lt;&gt;"ок"),"",IF(N(H20)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L20" s="5">
+        <f>IF(OR(B20="",E20=""),"",IF(NOT(ISNUMBER(H20)),"ЗАБЛОКИРОВАН",H20-K20))</f>
+        <v/>
+      </c>
+      <c r="M20" s="5">
+        <f>IF(OR(B20="",E20=""),"",IF(OR(NOT(ISNUMBER(L20)),N(I20)&gt;N(L20)),"ЗАБЛОКИРОВАН",L20-I20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="6">
+        <f>IF(AND(B20="",C20="",D20=""),"",IF(B20="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B20)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D20)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B20)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H20)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L20)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I20)&gt;N(L20),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O20" s="6">
+        <f>IF(OR(B20="",N20&lt;&gt;"ок"),"",IF(N(J20)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14490,19 +14746,31 @@
         <v/>
       </c>
       <c r="I21" s="5">
+        <f>IF(B21="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="5">
+        <f>IF(OR(B21="",E21=""),"",IF(OR(NOT(ISNUMBER(L21)),N(I21)&gt;N(L21)),"ЗАБЛОКИРОВАН",H21-I21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="5">
         <f>IF(OR(B21="",E21=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B21,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E21)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B21,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E21))</f>
         <v/>
       </c>
-      <c r="J21" s="5">
-        <f>IF(OR(B21="",E21=""),"",IF(NOT(ISNUMBER(H21)),"ЗАБЛОКИРОВАН",H21-I21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="6">
-        <f>IF(AND(B21="",C21="",D21=""),"",IF(B21="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B21)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D21)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B21)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H21)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J21)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L21" s="6">
-        <f>IF(OR(B21="",K21&lt;&gt;"ок"),"",IF(N(H21)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L21" s="5">
+        <f>IF(OR(B21="",E21=""),"",IF(NOT(ISNUMBER(H21)),"ЗАБЛОКИРОВАН",H21-K21))</f>
+        <v/>
+      </c>
+      <c r="M21" s="5">
+        <f>IF(OR(B21="",E21=""),"",IF(OR(NOT(ISNUMBER(L21)),N(I21)&gt;N(L21)),"ЗАБЛОКИРОВАН",L21-I21))</f>
+        <v/>
+      </c>
+      <c r="N21" s="6">
+        <f>IF(AND(B21="",C21="",D21=""),"",IF(B21="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B21)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D21)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B21)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H21)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L21)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I21)&gt;N(L21),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O21" s="6">
+        <f>IF(OR(B21="",N21&lt;&gt;"ок"),"",IF(N(J21)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14530,19 +14798,31 @@
         <v/>
       </c>
       <c r="I22" s="5">
+        <f>IF(B22="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="5">
+        <f>IF(OR(B22="",E22=""),"",IF(OR(NOT(ISNUMBER(L22)),N(I22)&gt;N(L22)),"ЗАБЛОКИРОВАН",H22-I22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="5">
         <f>IF(OR(B22="",E22=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B22,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E22)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B22,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E22))</f>
         <v/>
       </c>
-      <c r="J22" s="5">
-        <f>IF(OR(B22="",E22=""),"",IF(NOT(ISNUMBER(H22)),"ЗАБЛОКИРОВАН",H22-I22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="6">
-        <f>IF(AND(B22="",C22="",D22=""),"",IF(B22="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B22)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D22)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B22)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H22)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J22)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L22" s="6">
-        <f>IF(OR(B22="",K22&lt;&gt;"ок"),"",IF(N(H22)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L22" s="5">
+        <f>IF(OR(B22="",E22=""),"",IF(NOT(ISNUMBER(H22)),"ЗАБЛОКИРОВАН",H22-K22))</f>
+        <v/>
+      </c>
+      <c r="M22" s="5">
+        <f>IF(OR(B22="",E22=""),"",IF(OR(NOT(ISNUMBER(L22)),N(I22)&gt;N(L22)),"ЗАБЛОКИРОВАН",L22-I22))</f>
+        <v/>
+      </c>
+      <c r="N22" s="6">
+        <f>IF(AND(B22="",C22="",D22=""),"",IF(B22="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B22)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D22)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B22)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H22)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L22)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I22)&gt;N(L22),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O22" s="6">
+        <f>IF(OR(B22="",N22&lt;&gt;"ок"),"",IF(N(J22)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14570,19 +14850,31 @@
         <v/>
       </c>
       <c r="I23" s="5">
+        <f>IF(B23="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="5">
+        <f>IF(OR(B23="",E23=""),"",IF(OR(NOT(ISNUMBER(L23)),N(I23)&gt;N(L23)),"ЗАБЛОКИРОВАН",H23-I23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="5">
         <f>IF(OR(B23="",E23=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B23,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E23)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B23,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E23))</f>
         <v/>
       </c>
-      <c r="J23" s="5">
-        <f>IF(OR(B23="",E23=""),"",IF(NOT(ISNUMBER(H23)),"ЗАБЛОКИРОВАН",H23-I23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="6">
-        <f>IF(AND(B23="",C23="",D23=""),"",IF(B23="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B23)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D23)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B23)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H23)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J23)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L23" s="6">
-        <f>IF(OR(B23="",K23&lt;&gt;"ок"),"",IF(N(H23)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L23" s="5">
+        <f>IF(OR(B23="",E23=""),"",IF(NOT(ISNUMBER(H23)),"ЗАБЛОКИРОВАН",H23-K23))</f>
+        <v/>
+      </c>
+      <c r="M23" s="5">
+        <f>IF(OR(B23="",E23=""),"",IF(OR(NOT(ISNUMBER(L23)),N(I23)&gt;N(L23)),"ЗАБЛОКИРОВАН",L23-I23))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6">
+        <f>IF(AND(B23="",C23="",D23=""),"",IF(B23="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B23)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D23)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B23)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H23)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L23)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I23)&gt;N(L23),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O23" s="6">
+        <f>IF(OR(B23="",N23&lt;&gt;"ок"),"",IF(N(J23)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14610,19 +14902,31 @@
         <v/>
       </c>
       <c r="I24" s="5">
+        <f>IF(B24="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="5">
+        <f>IF(OR(B24="",E24=""),"",IF(OR(NOT(ISNUMBER(L24)),N(I24)&gt;N(L24)),"ЗАБЛОКИРОВАН",H24-I24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="5">
         <f>IF(OR(B24="",E24=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B24,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E24)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B24,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E24))</f>
         <v/>
       </c>
-      <c r="J24" s="5">
-        <f>IF(OR(B24="",E24=""),"",IF(NOT(ISNUMBER(H24)),"ЗАБЛОКИРОВАН",H24-I24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="6">
-        <f>IF(AND(B24="",C24="",D24=""),"",IF(B24="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B24)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D24)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B24)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H24)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J24)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L24" s="6">
-        <f>IF(OR(B24="",K24&lt;&gt;"ок"),"",IF(N(H24)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L24" s="5">
+        <f>IF(OR(B24="",E24=""),"",IF(NOT(ISNUMBER(H24)),"ЗАБЛОКИРОВАН",H24-K24))</f>
+        <v/>
+      </c>
+      <c r="M24" s="5">
+        <f>IF(OR(B24="",E24=""),"",IF(OR(NOT(ISNUMBER(L24)),N(I24)&gt;N(L24)),"ЗАБЛОКИРОВАН",L24-I24))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6">
+        <f>IF(AND(B24="",C24="",D24=""),"",IF(B24="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B24)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D24)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B24)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H24)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L24)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I24)&gt;N(L24),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O24" s="6">
+        <f>IF(OR(B24="",N24&lt;&gt;"ок"),"",IF(N(J24)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14650,19 +14954,31 @@
         <v/>
       </c>
       <c r="I25" s="5">
+        <f>IF(B25="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="5">
+        <f>IF(OR(B25="",E25=""),"",IF(OR(NOT(ISNUMBER(L25)),N(I25)&gt;N(L25)),"ЗАБЛОКИРОВАН",H25-I25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="5">
         <f>IF(OR(B25="",E25=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B25,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E25)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B25,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E25))</f>
         <v/>
       </c>
-      <c r="J25" s="5">
-        <f>IF(OR(B25="",E25=""),"",IF(NOT(ISNUMBER(H25)),"ЗАБЛОКИРОВАН",H25-I25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="6">
-        <f>IF(AND(B25="",C25="",D25=""),"",IF(B25="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B25)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D25)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B25)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H25)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J25)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L25" s="6">
-        <f>IF(OR(B25="",K25&lt;&gt;"ок"),"",IF(N(H25)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L25" s="5">
+        <f>IF(OR(B25="",E25=""),"",IF(NOT(ISNUMBER(H25)),"ЗАБЛОКИРОВАН",H25-K25))</f>
+        <v/>
+      </c>
+      <c r="M25" s="5">
+        <f>IF(OR(B25="",E25=""),"",IF(OR(NOT(ISNUMBER(L25)),N(I25)&gt;N(L25)),"ЗАБЛОКИРОВАН",L25-I25))</f>
+        <v/>
+      </c>
+      <c r="N25" s="6">
+        <f>IF(AND(B25="",C25="",D25=""),"",IF(B25="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B25)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D25)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B25)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H25)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L25)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I25)&gt;N(L25),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O25" s="6">
+        <f>IF(OR(B25="",N25&lt;&gt;"ок"),"",IF(N(J25)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14690,19 +15006,31 @@
         <v/>
       </c>
       <c r="I26" s="5">
+        <f>IF(B26="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="5">
+        <f>IF(OR(B26="",E26=""),"",IF(OR(NOT(ISNUMBER(L26)),N(I26)&gt;N(L26)),"ЗАБЛОКИРОВАН",H26-I26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="5">
         <f>IF(OR(B26="",E26=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B26,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E26)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B26,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E26))</f>
         <v/>
       </c>
-      <c r="J26" s="5">
-        <f>IF(OR(B26="",E26=""),"",IF(NOT(ISNUMBER(H26)),"ЗАБЛОКИРОВАН",H26-I26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="6">
-        <f>IF(AND(B26="",C26="",D26=""),"",IF(B26="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B26)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D26)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B26)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H26)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J26)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L26" s="6">
-        <f>IF(OR(B26="",K26&lt;&gt;"ок"),"",IF(N(H26)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L26" s="5">
+        <f>IF(OR(B26="",E26=""),"",IF(NOT(ISNUMBER(H26)),"ЗАБЛОКИРОВАН",H26-K26))</f>
+        <v/>
+      </c>
+      <c r="M26" s="5">
+        <f>IF(OR(B26="",E26=""),"",IF(OR(NOT(ISNUMBER(L26)),N(I26)&gt;N(L26)),"ЗАБЛОКИРОВАН",L26-I26))</f>
+        <v/>
+      </c>
+      <c r="N26" s="6">
+        <f>IF(AND(B26="",C26="",D26=""),"",IF(B26="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B26)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D26)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B26)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H26)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L26)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I26)&gt;N(L26),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O26" s="6">
+        <f>IF(OR(B26="",N26&lt;&gt;"ок"),"",IF(N(J26)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14730,19 +15058,31 @@
         <v/>
       </c>
       <c r="I27" s="5">
+        <f>IF(B27="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="5">
+        <f>IF(OR(B27="",E27=""),"",IF(OR(NOT(ISNUMBER(L27)),N(I27)&gt;N(L27)),"ЗАБЛОКИРОВАН",H27-I27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="5">
         <f>IF(OR(B27="",E27=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B27,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E27)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B27,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E27))</f>
         <v/>
       </c>
-      <c r="J27" s="5">
-        <f>IF(OR(B27="",E27=""),"",IF(NOT(ISNUMBER(H27)),"ЗАБЛОКИРОВАН",H27-I27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="6">
-        <f>IF(AND(B27="",C27="",D27=""),"",IF(B27="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B27)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D27)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B27)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H27)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J27)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L27" s="6">
-        <f>IF(OR(B27="",K27&lt;&gt;"ок"),"",IF(N(H27)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L27" s="5">
+        <f>IF(OR(B27="",E27=""),"",IF(NOT(ISNUMBER(H27)),"ЗАБЛОКИРОВАН",H27-K27))</f>
+        <v/>
+      </c>
+      <c r="M27" s="5">
+        <f>IF(OR(B27="",E27=""),"",IF(OR(NOT(ISNUMBER(L27)),N(I27)&gt;N(L27)),"ЗАБЛОКИРОВАН",L27-I27))</f>
+        <v/>
+      </c>
+      <c r="N27" s="6">
+        <f>IF(AND(B27="",C27="",D27=""),"",IF(B27="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B27)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D27)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B27)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H27)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L27)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I27)&gt;N(L27),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O27" s="6">
+        <f>IF(OR(B27="",N27&lt;&gt;"ок"),"",IF(N(J27)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14770,19 +15110,31 @@
         <v/>
       </c>
       <c r="I28" s="5">
+        <f>IF(B28="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="5">
+        <f>IF(OR(B28="",E28=""),"",IF(OR(NOT(ISNUMBER(L28)),N(I28)&gt;N(L28)),"ЗАБЛОКИРОВАН",H28-I28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="5">
         <f>IF(OR(B28="",E28=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B28,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E28)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B28,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E28))</f>
         <v/>
       </c>
-      <c r="J28" s="5">
-        <f>IF(OR(B28="",E28=""),"",IF(NOT(ISNUMBER(H28)),"ЗАБЛОКИРОВАН",H28-I28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="6">
-        <f>IF(AND(B28="",C28="",D28=""),"",IF(B28="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B28)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D28)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B28)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H28)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J28)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L28" s="6">
-        <f>IF(OR(B28="",K28&lt;&gt;"ок"),"",IF(N(H28)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L28" s="5">
+        <f>IF(OR(B28="",E28=""),"",IF(NOT(ISNUMBER(H28)),"ЗАБЛОКИРОВАН",H28-K28))</f>
+        <v/>
+      </c>
+      <c r="M28" s="5">
+        <f>IF(OR(B28="",E28=""),"",IF(OR(NOT(ISNUMBER(L28)),N(I28)&gt;N(L28)),"ЗАБЛОКИРОВАН",L28-I28))</f>
+        <v/>
+      </c>
+      <c r="N28" s="6">
+        <f>IF(AND(B28="",C28="",D28=""),"",IF(B28="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B28)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D28)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B28)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H28)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L28)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I28)&gt;N(L28),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O28" s="6">
+        <f>IF(OR(B28="",N28&lt;&gt;"ок"),"",IF(N(J28)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14810,19 +15162,31 @@
         <v/>
       </c>
       <c r="I29" s="5">
+        <f>IF(B29="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="5">
+        <f>IF(OR(B29="",E29=""),"",IF(OR(NOT(ISNUMBER(L29)),N(I29)&gt;N(L29)),"ЗАБЛОКИРОВАН",H29-I29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="5">
         <f>IF(OR(B29="",E29=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B29,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E29)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B29,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E29))</f>
         <v/>
       </c>
-      <c r="J29" s="5">
-        <f>IF(OR(B29="",E29=""),"",IF(NOT(ISNUMBER(H29)),"ЗАБЛОКИРОВАН",H29-I29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="6">
-        <f>IF(AND(B29="",C29="",D29=""),"",IF(B29="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B29)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D29)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B29)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H29)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J29)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L29" s="6">
-        <f>IF(OR(B29="",K29&lt;&gt;"ок"),"",IF(N(H29)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L29" s="5">
+        <f>IF(OR(B29="",E29=""),"",IF(NOT(ISNUMBER(H29)),"ЗАБЛОКИРОВАН",H29-K29))</f>
+        <v/>
+      </c>
+      <c r="M29" s="5">
+        <f>IF(OR(B29="",E29=""),"",IF(OR(NOT(ISNUMBER(L29)),N(I29)&gt;N(L29)),"ЗАБЛОКИРОВАН",L29-I29))</f>
+        <v/>
+      </c>
+      <c r="N29" s="6">
+        <f>IF(AND(B29="",C29="",D29=""),"",IF(B29="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B29)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D29)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B29)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H29)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L29)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I29)&gt;N(L29),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O29" s="6">
+        <f>IF(OR(B29="",N29&lt;&gt;"ок"),"",IF(N(J29)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14850,19 +15214,31 @@
         <v/>
       </c>
       <c r="I30" s="5">
+        <f>IF(B30="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="5">
+        <f>IF(OR(B30="",E30=""),"",IF(OR(NOT(ISNUMBER(L30)),N(I30)&gt;N(L30)),"ЗАБЛОКИРОВАН",H30-I30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="5">
         <f>IF(OR(B30="",E30=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B30,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E30)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B30,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E30))</f>
         <v/>
       </c>
-      <c r="J30" s="5">
-        <f>IF(OR(B30="",E30=""),"",IF(NOT(ISNUMBER(H30)),"ЗАБЛОКИРОВАН",H30-I30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="6">
-        <f>IF(AND(B30="",C30="",D30=""),"",IF(B30="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B30)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D30)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B30)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H30)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J30)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L30" s="6">
-        <f>IF(OR(B30="",K30&lt;&gt;"ок"),"",IF(N(H30)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L30" s="5">
+        <f>IF(OR(B30="",E30=""),"",IF(NOT(ISNUMBER(H30)),"ЗАБЛОКИРОВАН",H30-K30))</f>
+        <v/>
+      </c>
+      <c r="M30" s="5">
+        <f>IF(OR(B30="",E30=""),"",IF(OR(NOT(ISNUMBER(L30)),N(I30)&gt;N(L30)),"ЗАБЛОКИРОВАН",L30-I30))</f>
+        <v/>
+      </c>
+      <c r="N30" s="6">
+        <f>IF(AND(B30="",C30="",D30=""),"",IF(B30="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B30)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D30)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B30)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H30)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L30)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I30)&gt;N(L30),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O30" s="6">
+        <f>IF(OR(B30="",N30&lt;&gt;"ок"),"",IF(N(J30)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14890,19 +15266,31 @@
         <v/>
       </c>
       <c r="I31" s="5">
+        <f>IF(B31="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="5">
+        <f>IF(OR(B31="",E31=""),"",IF(OR(NOT(ISNUMBER(L31)),N(I31)&gt;N(L31)),"ЗАБЛОКИРОВАН",H31-I31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="5">
         <f>IF(OR(B31="",E31=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B31,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E31)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B31,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E31))</f>
         <v/>
       </c>
-      <c r="J31" s="5">
-        <f>IF(OR(B31="",E31=""),"",IF(NOT(ISNUMBER(H31)),"ЗАБЛОКИРОВАН",H31-I31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="6">
-        <f>IF(AND(B31="",C31="",D31=""),"",IF(B31="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B31)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D31)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B31)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H31)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J31)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L31" s="6">
-        <f>IF(OR(B31="",K31&lt;&gt;"ок"),"",IF(N(H31)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L31" s="5">
+        <f>IF(OR(B31="",E31=""),"",IF(NOT(ISNUMBER(H31)),"ЗАБЛОКИРОВАН",H31-K31))</f>
+        <v/>
+      </c>
+      <c r="M31" s="5">
+        <f>IF(OR(B31="",E31=""),"",IF(OR(NOT(ISNUMBER(L31)),N(I31)&gt;N(L31)),"ЗАБЛОКИРОВАН",L31-I31))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6">
+        <f>IF(AND(B31="",C31="",D31=""),"",IF(B31="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B31)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D31)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B31)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H31)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L31)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I31)&gt;N(L31),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O31" s="6">
+        <f>IF(OR(B31="",N31&lt;&gt;"ок"),"",IF(N(J31)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14930,19 +15318,31 @@
         <v/>
       </c>
       <c r="I32" s="5">
+        <f>IF(B32="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="5">
+        <f>IF(OR(B32="",E32=""),"",IF(OR(NOT(ISNUMBER(L32)),N(I32)&gt;N(L32)),"ЗАБЛОКИРОВАН",H32-I32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="5">
         <f>IF(OR(B32="",E32=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B32,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E32)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B32,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E32))</f>
         <v/>
       </c>
-      <c r="J32" s="5">
-        <f>IF(OR(B32="",E32=""),"",IF(NOT(ISNUMBER(H32)),"ЗАБЛОКИРОВАН",H32-I32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="6">
-        <f>IF(AND(B32="",C32="",D32=""),"",IF(B32="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B32)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D32)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B32)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H32)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J32)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L32" s="6">
-        <f>IF(OR(B32="",K32&lt;&gt;"ок"),"",IF(N(H32)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L32" s="5">
+        <f>IF(OR(B32="",E32=""),"",IF(NOT(ISNUMBER(H32)),"ЗАБЛОКИРОВАН",H32-K32))</f>
+        <v/>
+      </c>
+      <c r="M32" s="5">
+        <f>IF(OR(B32="",E32=""),"",IF(OR(NOT(ISNUMBER(L32)),N(I32)&gt;N(L32)),"ЗАБЛОКИРОВАН",L32-I32))</f>
+        <v/>
+      </c>
+      <c r="N32" s="6">
+        <f>IF(AND(B32="",C32="",D32=""),"",IF(B32="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B32)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D32)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B32)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H32)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L32)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I32)&gt;N(L32),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O32" s="6">
+        <f>IF(OR(B32="",N32&lt;&gt;"ок"),"",IF(N(J32)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -14970,19 +15370,31 @@
         <v/>
       </c>
       <c r="I33" s="5">
+        <f>IF(B33="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="5">
+        <f>IF(OR(B33="",E33=""),"",IF(OR(NOT(ISNUMBER(L33)),N(I33)&gt;N(L33)),"ЗАБЛОКИРОВАН",H33-I33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="5">
         <f>IF(OR(B33="",E33=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B33,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E33)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B33,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E33))</f>
         <v/>
       </c>
-      <c r="J33" s="5">
-        <f>IF(OR(B33="",E33=""),"",IF(NOT(ISNUMBER(H33)),"ЗАБЛОКИРОВАН",H33-I33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="6">
-        <f>IF(AND(B33="",C33="",D33=""),"",IF(B33="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B33)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D33)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B33)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H33)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J33)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L33" s="6">
-        <f>IF(OR(B33="",K33&lt;&gt;"ок"),"",IF(N(H33)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L33" s="5">
+        <f>IF(OR(B33="",E33=""),"",IF(NOT(ISNUMBER(H33)),"ЗАБЛОКИРОВАН",H33-K33))</f>
+        <v/>
+      </c>
+      <c r="M33" s="5">
+        <f>IF(OR(B33="",E33=""),"",IF(OR(NOT(ISNUMBER(L33)),N(I33)&gt;N(L33)),"ЗАБЛОКИРОВАН",L33-I33))</f>
+        <v/>
+      </c>
+      <c r="N33" s="6">
+        <f>IF(AND(B33="",C33="",D33=""),"",IF(B33="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B33)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D33)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B33)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H33)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L33)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I33)&gt;N(L33),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O33" s="6">
+        <f>IF(OR(B33="",N33&lt;&gt;"ок"),"",IF(N(J33)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
@@ -15010,26 +15422,38 @@
         <v/>
       </c>
       <c r="I34" s="5">
+        <f>IF(B34="","",SUMIFS(Взаиморасчёты!$H$5:$H$504,Взаиморасчёты!$F$5:$F$504,B34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="5">
+        <f>IF(OR(B34="",E34=""),"",IF(OR(NOT(ISNUMBER(L34)),N(I34)&gt;N(L34)),"ЗАБЛОКИРОВАН",H34-I34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="5">
         <f>IF(OR(B34="",E34=""),"",SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Оплата",Взаиморасчёты!$F$5:$F$504,B34,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E34)+SUMIFS(Взаиморасчёты!$E$5:$E$504,Взаиморасчёты!$C$5:$C$504,"Зачёт аванса по договору",Взаиморасчёты!$F$5:$F$504,B34,Взаиморасчёты!$B$5:$B$504,"&gt;="&amp;E34))</f>
         <v/>
       </c>
-      <c r="J34" s="5">
-        <f>IF(OR(B34="",E34=""),"",IF(NOT(ISNUMBER(H34)),"ЗАБЛОКИРОВАН",H34-I34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="6">
-        <f>IF(AND(B34="",C34="",D34=""),"",IF(B34="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B34)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D34)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B34)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H34)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(J34)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение","ок"))))))))</f>
-        <v/>
-      </c>
-      <c r="L34" s="6">
-        <f>IF(OR(B34="",K34&lt;&gt;"ок"),"",IF(N(H34)&gt;0,"да","нет: долга на первый день просрочки нет"))</f>
+      <c r="L34" s="5">
+        <f>IF(OR(B34="",E34=""),"",IF(NOT(ISNUMBER(H34)),"ЗАБЛОКИРОВАН",H34-K34))</f>
+        <v/>
+      </c>
+      <c r="M34" s="5">
+        <f>IF(OR(B34="",E34=""),"",IF(OR(NOT(ISNUMBER(L34)),N(I34)&gt;N(L34)),"ЗАБЛОКИРОВАН",L34-I34))</f>
+        <v/>
+      </c>
+      <c r="N34" s="6">
+        <f>IF(AND(B34="",C34="",D34=""),"",IF(B34="","БЛОК: нужен идентификатор акта — по нему распределяются оплаты",IF(COUNTIF($B$5:$B$34,B34)&gt;1,"БЛОК: идентификатор акта повторяется — оплату нельзя отнести однозначно",IF(NOT(ISNUMBER(D34)),"БЛОК: нужен последний день срока оплаты по этому акту",IF(COUNTIF(Взаиморасчёты!$F$5:$F$504,B34)=0,"БЛОК: во «Взаиморасчётах» нет ни одной операции по этому акту",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"БЛОК: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или платёж без акта) — исправьте строки с «БЛОК»: до этого долг по акту не посчитан и в файл 08 не переносится",IF(N(H34)&lt;0,"БЛОК: до первого дня просрочки оплачено и зачтено больше, чем начислено по акту — проверьте распределение",IF(N(L34)&lt;0,"БЛОК: оплаты с первого дня просрочки больше долга на первый день просрочки — проверьте распределение",IF(N(I34)&gt;N(L34),"БЛОК: спорная часть по акту (колонка I) больше общего остатка по акту — проверьте суммы удержания, зачёта встречного требования, неустойки и допработ и акт, к которому они отнесены: бесспорная часть не может быть отрицательной","ок")))))))))</f>
+        <v/>
+      </c>
+      <c r="O34" s="6">
+        <f>IF(OR(B34="",N34&lt;&gt;"ок"),"",IF(N(J34)&gt;0,"да","нет: бесспорного долга на первый день просрочки нет"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -15037,6 +15461,1320 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>АКТ СВЕРКИ ВЗАИМНЫХ РАСЧЁТОВ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="63" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Рабочая форма для направления заказчику. Заполняется автоматически из листов «Взаиморасчёты» и «Долг по актам»: впишите только стороны, договор и дату сверки. Показывает общий долг по данным Субподрядчика и отдельной графой — сумму, которую оспаривает Заказчик (удержание, зачёт встречного требования, неустойка, допработы без соглашения). Графу «По данным Заказчика» заполняет Заказчик. Правовое значение подписанного акта сверки и порядок работы со спорной частью — вопрос к специалисту; система их не оценивает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>IF(COUNTA('Долг по актам'!$B$5:$B$34)=0,"НЕ ГОТОВ: на листе «Долг по актам» нет ни одного акта",IF(NOT(ISNUMBER(Взаиморасчёты!$M$10)),"НЕ ГОТОВ: реестр «Взаиморасчёты» заблокирован (например, двойной учёт аванса или операция без акта) — исправьте строки с «БЛОК»",IF(COUNTIF('Долг по актам'!$N$5:$N$34,"БЛОК*")&gt;0,"НЕ ГОТОВ: на листе «Долг по актам» есть строки с «БЛОК» в колонке «Проверка»",IF(NOT(ISNUMBER(Взаиморасчёты!$M$12)),"НЕ ГОТОВ: бесспорная часть заблокирована — см. «Взаиморасчёты», свод",IF(ROUND(SUM(F13:F42)-Взаиморасчёты!$M$10,2)&lt;&gt;0,"НЕ ГОТОВ: сумма по актам не равна общему долгу реестра — проверьте, что все операции отнесены к актам этого листа","ГОТОВ")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Субподрядчик</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>наименование, ИНН</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>наименование, ИНН</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Договор</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>№, дата</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Дата сверки</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>дата</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Суммы — по данным Субподрядчика. Общий долг = начислено и скорректировано − оплачено и зачтено. «В том числе оспаривается Заказчиком» общий долг не уменьшает: это его часть, которую Заказчик не признаёт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Акт (идентификатор)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Документ (КС-2 / акт: №, дата)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Начислено и скорректировано, руб.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Оплачено и зачтено, руб.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Общий долг по данным Субподрядчика, руб.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>в том числе оспаривается Заказчиком, руб.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Бесспорная часть, руб.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>По данным Заказчика, руб.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Расхождение, комментарий Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6">
+        <f>IF('Долг по актам'!B5="","",'Долг по актам'!B5)</f>
+        <v/>
+      </c>
+      <c r="C13" s="6">
+        <f>IF('Долг по актам'!B5="","",'Долг по актам'!C5&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>IF('Долг по актам'!B5="","",N('Долг по актам'!F5))</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>IF('Долг по актам'!B5="","",IF(ISNUMBER('Долг по актам'!G5),'Долг по актам'!G5,0)+N('Долг по актам'!K5))</f>
+        <v/>
+      </c>
+      <c r="F13" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L5),'Долг по актам'!L5,"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="5">
+        <f>IF('Долг по актам'!B5="","",N('Долг по актам'!I5))</f>
+        <v/>
+      </c>
+      <c r="H13" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M5),'Долг по актам'!M5,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6">
+        <f>IF('Долг по актам'!B6="","",'Долг по актам'!B6)</f>
+        <v/>
+      </c>
+      <c r="C14" s="6">
+        <f>IF('Долг по актам'!B6="","",'Долг по актам'!C6&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IF('Долг по актам'!B6="","",N('Долг по актам'!F6))</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IF('Долг по актам'!B6="","",IF(ISNUMBER('Долг по актам'!G6),'Долг по актам'!G6,0)+N('Долг по актам'!K6))</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L6),'Долг по актам'!L6,"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="5">
+        <f>IF('Долг по актам'!B6="","",N('Долг по актам'!I6))</f>
+        <v/>
+      </c>
+      <c r="H14" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M6),'Долг по актам'!M6,"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="6">
+        <f>IF('Долг по актам'!B7="","",'Долг по актам'!B7)</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>IF('Долг по актам'!B7="","",'Долг по актам'!C7&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>IF('Долг по актам'!B7="","",N('Долг по актам'!F7))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>IF('Долг по актам'!B7="","",IF(ISNUMBER('Долг по актам'!G7),'Долг по актам'!G7,0)+N('Долг по актам'!K7))</f>
+        <v/>
+      </c>
+      <c r="F15" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L7),'Долг по актам'!L7,"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="5">
+        <f>IF('Долг по актам'!B7="","",N('Долг по актам'!I7))</f>
+        <v/>
+      </c>
+      <c r="H15" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M7),'Долг по актам'!M7,"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="6">
+        <f>IF('Долг по актам'!B8="","",'Долг по актам'!B8)</f>
+        <v/>
+      </c>
+      <c r="C16" s="6">
+        <f>IF('Долг по актам'!B8="","",'Долг по актам'!C8&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>IF('Долг по актам'!B8="","",N('Долг по актам'!F8))</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>IF('Долг по актам'!B8="","",IF(ISNUMBER('Долг по актам'!G8),'Долг по актам'!G8,0)+N('Долг по актам'!K8))</f>
+        <v/>
+      </c>
+      <c r="F16" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L8),'Долг по актам'!L8,"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="5">
+        <f>IF('Долг по актам'!B8="","",N('Долг по актам'!I8))</f>
+        <v/>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M8),'Долг по актам'!M8,"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="6">
+        <f>IF('Долг по актам'!B9="","",'Долг по актам'!B9)</f>
+        <v/>
+      </c>
+      <c r="C17" s="6">
+        <f>IF('Долг по актам'!B9="","",'Долг по актам'!C9&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>IF('Долг по актам'!B9="","",N('Долг по актам'!F9))</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>IF('Долг по актам'!B9="","",IF(ISNUMBER('Долг по актам'!G9),'Долг по актам'!G9,0)+N('Долг по актам'!K9))</f>
+        <v/>
+      </c>
+      <c r="F17" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L9),'Долг по актам'!L9,"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="5">
+        <f>IF('Долг по актам'!B9="","",N('Долг по актам'!I9))</f>
+        <v/>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M9),'Долг по актам'!M9,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="6">
+        <f>IF('Долг по актам'!B10="","",'Долг по актам'!B10)</f>
+        <v/>
+      </c>
+      <c r="C18" s="6">
+        <f>IF('Долг по актам'!B10="","",'Долг по актам'!C10&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>IF('Долг по актам'!B10="","",N('Долг по актам'!F10))</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>IF('Долг по актам'!B10="","",IF(ISNUMBER('Долг по актам'!G10),'Долг по актам'!G10,0)+N('Долг по актам'!K10))</f>
+        <v/>
+      </c>
+      <c r="F18" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L10),'Долг по актам'!L10,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="5">
+        <f>IF('Долг по актам'!B10="","",N('Долг по актам'!I10))</f>
+        <v/>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M10),'Долг по актам'!M10,"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6">
+        <f>IF('Долг по актам'!B11="","",'Долг по актам'!B11)</f>
+        <v/>
+      </c>
+      <c r="C19" s="6">
+        <f>IF('Долг по актам'!B11="","",'Долг по актам'!C11&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>IF('Долг по актам'!B11="","",N('Долг по актам'!F11))</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>IF('Долг по актам'!B11="","",IF(ISNUMBER('Долг по актам'!G11),'Долг по актам'!G11,0)+N('Долг по актам'!K11))</f>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L11),'Долг по актам'!L11,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="5">
+        <f>IF('Долг по актам'!B11="","",N('Долг по актам'!I11))</f>
+        <v/>
+      </c>
+      <c r="H19" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M11),'Долг по актам'!M11,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="6">
+        <f>IF('Долг по актам'!B12="","",'Долг по актам'!B12)</f>
+        <v/>
+      </c>
+      <c r="C20" s="6">
+        <f>IF('Долг по актам'!B12="","",'Долг по актам'!C12&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>IF('Долг по актам'!B12="","",N('Долг по актам'!F12))</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>IF('Долг по актам'!B12="","",IF(ISNUMBER('Долг по актам'!G12),'Долг по актам'!G12,0)+N('Долг по актам'!K12))</f>
+        <v/>
+      </c>
+      <c r="F20" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L12),'Долг по актам'!L12,"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="5">
+        <f>IF('Долг по актам'!B12="","",N('Долг по актам'!I12))</f>
+        <v/>
+      </c>
+      <c r="H20" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M12),'Долг по актам'!M12,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="6">
+        <f>IF('Долг по актам'!B13="","",'Долг по актам'!B13)</f>
+        <v/>
+      </c>
+      <c r="C21" s="6">
+        <f>IF('Долг по актам'!B13="","",'Долг по актам'!C13&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>IF('Долг по актам'!B13="","",N('Долг по актам'!F13))</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>IF('Долг по актам'!B13="","",IF(ISNUMBER('Долг по актам'!G13),'Долг по актам'!G13,0)+N('Долг по актам'!K13))</f>
+        <v/>
+      </c>
+      <c r="F21" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L13),'Долг по актам'!L13,"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="5">
+        <f>IF('Долг по актам'!B13="","",N('Долг по актам'!I13))</f>
+        <v/>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M13),'Долг по актам'!M13,"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="6">
+        <f>IF('Долг по актам'!B14="","",'Долг по актам'!B14)</f>
+        <v/>
+      </c>
+      <c r="C22" s="6">
+        <f>IF('Долг по актам'!B14="","",'Долг по актам'!C14&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>IF('Долг по актам'!B14="","",N('Долг по актам'!F14))</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>IF('Долг по актам'!B14="","",IF(ISNUMBER('Долг по актам'!G14),'Долг по актам'!G14,0)+N('Долг по актам'!K14))</f>
+        <v/>
+      </c>
+      <c r="F22" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L14),'Долг по актам'!L14,"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="5">
+        <f>IF('Долг по актам'!B14="","",N('Долг по актам'!I14))</f>
+        <v/>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M14),'Долг по актам'!M14,"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="6">
+        <f>IF('Долг по актам'!B15="","",'Долг по актам'!B15)</f>
+        <v/>
+      </c>
+      <c r="C23" s="6">
+        <f>IF('Долг по актам'!B15="","",'Долг по актам'!C15&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>IF('Долг по актам'!B15="","",N('Долг по актам'!F15))</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>IF('Долг по актам'!B15="","",IF(ISNUMBER('Долг по актам'!G15),'Долг по актам'!G15,0)+N('Долг по актам'!K15))</f>
+        <v/>
+      </c>
+      <c r="F23" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L15),'Долг по актам'!L15,"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="5">
+        <f>IF('Долг по актам'!B15="","",N('Долг по актам'!I15))</f>
+        <v/>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M15),'Долг по актам'!M15,"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="6">
+        <f>IF('Долг по актам'!B16="","",'Долг по актам'!B16)</f>
+        <v/>
+      </c>
+      <c r="C24" s="6">
+        <f>IF('Долг по актам'!B16="","",'Долг по актам'!C16&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>IF('Долг по актам'!B16="","",N('Долг по актам'!F16))</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>IF('Долг по актам'!B16="","",IF(ISNUMBER('Долг по актам'!G16),'Долг по актам'!G16,0)+N('Долг по актам'!K16))</f>
+        <v/>
+      </c>
+      <c r="F24" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L16),'Долг по актам'!L16,"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="5">
+        <f>IF('Долг по актам'!B16="","",N('Долг по актам'!I16))</f>
+        <v/>
+      </c>
+      <c r="H24" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M16),'Долг по актам'!M16,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="6">
+        <f>IF('Долг по актам'!B17="","",'Долг по актам'!B17)</f>
+        <v/>
+      </c>
+      <c r="C25" s="6">
+        <f>IF('Долг по актам'!B17="","",'Долг по актам'!C17&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>IF('Долг по актам'!B17="","",N('Долг по актам'!F17))</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>IF('Долг по актам'!B17="","",IF(ISNUMBER('Долг по актам'!G17),'Долг по актам'!G17,0)+N('Долг по актам'!K17))</f>
+        <v/>
+      </c>
+      <c r="F25" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L17),'Долг по актам'!L17,"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="5">
+        <f>IF('Долг по актам'!B17="","",N('Долг по актам'!I17))</f>
+        <v/>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M17),'Долг по актам'!M17,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="6">
+        <f>IF('Долг по актам'!B18="","",'Долг по актам'!B18)</f>
+        <v/>
+      </c>
+      <c r="C26" s="6">
+        <f>IF('Долг по актам'!B18="","",'Долг по актам'!C18&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>IF('Долг по актам'!B18="","",N('Долг по актам'!F18))</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>IF('Долг по актам'!B18="","",IF(ISNUMBER('Долг по актам'!G18),'Долг по актам'!G18,0)+N('Долг по актам'!K18))</f>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L18),'Долг по актам'!L18,"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="5">
+        <f>IF('Долг по актам'!B18="","",N('Долг по актам'!I18))</f>
+        <v/>
+      </c>
+      <c r="H26" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M18),'Долг по актам'!M18,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="6">
+        <f>IF('Долг по актам'!B19="","",'Долг по актам'!B19)</f>
+        <v/>
+      </c>
+      <c r="C27" s="6">
+        <f>IF('Долг по актам'!B19="","",'Долг по актам'!C19&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>IF('Долг по актам'!B19="","",N('Долг по актам'!F19))</f>
+        <v/>
+      </c>
+      <c r="E27" s="5">
+        <f>IF('Долг по актам'!B19="","",IF(ISNUMBER('Долг по актам'!G19),'Долг по актам'!G19,0)+N('Долг по актам'!K19))</f>
+        <v/>
+      </c>
+      <c r="F27" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L19),'Долг по актам'!L19,"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="5">
+        <f>IF('Долг по актам'!B19="","",N('Долг по актам'!I19))</f>
+        <v/>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M19),'Долг по актам'!M19,"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="6">
+        <f>IF('Долг по актам'!B20="","",'Долг по актам'!B20)</f>
+        <v/>
+      </c>
+      <c r="C28" s="6">
+        <f>IF('Долг по актам'!B20="","",'Долг по актам'!C20&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>IF('Долг по актам'!B20="","",N('Долг по актам'!F20))</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>IF('Долг по актам'!B20="","",IF(ISNUMBER('Долг по актам'!G20),'Долг по актам'!G20,0)+N('Долг по актам'!K20))</f>
+        <v/>
+      </c>
+      <c r="F28" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L20),'Долг по актам'!L20,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="5">
+        <f>IF('Долг по актам'!B20="","",N('Долг по актам'!I20))</f>
+        <v/>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M20),'Долг по актам'!M20,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="6">
+        <f>IF('Долг по актам'!B21="","",'Долг по актам'!B21)</f>
+        <v/>
+      </c>
+      <c r="C29" s="6">
+        <f>IF('Долг по актам'!B21="","",'Долг по актам'!C21&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5">
+        <f>IF('Долг по актам'!B21="","",N('Долг по актам'!F21))</f>
+        <v/>
+      </c>
+      <c r="E29" s="5">
+        <f>IF('Долг по актам'!B21="","",IF(ISNUMBER('Долг по актам'!G21),'Долг по актам'!G21,0)+N('Долг по актам'!K21))</f>
+        <v/>
+      </c>
+      <c r="F29" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L21),'Долг по актам'!L21,"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="5">
+        <f>IF('Долг по актам'!B21="","",N('Долг по актам'!I21))</f>
+        <v/>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M21),'Долг по актам'!M21,"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="6">
+        <f>IF('Долг по актам'!B22="","",'Долг по актам'!B22)</f>
+        <v/>
+      </c>
+      <c r="C30" s="6">
+        <f>IF('Долг по актам'!B22="","",'Долг по актам'!C22&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="5">
+        <f>IF('Долг по актам'!B22="","",N('Долг по актам'!F22))</f>
+        <v/>
+      </c>
+      <c r="E30" s="5">
+        <f>IF('Долг по актам'!B22="","",IF(ISNUMBER('Долг по актам'!G22),'Долг по актам'!G22,0)+N('Долг по актам'!K22))</f>
+        <v/>
+      </c>
+      <c r="F30" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L22),'Долг по актам'!L22,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="5">
+        <f>IF('Долг по актам'!B22="","",N('Долг по актам'!I22))</f>
+        <v/>
+      </c>
+      <c r="H30" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M22),'Долг по актам'!M22,"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="6">
+        <f>IF('Долг по актам'!B23="","",'Долг по актам'!B23)</f>
+        <v/>
+      </c>
+      <c r="C31" s="6">
+        <f>IF('Долг по актам'!B23="","",'Долг по актам'!C23&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5">
+        <f>IF('Долг по актам'!B23="","",N('Долг по актам'!F23))</f>
+        <v/>
+      </c>
+      <c r="E31" s="5">
+        <f>IF('Долг по актам'!B23="","",IF(ISNUMBER('Долг по актам'!G23),'Долг по актам'!G23,0)+N('Долг по актам'!K23))</f>
+        <v/>
+      </c>
+      <c r="F31" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L23),'Долг по актам'!L23,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="5">
+        <f>IF('Долг по актам'!B23="","",N('Долг по актам'!I23))</f>
+        <v/>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M23),'Долг по актам'!M23,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="6">
+        <f>IF('Долг по актам'!B24="","",'Долг по актам'!B24)</f>
+        <v/>
+      </c>
+      <c r="C32" s="6">
+        <f>IF('Долг по актам'!B24="","",'Долг по актам'!C24&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="5">
+        <f>IF('Долг по актам'!B24="","",N('Долг по актам'!F24))</f>
+        <v/>
+      </c>
+      <c r="E32" s="5">
+        <f>IF('Долг по актам'!B24="","",IF(ISNUMBER('Долг по актам'!G24),'Долг по актам'!G24,0)+N('Долг по актам'!K24))</f>
+        <v/>
+      </c>
+      <c r="F32" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L24),'Долг по актам'!L24,"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="5">
+        <f>IF('Долг по актам'!B24="","",N('Долг по актам'!I24))</f>
+        <v/>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M24),'Долг по актам'!M24,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="6">
+        <f>IF('Долг по актам'!B25="","",'Долг по актам'!B25)</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>IF('Долг по актам'!B25="","",'Долг по актам'!C25&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5">
+        <f>IF('Долг по актам'!B25="","",N('Долг по актам'!F25))</f>
+        <v/>
+      </c>
+      <c r="E33" s="5">
+        <f>IF('Долг по актам'!B25="","",IF(ISNUMBER('Долг по актам'!G25),'Долг по актам'!G25,0)+N('Долг по актам'!K25))</f>
+        <v/>
+      </c>
+      <c r="F33" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L25),'Долг по актам'!L25,"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="5">
+        <f>IF('Долг по актам'!B25="","",N('Долг по актам'!I25))</f>
+        <v/>
+      </c>
+      <c r="H33" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M25),'Долг по актам'!M25,"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="6">
+        <f>IF('Долг по актам'!B26="","",'Долг по актам'!B26)</f>
+        <v/>
+      </c>
+      <c r="C34" s="6">
+        <f>IF('Долг по актам'!B26="","",'Долг по актам'!C26&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5">
+        <f>IF('Долг по актам'!B26="","",N('Долг по актам'!F26))</f>
+        <v/>
+      </c>
+      <c r="E34" s="5">
+        <f>IF('Долг по актам'!B26="","",IF(ISNUMBER('Долг по актам'!G26),'Долг по актам'!G26,0)+N('Долг по актам'!K26))</f>
+        <v/>
+      </c>
+      <c r="F34" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L26),'Долг по актам'!L26,"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="5">
+        <f>IF('Долг по актам'!B26="","",N('Долг по актам'!I26))</f>
+        <v/>
+      </c>
+      <c r="H34" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M26),'Долг по актам'!M26,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="6">
+        <f>IF('Долг по актам'!B27="","",'Долг по актам'!B27)</f>
+        <v/>
+      </c>
+      <c r="C35" s="6">
+        <f>IF('Долг по актам'!B27="","",'Долг по актам'!C27&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="5">
+        <f>IF('Долг по актам'!B27="","",N('Долг по актам'!F27))</f>
+        <v/>
+      </c>
+      <c r="E35" s="5">
+        <f>IF('Долг по актам'!B27="","",IF(ISNUMBER('Долг по актам'!G27),'Долг по актам'!G27,0)+N('Долг по актам'!K27))</f>
+        <v/>
+      </c>
+      <c r="F35" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L27),'Долг по актам'!L27,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="5">
+        <f>IF('Долг по актам'!B27="","",N('Долг по актам'!I27))</f>
+        <v/>
+      </c>
+      <c r="H35" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M27),'Долг по актам'!M27,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="6">
+        <f>IF('Долг по актам'!B28="","",'Долг по актам'!B28)</f>
+        <v/>
+      </c>
+      <c r="C36" s="6">
+        <f>IF('Долг по актам'!B28="","",'Долг по актам'!C28&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="5">
+        <f>IF('Долг по актам'!B28="","",N('Долг по актам'!F28))</f>
+        <v/>
+      </c>
+      <c r="E36" s="5">
+        <f>IF('Долг по актам'!B28="","",IF(ISNUMBER('Долг по актам'!G28),'Долг по актам'!G28,0)+N('Долг по актам'!K28))</f>
+        <v/>
+      </c>
+      <c r="F36" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L28),'Долг по актам'!L28,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="5">
+        <f>IF('Долг по актам'!B28="","",N('Долг по актам'!I28))</f>
+        <v/>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M28),'Долг по актам'!M28,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="6">
+        <f>IF('Долг по актам'!B29="","",'Долг по актам'!B29)</f>
+        <v/>
+      </c>
+      <c r="C37" s="6">
+        <f>IF('Долг по актам'!B29="","",'Долг по актам'!C29&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="5">
+        <f>IF('Долг по актам'!B29="","",N('Долг по актам'!F29))</f>
+        <v/>
+      </c>
+      <c r="E37" s="5">
+        <f>IF('Долг по актам'!B29="","",IF(ISNUMBER('Долг по актам'!G29),'Долг по актам'!G29,0)+N('Долг по актам'!K29))</f>
+        <v/>
+      </c>
+      <c r="F37" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L29),'Долг по актам'!L29,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="5">
+        <f>IF('Долг по актам'!B29="","",N('Долг по актам'!I29))</f>
+        <v/>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M29),'Долг по актам'!M29,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="6">
+        <f>IF('Долг по актам'!B30="","",'Долг по актам'!B30)</f>
+        <v/>
+      </c>
+      <c r="C38" s="6">
+        <f>IF('Долг по актам'!B30="","",'Долг по актам'!C30&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="5">
+        <f>IF('Долг по актам'!B30="","",N('Долг по актам'!F30))</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>IF('Долг по актам'!B30="","",IF(ISNUMBER('Долг по актам'!G30),'Долг по актам'!G30,0)+N('Долг по актам'!K30))</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L30),'Долг по актам'!L30,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>IF('Долг по актам'!B30="","",N('Долг по актам'!I30))</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M30),'Долг по актам'!M30,"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="6">
+        <f>IF('Долг по актам'!B31="","",'Долг по актам'!B31)</f>
+        <v/>
+      </c>
+      <c r="C39" s="6">
+        <f>IF('Долг по актам'!B31="","",'Долг по актам'!C31&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="5">
+        <f>IF('Долг по актам'!B31="","",N('Долг по актам'!F31))</f>
+        <v/>
+      </c>
+      <c r="E39" s="5">
+        <f>IF('Долг по актам'!B31="","",IF(ISNUMBER('Долг по актам'!G31),'Долг по актам'!G31,0)+N('Долг по актам'!K31))</f>
+        <v/>
+      </c>
+      <c r="F39" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L31),'Долг по актам'!L31,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>IF('Долг по актам'!B31="","",N('Долг по актам'!I31))</f>
+        <v/>
+      </c>
+      <c r="H39" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M31),'Долг по актам'!M31,"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="6">
+        <f>IF('Долг по актам'!B32="","",'Долг по актам'!B32)</f>
+        <v/>
+      </c>
+      <c r="C40" s="6">
+        <f>IF('Долг по актам'!B32="","",'Долг по актам'!C32&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="5">
+        <f>IF('Долг по актам'!B32="","",N('Долг по актам'!F32))</f>
+        <v/>
+      </c>
+      <c r="E40" s="5">
+        <f>IF('Долг по актам'!B32="","",IF(ISNUMBER('Долг по актам'!G32),'Долг по актам'!G32,0)+N('Долг по актам'!K32))</f>
+        <v/>
+      </c>
+      <c r="F40" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L32),'Долг по актам'!L32,"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="5">
+        <f>IF('Долг по актам'!B32="","",N('Долг по актам'!I32))</f>
+        <v/>
+      </c>
+      <c r="H40" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M32),'Долг по актам'!M32,"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="6">
+        <f>IF('Долг по актам'!B33="","",'Долг по актам'!B33)</f>
+        <v/>
+      </c>
+      <c r="C41" s="6">
+        <f>IF('Долг по актам'!B33="","",'Долг по актам'!C33&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="5">
+        <f>IF('Долг по актам'!B33="","",N('Долг по актам'!F33))</f>
+        <v/>
+      </c>
+      <c r="E41" s="5">
+        <f>IF('Долг по актам'!B33="","",IF(ISNUMBER('Долг по актам'!G33),'Долг по актам'!G33,0)+N('Долг по актам'!K33))</f>
+        <v/>
+      </c>
+      <c r="F41" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L33),'Долг по актам'!L33,"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>IF('Долг по актам'!B33="","",N('Долг по актам'!I33))</f>
+        <v/>
+      </c>
+      <c r="H41" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M33),'Долг по актам'!M33,"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="6">
+        <f>IF('Долг по актам'!B34="","",'Долг по актам'!B34)</f>
+        <v/>
+      </c>
+      <c r="C42" s="6">
+        <f>IF('Долг по актам'!B34="","",'Долг по актам'!C34&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>IF('Долг по актам'!B34="","",N('Долг по актам'!F34))</f>
+        <v/>
+      </c>
+      <c r="E42" s="5">
+        <f>IF('Долг по актам'!B34="","",IF(ISNUMBER('Долг по актам'!G34),'Долг по актам'!G34,0)+N('Долг по актам'!K34))</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!L34),'Долг по актам'!L34,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>IF('Долг по актам'!B34="","",N('Долг по актам'!I34))</f>
+        <v/>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(ISNUMBER('Долг по актам'!M34),'Долг по актам'!M34,"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="15">
+        <f>IF($C$3="ГОТОВ",SUM(F13:F42),"НЕ ГОТОВ")</f>
+        <v/>
+      </c>
+      <c r="G43" s="15">
+        <f>IF($C$3="ГОТОВ",SUM(G13:G42),"НЕ ГОТОВ")</f>
+        <v/>
+      </c>
+      <c r="H43" s="15">
+        <f>IF($C$3="ГОТОВ",SUM(H13:H42),"НЕ ГОТОВ")</f>
+        <v/>
+      </c>
+      <c r="I43" s="5">
+        <f>IF(COUNT(I13:I42)=0,"",SUM(I13:I42))</f>
+        <v/>
+      </c>
+      <c r="J43" s="6" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="10">
+        <f>IF($C$3&lt;&gt;"ГОТОВ",$C$3,"По данным Субподрядчика задолженность Заказчика составляет "&amp;FIXED(F43,2)&amp;" руб., в том числе оспаривается Заказчиком "&amp;FIXED(G43,2)&amp;" руб.; бесспорная часть — "&amp;FIXED(H43,2)&amp;" руб.")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>По данным Заказчика задолженность составляет: ____________________ руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>От Субподрядчика</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>От Заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Должность, ФИО: ______________________</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Должность, ФИО: ______________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Подпись: ______________   М. П.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Подпись: ______________   М. П.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Дата: ____________</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Дата: ____________</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20555,7 +22293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
+++ b/tools/candidates/s1-oplata-za-raboty/04-uchet-raschetov-i-otpravok.xlsx
@@ -508,6 +508,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="62" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="46" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
@@ -519,10 +520,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Одна строка — одна операция. Начисления вводите положительными суммами, оплаты и зачёты — тоже положительными: знак ставит тип операции. Каждая операция, влияющая на долг, относится к конкретному акту: идентификатор акта в колонке F должен совпадать со строкой листа «Долг по актам». Система не распределяет платежи между актами сама — очередность зачёта определяется назначением платежа и договором, и правовой вывод за вас никто не делает. Спорные операции — «Удержание», «Зачёт встречного требования», «Неустойка заявлена», «Допработы без соглашения (спорно)» — общий долг не уменьшают: их сумма показывается отдельно как спорная часть, у каждой обязателен акт. В расчёт процентов и претензию идёт только бесспорная часть. Строк 500; записи ниже таблицы блокируют итог, а не отбрасываются.</t>
+          <t>Одна строка — одна операция. Начисления вводите положительными суммами, оплаты и зачёты — тоже положительными: знак ставит тип операции. Каждая операция, влияющая на долг, относится к конкретному акту: идентификатор акта в колонке F должен совпадать со строкой листа «Долг по актам». Система не распределяет платежи между актами сама — очередность зачёта определяется назначением платежа и договором, и правовой вывод за вас никто не делает. Спорные операции — «Удержание», «Зачёт встречного требования», «Неустойка заявлена», «Допработы без соглашения (спорно)» — общий долг не уменьшают: их сумма показывается отдельно как спорная часть, у каждой обязателен акт. В расчёт процентов и претензию идёт только бесспорная часть. Строк 500; записи ниже таблицы блокируют итог, а не отбрасываются. Полученный аванс вносится один раз — «Зачётом аванса по договору»; сам авансовый платёж «Оплатой» не вносится. Если сумма «Оплаты» равна зачёту аванса, строка просит сверку: подтвердите в колонке K, что это отдельный платёж.</t>
         </is>
       </c>
     </row>
@@ -575,6 +576,11 @@
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Общий долг нарастающим итогом</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Сверка с авансом (только если строка просит)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -605,13 +611,14 @@
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>IF(AND(B5="",C5="",D5="",E5="",F5=""),"",IF(OR(B5="",C5="",E5=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E5)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H5&lt;&gt;0,F5=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G5&lt;&gt;0,F5=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F5&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F5)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C5)*($E$5:$E$504=E5)*(($D$5:$D$504=D5)*(D5&lt;&gt;"")+($B$5:$B$504=B5)*(B5&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B5="",C5="",D5="",E5="",F5=""),"",IF(OR(B5="",C5="",E5=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E5)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H5&lt;&gt;0,F5=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G5&lt;&gt;0,F5=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F5&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F5)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C5)*($E$5:$E$504=E5)*(($D$5:$D$504=D5)*(D5&lt;&gt;"")+($B$5:$B$504=B5)*(B5&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C5="Оплата",K5&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E5)&gt;0,ROUND(E5-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J5" s="5">
         <f>IF(AND(B5="",C5="",E5=""),"",SUM($G$5:G5))</f>
         <v/>
       </c>
+      <c r="K5" s="8" t="n"/>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Оплачено</t>
@@ -640,13 +647,14 @@
         <v/>
       </c>
       <c r="I6" s="6">
-        <f>IF(AND(B6="",C6="",D6="",E6="",F6=""),"",IF(OR(B6="",C6="",E6=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E6)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H6&lt;&gt;0,F6=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G6&lt;&gt;0,F6=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F6&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F6)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C6)*($E$5:$E$504=E6)*(($D$5:$D$504=D6)*(D6&lt;&gt;"")+($B$5:$B$504=B6)*(B6&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B6="",C6="",D6="",E6="",F6=""),"",IF(OR(B6="",C6="",E6=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E6)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H6&lt;&gt;0,F6=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G6&lt;&gt;0,F6=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F6&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F6)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C6)*($E$5:$E$504=E6)*(($D$5:$D$504=D6)*(D6&lt;&gt;"")+($B$5:$B$504=B6)*(B6&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C6="Оплата",K6&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E6)&gt;0,ROUND(E6-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J6" s="5">
         <f>IF(AND(B6="",C6="",E6=""),"",SUM($G$5:G6))</f>
         <v/>
       </c>
+      <c r="K6" s="8" t="n"/>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Зачтён аванс</t>
@@ -675,13 +683,14 @@
         <v/>
       </c>
       <c r="I7" s="6">
-        <f>IF(AND(B7="",C7="",D7="",E7="",F7=""),"",IF(OR(B7="",C7="",E7=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E7)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H7&lt;&gt;0,F7=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G7&lt;&gt;0,F7=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F7&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F7)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C7)*($E$5:$E$504=E7)*(($D$5:$D$504=D7)*(D7&lt;&gt;"")+($B$5:$B$504=B7)*(B7&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B7="",C7="",D7="",E7="",F7=""),"",IF(OR(B7="",C7="",E7=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E7)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H7&lt;&gt;0,F7=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G7&lt;&gt;0,F7=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F7&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F7)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C7)*($E$5:$E$504=E7)*(($D$5:$D$504=D7)*(D7&lt;&gt;"")+($B$5:$B$504=B7)*(B7&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C7="Оплата",K7&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E7)&gt;0,ROUND(E7-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J7" s="5">
         <f>IF(AND(B7="",C7="",E7=""),"",SUM($G$5:G7))</f>
         <v/>
       </c>
+      <c r="K7" s="8" t="n"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Корректировки</t>
@@ -710,13 +719,14 @@
         <v/>
       </c>
       <c r="I8" s="6">
-        <f>IF(AND(B8="",C8="",D8="",E8="",F8=""),"",IF(OR(B8="",C8="",E8=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E8)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H8&lt;&gt;0,F8=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G8&lt;&gt;0,F8=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F8&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F8)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C8)*($E$5:$E$504=E8)*(($D$5:$D$504=D8)*(D8&lt;&gt;"")+($B$5:$B$504=B8)*(B8&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B8="",C8="",D8="",E8="",F8=""),"",IF(OR(B8="",C8="",E8=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E8)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H8&lt;&gt;0,F8=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G8&lt;&gt;0,F8=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F8&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F8)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C8)*($E$5:$E$504=E8)*(($D$5:$D$504=D8)*(D8&lt;&gt;"")+($B$5:$B$504=B8)*(B8&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C8="Оплата",K8&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E8)&gt;0,ROUND(E8-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J8" s="5">
         <f>IF(AND(B8="",C8="",E8=""),"",SUM($G$5:G8))</f>
         <v/>
       </c>
+      <c r="K8" s="8" t="n"/>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Спорные операции (удержание, зачёт встречного требования, неустойка, допработы без соглашения)</t>
@@ -745,13 +755,14 @@
         <v/>
       </c>
       <c r="I9" s="6">
-        <f>IF(AND(B9="",C9="",D9="",E9="",F9=""),"",IF(OR(B9="",C9="",E9=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E9)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H9&lt;&gt;0,F9=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G9&lt;&gt;0,F9=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F9&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F9)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C9)*($E$5:$E$504=E9)*(($D$5:$D$504=D9)*(D9&lt;&gt;"")+($B$5:$B$504=B9)*(B9&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B9="",C9="",D9="",E9="",F9=""),"",IF(OR(B9="",C9="",E9=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E9)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H9&lt;&gt;0,F9=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G9&lt;&gt;0,F9=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F9&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F9)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C9)*($E$5:$E$504=E9)*(($D$5:$D$504=D9)*(D9&lt;&gt;"")+($B$5:$B$504=B9)*(B9&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C9="Оплата",K9&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E9)&gt;0,ROUND(E9-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J9" s="5">
         <f>IF(AND(B9="",C9="",E9=""),"",SUM($G$5:G9))</f>
         <v/>
       </c>
+      <c r="K9" s="8" t="n"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Операций ниже таблицы (не учтены)</t>
@@ -780,13 +791,14 @@
         <v/>
       </c>
       <c r="I10" s="6">
-        <f>IF(AND(B10="",C10="",D10="",E10="",F10=""),"",IF(OR(B10="",C10="",E10=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E10)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H10&lt;&gt;0,F10=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G10&lt;&gt;0,F10=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F10&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F10)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C10)*($E$5:$E$504=E10)*(($D$5:$D$504=D10)*(D10&lt;&gt;"")+($B$5:$B$504=B10)*(B10&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B10="",C10="",D10="",E10="",F10=""),"",IF(OR(B10="",C10="",E10=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E10)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H10&lt;&gt;0,F10=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G10&lt;&gt;0,F10=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F10&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F10)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C10)*($E$5:$E$504=E10)*(($D$5:$D$504=D10)*(D10&lt;&gt;"")+($B$5:$B$504=B10)*(B10&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C10="Оплата",K10&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E10)&gt;0,ROUND(E10-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J10" s="5">
         <f>IF(AND(B10="",C10="",E10=""),"",SUM($G$5:G10))</f>
         <v/>
       </c>
+      <c r="K10" s="8" t="n"/>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>ОБЩИЙ ДОЛГ ПО ДАННЫМ СУБПОДРЯДЧИКА, руб.</t>
@@ -815,13 +827,14 @@
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>IF(AND(B11="",C11="",D11="",E11="",F11=""),"",IF(OR(B11="",C11="",E11=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E11)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H11&lt;&gt;0,F11=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G11&lt;&gt;0,F11=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F11&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F11)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C11)*($E$5:$E$504=E11)*(($D$5:$D$504=D11)*(D11&lt;&gt;"")+($B$5:$B$504=B11)*(B11&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B11="",C11="",D11="",E11="",F11=""),"",IF(OR(B11="",C11="",E11=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E11)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H11&lt;&gt;0,F11=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G11&lt;&gt;0,F11=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F11&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F11)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C11)*($E$5:$E$504=E11)*(($D$5:$D$504=D11)*(D11&lt;&gt;"")+($B$5:$B$504=B11)*(B11&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C11="Оплата",K11&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E11)&gt;0,ROUND(E11-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J11" s="5">
         <f>IF(AND(B11="",C11="",E11=""),"",SUM($G$5:G11))</f>
         <v/>
       </c>
+      <c r="K11" s="8" t="n"/>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>СПОРНАЯ ЧАСТЬ, руб. (в том числе оспаривается Заказчиком)</t>
@@ -850,13 +863,14 @@
         <v/>
       </c>
       <c r="I12" s="6">
-        <f>IF(AND(B12="",C12="",D12="",E12="",F12=""),"",IF(OR(B12="",C12="",E12=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E12)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H12&lt;&gt;0,F12=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G12&lt;&gt;0,F12=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F12&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F12)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C12)*($E$5:$E$504=E12)*(($D$5:$D$504=D12)*(D12&lt;&gt;"")+($B$5:$B$504=B12)*(B12&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B12="",C12="",D12="",E12="",F12=""),"",IF(OR(B12="",C12="",E12=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E12)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H12&lt;&gt;0,F12=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G12&lt;&gt;0,F12=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F12&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F12)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C12)*($E$5:$E$504=E12)*(($D$5:$D$504=D12)*(D12&lt;&gt;"")+($B$5:$B$504=B12)*(B12&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C12="Оплата",K12&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E12)&gt;0,ROUND(E12-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J12" s="5">
         <f>IF(AND(B12="",C12="",E12=""),"",SUM($G$5:G12))</f>
         <v/>
       </c>
+      <c r="K12" s="8" t="n"/>
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>БЕССПОРНАЯ ЧАСТЬ, руб. (общий долг − спорная часть; по актам — лист «Долг по актам»)</t>
@@ -885,13 +899,14 @@
         <v/>
       </c>
       <c r="I13" s="6">
-        <f>IF(AND(B13="",C13="",D13="",E13="",F13=""),"",IF(OR(B13="",C13="",E13=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E13)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H13&lt;&gt;0,F13=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G13&lt;&gt;0,F13=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F13&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F13)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C13)*($E$5:$E$504=E13)*(($D$5:$D$504=D13)*(D13&lt;&gt;"")+($B$5:$B$504=B13)*(B13&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B13="",C13="",D13="",E13="",F13=""),"",IF(OR(B13="",C13="",E13=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E13)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H13&lt;&gt;0,F13=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G13&lt;&gt;0,F13=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F13&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F13)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C13)*($E$5:$E$504=E13)*(($D$5:$D$504=D13)*(D13&lt;&gt;"")+($B$5:$B$504=B13)*(B13&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C13="Оплата",K13&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E13)&gt;0,ROUND(E13-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J13" s="5">
         <f>IF(AND(B13="",C13="",E13=""),"",SUM($G$5:G13))</f>
         <v/>
       </c>
+      <c r="K13" s="8" t="n"/>
       <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Граница</t>
@@ -920,13 +935,14 @@
         <v/>
       </c>
       <c r="I14" s="6">
-        <f>IF(AND(B14="",C14="",D14="",E14="",F14=""),"",IF(OR(B14="",C14="",E14=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E14)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H14&lt;&gt;0,F14=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G14&lt;&gt;0,F14=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F14&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F14)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C14)*($E$5:$E$504=E14)*(($D$5:$D$504=D14)*(D14&lt;&gt;"")+($B$5:$B$504=B14)*(B14&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B14="",C14="",D14="",E14="",F14=""),"",IF(OR(B14="",C14="",E14=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E14)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H14&lt;&gt;0,F14=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G14&lt;&gt;0,F14=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F14&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F14)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C14)*($E$5:$E$504=E14)*(($D$5:$D$504=D14)*(D14&lt;&gt;"")+($B$5:$B$504=B14)*(B14&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C14="Оплата",K14&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E14)&gt;0,ROUND(E14-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J14" s="5">
         <f>IF(AND(B14="",C14="",E14=""),"",SUM($G$5:G14))</f>
         <v/>
       </c>
+      <c r="K14" s="8" t="n"/>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Операций без типа или суммы</t>
@@ -955,13 +971,14 @@
         <v/>
       </c>
       <c r="I15" s="6">
-        <f>IF(AND(B15="",C15="",D15="",E15="",F15=""),"",IF(OR(B15="",C15="",E15=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E15)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H15&lt;&gt;0,F15=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G15&lt;&gt;0,F15=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F15&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F15)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C15)*($E$5:$E$504=E15)*(($D$5:$D$504=D15)*(D15&lt;&gt;"")+($B$5:$B$504=B15)*(B15&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B15="",C15="",D15="",E15="",F15=""),"",IF(OR(B15="",C15="",E15=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E15)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H15&lt;&gt;0,F15=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G15&lt;&gt;0,F15=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F15&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F15)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C15)*($E$5:$E$504=E15)*(($D$5:$D$504=D15)*(D15&lt;&gt;"")+($B$5:$B$504=B15)*(B15&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C15="Оплата",K15&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E15)&gt;0,ROUND(E15-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J15" s="5">
         <f>IF(AND(B15="",C15="",E15=""),"",SUM($G$5:G15))</f>
         <v/>
       </c>
+      <c r="K15" s="8" t="n"/>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Строк с ошибкой в колонке «Проверка строки»</t>
@@ -990,13 +1007,14 @@
         <v/>
       </c>
       <c r="I16" s="6">
-        <f>IF(AND(B16="",C16="",D16="",E16="",F16=""),"",IF(OR(B16="",C16="",E16=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E16)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H16&lt;&gt;0,F16=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G16&lt;&gt;0,F16=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F16&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F16)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C16)*($E$5:$E$504=E16)*(($D$5:$D$504=D16)*(D16&lt;&gt;"")+($B$5:$B$504=B16)*(B16&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B16="",C16="",D16="",E16="",F16=""),"",IF(OR(B16="",C16="",E16=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E16)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H16&lt;&gt;0,F16=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G16&lt;&gt;0,F16=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F16&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F16)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C16)*($E$5:$E$504=E16)*(($D$5:$D$504=D16)*(D16&lt;&gt;"")+($B$5:$B$504=B16)*(B16&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C16="Оплата",K16&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E16)&gt;0,ROUND(E16-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J16" s="5">
         <f>IF(AND(B16="",C16="",E16=""),"",SUM($G$5:G16))</f>
         <v/>
       </c>
+      <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1016,13 +1034,14 @@
         <v/>
       </c>
       <c r="I17" s="6">
-        <f>IF(AND(B17="",C17="",D17="",E17="",F17=""),"",IF(OR(B17="",C17="",E17=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E17)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H17&lt;&gt;0,F17=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G17&lt;&gt;0,F17=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F17&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F17)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C17)*($E$5:$E$504=E17)*(($D$5:$D$504=D17)*(D17&lt;&gt;"")+($B$5:$B$504=B17)*(B17&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B17="",C17="",D17="",E17="",F17=""),"",IF(OR(B17="",C17="",E17=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E17)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H17&lt;&gt;0,F17=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G17&lt;&gt;0,F17=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F17&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F17)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C17)*($E$5:$E$504=E17)*(($D$5:$D$504=D17)*(D17&lt;&gt;"")+($B$5:$B$504=B17)*(B17&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C17="Оплата",K17&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E17)&gt;0,ROUND(E17-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J17" s="5">
         <f>IF(AND(B17="",C17="",E17=""),"",SUM($G$5:G17))</f>
         <v/>
       </c>
+      <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1042,13 +1061,14 @@
         <v/>
       </c>
       <c r="I18" s="6">
-        <f>IF(AND(B18="",C18="",D18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E18)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H18&lt;&gt;0,F18=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G18&lt;&gt;0,F18=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F18&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F18)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C18)*($E$5:$E$504=E18)*(($D$5:$D$504=D18)*(D18&lt;&gt;"")+($B$5:$B$504=B18)*(B18&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B18="",C18="",D18="",E18="",F18=""),"",IF(OR(B18="",C18="",E18=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E18)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H18&lt;&gt;0,F18=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G18&lt;&gt;0,F18=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F18&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F18)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C18)*($E$5:$E$504=E18)*(($D$5:$D$504=D18)*(D18&lt;&gt;"")+($B$5:$B$504=B18)*(B18&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C18="Оплата",K18&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E18)&gt;0,ROUND(E18-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J18" s="5">
         <f>IF(AND(B18="",C18="",E18=""),"",SUM($G$5:G18))</f>
         <v/>
       </c>
+      <c r="K18" s="8" t="n"/>
       <c r="L18" s="10" t="inlineStr">
         <is>
           <t>Общий долг — ТЕКУЩИЙ остаток: из него уже вычтены все оплаты, в том числе поступившие после начала просрочки. В расчёт процентов (файл 08) его переносить нельзя — там нужен бесспорный долг на первый день просрочки по каждому акту. Спорная часть в расчёт процентов и претензию не идёт: её оценка — у специалиста. Числа по актам берите на листе «Долг по актам», для заказчика — лист «Акт сверки».</t>
@@ -1073,13 +1093,14 @@
         <v/>
       </c>
       <c r="I19" s="6">
-        <f>IF(AND(B19="",C19="",D19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E19)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H19&lt;&gt;0,F19=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G19&lt;&gt;0,F19=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F19&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F19)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C19)*($E$5:$E$504=E19)*(($D$5:$D$504=D19)*(D19&lt;&gt;"")+($B$5:$B$504=B19)*(B19&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B19="",C19="",D19="",E19="",F19=""),"",IF(OR(B19="",C19="",E19=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E19)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H19&lt;&gt;0,F19=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G19&lt;&gt;0,F19=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F19&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F19)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C19)*($E$5:$E$504=E19)*(($D$5:$D$504=D19)*(D19&lt;&gt;"")+($B$5:$B$504=B19)*(B19&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C19="Оплата",K19&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E19)&gt;0,ROUND(E19-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J19" s="5">
         <f>IF(AND(B19="",C19="",E19=""),"",SUM($G$5:G19))</f>
         <v/>
       </c>
+      <c r="K19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -1099,13 +1120,14 @@
         <v/>
       </c>
       <c r="I20" s="6">
-        <f>IF(AND(B20="",C20="",D20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E20)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H20&lt;&gt;0,F20=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G20&lt;&gt;0,F20=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F20&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F20)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C20)*($E$5:$E$504=E20)*(($D$5:$D$504=D20)*(D20&lt;&gt;"")+($B$5:$B$504=B20)*(B20&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B20="",C20="",D20="",E20="",F20=""),"",IF(OR(B20="",C20="",E20=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E20)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H20&lt;&gt;0,F20=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G20&lt;&gt;0,F20=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F20&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F20)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C20)*($E$5:$E$504=E20)*(($D$5:$D$504=D20)*(D20&lt;&gt;"")+($B$5:$B$504=B20)*(B20&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C20="Оплата",K20&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E20)&gt;0,ROUND(E20-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J20" s="5">
         <f>IF(AND(B20="",C20="",E20=""),"",SUM($G$5:G20))</f>
         <v/>
       </c>
+      <c r="K20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1125,13 +1147,14 @@
         <v/>
       </c>
       <c r="I21" s="6">
-        <f>IF(AND(B21="",C21="",D21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E21)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H21&lt;&gt;0,F21=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G21&lt;&gt;0,F21=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F21&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F21)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C21)*($E$5:$E$504=E21)*(($D$5:$D$504=D21)*(D21&lt;&gt;"")+($B$5:$B$504=B21)*(B21&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B21="",C21="",D21="",E21="",F21=""),"",IF(OR(B21="",C21="",E21=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E21)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H21&lt;&gt;0,F21=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G21&lt;&gt;0,F21=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F21&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F21)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C21)*($E$5:$E$504=E21)*(($D$5:$D$504=D21)*(D21&lt;&gt;"")+($B$5:$B$504=B21)*(B21&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C21="Оплата",K21&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E21)&gt;0,ROUND(E21-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J21" s="5">
         <f>IF(AND(B21="",C21="",E21=""),"",SUM($G$5:G21))</f>
         <v/>
       </c>
+      <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1151,13 +1174,14 @@
         <v/>
       </c>
       <c r="I22" s="6">
-        <f>IF(AND(B22="",C22="",D22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E22)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H22&lt;&gt;0,F22=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G22&lt;&gt;0,F22=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F22&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F22)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C22)*($E$5:$E$504=E22)*(($D$5:$D$504=D22)*(D22&lt;&gt;"")+($B$5:$B$504=B22)*(B22&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B22="",C22="",D22="",E22="",F22=""),"",IF(OR(B22="",C22="",E22=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E22)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H22&lt;&gt;0,F22=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G22&lt;&gt;0,F22=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F22&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F22)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C22)*($E$5:$E$504=E22)*(($D$5:$D$504=D22)*(D22&lt;&gt;"")+($B$5:$B$504=B22)*(B22&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C22="Оплата",K22&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E22)&gt;0,ROUND(E22-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J22" s="5">
         <f>IF(AND(B22="",C22="",E22=""),"",SUM($G$5:G22))</f>
         <v/>
       </c>
+      <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1177,13 +1201,14 @@
         <v/>
       </c>
       <c r="I23" s="6">
-        <f>IF(AND(B23="",C23="",D23="",E23="",F23=""),"",IF(OR(B23="",C23="",E23=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E23)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H23&lt;&gt;0,F23=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G23&lt;&gt;0,F23=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F23&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F23)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C23)*($E$5:$E$504=E23)*(($D$5:$D$504=D23)*(D23&lt;&gt;"")+($B$5:$B$504=B23)*(B23&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B23="",C23="",D23="",E23="",F23=""),"",IF(OR(B23="",C23="",E23=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E23)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H23&lt;&gt;0,F23=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G23&lt;&gt;0,F23=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F23&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F23)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C23)*($E$5:$E$504=E23)*(($D$5:$D$504=D23)*(D23&lt;&gt;"")+($B$5:$B$504=B23)*(B23&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C23="Оплата",K23&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E23)&gt;0,ROUND(E23-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J23" s="5">
         <f>IF(AND(B23="",C23="",E23=""),"",SUM($G$5:G23))</f>
         <v/>
       </c>
+      <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1203,13 +1228,14 @@
         <v/>
       </c>
       <c r="I24" s="6">
-        <f>IF(AND(B24="",C24="",D24="",E24="",F24=""),"",IF(OR(B24="",C24="",E24=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E24)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H24&lt;&gt;0,F24=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G24&lt;&gt;0,F24=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F24&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F24)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C24)*($E$5:$E$504=E24)*(($D$5:$D$504=D24)*(D24&lt;&gt;"")+($B$5:$B$504=B24)*(B24&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B24="",C24="",D24="",E24="",F24=""),"",IF(OR(B24="",C24="",E24=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E24)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H24&lt;&gt;0,F24=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G24&lt;&gt;0,F24=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F24&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F24)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C24)*($E$5:$E$504=E24)*(($D$5:$D$504=D24)*(D24&lt;&gt;"")+($B$5:$B$504=B24)*(B24&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C24="Оплата",K24&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E24)&gt;0,ROUND(E24-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J24" s="5">
         <f>IF(AND(B24="",C24="",E24=""),"",SUM($G$5:G24))</f>
         <v/>
       </c>
+      <c r="K24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1229,13 +1255,14 @@
         <v/>
       </c>
       <c r="I25" s="6">
-        <f>IF(AND(B25="",C25="",D25="",E25="",F25=""),"",IF(OR(B25="",C25="",E25=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E25)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H25&lt;&gt;0,F25=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G25&lt;&gt;0,F25=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F25&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F25)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C25)*($E$5:$E$504=E25)*(($D$5:$D$504=D25)*(D25&lt;&gt;"")+($B$5:$B$504=B25)*(B25&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B25="",C25="",D25="",E25="",F25=""),"",IF(OR(B25="",C25="",E25=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E25)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H25&lt;&gt;0,F25=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G25&lt;&gt;0,F25=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F25&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F25)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C25)*($E$5:$E$504=E25)*(($D$5:$D$504=D25)*(D25&lt;&gt;"")+($B$5:$B$504=B25)*(B25&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C25="Оплата",K25&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E25)&gt;0,ROUND(E25-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J25" s="5">
         <f>IF(AND(B25="",C25="",E25=""),"",SUM($G$5:G25))</f>
         <v/>
       </c>
+      <c r="K25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1255,13 +1282,14 @@
         <v/>
       </c>
       <c r="I26" s="6">
-        <f>IF(AND(B26="",C26="",D26="",E26="",F26=""),"",IF(OR(B26="",C26="",E26=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E26)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H26&lt;&gt;0,F26=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G26&lt;&gt;0,F26=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F26&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F26)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C26)*($E$5:$E$504=E26)*(($D$5:$D$504=D26)*(D26&lt;&gt;"")+($B$5:$B$504=B26)*(B26&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B26="",C26="",D26="",E26="",F26=""),"",IF(OR(B26="",C26="",E26=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E26)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H26&lt;&gt;0,F26=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G26&lt;&gt;0,F26=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F26&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F26)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C26)*($E$5:$E$504=E26)*(($D$5:$D$504=D26)*(D26&lt;&gt;"")+($B$5:$B$504=B26)*(B26&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C26="Оплата",K26&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E26)&gt;0,ROUND(E26-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J26" s="5">
         <f>IF(AND(B26="",C26="",E26=""),"",SUM($G$5:G26))</f>
         <v/>
       </c>
+      <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1281,13 +1309,14 @@
         <v/>
       </c>
       <c r="I27" s="6">
-        <f>IF(AND(B27="",C27="",D27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E27)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H27&lt;&gt;0,F27=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G27&lt;&gt;0,F27=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F27&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F27)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C27)*($E$5:$E$504=E27)*(($D$5:$D$504=D27)*(D27&lt;&gt;"")+($B$5:$B$504=B27)*(B27&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B27="",C27="",D27="",E27="",F27=""),"",IF(OR(B27="",C27="",E27=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E27)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H27&lt;&gt;0,F27=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G27&lt;&gt;0,F27=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F27&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F27)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C27)*($E$5:$E$504=E27)*(($D$5:$D$504=D27)*(D27&lt;&gt;"")+($B$5:$B$504=B27)*(B27&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C27="Оплата",K27&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E27)&gt;0,ROUND(E27-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J27" s="5">
         <f>IF(AND(B27="",C27="",E27=""),"",SUM($G$5:G27))</f>
         <v/>
       </c>
+      <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1307,13 +1336,14 @@
         <v/>
       </c>
       <c r="I28" s="6">
-        <f>IF(AND(B28="",C28="",D28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E28)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H28&lt;&gt;0,F28=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G28&lt;&gt;0,F28=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F28&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F28)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C28)*($E$5:$E$504=E28)*(($D$5:$D$504=D28)*(D28&lt;&gt;"")+($B$5:$B$504=B28)*(B28&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B28="",C28="",D28="",E28="",F28=""),"",IF(OR(B28="",C28="",E28=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E28)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H28&lt;&gt;0,F28=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G28&lt;&gt;0,F28=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F28&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F28)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C28)*($E$5:$E$504=E28)*(($D$5:$D$504=D28)*(D28&lt;&gt;"")+($B$5:$B$504=B28)*(B28&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C28="Оплата",K28&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E28)&gt;0,ROUND(E28-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J28" s="5">
         <f>IF(AND(B28="",C28="",E28=""),"",SUM($G$5:G28))</f>
         <v/>
       </c>
+      <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1333,13 +1363,14 @@
         <v/>
       </c>
       <c r="I29" s="6">
-        <f>IF(AND(B29="",C29="",D29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E29)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H29&lt;&gt;0,F29=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G29&lt;&gt;0,F29=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F29&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F29)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C29)*($E$5:$E$504=E29)*(($D$5:$D$504=D29)*(D29&lt;&gt;"")+($B$5:$B$504=B29)*(B29&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B29="",C29="",D29="",E29="",F29=""),"",IF(OR(B29="",C29="",E29=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E29)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H29&lt;&gt;0,F29=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G29&lt;&gt;0,F29=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F29&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F29)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C29)*($E$5:$E$504=E29)*(($D$5:$D$504=D29)*(D29&lt;&gt;"")+($B$5:$B$504=B29)*(B29&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C29="Оплата",K29&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E29)&gt;0,ROUND(E29-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J29" s="5">
         <f>IF(AND(B29="",C29="",E29=""),"",SUM($G$5:G29))</f>
         <v/>
       </c>
+      <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1359,13 +1390,14 @@
         <v/>
       </c>
       <c r="I30" s="6">
-        <f>IF(AND(B30="",C30="",D30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E30)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H30&lt;&gt;0,F30=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G30&lt;&gt;0,F30=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F30&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F30)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C30)*($E$5:$E$504=E30)*(($D$5:$D$504=D30)*(D30&lt;&gt;"")+($B$5:$B$504=B30)*(B30&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B30="",C30="",D30="",E30="",F30=""),"",IF(OR(B30="",C30="",E30=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E30)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H30&lt;&gt;0,F30=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G30&lt;&gt;0,F30=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F30&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F30)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C30)*($E$5:$E$504=E30)*(($D$5:$D$504=D30)*(D30&lt;&gt;"")+($B$5:$B$504=B30)*(B30&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C30="Оплата",K30&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E30)&gt;0,ROUND(E30-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J30" s="5">
         <f>IF(AND(B30="",C30="",E30=""),"",SUM($G$5:G30))</f>
         <v/>
       </c>
+      <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1385,13 +1417,14 @@
         <v/>
       </c>
       <c r="I31" s="6">
-        <f>IF(AND(B31="",C31="",D31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E31)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H31&lt;&gt;0,F31=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G31&lt;&gt;0,F31=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F31&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F31)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C31)*($E$5:$E$504=E31)*(($D$5:$D$504=D31)*(D31&lt;&gt;"")+($B$5:$B$504=B31)*(B31&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B31="",C31="",D31="",E31="",F31=""),"",IF(OR(B31="",C31="",E31=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E31)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H31&lt;&gt;0,F31=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G31&lt;&gt;0,F31=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F31&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F31)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C31)*($E$5:$E$504=E31)*(($D$5:$D$504=D31)*(D31&lt;&gt;"")+($B$5:$B$504=B31)*(B31&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C31="Оплата",K31&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E31)&gt;0,ROUND(E31-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J31" s="5">
         <f>IF(AND(B31="",C31="",E31=""),"",SUM($G$5:G31))</f>
         <v/>
       </c>
+      <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -1411,13 +1444,14 @@
         <v/>
       </c>
       <c r="I32" s="6">
-        <f>IF(AND(B32="",C32="",D32="",E32="",F32=""),"",IF(OR(B32="",C32="",E32=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E32)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H32&lt;&gt;0,F32=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G32&lt;&gt;0,F32=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F32&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F32)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C32)*($E$5:$E$504=E32)*(($D$5:$D$504=D32)*(D32&lt;&gt;"")+($B$5:$B$504=B32)*(B32&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B32="",C32="",D32="",E32="",F32=""),"",IF(OR(B32="",C32="",E32=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E32)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H32&lt;&gt;0,F32=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G32&lt;&gt;0,F32=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F32&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F32)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C32)*($E$5:$E$504=E32)*(($D$5:$D$504=D32)*(D32&lt;&gt;"")+($B$5:$B$504=B32)*(B32&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C32="Оплата",K32&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E32)&gt;0,ROUND(E32-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J32" s="5">
         <f>IF(AND(B32="",C32="",E32=""),"",SUM($G$5:G32))</f>
         <v/>
       </c>
+      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1437,13 +1471,14 @@
         <v/>
       </c>
       <c r="I33" s="6">
-        <f>IF(AND(B33="",C33="",D33="",E33="",F33=""),"",IF(OR(B33="",C33="",E33=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E33)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H33&lt;&gt;0,F33=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G33&lt;&gt;0,F33=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F33&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F33)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C33)*($E$5:$E$504=E33)*(($D$5:$D$504=D33)*(D33&lt;&gt;"")+($B$5:$B$504=B33)*(B33&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B33="",C33="",D33="",E33="",F33=""),"",IF(OR(B33="",C33="",E33=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E33)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H33&lt;&gt;0,F33=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G33&lt;&gt;0,F33=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F33&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F33)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C33)*($E$5:$E$504=E33)*(($D$5:$D$504=D33)*(D33&lt;&gt;"")+($B$5:$B$504=B33)*(B33&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C33="Оплата",K33&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E33)&gt;0,ROUND(E33-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J33" s="5">
         <f>IF(AND(B33="",C33="",E33=""),"",SUM($G$5:G33))</f>
         <v/>
       </c>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1463,13 +1498,14 @@
         <v/>
       </c>
       <c r="I34" s="6">
-        <f>IF(AND(B34="",C34="",D34="",E34="",F34=""),"",IF(OR(B34="",C34="",E34=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E34)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H34&lt;&gt;0,F34=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G34&lt;&gt;0,F34=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F34&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F34)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C34)*($E$5:$E$504=E34)*(($D$5:$D$504=D34)*(D34&lt;&gt;"")+($B$5:$B$504=B34)*(B34&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B34="",C34="",D34="",E34="",F34=""),"",IF(OR(B34="",C34="",E34=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E34)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H34&lt;&gt;0,F34=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G34&lt;&gt;0,F34=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F34&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F34)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C34)*($E$5:$E$504=E34)*(($D$5:$D$504=D34)*(D34&lt;&gt;"")+($B$5:$B$504=B34)*(B34&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C34="Оплата",K34&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E34)&gt;0,ROUND(E34-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J34" s="5">
         <f>IF(AND(B34="",C34="",E34=""),"",SUM($G$5:G34))</f>
         <v/>
       </c>
+      <c r="K34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1489,13 +1525,14 @@
         <v/>
       </c>
       <c r="I35" s="6">
-        <f>IF(AND(B35="",C35="",D35="",E35="",F35=""),"",IF(OR(B35="",C35="",E35=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E35)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H35&lt;&gt;0,F35=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G35&lt;&gt;0,F35=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F35&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F35)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C35)*($E$5:$E$504=E35)*(($D$5:$D$504=D35)*(D35&lt;&gt;"")+($B$5:$B$504=B35)*(B35&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B35="",C35="",D35="",E35="",F35=""),"",IF(OR(B35="",C35="",E35=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E35)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H35&lt;&gt;0,F35=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G35&lt;&gt;0,F35=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F35&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F35)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C35)*($E$5:$E$504=E35)*(($D$5:$D$504=D35)*(D35&lt;&gt;"")+($B$5:$B$504=B35)*(B35&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C35="Оплата",K35&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E35)&gt;0,ROUND(E35-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J35" s="5">
         <f>IF(AND(B35="",C35="",E35=""),"",SUM($G$5:G35))</f>
         <v/>
       </c>
+      <c r="K35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1515,13 +1552,14 @@
         <v/>
       </c>
       <c r="I36" s="6">
-        <f>IF(AND(B36="",C36="",D36="",E36="",F36=""),"",IF(OR(B36="",C36="",E36=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E36)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H36&lt;&gt;0,F36=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G36&lt;&gt;0,F36=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F36&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F36)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C36)*($E$5:$E$504=E36)*(($D$5:$D$504=D36)*(D36&lt;&gt;"")+($B$5:$B$504=B36)*(B36&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B36="",C36="",D36="",E36="",F36=""),"",IF(OR(B36="",C36="",E36=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E36)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H36&lt;&gt;0,F36=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G36&lt;&gt;0,F36=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F36&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F36)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C36)*($E$5:$E$504=E36)*(($D$5:$D$504=D36)*(D36&lt;&gt;"")+($B$5:$B$504=B36)*(B36&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C36="Оплата",K36&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E36)&gt;0,ROUND(E36-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J36" s="5">
         <f>IF(AND(B36="",C36="",E36=""),"",SUM($G$5:G36))</f>
         <v/>
       </c>
+      <c r="K36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1541,13 +1579,14 @@
         <v/>
       </c>
       <c r="I37" s="6">
-        <f>IF(AND(B37="",C37="",D37="",E37="",F37=""),"",IF(OR(B37="",C37="",E37=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E37)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H37&lt;&gt;0,F37=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G37&lt;&gt;0,F37=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F37&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F37)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C37)*($E$5:$E$504=E37)*(($D$5:$D$504=D37)*(D37&lt;&gt;"")+($B$5:$B$504=B37)*(B37&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B37="",C37="",D37="",E37="",F37=""),"",IF(OR(B37="",C37="",E37=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E37)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H37&lt;&gt;0,F37=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G37&lt;&gt;0,F37=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F37&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F37)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C37)*($E$5:$E$504=E37)*(($D$5:$D$504=D37)*(D37&lt;&gt;"")+($B$5:$B$504=B37)*(B37&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C37="Оплата",K37&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E37)&gt;0,ROUND(E37-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J37" s="5">
         <f>IF(AND(B37="",C37="",E37=""),"",SUM($G$5:G37))</f>
         <v/>
       </c>
+      <c r="K37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -1567,13 +1606,14 @@
         <v/>
       </c>
       <c r="I38" s="6">
-        <f>IF(AND(B38="",C38="",D38="",E38="",F38=""),"",IF(OR(B38="",C38="",E38=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E38)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H38&lt;&gt;0,F38=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G38&lt;&gt;0,F38=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F38&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F38)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C38)*($E$5:$E$504=E38)*(($D$5:$D$504=D38)*(D38&lt;&gt;"")+($B$5:$B$504=B38)*(B38&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B38="",C38="",D38="",E38="",F38=""),"",IF(OR(B38="",C38="",E38=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E38)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H38&lt;&gt;0,F38=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G38&lt;&gt;0,F38=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F38&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F38)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C38)*($E$5:$E$504=E38)*(($D$5:$D$504=D38)*(D38&lt;&gt;"")+($B$5:$B$504=B38)*(B38&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C38="Оплата",K38&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E38)&gt;0,ROUND(E38-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J38" s="5">
         <f>IF(AND(B38="",C38="",E38=""),"",SUM($G$5:G38))</f>
         <v/>
       </c>
+      <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1593,13 +1633,14 @@
         <v/>
       </c>
       <c r="I39" s="6">
-        <f>IF(AND(B39="",C39="",D39="",E39="",F39=""),"",IF(OR(B39="",C39="",E39=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E39)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H39&lt;&gt;0,F39=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G39&lt;&gt;0,F39=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F39&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F39)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C39)*($E$5:$E$504=E39)*(($D$5:$D$504=D39)*(D39&lt;&gt;"")+($B$5:$B$504=B39)*(B39&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B39="",C39="",D39="",E39="",F39=""),"",IF(OR(B39="",C39="",E39=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E39)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H39&lt;&gt;0,F39=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G39&lt;&gt;0,F39=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F39&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F39)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C39)*($E$5:$E$504=E39)*(($D$5:$D$504=D39)*(D39&lt;&gt;"")+($B$5:$B$504=B39)*(B39&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C39="Оплата",K39&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E39)&gt;0,ROUND(E39-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J39" s="5">
         <f>IF(AND(B39="",C39="",E39=""),"",SUM($G$5:G39))</f>
         <v/>
       </c>
+      <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -1619,13 +1660,14 @@
         <v/>
       </c>
       <c r="I40" s="6">
-        <f>IF(AND(B40="",C40="",D40="",E40="",F40=""),"",IF(OR(B40="",C40="",E40=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E40)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H40&lt;&gt;0,F40=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G40&lt;&gt;0,F40=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F40&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F40)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C40)*($E$5:$E$504=E40)*(($D$5:$D$504=D40)*(D40&lt;&gt;"")+($B$5:$B$504=B40)*(B40&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B40="",C40="",D40="",E40="",F40=""),"",IF(OR(B40="",C40="",E40=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E40)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H40&lt;&gt;0,F40=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G40&lt;&gt;0,F40=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F40&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F40)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C40)*($E$5:$E$504=E40)*(($D$5:$D$504=D40)*(D40&lt;&gt;"")+($B$5:$B$504=B40)*(B40&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C40="Оплата",K40&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E40)&gt;0,ROUND(E40-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J40" s="5">
         <f>IF(AND(B40="",C40="",E40=""),"",SUM($G$5:G40))</f>
         <v/>
       </c>
+      <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -1645,13 +1687,14 @@
         <v/>
       </c>
       <c r="I41" s="6">
-        <f>IF(AND(B41="",C41="",D41="",E41="",F41=""),"",IF(OR(B41="",C41="",E41=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E41)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H41&lt;&gt;0,F41=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G41&lt;&gt;0,F41=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F41&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F41)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C41)*($E$5:$E$504=E41)*(($D$5:$D$504=D41)*(D41&lt;&gt;"")+($B$5:$B$504=B41)*(B41&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B41="",C41="",D41="",E41="",F41=""),"",IF(OR(B41="",C41="",E41=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E41)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H41&lt;&gt;0,F41=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G41&lt;&gt;0,F41=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F41&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F41)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C41)*($E$5:$E$504=E41)*(($D$5:$D$504=D41)*(D41&lt;&gt;"")+($B$5:$B$504=B41)*(B41&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C41="Оплата",K41&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E41)&gt;0,ROUND(E41-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J41" s="5">
         <f>IF(AND(B41="",C41="",E41=""),"",SUM($G$5:G41))</f>
         <v/>
       </c>
+      <c r="K41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -1671,13 +1714,14 @@
         <v/>
       </c>
       <c r="I42" s="6">
-        <f>IF(AND(B42="",C42="",D42="",E42="",F42=""),"",IF(OR(B42="",C42="",E42=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E42)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H42&lt;&gt;0,F42=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G42&lt;&gt;0,F42=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F42&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F42)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C42)*($E$5:$E$504=E42)*(($D$5:$D$504=D42)*(D42&lt;&gt;"")+($B$5:$B$504=B42)*(B42&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B42="",C42="",D42="",E42="",F42=""),"",IF(OR(B42="",C42="",E42=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E42)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H42&lt;&gt;0,F42=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G42&lt;&gt;0,F42=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F42&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F42)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C42)*($E$5:$E$504=E42)*(($D$5:$D$504=D42)*(D42&lt;&gt;"")+($B$5:$B$504=B42)*(B42&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C42="Оплата",K42&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E42)&gt;0,ROUND(E42-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J42" s="5">
         <f>IF(AND(B42="",C42="",E42=""),"",SUM($G$5:G42))</f>
         <v/>
       </c>
+      <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -1697,13 +1741,14 @@
         <v/>
       </c>
       <c r="I43" s="6">
-        <f>IF(AND(B43="",C43="",D43="",E43="",F43=""),"",IF(OR(B43="",C43="",E43=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E43)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H43&lt;&gt;0,F43=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G43&lt;&gt;0,F43=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F43&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F43)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C43)*($E$5:$E$504=E43)*(($D$5:$D$504=D43)*(D43&lt;&gt;"")+($B$5:$B$504=B43)*(B43&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B43="",C43="",D43="",E43="",F43=""),"",IF(OR(B43="",C43="",E43=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E43)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H43&lt;&gt;0,F43=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G43&lt;&gt;0,F43=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F43&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F43)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C43)*($E$5:$E$504=E43)*(($D$5:$D$504=D43)*(D43&lt;&gt;"")+($B$5:$B$504=B43)*(B43&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C43="Оплата",K43&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E43)&gt;0,ROUND(E43-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J43" s="5">
         <f>IF(AND(B43="",C43="",E43=""),"",SUM($G$5:G43))</f>
         <v/>
       </c>
+      <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -1723,13 +1768,14 @@
         <v/>
       </c>
       <c r="I44" s="6">
-        <f>IF(AND(B44="",C44="",D44="",E44="",F44=""),"",IF(OR(B44="",C44="",E44=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E44)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H44&lt;&gt;0,F44=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G44&lt;&gt;0,F44=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F44&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F44)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C44)*($E$5:$E$504=E44)*(($D$5:$D$504=D44)*(D44&lt;&gt;"")+($B$5:$B$504=B44)*(B44&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B44="",C44="",D44="",E44="",F44=""),"",IF(OR(B44="",C44="",E44=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E44)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H44&lt;&gt;0,F44=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G44&lt;&gt;0,F44=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F44&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F44)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C44)*($E$5:$E$504=E44)*(($D$5:$D$504=D44)*(D44&lt;&gt;"")+($B$5:$B$504=B44)*(B44&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C44="Оплата",K44&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E44)&gt;0,ROUND(E44-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J44" s="5">
         <f>IF(AND(B44="",C44="",E44=""),"",SUM($G$5:G44))</f>
         <v/>
       </c>
+      <c r="K44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -1749,13 +1795,14 @@
         <v/>
       </c>
       <c r="I45" s="6">
-        <f>IF(AND(B45="",C45="",D45="",E45="",F45=""),"",IF(OR(B45="",C45="",E45=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E45)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H45&lt;&gt;0,F45=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G45&lt;&gt;0,F45=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F45&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F45)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C45)*($E$5:$E$504=E45)*(($D$5:$D$504=D45)*(D45&lt;&gt;"")+($B$5:$B$504=B45)*(B45&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B45="",C45="",D45="",E45="",F45=""),"",IF(OR(B45="",C45="",E45=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E45)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H45&lt;&gt;0,F45=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G45&lt;&gt;0,F45=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F45&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F45)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C45)*($E$5:$E$504=E45)*(($D$5:$D$504=D45)*(D45&lt;&gt;"")+($B$5:$B$504=B45)*(B45&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C45="Оплата",K45&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E45)&gt;0,ROUND(E45-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J45" s="5">
         <f>IF(AND(B45="",C45="",E45=""),"",SUM($G$5:G45))</f>
         <v/>
       </c>
+      <c r="K45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -1775,13 +1822,14 @@
         <v/>
       </c>
       <c r="I46" s="6">
-        <f>IF(AND(B46="",C46="",D46="",E46="",F46=""),"",IF(OR(B46="",C46="",E46=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E46)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H46&lt;&gt;0,F46=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G46&lt;&gt;0,F46=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F46&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F46)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C46)*($E$5:$E$504=E46)*(($D$5:$D$504=D46)*(D46&lt;&gt;"")+($B$5:$B$504=B46)*(B46&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B46="",C46="",D46="",E46="",F46=""),"",IF(OR(B46="",C46="",E46=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E46)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H46&lt;&gt;0,F46=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G46&lt;&gt;0,F46=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F46&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F46)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C46)*($E$5:$E$504=E46)*(($D$5:$D$504=D46)*(D46&lt;&gt;"")+($B$5:$B$504=B46)*(B46&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C46="Оплата",K46&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E46)&gt;0,ROUND(E46-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J46" s="5">
         <f>IF(AND(B46="",C46="",E46=""),"",SUM($G$5:G46))</f>
         <v/>
       </c>
+      <c r="K46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -1801,13 +1849,14 @@
         <v/>
       </c>
       <c r="I47" s="6">
-        <f>IF(AND(B47="",C47="",D47="",E47="",F47=""),"",IF(OR(B47="",C47="",E47=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E47)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H47&lt;&gt;0,F47=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G47&lt;&gt;0,F47=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F47&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F47)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C47)*($E$5:$E$504=E47)*(($D$5:$D$504=D47)*(D47&lt;&gt;"")+($B$5:$B$504=B47)*(B47&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B47="",C47="",D47="",E47="",F47=""),"",IF(OR(B47="",C47="",E47=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E47)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H47&lt;&gt;0,F47=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G47&lt;&gt;0,F47=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F47&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F47)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C47)*($E$5:$E$504=E47)*(($D$5:$D$504=D47)*(D47&lt;&gt;"")+($B$5:$B$504=B47)*(B47&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C47="Оплата",K47&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E47)&gt;0,ROUND(E47-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J47" s="5">
         <f>IF(AND(B47="",C47="",E47=""),"",SUM($G$5:G47))</f>
         <v/>
       </c>
+      <c r="K47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -1827,13 +1876,14 @@
         <v/>
       </c>
       <c r="I48" s="6">
-        <f>IF(AND(B48="",C48="",D48="",E48="",F48=""),"",IF(OR(B48="",C48="",E48=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E48)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H48&lt;&gt;0,F48=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G48&lt;&gt;0,F48=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F48&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F48)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C48)*($E$5:$E$504=E48)*(($D$5:$D$504=D48)*(D48&lt;&gt;"")+($B$5:$B$504=B48)*(B48&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B48="",C48="",D48="",E48="",F48=""),"",IF(OR(B48="",C48="",E48=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E48)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H48&lt;&gt;0,F48=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G48&lt;&gt;0,F48=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F48&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F48)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C48)*($E$5:$E$504=E48)*(($D$5:$D$504=D48)*(D48&lt;&gt;"")+($B$5:$B$504=B48)*(B48&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C48="Оплата",K48&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E48)&gt;0,ROUND(E48-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J48" s="5">
         <f>IF(AND(B48="",C48="",E48=""),"",SUM($G$5:G48))</f>
         <v/>
       </c>
+      <c r="K48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1853,13 +1903,14 @@
         <v/>
       </c>
       <c r="I49" s="6">
-        <f>IF(AND(B49="",C49="",D49="",E49="",F49=""),"",IF(OR(B49="",C49="",E49=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E49)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H49&lt;&gt;0,F49=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G49&lt;&gt;0,F49=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F49&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F49)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C49)*($E$5:$E$504=E49)*(($D$5:$D$504=D49)*(D49&lt;&gt;"")+($B$5:$B$504=B49)*(B49&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B49="",C49="",D49="",E49="",F49=""),"",IF(OR(B49="",C49="",E49=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E49)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H49&lt;&gt;0,F49=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G49&lt;&gt;0,F49=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F49&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F49)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C49)*($E$5:$E$504=E49)*(($D$5:$D$504=D49)*(D49&lt;&gt;"")+($B$5:$B$504=B49)*(B49&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C49="Оплата",K49&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E49)&gt;0,ROUND(E49-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J49" s="5">
         <f>IF(AND(B49="",C49="",E49=""),"",SUM($G$5:G49))</f>
         <v/>
       </c>
+      <c r="K49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -1879,13 +1930,14 @@
         <v/>
       </c>
       <c r="I50" s="6">
-        <f>IF(AND(B50="",C50="",D50="",E50="",F50=""),"",IF(OR(B50="",C50="",E50=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E50)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H50&lt;&gt;0,F50=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G50&lt;&gt;0,F50=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F50&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F50)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C50)*($E$5:$E$504=E50)*(($D$5:$D$504=D50)*(D50&lt;&gt;"")+($B$5:$B$504=B50)*(B50&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B50="",C50="",D50="",E50="",F50=""),"",IF(OR(B50="",C50="",E50=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E50)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H50&lt;&gt;0,F50=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G50&lt;&gt;0,F50=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F50&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F50)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C50)*($E$5:$E$504=E50)*(($D$5:$D$504=D50)*(D50&lt;&gt;"")+($B$5:$B$504=B50)*(B50&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C50="Оплата",K50&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E50)&gt;0,ROUND(E50-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J50" s="5">
         <f>IF(AND(B50="",C50="",E50=""),"",SUM($G$5:G50))</f>
         <v/>
       </c>
+      <c r="K50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -1905,13 +1957,14 @@
         <v/>
       </c>
       <c r="I51" s="6">
-        <f>IF(AND(B51="",C51="",D51="",E51="",F51=""),"",IF(OR(B51="",C51="",E51=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E51)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H51&lt;&gt;0,F51=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G51&lt;&gt;0,F51=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F51&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F51)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C51)*($E$5:$E$504=E51)*(($D$5:$D$504=D51)*(D51&lt;&gt;"")+($B$5:$B$504=B51)*(B51&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B51="",C51="",D51="",E51="",F51=""),"",IF(OR(B51="",C51="",E51=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E51)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H51&lt;&gt;0,F51=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G51&lt;&gt;0,F51=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F51&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F51)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C51)*($E$5:$E$504=E51)*(($D$5:$D$504=D51)*(D51&lt;&gt;"")+($B$5:$B$504=B51)*(B51&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C51="Оплата",K51&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E51)&gt;0,ROUND(E51-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J51" s="5">
         <f>IF(AND(B51="",C51="",E51=""),"",SUM($G$5:G51))</f>
         <v/>
       </c>
+      <c r="K51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -1931,13 +1984,14 @@
         <v/>
       </c>
       <c r="I52" s="6">
-        <f>IF(AND(B52="",C52="",D52="",E52="",F52=""),"",IF(OR(B52="",C52="",E52=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E52)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H52&lt;&gt;0,F52=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G52&lt;&gt;0,F52=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F52&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F52)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C52)*($E$5:$E$504=E52)*(($D$5:$D$504=D52)*(D52&lt;&gt;"")+($B$5:$B$504=B52)*(B52&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B52="",C52="",D52="",E52="",F52=""),"",IF(OR(B52="",C52="",E52=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E52)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H52&lt;&gt;0,F52=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G52&lt;&gt;0,F52=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F52&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F52)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C52)*($E$5:$E$504=E52)*(($D$5:$D$504=D52)*(D52&lt;&gt;"")+($B$5:$B$504=B52)*(B52&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C52="Оплата",K52&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E52)&gt;0,ROUND(E52-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J52" s="5">
         <f>IF(AND(B52="",C52="",E52=""),"",SUM($G$5:G52))</f>
         <v/>
       </c>
+      <c r="K52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -1957,13 +2011,14 @@
         <v/>
       </c>
       <c r="I53" s="6">
-        <f>IF(AND(B53="",C53="",D53="",E53="",F53=""),"",IF(OR(B53="",C53="",E53=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E53)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H53&lt;&gt;0,F53=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G53&lt;&gt;0,F53=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F53&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F53)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C53)*($E$5:$E$504=E53)*(($D$5:$D$504=D53)*(D53&lt;&gt;"")+($B$5:$B$504=B53)*(B53&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B53="",C53="",D53="",E53="",F53=""),"",IF(OR(B53="",C53="",E53=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E53)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H53&lt;&gt;0,F53=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G53&lt;&gt;0,F53=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F53&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F53)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C53)*($E$5:$E$504=E53)*(($D$5:$D$504=D53)*(D53&lt;&gt;"")+($B$5:$B$504=B53)*(B53&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C53="Оплата",K53&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E53)&gt;0,ROUND(E53-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J53" s="5">
         <f>IF(AND(B53="",C53="",E53=""),"",SUM($G$5:G53))</f>
         <v/>
       </c>
+      <c r="K53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -1983,13 +2038,14 @@
         <v/>
       </c>
       <c r="I54" s="6">
-        <f>IF(AND(B54="",C54="",D54="",E54="",F54=""),"",IF(OR(B54="",C54="",E54=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E54)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H54&lt;&gt;0,F54=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G54&lt;&gt;0,F54=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F54&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F54)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C54)*($E$5:$E$504=E54)*(($D$5:$D$504=D54)*(D54&lt;&gt;"")+($B$5:$B$504=B54)*(B54&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B54="",C54="",D54="",E54="",F54=""),"",IF(OR(B54="",C54="",E54=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E54)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H54&lt;&gt;0,F54=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G54&lt;&gt;0,F54=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F54&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F54)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C54)*($E$5:$E$504=E54)*(($D$5:$D$504=D54)*(D54&lt;&gt;"")+($B$5:$B$504=B54)*(B54&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C54="Оплата",K54&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E54)&gt;0,ROUND(E54-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J54" s="5">
         <f>IF(AND(B54="",C54="",E54=""),"",SUM($G$5:G54))</f>
         <v/>
       </c>
+      <c r="K54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2009,13 +2065,14 @@
         <v/>
       </c>
       <c r="I55" s="6">
-        <f>IF(AND(B55="",C55="",D55="",E55="",F55=""),"",IF(OR(B55="",C55="",E55=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E55)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H55&lt;&gt;0,F55=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G55&lt;&gt;0,F55=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F55&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F55)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C55)*($E$5:$E$504=E55)*(($D$5:$D$504=D55)*(D55&lt;&gt;"")+($B$5:$B$504=B55)*(B55&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B55="",C55="",D55="",E55="",F55=""),"",IF(OR(B55="",C55="",E55=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E55)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H55&lt;&gt;0,F55=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G55&lt;&gt;0,F55=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F55&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F55)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C55)*($E$5:$E$504=E55)*(($D$5:$D$504=D55)*(D55&lt;&gt;"")+($B$5:$B$504=B55)*(B55&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C55="Оплата",K55&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E55)&gt;0,ROUND(E55-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J55" s="5">
         <f>IF(AND(B55="",C55="",E55=""),"",SUM($G$5:G55))</f>
         <v/>
       </c>
+      <c r="K55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2035,13 +2092,14 @@
         <v/>
       </c>
       <c r="I56" s="6">
-        <f>IF(AND(B56="",C56="",D56="",E56="",F56=""),"",IF(OR(B56="",C56="",E56=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E56)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H56&lt;&gt;0,F56=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G56&lt;&gt;0,F56=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F56&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F56)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C56)*($E$5:$E$504=E56)*(($D$5:$D$504=D56)*(D56&lt;&gt;"")+($B$5:$B$504=B56)*(B56&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B56="",C56="",D56="",E56="",F56=""),"",IF(OR(B56="",C56="",E56=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E56)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H56&lt;&gt;0,F56=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G56&lt;&gt;0,F56=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F56&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F56)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C56)*($E$5:$E$504=E56)*(($D$5:$D$504=D56)*(D56&lt;&gt;"")+($B$5:$B$504=B56)*(B56&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C56="Оплата",K56&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E56)&gt;0,ROUND(E56-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J56" s="5">
         <f>IF(AND(B56="",C56="",E56=""),"",SUM($G$5:G56))</f>
         <v/>
       </c>
+      <c r="K56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2061,13 +2119,14 @@
         <v/>
       </c>
       <c r="I57" s="6">
-        <f>IF(AND(B57="",C57="",D57="",E57="",F57=""),"",IF(OR(B57="",C57="",E57=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E57)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H57&lt;&gt;0,F57=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G57&lt;&gt;0,F57=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F57&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F57)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C57)*($E$5:$E$504=E57)*(($D$5:$D$504=D57)*(D57&lt;&gt;"")+($B$5:$B$504=B57)*(B57&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B57="",C57="",D57="",E57="",F57=""),"",IF(OR(B57="",C57="",E57=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E57)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H57&lt;&gt;0,F57=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G57&lt;&gt;0,F57=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F57&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F57)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C57)*($E$5:$E$504=E57)*(($D$5:$D$504=D57)*(D57&lt;&gt;"")+($B$5:$B$504=B57)*(B57&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C57="Оплата",K57&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E57)&gt;0,ROUND(E57-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J57" s="5">
         <f>IF(AND(B57="",C57="",E57=""),"",SUM($G$5:G57))</f>
         <v/>
       </c>
+      <c r="K57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -2087,13 +2146,14 @@
         <v/>
       </c>
       <c r="I58" s="6">
-        <f>IF(AND(B58="",C58="",D58="",E58="",F58=""),"",IF(OR(B58="",C58="",E58=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E58)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H58&lt;&gt;0,F58=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G58&lt;&gt;0,F58=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F58&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F58)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C58)*($E$5:$E$504=E58)*(($D$5:$D$504=D58)*(D58&lt;&gt;"")+($B$5:$B$504=B58)*(B58&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B58="",C58="",D58="",E58="",F58=""),"",IF(OR(B58="",C58="",E58=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E58)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H58&lt;&gt;0,F58=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G58&lt;&gt;0,F58=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F58&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F58)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C58)*($E$5:$E$504=E58)*(($D$5:$D$504=D58)*(D58&lt;&gt;"")+($B$5:$B$504=B58)*(B58&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C58="Оплата",K58&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E58)&gt;0,ROUND(E58-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J58" s="5">
         <f>IF(AND(B58="",C58="",E58=""),"",SUM($G$5:G58))</f>
         <v/>
       </c>
+      <c r="K58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2113,13 +2173,14 @@
         <v/>
       </c>
       <c r="I59" s="6">
-        <f>IF(AND(B59="",C59="",D59="",E59="",F59=""),"",IF(OR(B59="",C59="",E59=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E59)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H59&lt;&gt;0,F59=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G59&lt;&gt;0,F59=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F59&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F59)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C59)*($E$5:$E$504=E59)*(($D$5:$D$504=D59)*(D59&lt;&gt;"")+($B$5:$B$504=B59)*(B59&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B59="",C59="",D59="",E59="",F59=""),"",IF(OR(B59="",C59="",E59=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E59)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H59&lt;&gt;0,F59=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G59&lt;&gt;0,F59=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F59&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F59)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C59)*($E$5:$E$504=E59)*(($D$5:$D$504=D59)*(D59&lt;&gt;"")+($B$5:$B$504=B59)*(B59&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C59="Оплата",K59&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E59)&gt;0,ROUND(E59-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J59" s="5">
         <f>IF(AND(B59="",C59="",E59=""),"",SUM($G$5:G59))</f>
         <v/>
       </c>
+      <c r="K59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -2139,13 +2200,14 @@
         <v/>
       </c>
       <c r="I60" s="6">
-        <f>IF(AND(B60="",C60="",D60="",E60="",F60=""),"",IF(OR(B60="",C60="",E60=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E60)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H60&lt;&gt;0,F60=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G60&lt;&gt;0,F60=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F60&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F60)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C60)*($E$5:$E$504=E60)*(($D$5:$D$504=D60)*(D60&lt;&gt;"")+($B$5:$B$504=B60)*(B60&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B60="",C60="",D60="",E60="",F60=""),"",IF(OR(B60="",C60="",E60=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E60)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H60&lt;&gt;0,F60=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G60&lt;&gt;0,F60=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F60&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F60)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C60)*($E$5:$E$504=E60)*(($D$5:$D$504=D60)*(D60&lt;&gt;"")+($B$5:$B$504=B60)*(B60&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C60="Оплата",K60&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E60)&gt;0,ROUND(E60-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J60" s="5">
         <f>IF(AND(B60="",C60="",E60=""),"",SUM($G$5:G60))</f>
         <v/>
       </c>
+      <c r="K60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -2165,13 +2227,14 @@
         <v/>
       </c>
       <c r="I61" s="6">
-        <f>IF(AND(B61="",C61="",D61="",E61="",F61=""),"",IF(OR(B61="",C61="",E61=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E61)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H61&lt;&gt;0,F61=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G61&lt;&gt;0,F61=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F61&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F61)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C61)*($E$5:$E$504=E61)*(($D$5:$D$504=D61)*(D61&lt;&gt;"")+($B$5:$B$504=B61)*(B61&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B61="",C61="",D61="",E61="",F61=""),"",IF(OR(B61="",C61="",E61=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E61)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H61&lt;&gt;0,F61=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G61&lt;&gt;0,F61=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F61&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F61)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C61)*($E$5:$E$504=E61)*(($D$5:$D$504=D61)*(D61&lt;&gt;"")+($B$5:$B$504=B61)*(B61&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C61="Оплата",K61&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E61)&gt;0,ROUND(E61-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J61" s="5">
         <f>IF(AND(B61="",C61="",E61=""),"",SUM($G$5:G61))</f>
         <v/>
       </c>
+      <c r="K61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -2191,13 +2254,14 @@
         <v/>
       </c>
       <c r="I62" s="6">
-        <f>IF(AND(B62="",C62="",D62="",E62="",F62=""),"",IF(OR(B62="",C62="",E62=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E62)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H62&lt;&gt;0,F62=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G62&lt;&gt;0,F62=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F62&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F62)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C62)*($E$5:$E$504=E62)*(($D$5:$D$504=D62)*(D62&lt;&gt;"")+($B$5:$B$504=B62)*(B62&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B62="",C62="",D62="",E62="",F62=""),"",IF(OR(B62="",C62="",E62=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E62)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H62&lt;&gt;0,F62=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G62&lt;&gt;0,F62=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F62&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F62)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C62)*($E$5:$E$504=E62)*(($D$5:$D$504=D62)*(D62&lt;&gt;"")+($B$5:$B$504=B62)*(B62&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C62="Оплата",K62&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E62)&gt;0,ROUND(E62-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J62" s="5">
         <f>IF(AND(B62="",C62="",E62=""),"",SUM($G$5:G62))</f>
         <v/>
       </c>
+      <c r="K62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -2217,13 +2281,14 @@
         <v/>
       </c>
       <c r="I63" s="6">
-        <f>IF(AND(B63="",C63="",D63="",E63="",F63=""),"",IF(OR(B63="",C63="",E63=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E63)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H63&lt;&gt;0,F63=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G63&lt;&gt;0,F63=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F63&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F63)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C63)*($E$5:$E$504=E63)*(($D$5:$D$504=D63)*(D63&lt;&gt;"")+($B$5:$B$504=B63)*(B63&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B63="",C63="",D63="",E63="",F63=""),"",IF(OR(B63="",C63="",E63=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E63)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H63&lt;&gt;0,F63=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G63&lt;&gt;0,F63=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F63&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F63)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C63)*($E$5:$E$504=E63)*(($D$5:$D$504=D63)*(D63&lt;&gt;"")+($B$5:$B$504=B63)*(B63&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C63="Оплата",K63&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E63)&gt;0,ROUND(E63-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J63" s="5">
         <f>IF(AND(B63="",C63="",E63=""),"",SUM($G$5:G63))</f>
         <v/>
       </c>
+      <c r="K63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -2243,13 +2308,14 @@
         <v/>
       </c>
       <c r="I64" s="6">
-        <f>IF(AND(B64="",C64="",D64="",E64="",F64=""),"",IF(OR(B64="",C64="",E64=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E64)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H64&lt;&gt;0,F64=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G64&lt;&gt;0,F64=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F64&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F64)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C64)*($E$5:$E$504=E64)*(($D$5:$D$504=D64)*(D64&lt;&gt;"")+($B$5:$B$504=B64)*(B64&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B64="",C64="",D64="",E64="",F64=""),"",IF(OR(B64="",C64="",E64=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E64)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H64&lt;&gt;0,F64=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G64&lt;&gt;0,F64=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F64&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F64)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C64)*($E$5:$E$504=E64)*(($D$5:$D$504=D64)*(D64&lt;&gt;"")+($B$5:$B$504=B64)*(B64&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C64="Оплата",K64&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E64)&gt;0,ROUND(E64-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J64" s="5">
         <f>IF(AND(B64="",C64="",E64=""),"",SUM($G$5:G64))</f>
         <v/>
       </c>
+      <c r="K64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -2269,13 +2335,14 @@
         <v/>
       </c>
       <c r="I65" s="6">
-        <f>IF(AND(B65="",C65="",D65="",E65="",F65=""),"",IF(OR(B65="",C65="",E65=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E65)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H65&lt;&gt;0,F65=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G65&lt;&gt;0,F65=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F65&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F65)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C65)*($E$5:$E$504=E65)*(($D$5:$D$504=D65)*(D65&lt;&gt;"")+($B$5:$B$504=B65)*(B65&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B65="",C65="",D65="",E65="",F65=""),"",IF(OR(B65="",C65="",E65=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E65)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H65&lt;&gt;0,F65=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G65&lt;&gt;0,F65=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F65&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F65)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C65)*($E$5:$E$504=E65)*(($D$5:$D$504=D65)*(D65&lt;&gt;"")+($B$5:$B$504=B65)*(B65&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C65="Оплата",K65&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E65)&gt;0,ROUND(E65-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J65" s="5">
         <f>IF(AND(B65="",C65="",E65=""),"",SUM($G$5:G65))</f>
         <v/>
       </c>
+      <c r="K65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -2295,13 +2362,14 @@
         <v/>
       </c>
       <c r="I66" s="6">
-        <f>IF(AND(B66="",C66="",D66="",E66="",F66=""),"",IF(OR(B66="",C66="",E66=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E66)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H66&lt;&gt;0,F66=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G66&lt;&gt;0,F66=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F66&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F66)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C66)*($E$5:$E$504=E66)*(($D$5:$D$504=D66)*(D66&lt;&gt;"")+($B$5:$B$504=B66)*(B66&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B66="",C66="",D66="",E66="",F66=""),"",IF(OR(B66="",C66="",E66=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E66)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H66&lt;&gt;0,F66=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G66&lt;&gt;0,F66=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F66&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F66)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C66)*($E$5:$E$504=E66)*(($D$5:$D$504=D66)*(D66&lt;&gt;"")+($B$5:$B$504=B66)*(B66&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C66="Оплата",K66&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E66)&gt;0,ROUND(E66-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J66" s="5">
         <f>IF(AND(B66="",C66="",E66=""),"",SUM($G$5:G66))</f>
         <v/>
       </c>
+      <c r="K66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -2321,13 +2389,14 @@
         <v/>
       </c>
       <c r="I67" s="6">
-        <f>IF(AND(B67="",C67="",D67="",E67="",F67=""),"",IF(OR(B67="",C67="",E67=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E67)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H67&lt;&gt;0,F67=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G67&lt;&gt;0,F67=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F67&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F67)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C67)*($E$5:$E$504=E67)*(($D$5:$D$504=D67)*(D67&lt;&gt;"")+($B$5:$B$504=B67)*(B67&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B67="",C67="",D67="",E67="",F67=""),"",IF(OR(B67="",C67="",E67=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E67)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H67&lt;&gt;0,F67=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G67&lt;&gt;0,F67=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F67&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F67)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C67)*($E$5:$E$504=E67)*(($D$5:$D$504=D67)*(D67&lt;&gt;"")+($B$5:$B$504=B67)*(B67&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C67="Оплата",K67&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E67)&gt;0,ROUND(E67-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J67" s="5">
         <f>IF(AND(B67="",C67="",E67=""),"",SUM($G$5:G67))</f>
         <v/>
       </c>
+      <c r="K67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
@@ -2347,13 +2416,14 @@
         <v/>
       </c>
       <c r="I68" s="6">
-        <f>IF(AND(B68="",C68="",D68="",E68="",F68=""),"",IF(OR(B68="",C68="",E68=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E68)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H68&lt;&gt;0,F68=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G68&lt;&gt;0,F68=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F68&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F68)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C68)*($E$5:$E$504=E68)*(($D$5:$D$504=D68)*(D68&lt;&gt;"")+($B$5:$B$504=B68)*(B68&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B68="",C68="",D68="",E68="",F68=""),"",IF(OR(B68="",C68="",E68=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E68)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H68&lt;&gt;0,F68=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G68&lt;&gt;0,F68=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F68&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F68)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C68)*($E$5:$E$504=E68)*(($D$5:$D$504=D68)*(D68&lt;&gt;"")+($B$5:$B$504=B68)*(B68&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C68="Оплата",K68&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E68)&gt;0,ROUND(E68-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J68" s="5">
         <f>IF(AND(B68="",C68="",E68=""),"",SUM($G$5:G68))</f>
         <v/>
       </c>
+      <c r="K68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -2373,13 +2443,14 @@
         <v/>
       </c>
       <c r="I69" s="6">
-        <f>IF(AND(B69="",C69="",D69="",E69="",F69=""),"",IF(OR(B69="",C69="",E69=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E69)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H69&lt;&gt;0,F69=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G69&lt;&gt;0,F69=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F69&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F69)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C69)*($E$5:$E$504=E69)*(($D$5:$D$504=D69)*(D69&lt;&gt;"")+($B$5:$B$504=B69)*(B69&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B69="",C69="",D69="",E69="",F69=""),"",IF(OR(B69="",C69="",E69=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E69)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H69&lt;&gt;0,F69=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G69&lt;&gt;0,F69=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F69&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F69)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C69)*($E$5:$E$504=E69)*(($D$5:$D$504=D69)*(D69&lt;&gt;"")+($B$5:$B$504=B69)*(B69&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C69="Оплата",K69&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E69)&gt;0,ROUND(E69-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J69" s="5">
         <f>IF(AND(B69="",C69="",E69=""),"",SUM($G$5:G69))</f>
         <v/>
       </c>
+      <c r="K69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -2399,13 +2470,14 @@
         <v/>
       </c>
       <c r="I70" s="6">
-        <f>IF(AND(B70="",C70="",D70="",E70="",F70=""),"",IF(OR(B70="",C70="",E70=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E70)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H70&lt;&gt;0,F70=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G70&lt;&gt;0,F70=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F70&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F70)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C70)*($E$5:$E$504=E70)*(($D$5:$D$504=D70)*(D70&lt;&gt;"")+($B$5:$B$504=B70)*(B70&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B70="",C70="",D70="",E70="",F70=""),"",IF(OR(B70="",C70="",E70=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E70)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H70&lt;&gt;0,F70=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G70&lt;&gt;0,F70=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F70&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F70)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C70)*($E$5:$E$504=E70)*(($D$5:$D$504=D70)*(D70&lt;&gt;"")+($B$5:$B$504=B70)*(B70&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C70="Оплата",K70&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E70)&gt;0,ROUND(E70-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J70" s="5">
         <f>IF(AND(B70="",C70="",E70=""),"",SUM($G$5:G70))</f>
         <v/>
       </c>
+      <c r="K70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -2425,13 +2497,14 @@
         <v/>
       </c>
       <c r="I71" s="6">
-        <f>IF(AND(B71="",C71="",D71="",E71="",F71=""),"",IF(OR(B71="",C71="",E71=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E71)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H71&lt;&gt;0,F71=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G71&lt;&gt;0,F71=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F71&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F71)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C71)*($E$5:$E$504=E71)*(($D$5:$D$504=D71)*(D71&lt;&gt;"")+($B$5:$B$504=B71)*(B71&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B71="",C71="",D71="",E71="",F71=""),"",IF(OR(B71="",C71="",E71=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E71)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H71&lt;&gt;0,F71=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G71&lt;&gt;0,F71=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F71&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F71)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C71)*($E$5:$E$504=E71)*(($D$5:$D$504=D71)*(D71&lt;&gt;"")+($B$5:$B$504=B71)*(B71&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C71="Оплата",K71&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E71)&gt;0,ROUND(E71-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J71" s="5">
         <f>IF(AND(B71="",C71="",E71=""),"",SUM($G$5:G71))</f>
         <v/>
       </c>
+      <c r="K71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -2451,13 +2524,14 @@
         <v/>
       </c>
       <c r="I72" s="6">
-        <f>IF(AND(B72="",C72="",D72="",E72="",F72=""),"",IF(OR(B72="",C72="",E72=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E72)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H72&lt;&gt;0,F72=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G72&lt;&gt;0,F72=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F72&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F72)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C72)*($E$5:$E$504=E72)*(($D$5:$D$504=D72)*(D72&lt;&gt;"")+($B$5:$B$504=B72)*(B72&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B72="",C72="",D72="",E72="",F72=""),"",IF(OR(B72="",C72="",E72=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E72)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H72&lt;&gt;0,F72=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G72&lt;&gt;0,F72=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F72&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F72)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C72)*($E$5:$E$504=E72)*(($D$5:$D$504=D72)*(D72&lt;&gt;"")+($B$5:$B$504=B72)*(B72&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C72="Оплата",K72&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E72)&gt;0,ROUND(E72-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J72" s="5">
         <f>IF(AND(B72="",C72="",E72=""),"",SUM($G$5:G72))</f>
         <v/>
       </c>
+      <c r="K72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -2477,13 +2551,14 @@
         <v/>
       </c>
       <c r="I73" s="6">
-        <f>IF(AND(B73="",C73="",D73="",E73="",F73=""),"",IF(OR(B73="",C73="",E73=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E73)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H73&lt;&gt;0,F73=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G73&lt;&gt;0,F73=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F73&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F73)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C73)*($E$5:$E$504=E73)*(($D$5:$D$504=D73)*(D73&lt;&gt;"")+($B$5:$B$504=B73)*(B73&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B73="",C73="",D73="",E73="",F73=""),"",IF(OR(B73="",C73="",E73=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E73)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H73&lt;&gt;0,F73=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G73&lt;&gt;0,F73=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F73&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F73)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C73)*($E$5:$E$504=E73)*(($D$5:$D$504=D73)*(D73&lt;&gt;"")+($B$5:$B$504=B73)*(B73&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C73="Оплата",K73&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E73)&gt;0,ROUND(E73-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J73" s="5">
         <f>IF(AND(B73="",C73="",E73=""),"",SUM($G$5:G73))</f>
         <v/>
       </c>
+      <c r="K73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -2503,13 +2578,14 @@
         <v/>
       </c>
       <c r="I74" s="6">
-        <f>IF(AND(B74="",C74="",D74="",E74="",F74=""),"",IF(OR(B74="",C74="",E74=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E74)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H74&lt;&gt;0,F74=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G74&lt;&gt;0,F74=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F74&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F74)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C74)*($E$5:$E$504=E74)*(($D$5:$D$504=D74)*(D74&lt;&gt;"")+($B$5:$B$504=B74)*(B74&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B74="",C74="",D74="",E74="",F74=""),"",IF(OR(B74="",C74="",E74=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E74)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H74&lt;&gt;0,F74=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G74&lt;&gt;0,F74=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F74&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F74)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C74)*($E$5:$E$504=E74)*(($D$5:$D$504=D74)*(D74&lt;&gt;"")+($B$5:$B$504=B74)*(B74&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C74="Оплата",K74&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E74)&gt;0,ROUND(E74-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J74" s="5">
         <f>IF(AND(B74="",C74="",E74=""),"",SUM($G$5:G74))</f>
         <v/>
       </c>
+      <c r="K74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -2529,13 +2605,14 @@
         <v/>
       </c>
       <c r="I75" s="6">
-        <f>IF(AND(B75="",C75="",D75="",E75="",F75=""),"",IF(OR(B75="",C75="",E75=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E75)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H75&lt;&gt;0,F75=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G75&lt;&gt;0,F75=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F75&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F75)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C75)*($E$5:$E$504=E75)*(($D$5:$D$504=D75)*(D75&lt;&gt;"")+($B$5:$B$504=B75)*(B75&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B75="",C75="",D75="",E75="",F75=""),"",IF(OR(B75="",C75="",E75=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E75)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H75&lt;&gt;0,F75=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G75&lt;&gt;0,F75=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F75&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F75)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C75)*($E$5:$E$504=E75)*(($D$5:$D$504=D75)*(D75&lt;&gt;"")+($B$5:$B$504=B75)*(B75&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C75="Оплата",K75&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E75)&gt;0,ROUND(E75-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J75" s="5">
         <f>IF(AND(B75="",C75="",E75=""),"",SUM($G$5:G75))</f>
         <v/>
       </c>
+      <c r="K75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -2555,13 +2632,14 @@
         <v/>
       </c>
       <c r="I76" s="6">
-        <f>IF(AND(B76="",C76="",D76="",E76="",F76=""),"",IF(OR(B76="",C76="",E76=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E76)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H76&lt;&gt;0,F76=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G76&lt;&gt;0,F76=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F76&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F76)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C76)*($E$5:$E$504=E76)*(($D$5:$D$504=D76)*(D76&lt;&gt;"")+($B$5:$B$504=B76)*(B76&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B76="",C76="",D76="",E76="",F76=""),"",IF(OR(B76="",C76="",E76=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E76)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H76&lt;&gt;0,F76=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G76&lt;&gt;0,F76=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F76&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F76)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C76)*($E$5:$E$504=E76)*(($D$5:$D$504=D76)*(D76&lt;&gt;"")+($B$5:$B$504=B76)*(B76&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C76="Оплата",K76&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E76)&gt;0,ROUND(E76-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J76" s="5">
         <f>IF(AND(B76="",C76="",E76=""),"",SUM($G$5:G76))</f>
         <v/>
       </c>
+      <c r="K76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -2581,13 +2659,14 @@
         <v/>
       </c>
       <c r="I77" s="6">
-        <f>IF(AND(B77="",C77="",D77="",E77="",F77=""),"",IF(OR(B77="",C77="",E77=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E77)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H77&lt;&gt;0,F77=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G77&lt;&gt;0,F77=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F77&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F77)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C77)*($E$5:$E$504=E77)*(($D$5:$D$504=D77)*(D77&lt;&gt;"")+($B$5:$B$504=B77)*(B77&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B77="",C77="",D77="",E77="",F77=""),"",IF(OR(B77="",C77="",E77=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E77)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H77&lt;&gt;0,F77=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G77&lt;&gt;0,F77=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F77&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F77)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C77)*($E$5:$E$504=E77)*(($D$5:$D$504=D77)*(D77&lt;&gt;"")+($B$5:$B$504=B77)*(B77&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C77="Оплата",K77&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E77)&gt;0,ROUND(E77-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J77" s="5">
         <f>IF(AND(B77="",C77="",E77=""),"",SUM($G$5:G77))</f>
         <v/>
       </c>
+      <c r="K77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n">
@@ -2607,13 +2686,14 @@
         <v/>
       </c>
       <c r="I78" s="6">
-        <f>IF(AND(B78="",C78="",D78="",E78="",F78=""),"",IF(OR(B78="",C78="",E78=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E78)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H78&lt;&gt;0,F78=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G78&lt;&gt;0,F78=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F78&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F78)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C78)*($E$5:$E$504=E78)*(($D$5:$D$504=D78)*(D78&lt;&gt;"")+($B$5:$B$504=B78)*(B78&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B78="",C78="",D78="",E78="",F78=""),"",IF(OR(B78="",C78="",E78=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E78)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H78&lt;&gt;0,F78=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G78&lt;&gt;0,F78=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F78&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F78)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C78)*($E$5:$E$504=E78)*(($D$5:$D$504=D78)*(D78&lt;&gt;"")+($B$5:$B$504=B78)*(B78&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C78="Оплата",K78&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E78)&gt;0,ROUND(E78-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J78" s="5">
         <f>IF(AND(B78="",C78="",E78=""),"",SUM($G$5:G78))</f>
         <v/>
       </c>
+      <c r="K78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -2633,13 +2713,14 @@
         <v/>
       </c>
       <c r="I79" s="6">
-        <f>IF(AND(B79="",C79="",D79="",E79="",F79=""),"",IF(OR(B79="",C79="",E79=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E79)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H79&lt;&gt;0,F79=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G79&lt;&gt;0,F79=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F79&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F79)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C79)*($E$5:$E$504=E79)*(($D$5:$D$504=D79)*(D79&lt;&gt;"")+($B$5:$B$504=B79)*(B79&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B79="",C79="",D79="",E79="",F79=""),"",IF(OR(B79="",C79="",E79=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E79)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H79&lt;&gt;0,F79=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G79&lt;&gt;0,F79=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F79&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F79)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C79)*($E$5:$E$504=E79)*(($D$5:$D$504=D79)*(D79&lt;&gt;"")+($B$5:$B$504=B79)*(B79&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C79="Оплата",K79&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E79)&gt;0,ROUND(E79-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J79" s="5">
         <f>IF(AND(B79="",C79="",E79=""),"",SUM($G$5:G79))</f>
         <v/>
       </c>
+      <c r="K79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
@@ -2659,13 +2740,14 @@
         <v/>
       </c>
       <c r="I80" s="6">
-        <f>IF(AND(B80="",C80="",D80="",E80="",F80=""),"",IF(OR(B80="",C80="",E80=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E80)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H80&lt;&gt;0,F80=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G80&lt;&gt;0,F80=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F80&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F80)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C80)*($E$5:$E$504=E80)*(($D$5:$D$504=D80)*(D80&lt;&gt;"")+($B$5:$B$504=B80)*(B80&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B80="",C80="",D80="",E80="",F80=""),"",IF(OR(B80="",C80="",E80=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E80)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H80&lt;&gt;0,F80=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G80&lt;&gt;0,F80=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F80&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F80)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C80)*($E$5:$E$504=E80)*(($D$5:$D$504=D80)*(D80&lt;&gt;"")+($B$5:$B$504=B80)*(B80&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C80="Оплата",K80&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E80)&gt;0,ROUND(E80-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J80" s="5">
         <f>IF(AND(B80="",C80="",E80=""),"",SUM($G$5:G80))</f>
         <v/>
       </c>
+      <c r="K80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -2685,13 +2767,14 @@
         <v/>
       </c>
       <c r="I81" s="6">
-        <f>IF(AND(B81="",C81="",D81="",E81="",F81=""),"",IF(OR(B81="",C81="",E81=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E81)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H81&lt;&gt;0,F81=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G81&lt;&gt;0,F81=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F81&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F81)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C81)*($E$5:$E$504=E81)*(($D$5:$D$504=D81)*(D81&lt;&gt;"")+($B$5:$B$504=B81)*(B81&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B81="",C81="",D81="",E81="",F81=""),"",IF(OR(B81="",C81="",E81=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E81)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H81&lt;&gt;0,F81=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G81&lt;&gt;0,F81=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F81&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F81)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C81)*($E$5:$E$504=E81)*(($D$5:$D$504=D81)*(D81&lt;&gt;"")+($B$5:$B$504=B81)*(B81&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C81="Оплата",K81&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E81)&gt;0,ROUND(E81-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J81" s="5">
         <f>IF(AND(B81="",C81="",E81=""),"",SUM($G$5:G81))</f>
         <v/>
       </c>
+      <c r="K81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -2711,13 +2794,14 @@
         <v/>
       </c>
       <c r="I82" s="6">
-        <f>IF(AND(B82="",C82="",D82="",E82="",F82=""),"",IF(OR(B82="",C82="",E82=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E82)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H82&lt;&gt;0,F82=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G82&lt;&gt;0,F82=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F82&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F82)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C82)*($E$5:$E$504=E82)*(($D$5:$D$504=D82)*(D82&lt;&gt;"")+($B$5:$B$504=B82)*(B82&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B82="",C82="",D82="",E82="",F82=""),"",IF(OR(B82="",C82="",E82=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E82)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H82&lt;&gt;0,F82=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G82&lt;&gt;0,F82=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F82&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F82)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C82)*($E$5:$E$504=E82)*(($D$5:$D$504=D82)*(D82&lt;&gt;"")+($B$5:$B$504=B82)*(B82&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C82="Оплата",K82&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E82)&gt;0,ROUND(E82-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J82" s="5">
         <f>IF(AND(B82="",C82="",E82=""),"",SUM($G$5:G82))</f>
         <v/>
       </c>
+      <c r="K82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -2737,13 +2821,14 @@
         <v/>
       </c>
       <c r="I83" s="6">
-        <f>IF(AND(B83="",C83="",D83="",E83="",F83=""),"",IF(OR(B83="",C83="",E83=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E83)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H83&lt;&gt;0,F83=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G83&lt;&gt;0,F83=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F83&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F83)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C83)*($E$5:$E$504=E83)*(($D$5:$D$504=D83)*(D83&lt;&gt;"")+($B$5:$B$504=B83)*(B83&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B83="",C83="",D83="",E83="",F83=""),"",IF(OR(B83="",C83="",E83=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E83)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H83&lt;&gt;0,F83=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G83&lt;&gt;0,F83=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F83&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F83)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C83)*($E$5:$E$504=E83)*(($D$5:$D$504=D83)*(D83&lt;&gt;"")+($B$5:$B$504=B83)*(B83&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C83="Оплата",K83&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E83)&gt;0,ROUND(E83-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J83" s="5">
         <f>IF(AND(B83="",C83="",E83=""),"",SUM($G$5:G83))</f>
         <v/>
       </c>
+      <c r="K83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -2763,13 +2848,14 @@
         <v/>
       </c>
       <c r="I84" s="6">
-        <f>IF(AND(B84="",C84="",D84="",E84="",F84=""),"",IF(OR(B84="",C84="",E84=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E84)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H84&lt;&gt;0,F84=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G84&lt;&gt;0,F84=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F84&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F84)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C84)*($E$5:$E$504=E84)*(($D$5:$D$504=D84)*(D84&lt;&gt;"")+($B$5:$B$504=B84)*(B84&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B84="",C84="",D84="",E84="",F84=""),"",IF(OR(B84="",C84="",E84=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E84)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H84&lt;&gt;0,F84=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G84&lt;&gt;0,F84=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F84&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F84)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C84)*($E$5:$E$504=E84)*(($D$5:$D$504=D84)*(D84&lt;&gt;"")+($B$5:$B$504=B84)*(B84&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C84="Оплата",K84&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E84)&gt;0,ROUND(E84-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J84" s="5">
         <f>IF(AND(B84="",C84="",E84=""),"",SUM($G$5:G84))</f>
         <v/>
       </c>
+      <c r="K84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -2789,13 +2875,14 @@
         <v/>
       </c>
       <c r="I85" s="6">
-        <f>IF(AND(B85="",C85="",D85="",E85="",F85=""),"",IF(OR(B85="",C85="",E85=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E85)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H85&lt;&gt;0,F85=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G85&lt;&gt;0,F85=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F85&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F85)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C85)*($E$5:$E$504=E85)*(($D$5:$D$504=D85)*(D85&lt;&gt;"")+($B$5:$B$504=B85)*(B85&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B85="",C85="",D85="",E85="",F85=""),"",IF(OR(B85="",C85="",E85=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E85)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H85&lt;&gt;0,F85=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G85&lt;&gt;0,F85=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F85&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F85)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C85)*($E$5:$E$504=E85)*(($D$5:$D$504=D85)*(D85&lt;&gt;"")+($B$5:$B$504=B85)*(B85&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C85="Оплата",K85&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E85)&gt;0,ROUND(E85-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J85" s="5">
         <f>IF(AND(B85="",C85="",E85=""),"",SUM($G$5:G85))</f>
         <v/>
       </c>
+      <c r="K85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -2815,13 +2902,14 @@
         <v/>
       </c>
       <c r="I86" s="6">
-        <f>IF(AND(B86="",C86="",D86="",E86="",F86=""),"",IF(OR(B86="",C86="",E86=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E86)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H86&lt;&gt;0,F86=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G86&lt;&gt;0,F86=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F86&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F86)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C86)*($E$5:$E$504=E86)*(($D$5:$D$504=D86)*(D86&lt;&gt;"")+($B$5:$B$504=B86)*(B86&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B86="",C86="",D86="",E86="",F86=""),"",IF(OR(B86="",C86="",E86=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E86)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H86&lt;&gt;0,F86=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G86&lt;&gt;0,F86=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F86&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F86)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C86)*($E$5:$E$504=E86)*(($D$5:$D$504=D86)*(D86&lt;&gt;"")+($B$5:$B$504=B86)*(B86&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C86="Оплата",K86&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E86)&gt;0,ROUND(E86-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J86" s="5">
         <f>IF(AND(B86="",C86="",E86=""),"",SUM($G$5:G86))</f>
         <v/>
       </c>
+      <c r="K86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -2841,13 +2929,14 @@
         <v/>
       </c>
       <c r="I87" s="6">
-        <f>IF(AND(B87="",C87="",D87="",E87="",F87=""),"",IF(OR(B87="",C87="",E87=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E87)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H87&lt;&gt;0,F87=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G87&lt;&gt;0,F87=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F87&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F87)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C87)*($E$5:$E$504=E87)*(($D$5:$D$504=D87)*(D87&lt;&gt;"")+($B$5:$B$504=B87)*(B87&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B87="",C87="",D87="",E87="",F87=""),"",IF(OR(B87="",C87="",E87=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E87)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H87&lt;&gt;0,F87=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G87&lt;&gt;0,F87=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F87&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F87)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C87)*($E$5:$E$504=E87)*(($D$5:$D$504=D87)*(D87&lt;&gt;"")+($B$5:$B$504=B87)*(B87&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C87="Оплата",K87&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E87)&gt;0,ROUND(E87-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J87" s="5">
         <f>IF(AND(B87="",C87="",E87=""),"",SUM($G$5:G87))</f>
         <v/>
       </c>
+      <c r="K87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
@@ -2867,13 +2956,14 @@
         <v/>
       </c>
       <c r="I88" s="6">
-        <f>IF(AND(B88="",C88="",D88="",E88="",F88=""),"",IF(OR(B88="",C88="",E88=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E88)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H88&lt;&gt;0,F88=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G88&lt;&gt;0,F88=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F88&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F88)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C88)*($E$5:$E$504=E88)*(($D$5:$D$504=D88)*(D88&lt;&gt;"")+($B$5:$B$504=B88)*(B88&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B88="",C88="",D88="",E88="",F88=""),"",IF(OR(B88="",C88="",E88=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E88)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H88&lt;&gt;0,F88=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G88&lt;&gt;0,F88=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F88&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F88)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C88)*($E$5:$E$504=E88)*(($D$5:$D$504=D88)*(D88&lt;&gt;"")+($B$5:$B$504=B88)*(B88&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C88="Оплата",K88&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E88)&gt;0,ROUND(E88-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J88" s="5">
         <f>IF(AND(B88="",C88="",E88=""),"",SUM($G$5:G88))</f>
         <v/>
       </c>
+      <c r="K88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -2893,13 +2983,14 @@
         <v/>
       </c>
       <c r="I89" s="6">
-        <f>IF(AND(B89="",C89="",D89="",E89="",F89=""),"",IF(OR(B89="",C89="",E89=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E89)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H89&lt;&gt;0,F89=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G89&lt;&gt;0,F89=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F89&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F89)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C89)*($E$5:$E$504=E89)*(($D$5:$D$504=D89)*(D89&lt;&gt;"")+($B$5:$B$504=B89)*(B89&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B89="",C89="",D89="",E89="",F89=""),"",IF(OR(B89="",C89="",E89=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E89)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H89&lt;&gt;0,F89=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G89&lt;&gt;0,F89=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F89&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F89)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C89)*($E$5:$E$504=E89)*(($D$5:$D$504=D89)*(D89&lt;&gt;"")+($B$5:$B$504=B89)*(B89&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C89="Оплата",K89&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E89)&gt;0,ROUND(E89-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J89" s="5">
         <f>IF(AND(B89="",C89="",E89=""),"",SUM($G$5:G89))</f>
         <v/>
       </c>
+      <c r="K89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
@@ -2919,13 +3010,14 @@
         <v/>
       </c>
       <c r="I90" s="6">
-        <f>IF(AND(B90="",C90="",D90="",E90="",F90=""),"",IF(OR(B90="",C90="",E90=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E90)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H90&lt;&gt;0,F90=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G90&lt;&gt;0,F90=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F90&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F90)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C90)*($E$5:$E$504=E90)*(($D$5:$D$504=D90)*(D90&lt;&gt;"")+($B$5:$B$504=B90)*(B90&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B90="",C90="",D90="",E90="",F90=""),"",IF(OR(B90="",C90="",E90=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E90)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H90&lt;&gt;0,F90=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G90&lt;&gt;0,F90=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F90&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F90)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C90)*($E$5:$E$504=E90)*(($D$5:$D$504=D90)*(D90&lt;&gt;"")+($B$5:$B$504=B90)*(B90&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C90="Оплата",K90&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E90)&gt;0,ROUND(E90-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J90" s="5">
         <f>IF(AND(B90="",C90="",E90=""),"",SUM($G$5:G90))</f>
         <v/>
       </c>
+      <c r="K90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -2945,13 +3037,14 @@
         <v/>
       </c>
       <c r="I91" s="6">
-        <f>IF(AND(B91="",C91="",D91="",E91="",F91=""),"",IF(OR(B91="",C91="",E91=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E91)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H91&lt;&gt;0,F91=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G91&lt;&gt;0,F91=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F91&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F91)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C91)*($E$5:$E$504=E91)*(($D$5:$D$504=D91)*(D91&lt;&gt;"")+($B$5:$B$504=B91)*(B91&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B91="",C91="",D91="",E91="",F91=""),"",IF(OR(B91="",C91="",E91=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E91)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H91&lt;&gt;0,F91=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G91&lt;&gt;0,F91=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F91&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F91)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C91)*($E$5:$E$504=E91)*(($D$5:$D$504=D91)*(D91&lt;&gt;"")+($B$5:$B$504=B91)*(B91&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C91="Оплата",K91&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E91)&gt;0,ROUND(E91-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J91" s="5">
         <f>IF(AND(B91="",C91="",E91=""),"",SUM($G$5:G91))</f>
         <v/>
       </c>
+      <c r="K91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -2971,13 +3064,14 @@
         <v/>
       </c>
       <c r="I92" s="6">
-        <f>IF(AND(B92="",C92="",D92="",E92="",F92=""),"",IF(OR(B92="",C92="",E92=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E92)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H92&lt;&gt;0,F92=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G92&lt;&gt;0,F92=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F92&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F92)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C92)*($E$5:$E$504=E92)*(($D$5:$D$504=D92)*(D92&lt;&gt;"")+($B$5:$B$504=B92)*(B92&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B92="",C92="",D92="",E92="",F92=""),"",IF(OR(B92="",C92="",E92=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E92)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H92&lt;&gt;0,F92=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G92&lt;&gt;0,F92=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F92&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F92)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C92)*($E$5:$E$504=E92)*(($D$5:$D$504=D92)*(D92&lt;&gt;"")+($B$5:$B$504=B92)*(B92&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C92="Оплата",K92&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E92)&gt;0,ROUND(E92-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J92" s="5">
         <f>IF(AND(B92="",C92="",E92=""),"",SUM($G$5:G92))</f>
         <v/>
       </c>
+      <c r="K92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -2997,13 +3091,14 @@
         <v/>
       </c>
       <c r="I93" s="6">
-        <f>IF(AND(B93="",C93="",D93="",E93="",F93=""),"",IF(OR(B93="",C93="",E93=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E93)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H93&lt;&gt;0,F93=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G93&lt;&gt;0,F93=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F93&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F93)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C93)*($E$5:$E$504=E93)*(($D$5:$D$504=D93)*(D93&lt;&gt;"")+($B$5:$B$504=B93)*(B93&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B93="",C93="",D93="",E93="",F93=""),"",IF(OR(B93="",C93="",E93=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E93)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H93&lt;&gt;0,F93=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G93&lt;&gt;0,F93=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F93&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F93)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C93)*($E$5:$E$504=E93)*(($D$5:$D$504=D93)*(D93&lt;&gt;"")+($B$5:$B$504=B93)*(B93&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C93="Оплата",K93&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E93)&gt;0,ROUND(E93-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J93" s="5">
         <f>IF(AND(B93="",C93="",E93=""),"",SUM($G$5:G93))</f>
         <v/>
       </c>
+      <c r="K93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -3023,13 +3118,14 @@
         <v/>
       </c>
       <c r="I94" s="6">
-        <f>IF(AND(B94="",C94="",D94="",E94="",F94=""),"",IF(OR(B94="",C94="",E94=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E94)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H94&lt;&gt;0,F94=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G94&lt;&gt;0,F94=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F94&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F94)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C94)*($E$5:$E$504=E94)*(($D$5:$D$504=D94)*(D94&lt;&gt;"")+($B$5:$B$504=B94)*(B94&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B94="",C94="",D94="",E94="",F94=""),"",IF(OR(B94="",C94="",E94=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E94)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H94&lt;&gt;0,F94=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G94&lt;&gt;0,F94=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F94&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F94)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C94)*($E$5:$E$504=E94)*(($D$5:$D$504=D94)*(D94&lt;&gt;"")+($B$5:$B$504=B94)*(B94&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C94="Оплата",K94&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E94)&gt;0,ROUND(E94-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J94" s="5">
         <f>IF(AND(B94="",C94="",E94=""),"",SUM($G$5:G94))</f>
         <v/>
       </c>
+      <c r="K94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -3049,13 +3145,14 @@
         <v/>
       </c>
       <c r="I95" s="6">
-        <f>IF(AND(B95="",C95="",D95="",E95="",F95=""),"",IF(OR(B95="",C95="",E95=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E95)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H95&lt;&gt;0,F95=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G95&lt;&gt;0,F95=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F95&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F95)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C95)*($E$5:$E$504=E95)*(($D$5:$D$504=D95)*(D95&lt;&gt;"")+($B$5:$B$504=B95)*(B95&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B95="",C95="",D95="",E95="",F95=""),"",IF(OR(B95="",C95="",E95=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E95)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H95&lt;&gt;0,F95=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G95&lt;&gt;0,F95=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F95&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F95)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C95)*($E$5:$E$504=E95)*(($D$5:$D$504=D95)*(D95&lt;&gt;"")+($B$5:$B$504=B95)*(B95&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C95="Оплата",K95&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E95)&gt;0,ROUND(E95-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J95" s="5">
         <f>IF(AND(B95="",C95="",E95=""),"",SUM($G$5:G95))</f>
         <v/>
       </c>
+      <c r="K95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -3075,13 +3172,14 @@
         <v/>
       </c>
       <c r="I96" s="6">
-        <f>IF(AND(B96="",C96="",D96="",E96="",F96=""),"",IF(OR(B96="",C96="",E96=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E96)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H96&lt;&gt;0,F96=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G96&lt;&gt;0,F96=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F96&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F96)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C96)*($E$5:$E$504=E96)*(($D$5:$D$504=D96)*(D96&lt;&gt;"")+($B$5:$B$504=B96)*(B96&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B96="",C96="",D96="",E96="",F96=""),"",IF(OR(B96="",C96="",E96=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E96)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H96&lt;&gt;0,F96=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G96&lt;&gt;0,F96=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F96&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F96)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C96)*($E$5:$E$504=E96)*(($D$5:$D$504=D96)*(D96&lt;&gt;"")+($B$5:$B$504=B96)*(B96&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C96="Оплата",K96&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E96)&gt;0,ROUND(E96-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J96" s="5">
         <f>IF(AND(B96="",C96="",E96=""),"",SUM($G$5:G96))</f>
         <v/>
       </c>
+      <c r="K96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -3101,13 +3199,14 @@
         <v/>
       </c>
       <c r="I97" s="6">
-        <f>IF(AND(B97="",C97="",D97="",E97="",F97=""),"",IF(OR(B97="",C97="",E97=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E97)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H97&lt;&gt;0,F97=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G97&lt;&gt;0,F97=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F97&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F97)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C97)*($E$5:$E$504=E97)*(($D$5:$D$504=D97)*(D97&lt;&gt;"")+($B$5:$B$504=B97)*(B97&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B97="",C97="",D97="",E97="",F97=""),"",IF(OR(B97="",C97="",E97=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E97)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H97&lt;&gt;0,F97=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G97&lt;&gt;0,F97=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F97&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F97)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C97)*($E$5:$E$504=E97)*(($D$5:$D$504=D97)*(D97&lt;&gt;"")+($B$5:$B$504=B97)*(B97&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C97="Оплата",K97&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E97)&gt;0,ROUND(E97-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J97" s="5">
         <f>IF(AND(B97="",C97="",E97=""),"",SUM($G$5:G97))</f>
         <v/>
       </c>
+      <c r="K97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -3127,13 +3226,14 @@
         <v/>
       </c>
       <c r="I98" s="6">
-        <f>IF(AND(B98="",C98="",D98="",E98="",F98=""),"",IF(OR(B98="",C98="",E98=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E98)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H98&lt;&gt;0,F98=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G98&lt;&gt;0,F98=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F98&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F98)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C98)*($E$5:$E$504=E98)*(($D$5:$D$504=D98)*(D98&lt;&gt;"")+($B$5:$B$504=B98)*(B98&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B98="",C98="",D98="",E98="",F98=""),"",IF(OR(B98="",C98="",E98=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E98)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H98&lt;&gt;0,F98=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G98&lt;&gt;0,F98=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F98&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F98)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C98)*($E$5:$E$504=E98)*(($D$5:$D$504=D98)*(D98&lt;&gt;"")+($B$5:$B$504=B98)*(B98&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C98="Оплата",K98&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E98)&gt;0,ROUND(E98-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J98" s="5">
         <f>IF(AND(B98="",C98="",E98=""),"",SUM($G$5:G98))</f>
         <v/>
       </c>
+      <c r="K98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -3153,13 +3253,14 @@
         <v/>
       </c>
       <c r="I99" s="6">
-        <f>IF(AND(B99="",C99="",D99="",E99="",F99=""),"",IF(OR(B99="",C99="",E99=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E99)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H99&lt;&gt;0,F99=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G99&lt;&gt;0,F99=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F99&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F99)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C99)*($E$5:$E$504=E99)*(($D$5:$D$504=D99)*(D99&lt;&gt;"")+($B$5:$B$504=B99)*(B99&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B99="",C99="",D99="",E99="",F99=""),"",IF(OR(B99="",C99="",E99=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E99)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H99&lt;&gt;0,F99=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G99&lt;&gt;0,F99=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F99&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F99)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C99)*($E$5:$E$504=E99)*(($D$5:$D$504=D99)*(D99&lt;&gt;"")+($B$5:$B$504=B99)*(B99&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C99="Оплата",K99&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E99)&gt;0,ROUND(E99-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J99" s="5">
         <f>IF(AND(B99="",C99="",E99=""),"",SUM($G$5:G99))</f>
         <v/>
       </c>
+      <c r="K99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
@@ -3179,13 +3280,14 @@
         <v/>
       </c>
       <c r="I100" s="6">
-        <f>IF(AND(B100="",C100="",D100="",E100="",F100=""),"",IF(OR(B100="",C100="",E100=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E100)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H100&lt;&gt;0,F100=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G100&lt;&gt;0,F100=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F100&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F100)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C100)*($E$5:$E$504=E100)*(($D$5:$D$504=D100)*(D100&lt;&gt;"")+($B$5:$B$504=B100)*(B100&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B100="",C100="",D100="",E100="",F100=""),"",IF(OR(B100="",C100="",E100=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E100)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H100&lt;&gt;0,F100=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G100&lt;&gt;0,F100=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F100&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F100)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C100)*($E$5:$E$504=E100)*(($D$5:$D$504=D100)*(D100&lt;&gt;"")+($B$5:$B$504=B100)*(B100&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C100="Оплата",K100&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E100)&gt;0,ROUND(E100-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J100" s="5">
         <f>IF(AND(B100="",C100="",E100=""),"",SUM($G$5:G100))</f>
         <v/>
       </c>
+      <c r="K100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -3205,13 +3307,14 @@
         <v/>
       </c>
       <c r="I101" s="6">
-        <f>IF(AND(B101="",C101="",D101="",E101="",F101=""),"",IF(OR(B101="",C101="",E101=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E101)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H101&lt;&gt;0,F101=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G101&lt;&gt;0,F101=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F101&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F101)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C101)*($E$5:$E$504=E101)*(($D$5:$D$504=D101)*(D101&lt;&gt;"")+($B$5:$B$504=B101)*(B101&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B101="",C101="",D101="",E101="",F101=""),"",IF(OR(B101="",C101="",E101=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E101)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H101&lt;&gt;0,F101=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G101&lt;&gt;0,F101=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F101&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F101)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C101)*($E$5:$E$504=E101)*(($D$5:$D$504=D101)*(D101&lt;&gt;"")+($B$5:$B$504=B101)*(B101&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C101="Оплата",K101&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E101)&gt;0,ROUND(E101-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J101" s="5">
         <f>IF(AND(B101="",C101="",E101=""),"",SUM($G$5:G101))</f>
         <v/>
       </c>
+      <c r="K101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
@@ -3231,13 +3334,14 @@
         <v/>
       </c>
       <c r="I102" s="6">
-        <f>IF(AND(B102="",C102="",D102="",E102="",F102=""),"",IF(OR(B102="",C102="",E102=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E102)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H102&lt;&gt;0,F102=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G102&lt;&gt;0,F102=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F102&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F102)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C102)*($E$5:$E$504=E102)*(($D$5:$D$504=D102)*(D102&lt;&gt;"")+($B$5:$B$504=B102)*(B102&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B102="",C102="",D102="",E102="",F102=""),"",IF(OR(B102="",C102="",E102=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E102)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H102&lt;&gt;0,F102=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G102&lt;&gt;0,F102=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F102&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F102)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C102)*($E$5:$E$504=E102)*(($D$5:$D$504=D102)*(D102&lt;&gt;"")+($B$5:$B$504=B102)*(B102&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C102="Оплата",K102&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E102)&gt;0,ROUND(E102-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J102" s="5">
         <f>IF(AND(B102="",C102="",E102=""),"",SUM($G$5:G102))</f>
         <v/>
       </c>
+      <c r="K102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -3257,13 +3361,14 @@
         <v/>
       </c>
       <c r="I103" s="6">
-        <f>IF(AND(B103="",C103="",D103="",E103="",F103=""),"",IF(OR(B103="",C103="",E103=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E103)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H103&lt;&gt;0,F103=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G103&lt;&gt;0,F103=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F103&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F103)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C103)*($E$5:$E$504=E103)*(($D$5:$D$504=D103)*(D103&lt;&gt;"")+($B$5:$B$504=B103)*(B103&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B103="",C103="",D103="",E103="",F103=""),"",IF(OR(B103="",C103="",E103=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E103)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H103&lt;&gt;0,F103=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G103&lt;&gt;0,F103=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F103&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F103)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C103)*($E$5:$E$504=E103)*(($D$5:$D$504=D103)*(D103&lt;&gt;"")+($B$5:$B$504=B103)*(B103&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C103="Оплата",K103&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E103)&gt;0,ROUND(E103-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J103" s="5">
         <f>IF(AND(B103="",C103="",E103=""),"",SUM($G$5:G103))</f>
         <v/>
       </c>
+      <c r="K103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
@@ -3283,13 +3388,14 @@
         <v/>
       </c>
       <c r="I104" s="6">
-        <f>IF(AND(B104="",C104="",D104="",E104="",F104=""),"",IF(OR(B104="",C104="",E104=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E104)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H104&lt;&gt;0,F104=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G104&lt;&gt;0,F104=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F104&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F104)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C104)*($E$5:$E$504=E104)*(($D$5:$D$504=D104)*(D104&lt;&gt;"")+($B$5:$B$504=B104)*(B104&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B104="",C104="",D104="",E104="",F104=""),"",IF(OR(B104="",C104="",E104=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E104)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H104&lt;&gt;0,F104=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G104&lt;&gt;0,F104=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F104&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F104)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C104)*($E$5:$E$504=E104)*(($D$5:$D$504=D104)*(D104&lt;&gt;"")+($B$5:$B$504=B104)*(B104&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C104="Оплата",K104&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E104)&gt;0,ROUND(E104-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J104" s="5">
         <f>IF(AND(B104="",C104="",E104=""),"",SUM($G$5:G104))</f>
         <v/>
       </c>
+      <c r="K104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -3309,13 +3415,14 @@
         <v/>
       </c>
       <c r="I105" s="6">
-        <f>IF(AND(B105="",C105="",D105="",E105="",F105=""),"",IF(OR(B105="",C105="",E105=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E105)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H105&lt;&gt;0,F105=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G105&lt;&gt;0,F105=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F105&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F105)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C105)*($E$5:$E$504=E105)*(($D$5:$D$504=D105)*(D105&lt;&gt;"")+($B$5:$B$504=B105)*(B105&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B105="",C105="",D105="",E105="",F105=""),"",IF(OR(B105="",C105="",E105=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E105)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H105&lt;&gt;0,F105=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G105&lt;&gt;0,F105=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F105&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F105)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C105)*($E$5:$E$504=E105)*(($D$5:$D$504=D105)*(D105&lt;&gt;"")+($B$5:$B$504=B105)*(B105&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C105="Оплата",K105&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E105)&gt;0,ROUND(E105-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J105" s="5">
         <f>IF(AND(B105="",C105="",E105=""),"",SUM($G$5:G105))</f>
         <v/>
       </c>
+      <c r="K105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n">
@@ -3335,13 +3442,14 @@
         <v/>
       </c>
       <c r="I106" s="6">
-        <f>IF(AND(B106="",C106="",D106="",E106="",F106=""),"",IF(OR(B106="",C106="",E106=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E106)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H106&lt;&gt;0,F106=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G106&lt;&gt;0,F106=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F106&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F106)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C106)*($E$5:$E$504=E106)*(($D$5:$D$504=D106)*(D106&lt;&gt;"")+($B$5:$B$504=B106)*(B106&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B106="",C106="",D106="",E106="",F106=""),"",IF(OR(B106="",C106="",E106=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E106)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H106&lt;&gt;0,F106=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G106&lt;&gt;0,F106=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F106&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F106)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C106)*($E$5:$E$504=E106)*(($D$5:$D$504=D106)*(D106&lt;&gt;"")+($B$5:$B$504=B106)*(B106&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C106="Оплата",K106&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E106)&gt;0,ROUND(E106-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J106" s="5">
         <f>IF(AND(B106="",C106="",E106=""),"",SUM($G$5:G106))</f>
         <v/>
       </c>
+      <c r="K106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -3361,13 +3469,14 @@
         <v/>
       </c>
       <c r="I107" s="6">
-        <f>IF(AND(B107="",C107="",D107="",E107="",F107=""),"",IF(OR(B107="",C107="",E107=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E107)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H107&lt;&gt;0,F107=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G107&lt;&gt;0,F107=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F107&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F107)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C107)*($E$5:$E$504=E107)*(($D$5:$D$504=D107)*(D107&lt;&gt;"")+($B$5:$B$504=B107)*(B107&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B107="",C107="",D107="",E107="",F107=""),"",IF(OR(B107="",C107="",E107=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E107)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H107&lt;&gt;0,F107=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G107&lt;&gt;0,F107=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F107&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F107)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C107)*($E$5:$E$504=E107)*(($D$5:$D$504=D107)*(D107&lt;&gt;"")+($B$5:$B$504=B107)*(B107&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C107="Оплата",K107&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E107)&gt;0,ROUND(E107-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J107" s="5">
         <f>IF(AND(B107="",C107="",E107=""),"",SUM($G$5:G107))</f>
         <v/>
       </c>
+      <c r="K107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
@@ -3387,13 +3496,14 @@
         <v/>
       </c>
       <c r="I108" s="6">
-        <f>IF(AND(B108="",C108="",D108="",E108="",F108=""),"",IF(OR(B108="",C108="",E108=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E108)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H108&lt;&gt;0,F108=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G108&lt;&gt;0,F108=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F108&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F108)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C108)*($E$5:$E$504=E108)*(($D$5:$D$504=D108)*(D108&lt;&gt;"")+($B$5:$B$504=B108)*(B108&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B108="",C108="",D108="",E108="",F108=""),"",IF(OR(B108="",C108="",E108=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E108)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H108&lt;&gt;0,F108=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G108&lt;&gt;0,F108=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F108&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F108)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C108)*($E$5:$E$504=E108)*(($D$5:$D$504=D108)*(D108&lt;&gt;"")+($B$5:$B$504=B108)*(B108&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C108="Оплата",K108&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E108)&gt;0,ROUND(E108-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J108" s="5">
         <f>IF(AND(B108="",C108="",E108=""),"",SUM($G$5:G108))</f>
         <v/>
       </c>
+      <c r="K108" s="8" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -3413,13 +3523,14 @@
         <v/>
       </c>
       <c r="I109" s="6">
-        <f>IF(AND(B109="",C109="",D109="",E109="",F109=""),"",IF(OR(B109="",C109="",E109=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E109)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H109&lt;&gt;0,F109=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G109&lt;&gt;0,F109=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F109&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F109)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C109)*($E$5:$E$504=E109)*(($D$5:$D$504=D109)*(D109&lt;&gt;"")+($B$5:$B$504=B109)*(B109&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B109="",C109="",D109="",E109="",F109=""),"",IF(OR(B109="",C109="",E109=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E109)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H109&lt;&gt;0,F109=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G109&lt;&gt;0,F109=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F109&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F109)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C109)*($E$5:$E$504=E109)*(($D$5:$D$504=D109)*(D109&lt;&gt;"")+($B$5:$B$504=B109)*(B109&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C109="Оплата",K109&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E109)&gt;0,ROUND(E109-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J109" s="5">
         <f>IF(AND(B109="",C109="",E109=""),"",SUM($G$5:G109))</f>
         <v/>
       </c>
+      <c r="K109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
@@ -3439,13 +3550,14 @@
         <v/>
       </c>
       <c r="I110" s="6">
-        <f>IF(AND(B110="",C110="",D110="",E110="",F110=""),"",IF(OR(B110="",C110="",E110=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E110)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H110&lt;&gt;0,F110=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G110&lt;&gt;0,F110=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F110&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F110)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C110)*($E$5:$E$504=E110)*(($D$5:$D$504=D110)*(D110&lt;&gt;"")+($B$5:$B$504=B110)*(B110&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B110="",C110="",D110="",E110="",F110=""),"",IF(OR(B110="",C110="",E110=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E110)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H110&lt;&gt;0,F110=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G110&lt;&gt;0,F110=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F110&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F110)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C110)*($E$5:$E$504=E110)*(($D$5:$D$504=D110)*(D110&lt;&gt;"")+($B$5:$B$504=B110)*(B110&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C110="Оплата",K110&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E110)&gt;0,ROUND(E110-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J110" s="5">
         <f>IF(AND(B110="",C110="",E110=""),"",SUM($G$5:G110))</f>
         <v/>
       </c>
+      <c r="K110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -3465,13 +3577,14 @@
         <v/>
       </c>
       <c r="I111" s="6">
-        <f>IF(AND(B111="",C111="",D111="",E111="",F111=""),"",IF(OR(B111="",C111="",E111=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E111)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H111&lt;&gt;0,F111=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G111&lt;&gt;0,F111=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F111&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F111)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C111)*($E$5:$E$504=E111)*(($D$5:$D$504=D111)*(D111&lt;&gt;"")+($B$5:$B$504=B111)*(B111&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B111="",C111="",D111="",E111="",F111=""),"",IF(OR(B111="",C111="",E111=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E111)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H111&lt;&gt;0,F111=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G111&lt;&gt;0,F111=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F111&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F111)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C111)*($E$5:$E$504=E111)*(($D$5:$D$504=D111)*(D111&lt;&gt;"")+($B$5:$B$504=B111)*(B111&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C111="Оплата",K111&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E111)&gt;0,ROUND(E111-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J111" s="5">
         <f>IF(AND(B111="",C111="",E111=""),"",SUM($G$5:G111))</f>
         <v/>
       </c>
+      <c r="K111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
@@ -3491,13 +3604,14 @@
         <v/>
       </c>
       <c r="I112" s="6">
-        <f>IF(AND(B112="",C112="",D112="",E112="",F112=""),"",IF(OR(B112="",C112="",E112=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E112)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H112&lt;&gt;0,F112=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G112&lt;&gt;0,F112=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F112&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F112)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C112)*($E$5:$E$504=E112)*(($D$5:$D$504=D112)*(D112&lt;&gt;"")+($B$5:$B$504=B112)*(B112&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B112="",C112="",D112="",E112="",F112=""),"",IF(OR(B112="",C112="",E112=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E112)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H112&lt;&gt;0,F112=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G112&lt;&gt;0,F112=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F112&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F112)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C112)*($E$5:$E$504=E112)*(($D$5:$D$504=D112)*(D112&lt;&gt;"")+($B$5:$B$504=B112)*(B112&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C112="Оплата",K112&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E112)&gt;0,ROUND(E112-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J112" s="5">
         <f>IF(AND(B112="",C112="",E112=""),"",SUM($G$5:G112))</f>
         <v/>
       </c>
+      <c r="K112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -3517,13 +3631,14 @@
         <v/>
       </c>
       <c r="I113" s="6">
-        <f>IF(AND(B113="",C113="",D113="",E113="",F113=""),"",IF(OR(B113="",C113="",E113=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E113)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H113&lt;&gt;0,F113=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G113&lt;&gt;0,F113=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F113&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F113)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C113)*($E$5:$E$504=E113)*(($D$5:$D$504=D113)*(D113&lt;&gt;"")+($B$5:$B$504=B113)*(B113&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B113="",C113="",D113="",E113="",F113=""),"",IF(OR(B113="",C113="",E113=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E113)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H113&lt;&gt;0,F113=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G113&lt;&gt;0,F113=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F113&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F113)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C113)*($E$5:$E$504=E113)*(($D$5:$D$504=D113)*(D113&lt;&gt;"")+($B$5:$B$504=B113)*(B113&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C113="Оплата",K113&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E113)&gt;0,ROUND(E113-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J113" s="5">
         <f>IF(AND(B113="",C113="",E113=""),"",SUM($G$5:G113))</f>
         <v/>
       </c>
+      <c r="K113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
@@ -3543,13 +3658,14 @@
         <v/>
       </c>
       <c r="I114" s="6">
-        <f>IF(AND(B114="",C114="",D114="",E114="",F114=""),"",IF(OR(B114="",C114="",E114=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E114)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H114&lt;&gt;0,F114=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G114&lt;&gt;0,F114=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F114&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F114)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C114)*($E$5:$E$504=E114)*(($D$5:$D$504=D114)*(D114&lt;&gt;"")+($B$5:$B$504=B114)*(B114&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B114="",C114="",D114="",E114="",F114=""),"",IF(OR(B114="",C114="",E114=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E114)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H114&lt;&gt;0,F114=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G114&lt;&gt;0,F114=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F114&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F114)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C114)*($E$5:$E$504=E114)*(($D$5:$D$504=D114)*(D114&lt;&gt;"")+($B$5:$B$504=B114)*(B114&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C114="Оплата",K114&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E114)&gt;0,ROUND(E114-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J114" s="5">
         <f>IF(AND(B114="",C114="",E114=""),"",SUM($G$5:G114))</f>
         <v/>
       </c>
+      <c r="K114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -3569,13 +3685,14 @@
         <v/>
       </c>
       <c r="I115" s="6">
-        <f>IF(AND(B115="",C115="",D115="",E115="",F115=""),"",IF(OR(B115="",C115="",E115=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E115)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H115&lt;&gt;0,F115=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G115&lt;&gt;0,F115=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F115&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F115)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C115)*($E$5:$E$504=E115)*(($D$5:$D$504=D115)*(D115&lt;&gt;"")+($B$5:$B$504=B115)*(B115&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B115="",C115="",D115="",E115="",F115=""),"",IF(OR(B115="",C115="",E115=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E115)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H115&lt;&gt;0,F115=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G115&lt;&gt;0,F115=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F115&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F115)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C115)*($E$5:$E$504=E115)*(($D$5:$D$504=D115)*(D115&lt;&gt;"")+($B$5:$B$504=B115)*(B115&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C115="Оплата",K115&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E115)&gt;0,ROUND(E115-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J115" s="5">
         <f>IF(AND(B115="",C115="",E115=""),"",SUM($G$5:G115))</f>
         <v/>
       </c>
+      <c r="K115" s="8" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
@@ -3595,13 +3712,14 @@
         <v/>
       </c>
       <c r="I116" s="6">
-        <f>IF(AND(B116="",C116="",D116="",E116="",F116=""),"",IF(OR(B116="",C116="",E116=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E116)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H116&lt;&gt;0,F116=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G116&lt;&gt;0,F116=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F116&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F116)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C116)*($E$5:$E$504=E116)*(($D$5:$D$504=D116)*(D116&lt;&gt;"")+($B$5:$B$504=B116)*(B116&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B116="",C116="",D116="",E116="",F116=""),"",IF(OR(B116="",C116="",E116=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E116)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H116&lt;&gt;0,F116=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G116&lt;&gt;0,F116=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F116&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F116)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C116)*($E$5:$E$504=E116)*(($D$5:$D$504=D116)*(D116&lt;&gt;"")+($B$5:$B$504=B116)*(B116&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C116="Оплата",K116&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E116)&gt;0,ROUND(E116-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J116" s="5">
         <f>IF(AND(B116="",C116="",E116=""),"",SUM($G$5:G116))</f>
         <v/>
       </c>
+      <c r="K116" s="8" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -3621,13 +3739,14 @@
         <v/>
       </c>
       <c r="I117" s="6">
-        <f>IF(AND(B117="",C117="",D117="",E117="",F117=""),"",IF(OR(B117="",C117="",E117=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E117)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H117&lt;&gt;0,F117=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G117&lt;&gt;0,F117=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F117&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F117)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C117)*($E$5:$E$504=E117)*(($D$5:$D$504=D117)*(D117&lt;&gt;"")+($B$5:$B$504=B117)*(B117&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B117="",C117="",D117="",E117="",F117=""),"",IF(OR(B117="",C117="",E117=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E117)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H117&lt;&gt;0,F117=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G117&lt;&gt;0,F117=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F117&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F117)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C117)*($E$5:$E$504=E117)*(($D$5:$D$504=D117)*(D117&lt;&gt;"")+($B$5:$B$504=B117)*(B117&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C117="Оплата",K117&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E117)&gt;0,ROUND(E117-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J117" s="5">
         <f>IF(AND(B117="",C117="",E117=""),"",SUM($G$5:G117))</f>
         <v/>
       </c>
+      <c r="K117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n">
@@ -3647,13 +3766,14 @@
         <v/>
       </c>
       <c r="I118" s="6">
-        <f>IF(AND(B118="",C118="",D118="",E118="",F118=""),"",IF(OR(B118="",C118="",E118=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E118)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H118&lt;&gt;0,F118=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G118&lt;&gt;0,F118=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F118&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F118)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C118)*($E$5:$E$504=E118)*(($D$5:$D$504=D118)*(D118&lt;&gt;"")+($B$5:$B$504=B118)*(B118&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B118="",C118="",D118="",E118="",F118=""),"",IF(OR(B118="",C118="",E118=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E118)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H118&lt;&gt;0,F118=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G118&lt;&gt;0,F118=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F118&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F118)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C118)*($E$5:$E$504=E118)*(($D$5:$D$504=D118)*(D118&lt;&gt;"")+($B$5:$B$504=B118)*(B118&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C118="Оплата",K118&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E118)&gt;0,ROUND(E118-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J118" s="5">
         <f>IF(AND(B118="",C118="",E118=""),"",SUM($G$5:G118))</f>
         <v/>
       </c>
+      <c r="K118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -3673,13 +3793,14 @@
         <v/>
       </c>
       <c r="I119" s="6">
-        <f>IF(AND(B119="",C119="",D119="",E119="",F119=""),"",IF(OR(B119="",C119="",E119=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E119)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H119&lt;&gt;0,F119=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G119&lt;&gt;0,F119=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F119&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F119)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C119)*($E$5:$E$504=E119)*(($D$5:$D$504=D119)*(D119&lt;&gt;"")+($B$5:$B$504=B119)*(B119&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B119="",C119="",D119="",E119="",F119=""),"",IF(OR(B119="",C119="",E119=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E119)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H119&lt;&gt;0,F119=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G119&lt;&gt;0,F119=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F119&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F119)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C119)*($E$5:$E$504=E119)*(($D$5:$D$504=D119)*(D119&lt;&gt;"")+($B$5:$B$504=B119)*(B119&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C119="Оплата",K119&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E119)&gt;0,ROUND(E119-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J119" s="5">
         <f>IF(AND(B119="",C119="",E119=""),"",SUM($G$5:G119))</f>
         <v/>
       </c>
+      <c r="K119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
@@ -3699,13 +3820,14 @@
         <v/>
       </c>
       <c r="I120" s="6">
-        <f>IF(AND(B120="",C120="",D120="",E120="",F120=""),"",IF(OR(B120="",C120="",E120=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E120)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H120&lt;&gt;0,F120=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G120&lt;&gt;0,F120=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F120&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F120)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C120)*($E$5:$E$504=E120)*(($D$5:$D$504=D120)*(D120&lt;&gt;"")+($B$5:$B$504=B120)*(B120&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B120="",C120="",D120="",E120="",F120=""),"",IF(OR(B120="",C120="",E120=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E120)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H120&lt;&gt;0,F120=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G120&lt;&gt;0,F120=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F120&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F120)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C120)*($E$5:$E$504=E120)*(($D$5:$D$504=D120)*(D120&lt;&gt;"")+($B$5:$B$504=B120)*(B120&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию",IF(AND(C120="Оплата",K120&lt;&gt;"Отдельный платёж — не сам аванс (сверено с выпиской банка)",OR(COUNTIFS($C$5:$C$504,"Зачёт аванса по договору",$E$5:$E$504,E120)&gt;0,ROUND(E120-$M$6,2)=0)),"БЛОК: нужна сверка с авансом — сумма этой оплаты равна зачёту аванса. Если это сам авансовый платёж, удалите строку: аванс учитывается один раз, зачётом. Если это отдельный платёж, сверьте его с выпиской банка и выберите в колонке K «Отдельный платёж — не сам аванс (сверено с выпиской банка)»","ок"))))))))</f>
         <v/>
       </c>
       <c r="J120" s="5">
         <f>IF(AND(B120="",C120="",E120=""),"",SUM($G$5:G120))</f>
         <v/>
       </c>
+      <c r="K120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
@@ -3725,13 +3847,14 @@
         <v/>
       </c>
       <c r="I121" s="6">
-        <f>IF(AND(B121="",C121="",D121="",E121="",F121=""),"",IF(OR(B121="",C121="",E121=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E121)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H121&lt;&gt;0,F121=""),"БЛОК: у спорной операции не указан акт — укажите акт, к которому относится удержание, зачёт, неустойка или допработы: без этого бесспорную часть по акту не отделить",IF(AND(G121&lt;&gt;0,F121=""),"БЛОК: не указан акт — платёж не отнесён к конкретному акту. Распределите его документально (назначение платежа, соглашение, письмо) и укажите акт: без этого долг на первый день просрочки и проценты посчитать нельзя",IF(AND(F121&lt;&gt;"",COUNTIF('Долг по актам'!$B$5:$B$34,F121)=0),"БЛОК: такого акта нет на листе «Долг по актам» — добавьте акт или исправьте идентификатор",IF(SUMPRODUCT((($C$5:$C$504="Оплата")+($C$5:$C$504="Зачёт аванса по договору")&gt;0)*($C$5:$C$504&lt;&gt;C121)*($E$5:$E$504=E121)*(($D$5:$D$504=D121)*(D121&lt;&gt;"")+($B$5:$B$504=B121)*(B121&lt;&gt;"")&gt;0))&gt;0,"БЛОК: двойной учёт аванса — эта сумма введена и как «Оплата», и как «Зачёт аванса по договору» с тем же документом или той же датой. Аванс, зачтённый в акт, учитывается один раз: оставьте одну операцию","ок")))))))</f>
+        <f>IF(AND(B121="",C121="",D121="",E121="",F121=""),"",IF(OR(B121="",C121="",E121=""),"БЛОК: нужны дата, тип операции и сумма",IF(N(E121)&lt;=0,"БЛОК: сумма должна быть больше нуля",IF(AND(H121&lt;&gt;0,F121=""),"БЛОК: у спорной операции не указа